--- a/Mouse 내역.xlsx
+++ b/Mouse 내역.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\heung\OneDrive\바탕 화면\동물실\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7027D2B8-8A85-4BC3-B8D9-9E4ECFAD5FB9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0FDA010-BDB2-4786-8347-9E4E0569BA1B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19080" windowHeight="9180" activeTab="1" xr2:uid="{5A73A69A-2AFB-4F3E-AC64-070DD7700CB2}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19080" windowHeight="9180" xr2:uid="{5A73A69A-2AFB-4F3E-AC64-070DD7700CB2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="122">
   <si>
     <t>Strain</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -111,18 +111,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Cre/+, f/+</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>+/+, f/+</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Cre/+, +/+</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>CD36 flox</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -131,14 +119,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>LysM Cre, Cd36 flox</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tmem119 Cre-ERT2, Cd36 flox</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>+/+, f/f</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -162,14 +142,6 @@
     <t>5F</t>
   </si>
   <si>
-    <t>Tmem119 Cre-ERT2, Cd36 flox</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tmem119 Cre-ERT2, Tsg101 flox</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>R1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -186,10 +158,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Cre/Cre, f/f</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>F</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -218,10 +186,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Weaned, or Provisino date</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>P1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -349,10 +313,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Exp. 1-8-1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>비고</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -486,6 +446,61 @@
   </si>
   <si>
     <t>E1.2.F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C2.B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Antibiotics Corn oil</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DW Corn oil</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Antibiotics Tamoxifen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DW Tamoxifen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Weaned; or Provisino date</t>
+  </si>
+  <si>
+    <t>Tmem119 Cre-ERT2; Cd36 flox</t>
+  </si>
+  <si>
+    <t>Cre/+; f/+</t>
+  </si>
+  <si>
+    <t>LysM Cre; Cd36 flox</t>
+  </si>
+  <si>
+    <t>Tmem119 Cre-ERT2; Cd36 flox</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tmem119 Cre-ERT2; Tsg101 flox</t>
+  </si>
+  <si>
+    <t>+/+; f/+</t>
+  </si>
+  <si>
+    <t>Cre/+; +/+</t>
+  </si>
+  <si>
+    <t>+/+; f/f</t>
+  </si>
+  <si>
+    <t>Cre/Cre; f/f</t>
+  </si>
+  <si>
+    <t>Exp. 1-7-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -717,7 +732,7 @@
       <xdr:row>6</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="3912225" cy="3249223"/>
+    <xdr:ext cx="3840860" cy="2273571"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="TextBox 1">
@@ -732,7 +747,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1381125" y="1428750"/>
-          <a:ext cx="3912225" cy="3249223"/>
+          <a:ext cx="3840860" cy="2273571"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -772,49 +787,11 @@
         <a:p>
           <a:r>
             <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
-            <a:t>B1.B cage </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1"/>
-            <a:t>없애기</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
-            <a:t>A1.B cage </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1"/>
-            <a:t>없애기</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
-            <a:t>A1.2F cage </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1"/>
-            <a:t>없애기</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
             <a:t>A2.B breader</a:t>
           </a:r>
           <a:r>
             <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1"/>
             <a:t>에 </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
-            <a:t>male </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1"/>
-            <a:t>없애고 </a:t>
           </a:r>
           <a:r>
             <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
@@ -899,44 +876,6 @@
             <a:t> Cd36-flox</a:t>
           </a:r>
           <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
-            <a:t>C1.B</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1"/>
-            <a:t>의 </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
-            <a:t>Male </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1"/>
-            <a:t>한마리 없애고  </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
-            <a:t>C1.2M</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1"/>
-            <a:t>의 </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
-            <a:t>L1 </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1"/>
-            <a:t>넣음 </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
-            <a:t>(C2.B)</a:t>
-          </a:r>
         </a:p>
         <a:p>
           <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
@@ -1318,13 +1257,14 @@
     <col min="5" max="5" width="7.625" customWidth="1"/>
     <col min="6" max="6" width="12.5" style="5" customWidth="1"/>
     <col min="7" max="7" width="11.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="9" customWidth="1"/>
     <col min="10" max="10" width="11.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.25" customWidth="1"/>
+    <col min="11" max="11" width="8.25" hidden="1" customWidth="1"/>
     <col min="12" max="12" width="6.375" customWidth="1"/>
-    <col min="14" max="14" width="13.125" style="2" customWidth="1"/>
+    <col min="14" max="14" width="13.125" style="2" hidden="1" customWidth="1"/>
     <col min="15" max="15" width="12.75" style="2" customWidth="1"/>
     <col min="16" max="16" width="13.25" customWidth="1"/>
-    <col min="17" max="17" width="13" customWidth="1"/>
+    <col min="17" max="17" width="19.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:17" x14ac:dyDescent="0.3">
@@ -1335,7 +1275,7 @@
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>6</v>
@@ -1353,7 +1293,7 @@
         <v>9</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>48</v>
+        <v>111</v>
       </c>
       <c r="K1" s="8" t="s">
         <v>14</v>
@@ -1362,7 +1302,7 @@
         <v>3</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="N1" s="3" t="s">
         <v>18</v>
@@ -1371,35 +1311,35 @@
         <v>17</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="2" spans="2:17" x14ac:dyDescent="0.3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>112</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="10" t="s">
-        <v>21</v>
+      <c r="F2" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="G2" s="2">
         <v>45135</v>
       </c>
       <c r="H2" s="4">
         <f ca="1">IF(QUOTIENT(_xlfn.DAYS(TODAY(),G2), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),G2), 7), "-")</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I2" s="4">
         <f ca="1">IF(_xlfn.DAYS(TODAY(),G2)&lt;10000, _xlfn.DAYS(TODAY(),G2), "-")</f>
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="K2" s="4" t="str">
         <f t="shared" ref="K2:K31" si="0">IF(_xlfn.DAYS(J2,G2)&gt;0, _xlfn.DAYS(J2,G2), "-")</f>
@@ -1409,34 +1349,36 @@
         <v>11</v>
       </c>
       <c r="M2" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
+      <c r="O2" s="7">
+        <v>45299</v>
+      </c>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>115</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="G3" s="2">
         <v>45135</v>
       </c>
       <c r="H3" s="4">
         <f t="shared" ref="H3:H65" ca="1" si="1">IF(QUOTIENT(_xlfn.DAYS(TODAY(),G3), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),G3), 7), "-")</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I3" s="4">
         <f t="shared" ref="I3:I31" ca="1" si="2">IF(_xlfn.DAYS(TODAY(),G3)&lt;10000, _xlfn.DAYS(TODAY(),G3), "-")</f>
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="K3" s="4" t="str">
         <f t="shared" si="0"/>
@@ -1446,7 +1388,7 @@
         <v>13</v>
       </c>
       <c r="M3" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="N3" s="7"/>
       <c r="O3" s="7"/>
@@ -1456,24 +1398,24 @@
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>112</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="G4" s="2">
         <v>45135</v>
       </c>
       <c r="H4" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I4" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="K4" s="4" t="str">
         <f t="shared" si="0"/>
@@ -1483,7 +1425,7 @@
         <v>13</v>
       </c>
       <c r="M4" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="N4" s="7"/>
       <c r="O4" s="7"/>
@@ -1493,7 +1435,7 @@
         <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>112</v>
       </c>
       <c r="D5">
         <v>871</v>
@@ -1502,18 +1444,18 @@
         <v>16</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="G5" s="2">
         <v>45266</v>
       </c>
       <c r="H5" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I5" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="J5" s="2">
         <v>45293</v>
@@ -1523,10 +1465,10 @@
         <v>27</v>
       </c>
       <c r="L5" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="M5" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="N5" s="7"/>
       <c r="O5" s="7"/>
@@ -1536,7 +1478,7 @@
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>112</v>
       </c>
       <c r="D6">
         <v>872</v>
@@ -1545,18 +1487,18 @@
         <v>16</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="G6" s="2">
         <v>45266</v>
       </c>
       <c r="H6" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I6" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="J6" s="2">
         <v>45293</v>
@@ -1566,10 +1508,10 @@
         <v>27</v>
       </c>
       <c r="L6" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="M6" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="N6" s="7"/>
       <c r="O6" s="7"/>
@@ -1579,7 +1521,7 @@
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>112</v>
       </c>
       <c r="D7">
         <v>873</v>
@@ -1588,18 +1530,18 @@
         <v>16</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="G7" s="2">
         <v>45266</v>
       </c>
       <c r="H7" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I7" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="J7" s="2">
         <v>45293</v>
@@ -1609,10 +1551,10 @@
         <v>27</v>
       </c>
       <c r="L7" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="M7" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="N7" s="7"/>
       <c r="O7" s="7"/>
@@ -1622,7 +1564,7 @@
         <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>112</v>
       </c>
       <c r="D8">
         <v>874</v>
@@ -1631,18 +1573,18 @@
         <v>15</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="G8" s="2">
         <v>45266</v>
       </c>
       <c r="H8" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I8" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="J8" s="2">
         <v>45293</v>
@@ -1652,10 +1594,10 @@
         <v>27</v>
       </c>
       <c r="L8" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="M8" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="N8" s="7"/>
       <c r="O8" s="7"/>
@@ -1665,7 +1607,7 @@
         <v>5</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>112</v>
       </c>
       <c r="D9">
         <v>921</v>
@@ -1674,18 +1616,18 @@
         <v>15</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="G9" s="2">
         <v>45266</v>
       </c>
       <c r="H9" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I9" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="J9" s="2">
         <v>45293</v>
@@ -1695,10 +1637,10 @@
         <v>27</v>
       </c>
       <c r="L9" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="M9" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="N9" s="7"/>
       <c r="O9" s="7"/>
@@ -1708,7 +1650,7 @@
         <v>5</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>112</v>
       </c>
       <c r="D10">
         <v>922</v>
@@ -1717,18 +1659,18 @@
         <v>15</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="G10" s="2">
         <v>45266</v>
       </c>
       <c r="H10" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I10" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="J10" s="2">
         <v>45293</v>
@@ -1738,10 +1680,10 @@
         <v>27</v>
       </c>
       <c r="L10" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="M10" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="N10" s="7"/>
       <c r="O10" s="7"/>
@@ -1751,7 +1693,7 @@
         <v>5</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>112</v>
       </c>
       <c r="D11">
         <v>923</v>
@@ -1760,18 +1702,18 @@
         <v>15</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="G11" s="2">
         <v>45266</v>
       </c>
       <c r="H11" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I11" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="J11" s="2">
         <v>45293</v>
@@ -1781,37 +1723,37 @@
         <v>27</v>
       </c>
       <c r="L11" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="M11" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="N11" s="7"/>
       <c r="O11" s="7"/>
     </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>5</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>112</v>
       </c>
       <c r="E12" t="s">
         <v>7</v>
       </c>
-      <c r="F12" s="10" t="s">
-        <v>21</v>
+      <c r="F12" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="G12" s="2">
         <v>45135</v>
       </c>
       <c r="H12" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I12" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="K12" s="4" t="str">
         <f t="shared" si="0"/>
@@ -1821,23 +1763,25 @@
         <v>10</v>
       </c>
       <c r="M12" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="N12" s="7"/>
-      <c r="O12" s="7"/>
-    </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="O12" s="7">
+        <v>45299</v>
+      </c>
+    </row>
+    <row r="13" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>5</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>112</v>
       </c>
       <c r="E13" t="s">
         <v>7</v>
       </c>
-      <c r="F13" s="10" t="s">
-        <v>21</v>
+      <c r="F13" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="H13" s="4" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -1855,23 +1799,25 @@
         <v>12</v>
       </c>
       <c r="M13" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="N13" s="7"/>
-      <c r="O13" s="7"/>
-    </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="O13" s="7">
+        <v>45299</v>
+      </c>
+    </row>
+    <row r="14" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>5</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>112</v>
       </c>
       <c r="E14" t="s">
         <v>7</v>
       </c>
-      <c r="F14" s="10" t="s">
-        <v>21</v>
+      <c r="F14" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="H14" s="4" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -1889,17 +1835,19 @@
         <v>12</v>
       </c>
       <c r="M14" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="N14" s="7"/>
-      <c r="O14" s="7"/>
+      <c r="O14" s="7">
+        <v>45299</v>
+      </c>
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>5</v>
       </c>
       <c r="C15" t="s">
-        <v>27</v>
+        <v>112</v>
       </c>
       <c r="D15">
         <v>972</v>
@@ -1908,18 +1856,18 @@
         <v>7</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="G15" s="2">
         <v>45047</v>
       </c>
       <c r="H15" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I15" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="K15" s="4" t="str">
         <f t="shared" si="0"/>
@@ -1929,7 +1877,7 @@
         <v>11</v>
       </c>
       <c r="M15" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="N15" s="7"/>
       <c r="O15" s="7"/>
@@ -1939,7 +1887,7 @@
         <v>5</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>112</v>
       </c>
       <c r="D16">
         <v>973</v>
@@ -1948,18 +1896,18 @@
         <v>7</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="G16" s="2">
         <v>45047</v>
       </c>
       <c r="H16" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I16" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="K16" s="4" t="str">
         <f t="shared" si="0"/>
@@ -1969,17 +1917,17 @@
         <v>11</v>
       </c>
       <c r="M16" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="N16" s="7"/>
       <c r="O16" s="7"/>
     </row>
-    <row r="17" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>5</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>112</v>
       </c>
       <c r="D17">
         <v>974</v>
@@ -1988,18 +1936,18 @@
         <v>7</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="G17" s="2">
         <v>45047</v>
       </c>
       <c r="H17" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I17" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="K17" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2009,15 +1957,15 @@
         <v>11</v>
       </c>
       <c r="M17" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="18" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>5</v>
       </c>
       <c r="C18" t="s">
-        <v>27</v>
+        <v>112</v>
       </c>
       <c r="D18">
         <v>975</v>
@@ -2026,18 +1974,18 @@
         <v>7</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="G18" s="2">
         <v>45047</v>
       </c>
       <c r="H18" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I18" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="K18" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2047,15 +1995,15 @@
         <v>11</v>
       </c>
       <c r="M18" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>5</v>
       </c>
       <c r="C19" t="s">
-        <v>27</v>
+        <v>112</v>
       </c>
       <c r="D19">
         <v>970</v>
@@ -2064,18 +2012,18 @@
         <v>7</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="G19" s="2">
         <v>45047</v>
       </c>
       <c r="H19" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I19" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="K19" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2085,32 +2033,32 @@
         <v>11</v>
       </c>
       <c r="M19" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="20" spans="2:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>5</v>
       </c>
       <c r="C20" t="s">
-        <v>27</v>
+        <v>112</v>
       </c>
       <c r="E20" t="s">
         <v>7</v>
       </c>
-      <c r="F20" s="10" t="s">
-        <v>21</v>
+      <c r="F20" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="G20" s="2">
         <v>45091</v>
       </c>
       <c r="H20" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I20" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="K20" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2120,21 +2068,24 @@
         <v>11</v>
       </c>
       <c r="M20" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+      <c r="O20" s="2">
+        <v>45299</v>
+      </c>
+    </row>
+    <row r="21" spans="2:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>5</v>
       </c>
       <c r="C21" t="s">
-        <v>27</v>
+        <v>112</v>
       </c>
       <c r="E21" t="s">
         <v>7</v>
       </c>
-      <c r="F21" s="10" t="s">
-        <v>22</v>
+      <c r="F21" s="1" t="s">
+        <v>117</v>
       </c>
       <c r="H21" s="4" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -2152,32 +2103,35 @@
         <v>13</v>
       </c>
       <c r="M21" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="22" spans="2:13" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+      <c r="O21" s="2">
+        <v>45299</v>
+      </c>
+    </row>
+    <row r="22" spans="2:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>5</v>
       </c>
       <c r="C22" t="s">
-        <v>27</v>
+        <v>112</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>23</v>
+        <v>118</v>
       </c>
       <c r="G22" s="2">
         <v>45115</v>
       </c>
       <c r="H22" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I22" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="J22" s="2">
         <v>45112</v>
@@ -2190,32 +2144,35 @@
         <v>13</v>
       </c>
       <c r="M22" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="23" spans="2:13" x14ac:dyDescent="0.3">
+        <v>56</v>
+      </c>
+      <c r="O22" s="2">
+        <v>45299</v>
+      </c>
+    </row>
+    <row r="23" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>5</v>
       </c>
       <c r="C23" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E23" t="s">
         <v>7</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G23" s="2">
         <v>45154</v>
       </c>
       <c r="H23" s="4">
         <f ca="1">IF(QUOTIENT(_xlfn.DAYS(TODAY(),G23), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),G23), 7), "-")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I23" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="J23" s="2">
         <v>45176</v>
@@ -2228,32 +2185,32 @@
         <v>11</v>
       </c>
       <c r="M23" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="24" spans="2:13" x14ac:dyDescent="0.3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="24" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>5</v>
       </c>
       <c r="C24" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E24" t="s">
         <v>7</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G24" s="2">
         <v>45154</v>
       </c>
       <c r="H24" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I24" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="J24" s="2">
         <v>45176</v>
@@ -2266,32 +2223,32 @@
         <v>11</v>
       </c>
       <c r="M24" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="25" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>5</v>
       </c>
       <c r="C25" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E25" t="s">
         <v>7</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G25" s="2">
         <v>45154</v>
       </c>
       <c r="H25" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I25" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="J25" s="2">
         <v>45176</v>
@@ -2304,32 +2261,32 @@
         <v>11</v>
       </c>
       <c r="M25" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="26" spans="2:13" x14ac:dyDescent="0.3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="26" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>5</v>
       </c>
       <c r="C26" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E26" t="s">
         <v>7</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G26" s="2">
         <v>45154</v>
       </c>
       <c r="H26" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I26" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="J26" s="2">
         <v>45176</v>
@@ -2342,32 +2299,32 @@
         <v>11</v>
       </c>
       <c r="M26" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="27" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>5</v>
       </c>
       <c r="C27" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E27" t="s">
         <v>7</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G27" s="2">
         <v>45154</v>
       </c>
       <c r="H27" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I27" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="J27" s="2">
         <v>45176</v>
@@ -2380,32 +2337,32 @@
         <v>11</v>
       </c>
       <c r="M27" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="28" spans="2:13" x14ac:dyDescent="0.3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="28" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>5</v>
       </c>
       <c r="C28" t="s">
-        <v>26</v>
+        <v>114</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>22</v>
+        <v>117</v>
       </c>
       <c r="G28" s="2">
         <v>45203</v>
       </c>
       <c r="H28" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I28" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J28" s="2">
         <v>45229</v>
@@ -2418,32 +2375,32 @@
         <v>11</v>
       </c>
       <c r="M28" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="29" spans="2:13" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="29" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
         <v>5</v>
       </c>
       <c r="C29" t="s">
-        <v>26</v>
+        <v>114</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="G29" s="2">
         <v>45203</v>
       </c>
       <c r="H29" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I29" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J29" s="2">
         <v>45229</v>
@@ -2456,32 +2413,32 @@
         <v>11</v>
       </c>
       <c r="M29" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="30" spans="2:13" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="30" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>5</v>
       </c>
       <c r="C30" t="s">
-        <v>26</v>
+        <v>114</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>22</v>
+        <v>117</v>
       </c>
       <c r="G30" s="2">
         <v>45203</v>
       </c>
       <c r="H30" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I30" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J30" s="2">
         <v>45229</v>
@@ -2494,32 +2451,32 @@
         <v>13</v>
       </c>
       <c r="M30" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="31" spans="2:13" x14ac:dyDescent="0.3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="31" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
         <v>5</v>
       </c>
       <c r="C31" t="s">
-        <v>26</v>
+        <v>114</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>22</v>
+        <v>117</v>
       </c>
       <c r="G31" s="2">
         <v>45203</v>
       </c>
       <c r="H31" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I31" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J31" s="2">
         <v>45229</v>
@@ -2532,32 +2489,32 @@
         <v>13</v>
       </c>
       <c r="M31" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="32" spans="2:13" x14ac:dyDescent="0.3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="32" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
         <v>5</v>
       </c>
       <c r="C32" t="s">
-        <v>26</v>
+        <v>114</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>22</v>
+        <v>117</v>
       </c>
       <c r="G32" s="2">
         <v>45203</v>
       </c>
       <c r="H32" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I32" s="4">
-        <f t="shared" ref="I32:I37" ca="1" si="3">IF(_xlfn.DAYS(TODAY(),G32)&lt;10000, _xlfn.DAYS(TODAY(),G32), "-")</f>
-        <v>93</v>
+        <f t="shared" ref="I32:I38" ca="1" si="3">IF(_xlfn.DAYS(TODAY(),G32)&lt;10000, _xlfn.DAYS(TODAY(),G32), "-")</f>
+        <v>103</v>
       </c>
       <c r="J32" s="2">
         <v>45229</v>
@@ -2570,21 +2527,21 @@
         <v>13</v>
       </c>
       <c r="M32" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
         <v>5</v>
       </c>
       <c r="C33" t="s">
-        <v>26</v>
+        <v>114</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
       </c>
-      <c r="F33" s="10" t="s">
-        <v>23</v>
+      <c r="F33" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="H33" s="4" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -2602,53 +2559,65 @@
         <v>11</v>
       </c>
       <c r="M33" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.3">
+        <v>60</v>
+      </c>
+      <c r="O33" s="2">
+        <v>45299</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
         <v>5</v>
       </c>
       <c r="C34" t="s">
+        <v>114</v>
+      </c>
+      <c r="D34" t="s">
+        <v>25</v>
+      </c>
+      <c r="E34" t="s">
+        <v>8</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G34" s="2">
+        <v>45231</v>
+      </c>
+      <c r="H34" s="4">
+        <f ca="1">IF(QUOTIENT(_xlfn.DAYS(TODAY(),G34), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),G34), 7), "-")</f>
+        <v>10</v>
+      </c>
+      <c r="I34" s="4">
+        <f ca="1">IF(_xlfn.DAYS(TODAY(),G34)&lt;10000, _xlfn.DAYS(TODAY(),G34), "-")</f>
+        <v>75</v>
+      </c>
+      <c r="J34" s="2">
+        <v>45257</v>
+      </c>
+      <c r="K34" s="4">
+        <f>IF(_xlfn.DAYS(J34,G34)&gt;0, _xlfn.DAYS(J34,G34), "-")</f>
         <v>26</v>
       </c>
-      <c r="E34" t="s">
-        <v>8</v>
-      </c>
-      <c r="F34" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="H34" s="4" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>-</v>
-      </c>
-      <c r="I34" s="4" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>-</v>
-      </c>
-      <c r="K34" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v>-</v>
-      </c>
       <c r="L34" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="M34" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.3">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
         <v>5</v>
       </c>
       <c r="C35" t="s">
-        <v>26</v>
+        <v>114</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>28</v>
+        <v>119</v>
       </c>
       <c r="H35" s="4" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -2666,76 +2635,67 @@
         <v>13</v>
       </c>
       <c r="M35" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.3">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="36" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B36" t="s">
         <v>5</v>
       </c>
       <c r="C36" t="s">
-        <v>26</v>
-      </c>
-      <c r="D36" t="s">
-        <v>29</v>
+        <v>114</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
       </c>
-      <c r="F36" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="G36" s="2">
-        <v>45231</v>
-      </c>
-      <c r="H36" s="4">
+      <c r="F36" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="H36" s="4" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="I36" s="4">
+        <v>-</v>
+      </c>
+      <c r="I36" s="4" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>65</v>
-      </c>
-      <c r="J36" s="2">
-        <v>45257</v>
-      </c>
-      <c r="K36" s="4">
+        <v>-</v>
+      </c>
+      <c r="K36" s="4" t="str">
         <f t="shared" si="4"/>
-        <v>26</v>
+        <v>-</v>
       </c>
       <c r="L36" t="s">
         <v>13</v>
       </c>
       <c r="M36" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.3">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B37" t="s">
         <v>5</v>
       </c>
       <c r="C37" t="s">
-        <v>26</v>
+        <v>114</v>
       </c>
       <c r="D37" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="G37" s="2">
         <v>45231</v>
       </c>
       <c r="H37" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I37" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="J37" s="2">
         <v>45257</v>
@@ -2748,35 +2708,35 @@
         <v>13</v>
       </c>
       <c r="M37" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="38" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B38" t="s">
         <v>5</v>
       </c>
       <c r="C38" t="s">
-        <v>26</v>
+        <v>114</v>
       </c>
       <c r="D38" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="G38" s="2">
         <v>45231</v>
       </c>
       <c r="H38" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I38" s="4">
-        <f t="shared" ref="I38:I41" ca="1" si="5">IF(_xlfn.DAYS(TODAY(),G38)&lt;10000, _xlfn.DAYS(TODAY(),G38), "-")</f>
-        <v>65</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>75</v>
       </c>
       <c r="J38" s="2">
         <v>45257</v>
@@ -2789,35 +2749,35 @@
         <v>13</v>
       </c>
       <c r="M38" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B39" t="s">
         <v>5</v>
       </c>
       <c r="C39" t="s">
+        <v>114</v>
+      </c>
+      <c r="D39" t="s">
         <v>26</v>
       </c>
-      <c r="D39" t="s">
-        <v>29</v>
-      </c>
       <c r="E39" t="s">
         <v>8</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="G39" s="2">
         <v>45231</v>
       </c>
       <c r="H39" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I39" s="4">
-        <f t="shared" ca="1" si="5"/>
-        <v>65</v>
+        <f t="shared" ref="I39:I41" ca="1" si="5">IF(_xlfn.DAYS(TODAY(),G39)&lt;10000, _xlfn.DAYS(TODAY(),G39), "-")</f>
+        <v>75</v>
       </c>
       <c r="J39" s="2">
         <v>45257</v>
@@ -2827,38 +2787,38 @@
         <v>26</v>
       </c>
       <c r="L39" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M39" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B40" t="s">
         <v>5</v>
       </c>
       <c r="C40" t="s">
-        <v>26</v>
+        <v>114</v>
       </c>
       <c r="D40" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E40" t="s">
         <v>8</v>
       </c>
-      <c r="F40" s="9" t="s">
-        <v>107</v>
+      <c r="F40" s="5" t="s">
+        <v>96</v>
       </c>
       <c r="G40" s="2">
         <v>45231</v>
       </c>
       <c r="H40" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I40" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="J40" s="2">
         <v>45257</v>
@@ -2871,35 +2831,35 @@
         <v>11</v>
       </c>
       <c r="M40" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B41" t="s">
         <v>5</v>
       </c>
       <c r="C41" t="s">
+        <v>114</v>
+      </c>
+      <c r="D41" t="s">
         <v>26</v>
       </c>
-      <c r="D41" t="s">
-        <v>31</v>
-      </c>
       <c r="E41" t="s">
         <v>8</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="G41" s="2">
         <v>45231</v>
       </c>
       <c r="H41" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I41" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="J41" s="2">
         <v>45257</v>
@@ -2912,15 +2872,15 @@
         <v>11</v>
       </c>
       <c r="M41" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B42" t="s">
         <v>5</v>
       </c>
       <c r="C42" t="s">
-        <v>34</v>
+        <v>112</v>
       </c>
       <c r="D42">
         <v>798</v>
@@ -2929,18 +2889,18 @@
         <v>8</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>23</v>
+        <v>118</v>
       </c>
       <c r="G42" s="2">
         <v>45135</v>
       </c>
       <c r="H42" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I42" s="4">
         <f t="shared" ref="I42" ca="1" si="6">IF(_xlfn.DAYS(TODAY(),G42)&lt;10000, _xlfn.DAYS(TODAY(),G42), "-")</f>
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="K42" s="4" t="str">
         <f t="shared" si="4"/>
@@ -2953,12 +2913,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B43" t="s">
         <v>5</v>
       </c>
       <c r="C43" t="s">
-        <v>34</v>
+        <v>112</v>
       </c>
       <c r="D43">
         <v>799</v>
@@ -2967,18 +2927,18 @@
         <v>8</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="G43" s="2">
         <v>45135</v>
       </c>
       <c r="H43" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I43" s="4">
         <f t="shared" ref="I43:I91" ca="1" si="7">IF(_xlfn.DAYS(TODAY(),G43)&lt;10000, _xlfn.DAYS(TODAY(),G43), "-")</f>
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="K43" s="4" t="str">
         <f t="shared" si="4"/>
@@ -2991,32 +2951,32 @@
         <v>19</v>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B44" t="s">
         <v>5</v>
       </c>
       <c r="C44" t="s">
-        <v>26</v>
+        <v>114</v>
       </c>
       <c r="D44">
         <v>815</v>
       </c>
       <c r="E44" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F44" s="12" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="G44" s="2">
         <v>45267</v>
       </c>
       <c r="H44" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I44" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="J44" s="2">
         <v>45293</v>
@@ -3026,38 +2986,38 @@
         <v>26</v>
       </c>
       <c r="L44" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="M44" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.3">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B45" t="s">
         <v>5</v>
       </c>
       <c r="C45" t="s">
-        <v>26</v>
+        <v>114</v>
       </c>
       <c r="D45">
         <v>816</v>
       </c>
       <c r="E45" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F45" s="12" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="G45" s="2">
         <v>45267</v>
       </c>
       <c r="H45" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I45" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="J45" s="2">
         <v>45293</v>
@@ -3067,38 +3027,38 @@
         <v>26</v>
       </c>
       <c r="L45" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="M45" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.3">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B46" t="s">
         <v>5</v>
       </c>
       <c r="C46" t="s">
-        <v>26</v>
+        <v>114</v>
       </c>
       <c r="D46">
         <v>817</v>
       </c>
       <c r="E46" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="G46" s="2">
         <v>45267</v>
       </c>
       <c r="H46" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I46" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="J46" s="2">
         <v>45293</v>
@@ -3108,38 +3068,38 @@
         <v>26</v>
       </c>
       <c r="L46" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="M46" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.3">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B47" t="s">
         <v>5</v>
       </c>
       <c r="C47" t="s">
-        <v>26</v>
+        <v>114</v>
       </c>
       <c r="D47">
         <v>819</v>
       </c>
       <c r="E47" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="G47" s="2">
         <v>45267</v>
       </c>
       <c r="H47" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I47" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="J47" s="2">
         <v>45293</v>
@@ -3149,38 +3109,38 @@
         <v>26</v>
       </c>
       <c r="L47" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="M47" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.3">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B48" t="s">
         <v>5</v>
       </c>
       <c r="C48" t="s">
-        <v>26</v>
+        <v>114</v>
       </c>
       <c r="D48">
         <v>820</v>
       </c>
       <c r="E48" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="G48" s="2">
         <v>45271</v>
       </c>
       <c r="H48" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I48" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="J48" s="2">
         <v>45293</v>
@@ -3190,10 +3150,10 @@
         <v>22</v>
       </c>
       <c r="L48" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="M48" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
     </row>
     <row r="49" spans="2:13" x14ac:dyDescent="0.3">
@@ -3201,27 +3161,27 @@
         <v>5</v>
       </c>
       <c r="C49" t="s">
-        <v>26</v>
+        <v>114</v>
       </c>
       <c r="D49">
         <v>821</v>
       </c>
       <c r="E49" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="G49" s="2">
         <v>45267</v>
       </c>
       <c r="H49" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I49" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="J49" s="2">
         <v>45293</v>
@@ -3231,10 +3191,10 @@
         <v>26</v>
       </c>
       <c r="L49" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="M49" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
     </row>
     <row r="50" spans="2:13" x14ac:dyDescent="0.3">
@@ -3242,27 +3202,27 @@
         <v>5</v>
       </c>
       <c r="C50" t="s">
-        <v>26</v>
+        <v>114</v>
       </c>
       <c r="D50">
         <v>822</v>
       </c>
       <c r="E50" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="G50" s="2">
         <v>45267</v>
       </c>
       <c r="H50" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I50" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="J50" s="2">
         <v>45293</v>
@@ -3272,10 +3232,10 @@
         <v>26</v>
       </c>
       <c r="L50" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="M50" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
     </row>
     <row r="51" spans="2:13" x14ac:dyDescent="0.3">
@@ -3283,27 +3243,27 @@
         <v>5</v>
       </c>
       <c r="C51" t="s">
-        <v>26</v>
+        <v>114</v>
       </c>
       <c r="D51">
         <v>823</v>
       </c>
       <c r="E51" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="G51" s="2">
         <v>45267</v>
       </c>
       <c r="H51" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I51" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="J51" s="2">
         <v>45293</v>
@@ -3313,10 +3273,10 @@
         <v>26</v>
       </c>
       <c r="L51" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="M51" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
     </row>
     <row r="52" spans="2:13" x14ac:dyDescent="0.3">
@@ -3324,27 +3284,27 @@
         <v>5</v>
       </c>
       <c r="C52" t="s">
-        <v>26</v>
+        <v>114</v>
       </c>
       <c r="D52">
         <v>824</v>
       </c>
       <c r="E52" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="G52" s="2">
         <v>45271</v>
       </c>
       <c r="H52" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I52" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="J52" s="2">
         <v>45293</v>
@@ -3354,10 +3314,10 @@
         <v>22</v>
       </c>
       <c r="L52" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="M52" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
     </row>
     <row r="53" spans="2:13" x14ac:dyDescent="0.3">
@@ -3365,27 +3325,27 @@
         <v>5</v>
       </c>
       <c r="C53" t="s">
-        <v>26</v>
+        <v>114</v>
       </c>
       <c r="D53">
         <v>825</v>
       </c>
       <c r="E53" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="G53" s="2">
         <v>45271</v>
       </c>
       <c r="H53" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I53" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="J53" s="2">
         <v>45293</v>
@@ -3395,38 +3355,38 @@
         <v>22</v>
       </c>
       <c r="L53" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="M53" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
     </row>
     <row r="54" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B54" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C54" t="s">
-        <v>35</v>
+        <v>116</v>
       </c>
       <c r="D54" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="E54" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="G54" s="2">
         <v>45208</v>
       </c>
       <c r="H54" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I54" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="J54" s="2">
         <v>45238</v>
@@ -3436,38 +3396,38 @@
         <v>30</v>
       </c>
       <c r="L54" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="M54" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
     </row>
     <row r="55" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B55" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C55" t="s">
-        <v>35</v>
+        <v>116</v>
       </c>
       <c r="D55" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E55" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="G55" s="2">
         <v>45208</v>
       </c>
       <c r="H55" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I55" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="J55" s="2">
         <v>45238</v>
@@ -3477,38 +3437,38 @@
         <v>30</v>
       </c>
       <c r="L55" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="M55" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
     </row>
     <row r="56" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B56" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C56" t="s">
-        <v>35</v>
+        <v>116</v>
       </c>
       <c r="D56" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="E56" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="G56" s="2">
         <v>45208</v>
       </c>
       <c r="H56" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I56" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="J56" s="2">
         <v>45238</v>
@@ -3518,102 +3478,102 @@
         <v>30</v>
       </c>
       <c r="L56" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="M56" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
     </row>
     <row r="57" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B57" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C57" t="s">
-        <v>35</v>
+        <v>116</v>
       </c>
       <c r="E57" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="G57" s="2">
         <v>45000</v>
       </c>
       <c r="H57" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I57" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="K57" s="4" t="str">
         <f t="shared" si="4"/>
         <v>-</v>
       </c>
       <c r="L57" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M57" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
     </row>
     <row r="58" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B58" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C58" t="s">
-        <v>35</v>
+        <v>116</v>
       </c>
       <c r="E58" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F58" s="6" t="s">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="G58" s="2">
         <v>45000</v>
       </c>
       <c r="H58" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I58" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="K58" s="4" t="str">
         <f t="shared" si="4"/>
         <v>-</v>
       </c>
       <c r="L58" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="M58" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
     </row>
     <row r="59" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B59" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C59" t="s">
-        <v>35</v>
+        <v>116</v>
       </c>
       <c r="E59" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G59" s="2">
         <v>45267</v>
       </c>
       <c r="H59" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I59" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="J59" s="2">
         <v>45295</v>
@@ -3623,32 +3583,32 @@
         <v>28</v>
       </c>
       <c r="L59" t="s">
-        <v>112</v>
-      </c>
-      <c r="M59" t="s">
-        <v>114</v>
+        <v>102</v>
+      </c>
+      <c r="M59" s="4" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="60" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B60" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C60" t="s">
-        <v>35</v>
+        <v>116</v>
       </c>
       <c r="E60" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G60" s="2">
         <v>45267</v>
       </c>
       <c r="H60" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I60" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="J60" s="2">
         <v>45295</v>
@@ -3658,32 +3618,32 @@
         <v>28</v>
       </c>
       <c r="L60" t="s">
-        <v>112</v>
-      </c>
-      <c r="M60" t="s">
-        <v>114</v>
+        <v>102</v>
+      </c>
+      <c r="M60" s="4" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="61" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B61" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C61" t="s">
-        <v>35</v>
+        <v>116</v>
       </c>
       <c r="E61" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G61" s="2">
         <v>45267</v>
       </c>
       <c r="H61" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I61" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="J61" s="2">
         <v>45295</v>
@@ -3693,32 +3653,32 @@
         <v>28</v>
       </c>
       <c r="L61" t="s">
-        <v>112</v>
-      </c>
-      <c r="M61" t="s">
-        <v>114</v>
+        <v>102</v>
+      </c>
+      <c r="M61" s="4" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="62" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B62" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C62" t="s">
-        <v>35</v>
+        <v>116</v>
       </c>
       <c r="E62" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G62" s="2">
         <v>45267</v>
       </c>
       <c r="H62" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I62" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="J62" s="2">
         <v>45295</v>
@@ -3728,32 +3688,32 @@
         <v>28</v>
       </c>
       <c r="L62" t="s">
-        <v>112</v>
-      </c>
-      <c r="M62" t="s">
-        <v>114</v>
+        <v>102</v>
+      </c>
+      <c r="M62" s="4" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="63" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B63" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C63" t="s">
-        <v>35</v>
+        <v>116</v>
       </c>
       <c r="E63" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G63" s="2">
         <v>45267</v>
       </c>
       <c r="H63" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I63" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="J63" s="2">
         <v>45295</v>
@@ -3763,32 +3723,32 @@
         <v>28</v>
       </c>
       <c r="L63" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="M63" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
     </row>
     <row r="64" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B64" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C64" t="s">
-        <v>35</v>
+        <v>116</v>
       </c>
       <c r="E64" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G64" s="2">
         <v>45267</v>
       </c>
       <c r="H64" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I64" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="J64" s="2">
         <v>45295</v>
@@ -3798,118 +3758,118 @@
         <v>28</v>
       </c>
       <c r="L64" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="M64" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
     </row>
     <row r="65" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B65" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C65" t="s">
-        <v>35</v>
+        <v>116</v>
       </c>
       <c r="E65" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F65" s="6" t="s">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="G65" s="2">
         <v>45000</v>
       </c>
       <c r="H65" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I65" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="K65" s="4" t="str">
         <f t="shared" si="4"/>
         <v>-</v>
       </c>
       <c r="L65" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="M65" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
     </row>
     <row r="66" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B66" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C66" t="s">
-        <v>35</v>
+        <v>116</v>
       </c>
       <c r="E66" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F66" s="6" t="s">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="G66" s="2">
         <v>45000</v>
       </c>
       <c r="H66" s="4">
         <f t="shared" ref="H66:H91" ca="1" si="8">IF(QUOTIENT(_xlfn.DAYS(TODAY(),G66), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),G66), 7), "-")</f>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I66" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="K66" s="4" t="str">
         <f t="shared" si="4"/>
         <v>-</v>
       </c>
       <c r="L66" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="M66" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
     </row>
     <row r="67" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B67" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C67" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="D67" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="E67" t="s">
         <v>8</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="G67" s="2">
         <v>45182</v>
       </c>
       <c r="H67" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I67" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="K67" s="4" t="str">
         <f t="shared" si="4"/>
         <v>-</v>
       </c>
       <c r="L67" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M67" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="N67" s="2">
         <v>45212</v>
@@ -3918,48 +3878,48 @@
         <v>45278</v>
       </c>
       <c r="P67" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="Q67" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
     </row>
     <row r="68" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B68" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C68" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="D68" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="E68" t="s">
         <v>8</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="G68" s="2">
         <v>45182</v>
       </c>
       <c r="H68" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I68" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="K68" s="4" t="str">
         <f t="shared" si="4"/>
         <v>-</v>
       </c>
       <c r="L68" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M68" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="N68" s="2">
         <v>45212</v>
@@ -3968,48 +3928,48 @@
         <v>45278</v>
       </c>
       <c r="P68" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="Q68" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
     </row>
     <row r="69" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B69" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C69" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="D69" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E69" t="s">
         <v>8</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="G69" s="2">
         <v>45182</v>
       </c>
       <c r="H69" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I69" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="K69" s="4" t="str">
         <f t="shared" si="4"/>
         <v>-</v>
       </c>
       <c r="L69" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M69" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="N69" s="2">
         <v>45212</v>
@@ -4018,48 +3978,48 @@
         <v>45278</v>
       </c>
       <c r="P69" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="Q69" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
     </row>
     <row r="70" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B70" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C70" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="D70" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="E70" t="s">
         <v>8</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="G70" s="2">
         <v>45182</v>
       </c>
       <c r="H70" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I70" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="K70" s="4" t="str">
         <f t="shared" si="4"/>
         <v>-</v>
       </c>
       <c r="L70" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M70" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="N70" s="2">
         <v>45212</v>
@@ -4068,48 +4028,48 @@
         <v>45278</v>
       </c>
       <c r="P70" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="Q70" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
     </row>
     <row r="71" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B71" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C71" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="D71" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="E71" t="s">
         <v>8</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="G71" s="2">
         <v>45182</v>
       </c>
       <c r="H71" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I71" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="K71" s="4" t="str">
         <f t="shared" si="4"/>
         <v>-</v>
       </c>
       <c r="L71" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M71" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="N71" s="2">
         <v>45212</v>
@@ -4118,48 +4078,48 @@
         <v>45278</v>
       </c>
       <c r="P71" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="Q71" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
     </row>
     <row r="72" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B72" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C72" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="D72" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="E72" t="s">
         <v>8</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="G72" s="2">
         <v>45182</v>
       </c>
       <c r="H72" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I72" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="K72" s="4" t="str">
         <f t="shared" si="4"/>
         <v>-</v>
       </c>
       <c r="L72" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M72" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="N72" s="2">
         <v>45212</v>
@@ -4168,48 +4128,48 @@
         <v>45278</v>
       </c>
       <c r="P72" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="Q72" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="73" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B73" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C73" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="D73" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="E73" t="s">
         <v>8</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="G73" s="2">
         <v>45182</v>
       </c>
       <c r="H73" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I73" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="K73" s="4" t="str">
         <f t="shared" si="4"/>
         <v>-</v>
       </c>
       <c r="L73" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M73" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="N73" s="2">
         <v>45212</v>
@@ -4218,48 +4178,48 @@
         <v>45275</v>
       </c>
       <c r="P73" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="Q73" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="74" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B74" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C74" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="D74" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E74" t="s">
         <v>8</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="G74" s="2">
         <v>45182</v>
       </c>
       <c r="H74" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I74" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="K74" s="4" t="str">
         <f t="shared" si="4"/>
         <v>-</v>
       </c>
       <c r="L74" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M74" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="N74" s="2">
         <v>45212</v>
@@ -4268,48 +4228,48 @@
         <v>45278</v>
       </c>
       <c r="P74" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="Q74" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="75" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B75" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C75" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="D75" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="E75" t="s">
         <v>8</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="G75" s="2">
         <v>45182</v>
       </c>
       <c r="H75" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I75" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="K75" s="4" t="str">
         <f t="shared" si="4"/>
         <v>-</v>
       </c>
       <c r="L75" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M75" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="N75" s="2">
         <v>45212</v>
@@ -4318,48 +4278,48 @@
         <v>45274</v>
       </c>
       <c r="P75" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="Q75" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="76" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B76" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C76" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="D76" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="E76" t="s">
         <v>8</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="G76" s="2">
         <v>45182</v>
       </c>
       <c r="H76" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I76" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="K76" s="4" t="str">
         <f t="shared" si="4"/>
         <v>-</v>
       </c>
       <c r="L76" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M76" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="N76" s="2">
         <v>45212</v>
@@ -4368,48 +4328,48 @@
         <v>45274</v>
       </c>
       <c r="P76" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="Q76" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="77" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B77" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C77" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="D77" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="E77" t="s">
         <v>8</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="G77" s="2">
         <v>45182</v>
       </c>
       <c r="H77" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I77" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="K77" s="4" t="str">
         <f t="shared" si="4"/>
         <v>-</v>
       </c>
       <c r="L77" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="M77" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="N77" s="2">
         <v>45212</v>
@@ -4418,48 +4378,48 @@
         <v>45278</v>
       </c>
       <c r="P77" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="Q77" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
     </row>
     <row r="78" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B78" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C78" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="D78" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="E78" t="s">
         <v>8</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="G78" s="2">
         <v>45182</v>
       </c>
       <c r="H78" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I78" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="K78" s="4" t="str">
         <f t="shared" si="4"/>
         <v>-</v>
       </c>
       <c r="L78" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="M78" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="N78" s="2">
         <v>45212</v>
@@ -4468,48 +4428,48 @@
         <v>45278</v>
       </c>
       <c r="P78" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="Q78" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
     </row>
     <row r="79" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B79" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C79" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="D79" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E79" t="s">
         <v>8</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="G79" s="2">
         <v>45182</v>
       </c>
       <c r="H79" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I79" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="K79" s="4" t="str">
         <f t="shared" si="4"/>
         <v>-</v>
       </c>
       <c r="L79" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="M79" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="N79" s="2">
         <v>45212</v>
@@ -4518,48 +4478,48 @@
         <v>45278</v>
       </c>
       <c r="P79" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="Q79" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
     </row>
     <row r="80" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B80" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C80" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="D80" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="E80" t="s">
         <v>8</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="G80" s="2">
         <v>45182</v>
       </c>
       <c r="H80" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I80" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="K80" s="4" t="str">
         <f t="shared" si="4"/>
         <v>-</v>
       </c>
       <c r="L80" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="M80" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="N80" s="2">
         <v>45212</v>
@@ -4568,48 +4528,48 @@
         <v>45278</v>
       </c>
       <c r="P80" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="Q80" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
     </row>
     <row r="81" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B81" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C81" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="D81" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="E81" t="s">
         <v>8</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="G81" s="2">
         <v>45182</v>
       </c>
       <c r="H81" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I81" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="K81" s="4" t="str">
         <f t="shared" si="4"/>
         <v>-</v>
       </c>
       <c r="L81" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="M81" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="N81" s="2">
         <v>45212</v>
@@ -4618,48 +4578,48 @@
         <v>45278</v>
       </c>
       <c r="P81" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="Q81" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
     </row>
     <row r="82" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B82" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C82" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="D82" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="E82" t="s">
         <v>8</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="G82" s="2">
         <v>45182</v>
       </c>
       <c r="H82" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I82" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="K82" s="4" t="str">
         <f t="shared" si="4"/>
         <v>-</v>
       </c>
       <c r="L82" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="M82" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="N82" s="2">
         <v>45212</v>
@@ -4668,48 +4628,48 @@
         <v>45270</v>
       </c>
       <c r="P82" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="Q82" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="83" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B83" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C83" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="D83" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="E83" t="s">
         <v>8</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="G83" s="2">
         <v>45182</v>
       </c>
       <c r="H83" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I83" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="K83" s="4" t="str">
         <f t="shared" si="4"/>
         <v>-</v>
       </c>
       <c r="L83" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="M83" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="N83" s="2">
         <v>45212</v>
@@ -4718,48 +4678,48 @@
         <v>45270</v>
       </c>
       <c r="P83" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="Q83" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="84" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B84" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C84" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="D84" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E84" t="s">
         <v>8</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="G84" s="2">
         <v>45182</v>
       </c>
       <c r="H84" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I84" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="K84" s="4" t="str">
         <f t="shared" si="4"/>
         <v>-</v>
       </c>
       <c r="L84" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="M84" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="N84" s="2">
         <v>45212</v>
@@ -4768,48 +4728,48 @@
         <v>45273</v>
       </c>
       <c r="P84" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="Q84" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="85" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B85" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C85" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="D85" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="E85" t="s">
         <v>8</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="G85" s="2">
         <v>45182</v>
       </c>
       <c r="H85" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I85" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="K85" s="4" t="str">
         <f t="shared" si="4"/>
         <v>-</v>
       </c>
       <c r="L85" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="M85" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="N85" s="2">
         <v>45212</v>
@@ -4818,48 +4778,48 @@
         <v>45277</v>
       </c>
       <c r="P85" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="Q85" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="86" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B86" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C86" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="D86" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="E86" t="s">
         <v>8</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="G86" s="2">
         <v>45182</v>
       </c>
       <c r="H86" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I86" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="K86" s="4" t="str">
         <f t="shared" si="4"/>
         <v>-</v>
       </c>
       <c r="L86" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="M86" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="N86" s="2">
         <v>45212</v>
@@ -4868,38 +4828,38 @@
         <v>45277</v>
       </c>
       <c r="P86" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="Q86" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="87" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B87" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C87" t="s">
-        <v>35</v>
+        <v>116</v>
       </c>
       <c r="D87" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="E87" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="G87" s="2">
         <v>45238</v>
       </c>
       <c r="H87" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I87" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="J87" s="2">
         <v>45272</v>
@@ -4909,38 +4869,41 @@
         <v>34</v>
       </c>
       <c r="L87" t="s">
-        <v>42</v>
-      </c>
-      <c r="M87" t="s">
-        <v>52</v>
+        <v>34</v>
+      </c>
+      <c r="M87" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q87" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="88" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B88" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C88" t="s">
-        <v>35</v>
+        <v>116</v>
       </c>
       <c r="D88" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E88" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="G88" s="2">
         <v>45238</v>
       </c>
       <c r="H88" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I88" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="J88" s="2">
         <v>45273</v>
@@ -4950,38 +4913,41 @@
         <v>35</v>
       </c>
       <c r="L88" t="s">
-        <v>42</v>
-      </c>
-      <c r="M88" t="s">
-        <v>52</v>
+        <v>34</v>
+      </c>
+      <c r="M88" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q88" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="89" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B89" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C89" t="s">
-        <v>35</v>
+        <v>116</v>
       </c>
       <c r="D89" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="E89" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="G89" s="2">
         <v>45238</v>
       </c>
       <c r="H89" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I89" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="J89" s="2">
         <v>45274</v>
@@ -4991,38 +4957,41 @@
         <v>36</v>
       </c>
       <c r="L89" t="s">
-        <v>42</v>
-      </c>
-      <c r="M89" t="s">
-        <v>52</v>
+        <v>34</v>
+      </c>
+      <c r="M89" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q89" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="90" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B90" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C90" t="s">
-        <v>35</v>
+        <v>116</v>
       </c>
       <c r="D90" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="E90" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="G90" s="2">
         <v>45238</v>
       </c>
       <c r="H90" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I90" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="J90" s="2">
         <v>45275</v>
@@ -5032,38 +5001,41 @@
         <v>37</v>
       </c>
       <c r="L90" t="s">
-        <v>41</v>
-      </c>
-      <c r="M90" t="s">
-        <v>51</v>
+        <v>33</v>
+      </c>
+      <c r="M90" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q90" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="91" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B91" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C91" t="s">
-        <v>35</v>
+        <v>116</v>
       </c>
       <c r="D91" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E91" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="G91" s="2">
         <v>45238</v>
       </c>
       <c r="H91" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I91" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="J91" s="2">
         <v>45276</v>
@@ -5073,38 +5045,41 @@
         <v>38</v>
       </c>
       <c r="L91" t="s">
-        <v>41</v>
-      </c>
-      <c r="M91" t="s">
-        <v>51</v>
+        <v>33</v>
+      </c>
+      <c r="M91" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q91" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="92" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B92" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C92" t="s">
-        <v>35</v>
+        <v>116</v>
       </c>
       <c r="D92" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="E92" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="G92" s="2">
         <v>45238</v>
       </c>
       <c r="H92" s="4">
         <f t="shared" ref="H92:H93" ca="1" si="9">IF(QUOTIENT(_xlfn.DAYS(TODAY(),G92), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),G92), 7), "-")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I92" s="4">
         <f t="shared" ref="I92:I93" ca="1" si="10">IF(_xlfn.DAYS(TODAY(),G92)&lt;10000, _xlfn.DAYS(TODAY(),G92), "-")</f>
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="J92" s="2">
         <v>45277</v>
@@ -5114,38 +5089,41 @@
         <v>39</v>
       </c>
       <c r="L92" t="s">
-        <v>41</v>
-      </c>
-      <c r="M92" t="s">
-        <v>51</v>
+        <v>33</v>
+      </c>
+      <c r="M92" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q92" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="93" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B93" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C93" t="s">
-        <v>35</v>
+        <v>116</v>
       </c>
       <c r="D93" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="E93" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F93" s="5" t="s">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="G93" s="2">
         <v>45238</v>
       </c>
       <c r="H93" s="4">
         <f t="shared" ca="1" si="9"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I93" s="4">
         <f t="shared" ca="1" si="10"/>
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="J93" s="2">
         <v>45278</v>
@@ -5155,38 +5133,41 @@
         <v>40</v>
       </c>
       <c r="L93" t="s">
-        <v>41</v>
-      </c>
-      <c r="M93" t="s">
-        <v>51</v>
+        <v>33</v>
+      </c>
+      <c r="M93" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q93" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="94" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B94" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C94" t="s">
-        <v>35</v>
+        <v>116</v>
       </c>
       <c r="D94">
         <v>615</v>
       </c>
       <c r="E94" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F94" s="5" t="s">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="G94" s="2">
         <v>45202</v>
       </c>
       <c r="H94" s="4">
         <f t="shared" ref="H94" ca="1" si="11">IF(QUOTIENT(_xlfn.DAYS(TODAY(),G94), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),G94), 7), "-")</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I94" s="4">
         <f t="shared" ref="I94" ca="1" si="12">IF(_xlfn.DAYS(TODAY(),G94)&lt;10000, _xlfn.DAYS(TODAY(),G94), "-")</f>
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J94" s="2">
         <v>45223</v>
@@ -5196,44 +5177,47 @@
         <v>21</v>
       </c>
       <c r="L94" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M94" t="s">
-        <v>53</v>
+        <v>44</v>
+      </c>
+      <c r="O94" s="2">
+        <v>45301</v>
       </c>
       <c r="P94" t="s">
-        <v>81</v>
+        <v>121</v>
       </c>
       <c r="Q94" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
     </row>
     <row r="95" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B95" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C95" t="s">
-        <v>35</v>
+        <v>116</v>
       </c>
       <c r="D95">
         <v>616</v>
       </c>
       <c r="E95" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="G95" s="2">
         <v>45202</v>
       </c>
       <c r="H95" s="4">
         <f t="shared" ref="H95:H117" ca="1" si="13">IF(QUOTIENT(_xlfn.DAYS(TODAY(),G95), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),G95), 7), "-")</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I95" s="4">
         <f t="shared" ref="I95:I117" ca="1" si="14">IF(_xlfn.DAYS(TODAY(),G95)&lt;10000, _xlfn.DAYS(TODAY(),G95), "-")</f>
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J95" s="2">
         <v>45223</v>
@@ -5243,44 +5227,47 @@
         <v>21</v>
       </c>
       <c r="L95" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M95" t="s">
-        <v>53</v>
+        <v>44</v>
+      </c>
+      <c r="O95" s="2">
+        <v>45301</v>
       </c>
       <c r="P95" t="s">
-        <v>81</v>
+        <v>121</v>
       </c>
       <c r="Q95" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
     </row>
     <row r="96" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B96" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C96" t="s">
-        <v>35</v>
+        <v>116</v>
       </c>
       <c r="D96">
         <v>617</v>
       </c>
       <c r="E96" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="G96" s="2">
         <v>45202</v>
       </c>
       <c r="H96" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I96" s="4">
         <f t="shared" ca="1" si="14"/>
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J96" s="2">
         <v>45223</v>
@@ -5290,44 +5277,47 @@
         <v>21</v>
       </c>
       <c r="L96" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M96" t="s">
-        <v>53</v>
+        <v>44</v>
+      </c>
+      <c r="O96" s="2">
+        <v>45301</v>
       </c>
       <c r="P96" t="s">
-        <v>81</v>
+        <v>121</v>
       </c>
       <c r="Q96" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
     </row>
     <row r="97" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B97" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C97" t="s">
-        <v>35</v>
+        <v>116</v>
       </c>
       <c r="D97">
         <v>618</v>
       </c>
       <c r="E97" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="G97" s="2">
         <v>45202</v>
       </c>
       <c r="H97" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I97" s="4">
         <f t="shared" ca="1" si="14"/>
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J97" s="2">
         <v>45223</v>
@@ -5337,44 +5327,47 @@
         <v>21</v>
       </c>
       <c r="L97" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M97" t="s">
-        <v>53</v>
+        <v>44</v>
+      </c>
+      <c r="O97" s="2">
+        <v>45301</v>
       </c>
       <c r="P97" t="s">
-        <v>81</v>
+        <v>121</v>
       </c>
       <c r="Q97" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
     </row>
     <row r="98" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B98" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C98" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="D98" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="E98" t="s">
         <v>8</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="G98" s="2">
         <v>45229</v>
       </c>
       <c r="H98" s="4">
         <f t="shared" ref="H98:H107" ca="1" si="16">IF(QUOTIENT(_xlfn.DAYS(TODAY(),G98), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),G98), 7), "-")</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I98" s="4">
         <f t="shared" ref="I98:I107" ca="1" si="17">IF(_xlfn.DAYS(TODAY(),G98)&lt;10000, _xlfn.DAYS(TODAY(),G98), "-")</f>
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="J98" s="2">
         <v>45267</v>
@@ -5384,47 +5377,47 @@
         <v>38</v>
       </c>
       <c r="L98" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M98" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="N98" s="2">
         <v>45278</v>
       </c>
       <c r="P98" s="2" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="Q98" s="2" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
     </row>
     <row r="99" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B99" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C99" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="D99" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="E99" t="s">
         <v>8</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="G99" s="2">
         <v>45229</v>
       </c>
       <c r="H99" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I99" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="J99" s="2">
         <v>45267</v>
@@ -5434,47 +5427,47 @@
         <v>38</v>
       </c>
       <c r="L99" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M99" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="N99" s="2">
         <v>45278</v>
       </c>
       <c r="P99" s="2" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="Q99" s="2" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
     </row>
     <row r="100" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B100" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C100" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="D100" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E100" t="s">
         <v>8</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="G100" s="2">
         <v>45229</v>
       </c>
       <c r="H100" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I100" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="J100" s="2">
         <v>45267</v>
@@ -5484,47 +5477,47 @@
         <v>38</v>
       </c>
       <c r="L100" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M100" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="N100" s="2">
         <v>45278</v>
       </c>
       <c r="P100" s="2" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="Q100" s="2" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
     </row>
     <row r="101" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B101" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C101" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="D101" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="E101" t="s">
         <v>8</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="G101" s="2">
         <v>45229</v>
       </c>
       <c r="H101" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I101" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="J101" s="2">
         <v>45267</v>
@@ -5534,47 +5527,47 @@
         <v>38</v>
       </c>
       <c r="L101" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M101" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="N101" s="2">
         <v>45278</v>
       </c>
       <c r="P101" s="2" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="Q101" s="2" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
     </row>
     <row r="102" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B102" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C102" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="D102" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="E102" t="s">
         <v>8</v>
       </c>
       <c r="F102" s="5" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="G102" s="2">
         <v>45229</v>
       </c>
       <c r="H102" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I102" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="J102" s="2">
         <v>45267</v>
@@ -5584,47 +5577,47 @@
         <v>38</v>
       </c>
       <c r="L102" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M102" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="N102" s="2">
         <v>45278</v>
       </c>
       <c r="P102" s="2" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="Q102" s="2" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
     </row>
     <row r="103" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B103" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C103" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="D103" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="E103" t="s">
         <v>8</v>
       </c>
       <c r="F103" s="5" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="G103" s="2">
         <v>45229</v>
       </c>
       <c r="H103" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I103" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="J103" s="2">
         <v>45267</v>
@@ -5634,47 +5627,47 @@
         <v>38</v>
       </c>
       <c r="L103" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M103" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="N103" s="2">
         <v>45278</v>
       </c>
       <c r="P103" s="2" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="Q103" s="2" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
     </row>
     <row r="104" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B104" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C104" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="D104" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="E104" t="s">
         <v>8</v>
       </c>
       <c r="F104" s="5" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="G104" s="2">
         <v>45229</v>
       </c>
       <c r="H104" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I104" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="J104" s="2">
         <v>45267</v>
@@ -5684,47 +5677,47 @@
         <v>38</v>
       </c>
       <c r="L104" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M104" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="N104" s="2">
         <v>45278</v>
       </c>
       <c r="P104" s="2" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="Q104" s="2" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
     </row>
     <row r="105" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B105" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C105" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="D105" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E105" t="s">
         <v>8</v>
       </c>
       <c r="F105" s="5" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="G105" s="2">
         <v>45229</v>
       </c>
       <c r="H105" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I105" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="J105" s="2">
         <v>45267</v>
@@ -5734,47 +5727,47 @@
         <v>38</v>
       </c>
       <c r="L105" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M105" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="N105" s="2">
         <v>45278</v>
       </c>
       <c r="P105" s="2" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="Q105" s="2" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
     </row>
     <row r="106" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B106" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C106" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="D106" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="E106" t="s">
         <v>8</v>
       </c>
       <c r="F106" s="5" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="G106" s="2">
         <v>45229</v>
       </c>
       <c r="H106" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I106" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="J106" s="2">
         <v>45267</v>
@@ -5784,47 +5777,47 @@
         <v>38</v>
       </c>
       <c r="L106" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M106" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="N106" s="2">
         <v>45278</v>
       </c>
       <c r="P106" s="2" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="Q106" s="2" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
     </row>
     <row r="107" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B107" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C107" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="D107" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="E107" t="s">
         <v>8</v>
       </c>
       <c r="F107" s="5" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="G107" s="2">
         <v>45229</v>
       </c>
       <c r="H107" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I107" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="J107" s="2">
         <v>45267</v>
@@ -5834,27 +5827,27 @@
         <v>38</v>
       </c>
       <c r="L107" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M107" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="N107" s="2">
         <v>45278</v>
       </c>
       <c r="P107" s="2" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="Q107" s="2" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
     </row>
     <row r="108" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B108" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C108" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="D108">
         <v>951</v>
@@ -5863,7 +5856,7 @@
         <v>8</v>
       </c>
       <c r="F108" s="5" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H108" s="4" t="str">
         <f t="shared" ca="1" si="13"/>
@@ -5878,21 +5871,21 @@
         <v>-</v>
       </c>
       <c r="M108" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="P108" s="2" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="Q108" s="2" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
     </row>
     <row r="109" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B109" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C109" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="D109">
         <v>954</v>
@@ -5901,7 +5894,7 @@
         <v>8</v>
       </c>
       <c r="F109" s="5" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H109" s="4" t="str">
         <f t="shared" ca="1" si="13"/>
@@ -5916,21 +5909,21 @@
         <v>-</v>
       </c>
       <c r="M109" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="P109" s="2" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="Q109" s="2" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
     </row>
     <row r="110" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B110" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C110" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="D110">
         <v>957</v>
@@ -5939,7 +5932,7 @@
         <v>8</v>
       </c>
       <c r="F110" s="5" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H110" s="4" t="str">
         <f t="shared" ca="1" si="13"/>
@@ -5954,21 +5947,21 @@
         <v>-</v>
       </c>
       <c r="M110" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="P110" s="2" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="Q110" s="2" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
     </row>
     <row r="111" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B111" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C111" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="D111">
         <v>960</v>
@@ -5977,7 +5970,7 @@
         <v>8</v>
       </c>
       <c r="F111" s="5" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H111" s="4" t="str">
         <f t="shared" ca="1" si="13"/>
@@ -5992,21 +5985,21 @@
         <v>-</v>
       </c>
       <c r="M111" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="P111" s="2" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="Q111" s="2" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
     </row>
     <row r="112" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B112" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C112" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="D112">
         <v>952</v>
@@ -6015,7 +6008,7 @@
         <v>8</v>
       </c>
       <c r="F112" s="5" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H112" s="4" t="str">
         <f t="shared" ca="1" si="13"/>
@@ -6030,24 +6023,24 @@
         <v>-</v>
       </c>
       <c r="M112" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="O112" s="2">
         <v>45289</v>
       </c>
       <c r="P112" s="2" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="Q112" s="2" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
     </row>
     <row r="113" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B113" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C113" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="D113">
         <v>955</v>
@@ -6056,7 +6049,7 @@
         <v>8</v>
       </c>
       <c r="F113" s="5" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H113" s="4" t="str">
         <f t="shared" ca="1" si="13"/>
@@ -6071,21 +6064,21 @@
         <v>-</v>
       </c>
       <c r="M113" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="P113" s="2" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="Q113" s="2" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
     </row>
     <row r="114" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B114" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C114" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="D114">
         <v>958</v>
@@ -6094,7 +6087,7 @@
         <v>8</v>
       </c>
       <c r="F114" s="5" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H114" s="4" t="str">
         <f t="shared" ca="1" si="13"/>
@@ -6109,24 +6102,24 @@
         <v>-</v>
       </c>
       <c r="M114" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="O114" s="2">
         <v>45289</v>
       </c>
       <c r="P114" s="2" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="Q114" s="2" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
     </row>
     <row r="115" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B115" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C115" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="D115">
         <v>961</v>
@@ -6135,7 +6128,7 @@
         <v>8</v>
       </c>
       <c r="F115" s="5" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H115" s="4" t="str">
         <f t="shared" ca="1" si="13"/>
@@ -6150,24 +6143,24 @@
         <v>-</v>
       </c>
       <c r="M115" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="O115" s="2">
         <v>45292</v>
       </c>
       <c r="P115" s="2" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="Q115" s="2" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
     </row>
     <row r="116" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B116" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C116" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="D116">
         <v>953</v>
@@ -6176,7 +6169,7 @@
         <v>8</v>
       </c>
       <c r="F116" s="5" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H116" s="4" t="str">
         <f t="shared" ca="1" si="13"/>
@@ -6191,24 +6184,24 @@
         <v>-</v>
       </c>
       <c r="M116" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="O116" s="2">
         <v>45289</v>
       </c>
       <c r="P116" s="2" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="Q116" s="2" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
     </row>
     <row r="117" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B117" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C117" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="D117">
         <v>956</v>
@@ -6217,7 +6210,7 @@
         <v>8</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H117" s="4" t="str">
         <f t="shared" ca="1" si="13"/>
@@ -6232,24 +6225,24 @@
         <v>-</v>
       </c>
       <c r="M117" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="O117" s="2">
         <v>45292</v>
       </c>
       <c r="P117" s="2" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="Q117" s="2" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
     </row>
     <row r="118" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B118" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C118" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="D118">
         <v>959</v>
@@ -6258,7 +6251,7 @@
         <v>8</v>
       </c>
       <c r="F118" s="5" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H118" s="4" t="str">
         <f t="shared" ref="H118:H123" ca="1" si="18">IF(QUOTIENT(_xlfn.DAYS(TODAY(),G118), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),G118), 7), "-")</f>
@@ -6273,21 +6266,21 @@
         <v>-</v>
       </c>
       <c r="M118" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="P118" s="2" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="Q118" s="2" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
     </row>
     <row r="119" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B119" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C119" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="D119">
         <v>962</v>
@@ -6296,7 +6289,7 @@
         <v>8</v>
       </c>
       <c r="F119" s="5" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H119" s="4" t="str">
         <f t="shared" ca="1" si="18"/>
@@ -6311,132 +6304,132 @@
         <v>-</v>
       </c>
       <c r="M119" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="O119" s="2">
         <v>45289</v>
       </c>
       <c r="P119" s="2" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="Q119" s="2" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
     </row>
     <row r="120" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B120" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="C120" t="s">
-        <v>27</v>
+        <v>112</v>
       </c>
       <c r="E120" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="G120" s="2">
         <v>45291</v>
       </c>
       <c r="H120" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I120" s="4">
         <f t="shared" ca="1" si="19"/>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="K120" s="4" t="str">
         <f t="shared" si="15"/>
         <v>-</v>
       </c>
       <c r="M120" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
     </row>
     <row r="121" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B121" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="C121" t="s">
-        <v>27</v>
+        <v>112</v>
       </c>
       <c r="E121" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="G121" s="2">
         <v>45291</v>
       </c>
       <c r="H121" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I121" s="4">
         <f t="shared" ca="1" si="19"/>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="K121" s="4" t="str">
         <f t="shared" si="15"/>
         <v>-</v>
       </c>
       <c r="M121" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
     </row>
     <row r="122" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B122" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="C122" t="s">
-        <v>27</v>
+        <v>112</v>
       </c>
       <c r="E122" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="G122" s="2">
         <v>45291</v>
       </c>
       <c r="H122" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I122" s="4">
         <f t="shared" ca="1" si="19"/>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="K122" s="4" t="str">
         <f t="shared" si="15"/>
         <v>-</v>
       </c>
       <c r="M122" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
     </row>
     <row r="123" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B123" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="C123" t="s">
-        <v>27</v>
+        <v>112</v>
       </c>
       <c r="E123" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="G123" s="2">
         <v>45291</v>
       </c>
       <c r="H123" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I123" s="4">
         <f t="shared" ca="1" si="19"/>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="K123" s="4" t="str">
         <f t="shared" si="15"/>
         <v>-</v>
       </c>
       <c r="M123" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -6452,13 +6445,13 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E1048576" xr:uid="{939E2B39-E841-4A9F-AD11-00C266DB2690}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E125 E127:E1048576" xr:uid="{939E2B39-E841-4A9F-AD11-00C266DB2690}">
       <formula1>"Y, N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L1:L1048576" xr:uid="{2DE54AC7-5B92-48D6-98C4-E6203F87CDD0}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L1:L125 L127:L1048576" xr:uid="{2DE54AC7-5B92-48D6-98C4-E6203F87CDD0}">
       <formula1>"M, F"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B1048576" xr:uid="{ACC76399-D52A-490E-9FEF-427013FFE2CE}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B125 B127:B1048576" xr:uid="{ACC76399-D52A-490E-9FEF-427013FFE2CE}">
       <formula1>"SPF, 5F"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6478,48 +6471,48 @@
   <sheetData>
     <row r="2" spans="3:8" x14ac:dyDescent="0.3">
       <c r="D2" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="E2" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="H2" s="13"/>
     </row>
     <row r="3" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C3" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="D3" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G3" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C4" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G4" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/Mouse 내역.xlsx
+++ b/Mouse 내역.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20405"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20406"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\heung\OneDrive\바탕 화면\동물실\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0FDA010-BDB2-4786-8347-9E4E0569BA1B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{065F5C17-C291-4E26-B412-1B16C97B6FC6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19080" windowHeight="9180" xr2:uid="{5A73A69A-2AFB-4F3E-AC64-070DD7700CB2}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19080" windowHeight="9180" activeTab="1" xr2:uid="{5A73A69A-2AFB-4F3E-AC64-070DD7700CB2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$Q$123</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$Q$130</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="134">
   <si>
     <t>Strain</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -501,6 +501,54 @@
   </si>
   <si>
     <t>Exp. 1-7-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>to 정우형</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SPF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A2.3.X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SPF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A2.4.X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R1, L1 확인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tag 떨어짐 다시 확인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A3.B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>f/+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>f/+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cd36 flox</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>같이 weaning</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -508,7 +556,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -574,6 +622,15 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <strike/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -603,7 +660,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -641,6 +698,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -659,7 +734,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -693,14 +768,68 @@
     <xf numFmtId="49" fontId="6" fillId="3" borderId="0" xfId="2" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1">
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="5" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -732,7 +861,7 @@
       <xdr:row>6</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="3840860" cy="2273571"/>
+    <xdr:ext cx="2234266" cy="2416944"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="TextBox 1">
@@ -747,7 +876,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1381125" y="1428750"/>
-          <a:ext cx="3840860" cy="2273571"/>
+          <a:ext cx="2234266" cy="2416944"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -776,91 +905,45 @@
         <a:p>
           <a:r>
             <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
-            <a:t>Tmem119-CreERT2</a:t>
+            <a:t>1)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
+            <a:t>A2.1.F</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" baseline="0"/>
-            <a:t>; Cd36-flox</a:t>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1"/>
+            <a:t>에서 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
+            <a:t>+/+; f/f female </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1"/>
+            <a:t>한마리</a:t>
           </a:r>
           <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
         </a:p>
         <a:p>
           <a:r>
             <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
-            <a:t>A2.B breader</a:t>
+            <a:t>B1.1.M</a:t>
           </a:r>
           <a:r>
             <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1"/>
-            <a:t>에 </a:t>
+            <a:t>에서 </a:t>
           </a:r>
           <a:r>
             <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
-            <a:t>B1.1M</a:t>
+            <a:t>+/+; f/f male </a:t>
           </a:r>
           <a:r>
             <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1"/>
-            <a:t>의 </a:t>
+            <a:t>한마리</a:t>
           </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
-            <a:t>male </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1"/>
-            <a:t>한마리 넣음 </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
-            <a:t>(A3.B)</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
-            <a:t>A2.1F</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1"/>
-            <a:t>의 </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
-            <a:t>874</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1"/>
-            <a:t>랑 </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
-            <a:t>B1.1M</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1"/>
-            <a:t>의 </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
-            <a:t>male </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1"/>
-            <a:t>한마리 </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
-            <a:t>breader </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1"/>
-            <a:t>만듦 </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
-            <a:t>(A4.B)</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
           <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
         </a:p>
         <a:p>
@@ -869,11 +952,52 @@
         <a:p>
           <a:r>
             <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
-            <a:t>LysM-Cre;</a:t>
+            <a:t>2)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
+            <a:t>A2.1.F</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1"/>
+            <a:t>엣 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
+            <a:t>Cre/+; f/f female </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1"/>
+            <a:t>한마리</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
+            <a:t>B1.1.M</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1"/>
+            <a:t>에서 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
+            <a:t>+/+;</a:t>
           </a:r>
           <a:r>
             <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" baseline="0"/>
-            <a:t> Cd36-flox</a:t>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
+            <a:t>f/f male </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1"/>
+            <a:t>한마리</a:t>
           </a:r>
           <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
         </a:p>
@@ -881,67 +1005,52 @@
           <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
         </a:p>
         <a:p>
-          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
-        </a:p>
-        <a:p>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1"/>
-            <a:t>나중에 할 거</a:t>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
+            <a:t>3)</a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
         </a:p>
         <a:p>
           <a:r>
             <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
-            <a:t>Lysm-Cre; Cd36-flox</a:t>
+            <a:t>C1.1.M</a:t>
           </a:r>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1"/>
+            <a:t>에서 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
+            <a:t>+/+;</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" baseline="0"/>
+            <a:t> f/+ male </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" baseline="0"/>
+            <a:t>한마리</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="1" baseline="0"/>
         </a:p>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
-            <a:t>C1.3F</a:t>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" baseline="0"/>
+            <a:t>C1.1.F</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1"/>
-            <a:t>의 </a:t>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" baseline="0"/>
+            <a:t>에서 </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
-            <a:t>815, 816</a:t>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" baseline="0"/>
+            <a:t>+/+; f/+ female </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1"/>
-            <a:t>과 </a:t>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" baseline="0"/>
+            <a:t>한마리</a:t>
           </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
-            <a:t>B1.1M</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1"/>
-            <a:t>의 </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
-            <a:t>male </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1"/>
-            <a:t>한마리 </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
-            <a:t>breader </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1"/>
-            <a:t>만듦 </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
-            <a:t>(C3.B)</a:t>
-          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -1248,7 +1357,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D71A6DC-E91C-489F-8F50-989C4712FA7C}">
   <sheetPr filterMode="1"/>
-  <dimension ref="B1:Q123"/>
+  <dimension ref="B1:Q130"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="10.5" customWidth="1"/>
@@ -1257,13 +1366,14 @@
     <col min="5" max="5" width="7.625" customWidth="1"/>
     <col min="6" max="6" width="12.5" style="5" customWidth="1"/>
     <col min="7" max="7" width="11.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="9" customWidth="1"/>
+    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="9" max="9" width="9" hidden="1" customWidth="1"/>
     <col min="10" max="10" width="11.125" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="8.25" hidden="1" customWidth="1"/>
     <col min="12" max="12" width="6.375" customWidth="1"/>
     <col min="14" max="14" width="13.125" style="2" hidden="1" customWidth="1"/>
     <col min="15" max="15" width="12.75" style="2" customWidth="1"/>
-    <col min="16" max="16" width="13.25" customWidth="1"/>
+    <col min="16" max="16" width="13.25" hidden="1" customWidth="1"/>
     <col min="17" max="17" width="19.875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1335,11 +1445,11 @@
       </c>
       <c r="H2" s="4">
         <f ca="1">IF(QUOTIENT(_xlfn.DAYS(TODAY(),G2), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),G2), 7), "-")</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I2" s="4">
         <f ca="1">IF(_xlfn.DAYS(TODAY(),G2)&lt;10000, _xlfn.DAYS(TODAY(),G2), "-")</f>
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="K2" s="4" t="str">
         <f t="shared" ref="K2:K31" si="0">IF(_xlfn.DAYS(J2,G2)&gt;0, _xlfn.DAYS(J2,G2), "-")</f>
@@ -1366,7 +1476,7 @@
       <c r="E3" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="10" t="s">
         <v>113</v>
       </c>
       <c r="G3" s="2">
@@ -1374,11 +1484,11 @@
       </c>
       <c r="H3" s="4">
         <f t="shared" ref="H3:H65" ca="1" si="1">IF(QUOTIENT(_xlfn.DAYS(TODAY(),G3), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),G3), 7), "-")</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I3" s="4">
         <f t="shared" ref="I3:I31" ca="1" si="2">IF(_xlfn.DAYS(TODAY(),G3)&lt;10000, _xlfn.DAYS(TODAY(),G3), "-")</f>
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="K3" s="4" t="str">
         <f t="shared" si="0"/>
@@ -1387,7 +1497,7 @@
       <c r="L3" t="s">
         <v>13</v>
       </c>
-      <c r="M3" t="s">
+      <c r="M3" s="1" t="s">
         <v>52</v>
       </c>
       <c r="N3" s="7"/>
@@ -1403,7 +1513,7 @@
       <c r="E4" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="10" t="s">
         <v>113</v>
       </c>
       <c r="G4" s="2">
@@ -1411,11 +1521,11 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I4" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="K4" s="4" t="str">
         <f t="shared" si="0"/>
@@ -1424,13 +1534,13 @@
       <c r="L4" t="s">
         <v>13</v>
       </c>
-      <c r="M4" t="s">
+      <c r="M4" s="1" t="s">
         <v>52</v>
       </c>
       <c r="N4" s="7"/>
       <c r="O4" s="7"/>
     </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>5</v>
       </c>
@@ -1451,11 +1561,11 @@
       </c>
       <c r="H5" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I5" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="J5" s="2">
         <v>45293</v>
@@ -1471,7 +1581,9 @@
         <v>79</v>
       </c>
       <c r="N5" s="7"/>
-      <c r="O5" s="7"/>
+      <c r="O5" s="7">
+        <v>45309</v>
+      </c>
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
@@ -1483,38 +1595,41 @@
       <c r="D6">
         <v>872</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6" s="21">
         <v>45266</v>
       </c>
-      <c r="H6" s="4">
+      <c r="H6" s="22">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I6" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>40</v>
-      </c>
-      <c r="J6" s="2">
+        <v>44</v>
+      </c>
+      <c r="J6" s="21">
         <v>45293</v>
       </c>
       <c r="K6" s="4">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="L6" t="s">
+      <c r="L6" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="M6" t="s">
+      <c r="M6" s="27" t="s">
         <v>79</v>
       </c>
       <c r="N6" s="7"/>
-      <c r="O6" s="7"/>
+      <c r="O6" s="29"/>
+      <c r="Q6" s="27" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
@@ -1526,40 +1641,43 @@
       <c r="D7">
         <v>873</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G7" s="17">
         <v>45266</v>
       </c>
-      <c r="H7" s="4">
+      <c r="H7" s="24">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I7" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>40</v>
-      </c>
-      <c r="J7" s="2">
+        <v>44</v>
+      </c>
+      <c r="J7" s="17">
         <v>45293</v>
       </c>
       <c r="K7" s="4">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="L7" t="s">
+      <c r="L7" s="28" t="s">
         <v>81</v>
       </c>
-      <c r="M7" t="s">
+      <c r="M7" s="28" t="s">
         <v>79</v>
       </c>
       <c r="N7" s="7"/>
-      <c r="O7" s="7"/>
-    </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="O7" s="30"/>
+      <c r="Q7" s="28" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="8" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>5</v>
       </c>
@@ -1569,38 +1687,41 @@
       <c r="D8">
         <v>874</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G8" s="15">
         <v>45266</v>
       </c>
-      <c r="H8" s="4">
+      <c r="H8" s="26">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I8" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>40</v>
-      </c>
-      <c r="J8" s="2">
+        <v>44</v>
+      </c>
+      <c r="J8" s="15">
         <v>45293</v>
       </c>
       <c r="K8" s="4">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="L8" t="s">
+      <c r="L8" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="M8" t="s">
+      <c r="M8" s="18" t="s">
         <v>79</v>
       </c>
       <c r="N8" s="7"/>
-      <c r="O8" s="7"/>
+      <c r="O8" s="31"/>
+      <c r="Q8" s="18" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
@@ -1623,11 +1744,11 @@
       </c>
       <c r="H9" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I9" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="J9" s="2">
         <v>45293</v>
@@ -1645,7 +1766,7 @@
       <c r="N9" s="7"/>
       <c r="O9" s="7"/>
     </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>5</v>
       </c>
@@ -1666,11 +1787,11 @@
       </c>
       <c r="H10" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I10" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="J10" s="2">
         <v>45293</v>
@@ -1686,9 +1807,11 @@
         <v>80</v>
       </c>
       <c r="N10" s="7"/>
-      <c r="O10" s="7"/>
-    </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="O10" s="7">
+        <v>45309</v>
+      </c>
+    </row>
+    <row r="11" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>5</v>
       </c>
@@ -1709,11 +1832,11 @@
       </c>
       <c r="H11" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I11" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="J11" s="2">
         <v>45293</v>
@@ -1729,7 +1852,9 @@
         <v>80</v>
       </c>
       <c r="N11" s="7"/>
-      <c r="O11" s="7"/>
+      <c r="O11" s="7">
+        <v>45309</v>
+      </c>
     </row>
     <row r="12" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
@@ -1749,11 +1874,11 @@
       </c>
       <c r="H12" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I12" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="K12" s="4" t="str">
         <f t="shared" si="0"/>
@@ -1867,7 +1992,7 @@
       </c>
       <c r="I15" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="K15" s="4" t="str">
         <f t="shared" si="0"/>
@@ -1907,7 +2032,7 @@
       </c>
       <c r="I16" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="K16" s="4" t="str">
         <f t="shared" si="0"/>
@@ -1922,7 +2047,7 @@
       <c r="N16" s="7"/>
       <c r="O16" s="7"/>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>5</v>
       </c>
@@ -1947,7 +2072,7 @@
       </c>
       <c r="I17" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="K17" s="4" t="str">
         <f t="shared" si="0"/>
@@ -1960,7 +2085,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>5</v>
       </c>
@@ -1973,7 +2098,7 @@
       <c r="E18" t="s">
         <v>7</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="F18" s="10" t="s">
         <v>113</v>
       </c>
       <c r="G18" s="2">
@@ -1985,7 +2110,7 @@
       </c>
       <c r="I18" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="K18" s="4" t="str">
         <f t="shared" si="0"/>
@@ -1994,11 +2119,11 @@
       <c r="L18" t="s">
         <v>11</v>
       </c>
-      <c r="M18" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="M18" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="19" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>5</v>
       </c>
@@ -2023,7 +2148,7 @@
       </c>
       <c r="I19" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="K19" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2036,7 +2161,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="20" spans="2:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>5</v>
       </c>
@@ -2054,11 +2179,11 @@
       </c>
       <c r="H20" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I20" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="K20" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2074,7 +2199,7 @@
         <v>45299</v>
       </c>
     </row>
-    <row r="21" spans="2:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>5</v>
       </c>
@@ -2109,7 +2234,7 @@
         <v>45299</v>
       </c>
     </row>
-    <row r="22" spans="2:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>5</v>
       </c>
@@ -2131,7 +2256,7 @@
       </c>
       <c r="I22" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="J22" s="2">
         <v>45112</v>
@@ -2150,7 +2275,7 @@
         <v>45299</v>
       </c>
     </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>5</v>
       </c>
@@ -2168,11 +2293,11 @@
       </c>
       <c r="H23" s="4">
         <f ca="1">IF(QUOTIENT(_xlfn.DAYS(TODAY(),G23), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),G23), 7), "-")</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I23" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="J23" s="2">
         <v>45176</v>
@@ -2187,8 +2312,14 @@
       <c r="M23" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="O23" s="2">
+        <v>45306</v>
+      </c>
+      <c r="Q23" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="24" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>5</v>
       </c>
@@ -2206,11 +2337,11 @@
       </c>
       <c r="H24" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I24" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="J24" s="2">
         <v>45176</v>
@@ -2225,8 +2356,14 @@
       <c r="M24" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="O24" s="2">
+        <v>45306</v>
+      </c>
+      <c r="Q24" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="25" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>5</v>
       </c>
@@ -2236,7 +2373,7 @@
       <c r="E25" t="s">
         <v>7</v>
       </c>
-      <c r="F25" s="12" t="s">
+      <c r="F25" s="11" t="s">
         <v>22</v>
       </c>
       <c r="G25" s="2">
@@ -2244,11 +2381,11 @@
       </c>
       <c r="H25" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I25" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="J25" s="2">
         <v>45176</v>
@@ -2263,8 +2400,14 @@
       <c r="M25" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="O25" s="2">
+        <v>45306</v>
+      </c>
+      <c r="Q25" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="26" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>5</v>
       </c>
@@ -2282,11 +2425,11 @@
       </c>
       <c r="H26" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I26" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="J26" s="2">
         <v>45176</v>
@@ -2301,8 +2444,9 @@
       <c r="M26" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="Q26" s="2"/>
+    </row>
+    <row r="27" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>5</v>
       </c>
@@ -2320,11 +2464,11 @@
       </c>
       <c r="H27" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I27" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="J27" s="2">
         <v>45176</v>
@@ -2339,106 +2483,115 @@
       <c r="M27" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="Q27" s="2"/>
+    </row>
+    <row r="28" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>5</v>
       </c>
       <c r="C28" t="s">
-        <v>114</v>
-      </c>
-      <c r="E28" t="s">
-        <v>8</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="G28" s="2">
+        <v>21</v>
+      </c>
+      <c r="E28" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="F28" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="G28" s="21">
         <v>45203</v>
       </c>
-      <c r="H28" s="4">
+      <c r="H28" s="22">
         <f t="shared" ca="1" si="1"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I28" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>103</v>
-      </c>
-      <c r="J28" s="2">
+        <v>107</v>
+      </c>
+      <c r="J28" s="21">
         <v>45229</v>
       </c>
       <c r="K28" s="4">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="L28" t="s">
+      <c r="L28" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="M28" t="s">
+      <c r="M28" s="27" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="O28" s="21"/>
+      <c r="Q28" s="27" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="29" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B29" t="s">
         <v>5</v>
       </c>
       <c r="C29" t="s">
         <v>114</v>
       </c>
-      <c r="E29" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" s="5" t="s">
+      <c r="E29" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="F29" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="G29" s="2">
+      <c r="G29" s="15">
         <v>45203</v>
       </c>
-      <c r="H29" s="4">
+      <c r="H29" s="26">
         <f t="shared" ca="1" si="1"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I29" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>103</v>
-      </c>
-      <c r="J29" s="2">
+        <v>107</v>
+      </c>
+      <c r="J29" s="15">
         <v>45229</v>
       </c>
       <c r="K29" s="4">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="L29" t="s">
+      <c r="L29" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="M29" t="s">
+      <c r="M29" s="18" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="O29" s="15"/>
+      <c r="Q29" s="18" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="30" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>5</v>
       </c>
       <c r="C30" t="s">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
       </c>
-      <c r="F30" s="5" t="s">
-        <v>117</v>
+      <c r="F30" s="10" t="s">
+        <v>130</v>
       </c>
       <c r="G30" s="2">
         <v>45203</v>
       </c>
       <c r="H30" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I30" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="J30" s="2">
         <v>45229</v>
@@ -2450,33 +2603,34 @@
       <c r="L30" t="s">
         <v>13</v>
       </c>
-      <c r="M30" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="M30" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q30" s="2"/>
+    </row>
+    <row r="31" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
         <v>5</v>
       </c>
       <c r="C31" t="s">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
       </c>
-      <c r="F31" s="5" t="s">
-        <v>117</v>
+      <c r="F31" s="10" t="s">
+        <v>130</v>
       </c>
       <c r="G31" s="2">
         <v>45203</v>
       </c>
       <c r="H31" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I31" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="J31" s="2">
         <v>45229</v>
@@ -2488,33 +2642,34 @@
       <c r="L31" t="s">
         <v>13</v>
       </c>
-      <c r="M31" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="32" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="M31" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q31" s="2"/>
+    </row>
+    <row r="32" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
         <v>5</v>
       </c>
       <c r="C32" t="s">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="G32" s="2">
         <v>45203</v>
       </c>
       <c r="H32" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I32" s="4">
         <f t="shared" ref="I32:I38" ca="1" si="3">IF(_xlfn.DAYS(TODAY(),G32)&lt;10000, _xlfn.DAYS(TODAY(),G32), "-")</f>
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="J32" s="2">
         <v>45229</v>
@@ -2529,8 +2684,9 @@
       <c r="M32" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q32" s="2"/>
+    </row>
+    <row r="33" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
         <v>5</v>
       </c>
@@ -2565,7 +2721,7 @@
         <v>45299</v>
       </c>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
         <v>5</v>
       </c>
@@ -2586,11 +2742,11 @@
       </c>
       <c r="H34" s="4">
         <f ca="1">IF(QUOTIENT(_xlfn.DAYS(TODAY(),G34), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),G34), 7), "-")</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I34" s="4">
         <f ca="1">IF(_xlfn.DAYS(TODAY(),G34)&lt;10000, _xlfn.DAYS(TODAY(),G34), "-")</f>
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="J34" s="2">
         <v>45257</v>
@@ -2605,8 +2761,14 @@
       <c r="M34" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="O34" s="2">
+        <v>45306</v>
+      </c>
+      <c r="Q34" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
         <v>5</v>
       </c>
@@ -2637,8 +2799,14 @@
       <c r="M35" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="36" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="O35" s="2">
+        <v>45306</v>
+      </c>
+      <c r="Q35" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="36" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B36" t="s">
         <v>5</v>
       </c>
@@ -2669,8 +2837,14 @@
       <c r="M36" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="O36" s="2">
+        <v>45306</v>
+      </c>
+      <c r="Q36" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B37" t="s">
         <v>5</v>
       </c>
@@ -2691,11 +2865,11 @@
       </c>
       <c r="H37" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I37" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="J37" s="2">
         <v>45257</v>
@@ -2710,8 +2884,14 @@
       <c r="M37" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="O37" s="2">
+        <v>45306</v>
+      </c>
+      <c r="Q37" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="38" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B38" t="s">
         <v>5</v>
       </c>
@@ -2732,11 +2912,11 @@
       </c>
       <c r="H38" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I38" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="J38" s="2">
         <v>45257</v>
@@ -2751,8 +2931,14 @@
       <c r="M38" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="O38" s="2">
+        <v>45306</v>
+      </c>
+      <c r="Q38" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="39" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B39" t="s">
         <v>5</v>
       </c>
@@ -2773,11 +2959,11 @@
       </c>
       <c r="H39" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I39" s="4">
         <f t="shared" ref="I39:I41" ca="1" si="5">IF(_xlfn.DAYS(TODAY(),G39)&lt;10000, _xlfn.DAYS(TODAY(),G39), "-")</f>
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="J39" s="2">
         <v>45257</v>
@@ -2792,13 +2978,19 @@
       <c r="M39" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="O39" s="2">
+        <v>45306</v>
+      </c>
+      <c r="Q39" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B40" t="s">
         <v>5</v>
       </c>
       <c r="C40" t="s">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="D40" t="s">
         <v>24</v>
@@ -2807,18 +2999,18 @@
         <v>8</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>96</v>
+        <v>131</v>
       </c>
       <c r="G40" s="2">
         <v>45231</v>
       </c>
       <c r="H40" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I40" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="J40" s="2">
         <v>45257</v>
@@ -2834,7 +3026,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B41" t="s">
         <v>5</v>
       </c>
@@ -2847,7 +3039,7 @@
       <c r="E41" t="s">
         <v>8</v>
       </c>
-      <c r="F41" s="5" t="s">
+      <c r="F41" s="12" t="s">
         <v>97</v>
       </c>
       <c r="G41" s="2">
@@ -2855,11 +3047,11 @@
       </c>
       <c r="H41" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I41" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="J41" s="2">
         <v>45257</v>
@@ -2875,7 +3067,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B42" t="s">
         <v>5</v>
       </c>
@@ -2896,11 +3088,11 @@
       </c>
       <c r="H42" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I42" s="4">
         <f t="shared" ref="I42" ca="1" si="6">IF(_xlfn.DAYS(TODAY(),G42)&lt;10000, _xlfn.DAYS(TODAY(),G42), "-")</f>
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="K42" s="4" t="str">
         <f t="shared" si="4"/>
@@ -2912,8 +3104,11 @@
       <c r="M42" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="O42" s="7">
+        <v>45309</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B43" t="s">
         <v>5</v>
       </c>
@@ -2934,11 +3129,11 @@
       </c>
       <c r="H43" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I43" s="4">
         <f t="shared" ref="I43:I91" ca="1" si="7">IF(_xlfn.DAYS(TODAY(),G43)&lt;10000, _xlfn.DAYS(TODAY(),G43), "-")</f>
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="K43" s="4" t="str">
         <f t="shared" si="4"/>
@@ -2951,7 +3146,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B44" t="s">
         <v>5</v>
       </c>
@@ -2964,7 +3159,7 @@
       <c r="E44" t="s">
         <v>8</v>
       </c>
-      <c r="F44" s="12" t="s">
+      <c r="F44" s="11" t="s">
         <v>97</v>
       </c>
       <c r="G44" s="2">
@@ -2972,11 +3167,11 @@
       </c>
       <c r="H44" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I44" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="J44" s="2">
         <v>45293</v>
@@ -2991,8 +3186,11 @@
       <c r="M44" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="O44" s="7">
+        <v>45309</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B45" t="s">
         <v>5</v>
       </c>
@@ -3005,7 +3203,7 @@
       <c r="E45" t="s">
         <v>8</v>
       </c>
-      <c r="F45" s="12" t="s">
+      <c r="F45" s="11" t="s">
         <v>97</v>
       </c>
       <c r="G45" s="2">
@@ -3013,11 +3211,11 @@
       </c>
       <c r="H45" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I45" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="J45" s="2">
         <v>45293</v>
@@ -3032,8 +3230,11 @@
       <c r="M45" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="O45" s="7">
+        <v>45309</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B46" t="s">
         <v>5</v>
       </c>
@@ -3054,11 +3255,11 @@
       </c>
       <c r="H46" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I46" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="J46" s="2">
         <v>45293</v>
@@ -3073,8 +3274,14 @@
       <c r="M46" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="O46" s="2">
+        <v>45306</v>
+      </c>
+      <c r="Q46" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B47" t="s">
         <v>5</v>
       </c>
@@ -3095,11 +3302,11 @@
       </c>
       <c r="H47" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I47" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="J47" s="2">
         <v>45293</v>
@@ -3114,8 +3321,14 @@
       <c r="M47" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="O47" s="2">
+        <v>45306</v>
+      </c>
+      <c r="Q47" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B48" t="s">
         <v>5</v>
       </c>
@@ -3140,7 +3353,7 @@
       </c>
       <c r="I48" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="J48" s="2">
         <v>45293</v>
@@ -3155,13 +3368,19 @@
       <c r="M48" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="49" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="O48" s="2">
+        <v>45306</v>
+      </c>
+      <c r="Q48" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="49" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B49" t="s">
         <v>5</v>
       </c>
       <c r="C49" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="D49">
         <v>821</v>
@@ -3170,18 +3389,18 @@
         <v>8</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>96</v>
+        <v>130</v>
       </c>
       <c r="G49" s="2">
         <v>45267</v>
       </c>
       <c r="H49" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I49" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="J49" s="2">
         <v>45293</v>
@@ -3197,12 +3416,12 @@
         <v>84</v>
       </c>
     </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B50" t="s">
         <v>5</v>
       </c>
       <c r="C50" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="D50">
         <v>822</v>
@@ -3211,18 +3430,18 @@
         <v>8</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>96</v>
+        <v>130</v>
       </c>
       <c r="G50" s="2">
         <v>45267</v>
       </c>
       <c r="H50" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I50" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="J50" s="2">
         <v>45293</v>
@@ -3238,7 +3457,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="B51" t="s">
         <v>5</v>
       </c>
@@ -3259,11 +3478,11 @@
       </c>
       <c r="H51" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I51" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="J51" s="2">
         <v>45293</v>
@@ -3278,8 +3497,11 @@
       <c r="M51" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="O51" s="7">
+        <v>45309</v>
+      </c>
+    </row>
+    <row r="52" spans="2:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="B52" t="s">
         <v>5</v>
       </c>
@@ -3304,7 +3526,7 @@
       </c>
       <c r="I52" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="J52" s="2">
         <v>45293</v>
@@ -3319,13 +3541,16 @@
       <c r="M52" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="53" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="O52" s="7">
+        <v>45309</v>
+      </c>
+    </row>
+    <row r="53" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B53" t="s">
         <v>5</v>
       </c>
       <c r="C53" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="D53">
         <v>825</v>
@@ -3334,7 +3559,7 @@
         <v>8</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>96</v>
+        <v>130</v>
       </c>
       <c r="G53" s="2">
         <v>45271</v>
@@ -3345,7 +3570,7 @@
       </c>
       <c r="I53" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="J53" s="2">
         <v>45293</v>
@@ -3361,7 +3586,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="54" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="B54" t="s">
         <v>28</v>
       </c>
@@ -3386,7 +3611,7 @@
       </c>
       <c r="I54" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J54" s="2">
         <v>45238</v>
@@ -3402,7 +3627,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="55" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="B55" t="s">
         <v>28</v>
       </c>
@@ -3427,7 +3652,7 @@
       </c>
       <c r="I55" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J55" s="2">
         <v>45238</v>
@@ -3443,7 +3668,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="56" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="B56" t="s">
         <v>28</v>
       </c>
@@ -3468,7 +3693,7 @@
       </c>
       <c r="I56" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J56" s="2">
         <v>45238</v>
@@ -3484,7 +3709,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="57" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="B57" t="s">
         <v>28</v>
       </c>
@@ -3502,11 +3727,11 @@
       </c>
       <c r="H57" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I57" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="K57" s="4" t="str">
         <f t="shared" si="4"/>
@@ -3519,7 +3744,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="58" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="B58" t="s">
         <v>28</v>
       </c>
@@ -3537,11 +3762,11 @@
       </c>
       <c r="H58" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I58" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="K58" s="4" t="str">
         <f t="shared" si="4"/>
@@ -3554,7 +3779,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="59" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="B59" t="s">
         <v>28</v>
       </c>
@@ -3569,11 +3794,11 @@
       </c>
       <c r="H59" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I59" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="J59" s="2">
         <v>45295</v>
@@ -3589,7 +3814,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="60" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="B60" t="s">
         <v>28</v>
       </c>
@@ -3604,11 +3829,11 @@
       </c>
       <c r="H60" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I60" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="J60" s="2">
         <v>45295</v>
@@ -3624,7 +3849,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="61" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="B61" t="s">
         <v>28</v>
       </c>
@@ -3639,11 +3864,11 @@
       </c>
       <c r="H61" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I61" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="J61" s="2">
         <v>45295</v>
@@ -3659,7 +3884,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="62" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="B62" t="s">
         <v>28</v>
       </c>
@@ -3674,11 +3899,11 @@
       </c>
       <c r="H62" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I62" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="J62" s="2">
         <v>45295</v>
@@ -3694,7 +3919,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="63" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="B63" t="s">
         <v>28</v>
       </c>
@@ -3709,11 +3934,11 @@
       </c>
       <c r="H63" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I63" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="J63" s="2">
         <v>45295</v>
@@ -3729,7 +3954,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="64" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="B64" t="s">
         <v>28</v>
       </c>
@@ -3744,11 +3969,11 @@
       </c>
       <c r="H64" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I64" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="J64" s="2">
         <v>45295</v>
@@ -3782,11 +4007,11 @@
       </c>
       <c r="H65" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I65" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="K65" s="4" t="str">
         <f t="shared" si="4"/>
@@ -3817,11 +4042,11 @@
       </c>
       <c r="H66" s="4">
         <f t="shared" ref="H66:H91" ca="1" si="8">IF(QUOTIENT(_xlfn.DAYS(TODAY(),G66), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),G66), 7), "-")</f>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I66" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="K66" s="4" t="str">
         <f t="shared" si="4"/>
@@ -3855,11 +4080,11 @@
       </c>
       <c r="H67" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I67" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="K67" s="4" t="str">
         <f t="shared" si="4"/>
@@ -3905,11 +4130,11 @@
       </c>
       <c r="H68" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I68" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="K68" s="4" t="str">
         <f t="shared" si="4"/>
@@ -3955,11 +4180,11 @@
       </c>
       <c r="H69" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I69" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="K69" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4005,11 +4230,11 @@
       </c>
       <c r="H70" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I70" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="K70" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4055,11 +4280,11 @@
       </c>
       <c r="H71" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I71" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="K71" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4105,11 +4330,11 @@
       </c>
       <c r="H72" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I72" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="K72" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4155,11 +4380,11 @@
       </c>
       <c r="H73" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I73" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="K73" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4205,11 +4430,11 @@
       </c>
       <c r="H74" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I74" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="K74" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4255,11 +4480,11 @@
       </c>
       <c r="H75" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I75" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="K75" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4305,11 +4530,11 @@
       </c>
       <c r="H76" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I76" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="K76" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4355,11 +4580,11 @@
       </c>
       <c r="H77" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I77" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="K77" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4405,11 +4630,11 @@
       </c>
       <c r="H78" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I78" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="K78" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4455,11 +4680,11 @@
       </c>
       <c r="H79" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I79" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="K79" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4505,11 +4730,11 @@
       </c>
       <c r="H80" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I80" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="K80" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4555,11 +4780,11 @@
       </c>
       <c r="H81" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I81" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="K81" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4605,11 +4830,11 @@
       </c>
       <c r="H82" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I82" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="K82" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4655,11 +4880,11 @@
       </c>
       <c r="H83" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I83" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="K83" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4705,11 +4930,11 @@
       </c>
       <c r="H84" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I84" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="K84" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4755,11 +4980,11 @@
       </c>
       <c r="H85" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I85" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="K85" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4805,11 +5030,11 @@
       </c>
       <c r="H86" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I86" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="K86" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4855,11 +5080,11 @@
       </c>
       <c r="H87" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I87" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="J87" s="2">
         <v>45272</v>
@@ -4899,11 +5124,11 @@
       </c>
       <c r="H88" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I88" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="J88" s="2">
         <v>45273</v>
@@ -4943,11 +5168,11 @@
       </c>
       <c r="H89" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I89" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="J89" s="2">
         <v>45274</v>
@@ -4987,11 +5212,11 @@
       </c>
       <c r="H90" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I90" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="J90" s="2">
         <v>45275</v>
@@ -5031,11 +5256,11 @@
       </c>
       <c r="H91" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I91" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="J91" s="2">
         <v>45276</v>
@@ -5075,11 +5300,11 @@
       </c>
       <c r="H92" s="4">
         <f t="shared" ref="H92:H93" ca="1" si="9">IF(QUOTIENT(_xlfn.DAYS(TODAY(),G92), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),G92), 7), "-")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I92" s="4">
         <f t="shared" ref="I92:I93" ca="1" si="10">IF(_xlfn.DAYS(TODAY(),G92)&lt;10000, _xlfn.DAYS(TODAY(),G92), "-")</f>
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="J92" s="2">
         <v>45277</v>
@@ -5119,11 +5344,11 @@
       </c>
       <c r="H93" s="4">
         <f t="shared" ca="1" si="9"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I93" s="4">
         <f t="shared" ca="1" si="10"/>
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="J93" s="2">
         <v>45278</v>
@@ -5163,11 +5388,11 @@
       </c>
       <c r="H94" s="4">
         <f t="shared" ref="H94" ca="1" si="11">IF(QUOTIENT(_xlfn.DAYS(TODAY(),G94), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),G94), 7), "-")</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I94" s="4">
         <f t="shared" ref="I94" ca="1" si="12">IF(_xlfn.DAYS(TODAY(),G94)&lt;10000, _xlfn.DAYS(TODAY(),G94), "-")</f>
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="J94" s="2">
         <v>45223</v>
@@ -5213,17 +5438,17 @@
       </c>
       <c r="H95" s="4">
         <f t="shared" ref="H95:H117" ca="1" si="13">IF(QUOTIENT(_xlfn.DAYS(TODAY(),G95), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),G95), 7), "-")</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I95" s="4">
         <f t="shared" ref="I95:I117" ca="1" si="14">IF(_xlfn.DAYS(TODAY(),G95)&lt;10000, _xlfn.DAYS(TODAY(),G95), "-")</f>
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="J95" s="2">
         <v>45223</v>
       </c>
       <c r="K95" s="4">
-        <f t="shared" ref="K95:K123" si="15">IF(_xlfn.DAYS(J95,G95)&gt;0, _xlfn.DAYS(J95,G95), "-")</f>
+        <f t="shared" ref="K95:K124" si="15">IF(_xlfn.DAYS(J95,G95)&gt;0, _xlfn.DAYS(J95,G95), "-")</f>
         <v>21</v>
       </c>
       <c r="L95" t="s">
@@ -5263,11 +5488,11 @@
       </c>
       <c r="H96" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I96" s="4">
         <f t="shared" ca="1" si="14"/>
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="J96" s="2">
         <v>45223</v>
@@ -5313,11 +5538,11 @@
       </c>
       <c r="H97" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I97" s="4">
         <f t="shared" ca="1" si="14"/>
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="J97" s="2">
         <v>45223</v>
@@ -5367,7 +5592,7 @@
       </c>
       <c r="I98" s="4">
         <f t="shared" ref="I98:I107" ca="1" si="17">IF(_xlfn.DAYS(TODAY(),G98)&lt;10000, _xlfn.DAYS(TODAY(),G98), "-")</f>
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="J98" s="2">
         <v>45267</v>
@@ -5417,7 +5642,7 @@
       </c>
       <c r="I99" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="J99" s="2">
         <v>45267</v>
@@ -5467,7 +5692,7 @@
       </c>
       <c r="I100" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="J100" s="2">
         <v>45267</v>
@@ -5517,7 +5742,7 @@
       </c>
       <c r="I101" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="J101" s="2">
         <v>45267</v>
@@ -5567,7 +5792,7 @@
       </c>
       <c r="I102" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="J102" s="2">
         <v>45267</v>
@@ -5617,7 +5842,7 @@
       </c>
       <c r="I103" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="J103" s="2">
         <v>45267</v>
@@ -5667,7 +5892,7 @@
       </c>
       <c r="I104" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="J104" s="2">
         <v>45267</v>
@@ -5717,7 +5942,7 @@
       </c>
       <c r="I105" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="J105" s="2">
         <v>45267</v>
@@ -5767,7 +5992,7 @@
       </c>
       <c r="I106" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="J106" s="2">
         <v>45267</v>
@@ -5817,7 +6042,7 @@
       </c>
       <c r="I107" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="J107" s="2">
         <v>45267</v>
@@ -5873,6 +6098,9 @@
       <c r="M108" t="s">
         <v>69</v>
       </c>
+      <c r="O108" s="2">
+        <v>45306</v>
+      </c>
       <c r="P108" s="2" t="s">
         <v>71</v>
       </c>
@@ -5911,6 +6139,9 @@
       <c r="M109" t="s">
         <v>69</v>
       </c>
+      <c r="O109" s="2">
+        <v>45306</v>
+      </c>
       <c r="P109" s="2" t="s">
         <v>71</v>
       </c>
@@ -6066,6 +6297,9 @@
       <c r="M113" t="s">
         <v>69</v>
       </c>
+      <c r="O113" s="2">
+        <v>45298</v>
+      </c>
       <c r="P113" s="2" t="s">
         <v>71</v>
       </c>
@@ -6145,9 +6379,6 @@
       <c r="M115" t="s">
         <v>70</v>
       </c>
-      <c r="O115" s="2">
-        <v>45292</v>
-      </c>
       <c r="P115" s="2" t="s">
         <v>71</v>
       </c>
@@ -6228,7 +6459,7 @@
         <v>70</v>
       </c>
       <c r="O117" s="2">
-        <v>45292</v>
+        <v>45308</v>
       </c>
       <c r="P117" s="2" t="s">
         <v>71</v>
@@ -6254,11 +6485,11 @@
         <v>62</v>
       </c>
       <c r="H118" s="4" t="str">
-        <f t="shared" ref="H118:H123" ca="1" si="18">IF(QUOTIENT(_xlfn.DAYS(TODAY(),G118), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),G118), 7), "-")</f>
+        <f t="shared" ref="H118:H124" ca="1" si="18">IF(QUOTIENT(_xlfn.DAYS(TODAY(),G118), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),G118), 7), "-")</f>
         <v>-</v>
       </c>
       <c r="I118" s="4" t="str">
-        <f t="shared" ref="I118:I123" ca="1" si="19">IF(_xlfn.DAYS(TODAY(),G118)&lt;10000, _xlfn.DAYS(TODAY(),G118), "-")</f>
+        <f t="shared" ref="I118:I124" ca="1" si="19">IF(_xlfn.DAYS(TODAY(),G118)&lt;10000, _xlfn.DAYS(TODAY(),G118), "-")</f>
         <v>-</v>
       </c>
       <c r="K118" s="4" t="str">
@@ -6267,6 +6498,9 @@
       </c>
       <c r="M118" t="s">
         <v>70</v>
+      </c>
+      <c r="O118" s="2">
+        <v>45657</v>
       </c>
       <c r="P118" s="2" t="s">
         <v>71</v>
@@ -6335,7 +6569,7 @@
       </c>
       <c r="I120" s="4">
         <f t="shared" ca="1" si="19"/>
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K120" s="4" t="str">
         <f t="shared" si="15"/>
@@ -6364,7 +6598,7 @@
       </c>
       <c r="I121" s="4">
         <f t="shared" ca="1" si="19"/>
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K121" s="4" t="str">
         <f t="shared" si="15"/>
@@ -6393,7 +6627,7 @@
       </c>
       <c r="I122" s="4">
         <f t="shared" ca="1" si="19"/>
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K122" s="4" t="str">
         <f t="shared" si="15"/>
@@ -6422,7 +6656,7 @@
       </c>
       <c r="I123" s="4">
         <f t="shared" ca="1" si="19"/>
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K123" s="4" t="str">
         <f t="shared" si="15"/>
@@ -6432,8 +6666,208 @@
         <v>95</v>
       </c>
     </row>
+    <row r="124" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B124" t="s">
+        <v>123</v>
+      </c>
+      <c r="C124" t="s">
+        <v>112</v>
+      </c>
+      <c r="E124" t="s">
+        <v>16</v>
+      </c>
+      <c r="G124" s="2">
+        <v>45304</v>
+      </c>
+      <c r="H124" s="4">
+        <f t="shared" ca="1" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="I124" s="4">
+        <f t="shared" ca="1" si="19"/>
+        <v>6</v>
+      </c>
+      <c r="K124" s="4" t="str">
+        <f t="shared" si="15"/>
+        <v>-</v>
+      </c>
+      <c r="M124" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q124" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="125" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B125" t="s">
+        <v>123</v>
+      </c>
+      <c r="C125" t="s">
+        <v>112</v>
+      </c>
+      <c r="E125" t="s">
+        <v>16</v>
+      </c>
+      <c r="G125" s="2">
+        <v>45304</v>
+      </c>
+      <c r="H125" s="4">
+        <f t="shared" ref="H125:H127" ca="1" si="20">IF(QUOTIENT(_xlfn.DAYS(TODAY(),G125), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),G125), 7), "-")</f>
+        <v>0</v>
+      </c>
+      <c r="I125" s="4">
+        <f t="shared" ref="I125:I127" ca="1" si="21">IF(_xlfn.DAYS(TODAY(),G125)&lt;10000, _xlfn.DAYS(TODAY(),G125), "-")</f>
+        <v>6</v>
+      </c>
+      <c r="M125" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q125" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="126" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B126" t="s">
+        <v>123</v>
+      </c>
+      <c r="C126" t="s">
+        <v>112</v>
+      </c>
+      <c r="E126" t="s">
+        <v>16</v>
+      </c>
+      <c r="G126" s="2">
+        <v>45304</v>
+      </c>
+      <c r="H126" s="4">
+        <f t="shared" ca="1" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="I126" s="4">
+        <f t="shared" ca="1" si="21"/>
+        <v>6</v>
+      </c>
+      <c r="M126" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q126" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="127" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B127" t="s">
+        <v>123</v>
+      </c>
+      <c r="C127" t="s">
+        <v>112</v>
+      </c>
+      <c r="E127" t="s">
+        <v>16</v>
+      </c>
+      <c r="G127" s="2">
+        <v>45304</v>
+      </c>
+      <c r="H127" s="4">
+        <f t="shared" ca="1" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="I127" s="4">
+        <f t="shared" ca="1" si="21"/>
+        <v>6</v>
+      </c>
+      <c r="M127" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q127" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="128" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B128" t="s">
+        <v>125</v>
+      </c>
+      <c r="C128" t="s">
+        <v>112</v>
+      </c>
+      <c r="E128" t="s">
+        <v>16</v>
+      </c>
+      <c r="G128" s="2">
+        <v>45309</v>
+      </c>
+      <c r="H128" s="4">
+        <f t="shared" ref="H128:H130" ca="1" si="22">IF(QUOTIENT(_xlfn.DAYS(TODAY(),G128), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),G128), 7), "-")</f>
+        <v>0</v>
+      </c>
+      <c r="I128" s="4">
+        <f t="shared" ref="I128:I130" ca="1" si="23">IF(_xlfn.DAYS(TODAY(),G128)&lt;10000, _xlfn.DAYS(TODAY(),G128), "-")</f>
+        <v>1</v>
+      </c>
+      <c r="M128" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q128" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="129" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B129" t="s">
+        <v>125</v>
+      </c>
+      <c r="C129" t="s">
+        <v>112</v>
+      </c>
+      <c r="E129" t="s">
+        <v>16</v>
+      </c>
+      <c r="G129" s="2">
+        <v>45309</v>
+      </c>
+      <c r="H129" s="4">
+        <f t="shared" ca="1" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="I129" s="4">
+        <f t="shared" ca="1" si="23"/>
+        <v>1</v>
+      </c>
+      <c r="M129" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q129" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="130" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B130" t="s">
+        <v>125</v>
+      </c>
+      <c r="C130" t="s">
+        <v>112</v>
+      </c>
+      <c r="E130" t="s">
+        <v>16</v>
+      </c>
+      <c r="G130" s="2">
+        <v>45309</v>
+      </c>
+      <c r="H130" s="4">
+        <f t="shared" ca="1" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="I130" s="4">
+        <f t="shared" ca="1" si="23"/>
+        <v>1</v>
+      </c>
+      <c r="M130" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q130" t="s">
+        <v>133</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="B1:Q123" xr:uid="{47ECCD65-6802-4B2B-901A-AED4A431A765}">
+  <autoFilter ref="B1:Q130" xr:uid="{47ECCD65-6802-4B2B-901A-AED4A431A765}">
     <filterColumn colId="0">
       <filters>
         <filter val="SPF"/>
@@ -6445,13 +6879,13 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E125 E127:E1048576" xr:uid="{939E2B39-E841-4A9F-AD11-00C266DB2690}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E1048576" xr:uid="{939E2B39-E841-4A9F-AD11-00C266DB2690}">
       <formula1>"Y, N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L1:L125 L127:L1048576" xr:uid="{2DE54AC7-5B92-48D6-98C4-E6203F87CDD0}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L1:L1048576" xr:uid="{2DE54AC7-5B92-48D6-98C4-E6203F87CDD0}">
       <formula1>"M, F"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B125 B127:B1048576" xr:uid="{ACC76399-D52A-490E-9FEF-427013FFE2CE}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B1048576" xr:uid="{ACC76399-D52A-490E-9FEF-427013FFE2CE}">
       <formula1>"SPF, 5F"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Mouse 내역.xlsx
+++ b/Mouse 내역.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\heung\OneDrive\바탕 화면\동물실\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{065F5C17-C291-4E26-B412-1B16C97B6FC6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36E3689C-F7DE-456A-9973-25B0928AB2EE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19080" windowHeight="9180" activeTab="1" xr2:uid="{5A73A69A-2AFB-4F3E-AC64-070DD7700CB2}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19080" windowHeight="9180" xr2:uid="{5A73A69A-2AFB-4F3E-AC64-070DD7700CB2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -774,9 +774,6 @@
     <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -830,6 +827,9 @@
     </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1595,16 +1595,16 @@
       <c r="D6">
         <v>872</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="E6" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="20" t="s">
+      <c r="F6" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="G6" s="21">
+      <c r="G6" s="20">
         <v>45266</v>
       </c>
-      <c r="H6" s="22">
+      <c r="H6" s="21">
         <f t="shared" ca="1" si="1"/>
         <v>6</v>
       </c>
@@ -1612,22 +1612,22 @@
         <f t="shared" ca="1" si="2"/>
         <v>44</v>
       </c>
-      <c r="J6" s="21">
+      <c r="J6" s="20">
         <v>45293</v>
       </c>
       <c r="K6" s="4">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="L6" s="27" t="s">
+      <c r="L6" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="M6" s="27" t="s">
+      <c r="M6" s="26" t="s">
         <v>79</v>
       </c>
       <c r="N6" s="7"/>
-      <c r="O6" s="29"/>
-      <c r="Q6" s="27" t="s">
+      <c r="O6" s="28"/>
+      <c r="Q6" s="26" t="s">
         <v>128</v>
       </c>
     </row>
@@ -1641,16 +1641,16 @@
       <c r="D7">
         <v>873</v>
       </c>
-      <c r="E7" s="23" t="s">
+      <c r="E7" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="16" t="s">
+      <c r="F7" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="G7" s="17">
+      <c r="G7" s="16">
         <v>45266</v>
       </c>
-      <c r="H7" s="24">
+      <c r="H7" s="23">
         <f t="shared" ca="1" si="1"/>
         <v>6</v>
       </c>
@@ -1658,22 +1658,22 @@
         <f t="shared" ca="1" si="2"/>
         <v>44</v>
       </c>
-      <c r="J7" s="17">
+      <c r="J7" s="16">
         <v>45293</v>
       </c>
       <c r="K7" s="4">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="L7" s="28" t="s">
+      <c r="L7" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="M7" s="28" t="s">
+      <c r="M7" s="27" t="s">
         <v>79</v>
       </c>
       <c r="N7" s="7"/>
-      <c r="O7" s="30"/>
-      <c r="Q7" s="28" t="s">
+      <c r="O7" s="29"/>
+      <c r="Q7" s="27" t="s">
         <v>128</v>
       </c>
     </row>
@@ -1687,16 +1687,16 @@
       <c r="D8">
         <v>874</v>
       </c>
-      <c r="E8" s="25" t="s">
+      <c r="E8" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="18" t="s">
+      <c r="F8" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="G8" s="15">
+      <c r="G8" s="14">
         <v>45266</v>
       </c>
-      <c r="H8" s="26">
+      <c r="H8" s="25">
         <f t="shared" ca="1" si="1"/>
         <v>6</v>
       </c>
@@ -1704,22 +1704,22 @@
         <f t="shared" ca="1" si="2"/>
         <v>44</v>
       </c>
-      <c r="J8" s="15">
+      <c r="J8" s="14">
         <v>45293</v>
       </c>
       <c r="K8" s="4">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="L8" s="18" t="s">
+      <c r="L8" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="M8" s="18" t="s">
+      <c r="M8" s="17" t="s">
         <v>79</v>
       </c>
       <c r="N8" s="7"/>
-      <c r="O8" s="31"/>
-      <c r="Q8" s="18" t="s">
+      <c r="O8" s="30"/>
+      <c r="Q8" s="17" t="s">
         <v>128</v>
       </c>
     </row>
@@ -2492,16 +2492,16 @@
       <c r="C28" t="s">
         <v>21</v>
       </c>
-      <c r="E28" s="19" t="s">
+      <c r="E28" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="F28" s="20" t="s">
+      <c r="F28" s="19" t="s">
         <v>130</v>
       </c>
-      <c r="G28" s="21">
+      <c r="G28" s="20">
         <v>45203</v>
       </c>
-      <c r="H28" s="22">
+      <c r="H28" s="21">
         <f t="shared" ca="1" si="1"/>
         <v>15</v>
       </c>
@@ -2509,21 +2509,21 @@
         <f t="shared" ca="1" si="2"/>
         <v>107</v>
       </c>
-      <c r="J28" s="21">
+      <c r="J28" s="20">
         <v>45229</v>
       </c>
       <c r="K28" s="4">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="L28" s="27" t="s">
+      <c r="L28" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="M28" s="27" t="s">
+      <c r="M28" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="O28" s="21"/>
-      <c r="Q28" s="27" t="s">
+      <c r="O28" s="20"/>
+      <c r="Q28" s="26" t="s">
         <v>127</v>
       </c>
     </row>
@@ -2534,16 +2534,16 @@
       <c r="C29" t="s">
         <v>114</v>
       </c>
-      <c r="E29" s="25" t="s">
+      <c r="E29" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="F29" s="14" t="s">
+      <c r="F29" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="G29" s="15">
+      <c r="G29" s="14">
         <v>45203</v>
       </c>
-      <c r="H29" s="26">
+      <c r="H29" s="25">
         <f t="shared" ca="1" si="1"/>
         <v>15</v>
       </c>
@@ -2551,21 +2551,21 @@
         <f t="shared" ca="1" si="2"/>
         <v>107</v>
       </c>
-      <c r="J29" s="15">
+      <c r="J29" s="14">
         <v>45229</v>
       </c>
       <c r="K29" s="4">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="L29" s="18" t="s">
+      <c r="L29" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="M29" s="18" t="s">
+      <c r="M29" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="O29" s="15"/>
-      <c r="Q29" s="18" t="s">
+      <c r="O29" s="14"/>
+      <c r="Q29" s="17" t="s">
         <v>127</v>
       </c>
     </row>
@@ -6910,10 +6910,10 @@
       <c r="E2" t="s">
         <v>78</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="G2" s="31" t="s">
         <v>92</v>
       </c>
-      <c r="H2" s="13"/>
+      <c r="H2" s="31"/>
     </row>
     <row r="3" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C3" t="s">

--- a/Mouse 내역.xlsx
+++ b/Mouse 내역.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\heung\OneDrive\바탕 화면\동물실\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36E3689C-F7DE-456A-9973-25B0928AB2EE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{110A8AF2-15BB-465E-8ADC-3FE7C908FA0D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19080" windowHeight="9180" xr2:uid="{5A73A69A-2AFB-4F3E-AC64-070DD7700CB2}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="930" uniqueCount="135">
   <si>
     <t>Strain</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -524,14 +524,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>R1, L1 확인</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tag 떨어짐 다시 확인</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>A3.B</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -549,6 +541,18 @@
   </si>
   <si>
     <t>같이 weaning</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>왼쪽 Tag, 오른쪽 아래 punch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오른쪽 tag</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>왼쪽 tag, 오른쪽 위 punch</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -660,7 +664,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -698,24 +702,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -734,7 +720,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -774,31 +760,10 @@
     <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
@@ -807,25 +772,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1449,7 +1402,7 @@
       </c>
       <c r="I2" s="4">
         <f ca="1">IF(_xlfn.DAYS(TODAY(),G2)&lt;10000, _xlfn.DAYS(TODAY(),G2), "-")</f>
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="K2" s="4" t="str">
         <f t="shared" ref="K2:K31" si="0">IF(_xlfn.DAYS(J2,G2)&gt;0, _xlfn.DAYS(J2,G2), "-")</f>
@@ -1488,7 +1441,7 @@
       </c>
       <c r="I3" s="4">
         <f t="shared" ref="I3:I31" ca="1" si="2">IF(_xlfn.DAYS(TODAY(),G3)&lt;10000, _xlfn.DAYS(TODAY(),G3), "-")</f>
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="K3" s="4" t="str">
         <f t="shared" si="0"/>
@@ -1525,7 +1478,7 @@
       </c>
       <c r="I4" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="K4" s="4" t="str">
         <f t="shared" si="0"/>
@@ -1561,11 +1514,11 @@
       </c>
       <c r="H5" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I5" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="J5" s="2">
         <v>45293</v>
@@ -1593,42 +1546,42 @@
         <v>112</v>
       </c>
       <c r="D6">
-        <v>872</v>
-      </c>
-      <c r="E6" s="18" t="s">
+        <v>686</v>
+      </c>
+      <c r="E6" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="19" t="s">
+      <c r="F6" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="G6" s="20">
+      <c r="G6" s="14">
         <v>45266</v>
       </c>
-      <c r="H6" s="21">
+      <c r="H6" s="16">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I6" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>44</v>
-      </c>
-      <c r="J6" s="20">
+        <v>49</v>
+      </c>
+      <c r="J6" s="14">
         <v>45293</v>
       </c>
       <c r="K6" s="4">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="L6" s="26" t="s">
+      <c r="L6" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="M6" s="26" t="s">
+      <c r="M6" s="17" t="s">
         <v>79</v>
       </c>
       <c r="N6" s="7"/>
-      <c r="O6" s="28"/>
-      <c r="Q6" s="26" t="s">
-        <v>128</v>
+      <c r="O6" s="18"/>
+      <c r="Q6" s="17" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.3">
@@ -1639,45 +1592,45 @@
         <v>112</v>
       </c>
       <c r="D7">
-        <v>873</v>
-      </c>
-      <c r="E7" s="22" t="s">
+        <v>687</v>
+      </c>
+      <c r="E7" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="15" t="s">
+      <c r="F7" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="14">
         <v>45266</v>
       </c>
-      <c r="H7" s="23">
+      <c r="H7" s="16">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I7" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>44</v>
-      </c>
-      <c r="J7" s="16">
+        <v>49</v>
+      </c>
+      <c r="J7" s="14">
         <v>45293</v>
       </c>
       <c r="K7" s="4">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="L7" s="27" t="s">
+      <c r="L7" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="M7" s="27" t="s">
+      <c r="M7" s="17" t="s">
         <v>79</v>
       </c>
       <c r="N7" s="7"/>
-      <c r="O7" s="29"/>
-      <c r="Q7" s="27" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="8" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="O7" s="18"/>
+      <c r="Q7" s="17" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="8" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>5</v>
       </c>
@@ -1685,9 +1638,9 @@
         <v>112</v>
       </c>
       <c r="D8">
-        <v>874</v>
-      </c>
-      <c r="E8" s="24" t="s">
+        <v>688</v>
+      </c>
+      <c r="E8" s="15" t="s">
         <v>15</v>
       </c>
       <c r="F8" s="17" t="s">
@@ -1696,13 +1649,13 @@
       <c r="G8" s="14">
         <v>45266</v>
       </c>
-      <c r="H8" s="25">
+      <c r="H8" s="16">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I8" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="J8" s="14">
         <v>45293</v>
@@ -1718,9 +1671,9 @@
         <v>79</v>
       </c>
       <c r="N8" s="7"/>
-      <c r="O8" s="30"/>
+      <c r="O8" s="18"/>
       <c r="Q8" s="17" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.3">
@@ -1744,11 +1697,11 @@
       </c>
       <c r="H9" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I9" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="J9" s="2">
         <v>45293</v>
@@ -1787,11 +1740,11 @@
       </c>
       <c r="H10" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I10" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="J10" s="2">
         <v>45293</v>
@@ -1832,11 +1785,11 @@
       </c>
       <c r="H11" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I11" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="J11" s="2">
         <v>45293</v>
@@ -1878,7 +1831,7 @@
       </c>
       <c r="I12" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="K12" s="4" t="str">
         <f t="shared" si="0"/>
@@ -1988,11 +1941,11 @@
       </c>
       <c r="H15" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I15" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="K15" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2028,11 +1981,11 @@
       </c>
       <c r="H16" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I16" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="K16" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2068,11 +2021,11 @@
       </c>
       <c r="H17" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I17" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="K17" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2106,11 +2059,11 @@
       </c>
       <c r="H18" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I18" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="K18" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2120,7 +2073,7 @@
         <v>11</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="19" spans="2:17" x14ac:dyDescent="0.3">
@@ -2144,11 +2097,11 @@
       </c>
       <c r="H19" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I19" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="K19" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2179,11 +2132,11 @@
       </c>
       <c r="H20" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I20" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="K20" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2252,11 +2205,11 @@
       </c>
       <c r="H22" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I22" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="J22" s="2">
         <v>45112</v>
@@ -2293,11 +2246,11 @@
       </c>
       <c r="H23" s="4">
         <f ca="1">IF(QUOTIENT(_xlfn.DAYS(TODAY(),G23), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),G23), 7), "-")</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I23" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="J23" s="2">
         <v>45176</v>
@@ -2337,11 +2290,11 @@
       </c>
       <c r="H24" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I24" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="J24" s="2">
         <v>45176</v>
@@ -2381,11 +2334,11 @@
       </c>
       <c r="H25" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I25" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="J25" s="2">
         <v>45176</v>
@@ -2425,11 +2378,11 @@
       </c>
       <c r="H26" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I26" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="J26" s="2">
         <v>45176</v>
@@ -2464,11 +2417,11 @@
       </c>
       <c r="H27" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I27" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="J27" s="2">
         <v>45176</v>
@@ -2485,71 +2438,71 @@
       </c>
       <c r="Q27" s="2"/>
     </row>
-    <row r="28" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>5</v>
       </c>
       <c r="C28" t="s">
         <v>21</v>
       </c>
-      <c r="E28" s="18" t="s">
+      <c r="E28" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="F28" s="19" t="s">
-        <v>130</v>
-      </c>
-      <c r="G28" s="20">
+      <c r="F28" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="G28" s="14">
         <v>45203</v>
       </c>
-      <c r="H28" s="21">
+      <c r="H28" s="16">
         <f t="shared" ca="1" si="1"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I28" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>107</v>
-      </c>
-      <c r="J28" s="20">
+        <v>112</v>
+      </c>
+      <c r="J28" s="14">
         <v>45229</v>
       </c>
       <c r="K28" s="4">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="L28" s="26" t="s">
+      <c r="L28" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="M28" s="26" t="s">
+      <c r="M28" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="O28" s="20"/>
-      <c r="Q28" s="26" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="29" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="O28" s="14">
+        <v>45310</v>
+      </c>
+      <c r="Q28" s="17"/>
+    </row>
+    <row r="29" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
         <v>5</v>
       </c>
       <c r="C29" t="s">
         <v>114</v>
       </c>
-      <c r="E29" s="24" t="s">
+      <c r="E29" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="F29" s="13" t="s">
+      <c r="F29" s="19" t="s">
         <v>113</v>
       </c>
       <c r="G29" s="14">
         <v>45203</v>
       </c>
-      <c r="H29" s="25">
+      <c r="H29" s="16">
         <f t="shared" ca="1" si="1"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I29" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="J29" s="14">
         <v>45229</v>
@@ -2564,10 +2517,10 @@
       <c r="M29" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="O29" s="14"/>
-      <c r="Q29" s="17" t="s">
-        <v>127</v>
-      </c>
+      <c r="O29" s="14">
+        <v>45310</v>
+      </c>
+      <c r="Q29" s="17"/>
     </row>
     <row r="30" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
@@ -2580,18 +2533,18 @@
         <v>8</v>
       </c>
       <c r="F30" s="10" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G30" s="2">
         <v>45203</v>
       </c>
       <c r="H30" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I30" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="J30" s="2">
         <v>45229</v>
@@ -2604,7 +2557,7 @@
         <v>13</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="Q30" s="2"/>
     </row>
@@ -2619,18 +2572,18 @@
         <v>8</v>
       </c>
       <c r="F31" s="10" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G31" s="2">
         <v>45203</v>
       </c>
       <c r="H31" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I31" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="J31" s="2">
         <v>45229</v>
@@ -2643,7 +2596,7 @@
         <v>13</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="Q31" s="2"/>
     </row>
@@ -2658,18 +2611,18 @@
         <v>8</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G32" s="2">
         <v>45203</v>
       </c>
       <c r="H32" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I32" s="4">
         <f t="shared" ref="I32:I38" ca="1" si="3">IF(_xlfn.DAYS(TODAY(),G32)&lt;10000, _xlfn.DAYS(TODAY(),G32), "-")</f>
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="J32" s="2">
         <v>45229</v>
@@ -2742,11 +2695,11 @@
       </c>
       <c r="H34" s="4">
         <f ca="1">IF(QUOTIENT(_xlfn.DAYS(TODAY(),G34), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),G34), 7), "-")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I34" s="4">
         <f ca="1">IF(_xlfn.DAYS(TODAY(),G34)&lt;10000, _xlfn.DAYS(TODAY(),G34), "-")</f>
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="J34" s="2">
         <v>45257</v>
@@ -2865,11 +2818,11 @@
       </c>
       <c r="H37" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I37" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="J37" s="2">
         <v>45257</v>
@@ -2912,11 +2865,11 @@
       </c>
       <c r="H38" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I38" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="J38" s="2">
         <v>45257</v>
@@ -2959,11 +2912,11 @@
       </c>
       <c r="H39" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I39" s="4">
         <f t="shared" ref="I39:I41" ca="1" si="5">IF(_xlfn.DAYS(TODAY(),G39)&lt;10000, _xlfn.DAYS(TODAY(),G39), "-")</f>
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="J39" s="2">
         <v>45257</v>
@@ -2999,18 +2952,18 @@
         <v>8</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G40" s="2">
         <v>45231</v>
       </c>
       <c r="H40" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I40" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="J40" s="2">
         <v>45257</v>
@@ -3047,11 +3000,11 @@
       </c>
       <c r="H41" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I41" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="J41" s="2">
         <v>45257</v>
@@ -3092,7 +3045,7 @@
       </c>
       <c r="I42" s="4">
         <f t="shared" ref="I42" ca="1" si="6">IF(_xlfn.DAYS(TODAY(),G42)&lt;10000, _xlfn.DAYS(TODAY(),G42), "-")</f>
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="K42" s="4" t="str">
         <f t="shared" si="4"/>
@@ -3133,7 +3086,7 @@
       </c>
       <c r="I43" s="4">
         <f t="shared" ref="I43:I91" ca="1" si="7">IF(_xlfn.DAYS(TODAY(),G43)&lt;10000, _xlfn.DAYS(TODAY(),G43), "-")</f>
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="K43" s="4" t="str">
         <f t="shared" si="4"/>
@@ -3171,7 +3124,7 @@
       </c>
       <c r="I44" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="J44" s="2">
         <v>45293</v>
@@ -3215,7 +3168,7 @@
       </c>
       <c r="I45" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="J45" s="2">
         <v>45293</v>
@@ -3259,7 +3212,7 @@
       </c>
       <c r="I46" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="J46" s="2">
         <v>45293</v>
@@ -3306,7 +3259,7 @@
       </c>
       <c r="I47" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="J47" s="2">
         <v>45293</v>
@@ -3349,11 +3302,11 @@
       </c>
       <c r="H48" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I48" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J48" s="2">
         <v>45293</v>
@@ -3380,7 +3333,7 @@
         <v>5</v>
       </c>
       <c r="C49" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D49">
         <v>821</v>
@@ -3389,7 +3342,7 @@
         <v>8</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G49" s="2">
         <v>45267</v>
@@ -3400,7 +3353,7 @@
       </c>
       <c r="I49" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="J49" s="2">
         <v>45293</v>
@@ -3421,7 +3374,7 @@
         <v>5</v>
       </c>
       <c r="C50" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D50">
         <v>822</v>
@@ -3430,7 +3383,7 @@
         <v>8</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G50" s="2">
         <v>45267</v>
@@ -3441,7 +3394,7 @@
       </c>
       <c r="I50" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="J50" s="2">
         <v>45293</v>
@@ -3482,7 +3435,7 @@
       </c>
       <c r="I51" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="J51" s="2">
         <v>45293</v>
@@ -3522,11 +3475,11 @@
       </c>
       <c r="H52" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I52" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J52" s="2">
         <v>45293</v>
@@ -3550,7 +3503,7 @@
         <v>5</v>
       </c>
       <c r="C53" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D53">
         <v>825</v>
@@ -3559,18 +3512,18 @@
         <v>8</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G53" s="2">
         <v>45271</v>
       </c>
       <c r="H53" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I53" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J53" s="2">
         <v>45293</v>
@@ -3607,11 +3560,11 @@
       </c>
       <c r="H54" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I54" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="J54" s="2">
         <v>45238</v>
@@ -3648,11 +3601,11 @@
       </c>
       <c r="H55" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I55" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="J55" s="2">
         <v>45238</v>
@@ -3689,11 +3642,11 @@
       </c>
       <c r="H56" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I56" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="J56" s="2">
         <v>45238</v>
@@ -3727,11 +3680,11 @@
       </c>
       <c r="H57" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I57" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="K57" s="4" t="str">
         <f t="shared" si="4"/>
@@ -3762,11 +3715,11 @@
       </c>
       <c r="H58" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I58" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="K58" s="4" t="str">
         <f t="shared" si="4"/>
@@ -3798,7 +3751,7 @@
       </c>
       <c r="I59" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="J59" s="2">
         <v>45295</v>
@@ -3833,7 +3786,7 @@
       </c>
       <c r="I60" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="J60" s="2">
         <v>45295</v>
@@ -3868,7 +3821,7 @@
       </c>
       <c r="I61" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="J61" s="2">
         <v>45295</v>
@@ -3903,7 +3856,7 @@
       </c>
       <c r="I62" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="J62" s="2">
         <v>45295</v>
@@ -3938,7 +3891,7 @@
       </c>
       <c r="I63" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="J63" s="2">
         <v>45295</v>
@@ -3973,7 +3926,7 @@
       </c>
       <c r="I64" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="J64" s="2">
         <v>45295</v>
@@ -4007,11 +3960,11 @@
       </c>
       <c r="H65" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I65" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="K65" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4042,11 +3995,11 @@
       </c>
       <c r="H66" s="4">
         <f t="shared" ref="H66:H91" ca="1" si="8">IF(QUOTIENT(_xlfn.DAYS(TODAY(),G66), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),G66), 7), "-")</f>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I66" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="K66" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4080,11 +4033,11 @@
       </c>
       <c r="H67" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I67" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="K67" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4130,11 +4083,11 @@
       </c>
       <c r="H68" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I68" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="K68" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4180,11 +4133,11 @@
       </c>
       <c r="H69" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I69" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="K69" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4230,11 +4183,11 @@
       </c>
       <c r="H70" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I70" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="K70" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4280,11 +4233,11 @@
       </c>
       <c r="H71" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I71" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="K71" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4330,11 +4283,11 @@
       </c>
       <c r="H72" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I72" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="K72" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4380,11 +4333,11 @@
       </c>
       <c r="H73" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I73" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="K73" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4430,11 +4383,11 @@
       </c>
       <c r="H74" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I74" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="K74" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4480,11 +4433,11 @@
       </c>
       <c r="H75" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I75" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="K75" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4530,11 +4483,11 @@
       </c>
       <c r="H76" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I76" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="K76" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4580,11 +4533,11 @@
       </c>
       <c r="H77" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I77" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="K77" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4630,11 +4583,11 @@
       </c>
       <c r="H78" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I78" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="K78" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4680,11 +4633,11 @@
       </c>
       <c r="H79" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I79" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="K79" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4730,11 +4683,11 @@
       </c>
       <c r="H80" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I80" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="K80" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4780,11 +4733,11 @@
       </c>
       <c r="H81" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I81" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="K81" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4830,11 +4783,11 @@
       </c>
       <c r="H82" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I82" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="K82" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4880,11 +4833,11 @@
       </c>
       <c r="H83" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I83" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="K83" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4930,11 +4883,11 @@
       </c>
       <c r="H84" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I84" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="K84" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4980,11 +4933,11 @@
       </c>
       <c r="H85" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I85" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="K85" s="4" t="str">
         <f t="shared" si="4"/>
@@ -5030,11 +4983,11 @@
       </c>
       <c r="H86" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I86" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="K86" s="4" t="str">
         <f t="shared" si="4"/>
@@ -5080,11 +5033,11 @@
       </c>
       <c r="H87" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I87" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="J87" s="2">
         <v>45272</v>
@@ -5124,11 +5077,11 @@
       </c>
       <c r="H88" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I88" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="J88" s="2">
         <v>45273</v>
@@ -5168,11 +5121,11 @@
       </c>
       <c r="H89" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I89" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="J89" s="2">
         <v>45274</v>
@@ -5212,11 +5165,11 @@
       </c>
       <c r="H90" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I90" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="J90" s="2">
         <v>45275</v>
@@ -5256,11 +5209,11 @@
       </c>
       <c r="H91" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I91" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="J91" s="2">
         <v>45276</v>
@@ -5300,11 +5253,11 @@
       </c>
       <c r="H92" s="4">
         <f t="shared" ref="H92:H93" ca="1" si="9">IF(QUOTIENT(_xlfn.DAYS(TODAY(),G92), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),G92), 7), "-")</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I92" s="4">
         <f t="shared" ref="I92:I93" ca="1" si="10">IF(_xlfn.DAYS(TODAY(),G92)&lt;10000, _xlfn.DAYS(TODAY(),G92), "-")</f>
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="J92" s="2">
         <v>45277</v>
@@ -5344,11 +5297,11 @@
       </c>
       <c r="H93" s="4">
         <f t="shared" ca="1" si="9"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I93" s="4">
         <f t="shared" ca="1" si="10"/>
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="J93" s="2">
         <v>45278</v>
@@ -5388,11 +5341,11 @@
       </c>
       <c r="H94" s="4">
         <f t="shared" ref="H94" ca="1" si="11">IF(QUOTIENT(_xlfn.DAYS(TODAY(),G94), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),G94), 7), "-")</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I94" s="4">
         <f t="shared" ref="I94" ca="1" si="12">IF(_xlfn.DAYS(TODAY(),G94)&lt;10000, _xlfn.DAYS(TODAY(),G94), "-")</f>
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="J94" s="2">
         <v>45223</v>
@@ -5438,11 +5391,11 @@
       </c>
       <c r="H95" s="4">
         <f t="shared" ref="H95:H117" ca="1" si="13">IF(QUOTIENT(_xlfn.DAYS(TODAY(),G95), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),G95), 7), "-")</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I95" s="4">
         <f t="shared" ref="I95:I117" ca="1" si="14">IF(_xlfn.DAYS(TODAY(),G95)&lt;10000, _xlfn.DAYS(TODAY(),G95), "-")</f>
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="J95" s="2">
         <v>45223</v>
@@ -5488,11 +5441,11 @@
       </c>
       <c r="H96" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I96" s="4">
         <f t="shared" ca="1" si="14"/>
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="J96" s="2">
         <v>45223</v>
@@ -5538,11 +5491,11 @@
       </c>
       <c r="H97" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I97" s="4">
         <f t="shared" ca="1" si="14"/>
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="J97" s="2">
         <v>45223</v>
@@ -5588,11 +5541,11 @@
       </c>
       <c r="H98" s="4">
         <f t="shared" ref="H98:H107" ca="1" si="16">IF(QUOTIENT(_xlfn.DAYS(TODAY(),G98), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),G98), 7), "-")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I98" s="4">
         <f t="shared" ref="I98:I107" ca="1" si="17">IF(_xlfn.DAYS(TODAY(),G98)&lt;10000, _xlfn.DAYS(TODAY(),G98), "-")</f>
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="J98" s="2">
         <v>45267</v>
@@ -5638,11 +5591,11 @@
       </c>
       <c r="H99" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I99" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="J99" s="2">
         <v>45267</v>
@@ -5688,11 +5641,11 @@
       </c>
       <c r="H100" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I100" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="J100" s="2">
         <v>45267</v>
@@ -5738,11 +5691,11 @@
       </c>
       <c r="H101" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I101" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="J101" s="2">
         <v>45267</v>
@@ -5788,11 +5741,11 @@
       </c>
       <c r="H102" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I102" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="J102" s="2">
         <v>45267</v>
@@ -5838,11 +5791,11 @@
       </c>
       <c r="H103" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I103" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="J103" s="2">
         <v>45267</v>
@@ -5888,11 +5841,11 @@
       </c>
       <c r="H104" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I104" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="J104" s="2">
         <v>45267</v>
@@ -5938,11 +5891,11 @@
       </c>
       <c r="H105" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I105" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="J105" s="2">
         <v>45267</v>
@@ -5988,11 +5941,11 @@
       </c>
       <c r="H106" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I106" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="J106" s="2">
         <v>45267</v>
@@ -6038,11 +5991,11 @@
       </c>
       <c r="H107" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I107" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="J107" s="2">
         <v>45267</v>
@@ -6180,6 +6133,9 @@
       <c r="M110" t="s">
         <v>69</v>
       </c>
+      <c r="O110" s="2">
+        <v>45312</v>
+      </c>
       <c r="P110" s="2" t="s">
         <v>71</v>
       </c>
@@ -6218,6 +6174,9 @@
       <c r="M111" t="s">
         <v>69</v>
       </c>
+      <c r="O111" s="2">
+        <v>45312</v>
+      </c>
       <c r="P111" s="2" t="s">
         <v>71</v>
       </c>
@@ -6565,11 +6524,11 @@
       </c>
       <c r="H120" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I120" s="4">
         <f t="shared" ca="1" si="19"/>
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K120" s="4" t="str">
         <f t="shared" si="15"/>
@@ -6594,11 +6553,11 @@
       </c>
       <c r="H121" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I121" s="4">
         <f t="shared" ca="1" si="19"/>
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K121" s="4" t="str">
         <f t="shared" si="15"/>
@@ -6623,11 +6582,11 @@
       </c>
       <c r="H122" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I122" s="4">
         <f t="shared" ca="1" si="19"/>
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K122" s="4" t="str">
         <f t="shared" si="15"/>
@@ -6652,11 +6611,11 @@
       </c>
       <c r="H123" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I123" s="4">
         <f t="shared" ca="1" si="19"/>
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K123" s="4" t="str">
         <f t="shared" si="15"/>
@@ -6681,11 +6640,11 @@
       </c>
       <c r="H124" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I124" s="4">
         <f t="shared" ca="1" si="19"/>
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="K124" s="4" t="str">
         <f t="shared" si="15"/>
@@ -6695,7 +6654,7 @@
         <v>124</v>
       </c>
       <c r="Q124" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="125" spans="2:17" x14ac:dyDescent="0.3">
@@ -6713,17 +6672,17 @@
       </c>
       <c r="H125" s="4">
         <f t="shared" ref="H125:H127" ca="1" si="20">IF(QUOTIENT(_xlfn.DAYS(TODAY(),G125), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),G125), 7), "-")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I125" s="4">
         <f t="shared" ref="I125:I127" ca="1" si="21">IF(_xlfn.DAYS(TODAY(),G125)&lt;10000, _xlfn.DAYS(TODAY(),G125), "-")</f>
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="M125" t="s">
         <v>124</v>
       </c>
       <c r="Q125" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="126" spans="2:17" x14ac:dyDescent="0.3">
@@ -6741,17 +6700,17 @@
       </c>
       <c r="H126" s="4">
         <f t="shared" ca="1" si="20"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I126" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="M126" t="s">
         <v>124</v>
       </c>
       <c r="Q126" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="127" spans="2:17" x14ac:dyDescent="0.3">
@@ -6769,17 +6728,17 @@
       </c>
       <c r="H127" s="4">
         <f t="shared" ca="1" si="20"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I127" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="M127" t="s">
         <v>124</v>
       </c>
       <c r="Q127" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="128" spans="2:17" x14ac:dyDescent="0.3">
@@ -6801,13 +6760,13 @@
       </c>
       <c r="I128" s="4">
         <f t="shared" ref="I128:I130" ca="1" si="23">IF(_xlfn.DAYS(TODAY(),G128)&lt;10000, _xlfn.DAYS(TODAY(),G128), "-")</f>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M128" t="s">
         <v>126</v>
       </c>
       <c r="Q128" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="129" spans="2:17" x14ac:dyDescent="0.3">
@@ -6829,13 +6788,13 @@
       </c>
       <c r="I129" s="4">
         <f t="shared" ca="1" si="23"/>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M129" t="s">
         <v>126</v>
       </c>
       <c r="Q129" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="130" spans="2:17" x14ac:dyDescent="0.3">
@@ -6857,13 +6816,13 @@
       </c>
       <c r="I130" s="4">
         <f t="shared" ca="1" si="23"/>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M130" t="s">
         <v>126</v>
       </c>
       <c r="Q130" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -6910,10 +6869,10 @@
       <c r="E2" t="s">
         <v>78</v>
       </c>
-      <c r="G2" s="31" t="s">
+      <c r="G2" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="H2" s="31"/>
+      <c r="H2" s="20"/>
     </row>
     <row r="3" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C3" t="s">

--- a/Mouse 내역.xlsx
+++ b/Mouse 내역.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\heung\OneDrive\바탕 화면\동물실\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{110A8AF2-15BB-465E-8ADC-3FE7C908FA0D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60EE4730-FC04-4ADC-BD4C-3E10FA7997B0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19080" windowHeight="9180" xr2:uid="{5A73A69A-2AFB-4F3E-AC64-070DD7700CB2}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$Q$130</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$Q$137</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="930" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="983" uniqueCount="153">
   <si>
     <t>Strain</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -194,14 +194,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>D1.2.F</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>D1.2.M</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>D1.1.M</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -405,10 +397,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>A2.2.X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>+/+; f/+</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -472,22 +460,12 @@
     <t>Weaned; or Provisino date</t>
   </si>
   <si>
-    <t>Tmem119 Cre-ERT2; Cd36 flox</t>
-  </si>
-  <si>
     <t>Cre/+; f/+</t>
   </si>
   <si>
     <t>LysM Cre; Cd36 flox</t>
   </si>
   <si>
-    <t>Tmem119 Cre-ERT2; Cd36 flox</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tmem119 Cre-ERT2; Tsg101 flox</t>
-  </si>
-  <si>
     <t>+/+; f/+</t>
   </si>
   <si>
@@ -536,10 +514,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Cd36 flox</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>같이 weaning</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -553,6 +527,101 @@
   </si>
   <si>
     <t>왼쪽 tag, 오른쪽 위 punch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>H1.B (A2.1.F)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>H1.B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Y</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A2.2.M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A2.2.F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tmem119-CreERT2; Cd36 flox</t>
+  </si>
+  <si>
+    <t>Tmem119-CreERT2; Tsg101 flox</t>
+  </si>
+  <si>
+    <t>Tmem119-CreERT2; Tsg101-flox</t>
+  </si>
+  <si>
+    <t>Tmem119-CreERT2; Tsg101-flox</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tmem119-CreERT2; Cd36-flox</t>
+  </si>
+  <si>
+    <t>Cd36-flox</t>
+  </si>
+  <si>
+    <t>F1.B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>G1.B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cre/+; f/+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cre/+; +/+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Passage: 7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D1.2.M_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D1.2.M_2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D1.2.F_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D1.2.F_2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Exp. 1-9-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cre/Cre; f/+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>+/+; f/+</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -720,7 +789,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -781,6 +850,12 @@
     <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -792,7 +867,18 @@
     <cellStyle name="좋음" xfId="1" builtinId="26"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1310,7 +1396,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D71A6DC-E91C-489F-8F50-989C4712FA7C}">
   <sheetPr filterMode="1"/>
-  <dimension ref="B1:Q130"/>
+  <dimension ref="B1:Q137"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="10.5" customWidth="1"/>
@@ -1326,7 +1412,7 @@
     <col min="12" max="12" width="6.375" customWidth="1"/>
     <col min="14" max="14" width="13.125" style="2" hidden="1" customWidth="1"/>
     <col min="15" max="15" width="12.75" style="2" customWidth="1"/>
-    <col min="16" max="16" width="13.25" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="13.25" customWidth="1"/>
     <col min="17" max="17" width="19.875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1338,7 +1424,7 @@
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>6</v>
@@ -1356,7 +1442,7 @@
         <v>9</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="K1" s="8" t="s">
         <v>14</v>
@@ -1365,7 +1451,7 @@
         <v>3</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="N1" s="3" t="s">
         <v>18</v>
@@ -1374,10 +1460,10 @@
         <v>17</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -1385,13 +1471,13 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="G2" s="2">
         <v>45135</v>
@@ -1402,7 +1488,7 @@
       </c>
       <c r="I2" s="4">
         <f ca="1">IF(_xlfn.DAYS(TODAY(),G2)&lt;10000, _xlfn.DAYS(TODAY(),G2), "-")</f>
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K2" s="4" t="str">
         <f t="shared" ref="K2:K31" si="0">IF(_xlfn.DAYS(J2,G2)&gt;0, _xlfn.DAYS(J2,G2), "-")</f>
@@ -1412,7 +1498,7 @@
         <v>11</v>
       </c>
       <c r="M2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="N2" s="7"/>
       <c r="O2" s="7">
@@ -1424,13 +1510,13 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>115</v>
+        <v>139</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="G3" s="2">
         <v>45135</v>
@@ -1441,7 +1527,7 @@
       </c>
       <c r="I3" s="4">
         <f t="shared" ref="I3:I31" ca="1" si="2">IF(_xlfn.DAYS(TODAY(),G3)&lt;10000, _xlfn.DAYS(TODAY(),G3), "-")</f>
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K3" s="4" t="str">
         <f t="shared" si="0"/>
@@ -1450,8 +1536,8 @@
       <c r="L3" t="s">
         <v>13</v>
       </c>
-      <c r="M3" s="1" t="s">
-        <v>52</v>
+      <c r="M3" s="4" t="s">
+        <v>50</v>
       </c>
       <c r="N3" s="7"/>
       <c r="O3" s="7"/>
@@ -1461,13 +1547,13 @@
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>112</v>
+        <v>139</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="G4" s="2">
         <v>45135</v>
@@ -1478,7 +1564,7 @@
       </c>
       <c r="I4" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K4" s="4" t="str">
         <f t="shared" si="0"/>
@@ -1487,8 +1573,8 @@
       <c r="L4" t="s">
         <v>13</v>
       </c>
-      <c r="M4" s="1" t="s">
-        <v>52</v>
+      <c r="M4" s="4" t="s">
+        <v>50</v>
       </c>
       <c r="N4" s="7"/>
       <c r="O4" s="7"/>
@@ -1498,7 +1584,7 @@
         <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="D5">
         <v>871</v>
@@ -1507,7 +1593,7 @@
         <v>16</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G5" s="2">
         <v>45266</v>
@@ -1518,7 +1604,7 @@
       </c>
       <c r="I5" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J5" s="2">
         <v>45293</v>
@@ -1528,10 +1614,10 @@
         <v>27</v>
       </c>
       <c r="L5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="M5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="N5" s="7"/>
       <c r="O5" s="7">
@@ -1543,16 +1629,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>112</v>
+        <v>139</v>
       </c>
       <c r="D6">
         <v>686</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="13" t="s">
-        <v>99</v>
+      <c r="F6" s="20" t="s">
+        <v>96</v>
       </c>
       <c r="G6" s="14">
         <v>45266</v>
@@ -1563,7 +1649,7 @@
       </c>
       <c r="I6" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J6" s="14">
         <v>45293</v>
@@ -1573,15 +1659,15 @@
         <v>27</v>
       </c>
       <c r="L6" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="M6" s="17" t="s">
         <v>79</v>
+      </c>
+      <c r="M6" s="16" t="s">
+        <v>128</v>
       </c>
       <c r="N6" s="7"/>
       <c r="O6" s="18"/>
       <c r="Q6" s="17" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.3">
@@ -1589,16 +1675,16 @@
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>112</v>
+        <v>139</v>
       </c>
       <c r="D7">
         <v>687</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" s="16" t="s">
         <v>16</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="G7" s="14">
         <v>45266</v>
@@ -1609,7 +1695,7 @@
       </c>
       <c r="I7" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J7" s="14">
         <v>45293</v>
@@ -1619,23 +1705,23 @@
         <v>27</v>
       </c>
       <c r="L7" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="M7" s="17" t="s">
         <v>79</v>
+      </c>
+      <c r="M7" s="16" t="s">
+        <v>77</v>
       </c>
       <c r="N7" s="7"/>
       <c r="O7" s="18"/>
       <c r="Q7" s="17" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.3">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="8" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="D8">
         <v>688</v>
@@ -1644,7 +1730,7 @@
         <v>15</v>
       </c>
       <c r="F8" s="17" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="G8" s="14">
         <v>45266</v>
@@ -1655,7 +1741,7 @@
       </c>
       <c r="I8" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J8" s="14">
         <v>45293</v>
@@ -1665,15 +1751,17 @@
         <v>27</v>
       </c>
       <c r="L8" s="17" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="M8" s="17" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="N8" s="7"/>
-      <c r="O8" s="18"/>
+      <c r="O8" s="18">
+        <v>45315</v>
+      </c>
       <c r="Q8" s="17" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.3">
@@ -1681,7 +1769,7 @@
         <v>5</v>
       </c>
       <c r="C9" t="s">
-        <v>112</v>
+        <v>139</v>
       </c>
       <c r="D9">
         <v>921</v>
@@ -1690,7 +1778,7 @@
         <v>15</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G9" s="2">
         <v>45266</v>
@@ -1701,7 +1789,7 @@
       </c>
       <c r="I9" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J9" s="2">
         <v>45293</v>
@@ -1711,10 +1799,10 @@
         <v>27</v>
       </c>
       <c r="L9" t="s">
-        <v>82</v>
-      </c>
-      <c r="M9" t="s">
         <v>80</v>
+      </c>
+      <c r="M9" s="4" t="s">
+        <v>78</v>
       </c>
       <c r="N9" s="7"/>
       <c r="O9" s="7"/>
@@ -1724,7 +1812,7 @@
         <v>5</v>
       </c>
       <c r="C10" t="s">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="D10">
         <v>922</v>
@@ -1733,7 +1821,7 @@
         <v>15</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G10" s="2">
         <v>45266</v>
@@ -1744,7 +1832,7 @@
       </c>
       <c r="I10" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J10" s="2">
         <v>45293</v>
@@ -1754,10 +1842,10 @@
         <v>27</v>
       </c>
       <c r="L10" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="M10" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="N10" s="7"/>
       <c r="O10" s="7">
@@ -1769,7 +1857,7 @@
         <v>5</v>
       </c>
       <c r="C11" t="s">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="D11">
         <v>923</v>
@@ -1778,7 +1866,7 @@
         <v>15</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="G11" s="2">
         <v>45266</v>
@@ -1789,7 +1877,7 @@
       </c>
       <c r="I11" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J11" s="2">
         <v>45293</v>
@@ -1799,10 +1887,10 @@
         <v>27</v>
       </c>
       <c r="L11" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="M11" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="N11" s="7"/>
       <c r="O11" s="7">
@@ -1814,13 +1902,13 @@
         <v>5</v>
       </c>
       <c r="C12" t="s">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="E12" t="s">
         <v>7</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="G12" s="2">
         <v>45135</v>
@@ -1831,7 +1919,7 @@
       </c>
       <c r="I12" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K12" s="4" t="str">
         <f t="shared" si="0"/>
@@ -1841,7 +1929,7 @@
         <v>10</v>
       </c>
       <c r="M12" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="N12" s="7"/>
       <c r="O12" s="7">
@@ -1853,13 +1941,13 @@
         <v>5</v>
       </c>
       <c r="C13" t="s">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="E13" t="s">
         <v>7</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="H13" s="4" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -1877,7 +1965,7 @@
         <v>12</v>
       </c>
       <c r="M13" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="N13" s="7"/>
       <c r="O13" s="7">
@@ -1889,13 +1977,13 @@
         <v>5</v>
       </c>
       <c r="C14" t="s">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="E14" t="s">
         <v>7</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="H14" s="4" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -1913,7 +2001,7 @@
         <v>12</v>
       </c>
       <c r="M14" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="N14" s="7"/>
       <c r="O14" s="7">
@@ -1925,7 +2013,7 @@
         <v>5</v>
       </c>
       <c r="C15" t="s">
-        <v>112</v>
+        <v>139</v>
       </c>
       <c r="D15">
         <v>972</v>
@@ -1934,7 +2022,7 @@
         <v>7</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="G15" s="2">
         <v>45047</v>
@@ -1945,7 +2033,7 @@
       </c>
       <c r="I15" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K15" s="4" t="str">
         <f t="shared" si="0"/>
@@ -1954,8 +2042,8 @@
       <c r="L15" t="s">
         <v>11</v>
       </c>
-      <c r="M15" t="s">
-        <v>54</v>
+      <c r="M15" s="4" t="s">
+        <v>52</v>
       </c>
       <c r="N15" s="7"/>
       <c r="O15" s="7"/>
@@ -1965,7 +2053,7 @@
         <v>5</v>
       </c>
       <c r="C16" t="s">
-        <v>112</v>
+        <v>139</v>
       </c>
       <c r="D16">
         <v>973</v>
@@ -1974,7 +2062,7 @@
         <v>7</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="G16" s="2">
         <v>45047</v>
@@ -1985,7 +2073,7 @@
       </c>
       <c r="I16" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K16" s="4" t="str">
         <f t="shared" si="0"/>
@@ -1994,8 +2082,8 @@
       <c r="L16" t="s">
         <v>11</v>
       </c>
-      <c r="M16" t="s">
-        <v>54</v>
+      <c r="M16" s="4" t="s">
+        <v>52</v>
       </c>
       <c r="N16" s="7"/>
       <c r="O16" s="7"/>
@@ -2005,7 +2093,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="s">
-        <v>112</v>
+        <v>139</v>
       </c>
       <c r="D17">
         <v>974</v>
@@ -2014,7 +2102,7 @@
         <v>7</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="G17" s="2">
         <v>45047</v>
@@ -2025,7 +2113,7 @@
       </c>
       <c r="I17" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K17" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2034,8 +2122,8 @@
       <c r="L17" t="s">
         <v>11</v>
       </c>
-      <c r="M17" t="s">
-        <v>54</v>
+      <c r="M17" s="4" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="18" spans="2:17" x14ac:dyDescent="0.3">
@@ -2043,7 +2131,7 @@
         <v>5</v>
       </c>
       <c r="C18" t="s">
-        <v>112</v>
+        <v>139</v>
       </c>
       <c r="D18">
         <v>975</v>
@@ -2052,7 +2140,7 @@
         <v>7</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="G18" s="2">
         <v>45047</v>
@@ -2063,7 +2151,7 @@
       </c>
       <c r="I18" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K18" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2072,8 +2160,8 @@
       <c r="L18" t="s">
         <v>11</v>
       </c>
-      <c r="M18" s="1" t="s">
-        <v>127</v>
+      <c r="M18" s="4" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="19" spans="2:17" x14ac:dyDescent="0.3">
@@ -2081,7 +2169,7 @@
         <v>5</v>
       </c>
       <c r="C19" t="s">
-        <v>112</v>
+        <v>139</v>
       </c>
       <c r="D19">
         <v>970</v>
@@ -2090,7 +2178,7 @@
         <v>7</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="G19" s="2">
         <v>45047</v>
@@ -2101,7 +2189,7 @@
       </c>
       <c r="I19" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K19" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2110,8 +2198,8 @@
       <c r="L19" t="s">
         <v>11</v>
       </c>
-      <c r="M19" t="s">
-        <v>54</v>
+      <c r="M19" s="4" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="20" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -2119,13 +2207,13 @@
         <v>5</v>
       </c>
       <c r="C20" t="s">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="E20" t="s">
         <v>7</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="G20" s="2">
         <v>45091</v>
@@ -2136,7 +2224,7 @@
       </c>
       <c r="I20" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K20" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2146,7 +2234,7 @@
         <v>11</v>
       </c>
       <c r="M20" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="O20" s="2">
         <v>45299</v>
@@ -2157,13 +2245,13 @@
         <v>5</v>
       </c>
       <c r="C21" t="s">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="E21" t="s">
         <v>7</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="H21" s="4" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -2181,7 +2269,7 @@
         <v>13</v>
       </c>
       <c r="M21" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="O21" s="2">
         <v>45299</v>
@@ -2192,13 +2280,13 @@
         <v>5</v>
       </c>
       <c r="C22" t="s">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="G22" s="2">
         <v>45115</v>
@@ -2209,7 +2297,7 @@
       </c>
       <c r="I22" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="J22" s="2">
         <v>45112</v>
@@ -2222,7 +2310,7 @@
         <v>13</v>
       </c>
       <c r="M22" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O22" s="2">
         <v>45299</v>
@@ -2250,7 +2338,7 @@
       </c>
       <c r="I23" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J23" s="2">
         <v>45176</v>
@@ -2263,13 +2351,13 @@
         <v>11</v>
       </c>
       <c r="M23" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="O23" s="2">
         <v>45306</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="24" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -2294,7 +2382,7 @@
       </c>
       <c r="I24" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J24" s="2">
         <v>45176</v>
@@ -2307,13 +2395,13 @@
         <v>11</v>
       </c>
       <c r="M24" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="O24" s="2">
         <v>45306</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="25" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -2338,7 +2426,7 @@
       </c>
       <c r="I25" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J25" s="2">
         <v>45176</v>
@@ -2351,13 +2439,13 @@
         <v>11</v>
       </c>
       <c r="M25" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="O25" s="2">
         <v>45306</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="26" spans="2:17" x14ac:dyDescent="0.3">
@@ -2365,7 +2453,7 @@
         <v>5</v>
       </c>
       <c r="C26" t="s">
-        <v>21</v>
+        <v>140</v>
       </c>
       <c r="E26" t="s">
         <v>7</v>
@@ -2382,7 +2470,7 @@
       </c>
       <c r="I26" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J26" s="2">
         <v>45176</v>
@@ -2394,8 +2482,8 @@
       <c r="L26" t="s">
         <v>11</v>
       </c>
-      <c r="M26" t="s">
-        <v>57</v>
+      <c r="M26" s="4" t="s">
+        <v>55</v>
       </c>
       <c r="Q26" s="2"/>
     </row>
@@ -2404,7 +2492,7 @@
         <v>5</v>
       </c>
       <c r="C27" t="s">
-        <v>21</v>
+        <v>140</v>
       </c>
       <c r="E27" t="s">
         <v>7</v>
@@ -2421,7 +2509,7 @@
       </c>
       <c r="I27" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J27" s="2">
         <v>45176</v>
@@ -2433,8 +2521,8 @@
       <c r="L27" t="s">
         <v>11</v>
       </c>
-      <c r="M27" t="s">
-        <v>57</v>
+      <c r="M27" s="4" t="s">
+        <v>55</v>
       </c>
       <c r="Q27" s="2"/>
     </row>
@@ -2449,7 +2537,7 @@
         <v>16</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="G28" s="14">
         <v>45203</v>
@@ -2460,7 +2548,7 @@
       </c>
       <c r="I28" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J28" s="14">
         <v>45229</v>
@@ -2473,7 +2561,7 @@
         <v>11</v>
       </c>
       <c r="M28" s="17" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="O28" s="14">
         <v>45310</v>
@@ -2485,13 +2573,13 @@
         <v>5</v>
       </c>
       <c r="C29" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E29" s="15" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="19" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="G29" s="14">
         <v>45203</v>
@@ -2502,7 +2590,7 @@
       </c>
       <c r="I29" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J29" s="14">
         <v>45229</v>
@@ -2515,7 +2603,7 @@
         <v>11</v>
       </c>
       <c r="M29" s="17" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="O29" s="14">
         <v>45310</v>
@@ -2527,13 +2615,13 @@
         <v>5</v>
       </c>
       <c r="C30" t="s">
-        <v>21</v>
+        <v>140</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
       </c>
       <c r="F30" s="10" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="G30" s="2">
         <v>45203</v>
@@ -2544,7 +2632,7 @@
       </c>
       <c r="I30" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J30" s="2">
         <v>45229</v>
@@ -2556,8 +2644,8 @@
       <c r="L30" t="s">
         <v>13</v>
       </c>
-      <c r="M30" s="1" t="s">
-        <v>127</v>
+      <c r="M30" s="4" t="s">
+        <v>121</v>
       </c>
       <c r="Q30" s="2"/>
     </row>
@@ -2566,13 +2654,13 @@
         <v>5</v>
       </c>
       <c r="C31" t="s">
-        <v>21</v>
+        <v>140</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
       </c>
       <c r="F31" s="10" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="G31" s="2">
         <v>45203</v>
@@ -2583,7 +2671,7 @@
       </c>
       <c r="I31" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J31" s="2">
         <v>45229</v>
@@ -2595,8 +2683,8 @@
       <c r="L31" t="s">
         <v>13</v>
       </c>
-      <c r="M31" s="1" t="s">
-        <v>127</v>
+      <c r="M31" s="4" t="s">
+        <v>121</v>
       </c>
       <c r="Q31" s="2"/>
     </row>
@@ -2605,13 +2693,13 @@
         <v>5</v>
       </c>
       <c r="C32" t="s">
-        <v>21</v>
+        <v>140</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="G32" s="2">
         <v>45203</v>
@@ -2622,7 +2710,7 @@
       </c>
       <c r="I32" s="4">
         <f t="shared" ref="I32:I38" ca="1" si="3">IF(_xlfn.DAYS(TODAY(),G32)&lt;10000, _xlfn.DAYS(TODAY(),G32), "-")</f>
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J32" s="2">
         <v>45229</v>
@@ -2634,8 +2722,8 @@
       <c r="L32" t="s">
         <v>13</v>
       </c>
-      <c r="M32" t="s">
-        <v>59</v>
+      <c r="M32" s="4" t="s">
+        <v>57</v>
       </c>
       <c r="Q32" s="2"/>
     </row>
@@ -2644,13 +2732,13 @@
         <v>5</v>
       </c>
       <c r="C33" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="H33" s="4" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -2668,7 +2756,7 @@
         <v>11</v>
       </c>
       <c r="M33" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="O33" s="2">
         <v>45299</v>
@@ -2679,7 +2767,7 @@
         <v>5</v>
       </c>
       <c r="C34" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D34" t="s">
         <v>25</v>
@@ -2688,7 +2776,7 @@
         <v>8</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G34" s="2">
         <v>45231</v>
@@ -2699,7 +2787,7 @@
       </c>
       <c r="I34" s="4">
         <f ca="1">IF(_xlfn.DAYS(TODAY(),G34)&lt;10000, _xlfn.DAYS(TODAY(),G34), "-")</f>
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J34" s="2">
         <v>45257</v>
@@ -2712,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="M34" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O34" s="2">
         <v>45306</v>
       </c>
       <c r="Q34" s="2" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="35" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -2726,13 +2814,13 @@
         <v>5</v>
       </c>
       <c r="C35" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="H35" s="4" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -2750,13 +2838,13 @@
         <v>13</v>
       </c>
       <c r="M35" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O35" s="2">
         <v>45306</v>
       </c>
       <c r="Q35" s="2" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="36" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -2764,13 +2852,13 @@
         <v>5</v>
       </c>
       <c r="C36" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="H36" s="4" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -2788,13 +2876,13 @@
         <v>13</v>
       </c>
       <c r="M36" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O36" s="2">
         <v>45306</v>
       </c>
       <c r="Q36" s="2" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="37" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -2802,7 +2890,7 @@
         <v>5</v>
       </c>
       <c r="C37" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D37" t="s">
         <v>24</v>
@@ -2811,7 +2899,7 @@
         <v>8</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G37" s="2">
         <v>45231</v>
@@ -2822,7 +2910,7 @@
       </c>
       <c r="I37" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J37" s="2">
         <v>45257</v>
@@ -2835,13 +2923,13 @@
         <v>13</v>
       </c>
       <c r="M37" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="O37" s="2">
         <v>45306</v>
       </c>
       <c r="Q37" s="2" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="38" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -2849,7 +2937,7 @@
         <v>5</v>
       </c>
       <c r="C38" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D38" t="s">
         <v>25</v>
@@ -2858,7 +2946,7 @@
         <v>8</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G38" s="2">
         <v>45231</v>
@@ -2869,7 +2957,7 @@
       </c>
       <c r="I38" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J38" s="2">
         <v>45257</v>
@@ -2882,13 +2970,13 @@
         <v>13</v>
       </c>
       <c r="M38" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="O38" s="2">
         <v>45306</v>
       </c>
       <c r="Q38" s="2" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="39" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -2896,7 +2984,7 @@
         <v>5</v>
       </c>
       <c r="C39" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D39" t="s">
         <v>26</v>
@@ -2905,7 +2993,7 @@
         <v>8</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G39" s="2">
         <v>45231</v>
@@ -2916,7 +3004,7 @@
       </c>
       <c r="I39" s="4">
         <f t="shared" ref="I39:I41" ca="1" si="5">IF(_xlfn.DAYS(TODAY(),G39)&lt;10000, _xlfn.DAYS(TODAY(),G39), "-")</f>
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J39" s="2">
         <v>45257</v>
@@ -2929,16 +3017,16 @@
         <v>13</v>
       </c>
       <c r="M39" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="O39" s="2">
         <v>45306</v>
       </c>
       <c r="Q39" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.3">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="40" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B40" t="s">
         <v>5</v>
       </c>
@@ -2952,7 +3040,7 @@
         <v>8</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="G40" s="2">
         <v>45231</v>
@@ -2963,7 +3051,7 @@
       </c>
       <c r="I40" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J40" s="2">
         <v>45257</v>
@@ -2976,15 +3064,18 @@
         <v>11</v>
       </c>
       <c r="M40" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.3">
+        <v>63</v>
+      </c>
+      <c r="O40" s="2">
+        <v>45315</v>
+      </c>
+    </row>
+    <row r="41" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B41" t="s">
         <v>5</v>
       </c>
       <c r="C41" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D41" t="s">
         <v>26</v>
@@ -2993,7 +3084,7 @@
         <v>8</v>
       </c>
       <c r="F41" s="12" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G41" s="2">
         <v>45231</v>
@@ -3004,7 +3095,7 @@
       </c>
       <c r="I41" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J41" s="2">
         <v>45257</v>
@@ -3017,7 +3108,10 @@
         <v>11</v>
       </c>
       <c r="M41" t="s">
-        <v>65</v>
+        <v>63</v>
+      </c>
+      <c r="O41" s="2">
+        <v>45315</v>
       </c>
     </row>
     <row r="42" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -3025,7 +3119,7 @@
         <v>5</v>
       </c>
       <c r="C42" t="s">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="D42">
         <v>798</v>
@@ -3034,7 +3128,7 @@
         <v>8</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="G42" s="2">
         <v>45135</v>
@@ -3045,7 +3139,7 @@
       </c>
       <c r="I42" s="4">
         <f t="shared" ref="I42" ca="1" si="6">IF(_xlfn.DAYS(TODAY(),G42)&lt;10000, _xlfn.DAYS(TODAY(),G42), "-")</f>
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K42" s="4" t="str">
         <f t="shared" si="4"/>
@@ -3066,7 +3160,7 @@
         <v>5</v>
       </c>
       <c r="C43" t="s">
-        <v>112</v>
+        <v>139</v>
       </c>
       <c r="D43">
         <v>799</v>
@@ -3075,7 +3169,7 @@
         <v>8</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="G43" s="2">
         <v>45135</v>
@@ -3086,7 +3180,7 @@
       </c>
       <c r="I43" s="4">
         <f t="shared" ref="I43:I91" ca="1" si="7">IF(_xlfn.DAYS(TODAY(),G43)&lt;10000, _xlfn.DAYS(TODAY(),G43), "-")</f>
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K43" s="4" t="str">
         <f t="shared" si="4"/>
@@ -3095,7 +3189,7 @@
       <c r="L43" t="s">
         <v>13</v>
       </c>
-      <c r="M43" t="s">
+      <c r="M43" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -3104,7 +3198,7 @@
         <v>5</v>
       </c>
       <c r="C44" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D44">
         <v>815</v>
@@ -3113,18 +3207,18 @@
         <v>8</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G44" s="2">
         <v>45267</v>
       </c>
       <c r="H44" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I44" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J44" s="2">
         <v>45293</v>
@@ -3134,10 +3228,10 @@
         <v>26</v>
       </c>
       <c r="L44" t="s">
+        <v>79</v>
+      </c>
+      <c r="M44" t="s">
         <v>81</v>
-      </c>
-      <c r="M44" t="s">
-        <v>83</v>
       </c>
       <c r="O44" s="7">
         <v>45309</v>
@@ -3148,7 +3242,7 @@
         <v>5</v>
       </c>
       <c r="C45" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D45">
         <v>816</v>
@@ -3157,18 +3251,18 @@
         <v>8</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G45" s="2">
         <v>45267</v>
       </c>
       <c r="H45" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I45" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J45" s="2">
         <v>45293</v>
@@ -3178,10 +3272,10 @@
         <v>26</v>
       </c>
       <c r="L45" t="s">
+        <v>79</v>
+      </c>
+      <c r="M45" t="s">
         <v>81</v>
-      </c>
-      <c r="M45" t="s">
-        <v>83</v>
       </c>
       <c r="O45" s="7">
         <v>45309</v>
@@ -3192,7 +3286,7 @@
         <v>5</v>
       </c>
       <c r="C46" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D46">
         <v>817</v>
@@ -3201,18 +3295,18 @@
         <v>8</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G46" s="2">
         <v>45267</v>
       </c>
       <c r="H46" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I46" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J46" s="2">
         <v>45293</v>
@@ -3222,16 +3316,16 @@
         <v>26</v>
       </c>
       <c r="L46" t="s">
+        <v>79</v>
+      </c>
+      <c r="M46" t="s">
         <v>81</v>
-      </c>
-      <c r="M46" t="s">
-        <v>83</v>
       </c>
       <c r="O46" s="2">
         <v>45306</v>
       </c>
       <c r="Q46" s="2" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="47" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -3239,7 +3333,7 @@
         <v>5</v>
       </c>
       <c r="C47" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D47">
         <v>819</v>
@@ -3248,18 +3342,18 @@
         <v>8</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G47" s="2">
         <v>45267</v>
       </c>
       <c r="H47" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I47" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J47" s="2">
         <v>45293</v>
@@ -3269,16 +3363,16 @@
         <v>26</v>
       </c>
       <c r="L47" t="s">
+        <v>79</v>
+      </c>
+      <c r="M47" t="s">
         <v>81</v>
-      </c>
-      <c r="M47" t="s">
-        <v>83</v>
       </c>
       <c r="O47" s="2">
         <v>45306</v>
       </c>
       <c r="Q47" s="2" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="48" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -3286,7 +3380,7 @@
         <v>5</v>
       </c>
       <c r="C48" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D48">
         <v>820</v>
@@ -3295,7 +3389,7 @@
         <v>8</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G48" s="2">
         <v>45271</v>
@@ -3306,7 +3400,7 @@
       </c>
       <c r="I48" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J48" s="2">
         <v>45293</v>
@@ -3316,16 +3410,16 @@
         <v>22</v>
       </c>
       <c r="L48" t="s">
+        <v>79</v>
+      </c>
+      <c r="M48" t="s">
         <v>81</v>
-      </c>
-      <c r="M48" t="s">
-        <v>83</v>
       </c>
       <c r="O48" s="2">
         <v>45306</v>
       </c>
       <c r="Q48" s="2" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="49" spans="2:15" x14ac:dyDescent="0.3">
@@ -3333,7 +3427,7 @@
         <v>5</v>
       </c>
       <c r="C49" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="D49">
         <v>821</v>
@@ -3342,18 +3436,18 @@
         <v>8</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="G49" s="2">
         <v>45267</v>
       </c>
       <c r="H49" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I49" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J49" s="2">
         <v>45293</v>
@@ -3363,10 +3457,10 @@
         <v>26</v>
       </c>
       <c r="L49" t="s">
+        <v>80</v>
+      </c>
+      <c r="M49" s="4" t="s">
         <v>82</v>
-      </c>
-      <c r="M49" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="50" spans="2:15" x14ac:dyDescent="0.3">
@@ -3374,7 +3468,7 @@
         <v>5</v>
       </c>
       <c r="C50" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="D50">
         <v>822</v>
@@ -3383,18 +3477,18 @@
         <v>8</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="G50" s="2">
         <v>45267</v>
       </c>
       <c r="H50" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I50" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J50" s="2">
         <v>45293</v>
@@ -3404,10 +3498,10 @@
         <v>26</v>
       </c>
       <c r="L50" t="s">
+        <v>80</v>
+      </c>
+      <c r="M50" t="s">
         <v>82</v>
-      </c>
-      <c r="M50" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="51" spans="2:15" hidden="1" x14ac:dyDescent="0.3">
@@ -3415,7 +3509,7 @@
         <v>5</v>
       </c>
       <c r="C51" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D51">
         <v>823</v>
@@ -3424,18 +3518,18 @@
         <v>8</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G51" s="2">
         <v>45267</v>
       </c>
       <c r="H51" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I51" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J51" s="2">
         <v>45293</v>
@@ -3445,10 +3539,10 @@
         <v>26</v>
       </c>
       <c r="L51" t="s">
+        <v>80</v>
+      </c>
+      <c r="M51" t="s">
         <v>82</v>
-      </c>
-      <c r="M51" t="s">
-        <v>84</v>
       </c>
       <c r="O51" s="7">
         <v>45309</v>
@@ -3459,7 +3553,7 @@
         <v>5</v>
       </c>
       <c r="C52" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D52">
         <v>824</v>
@@ -3468,7 +3562,7 @@
         <v>8</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G52" s="2">
         <v>45271</v>
@@ -3479,7 +3573,7 @@
       </c>
       <c r="I52" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J52" s="2">
         <v>45293</v>
@@ -3489,10 +3583,10 @@
         <v>22</v>
       </c>
       <c r="L52" t="s">
+        <v>80</v>
+      </c>
+      <c r="M52" t="s">
         <v>82</v>
-      </c>
-      <c r="M52" t="s">
-        <v>84</v>
       </c>
       <c r="O52" s="7">
         <v>45309</v>
@@ -3503,7 +3597,7 @@
         <v>5</v>
       </c>
       <c r="C53" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="D53">
         <v>825</v>
@@ -3512,7 +3606,7 @@
         <v>8</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="G53" s="2">
         <v>45271</v>
@@ -3523,7 +3617,7 @@
       </c>
       <c r="I53" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J53" s="2">
         <v>45293</v>
@@ -3533,10 +3627,10 @@
         <v>22</v>
       </c>
       <c r="L53" t="s">
+        <v>80</v>
+      </c>
+      <c r="M53" t="s">
         <v>82</v>
-      </c>
-      <c r="M53" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="54" spans="2:15" hidden="1" x14ac:dyDescent="0.3">
@@ -3544,7 +3638,7 @@
         <v>28</v>
       </c>
       <c r="C54" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="D54" t="s">
         <v>29</v>
@@ -3553,7 +3647,7 @@
         <v>32</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="G54" s="2">
         <v>45208</v>
@@ -3564,7 +3658,7 @@
       </c>
       <c r="I54" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J54" s="2">
         <v>45238</v>
@@ -3577,7 +3671,7 @@
         <v>33</v>
       </c>
       <c r="M54" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="55" spans="2:15" hidden="1" x14ac:dyDescent="0.3">
@@ -3585,7 +3679,7 @@
         <v>28</v>
       </c>
       <c r="C55" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="D55" t="s">
         <v>31</v>
@@ -3594,7 +3688,7 @@
         <v>32</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="G55" s="2">
         <v>45208</v>
@@ -3605,7 +3699,7 @@
       </c>
       <c r="I55" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J55" s="2">
         <v>45238</v>
@@ -3618,7 +3712,7 @@
         <v>33</v>
       </c>
       <c r="M55" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="56" spans="2:15" hidden="1" x14ac:dyDescent="0.3">
@@ -3626,7 +3720,7 @@
         <v>28</v>
       </c>
       <c r="C56" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="D56" t="s">
         <v>30</v>
@@ -3635,7 +3729,7 @@
         <v>32</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="G56" s="2">
         <v>45208</v>
@@ -3646,7 +3740,7 @@
       </c>
       <c r="I56" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J56" s="2">
         <v>45238</v>
@@ -3659,7 +3753,7 @@
         <v>33</v>
       </c>
       <c r="M56" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="57" spans="2:15" hidden="1" x14ac:dyDescent="0.3">
@@ -3667,13 +3761,13 @@
         <v>28</v>
       </c>
       <c r="C57" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="E57" t="s">
         <v>32</v>
       </c>
-      <c r="F57" s="6" t="s">
-        <v>120</v>
+      <c r="F57" s="21" t="s">
+        <v>114</v>
       </c>
       <c r="G57" s="2">
         <v>45000</v>
@@ -3684,7 +3778,7 @@
       </c>
       <c r="I57" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K57" s="4" t="str">
         <f t="shared" si="4"/>
@@ -3694,7 +3788,7 @@
         <v>34</v>
       </c>
       <c r="M57" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="58" spans="2:15" hidden="1" x14ac:dyDescent="0.3">
@@ -3702,13 +3796,13 @@
         <v>28</v>
       </c>
       <c r="C58" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="E58" t="s">
         <v>32</v>
       </c>
-      <c r="F58" s="6" t="s">
-        <v>120</v>
+      <c r="F58" s="21" t="s">
+        <v>114</v>
       </c>
       <c r="G58" s="2">
         <v>45000</v>
@@ -3719,7 +3813,7 @@
       </c>
       <c r="I58" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K58" s="4" t="str">
         <f t="shared" si="4"/>
@@ -3729,7 +3823,7 @@
         <v>33</v>
       </c>
       <c r="M58" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="59" spans="2:15" hidden="1" x14ac:dyDescent="0.3">
@@ -3737,7 +3831,7 @@
         <v>28</v>
       </c>
       <c r="C59" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="E59" t="s">
         <v>27</v>
@@ -3747,11 +3841,11 @@
       </c>
       <c r="H59" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I59" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J59" s="2">
         <v>45295</v>
@@ -3761,10 +3855,10 @@
         <v>28</v>
       </c>
       <c r="L59" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="M59" s="4" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="60" spans="2:15" hidden="1" x14ac:dyDescent="0.3">
@@ -3772,7 +3866,7 @@
         <v>28</v>
       </c>
       <c r="C60" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="E60" t="s">
         <v>27</v>
@@ -3782,11 +3876,11 @@
       </c>
       <c r="H60" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I60" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J60" s="2">
         <v>45295</v>
@@ -3796,10 +3890,10 @@
         <v>28</v>
       </c>
       <c r="L60" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="M60" s="4" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="61" spans="2:15" hidden="1" x14ac:dyDescent="0.3">
@@ -3807,7 +3901,7 @@
         <v>28</v>
       </c>
       <c r="C61" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="E61" t="s">
         <v>27</v>
@@ -3817,11 +3911,11 @@
       </c>
       <c r="H61" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I61" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J61" s="2">
         <v>45295</v>
@@ -3831,10 +3925,10 @@
         <v>28</v>
       </c>
       <c r="L61" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="M61" s="4" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="62" spans="2:15" hidden="1" x14ac:dyDescent="0.3">
@@ -3842,7 +3936,7 @@
         <v>28</v>
       </c>
       <c r="C62" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="E62" t="s">
         <v>27</v>
@@ -3852,11 +3946,11 @@
       </c>
       <c r="H62" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I62" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J62" s="2">
         <v>45295</v>
@@ -3866,10 +3960,10 @@
         <v>28</v>
       </c>
       <c r="L62" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="M62" s="4" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="63" spans="2:15" hidden="1" x14ac:dyDescent="0.3">
@@ -3877,7 +3971,7 @@
         <v>28</v>
       </c>
       <c r="C63" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="E63" t="s">
         <v>27</v>
@@ -3887,11 +3981,11 @@
       </c>
       <c r="H63" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I63" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J63" s="2">
         <v>45295</v>
@@ -3901,10 +3995,10 @@
         <v>28</v>
       </c>
       <c r="L63" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="M63" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="64" spans="2:15" hidden="1" x14ac:dyDescent="0.3">
@@ -3912,7 +4006,7 @@
         <v>28</v>
       </c>
       <c r="C64" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="E64" t="s">
         <v>27</v>
@@ -3922,11 +4016,11 @@
       </c>
       <c r="H64" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I64" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J64" s="2">
         <v>45295</v>
@@ -3936,10 +4030,10 @@
         <v>28</v>
       </c>
       <c r="L64" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="M64" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="65" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -3947,13 +4041,13 @@
         <v>28</v>
       </c>
       <c r="C65" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="E65" t="s">
         <v>32</v>
       </c>
-      <c r="F65" s="6" t="s">
-        <v>120</v>
+      <c r="F65" s="21" t="s">
+        <v>114</v>
       </c>
       <c r="G65" s="2">
         <v>45000</v>
@@ -3964,7 +4058,7 @@
       </c>
       <c r="I65" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K65" s="4" t="str">
         <f t="shared" si="4"/>
@@ -3974,7 +4068,7 @@
         <v>33</v>
       </c>
       <c r="M65" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="66" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -3982,13 +4076,13 @@
         <v>28</v>
       </c>
       <c r="C66" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="E66" t="s">
         <v>32</v>
       </c>
-      <c r="F66" s="6" t="s">
-        <v>120</v>
+      <c r="F66" s="21" t="s">
+        <v>114</v>
       </c>
       <c r="G66" s="2">
         <v>45000</v>
@@ -3999,7 +4093,7 @@
       </c>
       <c r="I66" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K66" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4009,7 +4103,7 @@
         <v>33</v>
       </c>
       <c r="M66" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="67" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -4017,7 +4111,7 @@
         <v>28</v>
       </c>
       <c r="C67" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D67" t="s">
         <v>37</v>
@@ -4026,7 +4120,7 @@
         <v>8</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G67" s="2">
         <v>45182</v>
@@ -4037,7 +4131,7 @@
       </c>
       <c r="I67" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K67" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4056,7 +4150,7 @@
         <v>45278</v>
       </c>
       <c r="P67" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="Q67" t="s">
         <v>38</v>
@@ -4067,7 +4161,7 @@
         <v>28</v>
       </c>
       <c r="C68" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D68" t="s">
         <v>29</v>
@@ -4076,7 +4170,7 @@
         <v>8</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G68" s="2">
         <v>45182</v>
@@ -4087,7 +4181,7 @@
       </c>
       <c r="I68" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K68" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4106,7 +4200,7 @@
         <v>45278</v>
       </c>
       <c r="P68" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="Q68" t="s">
         <v>38</v>
@@ -4117,7 +4211,7 @@
         <v>28</v>
       </c>
       <c r="C69" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D69" t="s">
         <v>31</v>
@@ -4126,7 +4220,7 @@
         <v>8</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G69" s="2">
         <v>45182</v>
@@ -4137,7 +4231,7 @@
       </c>
       <c r="I69" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K69" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4156,7 +4250,7 @@
         <v>45278</v>
       </c>
       <c r="P69" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="Q69" t="s">
         <v>38</v>
@@ -4167,7 +4261,7 @@
         <v>35</v>
       </c>
       <c r="C70" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D70" t="s">
         <v>30</v>
@@ -4176,7 +4270,7 @@
         <v>8</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G70" s="2">
         <v>45182</v>
@@ -4187,7 +4281,7 @@
       </c>
       <c r="I70" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K70" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4206,7 +4300,7 @@
         <v>45278</v>
       </c>
       <c r="P70" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="Q70" t="s">
         <v>38</v>
@@ -4217,7 +4311,7 @@
         <v>35</v>
       </c>
       <c r="C71" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D71" t="s">
         <v>36</v>
@@ -4226,7 +4320,7 @@
         <v>8</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G71" s="2">
         <v>45182</v>
@@ -4237,7 +4331,7 @@
       </c>
       <c r="I71" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K71" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4256,7 +4350,7 @@
         <v>45278</v>
       </c>
       <c r="P71" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="Q71" t="s">
         <v>38</v>
@@ -4267,7 +4361,7 @@
         <v>28</v>
       </c>
       <c r="C72" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D72" t="s">
         <v>37</v>
@@ -4276,7 +4370,7 @@
         <v>8</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G72" s="2">
         <v>45182</v>
@@ -4287,7 +4381,7 @@
       </c>
       <c r="I72" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K72" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4306,7 +4400,7 @@
         <v>45278</v>
       </c>
       <c r="P72" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="Q72" t="s">
         <v>39</v>
@@ -4317,7 +4411,7 @@
         <v>28</v>
       </c>
       <c r="C73" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D73" t="s">
         <v>29</v>
@@ -4326,7 +4420,7 @@
         <v>8</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G73" s="2">
         <v>45182</v>
@@ -4337,7 +4431,7 @@
       </c>
       <c r="I73" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K73" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4356,7 +4450,7 @@
         <v>45275</v>
       </c>
       <c r="P73" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="Q73" t="s">
         <v>39</v>
@@ -4367,7 +4461,7 @@
         <v>28</v>
       </c>
       <c r="C74" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D74" t="s">
         <v>31</v>
@@ -4376,7 +4470,7 @@
         <v>8</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G74" s="2">
         <v>45182</v>
@@ -4387,7 +4481,7 @@
       </c>
       <c r="I74" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K74" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4406,7 +4500,7 @@
         <v>45278</v>
       </c>
       <c r="P74" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="Q74" t="s">
         <v>39</v>
@@ -4417,7 +4511,7 @@
         <v>35</v>
       </c>
       <c r="C75" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D75" t="s">
         <v>30</v>
@@ -4426,7 +4520,7 @@
         <v>8</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G75" s="2">
         <v>45182</v>
@@ -4437,7 +4531,7 @@
       </c>
       <c r="I75" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K75" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4456,7 +4550,7 @@
         <v>45274</v>
       </c>
       <c r="P75" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="Q75" t="s">
         <v>39</v>
@@ -4467,7 +4561,7 @@
         <v>35</v>
       </c>
       <c r="C76" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D76" t="s">
         <v>36</v>
@@ -4476,7 +4570,7 @@
         <v>8</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G76" s="2">
         <v>45182</v>
@@ -4487,7 +4581,7 @@
       </c>
       <c r="I76" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K76" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4506,7 +4600,7 @@
         <v>45274</v>
       </c>
       <c r="P76" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="Q76" t="s">
         <v>39</v>
@@ -4517,7 +4611,7 @@
         <v>28</v>
       </c>
       <c r="C77" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D77" t="s">
         <v>37</v>
@@ -4526,7 +4620,7 @@
         <v>8</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G77" s="2">
         <v>45182</v>
@@ -4537,7 +4631,7 @@
       </c>
       <c r="I77" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K77" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4547,7 +4641,7 @@
         <v>33</v>
       </c>
       <c r="M77" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N77" s="2">
         <v>45212</v>
@@ -4556,7 +4650,7 @@
         <v>45278</v>
       </c>
       <c r="P77" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="Q77" t="s">
         <v>38</v>
@@ -4567,7 +4661,7 @@
         <v>28</v>
       </c>
       <c r="C78" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D78" t="s">
         <v>29</v>
@@ -4576,7 +4670,7 @@
         <v>8</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G78" s="2">
         <v>45182</v>
@@ -4587,7 +4681,7 @@
       </c>
       <c r="I78" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K78" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4597,7 +4691,7 @@
         <v>33</v>
       </c>
       <c r="M78" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N78" s="2">
         <v>45212</v>
@@ -4606,7 +4700,7 @@
         <v>45278</v>
       </c>
       <c r="P78" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="Q78" t="s">
         <v>38</v>
@@ -4617,7 +4711,7 @@
         <v>28</v>
       </c>
       <c r="C79" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D79" t="s">
         <v>31</v>
@@ -4626,7 +4720,7 @@
         <v>8</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G79" s="2">
         <v>45182</v>
@@ -4637,7 +4731,7 @@
       </c>
       <c r="I79" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K79" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4647,7 +4741,7 @@
         <v>33</v>
       </c>
       <c r="M79" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N79" s="2">
         <v>45212</v>
@@ -4656,7 +4750,7 @@
         <v>45278</v>
       </c>
       <c r="P79" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="Q79" t="s">
         <v>38</v>
@@ -4667,7 +4761,7 @@
         <v>35</v>
       </c>
       <c r="C80" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D80" t="s">
         <v>30</v>
@@ -4676,7 +4770,7 @@
         <v>8</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G80" s="2">
         <v>45182</v>
@@ -4687,7 +4781,7 @@
       </c>
       <c r="I80" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K80" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4697,7 +4791,7 @@
         <v>33</v>
       </c>
       <c r="M80" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N80" s="2">
         <v>45212</v>
@@ -4706,7 +4800,7 @@
         <v>45278</v>
       </c>
       <c r="P80" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="Q80" t="s">
         <v>38</v>
@@ -4717,7 +4811,7 @@
         <v>35</v>
       </c>
       <c r="C81" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D81" t="s">
         <v>36</v>
@@ -4726,7 +4820,7 @@
         <v>8</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G81" s="2">
         <v>45182</v>
@@ -4737,7 +4831,7 @@
       </c>
       <c r="I81" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K81" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4747,7 +4841,7 @@
         <v>33</v>
       </c>
       <c r="M81" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N81" s="2">
         <v>45212</v>
@@ -4756,7 +4850,7 @@
         <v>45278</v>
       </c>
       <c r="P81" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="Q81" t="s">
         <v>38</v>
@@ -4767,7 +4861,7 @@
         <v>28</v>
       </c>
       <c r="C82" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D82" t="s">
         <v>37</v>
@@ -4776,7 +4870,7 @@
         <v>8</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G82" s="2">
         <v>45182</v>
@@ -4787,7 +4881,7 @@
       </c>
       <c r="I82" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K82" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4797,7 +4891,7 @@
         <v>33</v>
       </c>
       <c r="M82" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="N82" s="2">
         <v>45212</v>
@@ -4806,7 +4900,7 @@
         <v>45270</v>
       </c>
       <c r="P82" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="Q82" t="s">
         <v>39</v>
@@ -4817,7 +4911,7 @@
         <v>28</v>
       </c>
       <c r="C83" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D83" t="s">
         <v>29</v>
@@ -4826,7 +4920,7 @@
         <v>8</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G83" s="2">
         <v>45182</v>
@@ -4837,7 +4931,7 @@
       </c>
       <c r="I83" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K83" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4847,7 +4941,7 @@
         <v>33</v>
       </c>
       <c r="M83" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="N83" s="2">
         <v>45212</v>
@@ -4856,7 +4950,7 @@
         <v>45270</v>
       </c>
       <c r="P83" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="Q83" t="s">
         <v>39</v>
@@ -4867,7 +4961,7 @@
         <v>28</v>
       </c>
       <c r="C84" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D84" t="s">
         <v>31</v>
@@ -4876,7 +4970,7 @@
         <v>8</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G84" s="2">
         <v>45182</v>
@@ -4887,7 +4981,7 @@
       </c>
       <c r="I84" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K84" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4897,7 +4991,7 @@
         <v>33</v>
       </c>
       <c r="M84" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="N84" s="2">
         <v>45212</v>
@@ -4906,7 +5000,7 @@
         <v>45273</v>
       </c>
       <c r="P84" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="Q84" t="s">
         <v>39</v>
@@ -4917,7 +5011,7 @@
         <v>35</v>
       </c>
       <c r="C85" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D85" t="s">
         <v>30</v>
@@ -4926,7 +5020,7 @@
         <v>8</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G85" s="2">
         <v>45182</v>
@@ -4937,7 +5031,7 @@
       </c>
       <c r="I85" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K85" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4947,7 +5041,7 @@
         <v>33</v>
       </c>
       <c r="M85" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="N85" s="2">
         <v>45212</v>
@@ -4956,7 +5050,7 @@
         <v>45277</v>
       </c>
       <c r="P85" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="Q85" t="s">
         <v>39</v>
@@ -4967,7 +5061,7 @@
         <v>35</v>
       </c>
       <c r="C86" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D86" t="s">
         <v>36</v>
@@ -4976,7 +5070,7 @@
         <v>8</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G86" s="2">
         <v>45182</v>
@@ -4987,7 +5081,7 @@
       </c>
       <c r="I86" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K86" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4997,7 +5091,7 @@
         <v>33</v>
       </c>
       <c r="M86" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="N86" s="2">
         <v>45212</v>
@@ -5006,7 +5100,7 @@
         <v>45277</v>
       </c>
       <c r="P86" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="Q86" t="s">
         <v>39</v>
@@ -5017,7 +5111,7 @@
         <v>28</v>
       </c>
       <c r="C87" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="D87" t="s">
         <v>29</v>
@@ -5026,7 +5120,7 @@
         <v>32</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="G87" s="2">
         <v>45238</v>
@@ -5037,7 +5131,7 @@
       </c>
       <c r="I87" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J87" s="2">
         <v>45272</v>
@@ -5049,11 +5143,14 @@
       <c r="L87" t="s">
         <v>34</v>
       </c>
-      <c r="M87" s="1" t="s">
-        <v>43</v>
+      <c r="M87" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="P87" t="s">
+        <v>150</v>
       </c>
       <c r="Q87" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="88" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -5061,7 +5158,7 @@
         <v>35</v>
       </c>
       <c r="C88" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="D88" t="s">
         <v>31</v>
@@ -5070,7 +5167,7 @@
         <v>32</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="G88" s="2">
         <v>45238</v>
@@ -5081,7 +5178,7 @@
       </c>
       <c r="I88" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J88" s="2">
         <v>45273</v>
@@ -5093,11 +5190,14 @@
       <c r="L88" t="s">
         <v>34</v>
       </c>
-      <c r="M88" s="1" t="s">
-        <v>43</v>
+      <c r="M88" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="P88" t="s">
+        <v>150</v>
       </c>
       <c r="Q88" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="89" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -5105,7 +5205,7 @@
         <v>35</v>
       </c>
       <c r="C89" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="D89" t="s">
         <v>30</v>
@@ -5114,7 +5214,7 @@
         <v>32</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="G89" s="2">
         <v>45238</v>
@@ -5125,7 +5225,7 @@
       </c>
       <c r="I89" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J89" s="2">
         <v>45274</v>
@@ -5137,11 +5237,14 @@
       <c r="L89" t="s">
         <v>34</v>
       </c>
-      <c r="M89" s="1" t="s">
-        <v>43</v>
+      <c r="M89" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="P89" t="s">
+        <v>150</v>
       </c>
       <c r="Q89" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="90" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -5149,7 +5252,7 @@
         <v>28</v>
       </c>
       <c r="C90" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="D90" t="s">
         <v>29</v>
@@ -5158,7 +5261,7 @@
         <v>32</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="G90" s="2">
         <v>45238</v>
@@ -5169,7 +5272,7 @@
       </c>
       <c r="I90" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J90" s="2">
         <v>45275</v>
@@ -5181,11 +5284,14 @@
       <c r="L90" t="s">
         <v>33</v>
       </c>
-      <c r="M90" s="1" t="s">
-        <v>42</v>
+      <c r="M90" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="P90" t="s">
+        <v>150</v>
       </c>
       <c r="Q90" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="91" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -5193,7 +5299,7 @@
         <v>28</v>
       </c>
       <c r="C91" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="D91" t="s">
         <v>31</v>
@@ -5202,7 +5308,7 @@
         <v>32</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="G91" s="2">
         <v>45238</v>
@@ -5213,7 +5319,7 @@
       </c>
       <c r="I91" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J91" s="2">
         <v>45276</v>
@@ -5225,11 +5331,14 @@
       <c r="L91" t="s">
         <v>33</v>
       </c>
-      <c r="M91" s="1" t="s">
-        <v>42</v>
+      <c r="M91" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="P91" t="s">
+        <v>150</v>
       </c>
       <c r="Q91" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="92" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -5237,7 +5346,7 @@
         <v>28</v>
       </c>
       <c r="C92" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="D92" t="s">
         <v>30</v>
@@ -5246,7 +5355,7 @@
         <v>32</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="G92" s="2">
         <v>45238</v>
@@ -5257,7 +5366,7 @@
       </c>
       <c r="I92" s="4">
         <f t="shared" ref="I92:I93" ca="1" si="10">IF(_xlfn.DAYS(TODAY(),G92)&lt;10000, _xlfn.DAYS(TODAY(),G92), "-")</f>
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J92" s="2">
         <v>45277</v>
@@ -5269,11 +5378,14 @@
       <c r="L92" t="s">
         <v>33</v>
       </c>
-      <c r="M92" s="1" t="s">
-        <v>42</v>
+      <c r="M92" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="P92" t="s">
+        <v>150</v>
       </c>
       <c r="Q92" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="93" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -5281,7 +5393,7 @@
         <v>35</v>
       </c>
       <c r="C93" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="D93" t="s">
         <v>36</v>
@@ -5290,7 +5402,7 @@
         <v>32</v>
       </c>
       <c r="F93" s="5" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="G93" s="2">
         <v>45238</v>
@@ -5301,7 +5413,7 @@
       </c>
       <c r="I93" s="4">
         <f t="shared" ca="1" si="10"/>
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J93" s="2">
         <v>45278</v>
@@ -5313,11 +5425,14 @@
       <c r="L93" t="s">
         <v>33</v>
       </c>
-      <c r="M93" s="1" t="s">
-        <v>42</v>
+      <c r="M93" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="P93" t="s">
+        <v>150</v>
       </c>
       <c r="Q93" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="94" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -5325,7 +5440,7 @@
         <v>35</v>
       </c>
       <c r="C94" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="D94">
         <v>615</v>
@@ -5334,7 +5449,7 @@
         <v>32</v>
       </c>
       <c r="F94" s="5" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="G94" s="2">
         <v>45202</v>
@@ -5345,7 +5460,7 @@
       </c>
       <c r="I94" s="4">
         <f t="shared" ref="I94" ca="1" si="12">IF(_xlfn.DAYS(TODAY(),G94)&lt;10000, _xlfn.DAYS(TODAY(),G94), "-")</f>
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J94" s="2">
         <v>45223</v>
@@ -5358,16 +5473,16 @@
         <v>34</v>
       </c>
       <c r="M94" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O94" s="2">
         <v>45301</v>
       </c>
       <c r="P94" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="Q94" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="95" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -5375,7 +5490,7 @@
         <v>35</v>
       </c>
       <c r="C95" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="D95">
         <v>616</v>
@@ -5384,7 +5499,7 @@
         <v>32</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="G95" s="2">
         <v>45202</v>
@@ -5395,7 +5510,7 @@
       </c>
       <c r="I95" s="4">
         <f t="shared" ref="I95:I117" ca="1" si="14">IF(_xlfn.DAYS(TODAY(),G95)&lt;10000, _xlfn.DAYS(TODAY(),G95), "-")</f>
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J95" s="2">
         <v>45223</v>
@@ -5408,16 +5523,16 @@
         <v>34</v>
       </c>
       <c r="M95" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O95" s="2">
         <v>45301</v>
       </c>
       <c r="P95" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="Q95" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="96" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -5425,7 +5540,7 @@
         <v>35</v>
       </c>
       <c r="C96" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="D96">
         <v>617</v>
@@ -5434,7 +5549,7 @@
         <v>32</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="G96" s="2">
         <v>45202</v>
@@ -5445,7 +5560,7 @@
       </c>
       <c r="I96" s="4">
         <f t="shared" ca="1" si="14"/>
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J96" s="2">
         <v>45223</v>
@@ -5458,16 +5573,16 @@
         <v>34</v>
       </c>
       <c r="M96" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O96" s="2">
         <v>45301</v>
       </c>
       <c r="P96" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="Q96" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="97" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -5475,7 +5590,7 @@
         <v>35</v>
       </c>
       <c r="C97" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="D97">
         <v>618</v>
@@ -5484,7 +5599,7 @@
         <v>32</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="G97" s="2">
         <v>45202</v>
@@ -5495,7 +5610,7 @@
       </c>
       <c r="I97" s="4">
         <f t="shared" ca="1" si="14"/>
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J97" s="2">
         <v>45223</v>
@@ -5508,16 +5623,16 @@
         <v>34</v>
       </c>
       <c r="M97" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O97" s="2">
         <v>45301</v>
       </c>
       <c r="P97" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="Q97" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="98" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -5525,7 +5640,7 @@
         <v>35</v>
       </c>
       <c r="C98" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D98" t="s">
         <v>37</v>
@@ -5534,7 +5649,7 @@
         <v>8</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G98" s="2">
         <v>45229</v>
@@ -5545,7 +5660,7 @@
       </c>
       <c r="I98" s="4">
         <f t="shared" ref="I98:I107" ca="1" si="17">IF(_xlfn.DAYS(TODAY(),G98)&lt;10000, _xlfn.DAYS(TODAY(),G98), "-")</f>
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J98" s="2">
         <v>45267</v>
@@ -5558,16 +5673,16 @@
         <v>34</v>
       </c>
       <c r="M98" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="N98" s="2">
         <v>45278</v>
       </c>
       <c r="P98" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="Q98" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="99" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -5575,7 +5690,7 @@
         <v>35</v>
       </c>
       <c r="C99" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D99" t="s">
         <v>29</v>
@@ -5584,7 +5699,7 @@
         <v>8</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G99" s="2">
         <v>45229</v>
@@ -5595,7 +5710,7 @@
       </c>
       <c r="I99" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J99" s="2">
         <v>45267</v>
@@ -5608,16 +5723,16 @@
         <v>34</v>
       </c>
       <c r="M99" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="N99" s="2">
         <v>45278</v>
       </c>
       <c r="P99" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="Q99" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="100" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -5625,7 +5740,7 @@
         <v>35</v>
       </c>
       <c r="C100" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D100" t="s">
         <v>31</v>
@@ -5634,7 +5749,7 @@
         <v>8</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G100" s="2">
         <v>45229</v>
@@ -5645,7 +5760,7 @@
       </c>
       <c r="I100" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J100" s="2">
         <v>45267</v>
@@ -5658,16 +5773,16 @@
         <v>34</v>
       </c>
       <c r="M100" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="N100" s="2">
         <v>45278</v>
       </c>
       <c r="P100" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="Q100" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="101" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -5675,7 +5790,7 @@
         <v>35</v>
       </c>
       <c r="C101" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D101" t="s">
         <v>30</v>
@@ -5684,7 +5799,7 @@
         <v>8</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G101" s="2">
         <v>45229</v>
@@ -5695,7 +5810,7 @@
       </c>
       <c r="I101" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J101" s="2">
         <v>45267</v>
@@ -5708,16 +5823,16 @@
         <v>34</v>
       </c>
       <c r="M101" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="N101" s="2">
         <v>45278</v>
       </c>
       <c r="P101" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="Q101" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="102" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -5725,7 +5840,7 @@
         <v>35</v>
       </c>
       <c r="C102" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D102" t="s">
         <v>36</v>
@@ -5734,7 +5849,7 @@
         <v>8</v>
       </c>
       <c r="F102" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G102" s="2">
         <v>45229</v>
@@ -5745,7 +5860,7 @@
       </c>
       <c r="I102" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J102" s="2">
         <v>45267</v>
@@ -5758,16 +5873,16 @@
         <v>34</v>
       </c>
       <c r="M102" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="N102" s="2">
         <v>45278</v>
       </c>
       <c r="P102" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="Q102" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="103" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -5775,7 +5890,7 @@
         <v>35</v>
       </c>
       <c r="C103" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D103" t="s">
         <v>37</v>
@@ -5784,7 +5899,7 @@
         <v>8</v>
       </c>
       <c r="F103" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G103" s="2">
         <v>45229</v>
@@ -5795,7 +5910,7 @@
       </c>
       <c r="I103" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J103" s="2">
         <v>45267</v>
@@ -5808,16 +5923,16 @@
         <v>34</v>
       </c>
       <c r="M103" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="N103" s="2">
         <v>45278</v>
       </c>
       <c r="P103" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="Q103" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="104" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -5825,7 +5940,7 @@
         <v>35</v>
       </c>
       <c r="C104" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D104" t="s">
         <v>29</v>
@@ -5834,7 +5949,7 @@
         <v>8</v>
       </c>
       <c r="F104" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G104" s="2">
         <v>45229</v>
@@ -5845,7 +5960,7 @@
       </c>
       <c r="I104" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J104" s="2">
         <v>45267</v>
@@ -5858,16 +5973,16 @@
         <v>34</v>
       </c>
       <c r="M104" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="N104" s="2">
         <v>45278</v>
       </c>
       <c r="P104" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="Q104" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="105" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -5875,7 +5990,7 @@
         <v>35</v>
       </c>
       <c r="C105" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D105" t="s">
         <v>31</v>
@@ -5884,7 +5999,7 @@
         <v>8</v>
       </c>
       <c r="F105" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G105" s="2">
         <v>45229</v>
@@ -5895,7 +6010,7 @@
       </c>
       <c r="I105" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J105" s="2">
         <v>45267</v>
@@ -5908,16 +6023,16 @@
         <v>34</v>
       </c>
       <c r="M105" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="N105" s="2">
         <v>45278</v>
       </c>
       <c r="P105" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="Q105" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="106" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -5925,7 +6040,7 @@
         <v>35</v>
       </c>
       <c r="C106" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D106" t="s">
         <v>30</v>
@@ -5934,7 +6049,7 @@
         <v>8</v>
       </c>
       <c r="F106" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G106" s="2">
         <v>45229</v>
@@ -5945,7 +6060,7 @@
       </c>
       <c r="I106" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J106" s="2">
         <v>45267</v>
@@ -5958,16 +6073,16 @@
         <v>34</v>
       </c>
       <c r="M106" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="N106" s="2">
         <v>45278</v>
       </c>
       <c r="P106" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="Q106" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="107" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -5975,7 +6090,7 @@
         <v>35</v>
       </c>
       <c r="C107" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D107" t="s">
         <v>36</v>
@@ -5984,7 +6099,7 @@
         <v>8</v>
       </c>
       <c r="F107" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G107" s="2">
         <v>45229</v>
@@ -5995,7 +6110,7 @@
       </c>
       <c r="I107" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J107" s="2">
         <v>45267</v>
@@ -6008,16 +6123,16 @@
         <v>34</v>
       </c>
       <c r="M107" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="N107" s="2">
         <v>45278</v>
       </c>
       <c r="P107" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="Q107" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="108" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -6025,7 +6140,7 @@
         <v>35</v>
       </c>
       <c r="C108" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D108">
         <v>951</v>
@@ -6034,7 +6149,7 @@
         <v>8</v>
       </c>
       <c r="F108" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H108" s="4" t="str">
         <f t="shared" ca="1" si="13"/>
@@ -6049,16 +6164,16 @@
         <v>-</v>
       </c>
       <c r="M108" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O108" s="2">
         <v>45306</v>
       </c>
       <c r="P108" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="Q108" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="109" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -6066,7 +6181,7 @@
         <v>35</v>
       </c>
       <c r="C109" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D109">
         <v>954</v>
@@ -6075,7 +6190,7 @@
         <v>8</v>
       </c>
       <c r="F109" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H109" s="4" t="str">
         <f t="shared" ca="1" si="13"/>
@@ -6090,16 +6205,16 @@
         <v>-</v>
       </c>
       <c r="M109" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O109" s="2">
         <v>45306</v>
       </c>
       <c r="P109" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="Q109" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="110" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -6107,7 +6222,7 @@
         <v>35</v>
       </c>
       <c r="C110" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D110">
         <v>957</v>
@@ -6116,7 +6231,7 @@
         <v>8</v>
       </c>
       <c r="F110" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H110" s="4" t="str">
         <f t="shared" ca="1" si="13"/>
@@ -6131,16 +6246,16 @@
         <v>-</v>
       </c>
       <c r="M110" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O110" s="2">
         <v>45312</v>
       </c>
       <c r="P110" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="Q110" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="111" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -6148,7 +6263,7 @@
         <v>35</v>
       </c>
       <c r="C111" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D111">
         <v>960</v>
@@ -6157,7 +6272,7 @@
         <v>8</v>
       </c>
       <c r="F111" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H111" s="4" t="str">
         <f t="shared" ca="1" si="13"/>
@@ -6172,16 +6287,16 @@
         <v>-</v>
       </c>
       <c r="M111" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O111" s="2">
         <v>45312</v>
       </c>
       <c r="P111" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="Q111" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="112" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -6189,7 +6304,7 @@
         <v>35</v>
       </c>
       <c r="C112" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D112">
         <v>952</v>
@@ -6198,7 +6313,7 @@
         <v>8</v>
       </c>
       <c r="F112" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H112" s="4" t="str">
         <f t="shared" ca="1" si="13"/>
@@ -6213,16 +6328,16 @@
         <v>-</v>
       </c>
       <c r="M112" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O112" s="2">
         <v>45289</v>
       </c>
       <c r="P112" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="Q112" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="113" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -6230,7 +6345,7 @@
         <v>35</v>
       </c>
       <c r="C113" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D113">
         <v>955</v>
@@ -6239,7 +6354,7 @@
         <v>8</v>
       </c>
       <c r="F113" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H113" s="4" t="str">
         <f t="shared" ca="1" si="13"/>
@@ -6254,16 +6369,16 @@
         <v>-</v>
       </c>
       <c r="M113" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O113" s="2">
         <v>45298</v>
       </c>
       <c r="P113" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="Q113" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="114" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -6271,7 +6386,7 @@
         <v>35</v>
       </c>
       <c r="C114" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D114">
         <v>958</v>
@@ -6280,7 +6395,7 @@
         <v>8</v>
       </c>
       <c r="F114" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H114" s="4" t="str">
         <f t="shared" ca="1" si="13"/>
@@ -6295,16 +6410,16 @@
         <v>-</v>
       </c>
       <c r="M114" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="O114" s="2">
         <v>45289</v>
       </c>
       <c r="P114" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="Q114" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="115" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -6312,7 +6427,7 @@
         <v>35</v>
       </c>
       <c r="C115" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D115">
         <v>961</v>
@@ -6321,7 +6436,7 @@
         <v>8</v>
       </c>
       <c r="F115" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H115" s="4" t="str">
         <f t="shared" ca="1" si="13"/>
@@ -6335,14 +6450,17 @@
         <f t="shared" si="15"/>
         <v>-</v>
       </c>
+      <c r="L115" t="s">
+        <v>130</v>
+      </c>
       <c r="M115" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="P115" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="Q115" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="116" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -6350,7 +6468,7 @@
         <v>35</v>
       </c>
       <c r="C116" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D116">
         <v>953</v>
@@ -6359,7 +6477,7 @@
         <v>8</v>
       </c>
       <c r="F116" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H116" s="4" t="str">
         <f t="shared" ca="1" si="13"/>
@@ -6374,16 +6492,16 @@
         <v>-</v>
       </c>
       <c r="M116" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="O116" s="2">
         <v>45289</v>
       </c>
       <c r="P116" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="Q116" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="117" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -6391,7 +6509,7 @@
         <v>35</v>
       </c>
       <c r="C117" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D117">
         <v>956</v>
@@ -6400,7 +6518,7 @@
         <v>8</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H117" s="4" t="str">
         <f t="shared" ca="1" si="13"/>
@@ -6415,16 +6533,16 @@
         <v>-</v>
       </c>
       <c r="M117" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="O117" s="2">
         <v>45308</v>
       </c>
       <c r="P117" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="Q117" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="118" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -6432,7 +6550,7 @@
         <v>35</v>
       </c>
       <c r="C118" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D118">
         <v>959</v>
@@ -6441,7 +6559,7 @@
         <v>8</v>
       </c>
       <c r="F118" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H118" s="4" t="str">
         <f t="shared" ref="H118:H124" ca="1" si="18">IF(QUOTIENT(_xlfn.DAYS(TODAY(),G118), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),G118), 7), "-")</f>
@@ -6456,16 +6574,16 @@
         <v>-</v>
       </c>
       <c r="M118" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="O118" s="2">
         <v>45657</v>
       </c>
       <c r="P118" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="Q118" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="119" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -6473,7 +6591,7 @@
         <v>35</v>
       </c>
       <c r="C119" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D119">
         <v>962</v>
@@ -6482,7 +6600,7 @@
         <v>8</v>
       </c>
       <c r="F119" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H119" s="4" t="str">
         <f t="shared" ca="1" si="18"/>
@@ -6497,27 +6615,33 @@
         <v>-</v>
       </c>
       <c r="M119" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="O119" s="2">
         <v>45289</v>
       </c>
       <c r="P119" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="Q119" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="120" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B120" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C120" t="s">
-        <v>112</v>
+        <v>139</v>
+      </c>
+      <c r="D120">
+        <v>645</v>
       </c>
       <c r="E120" t="s">
-        <v>94</v>
+        <v>92</v>
+      </c>
+      <c r="F120" s="21" t="s">
+        <v>151</v>
       </c>
       <c r="G120" s="2">
         <v>45291</v>
@@ -6528,25 +6652,37 @@
       </c>
       <c r="I120" s="4">
         <f t="shared" ca="1" si="19"/>
+        <v>25</v>
+      </c>
+      <c r="J120" s="2">
+        <v>45315</v>
+      </c>
+      <c r="K120" s="4">
+        <f t="shared" si="15"/>
         <v>24</v>
       </c>
-      <c r="K120" s="4" t="str">
-        <f t="shared" si="15"/>
-        <v>-</v>
+      <c r="L120" t="s">
+        <v>130</v>
       </c>
       <c r="M120" t="s">
-        <v>95</v>
+        <v>132</v>
       </c>
     </row>
     <row r="121" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B121" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C121" t="s">
-        <v>112</v>
+        <v>139</v>
+      </c>
+      <c r="D121">
+        <v>646</v>
       </c>
       <c r="E121" t="s">
-        <v>94</v>
+        <v>92</v>
+      </c>
+      <c r="F121" s="21" t="s">
+        <v>97</v>
       </c>
       <c r="G121" s="2">
         <v>45291</v>
@@ -6557,25 +6693,37 @@
       </c>
       <c r="I121" s="4">
         <f t="shared" ca="1" si="19"/>
+        <v>25</v>
+      </c>
+      <c r="J121" s="2">
+        <v>45315</v>
+      </c>
+      <c r="K121" s="4">
+        <f t="shared" si="15"/>
         <v>24</v>
       </c>
-      <c r="K121" s="4" t="str">
-        <f t="shared" si="15"/>
-        <v>-</v>
+      <c r="L121" t="s">
+        <v>130</v>
       </c>
       <c r="M121" t="s">
-        <v>95</v>
+        <v>132</v>
       </c>
     </row>
     <row r="122" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B122" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C122" t="s">
-        <v>112</v>
+        <v>139</v>
+      </c>
+      <c r="D122">
+        <v>647</v>
       </c>
       <c r="E122" t="s">
-        <v>94</v>
+        <v>92</v>
+      </c>
+      <c r="F122" s="21" t="s">
+        <v>152</v>
       </c>
       <c r="G122" s="2">
         <v>45291</v>
@@ -6586,25 +6734,37 @@
       </c>
       <c r="I122" s="4">
         <f t="shared" ca="1" si="19"/>
+        <v>25</v>
+      </c>
+      <c r="J122" s="2">
+        <v>45315</v>
+      </c>
+      <c r="K122" s="4">
+        <f t="shared" si="15"/>
         <v>24</v>
       </c>
-      <c r="K122" s="4" t="str">
-        <f t="shared" si="15"/>
-        <v>-</v>
+      <c r="L122" t="s">
+        <v>134</v>
       </c>
       <c r="M122" t="s">
-        <v>95</v>
+        <v>133</v>
       </c>
     </row>
     <row r="123" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B123" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C123" t="s">
-        <v>112</v>
+        <v>139</v>
+      </c>
+      <c r="D123">
+        <v>648</v>
       </c>
       <c r="E123" t="s">
-        <v>94</v>
+        <v>92</v>
+      </c>
+      <c r="F123" s="21" t="s">
+        <v>95</v>
       </c>
       <c r="G123" s="2">
         <v>45291</v>
@@ -6615,22 +6775,28 @@
       </c>
       <c r="I123" s="4">
         <f t="shared" ca="1" si="19"/>
+        <v>25</v>
+      </c>
+      <c r="J123" s="2">
+        <v>45315</v>
+      </c>
+      <c r="K123" s="4">
+        <f t="shared" si="15"/>
         <v>24</v>
       </c>
-      <c r="K123" s="4" t="str">
-        <f t="shared" si="15"/>
-        <v>-</v>
+      <c r="L123" t="s">
+        <v>134</v>
       </c>
       <c r="M123" t="s">
-        <v>95</v>
+        <v>133</v>
       </c>
     </row>
     <row r="124" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B124" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C124" t="s">
-        <v>112</v>
+        <v>139</v>
       </c>
       <c r="E124" t="s">
         <v>16</v>
@@ -6644,25 +6810,25 @@
       </c>
       <c r="I124" s="4">
         <f t="shared" ca="1" si="19"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K124" s="4" t="str">
         <f t="shared" si="15"/>
         <v>-</v>
       </c>
       <c r="M124" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q124" t="s">
         <v>124</v>
-      </c>
-      <c r="Q124" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="125" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B125" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C125" t="s">
-        <v>112</v>
+        <v>139</v>
       </c>
       <c r="E125" t="s">
         <v>16</v>
@@ -6676,21 +6842,21 @@
       </c>
       <c r="I125" s="4">
         <f t="shared" ref="I125:I127" ca="1" si="21">IF(_xlfn.DAYS(TODAY(),G125)&lt;10000, _xlfn.DAYS(TODAY(),G125), "-")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M125" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q125" t="s">
         <v>124</v>
-      </c>
-      <c r="Q125" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="126" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B126" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C126" t="s">
-        <v>112</v>
+        <v>139</v>
       </c>
       <c r="E126" t="s">
         <v>16</v>
@@ -6704,21 +6870,21 @@
       </c>
       <c r="I126" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M126" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q126" t="s">
         <v>124</v>
-      </c>
-      <c r="Q126" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="127" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B127" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C127" t="s">
-        <v>112</v>
+        <v>139</v>
       </c>
       <c r="E127" t="s">
         <v>16</v>
@@ -6732,21 +6898,21 @@
       </c>
       <c r="I127" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M127" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q127" t="s">
         <v>124</v>
-      </c>
-      <c r="Q127" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="128" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B128" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="C128" t="s">
-        <v>112</v>
+        <v>139</v>
       </c>
       <c r="E128" t="s">
         <v>16</v>
@@ -6755,26 +6921,26 @@
         <v>45309</v>
       </c>
       <c r="H128" s="4">
-        <f t="shared" ref="H128:H130" ca="1" si="22">IF(QUOTIENT(_xlfn.DAYS(TODAY(),G128), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),G128), 7), "-")</f>
-        <v>0</v>
+        <f t="shared" ref="H128:H137" ca="1" si="22">IF(QUOTIENT(_xlfn.DAYS(TODAY(),G128), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),G128), 7), "-")</f>
+        <v>1</v>
       </c>
       <c r="I128" s="4">
         <f t="shared" ref="I128:I130" ca="1" si="23">IF(_xlfn.DAYS(TODAY(),G128)&lt;10000, _xlfn.DAYS(TODAY(),G128), "-")</f>
-        <v>6</v>
-      </c>
-      <c r="M128" t="s">
-        <v>126</v>
+        <v>7</v>
+      </c>
+      <c r="M128" s="4" t="s">
+        <v>120</v>
       </c>
       <c r="Q128" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
     </row>
     <row r="129" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B129" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="C129" t="s">
-        <v>112</v>
+        <v>139</v>
       </c>
       <c r="E129" t="s">
         <v>16</v>
@@ -6784,25 +6950,25 @@
       </c>
       <c r="H129" s="4">
         <f t="shared" ca="1" si="22"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I129" s="4">
         <f t="shared" ca="1" si="23"/>
-        <v>6</v>
-      </c>
-      <c r="M129" t="s">
-        <v>126</v>
+        <v>7</v>
+      </c>
+      <c r="M129" s="4" t="s">
+        <v>120</v>
       </c>
       <c r="Q129" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
     </row>
     <row r="130" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B130" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="C130" t="s">
-        <v>112</v>
+        <v>139</v>
       </c>
       <c r="E130" t="s">
         <v>16</v>
@@ -6812,21 +6978,193 @@
       </c>
       <c r="H130" s="4">
         <f t="shared" ca="1" si="22"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I130" s="4">
         <f t="shared" ca="1" si="23"/>
-        <v>6</v>
-      </c>
-      <c r="M130" t="s">
-        <v>126</v>
+        <v>7</v>
+      </c>
+      <c r="M130" s="4" t="s">
+        <v>120</v>
       </c>
       <c r="Q130" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="131" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B131" t="s">
+        <v>5</v>
+      </c>
+      <c r="C131" t="s">
+        <v>62</v>
+      </c>
+      <c r="E131" t="s">
         <v>131</v>
       </c>
+      <c r="F131" s="10"/>
+      <c r="H131" s="4" t="str">
+        <f t="shared" ca="1" si="22"/>
+        <v>-</v>
+      </c>
+      <c r="L131" t="s">
+        <v>130</v>
+      </c>
+      <c r="M131" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="132" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B132" t="s">
+        <v>5</v>
+      </c>
+      <c r="C132" t="s">
+        <v>138</v>
+      </c>
+      <c r="F132" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="G132" s="2">
+        <v>45155</v>
+      </c>
+      <c r="H132" s="4">
+        <f t="shared" ca="1" si="22"/>
+        <v>23</v>
+      </c>
+      <c r="L132" t="s">
+        <v>130</v>
+      </c>
+      <c r="M132" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="Q132" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="133" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B133" t="s">
+        <v>5</v>
+      </c>
+      <c r="C133" t="s">
+        <v>138</v>
+      </c>
+      <c r="F133" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="G133" s="2">
+        <v>44885</v>
+      </c>
+      <c r="H133" s="4">
+        <f t="shared" ca="1" si="22"/>
+        <v>61</v>
+      </c>
+      <c r="L133" t="s">
+        <v>134</v>
+      </c>
+      <c r="M133" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="134" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B134" t="s">
+        <v>5</v>
+      </c>
+      <c r="C134" t="s">
+        <v>138</v>
+      </c>
+      <c r="F134" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="G134" s="2">
+        <v>44885</v>
+      </c>
+      <c r="H134" s="4">
+        <f t="shared" ca="1" si="22"/>
+        <v>61</v>
+      </c>
+      <c r="L134" t="s">
+        <v>134</v>
+      </c>
+      <c r="M134" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="135" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B135" t="s">
+        <v>5</v>
+      </c>
+      <c r="C135" t="s">
+        <v>138</v>
+      </c>
+      <c r="F135" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="G135" s="2">
+        <v>45155</v>
+      </c>
+      <c r="H135" s="4">
+        <f t="shared" ca="1" si="22"/>
+        <v>23</v>
+      </c>
+      <c r="L135" t="s">
+        <v>130</v>
+      </c>
+      <c r="M135" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q135" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="136" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B136" t="s">
+        <v>5</v>
+      </c>
+      <c r="C136" t="s">
+        <v>138</v>
+      </c>
+      <c r="F136" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="G136" s="2">
+        <v>44885</v>
+      </c>
+      <c r="H136" s="4">
+        <f t="shared" ca="1" si="22"/>
+        <v>61</v>
+      </c>
+      <c r="L136" t="s">
+        <v>134</v>
+      </c>
+      <c r="M136" s="4" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="137" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B137" t="s">
+        <v>5</v>
+      </c>
+      <c r="C137" t="s">
+        <v>138</v>
+      </c>
+      <c r="F137" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="G137" s="2">
+        <v>44885</v>
+      </c>
+      <c r="H137" s="4">
+        <f t="shared" ca="1" si="22"/>
+        <v>61</v>
+      </c>
+      <c r="L137" t="s">
+        <v>134</v>
+      </c>
+      <c r="M137" s="4" t="s">
+        <v>142</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="B1:Q130" xr:uid="{47ECCD65-6802-4B2B-901A-AED4A431A765}">
+  <autoFilter ref="B1:Q137" xr:uid="{47ECCD65-6802-4B2B-901A-AED4A431A765}">
     <filterColumn colId="0">
       <filters>
         <filter val="SPF"/>
@@ -6837,6 +7175,11 @@
     </filterColumn>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="M1:M1048576">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text=".B">
+      <formula>NOT(ISERROR(SEARCH(".B",M1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E1048576" xr:uid="{939E2B39-E841-4A9F-AD11-00C266DB2690}">
       <formula1>"Y, N"</formula1>
@@ -6864,28 +7207,28 @@
   <sheetData>
     <row r="2" spans="3:8" x14ac:dyDescent="0.3">
       <c r="D2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G2" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="H2" s="20"/>
+        <v>76</v>
+      </c>
+      <c r="G2" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2" s="22"/>
     </row>
     <row r="3" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D3" t="s">
         <v>88</v>
-      </c>
-      <c r="D3" t="s">
-        <v>90</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>23</v>
       </c>
       <c r="G3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H3" s="5" t="s">
         <v>23</v>
@@ -6893,16 +7236,16 @@
     </row>
     <row r="4" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>23</v>
       </c>
       <c r="G4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H4" s="5" t="s">
         <v>23</v>

--- a/Mouse 내역.xlsx
+++ b/Mouse 내역.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\heung\OneDrive\바탕 화면\동물실\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A19DAB4-C859-4F8A-A1E1-287A91EA9F8B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F7A179C-60FE-4C56-96D0-ABE1F39DCC15}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19080" windowHeight="9180" xr2:uid="{5A73A69A-2AFB-4F3E-AC64-070DD7700CB2}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19080" windowHeight="9180" activeTab="1" xr2:uid="{5A73A69A-2AFB-4F3E-AC64-070DD7700CB2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1190" uniqueCount="183">
   <si>
     <t>Strain</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -628,10 +628,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>rotation (H1.B, H2.B)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Cre/+; f/f</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -676,69 +672,77 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Cre/?; f/f</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>+/+; f/f</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>H0.3.M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>H0.4.M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>H0.5.F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>H1.1.M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>H1.1.F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>H0.6.F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tmem119-CreERT2; Tsg101-flox</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CD36-flox</t>
+  </si>
+  <si>
+    <t>LysM Cre; Cd36-flox</t>
+  </si>
+  <si>
+    <t>피부병? 같고 크기도 작음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>+/+; f/f</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cre/Cre; f/f</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cre/+; f/f</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tam 찌른 후 Tsg 없어진거 확인용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나중에 H3.B의 female과 breader?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>geno</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>H0.3.M</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>H0.4.M</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>H0.5.F</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>H1.1.M</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>H1.1.F</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>H0.6.F</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tmem119-CreERT2; Tsg101-flox</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>죽임</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CD36-flox</t>
-  </si>
-  <si>
-    <t>LysM Cre; Cd36-flox</t>
-  </si>
-  <si>
-    <t>geno, Cre/+; f/f male이랑 breader</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tam 찔러보기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>B6 WT male이랑 mating</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>B6 WT male이랑 mating (?)</t>
+    <t>H0.5.F와 합사</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>H1.1.F와 합사</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -746,7 +750,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -818,6 +822,15 @@
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
@@ -906,7 +919,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -976,6 +989,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="4" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="4" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="계산" xfId="3" builtinId="22"/>
@@ -1027,7 +1049,7 @@
       <xdr:row>6</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2234266" cy="2416944"/>
+    <xdr:ext cx="2636684" cy="3980962"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="TextBox 1">
@@ -1042,7 +1064,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1381125" y="1428750"/>
-          <a:ext cx="2234266" cy="2416944"/>
+          <a:ext cx="2636684" cy="3980962"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1071,46 +1093,8 @@
         <a:p>
           <a:r>
             <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
-            <a:t>1)</a:t>
+            <a:t>1. H1.B weaning</a:t>
           </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
-            <a:t>A2.1.F</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1"/>
-            <a:t>에서 </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
-            <a:t>+/+; f/f female </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1"/>
-            <a:t>한마리</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
-            <a:t>B1.1.M</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1"/>
-            <a:t>에서 </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
-            <a:t>+/+; f/f male </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1"/>
-            <a:t>한마리</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
         </a:p>
         <a:p>
           <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
@@ -1118,54 +1102,30 @@
         <a:p>
           <a:r>
             <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
-            <a:t>2)</a:t>
+            <a:t>2. H1.B</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1"/>
+            <a:t>의 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
+            <a:t>cre/+; f/f female</a:t>
           </a:r>
         </a:p>
         <a:p>
           <a:r>
             <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
-            <a:t>A2.1.F</a:t>
+            <a:t>H0.3.M</a:t>
           </a:r>
           <a:r>
             <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1"/>
-            <a:t>엣 </a:t>
+            <a:t>의 </a:t>
           </a:r>
           <a:r>
             <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
-            <a:t>Cre/+; f/f female </a:t>
+            <a:t>+/+; f/f male breader -&gt; (H5.B)</a:t>
           </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1"/>
-            <a:t>한마리</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
-            <a:t>B1.1.M</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1"/>
-            <a:t>에서 </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
-            <a:t>+/+;</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" baseline="0"/>
-            <a:t> </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
-            <a:t>f/f male </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1"/>
-            <a:t>한마리</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
         </a:p>
         <a:p>
           <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
@@ -1173,49 +1133,143 @@
         <a:p>
           <a:r>
             <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
-            <a:t>3)</a:t>
+            <a:t>3. H2.B</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1"/>
+            <a:t>의 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
+            <a:t>Cre/+; f/f female</a:t>
           </a:r>
         </a:p>
         <a:p>
           <a:r>
             <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
-            <a:t>C1.1.M</a:t>
+            <a:t>H0.3.M</a:t>
           </a:r>
           <a:r>
             <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1"/>
-            <a:t>에서 </a:t>
+            <a:t>의 </a:t>
           </a:r>
           <a:r>
             <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
-            <a:t>+/+;</a:t>
+            <a:t>+/+; f/f male breader -&gt; (H6.B)</a:t>
           </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" baseline="0"/>
-            <a:t> f/+ male </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" baseline="0"/>
-            <a:t>한마리</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="1" baseline="0"/>
         </a:p>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" baseline="0"/>
-            <a:t>C1.1.F</a:t>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
+            <a:t>H2.B</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" baseline="0"/>
-            <a:t>에서 </a:t>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1"/>
+            <a:t>의 </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" baseline="0"/>
-            <a:t>+/+; f/+ female </a:t>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
+            <a:t>male</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" baseline="0"/>
-            <a:t>한마리</a:t>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1"/>
+            <a:t>은 죽임</a:t>
           </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
+            <a:t>4. H3.B</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1"/>
+            <a:t>의 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
+            <a:t>Cre/+; f/f male</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
+            <a:t>H0.2.F</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1"/>
+            <a:t>의 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
+            <a:t>+/+; f/f female breader -&gt; (H7.B)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
+            <a:t>5. H0.6.F</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1"/>
+            <a:t>의 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
+            <a:t>Cre/+; f/f female</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
+            <a:t>H0.4.M</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1"/>
+            <a:t>의 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
+            <a:t>+/+; f/f male breader -&gt; (H8.B)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
+            <a:t>6. H0.2.F</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1"/>
+            <a:t>의 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
+            <a:t>+/+; f/f female</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
+            <a:t>H1.1.F</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1"/>
+            <a:t>의 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
+            <a:t>Cre/+; f/f male breader -&gt; (H9.B)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
           <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="1"/>
         </a:p>
       </xdr:txBody>
@@ -1534,7 +1588,7 @@
     <col min="7" max="7" width="6.375" customWidth="1"/>
     <col min="8" max="8" width="11.125" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="9" customWidth="1"/>
-    <col min="11" max="11" width="11.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.125" style="2" customWidth="1"/>
     <col min="12" max="12" width="8.25" customWidth="1"/>
     <col min="14" max="14" width="13.125" style="2" customWidth="1"/>
     <col min="15" max="15" width="12.75" style="2" customWidth="1"/>
@@ -1617,7 +1671,7 @@
       </c>
       <c r="J2" s="4">
         <f ca="1">IF(_xlfn.DAYS(TODAY(),H2)&lt;10000, _xlfn.DAYS(TODAY(),H2), "-")</f>
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="L2" s="4" t="str">
         <f t="shared" ref="L2:L31" si="0">IF(_xlfn.DAYS(K2,H2)&gt;0, _xlfn.DAYS(K2,H2), "-")</f>
@@ -1656,7 +1710,7 @@
       </c>
       <c r="J3" s="4">
         <f t="shared" ref="J3:J31" ca="1" si="2">IF(_xlfn.DAYS(TODAY(),H3)&lt;10000, _xlfn.DAYS(TODAY(),H3), "-")</f>
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="L3" s="4" t="str">
         <f t="shared" si="0"/>
@@ -1693,7 +1747,7 @@
       </c>
       <c r="J4" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="L4" s="4" t="str">
         <f t="shared" si="0"/>
@@ -1729,11 +1783,11 @@
       </c>
       <c r="I5" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J5" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K5" s="2">
         <v>45293</v>
@@ -1755,7 +1809,7 @@
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D6">
         <v>686</v>
@@ -1774,11 +1828,11 @@
       </c>
       <c r="I6" s="16">
         <f t="shared" ca="1" si="1"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J6" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K6" s="14">
         <v>45293</v>
@@ -1820,11 +1874,11 @@
       </c>
       <c r="I7" s="16">
         <f t="shared" ca="1" si="1"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J7" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K7" s="14">
         <v>45293</v>
@@ -1864,11 +1918,11 @@
       </c>
       <c r="I8" s="16">
         <f t="shared" ca="1" si="1"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J8" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K8" s="14">
         <v>45293</v>
@@ -1912,11 +1966,11 @@
       </c>
       <c r="I9" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J9" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K9" s="2">
         <v>45293</v>
@@ -1955,11 +2009,11 @@
       </c>
       <c r="I10" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J10" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K10" s="2">
         <v>45293</v>
@@ -2000,11 +2054,11 @@
       </c>
       <c r="I11" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J11" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K11" s="2">
         <v>45293</v>
@@ -2046,7 +2100,7 @@
       </c>
       <c r="J12" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="L12" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2160,7 +2214,7 @@
       </c>
       <c r="J15" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="L15" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2200,7 +2254,7 @@
       </c>
       <c r="J16" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="L16" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2240,7 +2294,7 @@
       </c>
       <c r="J17" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="L17" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2278,7 +2332,7 @@
       </c>
       <c r="J18" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="L18" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2316,7 +2370,7 @@
       </c>
       <c r="J19" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="L19" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2347,11 +2401,11 @@
       </c>
       <c r="I20" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J20" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="L20" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2424,7 +2478,7 @@
       </c>
       <c r="J22" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K22" s="2">
         <v>45112</v>
@@ -2445,7 +2499,7 @@
         <v>5</v>
       </c>
       <c r="C23" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E23" t="s">
         <v>7</v>
@@ -2461,11 +2515,11 @@
       </c>
       <c r="I23" s="4">
         <f ca="1">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H23), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H23), 7), "-")</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J23" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="K23" s="2">
         <v>45176</v>
@@ -2489,7 +2543,7 @@
         <v>5</v>
       </c>
       <c r="C24" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E24" t="s">
         <v>7</v>
@@ -2505,11 +2559,11 @@
       </c>
       <c r="I24" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J24" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="K24" s="2">
         <v>45176</v>
@@ -2533,7 +2587,7 @@
         <v>5</v>
       </c>
       <c r="C25" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E25" t="s">
         <v>7</v>
@@ -2549,11 +2603,11 @@
       </c>
       <c r="I25" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J25" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="K25" s="2">
         <v>45176</v>
@@ -2593,11 +2647,11 @@
       </c>
       <c r="I26" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J26" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="K26" s="2">
         <v>45176</v>
@@ -2632,11 +2686,11 @@
       </c>
       <c r="I27" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J27" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="K27" s="2">
         <v>45176</v>
@@ -2655,7 +2709,7 @@
         <v>5</v>
       </c>
       <c r="C28" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E28" s="15" t="s">
         <v>16</v>
@@ -2671,11 +2725,11 @@
       </c>
       <c r="I28" s="16">
         <f t="shared" ca="1" si="1"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J28" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="K28" s="14">
         <v>45229</v>
@@ -2697,7 +2751,7 @@
         <v>5</v>
       </c>
       <c r="C29" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="E29" s="15" t="s">
         <v>16</v>
@@ -2713,11 +2767,11 @@
       </c>
       <c r="I29" s="16">
         <f t="shared" ca="1" si="1"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J29" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="K29" s="14">
         <v>45229</v>
@@ -2755,11 +2809,11 @@
       </c>
       <c r="I30" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J30" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="K30" s="2">
         <v>45229</v>
@@ -2794,11 +2848,11 @@
       </c>
       <c r="I31" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J31" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="K31" s="2">
         <v>45229</v>
@@ -2833,11 +2887,11 @@
       </c>
       <c r="I32" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J32" s="4">
         <f t="shared" ref="J32:J38" ca="1" si="3">IF(_xlfn.DAYS(TODAY(),H32)&lt;10000, _xlfn.DAYS(TODAY(),H32), "-")</f>
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="K32" s="2">
         <v>45229</v>
@@ -2856,7 +2910,7 @@
         <v>5</v>
       </c>
       <c r="C33" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
@@ -2891,7 +2945,7 @@
         <v>5</v>
       </c>
       <c r="C34" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D34" t="s">
         <v>24</v>
@@ -2910,11 +2964,11 @@
       </c>
       <c r="I34" s="4">
         <f ca="1">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H34), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H34), 7), "-")</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J34" s="4">
         <f ca="1">IF(_xlfn.DAYS(TODAY(),H34)&lt;10000, _xlfn.DAYS(TODAY(),H34), "-")</f>
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K34" s="2">
         <v>45257</v>
@@ -2938,7 +2992,7 @@
         <v>5</v>
       </c>
       <c r="C35" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
@@ -2976,7 +3030,7 @@
         <v>5</v>
       </c>
       <c r="C36" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
@@ -3014,7 +3068,7 @@
         <v>5</v>
       </c>
       <c r="C37" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D37" t="s">
         <v>23</v>
@@ -3033,11 +3087,11 @@
       </c>
       <c r="I37" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J37" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K37" s="2">
         <v>45257</v>
@@ -3061,7 +3115,7 @@
         <v>5</v>
       </c>
       <c r="C38" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D38" t="s">
         <v>24</v>
@@ -3080,11 +3134,11 @@
       </c>
       <c r="I38" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J38" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K38" s="2">
         <v>45257</v>
@@ -3108,7 +3162,7 @@
         <v>5</v>
       </c>
       <c r="C39" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D39" t="s">
         <v>25</v>
@@ -3127,11 +3181,11 @@
       </c>
       <c r="I39" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J39" s="4">
         <f t="shared" ref="J39:J41" ca="1" si="5">IF(_xlfn.DAYS(TODAY(),H39)&lt;10000, _xlfn.DAYS(TODAY(),H39), "-")</f>
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K39" s="2">
         <v>45257</v>
@@ -3155,7 +3209,7 @@
         <v>5</v>
       </c>
       <c r="C40" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D40" t="s">
         <v>23</v>
@@ -3174,11 +3228,11 @@
       </c>
       <c r="I40" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J40" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K40" s="2">
         <v>45257</v>
@@ -3199,7 +3253,7 @@
         <v>5</v>
       </c>
       <c r="C41" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D41" t="s">
         <v>25</v>
@@ -3218,11 +3272,11 @@
       </c>
       <c r="I41" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J41" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K41" s="2">
         <v>45257</v>
@@ -3266,7 +3320,7 @@
       </c>
       <c r="J42" s="4">
         <f t="shared" ref="J42" ca="1" si="6">IF(_xlfn.DAYS(TODAY(),H42)&lt;10000, _xlfn.DAYS(TODAY(),H42), "-")</f>
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="L42" s="4" t="str">
         <f t="shared" si="4"/>
@@ -3307,7 +3361,7 @@
       </c>
       <c r="J43" s="4">
         <f t="shared" ref="J43:J91" ca="1" si="7">IF(_xlfn.DAYS(TODAY(),H43)&lt;10000, _xlfn.DAYS(TODAY(),H43), "-")</f>
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="L43" s="4" t="str">
         <f t="shared" si="4"/>
@@ -3322,7 +3376,7 @@
         <v>5</v>
       </c>
       <c r="C44" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D44">
         <v>815</v>
@@ -3345,7 +3399,7 @@
       </c>
       <c r="J44" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K44" s="2">
         <v>45293</v>
@@ -3366,7 +3420,7 @@
         <v>5</v>
       </c>
       <c r="C45" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D45">
         <v>816</v>
@@ -3389,7 +3443,7 @@
       </c>
       <c r="J45" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K45" s="2">
         <v>45293</v>
@@ -3410,7 +3464,7 @@
         <v>5</v>
       </c>
       <c r="C46" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D46">
         <v>817</v>
@@ -3433,7 +3487,7 @@
       </c>
       <c r="J46" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K46" s="2">
         <v>45293</v>
@@ -3457,7 +3511,7 @@
         <v>5</v>
       </c>
       <c r="C47" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D47">
         <v>819</v>
@@ -3480,7 +3534,7 @@
       </c>
       <c r="J47" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K47" s="2">
         <v>45293</v>
@@ -3504,7 +3558,7 @@
         <v>5</v>
       </c>
       <c r="C48" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D48">
         <v>820</v>
@@ -3527,7 +3581,7 @@
       </c>
       <c r="J48" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K48" s="2">
         <v>45293</v>
@@ -3574,7 +3628,7 @@
       </c>
       <c r="J49" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K49" s="2">
         <v>45293</v>
@@ -3615,7 +3669,7 @@
       </c>
       <c r="J50" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K50" s="2">
         <v>45293</v>
@@ -3633,7 +3687,7 @@
         <v>5</v>
       </c>
       <c r="C51" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D51">
         <v>823</v>
@@ -3656,7 +3710,7 @@
       </c>
       <c r="J51" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K51" s="2">
         <v>45293</v>
@@ -3677,7 +3731,7 @@
         <v>5</v>
       </c>
       <c r="C52" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D52">
         <v>824</v>
@@ -3700,7 +3754,7 @@
       </c>
       <c r="J52" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K52" s="2">
         <v>45293</v>
@@ -3744,7 +3798,7 @@
       </c>
       <c r="J53" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K53" s="2">
         <v>45293</v>
@@ -3785,7 +3839,7 @@
       </c>
       <c r="J54" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="K54" s="2">
         <v>45238</v>
@@ -3826,7 +3880,7 @@
       </c>
       <c r="J55" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="K55" s="2">
         <v>45238</v>
@@ -3867,7 +3921,7 @@
       </c>
       <c r="J56" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="K56" s="2">
         <v>45238</v>
@@ -3901,11 +3955,11 @@
       </c>
       <c r="I57" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J57" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L57" s="4" t="str">
         <f t="shared" si="4"/>
@@ -3936,11 +3990,11 @@
       </c>
       <c r="I58" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J58" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L58" s="4" t="str">
         <f t="shared" si="4"/>
@@ -3972,7 +4026,7 @@
       </c>
       <c r="J59" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K59" s="2">
         <v>45295</v>
@@ -4007,7 +4061,7 @@
       </c>
       <c r="J60" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K60" s="2">
         <v>45295</v>
@@ -4042,7 +4096,7 @@
       </c>
       <c r="J61" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K61" s="2">
         <v>45295</v>
@@ -4077,7 +4131,7 @@
       </c>
       <c r="J62" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K62" s="2">
         <v>45295</v>
@@ -4112,7 +4166,7 @@
       </c>
       <c r="J63" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K63" s="2">
         <v>45295</v>
@@ -4147,7 +4201,7 @@
       </c>
       <c r="J64" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K64" s="2">
         <v>45295</v>
@@ -4181,11 +4235,11 @@
       </c>
       <c r="I65" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J65" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L65" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4216,11 +4270,11 @@
       </c>
       <c r="I66" s="4">
         <f t="shared" ref="I66:I91" ca="1" si="8">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H66), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H66), 7), "-")</f>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J66" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L66" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4254,11 +4308,11 @@
       </c>
       <c r="I67" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J67" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L67" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4304,11 +4358,11 @@
       </c>
       <c r="I68" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J68" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L68" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4354,11 +4408,11 @@
       </c>
       <c r="I69" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J69" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L69" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4404,11 +4458,11 @@
       </c>
       <c r="I70" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J70" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L70" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4454,11 +4508,11 @@
       </c>
       <c r="I71" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J71" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L71" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4504,11 +4558,11 @@
       </c>
       <c r="I72" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J72" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L72" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4554,11 +4608,11 @@
       </c>
       <c r="I73" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J73" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L73" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4604,11 +4658,11 @@
       </c>
       <c r="I74" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J74" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L74" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4654,11 +4708,11 @@
       </c>
       <c r="I75" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J75" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L75" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4704,11 +4758,11 @@
       </c>
       <c r="I76" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J76" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L76" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4754,11 +4808,11 @@
       </c>
       <c r="I77" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J77" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L77" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4804,11 +4858,11 @@
       </c>
       <c r="I78" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J78" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L78" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4854,11 +4908,11 @@
       </c>
       <c r="I79" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J79" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L79" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4904,11 +4958,11 @@
       </c>
       <c r="I80" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J80" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L80" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4954,11 +5008,11 @@
       </c>
       <c r="I81" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J81" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L81" s="4" t="str">
         <f t="shared" si="4"/>
@@ -5004,11 +5058,11 @@
       </c>
       <c r="I82" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J82" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L82" s="4" t="str">
         <f t="shared" si="4"/>
@@ -5054,11 +5108,11 @@
       </c>
       <c r="I83" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J83" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L83" s="4" t="str">
         <f t="shared" si="4"/>
@@ -5104,11 +5158,11 @@
       </c>
       <c r="I84" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J84" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L84" s="4" t="str">
         <f t="shared" si="4"/>
@@ -5154,11 +5208,11 @@
       </c>
       <c r="I85" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J85" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L85" s="4" t="str">
         <f t="shared" si="4"/>
@@ -5204,11 +5258,11 @@
       </c>
       <c r="I86" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J86" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L86" s="4" t="str">
         <f t="shared" si="4"/>
@@ -5254,11 +5308,11 @@
       </c>
       <c r="I87" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J87" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K87" s="2">
         <v>45272</v>
@@ -5274,7 +5328,7 @@
         <v>141</v>
       </c>
       <c r="Q87" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="88" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -5301,11 +5355,11 @@
       </c>
       <c r="I88" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J88" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K88" s="2">
         <v>45273</v>
@@ -5321,7 +5375,7 @@
         <v>141</v>
       </c>
       <c r="Q88" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="89" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -5348,11 +5402,11 @@
       </c>
       <c r="I89" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J89" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K89" s="2">
         <v>45274</v>
@@ -5368,7 +5422,7 @@
         <v>141</v>
       </c>
       <c r="Q89" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="90" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -5395,11 +5449,11 @@
       </c>
       <c r="I90" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J90" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K90" s="2">
         <v>45275</v>
@@ -5415,7 +5469,7 @@
         <v>141</v>
       </c>
       <c r="Q90" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="91" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -5442,11 +5496,11 @@
       </c>
       <c r="I91" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J91" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K91" s="2">
         <v>45276</v>
@@ -5462,7 +5516,7 @@
         <v>141</v>
       </c>
       <c r="Q91" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="92" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -5489,11 +5543,11 @@
       </c>
       <c r="I92" s="4">
         <f t="shared" ref="I92:I93" ca="1" si="9">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H92), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H92), 7), "-")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J92" s="4">
         <f t="shared" ref="J92:J93" ca="1" si="10">IF(_xlfn.DAYS(TODAY(),H92)&lt;10000, _xlfn.DAYS(TODAY(),H92), "-")</f>
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K92" s="2">
         <v>45277</v>
@@ -5509,7 +5563,7 @@
         <v>141</v>
       </c>
       <c r="Q92" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="93" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -5536,11 +5590,11 @@
       </c>
       <c r="I93" s="4">
         <f t="shared" ca="1" si="9"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J93" s="4">
         <f t="shared" ca="1" si="10"/>
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K93" s="2">
         <v>45278</v>
@@ -5583,11 +5637,11 @@
       </c>
       <c r="I94" s="4">
         <f t="shared" ref="I94" ca="1" si="11">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H94), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H94), 7), "-")</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J94" s="4">
         <f t="shared" ref="J94" ca="1" si="12">IF(_xlfn.DAYS(TODAY(),H94)&lt;10000, _xlfn.DAYS(TODAY(),H94), "-")</f>
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K94" s="2">
         <v>45223</v>
@@ -5633,11 +5687,11 @@
       </c>
       <c r="I95" s="4">
         <f t="shared" ref="I95:I117" ca="1" si="13">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H95), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H95), 7), "-")</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J95" s="4">
         <f t="shared" ref="J95:J117" ca="1" si="14">IF(_xlfn.DAYS(TODAY(),H95)&lt;10000, _xlfn.DAYS(TODAY(),H95), "-")</f>
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K95" s="2">
         <v>45223</v>
@@ -5683,11 +5737,11 @@
       </c>
       <c r="I96" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J96" s="4">
         <f t="shared" ca="1" si="14"/>
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K96" s="2">
         <v>45223</v>
@@ -5733,11 +5787,11 @@
       </c>
       <c r="I97" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J97" s="4">
         <f t="shared" ca="1" si="14"/>
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K97" s="2">
         <v>45223</v>
@@ -5787,7 +5841,7 @@
       </c>
       <c r="J98" s="4">
         <f t="shared" ref="J98:J107" ca="1" si="17">IF(_xlfn.DAYS(TODAY(),H98)&lt;10000, _xlfn.DAYS(TODAY(),H98), "-")</f>
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K98" s="2">
         <v>45267</v>
@@ -5802,6 +5856,9 @@
       <c r="N98" s="2">
         <v>45278</v>
       </c>
+      <c r="O98" s="2">
+        <v>45318</v>
+      </c>
       <c r="P98" s="2" t="s">
         <v>72</v>
       </c>
@@ -5837,7 +5894,7 @@
       </c>
       <c r="J99" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K99" s="2">
         <v>45267</v>
@@ -5852,6 +5909,9 @@
       <c r="N99" s="2">
         <v>45278</v>
       </c>
+      <c r="O99" s="2">
+        <v>45320</v>
+      </c>
       <c r="P99" s="2" t="s">
         <v>72</v>
       </c>
@@ -5887,7 +5947,7 @@
       </c>
       <c r="J100" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K100" s="2">
         <v>45267</v>
@@ -5902,6 +5962,9 @@
       <c r="N100" s="2">
         <v>45278</v>
       </c>
+      <c r="O100" s="2">
+        <v>45320</v>
+      </c>
       <c r="P100" s="2" t="s">
         <v>72</v>
       </c>
@@ -5937,7 +6000,7 @@
       </c>
       <c r="J101" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K101" s="2">
         <v>45267</v>
@@ -5952,6 +6015,9 @@
       <c r="N101" s="2">
         <v>45278</v>
       </c>
+      <c r="O101" s="2">
+        <v>45318</v>
+      </c>
       <c r="P101" s="2" t="s">
         <v>72</v>
       </c>
@@ -5987,7 +6053,7 @@
       </c>
       <c r="J102" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K102" s="2">
         <v>45267</v>
@@ -6002,6 +6068,9 @@
       <c r="N102" s="2">
         <v>45278</v>
       </c>
+      <c r="O102" s="2">
+        <v>45318</v>
+      </c>
       <c r="P102" s="2" t="s">
         <v>72</v>
       </c>
@@ -6037,7 +6106,7 @@
       </c>
       <c r="J103" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K103" s="2">
         <v>45267</v>
@@ -6087,7 +6156,7 @@
       </c>
       <c r="J104" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K104" s="2">
         <v>45267</v>
@@ -6137,7 +6206,7 @@
       </c>
       <c r="J105" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K105" s="2">
         <v>45267</v>
@@ -6152,6 +6221,9 @@
       <c r="N105" s="2">
         <v>45278</v>
       </c>
+      <c r="O105" s="2">
+        <v>45317</v>
+      </c>
       <c r="P105" s="2" t="s">
         <v>72</v>
       </c>
@@ -6187,7 +6259,7 @@
       </c>
       <c r="J106" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K106" s="2">
         <v>45267</v>
@@ -6237,7 +6309,7 @@
       </c>
       <c r="J107" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K107" s="2">
         <v>45267</v>
@@ -6580,6 +6652,9 @@
       <c r="M115" t="s">
         <v>67</v>
       </c>
+      <c r="O115" s="2">
+        <v>45315</v>
+      </c>
       <c r="P115" s="2" t="s">
         <v>68</v>
       </c>
@@ -6779,7 +6854,7 @@
       </c>
       <c r="J120" s="4">
         <f t="shared" ca="1" si="19"/>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K120" s="2">
         <v>45315</v>
@@ -6820,7 +6895,7 @@
       </c>
       <c r="J121" s="4">
         <f t="shared" ca="1" si="19"/>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K121" s="2">
         <v>45315</v>
@@ -6861,7 +6936,7 @@
       </c>
       <c r="J122" s="4">
         <f t="shared" ca="1" si="19"/>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K122" s="2">
         <v>45315</v>
@@ -6902,7 +6977,7 @@
       </c>
       <c r="J123" s="4">
         <f t="shared" ca="1" si="19"/>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K123" s="2">
         <v>45315</v>
@@ -6934,7 +7009,7 @@
       </c>
       <c r="J124" s="4">
         <f t="shared" ca="1" si="19"/>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L124" s="4" t="str">
         <f t="shared" si="15"/>
@@ -6966,7 +7041,7 @@
       </c>
       <c r="J125" s="4">
         <f t="shared" ref="J125:J127" ca="1" si="21">IF(_xlfn.DAYS(TODAY(),H125)&lt;10000, _xlfn.DAYS(TODAY(),H125), "-")</f>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L125" s="4" t="str">
         <f t="shared" si="15"/>
@@ -6998,7 +7073,7 @@
       </c>
       <c r="J126" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L126" s="4" t="str">
         <f t="shared" si="15"/>
@@ -7030,7 +7105,7 @@
       </c>
       <c r="J127" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L127" s="4" t="str">
         <f t="shared" si="15"/>
@@ -7062,7 +7137,7 @@
       </c>
       <c r="J128" s="4">
         <f t="shared" ref="J128:J130" ca="1" si="23">IF(_xlfn.DAYS(TODAY(),H128)&lt;10000, _xlfn.DAYS(TODAY(),H128), "-")</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L128" s="4" t="str">
         <f t="shared" si="15"/>
@@ -7094,7 +7169,7 @@
       </c>
       <c r="J129" s="4">
         <f t="shared" ca="1" si="23"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L129" s="4" t="str">
         <f t="shared" si="15"/>
@@ -7126,7 +7201,7 @@
       </c>
       <c r="J130" s="4">
         <f t="shared" ca="1" si="23"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L130" s="4" t="str">
         <f t="shared" si="15"/>
@@ -7191,7 +7266,7 @@
       </c>
       <c r="J132" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="L132" s="4" t="str">
         <f t="shared" si="26"/>
@@ -7226,7 +7301,7 @@
       </c>
       <c r="J133" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="L133" s="4" t="str">
         <f t="shared" si="26"/>
@@ -7258,7 +7333,7 @@
       </c>
       <c r="J134" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="L134" s="4" t="str">
         <f t="shared" si="26"/>
@@ -7290,7 +7365,7 @@
       </c>
       <c r="J135" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="L135" s="4" t="str">
         <f t="shared" si="26"/>
@@ -7325,7 +7400,7 @@
       </c>
       <c r="J136" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="L136" s="4" t="str">
         <f t="shared" si="26"/>
@@ -7357,7 +7432,7 @@
       </c>
       <c r="J137" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="L137" s="4" t="str">
         <f t="shared" si="26"/>
@@ -7375,7 +7450,7 @@
         <v>148</v>
       </c>
       <c r="F138" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G138" t="s">
         <v>151</v>
@@ -7392,7 +7467,7 @@
         <f t="shared" si="26"/>
         <v>-</v>
       </c>
-      <c r="M138" s="4" t="s">
+      <c r="M138" s="1" t="s">
         <v>149</v>
       </c>
     </row>
@@ -7404,7 +7479,7 @@
         <v>148</v>
       </c>
       <c r="F139" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G139" t="s">
         <v>152</v>
@@ -7421,11 +7496,8 @@
         <f t="shared" si="26"/>
         <v>-</v>
       </c>
-      <c r="M139" s="4" t="s">
+      <c r="M139" s="23" t="s">
         <v>150</v>
-      </c>
-      <c r="Q139" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="140" spans="2:17" x14ac:dyDescent="0.3">
@@ -7436,7 +7508,7 @@
         <v>148</v>
       </c>
       <c r="F140" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G140" t="s">
         <v>151</v>
@@ -7453,7 +7525,7 @@
         <f t="shared" si="26"/>
         <v>-</v>
       </c>
-      <c r="M140" s="4" t="s">
+      <c r="M140" s="1" t="s">
         <v>150</v>
       </c>
     </row>
@@ -7465,25 +7537,28 @@
         <v>148</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H141" s="2">
         <v>45301</v>
       </c>
       <c r="I141" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J141" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L141" s="4" t="str">
         <f t="shared" si="26"/>
         <v>-</v>
       </c>
       <c r="M141" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
+      </c>
+      <c r="Q141" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="142" spans="2:17" x14ac:dyDescent="0.3">
@@ -7494,25 +7569,28 @@
         <v>148</v>
       </c>
       <c r="E142" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H142" s="2">
         <v>45301</v>
       </c>
       <c r="I142" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J142" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L142" s="4" t="str">
         <f t="shared" si="26"/>
         <v>-</v>
       </c>
       <c r="M142" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
+      </c>
+      <c r="Q142" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="143" spans="2:17" x14ac:dyDescent="0.3">
@@ -7523,25 +7601,28 @@
         <v>148</v>
       </c>
       <c r="E143" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H143" s="2">
         <v>45301</v>
       </c>
       <c r="I143" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J143" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L143" s="4" t="str">
         <f t="shared" si="26"/>
         <v>-</v>
       </c>
       <c r="M143" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
+      </c>
+      <c r="Q143" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="144" spans="2:17" x14ac:dyDescent="0.3">
@@ -7552,25 +7633,28 @@
         <v>148</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H144" s="2">
         <v>45301</v>
       </c>
       <c r="I144" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J144" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L144" s="4" t="str">
         <f t="shared" si="26"/>
         <v>-</v>
       </c>
       <c r="M144" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
+      </c>
+      <c r="Q144" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="145" spans="2:17" x14ac:dyDescent="0.3">
@@ -7581,25 +7665,28 @@
         <v>148</v>
       </c>
       <c r="E145" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H145" s="2">
         <v>45301</v>
       </c>
       <c r="I145" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J145" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L145" s="4" t="str">
         <f t="shared" si="26"/>
         <v>-</v>
       </c>
       <c r="M145" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
+      </c>
+      <c r="Q145" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="146" spans="2:17" x14ac:dyDescent="0.3">
@@ -7610,25 +7697,28 @@
         <v>148</v>
       </c>
       <c r="E146" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H146" s="2">
         <v>45301</v>
       </c>
       <c r="I146" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J146" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L146" s="4" t="str">
         <f t="shared" si="26"/>
         <v>-</v>
       </c>
       <c r="M146" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
+      </c>
+      <c r="Q146" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="147" spans="2:17" x14ac:dyDescent="0.3">
@@ -7639,7 +7729,7 @@
         <v>148</v>
       </c>
       <c r="F147" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G147" t="s">
         <v>151</v>
@@ -7657,7 +7747,7 @@
         <v>-</v>
       </c>
       <c r="M147" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="148" spans="2:17" x14ac:dyDescent="0.3">
@@ -7668,7 +7758,7 @@
         <v>148</v>
       </c>
       <c r="F148" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G148" t="s">
         <v>152</v>
@@ -7685,8 +7775,8 @@
         <f t="shared" si="29"/>
         <v>-</v>
       </c>
-      <c r="M148" s="4" t="s">
-        <v>156</v>
+      <c r="M148" s="1" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="149" spans="2:17" x14ac:dyDescent="0.3">
@@ -7697,7 +7787,7 @@
         <v>148</v>
       </c>
       <c r="F149" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G149" t="s">
         <v>151</v>
@@ -7715,7 +7805,7 @@
         <v>-</v>
       </c>
       <c r="M149" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="150" spans="2:17" x14ac:dyDescent="0.3">
@@ -7726,7 +7816,7 @@
         <v>148</v>
       </c>
       <c r="F150" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G150" t="s">
         <v>152</v>
@@ -7744,7 +7834,7 @@
         <v>-</v>
       </c>
       <c r="M150" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="151" spans="2:17" x14ac:dyDescent="0.3">
@@ -7755,25 +7845,25 @@
         <v>148</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H151" s="2">
         <v>45307</v>
       </c>
       <c r="I151" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J151" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L151" s="4" t="str">
         <f t="shared" si="29"/>
         <v>-</v>
       </c>
       <c r="M151" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="152" spans="2:17" x14ac:dyDescent="0.3">
@@ -7784,25 +7874,25 @@
         <v>148</v>
       </c>
       <c r="E152" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H152" s="2">
         <v>45307</v>
       </c>
       <c r="I152" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J152" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L152" s="4" t="str">
         <f t="shared" si="29"/>
         <v>-</v>
       </c>
       <c r="M152" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="153" spans="2:17" x14ac:dyDescent="0.3">
@@ -7813,25 +7903,25 @@
         <v>148</v>
       </c>
       <c r="E153" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H153" s="2">
         <v>45307</v>
       </c>
       <c r="I153" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J153" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L153" s="4" t="str">
         <f t="shared" si="29"/>
         <v>-</v>
       </c>
       <c r="M153" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="154" spans="2:17" x14ac:dyDescent="0.3">
@@ -7842,25 +7932,25 @@
         <v>148</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H154" s="2">
         <v>45307</v>
       </c>
       <c r="I154" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J154" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L154" s="4" t="str">
         <f t="shared" si="29"/>
         <v>-</v>
       </c>
       <c r="M154" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="155" spans="2:17" x14ac:dyDescent="0.3">
@@ -7871,25 +7961,25 @@
         <v>148</v>
       </c>
       <c r="E155" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H155" s="2">
         <v>45307</v>
       </c>
       <c r="I155" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J155" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L155" s="4" t="str">
         <f t="shared" si="29"/>
         <v>-</v>
       </c>
       <c r="M155" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="156" spans="2:17" x14ac:dyDescent="0.3">
@@ -7900,25 +7990,25 @@
         <v>148</v>
       </c>
       <c r="E156" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H156" s="2">
         <v>45307</v>
       </c>
       <c r="I156" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J156" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L156" s="4" t="str">
         <f t="shared" si="29"/>
         <v>-</v>
       </c>
       <c r="M156" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="157" spans="2:17" x14ac:dyDescent="0.3">
@@ -7931,8 +8021,11 @@
       <c r="D157">
         <v>710</v>
       </c>
+      <c r="E157" t="s">
+        <v>8</v>
+      </c>
       <c r="F157" s="5" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="G157" t="s">
         <v>151</v>
@@ -7942,21 +8035,21 @@
       </c>
       <c r="I157" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J157" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L157" s="4" t="str">
         <f t="shared" si="29"/>
         <v>-</v>
       </c>
-      <c r="M157" s="4" t="s">
-        <v>162</v>
+      <c r="M157" s="25" t="s">
+        <v>161</v>
       </c>
       <c r="Q157" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="158" spans="2:17" x14ac:dyDescent="0.3">
@@ -7970,7 +8063,7 @@
         <v>708</v>
       </c>
       <c r="F158" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G158" t="s">
         <v>152</v>
@@ -7987,11 +8080,8 @@
         <f t="shared" si="29"/>
         <v>-</v>
       </c>
-      <c r="M158" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q158" t="s">
-        <v>175</v>
+      <c r="M158" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="159" spans="2:17" x14ac:dyDescent="0.3">
@@ -8005,7 +8095,7 @@
         <v>767</v>
       </c>
       <c r="F159" s="5" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G159" t="s">
         <v>151</v>
@@ -8022,11 +8112,8 @@
         <f t="shared" si="29"/>
         <v>-</v>
       </c>
-      <c r="M159" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="Q159" t="s">
-        <v>180</v>
+      <c r="M159" s="1" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="160" spans="2:17" x14ac:dyDescent="0.3">
@@ -8040,7 +8127,7 @@
         <v>769</v>
       </c>
       <c r="F160" s="5" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G160" t="s">
         <v>151</v>
@@ -8057,11 +8144,8 @@
         <f t="shared" si="29"/>
         <v>-</v>
       </c>
-      <c r="M160" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="Q160" t="s">
-        <v>178</v>
+      <c r="M160" s="1" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="161" spans="2:17" x14ac:dyDescent="0.3">
@@ -8075,7 +8159,10 @@
         <v>606</v>
       </c>
       <c r="E161" t="s">
-        <v>161</v>
+        <v>8</v>
+      </c>
+      <c r="F161" s="5" t="s">
+        <v>175</v>
       </c>
       <c r="G161" t="s">
         <v>152</v>
@@ -8089,7 +8176,7 @@
       </c>
       <c r="J161" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K161" s="2">
         <v>45301</v>
@@ -8098,11 +8185,8 @@
         <f t="shared" si="29"/>
         <v>32</v>
       </c>
-      <c r="M161" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="Q161" t="s">
-        <v>167</v>
+      <c r="M161" s="1" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="162" spans="2:17" x14ac:dyDescent="0.3">
@@ -8116,7 +8200,10 @@
         <v>607</v>
       </c>
       <c r="E162" t="s">
-        <v>161</v>
+        <v>8</v>
+      </c>
+      <c r="F162" s="5" t="s">
+        <v>175</v>
       </c>
       <c r="G162" t="s">
         <v>152</v>
@@ -8130,7 +8217,7 @@
       </c>
       <c r="J162" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K162" s="2">
         <v>45301</v>
@@ -8139,14 +8226,11 @@
         <f t="shared" si="29"/>
         <v>32</v>
       </c>
-      <c r="M162" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="Q162" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="163" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="M162" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="163" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B163" t="s">
         <v>147</v>
       </c>
@@ -8157,7 +8241,7 @@
         <v>608</v>
       </c>
       <c r="E163" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G163" t="s">
         <v>152</v>
@@ -8171,7 +8255,7 @@
       </c>
       <c r="J163" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K163" s="2">
         <v>45301</v>
@@ -8181,10 +8265,13 @@
         <v>32</v>
       </c>
       <c r="M163" s="4" t="s">
-        <v>168</v>
+        <v>165</v>
+      </c>
+      <c r="O163" s="2">
+        <v>45321</v>
       </c>
       <c r="Q163" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
     </row>
     <row r="164" spans="2:17" x14ac:dyDescent="0.3">
@@ -8198,7 +8285,10 @@
         <v>609</v>
       </c>
       <c r="E164" t="s">
-        <v>161</v>
+        <v>8</v>
+      </c>
+      <c r="F164" s="5" t="s">
+        <v>175</v>
       </c>
       <c r="G164" t="s">
         <v>152</v>
@@ -8212,7 +8302,7 @@
       </c>
       <c r="J164" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K164" s="2">
         <v>45301</v>
@@ -8221,11 +8311,8 @@
         <f t="shared" si="29"/>
         <v>32</v>
       </c>
-      <c r="M164" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="Q164" t="s">
-        <v>167</v>
+      <c r="M164" s="1" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="165" spans="2:17" x14ac:dyDescent="0.3">
@@ -8239,7 +8326,10 @@
         <v>610</v>
       </c>
       <c r="E165" t="s">
-        <v>161</v>
+        <v>8</v>
+      </c>
+      <c r="F165" s="5" t="s">
+        <v>176</v>
       </c>
       <c r="G165" t="s">
         <v>152</v>
@@ -8253,7 +8343,7 @@
       </c>
       <c r="J165" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K165" s="2">
         <v>45301</v>
@@ -8262,11 +8352,11 @@
         <f t="shared" si="29"/>
         <v>32</v>
       </c>
-      <c r="M165" s="4" t="s">
-        <v>169</v>
+      <c r="M165" s="8" t="s">
+        <v>166</v>
       </c>
       <c r="Q165" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
     </row>
     <row r="166" spans="2:17" x14ac:dyDescent="0.3">
@@ -8280,7 +8370,10 @@
         <v>611</v>
       </c>
       <c r="E166" t="s">
-        <v>161</v>
+        <v>8</v>
+      </c>
+      <c r="F166" s="5" t="s">
+        <v>175</v>
       </c>
       <c r="G166" t="s">
         <v>152</v>
@@ -8294,7 +8387,7 @@
       </c>
       <c r="J166" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K166" s="2">
         <v>45301</v>
@@ -8304,10 +8397,10 @@
         <v>32</v>
       </c>
       <c r="M166" s="4" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="Q166" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
     </row>
     <row r="167" spans="2:17" x14ac:dyDescent="0.3">
@@ -8321,7 +8414,7 @@
         <v>708</v>
       </c>
       <c r="F167" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G167" t="s">
         <v>151</v>
@@ -8331,21 +8424,18 @@
       </c>
       <c r="I167" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J167" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L167" s="4" t="str">
         <f t="shared" si="29"/>
         <v>-</v>
       </c>
-      <c r="M167" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="Q167" t="s">
-        <v>181</v>
+      <c r="M167" s="24" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="168" spans="2:17" x14ac:dyDescent="0.3">
@@ -8359,7 +8449,7 @@
         <v>709</v>
       </c>
       <c r="F168" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G168" t="s">
         <v>151</v>
@@ -8369,18 +8459,18 @@
       </c>
       <c r="I168" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J168" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L168" s="4" t="str">
         <f t="shared" si="29"/>
         <v>-</v>
       </c>
-      <c r="M168" s="4" t="s">
-        <v>170</v>
+      <c r="M168" s="24" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="169" spans="2:17" x14ac:dyDescent="0.3">
@@ -8394,7 +8484,7 @@
         <v>711</v>
       </c>
       <c r="F169" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G169" t="s">
         <v>151</v>
@@ -8404,18 +8494,18 @@
       </c>
       <c r="I169" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J169" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L169" s="4" t="str">
         <f t="shared" si="29"/>
         <v>-</v>
       </c>
-      <c r="M169" s="4" t="s">
-        <v>170</v>
+      <c r="M169" s="24" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="170" spans="2:17" x14ac:dyDescent="0.3">
@@ -8429,7 +8519,10 @@
         <v>601</v>
       </c>
       <c r="E170" t="s">
-        <v>161</v>
+        <v>8</v>
+      </c>
+      <c r="F170" s="5" t="s">
+        <v>176</v>
       </c>
       <c r="G170" t="s">
         <v>152</v>
@@ -8443,7 +8536,7 @@
       </c>
       <c r="J170" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K170" s="2">
         <v>45301</v>
@@ -8452,11 +8545,11 @@
         <f t="shared" si="29"/>
         <v>32</v>
       </c>
-      <c r="M170" s="4" t="s">
-        <v>171</v>
+      <c r="M170" s="8" t="s">
+        <v>168</v>
       </c>
       <c r="Q170" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
     </row>
     <row r="171" spans="2:17" x14ac:dyDescent="0.3">
@@ -8470,7 +8563,10 @@
         <v>602</v>
       </c>
       <c r="E171" t="s">
-        <v>161</v>
+        <v>8</v>
+      </c>
+      <c r="F171" s="5" t="s">
+        <v>177</v>
       </c>
       <c r="G171" t="s">
         <v>152</v>
@@ -8484,7 +8580,7 @@
       </c>
       <c r="J171" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K171" s="2">
         <v>45301</v>
@@ -8493,11 +8589,8 @@
         <f t="shared" si="29"/>
         <v>32</v>
       </c>
-      <c r="M171" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="Q171" t="s">
-        <v>167</v>
+      <c r="M171" s="1" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="172" spans="2:17" x14ac:dyDescent="0.3">
@@ -8511,7 +8604,10 @@
         <v>603</v>
       </c>
       <c r="E172" t="s">
-        <v>161</v>
+        <v>8</v>
+      </c>
+      <c r="F172" s="5" t="s">
+        <v>176</v>
       </c>
       <c r="G172" t="s">
         <v>151</v>
@@ -8525,7 +8621,7 @@
       </c>
       <c r="J172" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K172" s="2">
         <v>45301</v>
@@ -8534,11 +8630,8 @@
         <f t="shared" si="29"/>
         <v>32</v>
       </c>
-      <c r="M172" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="Q172" t="s">
-        <v>167</v>
+      <c r="M172" s="24" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="173" spans="2:17" x14ac:dyDescent="0.3">
@@ -8552,7 +8645,10 @@
         <v>604</v>
       </c>
       <c r="E173" t="s">
-        <v>161</v>
+        <v>8</v>
+      </c>
+      <c r="F173" s="5" t="s">
+        <v>176</v>
       </c>
       <c r="G173" t="s">
         <v>151</v>
@@ -8566,7 +8662,7 @@
       </c>
       <c r="J173" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K173" s="2">
         <v>45301</v>
@@ -8575,11 +8671,8 @@
         <f t="shared" si="29"/>
         <v>32</v>
       </c>
-      <c r="M173" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="Q173" t="s">
-        <v>167</v>
+      <c r="M173" s="24" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="174" spans="2:17" x14ac:dyDescent="0.3">
@@ -8593,7 +8686,10 @@
         <v>605</v>
       </c>
       <c r="E174" t="s">
-        <v>161</v>
+        <v>8</v>
+      </c>
+      <c r="F174" s="5" t="s">
+        <v>176</v>
       </c>
       <c r="G174" t="s">
         <v>151</v>
@@ -8607,7 +8703,7 @@
       </c>
       <c r="J174" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K174" s="2">
         <v>45301</v>
@@ -8616,11 +8712,8 @@
         <f t="shared" si="29"/>
         <v>32</v>
       </c>
-      <c r="M174" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="Q174" t="s">
-        <v>167</v>
+      <c r="M174" s="24" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="175" spans="2:17" x14ac:dyDescent="0.3">
@@ -8630,8 +8723,14 @@
       <c r="C175" t="s">
         <v>148</v>
       </c>
+      <c r="D175">
+        <v>649</v>
+      </c>
       <c r="E175" t="s">
-        <v>161</v>
+        <v>8</v>
+      </c>
+      <c r="F175" s="5" t="s">
+        <v>177</v>
       </c>
       <c r="G175" t="s">
         <v>151</v>
@@ -8645,17 +8744,14 @@
       </c>
       <c r="J175" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="L175" s="4" t="str">
         <f t="shared" si="29"/>
         <v>-</v>
       </c>
-      <c r="M175" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="Q175" t="s">
-        <v>167</v>
+      <c r="M175" s="1" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="176" spans="2:17" x14ac:dyDescent="0.3">
@@ -8665,8 +8761,14 @@
       <c r="C176" t="s">
         <v>148</v>
       </c>
+      <c r="D176">
+        <v>650</v>
+      </c>
       <c r="E176" t="s">
-        <v>161</v>
+        <v>8</v>
+      </c>
+      <c r="F176" s="5" t="s">
+        <v>176</v>
       </c>
       <c r="G176" t="s">
         <v>151</v>
@@ -8680,17 +8782,17 @@
       </c>
       <c r="J176" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="L176" s="4" t="str">
         <f t="shared" si="29"/>
         <v>-</v>
       </c>
-      <c r="M176" s="4" t="s">
-        <v>173</v>
+      <c r="M176" s="24" t="s">
+        <v>170</v>
       </c>
       <c r="Q176" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
     </row>
     <row r="177" spans="9:12" hidden="1" x14ac:dyDescent="0.3">
@@ -12461,15 +12563,13 @@
     </row>
   </sheetData>
   <autoFilter ref="B1:Q445" xr:uid="{47ECCD65-6802-4B2B-901A-AED4A431A765}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="SPF"/>
-      </filters>
-    </filterColumn>
     <filterColumn colId="1">
       <filters>
         <filter val="Tcrd-CreER; Tsg101-flox"/>
       </filters>
+    </filterColumn>
+    <filterColumn colId="13">
+      <filters blank="1"/>
     </filterColumn>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -12482,7 +12582,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E140 E142:E143 E145:E150 E152:E153 E155:E158 E160:E1048576" xr:uid="{939E2B39-E841-4A9F-AD11-00C266DB2690}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E140 E142:E143 E145:E150 E152:E153 E160:E1048576 E155:E158" xr:uid="{939E2B39-E841-4A9F-AD11-00C266DB2690}">
       <formula1>"Y, N"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1:G1048576" xr:uid="{2DE54AC7-5B92-48D6-98C4-E6203F87CDD0}">

--- a/Mouse 내역.xlsx
+++ b/Mouse 내역.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\heung\OneDrive\바탕 화면\동물실\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F7A179C-60FE-4C56-96D0-ABE1F39DCC15}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FB30608-D876-4DE2-AFF4-4F3E10DBB6E1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19080" windowHeight="9180" activeTab="1" xr2:uid="{5A73A69A-2AFB-4F3E-AC64-070DD7700CB2}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19080" windowHeight="9180" xr2:uid="{5A73A69A-2AFB-4F3E-AC64-070DD7700CB2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$Q$445</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$Q$455</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1190" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1250" uniqueCount="194">
   <si>
     <t>Strain</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -301,10 +301,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>비고</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>DMSO</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -612,10 +608,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>H1.B</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>H2.B</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -632,10 +624,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>H1.2.X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>H3.B</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -660,18 +648,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>H0.1.F</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>H0.1.M</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>H0.2.F</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>+/+; f/f</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -696,10 +676,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>H0.6.F</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Tmem119-CreERT2; Tsg101-flox</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -738,11 +714,79 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>H0.5.F와 합사</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>H1.1.F와 합사</t>
+    <t>H5.B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>H6.B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>H1.2.M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>H1.2.F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>H7.B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>from H0.1.F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>from H0.6.F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Exp. 4-1-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>H9.B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>H8.B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Exp. 4-2-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D1.3.F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D1.3.M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>from E1.2.M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E1.3.X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Breader A4.B</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -750,6 +794,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
+  </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -986,16 +1033,16 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="4" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="4" applyFont="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1577,7 +1624,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D71A6DC-E91C-489F-8F50-989C4712FA7C}">
   <sheetPr filterMode="1"/>
-  <dimension ref="B1:Q445"/>
+  <dimension ref="B1:Q455"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="10.5" customWidth="1"/>
@@ -1625,7 +1672,7 @@
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L1" s="8" t="s">
         <v>14</v>
@@ -1642,22 +1689,20 @@
       <c r="P1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="Q1" s="1" t="s">
-        <v>69</v>
-      </c>
+      <c r="Q1" s="1"/>
     </row>
     <row r="2" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G2" t="s">
         <v>11</v>
@@ -1667,11 +1712,11 @@
       </c>
       <c r="I2" s="4">
         <f ca="1">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H2), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H2), 7), "-")</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J2" s="4">
         <f ca="1">IF(_xlfn.DAYS(TODAY(),H2)&lt;10000, _xlfn.DAYS(TODAY(),H2), "-")</f>
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="L2" s="4" t="str">
         <f t="shared" ref="L2:L31" si="0">IF(_xlfn.DAYS(K2,H2)&gt;0, _xlfn.DAYS(K2,H2), "-")</f>
@@ -1685,18 +1730,18 @@
         <v>45299</v>
       </c>
     </row>
-    <row r="3" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G3" t="s">
         <v>13</v>
@@ -1706,11 +1751,11 @@
       </c>
       <c r="I3" s="4">
         <f t="shared" ref="I3:I65" ca="1" si="1">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H3), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H3), 7), "-")</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J3" s="4">
         <f t="shared" ref="J3:J31" ca="1" si="2">IF(_xlfn.DAYS(TODAY(),H3)&lt;10000, _xlfn.DAYS(TODAY(),H3), "-")</f>
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="L3" s="4" t="str">
         <f t="shared" si="0"/>
@@ -1722,18 +1767,18 @@
       <c r="N3" s="7"/>
       <c r="O3" s="7"/>
     </row>
-    <row r="4" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G4" t="s">
         <v>13</v>
@@ -1743,11 +1788,11 @@
       </c>
       <c r="I4" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J4" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="L4" s="4" t="str">
         <f t="shared" si="0"/>
@@ -1764,7 +1809,7 @@
         <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D5">
         <v>871</v>
@@ -1773,10 +1818,10 @@
         <v>16</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H5" s="2">
         <v>45266</v>
@@ -1787,7 +1832,7 @@
       </c>
       <c r="J5" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="K5" s="2">
         <v>45293</v>
@@ -1797,7 +1842,7 @@
         <v>27</v>
       </c>
       <c r="M5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="N5" s="7"/>
       <c r="O5" s="7">
@@ -1809,7 +1854,7 @@
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="D6">
         <v>686</v>
@@ -1818,10 +1863,10 @@
         <v>16</v>
       </c>
       <c r="F6" s="20" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H6" s="14">
         <v>45266</v>
@@ -1832,7 +1877,7 @@
       </c>
       <c r="J6" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="K6" s="14">
         <v>45293</v>
@@ -1842,20 +1887,20 @@
         <v>27</v>
       </c>
       <c r="M6" s="16" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="N6" s="7"/>
       <c r="O6" s="18"/>
       <c r="Q6" s="17" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="7" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="7" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D7">
         <v>687</v>
@@ -1863,11 +1908,11 @@
       <c r="E7" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="G7" s="17" t="s">
-        <v>78</v>
+      <c r="F7" s="25" t="s">
+        <v>96</v>
+      </c>
+      <c r="G7" s="15" t="s">
+        <v>77</v>
       </c>
       <c r="H7" s="14">
         <v>45266</v>
@@ -1878,7 +1923,7 @@
       </c>
       <c r="J7" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="K7" s="14">
         <v>45293</v>
@@ -1887,19 +1932,21 @@
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="M7" s="16" t="s">
-        <v>76</v>
+      <c r="M7" s="15" t="s">
+        <v>75</v>
       </c>
       <c r="N7" s="7"/>
       <c r="O7" s="18"/>
-      <c r="Q7" s="17"/>
+      <c r="Q7" t="s">
+        <v>193</v>
+      </c>
     </row>
     <row r="8" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D8">
         <v>688</v>
@@ -1908,10 +1955,10 @@
         <v>15</v>
       </c>
       <c r="F8" s="17" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H8" s="14">
         <v>45266</v>
@@ -1922,7 +1969,7 @@
       </c>
       <c r="J8" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="K8" s="14">
         <v>45293</v>
@@ -1932,22 +1979,22 @@
         <v>27</v>
       </c>
       <c r="M8" s="17" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="N8" s="7"/>
       <c r="O8" s="18">
         <v>45315</v>
       </c>
       <c r="Q8" s="17" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="9" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="9" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>5</v>
       </c>
       <c r="C9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D9">
         <v>921</v>
@@ -1956,10 +2003,10 @@
         <v>15</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H9" s="2">
         <v>45266</v>
@@ -1970,7 +2017,7 @@
       </c>
       <c r="J9" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="K9" s="2">
         <v>45293</v>
@@ -1980,7 +2027,7 @@
         <v>27</v>
       </c>
       <c r="M9" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N9" s="7"/>
       <c r="O9" s="7"/>
@@ -1990,7 +2037,7 @@
         <v>5</v>
       </c>
       <c r="C10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D10">
         <v>922</v>
@@ -1999,10 +2046,10 @@
         <v>15</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H10" s="2">
         <v>45266</v>
@@ -2013,7 +2060,7 @@
       </c>
       <c r="J10" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="K10" s="2">
         <v>45293</v>
@@ -2023,7 +2070,7 @@
         <v>27</v>
       </c>
       <c r="M10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N10" s="7"/>
       <c r="O10" s="7">
@@ -2035,7 +2082,7 @@
         <v>5</v>
       </c>
       <c r="C11" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D11">
         <v>923</v>
@@ -2044,10 +2091,10 @@
         <v>15</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H11" s="2">
         <v>45266</v>
@@ -2058,7 +2105,7 @@
       </c>
       <c r="J11" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="K11" s="2">
         <v>45293</v>
@@ -2068,7 +2115,7 @@
         <v>27</v>
       </c>
       <c r="M11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N11" s="7"/>
       <c r="O11" s="7">
@@ -2080,13 +2127,13 @@
         <v>5</v>
       </c>
       <c r="C12" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E12" t="s">
         <v>7</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G12" t="s">
         <v>10</v>
@@ -2096,11 +2143,11 @@
       </c>
       <c r="I12" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J12" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="L12" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2119,13 +2166,13 @@
         <v>5</v>
       </c>
       <c r="C13" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E13" t="s">
         <v>7</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G13" t="s">
         <v>12</v>
@@ -2155,13 +2202,13 @@
         <v>5</v>
       </c>
       <c r="C14" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E14" t="s">
         <v>7</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G14" t="s">
         <v>12</v>
@@ -2186,12 +2233,12 @@
         <v>45299</v>
       </c>
     </row>
-    <row r="15" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>5</v>
       </c>
       <c r="C15" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D15">
         <v>972</v>
@@ -2200,7 +2247,7 @@
         <v>7</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G15" t="s">
         <v>11</v>
@@ -2210,11 +2257,11 @@
       </c>
       <c r="I15" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J15" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="L15" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2226,12 +2273,12 @@
       <c r="N15" s="7"/>
       <c r="O15" s="7"/>
     </row>
-    <row r="16" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>5</v>
       </c>
       <c r="C16" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D16">
         <v>973</v>
@@ -2240,7 +2287,7 @@
         <v>7</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G16" t="s">
         <v>11</v>
@@ -2250,11 +2297,11 @@
       </c>
       <c r="I16" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J16" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="L16" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2266,12 +2313,12 @@
       <c r="N16" s="7"/>
       <c r="O16" s="7"/>
     </row>
-    <row r="17" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>5</v>
       </c>
       <c r="C17" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D17">
         <v>974</v>
@@ -2280,7 +2327,7 @@
         <v>7</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G17" t="s">
         <v>11</v>
@@ -2290,11 +2337,11 @@
       </c>
       <c r="I17" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J17" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="L17" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2304,12 +2351,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="18" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>5</v>
       </c>
       <c r="C18" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D18">
         <v>975</v>
@@ -2318,7 +2365,7 @@
         <v>7</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G18" t="s">
         <v>11</v>
@@ -2328,26 +2375,26 @@
       </c>
       <c r="I18" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J18" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="L18" s="4" t="str">
         <f t="shared" si="0"/>
         <v>-</v>
       </c>
       <c r="M18" s="4" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="19" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="19" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>5</v>
       </c>
       <c r="C19" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D19">
         <v>970</v>
@@ -2356,7 +2403,7 @@
         <v>7</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G19" t="s">
         <v>11</v>
@@ -2366,11 +2413,11 @@
       </c>
       <c r="I19" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J19" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="L19" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2385,13 +2432,13 @@
         <v>5</v>
       </c>
       <c r="C20" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E20" t="s">
         <v>7</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G20" t="s">
         <v>11</v>
@@ -2405,7 +2452,7 @@
       </c>
       <c r="J20" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="L20" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2423,13 +2470,13 @@
         <v>5</v>
       </c>
       <c r="C21" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E21" t="s">
         <v>7</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G21" t="s">
         <v>13</v>
@@ -2458,13 +2505,13 @@
         <v>5</v>
       </c>
       <c r="C22" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G22" t="s">
         <v>13</v>
@@ -2474,11 +2521,11 @@
       </c>
       <c r="I22" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J22" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="K22" s="2">
         <v>45112</v>
@@ -2499,7 +2546,7 @@
         <v>5</v>
       </c>
       <c r="C23" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="E23" t="s">
         <v>7</v>
@@ -2519,7 +2566,7 @@
       </c>
       <c r="J23" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="K23" s="2">
         <v>45176</v>
@@ -2535,7 +2582,7 @@
         <v>45306</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="24" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -2543,7 +2590,7 @@
         <v>5</v>
       </c>
       <c r="C24" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="E24" t="s">
         <v>7</v>
@@ -2563,7 +2610,7 @@
       </c>
       <c r="J24" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="K24" s="2">
         <v>45176</v>
@@ -2579,7 +2626,7 @@
         <v>45306</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="25" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -2587,7 +2634,7 @@
         <v>5</v>
       </c>
       <c r="C25" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="E25" t="s">
         <v>7</v>
@@ -2607,7 +2654,7 @@
       </c>
       <c r="J25" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="K25" s="2">
         <v>45176</v>
@@ -2623,15 +2670,15 @@
         <v>45306</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="26" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="26" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>5</v>
       </c>
       <c r="C26" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E26" t="s">
         <v>7</v>
@@ -2651,7 +2698,7 @@
       </c>
       <c r="J26" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="K26" s="2">
         <v>45176</v>
@@ -2665,12 +2712,12 @@
       </c>
       <c r="Q26" s="2"/>
     </row>
-    <row r="27" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>5</v>
       </c>
       <c r="C27" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E27" t="s">
         <v>7</v>
@@ -2690,7 +2737,7 @@
       </c>
       <c r="J27" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="K27" s="2">
         <v>45176</v>
@@ -2709,13 +2756,13 @@
         <v>5</v>
       </c>
       <c r="C28" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="E28" s="15" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G28" s="17" t="s">
         <v>11</v>
@@ -2729,7 +2776,7 @@
       </c>
       <c r="J28" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="K28" s="14">
         <v>45229</v>
@@ -2751,13 +2798,13 @@
         <v>5</v>
       </c>
       <c r="C29" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="E29" s="15" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="19" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G29" s="17" t="s">
         <v>11</v>
@@ -2771,7 +2818,7 @@
       </c>
       <c r="J29" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="K29" s="14">
         <v>45229</v>
@@ -2788,18 +2835,18 @@
       </c>
       <c r="Q29" s="17"/>
     </row>
-    <row r="30" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>5</v>
       </c>
       <c r="C30" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
       </c>
       <c r="F30" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G30" t="s">
         <v>13</v>
@@ -2813,7 +2860,7 @@
       </c>
       <c r="J30" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="K30" s="2">
         <v>45229</v>
@@ -2823,22 +2870,22 @@
         <v>26</v>
       </c>
       <c r="M30" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q30" s="2"/>
     </row>
-    <row r="31" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
         <v>5</v>
       </c>
       <c r="C31" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
       </c>
       <c r="F31" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G31" t="s">
         <v>13</v>
@@ -2852,7 +2899,7 @@
       </c>
       <c r="J31" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="K31" s="2">
         <v>45229</v>
@@ -2862,22 +2909,22 @@
         <v>26</v>
       </c>
       <c r="M31" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q31" s="2"/>
     </row>
-    <row r="32" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
         <v>5</v>
       </c>
       <c r="C32" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G32" t="s">
         <v>13</v>
@@ -2891,7 +2938,7 @@
       </c>
       <c r="J32" s="4">
         <f t="shared" ref="J32:J38" ca="1" si="3">IF(_xlfn.DAYS(TODAY(),H32)&lt;10000, _xlfn.DAYS(TODAY(),H32), "-")</f>
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="K32" s="2">
         <v>45229</v>
@@ -2910,13 +2957,13 @@
         <v>5</v>
       </c>
       <c r="C33" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G33" t="s">
         <v>11</v>
@@ -2945,7 +2992,7 @@
         <v>5</v>
       </c>
       <c r="C34" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="D34" t="s">
         <v>24</v>
@@ -2954,7 +3001,7 @@
         <v>8</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G34" t="s">
         <v>11</v>
@@ -2968,7 +3015,7 @@
       </c>
       <c r="J34" s="4">
         <f ca="1">IF(_xlfn.DAYS(TODAY(),H34)&lt;10000, _xlfn.DAYS(TODAY(),H34), "-")</f>
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="K34" s="2">
         <v>45257</v>
@@ -2978,13 +3025,13 @@
         <v>26</v>
       </c>
       <c r="M34" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O34" s="2">
         <v>45306</v>
       </c>
       <c r="Q34" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="35" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -2992,13 +3039,13 @@
         <v>5</v>
       </c>
       <c r="C35" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G35" t="s">
         <v>13</v>
@@ -3016,13 +3063,13 @@
         <v>-</v>
       </c>
       <c r="M35" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O35" s="2">
         <v>45306</v>
       </c>
       <c r="Q35" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="36" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -3030,13 +3077,13 @@
         <v>5</v>
       </c>
       <c r="C36" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G36" t="s">
         <v>13</v>
@@ -3054,13 +3101,13 @@
         <v>-</v>
       </c>
       <c r="M36" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O36" s="2">
         <v>45306</v>
       </c>
       <c r="Q36" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="37" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -3068,7 +3115,7 @@
         <v>5</v>
       </c>
       <c r="C37" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="D37" t="s">
         <v>23</v>
@@ -3077,7 +3124,7 @@
         <v>8</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G37" t="s">
         <v>13</v>
@@ -3091,7 +3138,7 @@
       </c>
       <c r="J37" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="K37" s="2">
         <v>45257</v>
@@ -3107,7 +3154,7 @@
         <v>45306</v>
       </c>
       <c r="Q37" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="38" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -3115,7 +3162,7 @@
         <v>5</v>
       </c>
       <c r="C38" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="D38" t="s">
         <v>24</v>
@@ -3124,7 +3171,7 @@
         <v>8</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G38" t="s">
         <v>13</v>
@@ -3138,7 +3185,7 @@
       </c>
       <c r="J38" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="K38" s="2">
         <v>45257</v>
@@ -3154,7 +3201,7 @@
         <v>45306</v>
       </c>
       <c r="Q38" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="39" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -3162,7 +3209,7 @@
         <v>5</v>
       </c>
       <c r="C39" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="D39" t="s">
         <v>25</v>
@@ -3171,7 +3218,7 @@
         <v>8</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G39" t="s">
         <v>13</v>
@@ -3185,7 +3232,7 @@
       </c>
       <c r="J39" s="4">
         <f t="shared" ref="J39:J41" ca="1" si="5">IF(_xlfn.DAYS(TODAY(),H39)&lt;10000, _xlfn.DAYS(TODAY(),H39), "-")</f>
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="K39" s="2">
         <v>45257</v>
@@ -3201,7 +3248,7 @@
         <v>45306</v>
       </c>
       <c r="Q39" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="40" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -3209,7 +3256,7 @@
         <v>5</v>
       </c>
       <c r="C40" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="D40" t="s">
         <v>23</v>
@@ -3218,7 +3265,7 @@
         <v>8</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G40" t="s">
         <v>11</v>
@@ -3232,7 +3279,7 @@
       </c>
       <c r="J40" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="K40" s="2">
         <v>45257</v>
@@ -3253,7 +3300,7 @@
         <v>5</v>
       </c>
       <c r="C41" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="D41" t="s">
         <v>25</v>
@@ -3262,7 +3309,7 @@
         <v>8</v>
       </c>
       <c r="F41" s="12" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G41" t="s">
         <v>11</v>
@@ -3276,7 +3323,7 @@
       </c>
       <c r="J41" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="K41" s="2">
         <v>45257</v>
@@ -3297,7 +3344,7 @@
         <v>5</v>
       </c>
       <c r="C42" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D42">
         <v>798</v>
@@ -3306,7 +3353,7 @@
         <v>8</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G42" t="s">
         <v>13</v>
@@ -3316,11 +3363,11 @@
       </c>
       <c r="I42" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J42" s="4">
         <f t="shared" ref="J42" ca="1" si="6">IF(_xlfn.DAYS(TODAY(),H42)&lt;10000, _xlfn.DAYS(TODAY(),H42), "-")</f>
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="L42" s="4" t="str">
         <f t="shared" si="4"/>
@@ -3333,12 +3380,12 @@
         <v>45309</v>
       </c>
     </row>
-    <row r="43" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B43" t="s">
         <v>5</v>
       </c>
       <c r="C43" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D43">
         <v>799</v>
@@ -3347,7 +3394,7 @@
         <v>8</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G43" t="s">
         <v>13</v>
@@ -3357,11 +3404,11 @@
       </c>
       <c r="I43" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J43" s="4">
         <f t="shared" ref="J43:J91" ca="1" si="7">IF(_xlfn.DAYS(TODAY(),H43)&lt;10000, _xlfn.DAYS(TODAY(),H43), "-")</f>
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="L43" s="4" t="str">
         <f t="shared" si="4"/>
@@ -3376,7 +3423,7 @@
         <v>5</v>
       </c>
       <c r="C44" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="D44">
         <v>815</v>
@@ -3385,21 +3432,21 @@
         <v>8</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G44" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H44" s="2">
         <v>45267</v>
       </c>
       <c r="I44" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J44" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="K44" s="2">
         <v>45293</v>
@@ -3409,7 +3456,7 @@
         <v>26</v>
       </c>
       <c r="M44" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O44" s="7">
         <v>45309</v>
@@ -3420,7 +3467,7 @@
         <v>5</v>
       </c>
       <c r="C45" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="D45">
         <v>816</v>
@@ -3429,21 +3476,21 @@
         <v>8</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G45" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H45" s="2">
         <v>45267</v>
       </c>
       <c r="I45" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J45" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="K45" s="2">
         <v>45293</v>
@@ -3453,7 +3500,7 @@
         <v>26</v>
       </c>
       <c r="M45" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O45" s="7">
         <v>45309</v>
@@ -3464,7 +3511,7 @@
         <v>5</v>
       </c>
       <c r="C46" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="D46">
         <v>817</v>
@@ -3473,21 +3520,21 @@
         <v>8</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G46" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H46" s="2">
         <v>45267</v>
       </c>
       <c r="I46" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J46" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="K46" s="2">
         <v>45293</v>
@@ -3497,13 +3544,13 @@
         <v>26</v>
       </c>
       <c r="M46" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O46" s="2">
         <v>45306</v>
       </c>
       <c r="Q46" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="47" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -3511,7 +3558,7 @@
         <v>5</v>
       </c>
       <c r="C47" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="D47">
         <v>819</v>
@@ -3520,21 +3567,21 @@
         <v>8</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G47" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H47" s="2">
         <v>45267</v>
       </c>
       <c r="I47" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J47" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="K47" s="2">
         <v>45293</v>
@@ -3544,13 +3591,13 @@
         <v>26</v>
       </c>
       <c r="M47" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O47" s="2">
         <v>45306</v>
       </c>
       <c r="Q47" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="48" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -3558,7 +3605,7 @@
         <v>5</v>
       </c>
       <c r="C48" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="D48">
         <v>820</v>
@@ -3567,21 +3614,21 @@
         <v>8</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G48" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H48" s="2">
         <v>45271</v>
       </c>
       <c r="I48" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J48" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="K48" s="2">
         <v>45293</v>
@@ -3591,21 +3638,21 @@
         <v>22</v>
       </c>
       <c r="M48" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O48" s="2">
         <v>45306</v>
       </c>
       <c r="Q48" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="49" spans="2:15" hidden="1" x14ac:dyDescent="0.3">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="49" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B49" t="s">
         <v>5</v>
       </c>
       <c r="C49" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D49">
         <v>821</v>
@@ -3614,21 +3661,21 @@
         <v>8</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G49" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H49" s="2">
         <v>45267</v>
       </c>
       <c r="I49" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J49" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="K49" s="2">
         <v>45293</v>
@@ -3638,15 +3685,15 @@
         <v>26</v>
       </c>
       <c r="M49" s="4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="50" spans="2:15" hidden="1" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="50" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B50" t="s">
         <v>5</v>
       </c>
       <c r="C50" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D50">
         <v>822</v>
@@ -3655,21 +3702,21 @@
         <v>8</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G50" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H50" s="2">
         <v>45267</v>
       </c>
       <c r="I50" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J50" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="K50" s="2">
         <v>45293</v>
@@ -3679,15 +3726,15 @@
         <v>26</v>
       </c>
       <c r="M50" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="51" spans="2:15" hidden="1" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="51" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B51" t="s">
         <v>5</v>
       </c>
       <c r="C51" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="D51">
         <v>823</v>
@@ -3696,21 +3743,21 @@
         <v>8</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G51" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H51" s="2">
         <v>45267</v>
       </c>
       <c r="I51" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J51" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="K51" s="2">
         <v>45293</v>
@@ -3720,18 +3767,18 @@
         <v>26</v>
       </c>
       <c r="M51" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O51" s="7">
         <v>45309</v>
       </c>
     </row>
-    <row r="52" spans="2:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B52" t="s">
         <v>5</v>
       </c>
       <c r="C52" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="D52">
         <v>824</v>
@@ -3740,21 +3787,21 @@
         <v>8</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G52" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H52" s="2">
         <v>45271</v>
       </c>
       <c r="I52" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J52" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="K52" s="2">
         <v>45293</v>
@@ -3764,18 +3811,18 @@
         <v>22</v>
       </c>
       <c r="M52" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O52" s="7">
         <v>45309</v>
       </c>
     </row>
-    <row r="53" spans="2:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B53" t="s">
         <v>5</v>
       </c>
       <c r="C53" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D53">
         <v>825</v>
@@ -3784,21 +3831,21 @@
         <v>8</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G53" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H53" s="2">
         <v>45271</v>
       </c>
       <c r="I53" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J53" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="K53" s="2">
         <v>45293</v>
@@ -3808,15 +3855,15 @@
         <v>22</v>
       </c>
       <c r="M53" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="54" spans="2:15" hidden="1" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="54" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B54" t="s">
         <v>27</v>
       </c>
       <c r="C54" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D54" t="s">
         <v>28</v>
@@ -3825,7 +3872,7 @@
         <v>31</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G54" t="s">
         <v>32</v>
@@ -3835,11 +3882,11 @@
       </c>
       <c r="I54" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J54" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="K54" s="2">
         <v>45238</v>
@@ -3852,12 +3899,12 @@
         <v>42</v>
       </c>
     </row>
-    <row r="55" spans="2:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B55" t="s">
         <v>27</v>
       </c>
       <c r="C55" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D55" t="s">
         <v>30</v>
@@ -3866,7 +3913,7 @@
         <v>31</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G55" t="s">
         <v>32</v>
@@ -3876,11 +3923,11 @@
       </c>
       <c r="I55" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J55" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="K55" s="2">
         <v>45238</v>
@@ -3893,12 +3940,12 @@
         <v>42</v>
       </c>
     </row>
-    <row r="56" spans="2:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B56" t="s">
         <v>27</v>
       </c>
       <c r="C56" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D56" t="s">
         <v>29</v>
@@ -3907,7 +3954,7 @@
         <v>31</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G56" t="s">
         <v>32</v>
@@ -3917,11 +3964,11 @@
       </c>
       <c r="I56" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J56" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="K56" s="2">
         <v>45238</v>
@@ -3934,18 +3981,18 @@
         <v>42</v>
       </c>
     </row>
-    <row r="57" spans="2:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B57" t="s">
         <v>27</v>
       </c>
       <c r="C57" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E57" t="s">
         <v>31</v>
       </c>
       <c r="F57" s="21" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G57" t="s">
         <v>33</v>
@@ -3959,7 +4006,7 @@
       </c>
       <c r="J57" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="L57" s="4" t="str">
         <f t="shared" si="4"/>
@@ -3969,18 +4016,18 @@
         <v>43</v>
       </c>
     </row>
-    <row r="58" spans="2:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B58" t="s">
         <v>27</v>
       </c>
       <c r="C58" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E58" t="s">
         <v>31</v>
       </c>
       <c r="F58" s="21" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G58" t="s">
         <v>32</v>
@@ -3994,7 +4041,7 @@
       </c>
       <c r="J58" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="L58" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4004,29 +4051,29 @@
         <v>43</v>
       </c>
     </row>
-    <row r="59" spans="2:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B59" t="s">
         <v>27</v>
       </c>
       <c r="C59" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E59" t="s">
         <v>26</v>
       </c>
       <c r="G59" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H59" s="2">
         <v>45267</v>
       </c>
       <c r="I59" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J59" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="K59" s="2">
         <v>45295</v>
@@ -4036,32 +4083,35 @@
         <v>28</v>
       </c>
       <c r="M59" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="60" spans="2:15" hidden="1" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="60" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B60" t="s">
         <v>27</v>
       </c>
       <c r="C60" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E60" t="s">
         <v>26</v>
       </c>
       <c r="G60" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H60" s="2">
         <v>45267</v>
       </c>
       <c r="I60" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J60" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="K60" s="2">
         <v>45295</v>
@@ -4071,32 +4121,32 @@
         <v>28</v>
       </c>
       <c r="M60" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="61" spans="2:15" hidden="1" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="61" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B61" t="s">
         <v>27</v>
       </c>
       <c r="C61" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E61" t="s">
         <v>26</v>
       </c>
       <c r="G61" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H61" s="2">
         <v>45267</v>
       </c>
       <c r="I61" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J61" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="K61" s="2">
         <v>45295</v>
@@ -4106,32 +4156,32 @@
         <v>28</v>
       </c>
       <c r="M61" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="62" spans="2:15" hidden="1" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="62" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B62" t="s">
         <v>27</v>
       </c>
       <c r="C62" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E62" t="s">
         <v>26</v>
       </c>
       <c r="G62" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H62" s="2">
         <v>45267</v>
       </c>
       <c r="I62" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J62" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="K62" s="2">
         <v>45295</v>
@@ -4141,32 +4191,32 @@
         <v>28</v>
       </c>
       <c r="M62" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="63" spans="2:15" hidden="1" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="63" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B63" t="s">
         <v>27</v>
       </c>
       <c r="C63" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E63" t="s">
         <v>26</v>
       </c>
       <c r="G63" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H63" s="2">
         <v>45267</v>
       </c>
       <c r="I63" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J63" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="K63" s="2">
         <v>45295</v>
@@ -4176,32 +4226,32 @@
         <v>28</v>
       </c>
       <c r="M63" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="64" spans="2:15" hidden="1" x14ac:dyDescent="0.3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="64" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B64" t="s">
         <v>27</v>
       </c>
       <c r="C64" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E64" t="s">
         <v>26</v>
       </c>
       <c r="G64" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H64" s="2">
         <v>45267</v>
       </c>
       <c r="I64" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J64" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="K64" s="2">
         <v>45295</v>
@@ -4211,7 +4261,7 @@
         <v>28</v>
       </c>
       <c r="M64" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="65" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -4219,13 +4269,13 @@
         <v>27</v>
       </c>
       <c r="C65" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E65" t="s">
         <v>31</v>
       </c>
       <c r="F65" s="21" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G65" t="s">
         <v>32</v>
@@ -4239,7 +4289,7 @@
       </c>
       <c r="J65" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="L65" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4254,13 +4304,13 @@
         <v>27</v>
       </c>
       <c r="C66" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E66" t="s">
         <v>31</v>
       </c>
       <c r="F66" s="21" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G66" t="s">
         <v>32</v>
@@ -4274,7 +4324,7 @@
       </c>
       <c r="J66" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="L66" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4312,7 +4362,7 @@
       </c>
       <c r="J67" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="L67" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4328,7 +4378,7 @@
         <v>45278</v>
       </c>
       <c r="P67" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q67" t="s">
         <v>37</v>
@@ -4362,7 +4412,7 @@
       </c>
       <c r="J68" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="L68" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4378,7 +4428,7 @@
         <v>45278</v>
       </c>
       <c r="P68" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q68" t="s">
         <v>37</v>
@@ -4412,7 +4462,7 @@
       </c>
       <c r="J69" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="L69" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4428,7 +4478,7 @@
         <v>45278</v>
       </c>
       <c r="P69" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q69" t="s">
         <v>37</v>
@@ -4462,7 +4512,7 @@
       </c>
       <c r="J70" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="L70" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4478,7 +4528,7 @@
         <v>45278</v>
       </c>
       <c r="P70" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q70" t="s">
         <v>37</v>
@@ -4512,7 +4562,7 @@
       </c>
       <c r="J71" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="L71" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4528,7 +4578,7 @@
         <v>45278</v>
       </c>
       <c r="P71" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q71" t="s">
         <v>37</v>
@@ -4562,7 +4612,7 @@
       </c>
       <c r="J72" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="L72" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4578,7 +4628,7 @@
         <v>45278</v>
       </c>
       <c r="P72" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q72" t="s">
         <v>38</v>
@@ -4612,7 +4662,7 @@
       </c>
       <c r="J73" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="L73" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4628,7 +4678,7 @@
         <v>45275</v>
       </c>
       <c r="P73" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q73" t="s">
         <v>38</v>
@@ -4662,7 +4712,7 @@
       </c>
       <c r="J74" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="L74" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4678,7 +4728,7 @@
         <v>45278</v>
       </c>
       <c r="P74" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q74" t="s">
         <v>38</v>
@@ -4712,7 +4762,7 @@
       </c>
       <c r="J75" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="L75" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4728,7 +4778,7 @@
         <v>45274</v>
       </c>
       <c r="P75" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q75" t="s">
         <v>38</v>
@@ -4762,7 +4812,7 @@
       </c>
       <c r="J76" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="L76" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4778,7 +4828,7 @@
         <v>45274</v>
       </c>
       <c r="P76" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q76" t="s">
         <v>38</v>
@@ -4812,7 +4862,7 @@
       </c>
       <c r="J77" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="L77" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4828,7 +4878,7 @@
         <v>45278</v>
       </c>
       <c r="P77" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q77" t="s">
         <v>37</v>
@@ -4862,7 +4912,7 @@
       </c>
       <c r="J78" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="L78" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4878,7 +4928,7 @@
         <v>45278</v>
       </c>
       <c r="P78" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q78" t="s">
         <v>37</v>
@@ -4912,7 +4962,7 @@
       </c>
       <c r="J79" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="L79" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4928,7 +4978,7 @@
         <v>45278</v>
       </c>
       <c r="P79" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q79" t="s">
         <v>37</v>
@@ -4962,7 +5012,7 @@
       </c>
       <c r="J80" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="L80" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4978,7 +5028,7 @@
         <v>45278</v>
       </c>
       <c r="P80" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q80" t="s">
         <v>37</v>
@@ -5012,7 +5062,7 @@
       </c>
       <c r="J81" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="L81" s="4" t="str">
         <f t="shared" si="4"/>
@@ -5028,7 +5078,7 @@
         <v>45278</v>
       </c>
       <c r="P81" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q81" t="s">
         <v>37</v>
@@ -5062,7 +5112,7 @@
       </c>
       <c r="J82" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="L82" s="4" t="str">
         <f t="shared" si="4"/>
@@ -5078,7 +5128,7 @@
         <v>45270</v>
       </c>
       <c r="P82" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q82" t="s">
         <v>38</v>
@@ -5112,7 +5162,7 @@
       </c>
       <c r="J83" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="L83" s="4" t="str">
         <f t="shared" si="4"/>
@@ -5128,7 +5178,7 @@
         <v>45270</v>
       </c>
       <c r="P83" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q83" t="s">
         <v>38</v>
@@ -5162,7 +5212,7 @@
       </c>
       <c r="J84" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="L84" s="4" t="str">
         <f t="shared" si="4"/>
@@ -5178,7 +5228,7 @@
         <v>45273</v>
       </c>
       <c r="P84" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q84" t="s">
         <v>38</v>
@@ -5212,7 +5262,7 @@
       </c>
       <c r="J85" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="L85" s="4" t="str">
         <f t="shared" si="4"/>
@@ -5228,7 +5278,7 @@
         <v>45277</v>
       </c>
       <c r="P85" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q85" t="s">
         <v>38</v>
@@ -5262,7 +5312,7 @@
       </c>
       <c r="J86" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="L86" s="4" t="str">
         <f t="shared" si="4"/>
@@ -5278,7 +5328,7 @@
         <v>45277</v>
       </c>
       <c r="P86" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q86" t="s">
         <v>38</v>
@@ -5289,7 +5339,7 @@
         <v>27</v>
       </c>
       <c r="C87" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D87" t="s">
         <v>28</v>
@@ -5298,7 +5348,7 @@
         <v>31</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G87" t="s">
         <v>33</v>
@@ -5312,7 +5362,7 @@
       </c>
       <c r="J87" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="K87" s="2">
         <v>45272</v>
@@ -5322,13 +5372,16 @@
         <v>34</v>
       </c>
       <c r="M87" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
+      </c>
+      <c r="O87" s="2">
+        <v>45323</v>
       </c>
       <c r="P87" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="Q87" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="88" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -5336,7 +5389,7 @@
         <v>34</v>
       </c>
       <c r="C88" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D88" t="s">
         <v>30</v>
@@ -5345,7 +5398,7 @@
         <v>31</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G88" t="s">
         <v>33</v>
@@ -5359,7 +5412,7 @@
       </c>
       <c r="J88" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="K88" s="2">
         <v>45273</v>
@@ -5369,13 +5422,16 @@
         <v>35</v>
       </c>
       <c r="M88" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
+      </c>
+      <c r="O88" s="2">
+        <v>45323</v>
       </c>
       <c r="P88" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="Q88" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="89" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -5383,7 +5439,7 @@
         <v>34</v>
       </c>
       <c r="C89" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D89" t="s">
         <v>29</v>
@@ -5392,7 +5448,7 @@
         <v>31</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G89" t="s">
         <v>33</v>
@@ -5406,7 +5462,7 @@
       </c>
       <c r="J89" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="K89" s="2">
         <v>45274</v>
@@ -5416,13 +5472,16 @@
         <v>36</v>
       </c>
       <c r="M89" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
+      </c>
+      <c r="O89" s="2">
+        <v>45323</v>
       </c>
       <c r="P89" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="Q89" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="90" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -5430,7 +5489,7 @@
         <v>27</v>
       </c>
       <c r="C90" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D90" t="s">
         <v>28</v>
@@ -5439,7 +5498,7 @@
         <v>31</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G90" t="s">
         <v>32</v>
@@ -5453,7 +5512,7 @@
       </c>
       <c r="J90" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="K90" s="2">
         <v>45275</v>
@@ -5463,13 +5522,16 @@
         <v>37</v>
       </c>
       <c r="M90" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
+      </c>
+      <c r="O90" s="2">
+        <v>45323</v>
       </c>
       <c r="P90" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="Q90" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="91" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -5477,7 +5539,7 @@
         <v>27</v>
       </c>
       <c r="C91" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D91" t="s">
         <v>30</v>
@@ -5486,7 +5548,7 @@
         <v>31</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G91" t="s">
         <v>32</v>
@@ -5500,7 +5562,7 @@
       </c>
       <c r="J91" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="K91" s="2">
         <v>45276</v>
@@ -5510,13 +5572,16 @@
         <v>38</v>
       </c>
       <c r="M91" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="O91" s="2">
+        <v>45323</v>
+      </c>
+      <c r="P91" t="s">
         <v>140</v>
       </c>
-      <c r="P91" t="s">
-        <v>141</v>
-      </c>
       <c r="Q91" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="92" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -5524,7 +5589,7 @@
         <v>27</v>
       </c>
       <c r="C92" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D92" t="s">
         <v>29</v>
@@ -5533,7 +5598,7 @@
         <v>31</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G92" t="s">
         <v>32</v>
@@ -5547,7 +5612,7 @@
       </c>
       <c r="J92" s="4">
         <f t="shared" ref="J92:J93" ca="1" si="10">IF(_xlfn.DAYS(TODAY(),H92)&lt;10000, _xlfn.DAYS(TODAY(),H92), "-")</f>
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="K92" s="2">
         <v>45277</v>
@@ -5557,13 +5622,16 @@
         <v>39</v>
       </c>
       <c r="M92" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
+      </c>
+      <c r="O92" s="2">
+        <v>45323</v>
       </c>
       <c r="P92" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="Q92" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="93" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -5571,7 +5639,7 @@
         <v>34</v>
       </c>
       <c r="C93" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D93" t="s">
         <v>35</v>
@@ -5580,7 +5648,7 @@
         <v>31</v>
       </c>
       <c r="F93" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G93" t="s">
         <v>32</v>
@@ -5594,7 +5662,7 @@
       </c>
       <c r="J93" s="4">
         <f t="shared" ca="1" si="10"/>
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="K93" s="2">
         <v>45278</v>
@@ -5604,13 +5672,16 @@
         <v>40</v>
       </c>
       <c r="M93" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="O93" s="2">
+        <v>45323</v>
+      </c>
+      <c r="P93" t="s">
         <v>140</v>
       </c>
-      <c r="P93" t="s">
-        <v>141</v>
-      </c>
       <c r="Q93" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="94" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -5618,7 +5689,7 @@
         <v>34</v>
       </c>
       <c r="C94" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D94">
         <v>615</v>
@@ -5627,7 +5698,7 @@
         <v>31</v>
       </c>
       <c r="F94" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G94" t="s">
         <v>33</v>
@@ -5641,7 +5712,7 @@
       </c>
       <c r="J94" s="4">
         <f t="shared" ref="J94" ca="1" si="12">IF(_xlfn.DAYS(TODAY(),H94)&lt;10000, _xlfn.DAYS(TODAY(),H94), "-")</f>
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="K94" s="2">
         <v>45223</v>
@@ -5657,10 +5728,10 @@
         <v>45301</v>
       </c>
       <c r="P94" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="Q94" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="95" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -5668,7 +5739,7 @@
         <v>34</v>
       </c>
       <c r="C95" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D95">
         <v>616</v>
@@ -5677,7 +5748,7 @@
         <v>31</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G95" t="s">
         <v>33</v>
@@ -5691,7 +5762,7 @@
       </c>
       <c r="J95" s="4">
         <f t="shared" ref="J95:J117" ca="1" si="14">IF(_xlfn.DAYS(TODAY(),H95)&lt;10000, _xlfn.DAYS(TODAY(),H95), "-")</f>
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="K95" s="2">
         <v>45223</v>
@@ -5707,10 +5778,10 @@
         <v>45301</v>
       </c>
       <c r="P95" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="Q95" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="96" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -5718,7 +5789,7 @@
         <v>34</v>
       </c>
       <c r="C96" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D96">
         <v>617</v>
@@ -5727,7 +5798,7 @@
         <v>31</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G96" t="s">
         <v>33</v>
@@ -5741,7 +5812,7 @@
       </c>
       <c r="J96" s="4">
         <f t="shared" ca="1" si="14"/>
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="K96" s="2">
         <v>45223</v>
@@ -5757,10 +5828,10 @@
         <v>45301</v>
       </c>
       <c r="P96" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="Q96" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="97" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -5768,7 +5839,7 @@
         <v>34</v>
       </c>
       <c r="C97" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D97">
         <v>618</v>
@@ -5777,7 +5848,7 @@
         <v>31</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G97" t="s">
         <v>33</v>
@@ -5791,7 +5862,7 @@
       </c>
       <c r="J97" s="4">
         <f t="shared" ca="1" si="14"/>
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="K97" s="2">
         <v>45223</v>
@@ -5807,10 +5878,10 @@
         <v>45301</v>
       </c>
       <c r="P97" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="Q97" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="98" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -5837,11 +5908,11 @@
       </c>
       <c r="I98" s="4">
         <f t="shared" ref="I98:I107" ca="1" si="16">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H98), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H98), 7), "-")</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J98" s="4">
         <f t="shared" ref="J98:J107" ca="1" si="17">IF(_xlfn.DAYS(TODAY(),H98)&lt;10000, _xlfn.DAYS(TODAY(),H98), "-")</f>
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="K98" s="2">
         <v>45267</v>
@@ -5860,10 +5931,10 @@
         <v>45318</v>
       </c>
       <c r="P98" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q98" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="99" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -5890,11 +5961,11 @@
       </c>
       <c r="I99" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J99" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="K99" s="2">
         <v>45267</v>
@@ -5913,10 +5984,10 @@
         <v>45320</v>
       </c>
       <c r="P99" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q99" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="100" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -5943,11 +6014,11 @@
       </c>
       <c r="I100" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J100" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="K100" s="2">
         <v>45267</v>
@@ -5966,10 +6037,10 @@
         <v>45320</v>
       </c>
       <c r="P100" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q100" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="101" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -5996,11 +6067,11 @@
       </c>
       <c r="I101" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J101" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="K101" s="2">
         <v>45267</v>
@@ -6019,10 +6090,10 @@
         <v>45318</v>
       </c>
       <c r="P101" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q101" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="102" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -6049,11 +6120,11 @@
       </c>
       <c r="I102" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J102" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="K102" s="2">
         <v>45267</v>
@@ -6072,10 +6143,10 @@
         <v>45318</v>
       </c>
       <c r="P102" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q102" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="103" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -6102,11 +6173,11 @@
       </c>
       <c r="I103" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J103" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="K103" s="2">
         <v>45267</v>
@@ -6121,11 +6192,14 @@
       <c r="N103" s="2">
         <v>45278</v>
       </c>
+      <c r="O103" s="2">
+        <v>45322</v>
+      </c>
       <c r="P103" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q103" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="104" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -6152,11 +6226,11 @@
       </c>
       <c r="I104" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J104" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="K104" s="2">
         <v>45267</v>
@@ -6171,11 +6245,14 @@
       <c r="N104" s="2">
         <v>45278</v>
       </c>
+      <c r="O104" s="2">
+        <v>45322</v>
+      </c>
       <c r="P104" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q104" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="105" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -6202,11 +6279,11 @@
       </c>
       <c r="I105" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J105" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="K105" s="2">
         <v>45267</v>
@@ -6225,10 +6302,10 @@
         <v>45317</v>
       </c>
       <c r="P105" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q105" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="106" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -6255,11 +6332,11 @@
       </c>
       <c r="I106" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J106" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="K106" s="2">
         <v>45267</v>
@@ -6274,11 +6351,14 @@
       <c r="N106" s="2">
         <v>45278</v>
       </c>
+      <c r="O106" s="2">
+        <v>45322</v>
+      </c>
       <c r="P106" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q106" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="107" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -6305,11 +6385,11 @@
       </c>
       <c r="I107" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J107" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="K107" s="2">
         <v>45267</v>
@@ -6324,11 +6404,14 @@
       <c r="N107" s="2">
         <v>45278</v>
       </c>
+      <c r="O107" s="2">
+        <v>45322</v>
+      </c>
       <c r="P107" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q107" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="108" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -6369,7 +6452,7 @@
         <v>68</v>
       </c>
       <c r="Q108" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="109" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -6410,7 +6493,7 @@
         <v>68</v>
       </c>
       <c r="Q109" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="110" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -6451,7 +6534,7 @@
         <v>68</v>
       </c>
       <c r="Q110" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="111" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -6492,7 +6575,7 @@
         <v>68</v>
       </c>
       <c r="Q111" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="112" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -6533,7 +6616,7 @@
         <v>68</v>
       </c>
       <c r="Q112" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="113" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -6574,7 +6657,7 @@
         <v>68</v>
       </c>
       <c r="Q113" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="114" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -6615,7 +6698,7 @@
         <v>68</v>
       </c>
       <c r="Q114" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="115" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -6635,7 +6718,7 @@
         <v>59</v>
       </c>
       <c r="G115" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I115" s="4" t="str">
         <f t="shared" ca="1" si="13"/>
@@ -6659,7 +6742,7 @@
         <v>68</v>
       </c>
       <c r="Q115" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="116" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -6700,7 +6783,7 @@
         <v>68</v>
       </c>
       <c r="Q116" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="117" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -6741,7 +6824,7 @@
         <v>68</v>
       </c>
       <c r="Q117" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="118" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -6782,7 +6865,7 @@
         <v>68</v>
       </c>
       <c r="Q118" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="119" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -6823,38 +6906,38 @@
         <v>68</v>
       </c>
       <c r="Q119" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="120" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="120" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B120" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C120" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D120">
         <v>645</v>
       </c>
       <c r="E120" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F120" s="21" t="s">
-        <v>142</v>
-      </c>
-      <c r="G120" t="s">
-        <v>124</v>
+        <v>141</v>
+      </c>
+      <c r="G120" s="4" t="s">
+        <v>123</v>
       </c>
       <c r="H120" s="2">
         <v>45291</v>
       </c>
       <c r="I120" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J120" s="4">
         <f t="shared" ca="1" si="19"/>
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="K120" s="2">
         <v>45315</v>
@@ -6863,39 +6946,39 @@
         <f t="shared" si="15"/>
         <v>24</v>
       </c>
-      <c r="M120" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="121" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+      <c r="M120" s="4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="121" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B121" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C121" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D121">
         <v>646</v>
       </c>
       <c r="E121" t="s">
-        <v>91</v>
-      </c>
-      <c r="F121" s="21" t="s">
-        <v>96</v>
-      </c>
-      <c r="G121" t="s">
-        <v>124</v>
+        <v>90</v>
+      </c>
+      <c r="F121" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="G121" s="1" t="s">
+        <v>123</v>
       </c>
       <c r="H121" s="2">
         <v>45291</v>
       </c>
       <c r="I121" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J121" s="4">
         <f t="shared" ca="1" si="19"/>
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="K121" s="2">
         <v>45315</v>
@@ -6904,39 +6987,42 @@
         <f t="shared" si="15"/>
         <v>24</v>
       </c>
-      <c r="M121" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="122" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+      <c r="M121" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q121" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="122" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B122" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C122" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D122">
         <v>647</v>
       </c>
       <c r="E122" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F122" s="21" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G122" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H122" s="2">
         <v>45291</v>
       </c>
       <c r="I122" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J122" s="4">
         <f t="shared" ca="1" si="19"/>
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="K122" s="2">
         <v>45315</v>
@@ -6946,38 +7032,38 @@
         <v>24</v>
       </c>
       <c r="M122" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="123" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="123" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B123" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C123" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D123">
         <v>648</v>
       </c>
       <c r="E123" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F123" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G123" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H123" s="2">
         <v>45291</v>
       </c>
       <c r="I123" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J123" s="4">
         <f t="shared" ca="1" si="19"/>
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="K123" s="2">
         <v>45315</v>
@@ -6987,15 +7073,15 @@
         <v>24</v>
       </c>
       <c r="M123" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="124" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="124" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B124" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C124" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E124" t="s">
         <v>16</v>
@@ -7005,29 +7091,29 @@
       </c>
       <c r="I124" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J124" s="4">
         <f t="shared" ca="1" si="19"/>
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="L124" s="4" t="str">
         <f t="shared" si="15"/>
         <v>-</v>
       </c>
       <c r="M124" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q124" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="125" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="125" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B125" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C125" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E125" t="s">
         <v>16</v>
@@ -7037,29 +7123,29 @@
       </c>
       <c r="I125" s="4">
         <f t="shared" ref="I125:I127" ca="1" si="20">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H125), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H125), 7), "-")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J125" s="4">
         <f t="shared" ref="J125:J127" ca="1" si="21">IF(_xlfn.DAYS(TODAY(),H125)&lt;10000, _xlfn.DAYS(TODAY(),H125), "-")</f>
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="L125" s="4" t="str">
         <f t="shared" si="15"/>
         <v>-</v>
       </c>
       <c r="M125" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q125" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="126" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="126" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B126" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C126" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E126" t="s">
         <v>16</v>
@@ -7069,29 +7155,29 @@
       </c>
       <c r="I126" s="4">
         <f t="shared" ca="1" si="20"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J126" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="L126" s="4" t="str">
         <f t="shared" si="15"/>
         <v>-</v>
       </c>
       <c r="M126" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q126" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="127" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="127" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B127" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C127" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E127" t="s">
         <v>16</v>
@@ -7101,29 +7187,29 @@
       </c>
       <c r="I127" s="4">
         <f t="shared" ca="1" si="20"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J127" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="L127" s="4" t="str">
         <f t="shared" si="15"/>
         <v>-</v>
       </c>
       <c r="M127" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q127" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="128" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B128" t="s">
         <v>116</v>
       </c>
-      <c r="Q127" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="128" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
-      <c r="B128" t="s">
-        <v>117</v>
-      </c>
       <c r="C128" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E128" t="s">
         <v>16</v>
@@ -7133,29 +7219,29 @@
       </c>
       <c r="I128" s="4">
         <f t="shared" ref="I128:I130" ca="1" si="22">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H128), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H128), 7), "-")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J128" s="4">
         <f t="shared" ref="J128:J130" ca="1" si="23">IF(_xlfn.DAYS(TODAY(),H128)&lt;10000, _xlfn.DAYS(TODAY(),H128), "-")</f>
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="L128" s="4" t="str">
         <f t="shared" si="15"/>
         <v>-</v>
       </c>
       <c r="M128" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Q128" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="129" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="129" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B129" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C129" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E129" t="s">
         <v>16</v>
@@ -7165,29 +7251,29 @@
       </c>
       <c r="I129" s="4">
         <f t="shared" ca="1" si="22"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J129" s="4">
         <f t="shared" ca="1" si="23"/>
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="L129" s="4" t="str">
         <f t="shared" si="15"/>
         <v>-</v>
       </c>
       <c r="M129" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Q129" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="130" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="130" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B130" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C130" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E130" t="s">
         <v>16</v>
@@ -7197,21 +7283,21 @@
       </c>
       <c r="I130" s="4">
         <f t="shared" ca="1" si="22"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J130" s="4">
         <f t="shared" ca="1" si="23"/>
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="L130" s="4" t="str">
         <f t="shared" si="15"/>
         <v>-</v>
       </c>
       <c r="M130" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Q130" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="131" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -7222,11 +7308,11 @@
         <v>61</v>
       </c>
       <c r="E131" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F131" s="10"/>
       <c r="G131" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I131" s="4" t="str">
         <f t="shared" ref="I131:I146" ca="1" si="24">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H131), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H131), 7), "-")</f>
@@ -7241,7 +7327,7 @@
         <v>-</v>
       </c>
       <c r="M131" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="132" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -7249,34 +7335,34 @@
         <v>5</v>
       </c>
       <c r="C132" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F132" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G132" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H132" s="2">
         <v>45155</v>
       </c>
       <c r="I132" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J132" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="L132" s="4" t="str">
         <f t="shared" si="26"/>
         <v>-</v>
       </c>
       <c r="M132" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Q132" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="133" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -7284,31 +7370,31 @@
         <v>5</v>
       </c>
       <c r="C133" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F133" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G133" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H133" s="2">
         <v>44885</v>
       </c>
       <c r="I133" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J133" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="L133" s="4" t="str">
         <f t="shared" si="26"/>
         <v>-</v>
       </c>
       <c r="M133" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="134" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -7316,31 +7402,31 @@
         <v>5</v>
       </c>
       <c r="C134" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F134" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G134" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H134" s="2">
         <v>44885</v>
       </c>
       <c r="I134" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J134" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="L134" s="4" t="str">
         <f t="shared" si="26"/>
         <v>-</v>
       </c>
       <c r="M134" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="135" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -7348,34 +7434,34 @@
         <v>5</v>
       </c>
       <c r="C135" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F135" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G135" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H135" s="2">
         <v>45155</v>
       </c>
       <c r="I135" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J135" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="L135" s="4" t="str">
         <f t="shared" si="26"/>
         <v>-</v>
       </c>
       <c r="M135" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="Q135" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="136" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -7383,31 +7469,31 @@
         <v>5</v>
       </c>
       <c r="C136" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F136" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G136" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H136" s="2">
         <v>44885</v>
       </c>
       <c r="I136" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J136" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="L136" s="4" t="str">
         <f t="shared" si="26"/>
         <v>-</v>
       </c>
       <c r="M136" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="137" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -7415,45 +7501,45 @@
         <v>5</v>
       </c>
       <c r="C137" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F137" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G137" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H137" s="2">
         <v>44885</v>
       </c>
       <c r="I137" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J137" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="L137" s="4" t="str">
         <f t="shared" si="26"/>
         <v>-</v>
       </c>
       <c r="M137" s="4" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="138" spans="2:17" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="138" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B138" t="s">
+        <v>146</v>
+      </c>
+      <c r="C138" t="s">
         <v>147</v>
       </c>
-      <c r="C138" t="s">
-        <v>148</v>
-      </c>
       <c r="F138" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G138" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="I138" s="4" t="str">
         <f t="shared" ca="1" si="24"/>
@@ -7467,22 +7553,22 @@
         <f t="shared" si="26"/>
         <v>-</v>
       </c>
-      <c r="M138" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="139" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="M138" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="139" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B139" t="s">
+        <v>146</v>
+      </c>
+      <c r="C139" t="s">
         <v>147</v>
       </c>
-      <c r="C139" t="s">
-        <v>148</v>
-      </c>
       <c r="F139" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G139" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I139" s="4" t="str">
         <f t="shared" ca="1" si="24"/>
@@ -7496,22 +7582,25 @@
         <f t="shared" si="26"/>
         <v>-</v>
       </c>
-      <c r="M139" s="23" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="140" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="M139" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="O139" s="2">
+        <v>45322</v>
+      </c>
+    </row>
+    <row r="140" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B140" t="s">
+        <v>146</v>
+      </c>
+      <c r="C140" t="s">
         <v>147</v>
       </c>
-      <c r="C140" t="s">
-        <v>148</v>
-      </c>
       <c r="F140" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G140" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="I140" s="4" t="str">
         <f t="shared" ca="1" si="24"/>
@@ -7525,19 +7614,19 @@
         <f t="shared" si="26"/>
         <v>-</v>
       </c>
-      <c r="M140" s="1" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="141" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="M140" s="4" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="141" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B141" t="s">
+        <v>146</v>
+      </c>
+      <c r="C141" t="s">
         <v>147</v>
       </c>
-      <c r="C141" t="s">
-        <v>148</v>
-      </c>
       <c r="E141" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="H141" s="2">
         <v>45301</v>
@@ -7548,28 +7637,28 @@
       </c>
       <c r="J141" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="L141" s="4" t="str">
         <f t="shared" si="26"/>
         <v>-</v>
       </c>
       <c r="M141" s="4" t="s">
-        <v>154</v>
+        <v>178</v>
       </c>
       <c r="Q141" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="142" spans="2:17" x14ac:dyDescent="0.3">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="142" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B142" t="s">
+        <v>146</v>
+      </c>
+      <c r="C142" t="s">
         <v>147</v>
       </c>
-      <c r="C142" t="s">
-        <v>148</v>
-      </c>
       <c r="E142" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="H142" s="2">
         <v>45301</v>
@@ -7580,28 +7669,28 @@
       </c>
       <c r="J142" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="L142" s="4" t="str">
         <f t="shared" si="26"/>
         <v>-</v>
       </c>
       <c r="M142" s="4" t="s">
-        <v>154</v>
+        <v>177</v>
       </c>
       <c r="Q142" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="143" spans="2:17" x14ac:dyDescent="0.3">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="143" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B143" t="s">
+        <v>146</v>
+      </c>
+      <c r="C143" t="s">
         <v>147</v>
       </c>
-      <c r="C143" t="s">
-        <v>148</v>
-      </c>
       <c r="E143" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="H143" s="2">
         <v>45301</v>
@@ -7612,28 +7701,28 @@
       </c>
       <c r="J143" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="L143" s="4" t="str">
         <f t="shared" si="26"/>
         <v>-</v>
       </c>
       <c r="M143" s="4" t="s">
-        <v>154</v>
+        <v>177</v>
       </c>
       <c r="Q143" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="144" spans="2:17" x14ac:dyDescent="0.3">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="144" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B144" t="s">
+        <v>146</v>
+      </c>
+      <c r="C144" t="s">
         <v>147</v>
       </c>
-      <c r="C144" t="s">
-        <v>148</v>
-      </c>
       <c r="E144" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="H144" s="2">
         <v>45301</v>
@@ -7644,28 +7733,28 @@
       </c>
       <c r="J144" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="L144" s="4" t="str">
         <f t="shared" si="26"/>
         <v>-</v>
       </c>
       <c r="M144" s="4" t="s">
-        <v>154</v>
+        <v>177</v>
       </c>
       <c r="Q144" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="145" spans="2:17" x14ac:dyDescent="0.3">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="145" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B145" t="s">
+        <v>146</v>
+      </c>
+      <c r="C145" t="s">
         <v>147</v>
       </c>
-      <c r="C145" t="s">
-        <v>148</v>
-      </c>
       <c r="E145" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="H145" s="2">
         <v>45301</v>
@@ -7676,28 +7765,28 @@
       </c>
       <c r="J145" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="L145" s="4" t="str">
         <f t="shared" si="26"/>
         <v>-</v>
       </c>
       <c r="M145" s="4" t="s">
-        <v>154</v>
+        <v>177</v>
       </c>
       <c r="Q145" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="146" spans="2:17" x14ac:dyDescent="0.3">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="146" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B146" t="s">
+        <v>146</v>
+      </c>
+      <c r="C146" t="s">
         <v>147</v>
       </c>
-      <c r="C146" t="s">
-        <v>148</v>
-      </c>
       <c r="E146" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="H146" s="2">
         <v>45301</v>
@@ -7708,31 +7797,31 @@
       </c>
       <c r="J146" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="L146" s="4" t="str">
         <f t="shared" si="26"/>
         <v>-</v>
       </c>
       <c r="M146" s="4" t="s">
-        <v>154</v>
+        <v>177</v>
       </c>
       <c r="Q146" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="147" spans="2:17" x14ac:dyDescent="0.3">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="147" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B147" t="s">
+        <v>146</v>
+      </c>
+      <c r="C147" t="s">
         <v>147</v>
       </c>
-      <c r="C147" t="s">
-        <v>148</v>
-      </c>
       <c r="F147" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G147" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="I147" s="4" t="str">
         <f t="shared" ref="I147:I210" ca="1" si="27">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H147), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H147), 7), "-")</f>
@@ -7747,21 +7836,21 @@
         <v>-</v>
       </c>
       <c r="M147" s="4" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="148" spans="2:17" x14ac:dyDescent="0.3">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="148" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B148" t="s">
+        <v>146</v>
+      </c>
+      <c r="C148" t="s">
         <v>147</v>
       </c>
-      <c r="C148" t="s">
-        <v>148</v>
-      </c>
       <c r="F148" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G148" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I148" s="4" t="str">
         <f t="shared" ca="1" si="27"/>
@@ -7775,22 +7864,22 @@
         <f t="shared" si="29"/>
         <v>-</v>
       </c>
-      <c r="M148" s="1" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="149" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="M148" s="4" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="149" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B149" t="s">
+        <v>146</v>
+      </c>
+      <c r="C149" t="s">
         <v>147</v>
       </c>
-      <c r="C149" t="s">
-        <v>148</v>
-      </c>
       <c r="F149" s="5" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G149" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="I149" s="4" t="str">
         <f t="shared" ca="1" si="27"/>
@@ -7805,21 +7894,21 @@
         <v>-</v>
       </c>
       <c r="M149" s="4" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="150" spans="2:17" x14ac:dyDescent="0.3">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="150" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B150" t="s">
+        <v>146</v>
+      </c>
+      <c r="C150" t="s">
         <v>147</v>
       </c>
-      <c r="C150" t="s">
-        <v>148</v>
-      </c>
       <c r="F150" s="5" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G150" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I150" s="4" t="str">
         <f t="shared" ca="1" si="27"/>
@@ -7834,18 +7923,18 @@
         <v>-</v>
       </c>
       <c r="M150" s="4" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="151" spans="2:17" x14ac:dyDescent="0.3">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="151" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B151" t="s">
+        <v>146</v>
+      </c>
+      <c r="C151" t="s">
         <v>147</v>
       </c>
-      <c r="C151" t="s">
-        <v>148</v>
-      </c>
       <c r="E151" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="H151" s="2">
         <v>45307</v>
@@ -7856,25 +7945,25 @@
       </c>
       <c r="J151" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="L151" s="4" t="str">
         <f t="shared" si="29"/>
         <v>-</v>
       </c>
       <c r="M151" s="4" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="152" spans="2:17" x14ac:dyDescent="0.3">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="152" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B152" t="s">
+        <v>146</v>
+      </c>
+      <c r="C152" t="s">
         <v>147</v>
       </c>
-      <c r="C152" t="s">
-        <v>148</v>
-      </c>
       <c r="E152" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="H152" s="2">
         <v>45307</v>
@@ -7885,25 +7974,25 @@
       </c>
       <c r="J152" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="L152" s="4" t="str">
         <f t="shared" si="29"/>
         <v>-</v>
       </c>
       <c r="M152" s="4" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="153" spans="2:17" x14ac:dyDescent="0.3">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="153" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B153" t="s">
+        <v>146</v>
+      </c>
+      <c r="C153" t="s">
         <v>147</v>
       </c>
-      <c r="C153" t="s">
-        <v>148</v>
-      </c>
       <c r="E153" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="H153" s="2">
         <v>45307</v>
@@ -7914,25 +8003,25 @@
       </c>
       <c r="J153" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="L153" s="4" t="str">
         <f t="shared" si="29"/>
         <v>-</v>
       </c>
       <c r="M153" s="4" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="154" spans="2:17" x14ac:dyDescent="0.3">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="154" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B154" t="s">
+        <v>146</v>
+      </c>
+      <c r="C154" t="s">
         <v>147</v>
       </c>
-      <c r="C154" t="s">
-        <v>148</v>
-      </c>
       <c r="E154" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="H154" s="2">
         <v>45307</v>
@@ -7943,25 +8032,25 @@
       </c>
       <c r="J154" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="L154" s="4" t="str">
         <f t="shared" si="29"/>
         <v>-</v>
       </c>
       <c r="M154" s="4" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="155" spans="2:17" x14ac:dyDescent="0.3">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="155" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B155" t="s">
+        <v>146</v>
+      </c>
+      <c r="C155" t="s">
         <v>147</v>
       </c>
-      <c r="C155" t="s">
-        <v>148</v>
-      </c>
       <c r="E155" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="H155" s="2">
         <v>45307</v>
@@ -7972,25 +8061,25 @@
       </c>
       <c r="J155" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="L155" s="4" t="str">
         <f t="shared" si="29"/>
         <v>-</v>
       </c>
       <c r="M155" s="4" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="156" spans="2:17" x14ac:dyDescent="0.3">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="156" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B156" t="s">
+        <v>146</v>
+      </c>
+      <c r="C156" t="s">
         <v>147</v>
       </c>
-      <c r="C156" t="s">
-        <v>148</v>
-      </c>
       <c r="E156" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="H156" s="2">
         <v>45307</v>
@@ -8001,22 +8090,22 @@
       </c>
       <c r="J156" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="L156" s="4" t="str">
         <f t="shared" si="29"/>
         <v>-</v>
       </c>
       <c r="M156" s="4" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="157" spans="2:17" x14ac:dyDescent="0.3">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="157" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B157" t="s">
+        <v>34</v>
+      </c>
+      <c r="C157" t="s">
         <v>147</v>
-      </c>
-      <c r="C157" t="s">
-        <v>148</v>
       </c>
       <c r="D157">
         <v>710</v>
@@ -8025,10 +8114,10 @@
         <v>8</v>
       </c>
       <c r="F157" s="5" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G157" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="H157" s="2">
         <v>45189</v>
@@ -8039,34 +8128,40 @@
       </c>
       <c r="J157" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="L157" s="4" t="str">
         <f t="shared" si="29"/>
         <v>-</v>
       </c>
-      <c r="M157" s="25" t="s">
-        <v>161</v>
+      <c r="M157" t="s">
+        <v>162</v>
+      </c>
+      <c r="N157" s="2">
+        <v>45322</v>
+      </c>
+      <c r="P157" t="s">
+        <v>185</v>
       </c>
       <c r="Q157" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="158" spans="2:17" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="158" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B158" t="s">
+        <v>146</v>
+      </c>
+      <c r="C158" t="s">
         <v>147</v>
-      </c>
-      <c r="C158" t="s">
-        <v>148</v>
       </c>
       <c r="D158">
         <v>708</v>
       </c>
       <c r="F158" s="5" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G158" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I158" s="4" t="str">
         <f t="shared" ca="1" si="27"/>
@@ -8081,24 +8176,24 @@
         <v>-</v>
       </c>
       <c r="M158" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="159" spans="2:17" x14ac:dyDescent="0.3">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="159" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B159" t="s">
+        <v>146</v>
+      </c>
+      <c r="C159" t="s">
         <v>147</v>
-      </c>
-      <c r="C159" t="s">
-        <v>148</v>
       </c>
       <c r="D159">
         <v>767</v>
       </c>
       <c r="F159" s="5" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="G159" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="I159" s="4" t="str">
         <f t="shared" ca="1" si="27"/>
@@ -8112,25 +8207,25 @@
         <f t="shared" si="29"/>
         <v>-</v>
       </c>
-      <c r="M159" s="1" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="160" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="M159" s="4" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="160" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B160" t="s">
+        <v>146</v>
+      </c>
+      <c r="C160" t="s">
         <v>147</v>
-      </c>
-      <c r="C160" t="s">
-        <v>148</v>
       </c>
       <c r="D160">
         <v>769</v>
       </c>
       <c r="F160" s="5" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="G160" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="I160" s="4" t="str">
         <f t="shared" ca="1" si="27"/>
@@ -8144,16 +8239,16 @@
         <f t="shared" si="29"/>
         <v>-</v>
       </c>
-      <c r="M160" s="1" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="161" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="M160" s="4" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="161" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B161" t="s">
+        <v>146</v>
+      </c>
+      <c r="C161" t="s">
         <v>147</v>
-      </c>
-      <c r="C161" t="s">
-        <v>148</v>
       </c>
       <c r="D161">
         <v>606</v>
@@ -8162,21 +8257,21 @@
         <v>8</v>
       </c>
       <c r="F161" s="5" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="G161" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H161" s="2">
         <v>45269</v>
       </c>
       <c r="I161" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J161" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="K161" s="2">
         <v>45301</v>
@@ -8185,16 +8280,16 @@
         <f t="shared" si="29"/>
         <v>32</v>
       </c>
-      <c r="M161" s="1" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="162" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="M161" s="4" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="162" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B162" t="s">
+        <v>146</v>
+      </c>
+      <c r="C162" t="s">
         <v>147</v>
-      </c>
-      <c r="C162" t="s">
-        <v>148</v>
       </c>
       <c r="D162">
         <v>607</v>
@@ -8203,21 +8298,21 @@
         <v>8</v>
       </c>
       <c r="F162" s="5" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="G162" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H162" s="2">
         <v>45269</v>
       </c>
       <c r="I162" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J162" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="K162" s="2">
         <v>45301</v>
@@ -8226,36 +8321,36 @@
         <f t="shared" si="29"/>
         <v>32</v>
       </c>
-      <c r="M162" s="1" t="s">
-        <v>165</v>
+      <c r="M162" s="4" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="163" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B163" t="s">
+        <v>146</v>
+      </c>
+      <c r="C163" t="s">
         <v>147</v>
-      </c>
-      <c r="C163" t="s">
-        <v>148</v>
       </c>
       <c r="D163">
         <v>608</v>
       </c>
       <c r="E163" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="G163" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H163" s="2">
         <v>45269</v>
       </c>
       <c r="I163" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J163" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="K163" s="2">
         <v>45301</v>
@@ -8265,21 +8360,21 @@
         <v>32</v>
       </c>
       <c r="M163" s="4" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="O163" s="2">
         <v>45321</v>
       </c>
       <c r="Q163" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="164" spans="2:17" x14ac:dyDescent="0.3">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="164" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B164" t="s">
+        <v>146</v>
+      </c>
+      <c r="C164" t="s">
         <v>147</v>
-      </c>
-      <c r="C164" t="s">
-        <v>148</v>
       </c>
       <c r="D164">
         <v>609</v>
@@ -8288,21 +8383,21 @@
         <v>8</v>
       </c>
       <c r="F164" s="5" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="G164" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H164" s="2">
         <v>45269</v>
       </c>
       <c r="I164" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J164" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="K164" s="2">
         <v>45301</v>
@@ -8311,16 +8406,16 @@
         <f t="shared" si="29"/>
         <v>32</v>
       </c>
-      <c r="M164" s="1" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="165" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="M164" s="4" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="165" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B165" t="s">
+        <v>34</v>
+      </c>
+      <c r="C165" t="s">
         <v>147</v>
-      </c>
-      <c r="C165" t="s">
-        <v>148</v>
       </c>
       <c r="D165">
         <v>610</v>
@@ -8329,21 +8424,21 @@
         <v>8</v>
       </c>
       <c r="F165" s="5" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="G165" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H165" s="2">
         <v>45269</v>
       </c>
       <c r="I165" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J165" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="K165" s="2">
         <v>45301</v>
@@ -8352,19 +8447,25 @@
         <f t="shared" si="29"/>
         <v>32</v>
       </c>
-      <c r="M165" s="8" t="s">
-        <v>166</v>
+      <c r="M165" t="s">
+        <v>161</v>
+      </c>
+      <c r="N165" s="2">
+        <v>45322</v>
+      </c>
+      <c r="P165" t="s">
+        <v>182</v>
       </c>
       <c r="Q165" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="166" spans="2:17" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="166" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B166" t="s">
+        <v>146</v>
+      </c>
+      <c r="C166" t="s">
         <v>147</v>
-      </c>
-      <c r="C166" t="s">
-        <v>148</v>
       </c>
       <c r="D166">
         <v>611</v>
@@ -8373,21 +8474,21 @@
         <v>8</v>
       </c>
       <c r="F166" s="5" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="G166" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H166" s="2">
         <v>45269</v>
       </c>
       <c r="I166" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J166" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="K166" s="2">
         <v>45301</v>
@@ -8397,27 +8498,27 @@
         <v>32</v>
       </c>
       <c r="M166" s="4" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="Q166" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="167" spans="2:17" x14ac:dyDescent="0.3">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="167" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B167" t="s">
+        <v>34</v>
+      </c>
+      <c r="C167" t="s">
         <v>147</v>
-      </c>
-      <c r="C167" t="s">
-        <v>148</v>
       </c>
       <c r="D167">
         <v>708</v>
       </c>
       <c r="F167" s="5" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G167" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="H167" s="2">
         <v>45189</v>
@@ -8428,31 +8529,37 @@
       </c>
       <c r="J167" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="L167" s="4" t="str">
         <f t="shared" si="29"/>
         <v>-</v>
       </c>
-      <c r="M167" s="24" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="168" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="M167" t="s">
+        <v>162</v>
+      </c>
+      <c r="N167" s="2">
+        <v>45322</v>
+      </c>
+      <c r="P167" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="168" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B168" t="s">
+        <v>34</v>
+      </c>
+      <c r="C168" t="s">
         <v>147</v>
-      </c>
-      <c r="C168" t="s">
-        <v>148</v>
       </c>
       <c r="D168">
         <v>709</v>
       </c>
       <c r="F168" s="5" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G168" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="H168" s="2">
         <v>45189</v>
@@ -8463,31 +8570,37 @@
       </c>
       <c r="J168" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="L168" s="4" t="str">
         <f t="shared" si="29"/>
         <v>-</v>
       </c>
-      <c r="M168" s="24" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="169" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="M168" t="s">
+        <v>162</v>
+      </c>
+      <c r="N168" s="2">
+        <v>45322</v>
+      </c>
+      <c r="P168" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="169" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B169" t="s">
+        <v>34</v>
+      </c>
+      <c r="C169" t="s">
         <v>147</v>
-      </c>
-      <c r="C169" t="s">
-        <v>148</v>
       </c>
       <c r="D169">
         <v>711</v>
       </c>
       <c r="F169" s="5" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G169" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="H169" s="2">
         <v>45189</v>
@@ -8498,22 +8611,28 @@
       </c>
       <c r="J169" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="L169" s="4" t="str">
         <f t="shared" si="29"/>
         <v>-</v>
       </c>
-      <c r="M169" s="24" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="170" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="M169" t="s">
+        <v>162</v>
+      </c>
+      <c r="N169" s="2">
+        <v>45322</v>
+      </c>
+      <c r="P169" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="170" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B170" t="s">
+        <v>34</v>
+      </c>
+      <c r="C170" t="s">
         <v>147</v>
-      </c>
-      <c r="C170" t="s">
-        <v>148</v>
       </c>
       <c r="D170">
         <v>601</v>
@@ -8522,21 +8641,21 @@
         <v>8</v>
       </c>
       <c r="F170" s="5" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="G170" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H170" s="2">
         <v>45269</v>
       </c>
       <c r="I170" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J170" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="K170" s="2">
         <v>45301</v>
@@ -8545,19 +8664,25 @@
         <f t="shared" si="29"/>
         <v>32</v>
       </c>
-      <c r="M170" s="8" t="s">
-        <v>168</v>
+      <c r="M170" t="s">
+        <v>163</v>
+      </c>
+      <c r="N170" s="2">
+        <v>45322</v>
+      </c>
+      <c r="P170" t="s">
+        <v>182</v>
       </c>
       <c r="Q170" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="171" spans="2:17" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="171" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B171" t="s">
+        <v>146</v>
+      </c>
+      <c r="C171" t="s">
         <v>147</v>
-      </c>
-      <c r="C171" t="s">
-        <v>148</v>
       </c>
       <c r="D171">
         <v>602</v>
@@ -8566,21 +8691,21 @@
         <v>8</v>
       </c>
       <c r="F171" s="5" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="G171" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H171" s="2">
         <v>45269</v>
       </c>
       <c r="I171" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J171" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="K171" s="2">
         <v>45301</v>
@@ -8589,16 +8714,16 @@
         <f t="shared" si="29"/>
         <v>32</v>
       </c>
-      <c r="M171" s="1" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="172" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="M171" s="4" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="172" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B172" t="s">
+        <v>34</v>
+      </c>
+      <c r="C172" t="s">
         <v>147</v>
-      </c>
-      <c r="C172" t="s">
-        <v>148</v>
       </c>
       <c r="D172">
         <v>603</v>
@@ -8607,21 +8732,21 @@
         <v>8</v>
       </c>
       <c r="F172" s="5" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="G172" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="H172" s="2">
         <v>45269</v>
       </c>
       <c r="I172" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J172" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="K172" s="2">
         <v>45301</v>
@@ -8630,16 +8755,22 @@
         <f t="shared" si="29"/>
         <v>32</v>
       </c>
-      <c r="M172" s="24" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="173" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="M172" t="s">
+        <v>164</v>
+      </c>
+      <c r="N172" s="2">
+        <v>45322</v>
+      </c>
+      <c r="P172" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="173" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B173" t="s">
+        <v>34</v>
+      </c>
+      <c r="C173" t="s">
         <v>147</v>
-      </c>
-      <c r="C173" t="s">
-        <v>148</v>
       </c>
       <c r="D173">
         <v>604</v>
@@ -8648,21 +8779,21 @@
         <v>8</v>
       </c>
       <c r="F173" s="5" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="G173" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="H173" s="2">
         <v>45269</v>
       </c>
       <c r="I173" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J173" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="K173" s="2">
         <v>45301</v>
@@ -8671,16 +8802,22 @@
         <f t="shared" si="29"/>
         <v>32</v>
       </c>
-      <c r="M173" s="24" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="174" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="M173" t="s">
+        <v>164</v>
+      </c>
+      <c r="N173" s="2">
+        <v>45322</v>
+      </c>
+      <c r="P173" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="174" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B174" t="s">
+        <v>34</v>
+      </c>
+      <c r="C174" t="s">
         <v>147</v>
-      </c>
-      <c r="C174" t="s">
-        <v>148</v>
       </c>
       <c r="D174">
         <v>605</v>
@@ -8689,21 +8826,21 @@
         <v>8</v>
       </c>
       <c r="F174" s="5" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="G174" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="H174" s="2">
         <v>45269</v>
       </c>
       <c r="I174" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J174" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="K174" s="2">
         <v>45301</v>
@@ -8712,16 +8849,22 @@
         <f t="shared" si="29"/>
         <v>32</v>
       </c>
-      <c r="M174" s="24" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="175" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="M174" t="s">
+        <v>164</v>
+      </c>
+      <c r="N174" s="2">
+        <v>45322</v>
+      </c>
+      <c r="P174" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="175" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B175" t="s">
+        <v>146</v>
+      </c>
+      <c r="C175" t="s">
         <v>147</v>
-      </c>
-      <c r="C175" t="s">
-        <v>148</v>
       </c>
       <c r="D175">
         <v>649</v>
@@ -8730,36 +8873,36 @@
         <v>8</v>
       </c>
       <c r="F175" s="5" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="G175" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="H175" s="2">
         <v>45269</v>
       </c>
       <c r="I175" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J175" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="L175" s="4" t="str">
         <f t="shared" si="29"/>
         <v>-</v>
       </c>
-      <c r="M175" s="1" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="176" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="M175" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="176" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B176" t="s">
+        <v>34</v>
+      </c>
+      <c r="C176" t="s">
         <v>147</v>
-      </c>
-      <c r="C176" t="s">
-        <v>148</v>
       </c>
       <c r="D176">
         <v>650</v>
@@ -8768,31 +8911,37 @@
         <v>8</v>
       </c>
       <c r="F176" s="5" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="G176" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="H176" s="2">
         <v>45269</v>
       </c>
       <c r="I176" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J176" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="L176" s="4" t="str">
         <f t="shared" si="29"/>
         <v>-</v>
       </c>
-      <c r="M176" s="24" t="s">
-        <v>170</v>
+      <c r="M176" t="s">
+        <v>164</v>
+      </c>
+      <c r="N176" s="2">
+        <v>45322</v>
+      </c>
+      <c r="P176" t="s">
+        <v>185</v>
       </c>
       <c r="Q176" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="177" spans="9:12" hidden="1" x14ac:dyDescent="0.3">
@@ -11961,15 +12110,15 @@
     </row>
     <row r="403" spans="9:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="I403" s="4" t="str">
-        <f t="shared" ref="I403:I445" ca="1" si="39">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H403), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H403), 7), "-")</f>
+        <f t="shared" ref="I403:I446" ca="1" si="39">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H403), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H403), 7), "-")</f>
         <v>-</v>
       </c>
       <c r="J403" s="4" t="str">
-        <f t="shared" ref="J403:J445" ca="1" si="40">IF(_xlfn.DAYS(TODAY(),H403)&lt;10000, _xlfn.DAYS(TODAY(),H403), "-")</f>
+        <f t="shared" ref="J403:J446" ca="1" si="40">IF(_xlfn.DAYS(TODAY(),H403)&lt;10000, _xlfn.DAYS(TODAY(),H403), "-")</f>
         <v>-</v>
       </c>
       <c r="L403" s="4" t="str">
-        <f t="shared" ref="L403:L445" si="41">IF(_xlfn.DAYS(K403,H403)&gt;0, _xlfn.DAYS(K403,H403), "-")</f>
+        <f t="shared" ref="L403:L446" si="41">IF(_xlfn.DAYS(K403,H403)&gt;0, _xlfn.DAYS(K403,H403), "-")</f>
         <v>-</v>
       </c>
     </row>
@@ -12379,7 +12528,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="433" spans="9:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="I433" s="4" t="str">
         <f t="shared" ca="1" si="39"/>
         <v>-</v>
@@ -12393,7 +12542,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="434" spans="9:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="I434" s="4" t="str">
         <f t="shared" ca="1" si="39"/>
         <v>-</v>
@@ -12407,7 +12556,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="435" spans="9:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="I435" s="4" t="str">
         <f t="shared" ca="1" si="39"/>
         <v>-</v>
@@ -12421,7 +12570,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="436" spans="9:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="I436" s="4" t="str">
         <f t="shared" ca="1" si="39"/>
         <v>-</v>
@@ -12435,7 +12584,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="437" spans="9:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="I437" s="4" t="str">
         <f t="shared" ca="1" si="39"/>
         <v>-</v>
@@ -12449,7 +12598,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="438" spans="9:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="I438" s="4" t="str">
         <f t="shared" ca="1" si="39"/>
         <v>-</v>
@@ -12463,7 +12612,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="439" spans="9:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="I439" s="4" t="str">
         <f t="shared" ca="1" si="39"/>
         <v>-</v>
@@ -12477,7 +12626,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="440" spans="9:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="I440" s="4" t="str">
         <f t="shared" ca="1" si="39"/>
         <v>-</v>
@@ -12491,7 +12640,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="441" spans="9:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="I441" s="4" t="str">
         <f t="shared" ca="1" si="39"/>
         <v>-</v>
@@ -12505,7 +12654,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="442" spans="9:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="I442" s="4" t="str">
         <f t="shared" ca="1" si="39"/>
         <v>-</v>
@@ -12519,7 +12668,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="443" spans="9:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="I443" s="4" t="str">
         <f t="shared" ca="1" si="39"/>
         <v>-</v>
@@ -12533,7 +12682,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="444" spans="9:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="I444" s="4" t="str">
         <f t="shared" ca="1" si="39"/>
         <v>-</v>
@@ -12547,7 +12696,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="445" spans="9:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="I445" s="4" t="str">
         <f t="shared" ca="1" si="39"/>
         <v>-</v>
@@ -12561,11 +12710,354 @@
         <v>-</v>
       </c>
     </row>
+    <row r="446" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B446" t="s">
+        <v>34</v>
+      </c>
+      <c r="C446" t="s">
+        <v>128</v>
+      </c>
+      <c r="E446" t="s">
+        <v>16</v>
+      </c>
+      <c r="G446" t="s">
+        <v>188</v>
+      </c>
+      <c r="H446" s="2">
+        <v>45300</v>
+      </c>
+      <c r="I446" s="4">
+        <f t="shared" ca="1" si="39"/>
+        <v>3</v>
+      </c>
+      <c r="J446" s="4">
+        <f t="shared" ca="1" si="40"/>
+        <v>27</v>
+      </c>
+      <c r="K446" s="23">
+        <v>45324</v>
+      </c>
+      <c r="L446" s="4">
+        <f t="shared" si="41"/>
+        <v>24</v>
+      </c>
+      <c r="M446" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="447" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B447" t="s">
+        <v>34</v>
+      </c>
+      <c r="C447" t="s">
+        <v>128</v>
+      </c>
+      <c r="E447" t="s">
+        <v>16</v>
+      </c>
+      <c r="G447" t="s">
+        <v>188</v>
+      </c>
+      <c r="H447" s="2">
+        <v>45300</v>
+      </c>
+      <c r="I447" s="4">
+        <f t="shared" ref="I447:I455" ca="1" si="42">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H447), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H447), 7), "-")</f>
+        <v>3</v>
+      </c>
+      <c r="J447" s="4">
+        <f t="shared" ref="J447:J455" ca="1" si="43">IF(_xlfn.DAYS(TODAY(),H447)&lt;10000, _xlfn.DAYS(TODAY(),H447), "-")</f>
+        <v>27</v>
+      </c>
+      <c r="K447" s="23">
+        <v>45324</v>
+      </c>
+      <c r="L447" s="4">
+        <f t="shared" ref="L447:L454" si="44">IF(_xlfn.DAYS(K447,H447)&gt;0, _xlfn.DAYS(K447,H447), "-")</f>
+        <v>24</v>
+      </c>
+      <c r="M447" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="448" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B448" t="s">
+        <v>34</v>
+      </c>
+      <c r="C448" t="s">
+        <v>128</v>
+      </c>
+      <c r="E448" t="s">
+        <v>16</v>
+      </c>
+      <c r="G448" t="s">
+        <v>188</v>
+      </c>
+      <c r="H448" s="2">
+        <v>45300</v>
+      </c>
+      <c r="I448" s="4">
+        <f t="shared" ca="1" si="42"/>
+        <v>3</v>
+      </c>
+      <c r="J448" s="4">
+        <f t="shared" ca="1" si="43"/>
+        <v>27</v>
+      </c>
+      <c r="K448" s="23">
+        <v>45324</v>
+      </c>
+      <c r="L448" s="4">
+        <f t="shared" si="44"/>
+        <v>24</v>
+      </c>
+      <c r="M448" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="449" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B449" t="s">
+        <v>34</v>
+      </c>
+      <c r="C449" t="s">
+        <v>128</v>
+      </c>
+      <c r="E449" t="s">
+        <v>16</v>
+      </c>
+      <c r="G449" t="s">
+        <v>189</v>
+      </c>
+      <c r="H449" s="2">
+        <v>45300</v>
+      </c>
+      <c r="I449" s="4">
+        <f t="shared" ca="1" si="42"/>
+        <v>3</v>
+      </c>
+      <c r="J449" s="4">
+        <f t="shared" ca="1" si="43"/>
+        <v>27</v>
+      </c>
+      <c r="K449" s="23">
+        <v>45324</v>
+      </c>
+      <c r="L449" s="4">
+        <f t="shared" si="44"/>
+        <v>24</v>
+      </c>
+      <c r="M449" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="450" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B450" t="s">
+        <v>34</v>
+      </c>
+      <c r="C450" t="s">
+        <v>128</v>
+      </c>
+      <c r="E450" t="s">
+        <v>16</v>
+      </c>
+      <c r="G450" t="s">
+        <v>189</v>
+      </c>
+      <c r="H450" s="2">
+        <v>45300</v>
+      </c>
+      <c r="I450" s="4">
+        <f t="shared" ca="1" si="42"/>
+        <v>3</v>
+      </c>
+      <c r="J450" s="4">
+        <f t="shared" ca="1" si="43"/>
+        <v>27</v>
+      </c>
+      <c r="K450" s="23">
+        <v>45324</v>
+      </c>
+      <c r="L450" s="4">
+        <f t="shared" si="44"/>
+        <v>24</v>
+      </c>
+      <c r="M450" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="451" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B451" t="s">
+        <v>34</v>
+      </c>
+      <c r="C451" t="s">
+        <v>128</v>
+      </c>
+      <c r="E451" t="s">
+        <v>16</v>
+      </c>
+      <c r="G451" t="s">
+        <v>189</v>
+      </c>
+      <c r="H451" s="2">
+        <v>45300</v>
+      </c>
+      <c r="I451" s="4">
+        <f t="shared" ca="1" si="42"/>
+        <v>3</v>
+      </c>
+      <c r="J451" s="4">
+        <f t="shared" ca="1" si="43"/>
+        <v>27</v>
+      </c>
+      <c r="K451" s="23">
+        <v>45324</v>
+      </c>
+      <c r="L451" s="4">
+        <f t="shared" si="44"/>
+        <v>24</v>
+      </c>
+      <c r="M451" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="452" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B452" t="s">
+        <v>34</v>
+      </c>
+      <c r="C452" t="s">
+        <v>128</v>
+      </c>
+      <c r="E452" t="s">
+        <v>16</v>
+      </c>
+      <c r="G452" t="s">
+        <v>189</v>
+      </c>
+      <c r="H452" s="2">
+        <v>45300</v>
+      </c>
+      <c r="I452" s="4">
+        <f t="shared" ca="1" si="42"/>
+        <v>3</v>
+      </c>
+      <c r="J452" s="4">
+        <f t="shared" ca="1" si="43"/>
+        <v>27</v>
+      </c>
+      <c r="K452" s="23">
+        <v>45324</v>
+      </c>
+      <c r="L452" s="4">
+        <f t="shared" si="44"/>
+        <v>24</v>
+      </c>
+      <c r="M452" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="453" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B453" t="s">
+        <v>34</v>
+      </c>
+      <c r="C453" t="s">
+        <v>128</v>
+      </c>
+      <c r="E453" t="s">
+        <v>16</v>
+      </c>
+      <c r="G453" t="s">
+        <v>189</v>
+      </c>
+      <c r="H453" s="2">
+        <v>45300</v>
+      </c>
+      <c r="I453" s="4">
+        <f t="shared" ca="1" si="42"/>
+        <v>3</v>
+      </c>
+      <c r="J453" s="4">
+        <f t="shared" ca="1" si="43"/>
+        <v>27</v>
+      </c>
+      <c r="K453" s="23">
+        <v>45324</v>
+      </c>
+      <c r="L453" s="4">
+        <f t="shared" si="44"/>
+        <v>24</v>
+      </c>
+      <c r="M453" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="454" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B454" t="s">
+        <v>34</v>
+      </c>
+      <c r="C454" t="s">
+        <v>128</v>
+      </c>
+      <c r="E454" t="s">
+        <v>16</v>
+      </c>
+      <c r="G454" t="s">
+        <v>189</v>
+      </c>
+      <c r="H454" s="2">
+        <v>45300</v>
+      </c>
+      <c r="I454" s="4">
+        <f t="shared" ca="1" si="42"/>
+        <v>3</v>
+      </c>
+      <c r="J454" s="4">
+        <f t="shared" ca="1" si="43"/>
+        <v>27</v>
+      </c>
+      <c r="K454" s="23">
+        <v>45324</v>
+      </c>
+      <c r="L454" s="4">
+        <f t="shared" si="44"/>
+        <v>24</v>
+      </c>
+      <c r="M454" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="455" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B455" t="s">
+        <v>191</v>
+      </c>
+      <c r="C455" t="s">
+        <v>128</v>
+      </c>
+      <c r="H455" s="2">
+        <v>45324</v>
+      </c>
+      <c r="I455" s="4">
+        <f t="shared" ca="1" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="J455" s="4">
+        <f t="shared" ca="1" si="43"/>
+        <v>3</v>
+      </c>
+      <c r="M455" t="s">
+        <v>192</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="B1:Q445" xr:uid="{47ECCD65-6802-4B2B-901A-AED4A431A765}">
+  <autoFilter ref="B1:Q455" xr:uid="{47ECCD65-6802-4B2B-901A-AED4A431A765}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="SPF"/>
+      </filters>
+    </filterColumn>
     <filterColumn colId="1">
       <filters>
-        <filter val="Tcrd-CreER; Tsg101-flox"/>
+        <filter val="Cd36-flox"/>
+        <filter val="Tmem119-CreERT2; Cd36-flox"/>
       </filters>
     </filterColumn>
     <filterColumn colId="13">
@@ -12582,7 +13074,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E140 E142:E143 E145:E150 E152:E153 E160:E1048576 E155:E158" xr:uid="{939E2B39-E841-4A9F-AD11-00C266DB2690}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E140 E142:E143 E145:E150 E152:E153 E155:E158 E160:E1048576" xr:uid="{939E2B39-E841-4A9F-AD11-00C266DB2690}">
       <formula1>"Y, N"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1:G1048576" xr:uid="{2DE54AC7-5B92-48D6-98C4-E6203F87CDD0}">
@@ -12608,28 +13100,28 @@
   <sheetData>
     <row r="2" spans="3:8" x14ac:dyDescent="0.3">
       <c r="D2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G2" s="24" t="s">
         <v>88</v>
       </c>
-      <c r="E2" t="s">
-        <v>75</v>
-      </c>
-      <c r="G2" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="H2" s="22"/>
+      <c r="H2" s="24"/>
     </row>
     <row r="3" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>22</v>
       </c>
       <c r="G3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H3" s="5" t="s">
         <v>22</v>
@@ -12637,16 +13129,16 @@
     </row>
     <row r="4" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D4" t="s">
         <v>86</v>
-      </c>
-      <c r="D4" t="s">
-        <v>87</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>22</v>
       </c>
       <c r="G4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H4" s="5" t="s">
         <v>22</v>

--- a/Mouse 내역.xlsx
+++ b/Mouse 내역.xlsx
@@ -5,19 +5,20 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\heung\OneDrive\바탕 화면\동물실\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\heung\Dropbox\02. Lab. of Host Defenses\03. 동물실\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B733ACE5-AB32-4E7C-A9E1-EC8D439CD952}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72AD19B1-BFFB-4408-BA85-3DA56D26BBF8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19080" windowHeight="9180" xr2:uid="{5A73A69A-2AFB-4F3E-AC64-070DD7700CB2}"/>
+    <workbookView xWindow="0" yWindow="495" windowWidth="28800" windowHeight="16245" xr2:uid="{5A73A69A-2AFB-4F3E-AC64-070DD7700CB2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1 (2)" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$Q$201</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$Q$200</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1324" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1360" uniqueCount="226">
   <si>
     <t>Strain</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -475,18 +476,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>A2.3.X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>SPF</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>A2.4.X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>A3.B</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -499,10 +492,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>같이 weaning</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>왼쪽 tag, 오른쪽 위 punch</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -628,14 +617,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>H3.1.X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>H4.1.X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>N</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -766,10 +747,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>from E1.2.M</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>5F</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -798,14 +775,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>G1.1.X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>생존 못할수 있음</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>SPF</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -847,6 +816,106 @@
   </si>
   <si>
     <t>WT B6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>죽이기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>To D2.B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>To E2.B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>To D2.B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tcrd Tsg101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Exp. 1-11-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3 by 3으로 D-5, D-3 Tam/Corn 찌르고 D0 peritoneal cavity에서 Macrophage FACS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tmem119 Tsg101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Exp. 1-10-1 (Repeat of Exp. 1-4-3)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D-5, D-3에 Tam/Corn 찌르고 D0에 Intestine H&amp;E</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>46, 46</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8, 46, 46</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MFF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>H4.1.M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>H3.1.F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A2.3.M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A2.3.F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tmem119-CreERT2; Tsg101-flox</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -970,7 +1039,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1008,6 +1077,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1026,7 +1106,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1066,27 +1146,6 @@
     <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="6" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1097,6 +1156,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="4" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="4" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="2">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1110,7 +1181,27 @@
     <cellStyle name="좋음" xfId="1" builtinId="26"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1681,8 +1772,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D71A6DC-E91C-489F-8F50-989C4712FA7C}">
   <sheetPr filterMode="1"/>
-  <dimension ref="B1:Q201"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="B1:Q200"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="10.5" customWidth="1"/>
     <col min="3" max="3" width="29.125" bestFit="1" customWidth="1"/>
@@ -1693,10 +1784,10 @@
     <col min="8" max="8" width="11.125" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="9" customWidth="1"/>
     <col min="11" max="11" width="11.125" style="2" customWidth="1"/>
-    <col min="12" max="12" width="8.25" customWidth="1"/>
-    <col min="14" max="14" width="13.125" style="2" customWidth="1"/>
-    <col min="15" max="15" width="12.75" style="2" customWidth="1"/>
-    <col min="16" max="16" width="13.25" customWidth="1"/>
+    <col min="12" max="12" width="8.125" customWidth="1"/>
+    <col min="14" max="14" width="13.125" style="2" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="12.625" style="2" customWidth="1"/>
+    <col min="16" max="16" width="13.125" customWidth="1"/>
     <col min="17" max="17" width="31.625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1753,7 +1844,7 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1769,11 +1860,11 @@
       </c>
       <c r="I2" s="4">
         <f ca="1">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H2), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H2), 7), "-")</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J2" s="4">
         <f ca="1">IF(_xlfn.DAYS(TODAY(),H2)&lt;10000, _xlfn.DAYS(TODAY(),H2), "-")</f>
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="L2" s="4" t="str">
         <f t="shared" ref="L2:L31" si="0">IF(_xlfn.DAYS(K2,H2)&gt;0, _xlfn.DAYS(K2,H2), "-")</f>
@@ -1787,12 +1878,12 @@
         <v>45299</v>
       </c>
     </row>
-    <row r="3" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1808,11 +1899,11 @@
       </c>
       <c r="I3" s="4">
         <f t="shared" ref="I3:I65" ca="1" si="1">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H3), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H3), 7), "-")</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J3" s="4">
         <f t="shared" ref="J3:J31" ca="1" si="2">IF(_xlfn.DAYS(TODAY(),H3)&lt;10000, _xlfn.DAYS(TODAY(),H3), "-")</f>
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="L3" s="4" t="str">
         <f t="shared" si="0"/>
@@ -1824,12 +1915,12 @@
       <c r="N3" s="7"/>
       <c r="O3" s="7"/>
     </row>
-    <row r="4" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1845,11 +1936,11 @@
       </c>
       <c r="I4" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J4" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="L4" s="4" t="str">
         <f t="shared" si="0"/>
@@ -1866,7 +1957,7 @@
         <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D5">
         <v>871</v>
@@ -1885,11 +1976,11 @@
       </c>
       <c r="I5" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J5" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="K5" s="2">
         <v>45293</v>
@@ -1906,96 +1997,96 @@
         <v>45309</v>
       </c>
     </row>
-    <row r="6" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="D6">
         <v>686</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="E6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="20" t="s">
+      <c r="F6" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="G6" s="17" t="s">
+      <c r="G6" t="s">
         <v>76</v>
       </c>
-      <c r="H6" s="14">
+      <c r="H6" s="2">
         <v>45266</v>
       </c>
-      <c r="I6" s="16">
+      <c r="I6" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J6" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>62</v>
-      </c>
-      <c r="K6" s="14">
+        <v>70</v>
+      </c>
+      <c r="K6" s="2">
         <v>45293</v>
       </c>
       <c r="L6" s="4">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="M6" s="16" t="s">
-        <v>141</v>
+      <c r="M6" s="4" t="s">
+        <v>138</v>
       </c>
       <c r="N6" s="7"/>
-      <c r="O6" s="18"/>
-      <c r="Q6" s="17" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="O6" s="7"/>
+      <c r="Q6" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="7" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D7">
         <v>687</v>
       </c>
-      <c r="E7" s="16" t="s">
+      <c r="E7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="20" t="s">
+      <c r="F7" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="G7" s="16" t="s">
+      <c r="G7" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="H7" s="14">
+      <c r="H7" s="2">
         <v>45266</v>
       </c>
-      <c r="I7" s="16">
+      <c r="I7" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J7" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>62</v>
-      </c>
-      <c r="K7" s="14">
+        <v>70</v>
+      </c>
+      <c r="K7" s="2">
         <v>45293</v>
       </c>
       <c r="L7" s="4">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="M7" s="16" t="s">
-        <v>193</v>
+      <c r="M7" s="4" t="s">
+        <v>187</v>
       </c>
       <c r="N7" s="7"/>
-      <c r="O7" s="18"/>
+      <c r="O7" s="7"/>
       <c r="Q7" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="8" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -2003,55 +2094,55 @@
         <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D8">
         <v>688</v>
       </c>
-      <c r="E8" s="15" t="s">
+      <c r="E8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="17" t="s">
+      <c r="F8" t="s">
         <v>94</v>
       </c>
-      <c r="G8" s="17" t="s">
+      <c r="G8" t="s">
         <v>76</v>
       </c>
-      <c r="H8" s="14">
+      <c r="H8" s="2">
         <v>45266</v>
       </c>
-      <c r="I8" s="16">
+      <c r="I8" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J8" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>62</v>
-      </c>
-      <c r="K8" s="14">
+        <v>70</v>
+      </c>
+      <c r="K8" s="2">
         <v>45293</v>
       </c>
       <c r="L8" s="4">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="M8" s="17" t="s">
+      <c r="M8" t="s">
         <v>74</v>
       </c>
       <c r="N8" s="7"/>
-      <c r="O8" s="18">
+      <c r="O8" s="7">
         <v>45315</v>
       </c>
-      <c r="Q8" s="17" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="Q8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="9" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>5</v>
       </c>
       <c r="C9" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D9">
         <v>921</v>
@@ -2070,11 +2161,11 @@
       </c>
       <c r="I9" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J9" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="K9" s="2">
         <v>45293</v>
@@ -2094,7 +2185,7 @@
         <v>5</v>
       </c>
       <c r="C10" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D10">
         <v>922</v>
@@ -2113,11 +2204,11 @@
       </c>
       <c r="I10" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J10" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="K10" s="2">
         <v>45293</v>
@@ -2139,7 +2230,7 @@
         <v>5</v>
       </c>
       <c r="C11" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D11">
         <v>923</v>
@@ -2158,11 +2249,11 @@
       </c>
       <c r="I11" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J11" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="K11" s="2">
         <v>45293</v>
@@ -2184,7 +2275,7 @@
         <v>5</v>
       </c>
       <c r="C12" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E12" t="s">
         <v>7</v>
@@ -2200,11 +2291,11 @@
       </c>
       <c r="I12" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J12" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="L12" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2223,7 +2314,7 @@
         <v>5</v>
       </c>
       <c r="C13" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E13" t="s">
         <v>7</v>
@@ -2259,7 +2350,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E14" t="s">
         <v>7</v>
@@ -2290,12 +2381,12 @@
         <v>45299</v>
       </c>
     </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>5</v>
       </c>
       <c r="C15" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D15">
         <v>972</v>
@@ -2314,11 +2405,11 @@
       </c>
       <c r="I15" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J15" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="L15" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2330,12 +2421,12 @@
       <c r="N15" s="7"/>
       <c r="O15" s="7"/>
     </row>
-    <row r="16" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>5</v>
       </c>
       <c r="C16" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D16">
         <v>973</v>
@@ -2354,11 +2445,11 @@
       </c>
       <c r="I16" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J16" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="L16" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2370,12 +2461,12 @@
       <c r="N16" s="7"/>
       <c r="O16" s="7"/>
     </row>
-    <row r="17" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>5</v>
       </c>
       <c r="C17" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D17">
         <v>974</v>
@@ -2394,11 +2485,11 @@
       </c>
       <c r="I17" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J17" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="L17" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2413,7 +2504,7 @@
         <v>5</v>
       </c>
       <c r="C18" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D18">
         <v>975</v>
@@ -2432,29 +2523,29 @@
       </c>
       <c r="I18" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J18" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="L18" s="4" t="str">
         <f t="shared" si="0"/>
         <v>-</v>
       </c>
       <c r="M18" s="4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="O18" s="2">
         <v>45327</v>
       </c>
     </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>5</v>
       </c>
       <c r="C19" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D19">
         <v>970</v>
@@ -2473,11 +2564,11 @@
       </c>
       <c r="I19" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J19" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="L19" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2492,7 +2583,7 @@
         <v>5</v>
       </c>
       <c r="C20" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E20" t="s">
         <v>7</v>
@@ -2508,11 +2599,11 @@
       </c>
       <c r="I20" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J20" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="L20" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2530,7 +2621,7 @@
         <v>5</v>
       </c>
       <c r="C21" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E21" t="s">
         <v>7</v>
@@ -2565,7 +2656,7 @@
         <v>5</v>
       </c>
       <c r="C22" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -2581,11 +2672,11 @@
       </c>
       <c r="I22" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J22" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="K22" s="2">
         <v>45112</v>
@@ -2606,7 +2697,7 @@
         <v>5</v>
       </c>
       <c r="C23" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="E23" t="s">
         <v>7</v>
@@ -2622,11 +2713,11 @@
       </c>
       <c r="I23" s="4">
         <f ca="1">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H23), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H23), 7), "-")</f>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J23" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="K23" s="2">
         <v>45176</v>
@@ -2650,7 +2741,7 @@
         <v>5</v>
       </c>
       <c r="C24" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="E24" t="s">
         <v>7</v>
@@ -2666,11 +2757,11 @@
       </c>
       <c r="I24" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J24" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="K24" s="2">
         <v>45176</v>
@@ -2694,7 +2785,7 @@
         <v>5</v>
       </c>
       <c r="C25" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="E25" t="s">
         <v>7</v>
@@ -2710,11 +2801,11 @@
       </c>
       <c r="I25" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J25" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="K25" s="2">
         <v>45176</v>
@@ -2733,12 +2824,12 @@
         <v>112</v>
       </c>
     </row>
-    <row r="26" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>5</v>
       </c>
       <c r="C26" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E26" t="s">
         <v>7</v>
@@ -2754,11 +2845,11 @@
       </c>
       <c r="I26" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J26" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="K26" s="2">
         <v>45176</v>
@@ -2768,16 +2859,16 @@
         <v>22</v>
       </c>
       <c r="M26" s="4" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="Q26" s="2"/>
     </row>
-    <row r="27" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>5</v>
       </c>
       <c r="C27" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E27" t="s">
         <v>7</v>
@@ -2793,11 +2884,11 @@
       </c>
       <c r="I27" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J27" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="K27" s="2">
         <v>45176</v>
@@ -2807,7 +2898,7 @@
         <v>22</v>
       </c>
       <c r="M27" s="4" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="Q27" s="2"/>
     </row>
@@ -2816,97 +2907,95 @@
         <v>5</v>
       </c>
       <c r="C28" t="s">
-        <v>164</v>
-      </c>
-      <c r="E28" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="E28" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F28" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="G28" s="17" t="s">
+      <c r="F28" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="G28" t="s">
         <v>11</v>
       </c>
-      <c r="H28" s="14">
+      <c r="H28" s="2">
         <v>45203</v>
       </c>
-      <c r="I28" s="16">
+      <c r="I28" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J28" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>125</v>
-      </c>
-      <c r="K28" s="14">
+        <v>133</v>
+      </c>
+      <c r="K28" s="2">
         <v>45229</v>
       </c>
       <c r="L28" s="4">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="M28" s="17" t="s">
+      <c r="M28" t="s">
         <v>55</v>
       </c>
-      <c r="O28" s="14">
+      <c r="O28" s="2">
         <v>45310</v>
       </c>
-      <c r="Q28" s="17"/>
     </row>
     <row r="29" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
         <v>5</v>
       </c>
       <c r="C29" t="s">
-        <v>165</v>
-      </c>
-      <c r="E29" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F29" s="19" t="s">
+      <c r="F29" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="G29" s="17" t="s">
+      <c r="G29" t="s">
         <v>11</v>
       </c>
-      <c r="H29" s="14">
+      <c r="H29" s="2">
         <v>45203</v>
       </c>
-      <c r="I29" s="16">
+      <c r="I29" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J29" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>125</v>
-      </c>
-      <c r="K29" s="14">
+        <v>133</v>
+      </c>
+      <c r="K29" s="2">
         <v>45229</v>
       </c>
       <c r="L29" s="4">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="M29" s="17" t="s">
+      <c r="M29" t="s">
         <v>55</v>
       </c>
-      <c r="O29" s="14">
+      <c r="O29" s="2">
         <v>45310</v>
       </c>
-      <c r="Q29" s="17"/>
-    </row>
-    <row r="30" spans="2:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>5</v>
       </c>
       <c r="C30" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
       </c>
       <c r="F30" s="10" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G30" t="s">
         <v>13</v>
@@ -2916,11 +3005,11 @@
       </c>
       <c r="I30" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J30" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="K30" s="2">
         <v>45229</v>
@@ -2930,22 +3019,22 @@
         <v>26</v>
       </c>
       <c r="M30" s="4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="Q30" s="2"/>
     </row>
-    <row r="31" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
         <v>5</v>
       </c>
       <c r="C31" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
       </c>
       <c r="F31" s="10" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G31" t="s">
         <v>13</v>
@@ -2955,11 +3044,11 @@
       </c>
       <c r="I31" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J31" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="K31" s="2">
         <v>45229</v>
@@ -2969,22 +3058,22 @@
         <v>26</v>
       </c>
       <c r="M31" s="4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="Q31" s="2"/>
     </row>
-    <row r="32" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
         <v>5</v>
       </c>
       <c r="C32" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
       </c>
       <c r="F32" s="10" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G32" t="s">
         <v>13</v>
@@ -2994,11 +3083,11 @@
       </c>
       <c r="I32" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J32" s="4">
         <f t="shared" ref="J32:J38" ca="1" si="3">IF(_xlfn.DAYS(TODAY(),H32)&lt;10000, _xlfn.DAYS(TODAY(),H32), "-")</f>
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="K32" s="2">
         <v>45229</v>
@@ -3008,7 +3097,7 @@
         <v>26</v>
       </c>
       <c r="M32" s="4" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="Q32" s="2"/>
     </row>
@@ -3017,7 +3106,7 @@
         <v>5</v>
       </c>
       <c r="C33" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
@@ -3052,7 +3141,7 @@
         <v>5</v>
       </c>
       <c r="C34" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D34" t="s">
         <v>24</v>
@@ -3071,11 +3160,11 @@
       </c>
       <c r="I34" s="4">
         <f ca="1">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H34), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H34), 7), "-")</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J34" s="4">
         <f ca="1">IF(_xlfn.DAYS(TODAY(),H34)&lt;10000, _xlfn.DAYS(TODAY(),H34), "-")</f>
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="K34" s="2">
         <v>45257</v>
@@ -3099,7 +3188,7 @@
         <v>5</v>
       </c>
       <c r="C35" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
@@ -3137,7 +3226,7 @@
         <v>5</v>
       </c>
       <c r="C36" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
@@ -3175,7 +3264,7 @@
         <v>5</v>
       </c>
       <c r="C37" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D37" t="s">
         <v>23</v>
@@ -3194,11 +3283,11 @@
       </c>
       <c r="I37" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J37" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="K37" s="2">
         <v>45257</v>
@@ -3222,7 +3311,7 @@
         <v>5</v>
       </c>
       <c r="C38" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D38" t="s">
         <v>24</v>
@@ -3241,11 +3330,11 @@
       </c>
       <c r="I38" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J38" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="K38" s="2">
         <v>45257</v>
@@ -3269,7 +3358,7 @@
         <v>5</v>
       </c>
       <c r="C39" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D39" t="s">
         <v>25</v>
@@ -3288,11 +3377,11 @@
       </c>
       <c r="I39" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J39" s="4">
         <f t="shared" ref="J39:J41" ca="1" si="5">IF(_xlfn.DAYS(TODAY(),H39)&lt;10000, _xlfn.DAYS(TODAY(),H39), "-")</f>
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="K39" s="2">
         <v>45257</v>
@@ -3316,7 +3405,7 @@
         <v>5</v>
       </c>
       <c r="C40" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="D40" t="s">
         <v>23</v>
@@ -3325,7 +3414,7 @@
         <v>8</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G40" t="s">
         <v>11</v>
@@ -3335,11 +3424,11 @@
       </c>
       <c r="I40" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J40" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="K40" s="2">
         <v>45257</v>
@@ -3360,7 +3449,7 @@
         <v>5</v>
       </c>
       <c r="C41" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D41" t="s">
         <v>25</v>
@@ -3379,11 +3468,11 @@
       </c>
       <c r="I41" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J41" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="K41" s="2">
         <v>45257</v>
@@ -3404,7 +3493,7 @@
         <v>5</v>
       </c>
       <c r="C42" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D42">
         <v>798</v>
@@ -3423,11 +3512,11 @@
       </c>
       <c r="I42" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J42" s="4">
         <f t="shared" ref="J42" ca="1" si="6">IF(_xlfn.DAYS(TODAY(),H42)&lt;10000, _xlfn.DAYS(TODAY(),H42), "-")</f>
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="L42" s="4" t="str">
         <f t="shared" si="4"/>
@@ -3440,12 +3529,12 @@
         <v>45309</v>
       </c>
     </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B43" t="s">
         <v>5</v>
       </c>
       <c r="C43" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D43">
         <v>799</v>
@@ -3464,18 +3553,18 @@
       </c>
       <c r="I43" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J43" s="4">
         <f t="shared" ref="J43:J91" ca="1" si="7">IF(_xlfn.DAYS(TODAY(),H43)&lt;10000, _xlfn.DAYS(TODAY(),H43), "-")</f>
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="L43" s="4" t="str">
         <f t="shared" si="4"/>
         <v>-</v>
       </c>
       <c r="M43" s="4" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -3483,7 +3572,7 @@
         <v>5</v>
       </c>
       <c r="C44" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D44">
         <v>815</v>
@@ -3502,11 +3591,11 @@
       </c>
       <c r="I44" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J44" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="K44" s="2">
         <v>45293</v>
@@ -3527,7 +3616,7 @@
         <v>5</v>
       </c>
       <c r="C45" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D45">
         <v>816</v>
@@ -3546,11 +3635,11 @@
       </c>
       <c r="I45" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J45" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="K45" s="2">
         <v>45293</v>
@@ -3571,7 +3660,7 @@
         <v>5</v>
       </c>
       <c r="C46" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D46">
         <v>817</v>
@@ -3590,11 +3679,11 @@
       </c>
       <c r="I46" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J46" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="K46" s="2">
         <v>45293</v>
@@ -3618,7 +3707,7 @@
         <v>5</v>
       </c>
       <c r="C47" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D47">
         <v>819</v>
@@ -3637,11 +3726,11 @@
       </c>
       <c r="I47" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J47" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="K47" s="2">
         <v>45293</v>
@@ -3665,7 +3754,7 @@
         <v>5</v>
       </c>
       <c r="C48" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D48">
         <v>820</v>
@@ -3684,11 +3773,11 @@
       </c>
       <c r="I48" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J48" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="K48" s="2">
         <v>45293</v>
@@ -3707,12 +3796,12 @@
         <v>112</v>
       </c>
     </row>
-    <row r="49" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B49" t="s">
         <v>5</v>
       </c>
       <c r="C49" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D49">
         <v>821</v>
@@ -3721,7 +3810,7 @@
         <v>8</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G49" t="s">
         <v>77</v>
@@ -3731,11 +3820,11 @@
       </c>
       <c r="I49" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J49" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="K49" s="2">
         <v>45293</v>
@@ -3748,12 +3837,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="50" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B50" t="s">
         <v>5</v>
       </c>
       <c r="C50" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D50">
         <v>822</v>
@@ -3762,7 +3851,7 @@
         <v>8</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G50" t="s">
         <v>77</v>
@@ -3772,11 +3861,11 @@
       </c>
       <c r="I50" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J50" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="K50" s="2">
         <v>45293</v>
@@ -3794,7 +3883,7 @@
         <v>5</v>
       </c>
       <c r="C51" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D51">
         <v>823</v>
@@ -3813,11 +3902,11 @@
       </c>
       <c r="I51" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J51" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="K51" s="2">
         <v>45293</v>
@@ -3838,7 +3927,7 @@
         <v>5</v>
       </c>
       <c r="C52" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D52">
         <v>824</v>
@@ -3857,11 +3946,11 @@
       </c>
       <c r="I52" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J52" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="K52" s="2">
         <v>45293</v>
@@ -3877,12 +3966,12 @@
         <v>45309</v>
       </c>
     </row>
-    <row r="53" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B53" t="s">
         <v>5</v>
       </c>
       <c r="C53" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D53">
         <v>825</v>
@@ -3891,7 +3980,7 @@
         <v>8</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G53" t="s">
         <v>77</v>
@@ -3901,11 +3990,11 @@
       </c>
       <c r="I53" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J53" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="K53" s="2">
         <v>45293</v>
@@ -3918,12 +4007,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="54" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B54" t="s">
         <v>27</v>
       </c>
       <c r="C54" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D54" t="s">
         <v>28</v>
@@ -3942,11 +4031,11 @@
       </c>
       <c r="I54" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J54" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="K54" s="2">
         <v>45238</v>
@@ -3958,13 +4047,16 @@
       <c r="M54" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="55" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q54" s="17" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="55" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B55" t="s">
         <v>27</v>
       </c>
       <c r="C55" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D55" t="s">
         <v>30</v>
@@ -3983,11 +4075,11 @@
       </c>
       <c r="I55" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J55" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="K55" s="2">
         <v>45238</v>
@@ -3999,13 +4091,16 @@
       <c r="M55" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="56" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q55" s="17" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="56" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B56" t="s">
         <v>27</v>
       </c>
       <c r="C56" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D56" t="s">
         <v>29</v>
@@ -4024,11 +4119,11 @@
       </c>
       <c r="I56" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J56" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="K56" s="2">
         <v>45238</v>
@@ -4040,18 +4135,21 @@
       <c r="M56" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="57" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q56" s="17" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="57" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B57" t="s">
         <v>27</v>
       </c>
       <c r="C57" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E57" t="s">
         <v>31</v>
       </c>
-      <c r="F57" s="21" t="s">
+      <c r="F57" s="14" t="s">
         <v>110</v>
       </c>
       <c r="G57" t="s">
@@ -4062,11 +4160,11 @@
       </c>
       <c r="I57" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J57" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="L57" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4075,18 +4173,21 @@
       <c r="M57" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="58" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q57" s="17" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="58" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B58" t="s">
         <v>27</v>
       </c>
       <c r="C58" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E58" t="s">
         <v>31</v>
       </c>
-      <c r="F58" s="21" t="s">
+      <c r="F58" s="14" t="s">
         <v>110</v>
       </c>
       <c r="G58" t="s">
@@ -4097,11 +4198,11 @@
       </c>
       <c r="I58" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J58" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="L58" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4110,13 +4211,16 @@
       <c r="M58" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="59" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q58" s="17" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="59" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B59" t="s">
         <v>27</v>
       </c>
       <c r="C59" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E59" t="s">
         <v>26</v>
@@ -4129,11 +4233,11 @@
       </c>
       <c r="I59" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J59" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="K59" s="2">
         <v>45295</v>
@@ -4145,16 +4249,16 @@
       <c r="M59" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="Q59" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="60" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q59" s="17" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="60" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B60" t="s">
         <v>27</v>
       </c>
       <c r="C60" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E60" t="s">
         <v>26</v>
@@ -4167,11 +4271,11 @@
       </c>
       <c r="I60" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J60" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="K60" s="2">
         <v>45295</v>
@@ -4183,13 +4287,16 @@
       <c r="M60" s="4" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="61" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q60" s="18" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="61" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B61" t="s">
         <v>27</v>
       </c>
       <c r="C61" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E61" t="s">
         <v>26</v>
@@ -4202,11 +4309,11 @@
       </c>
       <c r="I61" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J61" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="K61" s="2">
         <v>45295</v>
@@ -4219,12 +4326,12 @@
         <v>98</v>
       </c>
     </row>
-    <row r="62" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B62" t="s">
         <v>27</v>
       </c>
       <c r="C62" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E62" t="s">
         <v>26</v>
@@ -4237,11 +4344,11 @@
       </c>
       <c r="I62" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J62" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="K62" s="2">
         <v>45295</v>
@@ -4254,12 +4361,12 @@
         <v>98</v>
       </c>
     </row>
-    <row r="63" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B63" t="s">
         <v>27</v>
       </c>
       <c r="C63" t="s">
-        <v>126</v>
+        <v>225</v>
       </c>
       <c r="E63" t="s">
         <v>26</v>
@@ -4272,11 +4379,11 @@
       </c>
       <c r="I63" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J63" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="K63" s="2">
         <v>45295</v>
@@ -4289,12 +4396,12 @@
         <v>99</v>
       </c>
     </row>
-    <row r="64" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B64" t="s">
         <v>27</v>
       </c>
       <c r="C64" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E64" t="s">
         <v>26</v>
@@ -4307,11 +4414,11 @@
       </c>
       <c r="I64" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J64" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="K64" s="2">
         <v>45295</v>
@@ -4324,17 +4431,17 @@
         <v>99</v>
       </c>
     </row>
-    <row r="65" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B65" t="s">
         <v>27</v>
       </c>
       <c r="C65" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E65" t="s">
         <v>31</v>
       </c>
-      <c r="F65" s="21" t="s">
+      <c r="F65" s="14" t="s">
         <v>110</v>
       </c>
       <c r="G65" t="s">
@@ -4345,11 +4452,11 @@
       </c>
       <c r="I65" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J65" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="L65" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4358,18 +4465,21 @@
       <c r="M65" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q65" s="17" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B66" t="s">
         <v>27</v>
       </c>
       <c r="C66" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E66" t="s">
         <v>31</v>
       </c>
-      <c r="F66" s="21" t="s">
+      <c r="F66" s="14" t="s">
         <v>110</v>
       </c>
       <c r="G66" t="s">
@@ -4380,11 +4490,11 @@
       </c>
       <c r="I66" s="4">
         <f t="shared" ref="I66:I91" ca="1" si="8">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H66), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H66), 7), "-")</f>
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J66" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="L66" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4392,6 +4502,9 @@
       </c>
       <c r="M66" t="s">
         <v>44</v>
+      </c>
+      <c r="Q66" s="17" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="67" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -4418,11 +4531,11 @@
       </c>
       <c r="I67" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J67" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="L67" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4468,11 +4581,11 @@
       </c>
       <c r="I68" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J68" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="L68" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4518,11 +4631,11 @@
       </c>
       <c r="I69" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J69" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="L69" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4568,11 +4681,11 @@
       </c>
       <c r="I70" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J70" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="L70" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4618,11 +4731,11 @@
       </c>
       <c r="I71" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J71" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="L71" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4668,11 +4781,11 @@
       </c>
       <c r="I72" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J72" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="L72" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4718,11 +4831,11 @@
       </c>
       <c r="I73" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J73" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="L73" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4768,11 +4881,11 @@
       </c>
       <c r="I74" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J74" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="L74" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4818,11 +4931,11 @@
       </c>
       <c r="I75" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J75" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="L75" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4868,11 +4981,11 @@
       </c>
       <c r="I76" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J76" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="L76" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4918,11 +5031,11 @@
       </c>
       <c r="I77" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J77" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="L77" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4968,11 +5081,11 @@
       </c>
       <c r="I78" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J78" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="L78" s="4" t="str">
         <f t="shared" si="4"/>
@@ -5018,11 +5131,11 @@
       </c>
       <c r="I79" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J79" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="L79" s="4" t="str">
         <f t="shared" si="4"/>
@@ -5068,11 +5181,11 @@
       </c>
       <c r="I80" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J80" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="L80" s="4" t="str">
         <f t="shared" si="4"/>
@@ -5118,11 +5231,11 @@
       </c>
       <c r="I81" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J81" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="L81" s="4" t="str">
         <f t="shared" si="4"/>
@@ -5168,11 +5281,11 @@
       </c>
       <c r="I82" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J82" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="L82" s="4" t="str">
         <f t="shared" si="4"/>
@@ -5218,11 +5331,11 @@
       </c>
       <c r="I83" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J83" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="L83" s="4" t="str">
         <f t="shared" si="4"/>
@@ -5268,11 +5381,11 @@
       </c>
       <c r="I84" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J84" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="L84" s="4" t="str">
         <f t="shared" si="4"/>
@@ -5318,11 +5431,11 @@
       </c>
       <c r="I85" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J85" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="L85" s="4" t="str">
         <f t="shared" si="4"/>
@@ -5368,11 +5481,11 @@
       </c>
       <c r="I86" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J86" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="L86" s="4" t="str">
         <f t="shared" si="4"/>
@@ -5399,7 +5512,7 @@
         <v>27</v>
       </c>
       <c r="C87" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D87" t="s">
         <v>28</v>
@@ -5418,11 +5531,11 @@
       </c>
       <c r="I87" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J87" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="K87" s="2">
         <v>45272</v>
@@ -5432,13 +5545,13 @@
         <v>34</v>
       </c>
       <c r="M87" s="4" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="O87" s="2">
         <v>45323</v>
       </c>
       <c r="P87" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="Q87" t="s">
         <v>101</v>
@@ -5449,7 +5562,7 @@
         <v>34</v>
       </c>
       <c r="C88" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D88" t="s">
         <v>30</v>
@@ -5468,11 +5581,11 @@
       </c>
       <c r="I88" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J88" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="K88" s="2">
         <v>45273</v>
@@ -5482,13 +5595,13 @@
         <v>35</v>
       </c>
       <c r="M88" s="4" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="O88" s="2">
         <v>45323</v>
       </c>
       <c r="P88" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="Q88" t="s">
         <v>104</v>
@@ -5499,7 +5612,7 @@
         <v>34</v>
       </c>
       <c r="C89" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D89" t="s">
         <v>29</v>
@@ -5518,11 +5631,11 @@
       </c>
       <c r="I89" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J89" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="K89" s="2">
         <v>45274</v>
@@ -5532,13 +5645,13 @@
         <v>36</v>
       </c>
       <c r="M89" s="4" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="O89" s="2">
         <v>45323</v>
       </c>
       <c r="P89" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="Q89" t="s">
         <v>103</v>
@@ -5549,7 +5662,7 @@
         <v>27</v>
       </c>
       <c r="C90" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D90" t="s">
         <v>28</v>
@@ -5568,11 +5681,11 @@
       </c>
       <c r="I90" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J90" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="K90" s="2">
         <v>45275</v>
@@ -5582,13 +5695,13 @@
         <v>37</v>
       </c>
       <c r="M90" s="4" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="O90" s="2">
         <v>45323</v>
       </c>
       <c r="P90" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="Q90" t="s">
         <v>103</v>
@@ -5599,7 +5712,7 @@
         <v>27</v>
       </c>
       <c r="C91" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D91" t="s">
         <v>30</v>
@@ -5618,11 +5731,11 @@
       </c>
       <c r="I91" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J91" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="K91" s="2">
         <v>45276</v>
@@ -5632,13 +5745,13 @@
         <v>38</v>
       </c>
       <c r="M91" s="4" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="O91" s="2">
         <v>45323</v>
       </c>
       <c r="P91" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="Q91" t="s">
         <v>101</v>
@@ -5649,7 +5762,7 @@
         <v>27</v>
       </c>
       <c r="C92" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D92" t="s">
         <v>29</v>
@@ -5668,11 +5781,11 @@
       </c>
       <c r="I92" s="4">
         <f t="shared" ref="I92:I93" ca="1" si="9">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H92), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H92), 7), "-")</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J92" s="4">
         <f t="shared" ref="J92:J93" ca="1" si="10">IF(_xlfn.DAYS(TODAY(),H92)&lt;10000, _xlfn.DAYS(TODAY(),H92), "-")</f>
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="K92" s="2">
         <v>45277</v>
@@ -5682,13 +5795,13 @@
         <v>39</v>
       </c>
       <c r="M92" s="4" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="O92" s="2">
         <v>45323</v>
       </c>
       <c r="P92" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="Q92" t="s">
         <v>102</v>
@@ -5699,7 +5812,7 @@
         <v>34</v>
       </c>
       <c r="C93" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D93" t="s">
         <v>35</v>
@@ -5718,11 +5831,11 @@
       </c>
       <c r="I93" s="4">
         <f t="shared" ca="1" si="9"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J93" s="4">
         <f t="shared" ca="1" si="10"/>
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="K93" s="2">
         <v>45278</v>
@@ -5732,13 +5845,13 @@
         <v>40</v>
       </c>
       <c r="M93" s="4" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="O93" s="2">
         <v>45323</v>
       </c>
       <c r="P93" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="Q93" t="s">
         <v>104</v>
@@ -5749,7 +5862,7 @@
         <v>34</v>
       </c>
       <c r="C94" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D94">
         <v>615</v>
@@ -5768,11 +5881,11 @@
       </c>
       <c r="I94" s="4">
         <f t="shared" ref="I94" ca="1" si="11">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H94), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H94), 7), "-")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J94" s="4">
         <f t="shared" ref="J94" ca="1" si="12">IF(_xlfn.DAYS(TODAY(),H94)&lt;10000, _xlfn.DAYS(TODAY(),H94), "-")</f>
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="K94" s="2">
         <v>45223</v>
@@ -5799,7 +5912,7 @@
         <v>34</v>
       </c>
       <c r="C95" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D95">
         <v>616</v>
@@ -5818,11 +5931,11 @@
       </c>
       <c r="I95" s="4">
         <f t="shared" ref="I95:I117" ca="1" si="13">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H95), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H95), 7), "-")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J95" s="4">
         <f t="shared" ref="J95:J117" ca="1" si="14">IF(_xlfn.DAYS(TODAY(),H95)&lt;10000, _xlfn.DAYS(TODAY(),H95), "-")</f>
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="K95" s="2">
         <v>45223</v>
@@ -5849,7 +5962,7 @@
         <v>34</v>
       </c>
       <c r="C96" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D96">
         <v>617</v>
@@ -5868,11 +5981,11 @@
       </c>
       <c r="I96" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J96" s="4">
         <f t="shared" ca="1" si="14"/>
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="K96" s="2">
         <v>45223</v>
@@ -5899,7 +6012,7 @@
         <v>34</v>
       </c>
       <c r="C97" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D97">
         <v>618</v>
@@ -5918,11 +6031,11 @@
       </c>
       <c r="I97" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J97" s="4">
         <f t="shared" ca="1" si="14"/>
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="K97" s="2">
         <v>45223</v>
@@ -5968,11 +6081,11 @@
       </c>
       <c r="I98" s="4">
         <f t="shared" ref="I98:I107" ca="1" si="16">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H98), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H98), 7), "-")</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J98" s="4">
         <f t="shared" ref="J98:J107" ca="1" si="17">IF(_xlfn.DAYS(TODAY(),H98)&lt;10000, _xlfn.DAYS(TODAY(),H98), "-")</f>
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="K98" s="2">
         <v>45267</v>
@@ -6021,11 +6134,11 @@
       </c>
       <c r="I99" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J99" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="K99" s="2">
         <v>45267</v>
@@ -6074,11 +6187,11 @@
       </c>
       <c r="I100" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J100" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="K100" s="2">
         <v>45267</v>
@@ -6127,11 +6240,11 @@
       </c>
       <c r="I101" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J101" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="K101" s="2">
         <v>45267</v>
@@ -6180,11 +6293,11 @@
       </c>
       <c r="I102" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J102" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="K102" s="2">
         <v>45267</v>
@@ -6233,11 +6346,11 @@
       </c>
       <c r="I103" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J103" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="K103" s="2">
         <v>45267</v>
@@ -6286,11 +6399,11 @@
       </c>
       <c r="I104" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J104" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="K104" s="2">
         <v>45267</v>
@@ -6339,11 +6452,11 @@
       </c>
       <c r="I105" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J105" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="K105" s="2">
         <v>45267</v>
@@ -6392,11 +6505,11 @@
       </c>
       <c r="I106" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J106" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="K106" s="2">
         <v>45267</v>
@@ -6445,11 +6558,11 @@
       </c>
       <c r="I107" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J107" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="K107" s="2">
         <v>45267</v>
@@ -6778,7 +6891,7 @@
         <v>58</v>
       </c>
       <c r="G115" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="I115" s="4" t="str">
         <f t="shared" ca="1" si="13"/>
@@ -6969,12 +7082,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="120" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="120" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B120" t="s">
         <v>88</v>
       </c>
       <c r="C120" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D120">
         <v>645</v>
@@ -6982,22 +7095,22 @@
       <c r="E120" t="s">
         <v>89</v>
       </c>
-      <c r="F120" s="21" t="s">
-        <v>139</v>
+      <c r="F120" s="14" t="s">
+        <v>136</v>
       </c>
       <c r="G120" s="4" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="H120" s="2">
         <v>45291</v>
       </c>
       <c r="I120" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J120" s="4">
         <f t="shared" ca="1" si="19"/>
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="K120" s="2">
         <v>45315</v>
@@ -7007,15 +7120,15 @@
         <v>24</v>
       </c>
       <c r="M120" s="4" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="121" spans="2:17" x14ac:dyDescent="0.3">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="121" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B121" t="s">
         <v>88</v>
       </c>
       <c r="C121" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D121">
         <v>646</v>
@@ -7027,18 +7140,18 @@
         <v>94</v>
       </c>
       <c r="G121" s="4" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="H121" s="2">
         <v>45291</v>
       </c>
       <c r="I121" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J121" s="4">
         <f t="shared" ca="1" si="19"/>
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="K121" s="2">
         <v>45315</v>
@@ -7048,18 +7161,18 @@
         <v>24</v>
       </c>
       <c r="M121" s="4" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="Q121" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="122" spans="2:17" x14ac:dyDescent="0.3">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="122" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B122" t="s">
         <v>88</v>
       </c>
       <c r="C122" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D122">
         <v>647</v>
@@ -7067,22 +7180,22 @@
       <c r="E122" t="s">
         <v>89</v>
       </c>
-      <c r="F122" s="21" t="s">
-        <v>140</v>
+      <c r="F122" s="14" t="s">
+        <v>137</v>
       </c>
       <c r="G122" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="H122" s="2">
         <v>45291</v>
       </c>
       <c r="I122" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J122" s="4">
         <f t="shared" ca="1" si="19"/>
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="K122" s="2">
         <v>45315</v>
@@ -7092,15 +7205,15 @@
         <v>24</v>
       </c>
       <c r="M122" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="123" spans="2:17" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="123" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B123" t="s">
         <v>88</v>
       </c>
       <c r="C123" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D123">
         <v>648</v>
@@ -7108,22 +7221,22 @@
       <c r="E123" t="s">
         <v>89</v>
       </c>
-      <c r="F123" s="21" t="s">
+      <c r="F123" s="14" t="s">
         <v>92</v>
       </c>
       <c r="G123" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="H123" s="2">
         <v>45291</v>
       </c>
       <c r="I123" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J123" s="4">
         <f t="shared" ca="1" si="19"/>
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="K123" s="2">
         <v>45315</v>
@@ -7133,21 +7246,21 @@
         <v>24</v>
       </c>
       <c r="M123" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="124" spans="2:17" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="124" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B124" t="s">
         <v>113</v>
       </c>
       <c r="C124" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E124" t="s">
         <v>16</v>
       </c>
       <c r="H124" s="2">
-        <v>45304</v>
+        <v>45309</v>
       </c>
       <c r="I124" s="4">
         <f t="shared" ca="1" si="18"/>
@@ -7155,31 +7268,28 @@
       </c>
       <c r="J124" s="4">
         <f t="shared" ca="1" si="19"/>
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="L124" s="4" t="str">
         <f t="shared" si="15"/>
         <v>-</v>
       </c>
       <c r="M124" t="s">
-        <v>114</v>
-      </c>
-      <c r="Q124" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="125" spans="2:17" x14ac:dyDescent="0.3">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="125" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B125" t="s">
         <v>113</v>
       </c>
       <c r="C125" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E125" t="s">
         <v>16</v>
       </c>
       <c r="H125" s="2">
-        <v>45304</v>
+        <v>45309</v>
       </c>
       <c r="I125" s="4">
         <f t="shared" ref="I125:I127" ca="1" si="20">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H125), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H125), 7), "-")</f>
@@ -7187,31 +7297,28 @@
       </c>
       <c r="J125" s="4">
         <f t="shared" ref="J125:J127" ca="1" si="21">IF(_xlfn.DAYS(TODAY(),H125)&lt;10000, _xlfn.DAYS(TODAY(),H125), "-")</f>
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="L125" s="4" t="str">
         <f t="shared" si="15"/>
         <v>-</v>
       </c>
       <c r="M125" t="s">
-        <v>114</v>
-      </c>
-      <c r="Q125" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="126" spans="2:17" x14ac:dyDescent="0.3">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="126" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B126" t="s">
         <v>113</v>
       </c>
       <c r="C126" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E126" t="s">
         <v>16</v>
       </c>
       <c r="H126" s="2">
-        <v>45304</v>
+        <v>45309</v>
       </c>
       <c r="I126" s="4">
         <f t="shared" ca="1" si="20"/>
@@ -7219,31 +7326,28 @@
       </c>
       <c r="J126" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="L126" s="4" t="str">
         <f t="shared" si="15"/>
         <v>-</v>
       </c>
       <c r="M126" t="s">
-        <v>114</v>
-      </c>
-      <c r="Q126" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="127" spans="2:17" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="127" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B127" t="s">
         <v>113</v>
       </c>
       <c r="C127" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E127" t="s">
         <v>16</v>
       </c>
       <c r="H127" s="2">
-        <v>45304</v>
+        <v>45309</v>
       </c>
       <c r="I127" s="4">
         <f t="shared" ca="1" si="20"/>
@@ -7251,25 +7355,22 @@
       </c>
       <c r="J127" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="L127" s="4" t="str">
         <f t="shared" si="15"/>
         <v>-</v>
       </c>
       <c r="M127" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="128" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B128" t="s">
         <v>114</v>
       </c>
-      <c r="Q127" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="128" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B128" t="s">
-        <v>115</v>
-      </c>
       <c r="C128" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E128" t="s">
         <v>16</v>
@@ -7279,29 +7380,26 @@
       </c>
       <c r="I128" s="4">
         <f t="shared" ref="I128:I130" ca="1" si="22">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H128), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H128), 7), "-")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J128" s="4">
         <f t="shared" ref="J128:J130" ca="1" si="23">IF(_xlfn.DAYS(TODAY(),H128)&lt;10000, _xlfn.DAYS(TODAY(),H128), "-")</f>
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="L128" s="4" t="str">
         <f t="shared" si="15"/>
         <v>-</v>
       </c>
-      <c r="M128" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q128" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="129" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="M128" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="129" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B129" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C129" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E129" t="s">
         <v>16</v>
@@ -7311,29 +7409,26 @@
       </c>
       <c r="I129" s="4">
         <f t="shared" ca="1" si="22"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J129" s="4">
         <f t="shared" ca="1" si="23"/>
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="L129" s="4" t="str">
         <f t="shared" si="15"/>
         <v>-</v>
       </c>
-      <c r="M129" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q129" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="130" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="M129" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="130" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B130" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C130" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E130" t="s">
         <v>16</v>
@@ -7343,35 +7438,32 @@
       </c>
       <c r="I130" s="4">
         <f t="shared" ca="1" si="22"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J130" s="4">
         <f t="shared" ca="1" si="23"/>
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="L130" s="4" t="str">
         <f t="shared" si="15"/>
         <v>-</v>
       </c>
-      <c r="M130" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q130" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="131" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="M130" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="131" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B131" t="s">
         <v>5</v>
       </c>
       <c r="C131" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="F131" s="10" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="G131" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="I131" s="4" t="str">
         <f t="shared" ref="I131:I146" ca="1" si="24">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H131), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H131), 7), "-")</f>
@@ -7386,219 +7478,219 @@
         <v>-</v>
       </c>
       <c r="M131" s="4" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="132" spans="2:17" x14ac:dyDescent="0.3">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="132" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B132" t="s">
         <v>5</v>
       </c>
       <c r="C132" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="F132" s="10" t="s">
         <v>91</v>
       </c>
       <c r="G132" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="H132" s="2">
         <v>45155</v>
       </c>
       <c r="I132" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J132" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="L132" s="4" t="str">
         <f t="shared" si="26"/>
         <v>-</v>
       </c>
       <c r="M132" s="4" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="Q132" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="133" spans="2:17" x14ac:dyDescent="0.3">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="133" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B133" t="s">
         <v>5</v>
       </c>
       <c r="C133" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="F133" s="10" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="G133" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="H133" s="2">
         <v>44885</v>
       </c>
       <c r="I133" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J133" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="L133" s="4" t="str">
         <f t="shared" si="26"/>
         <v>-</v>
       </c>
       <c r="M133" s="4" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="134" spans="2:17" x14ac:dyDescent="0.3">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="134" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B134" t="s">
         <v>5</v>
       </c>
       <c r="C134" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="F134" s="10" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="G134" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="H134" s="2">
         <v>44885</v>
       </c>
       <c r="I134" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J134" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="L134" s="4" t="str">
         <f t="shared" si="26"/>
         <v>-</v>
       </c>
       <c r="M134" s="4" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="135" spans="2:17" x14ac:dyDescent="0.3">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="135" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B135" t="s">
         <v>5</v>
       </c>
       <c r="C135" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="F135" s="10" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="G135" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="H135" s="2">
         <v>45155</v>
       </c>
       <c r="I135" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J135" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="L135" s="4" t="str">
         <f t="shared" si="26"/>
         <v>-</v>
       </c>
       <c r="M135" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q135" t="s">
         <v>130</v>
       </c>
-      <c r="Q135" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="136" spans="2:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="136" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B136" t="s">
         <v>5</v>
       </c>
       <c r="C136" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="F136" s="10" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="G136" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="H136" s="2">
         <v>44885</v>
       </c>
       <c r="I136" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J136" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="L136" s="4" t="str">
         <f t="shared" si="26"/>
         <v>-</v>
       </c>
       <c r="M136" s="4" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="137" spans="2:17" x14ac:dyDescent="0.3">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="137" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B137" t="s">
         <v>5</v>
       </c>
       <c r="C137" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="F137" s="10" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="G137" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="H137" s="2">
         <v>44885</v>
       </c>
       <c r="I137" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J137" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="L137" s="4" t="str">
         <f t="shared" si="26"/>
         <v>-</v>
       </c>
       <c r="M137" s="4" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="138" spans="2:17" x14ac:dyDescent="0.3">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="138" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B138" t="s">
+        <v>141</v>
+      </c>
+      <c r="C138" t="s">
+        <v>142</v>
+      </c>
+      <c r="F138" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="G138" t="s">
         <v>144</v>
-      </c>
-      <c r="C138" t="s">
-        <v>145</v>
-      </c>
-      <c r="F138" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="G138" t="s">
-        <v>147</v>
       </c>
       <c r="I138" s="4" t="str">
         <f t="shared" ca="1" si="24"/>
@@ -7613,21 +7705,21 @@
         <v>-</v>
       </c>
       <c r="M138" s="4" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
     </row>
     <row r="139" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B139" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C139" t="s">
+        <v>142</v>
+      </c>
+      <c r="F139" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="G139" t="s">
         <v>145</v>
-      </c>
-      <c r="F139" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="G139" t="s">
-        <v>148</v>
       </c>
       <c r="I139" s="4" t="str">
         <f t="shared" ca="1" si="24"/>
@@ -7641,25 +7733,25 @@
         <f t="shared" si="26"/>
         <v>-</v>
       </c>
-      <c r="M139" s="22" t="s">
-        <v>146</v>
+      <c r="M139" s="15" t="s">
+        <v>143</v>
       </c>
       <c r="O139" s="2">
         <v>45322</v>
       </c>
     </row>
-    <row r="140" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="140" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B140" t="s">
+        <v>141</v>
+      </c>
+      <c r="C140" t="s">
+        <v>142</v>
+      </c>
+      <c r="F140" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="G140" t="s">
         <v>144</v>
-      </c>
-      <c r="C140" t="s">
-        <v>145</v>
-      </c>
-      <c r="F140" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="G140" t="s">
-        <v>147</v>
       </c>
       <c r="I140" s="4" t="str">
         <f t="shared" ca="1" si="24"/>
@@ -7674,213 +7766,213 @@
         <v>-</v>
       </c>
       <c r="M140" s="4" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="141" spans="2:17" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="141" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B141" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C141" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="H141" s="2">
         <v>45301</v>
       </c>
       <c r="I141" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J141" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="L141" s="4" t="str">
         <f t="shared" si="26"/>
         <v>-</v>
       </c>
       <c r="M141" s="4" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="Q141" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="142" spans="2:17" x14ac:dyDescent="0.3">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="142" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B142" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C142" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E142" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="H142" s="2">
         <v>45301</v>
       </c>
       <c r="I142" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J142" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="L142" s="4" t="str">
         <f t="shared" si="26"/>
         <v>-</v>
       </c>
       <c r="M142" s="4" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="Q142" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="143" spans="2:17" x14ac:dyDescent="0.3">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="143" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B143" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C143" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E143" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="H143" s="2">
         <v>45301</v>
       </c>
       <c r="I143" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J143" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="L143" s="4" t="str">
         <f t="shared" si="26"/>
         <v>-</v>
       </c>
       <c r="M143" s="4" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="Q143" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="144" spans="2:17" x14ac:dyDescent="0.3">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="144" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B144" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C144" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="H144" s="2">
         <v>45301</v>
       </c>
       <c r="I144" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J144" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="L144" s="4" t="str">
         <f t="shared" si="26"/>
         <v>-</v>
       </c>
       <c r="M144" s="4" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="Q144" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="145" spans="2:17" x14ac:dyDescent="0.3">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="145" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B145" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C145" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E145" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="H145" s="2">
         <v>45301</v>
       </c>
       <c r="I145" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J145" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="L145" s="4" t="str">
         <f t="shared" si="26"/>
         <v>-</v>
       </c>
       <c r="M145" s="4" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="Q145" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="146" spans="2:17" x14ac:dyDescent="0.3">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="146" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B146" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C146" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E146" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="H146" s="2">
         <v>45301</v>
       </c>
       <c r="I146" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J146" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="L146" s="4" t="str">
         <f t="shared" si="26"/>
         <v>-</v>
       </c>
       <c r="M146" s="4" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="Q146" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="147" spans="2:17" x14ac:dyDescent="0.3">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="147" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B147" t="s">
+        <v>141</v>
+      </c>
+      <c r="C147" t="s">
+        <v>142</v>
+      </c>
+      <c r="F147" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="G147" t="s">
         <v>144</v>
-      </c>
-      <c r="C147" t="s">
-        <v>145</v>
-      </c>
-      <c r="F147" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="G147" t="s">
-        <v>147</v>
       </c>
       <c r="I147" s="4" t="str">
         <f t="shared" ref="I147:I176" ca="1" si="27">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H147), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H147), 7), "-")</f>
@@ -7895,21 +7987,21 @@
         <v>-</v>
       </c>
       <c r="M147" s="4" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="148" spans="2:17" x14ac:dyDescent="0.3">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="148" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B148" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C148" t="s">
+        <v>142</v>
+      </c>
+      <c r="F148" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="G148" t="s">
         <v>145</v>
-      </c>
-      <c r="F148" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="G148" t="s">
-        <v>148</v>
       </c>
       <c r="I148" s="4" t="str">
         <f t="shared" ca="1" si="27"/>
@@ -7924,21 +8016,21 @@
         <v>-</v>
       </c>
       <c r="M148" s="4" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="149" spans="2:17" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="149" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B149" t="s">
+        <v>141</v>
+      </c>
+      <c r="C149" t="s">
+        <v>142</v>
+      </c>
+      <c r="F149" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="G149" t="s">
         <v>144</v>
-      </c>
-      <c r="C149" t="s">
-        <v>145</v>
-      </c>
-      <c r="F149" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="G149" t="s">
-        <v>147</v>
       </c>
       <c r="I149" s="4" t="str">
         <f t="shared" ca="1" si="27"/>
@@ -7953,21 +8045,21 @@
         <v>-</v>
       </c>
       <c r="M149" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="150" spans="2:17" x14ac:dyDescent="0.3">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="150" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B150" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C150" t="s">
+        <v>142</v>
+      </c>
+      <c r="F150" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="G150" t="s">
         <v>145</v>
-      </c>
-      <c r="F150" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="G150" t="s">
-        <v>148</v>
       </c>
       <c r="I150" s="4" t="str">
         <f t="shared" ca="1" si="27"/>
@@ -7982,181 +8074,181 @@
         <v>-</v>
       </c>
       <c r="M150" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="151" spans="2:17" x14ac:dyDescent="0.3">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="151" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B151" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C151" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="H151" s="2">
         <v>45307</v>
       </c>
       <c r="I151" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J151" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="L151" s="4" t="str">
         <f t="shared" si="29"/>
         <v>-</v>
       </c>
       <c r="M151" s="4" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="152" spans="2:17" x14ac:dyDescent="0.3">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="152" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B152" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C152" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E152" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="H152" s="2">
         <v>45307</v>
       </c>
       <c r="I152" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J152" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="L152" s="4" t="str">
         <f t="shared" si="29"/>
         <v>-</v>
       </c>
       <c r="M152" s="4" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="153" spans="2:17" x14ac:dyDescent="0.3">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="153" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B153" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C153" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E153" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="H153" s="2">
         <v>45307</v>
       </c>
       <c r="I153" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J153" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="L153" s="4" t="str">
         <f t="shared" si="29"/>
         <v>-</v>
       </c>
       <c r="M153" s="4" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="154" spans="2:17" x14ac:dyDescent="0.3">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="154" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B154" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C154" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="H154" s="2">
         <v>45307</v>
       </c>
       <c r="I154" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J154" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="L154" s="4" t="str">
         <f t="shared" si="29"/>
         <v>-</v>
       </c>
       <c r="M154" s="4" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="155" spans="2:17" x14ac:dyDescent="0.3">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="155" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B155" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C155" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E155" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="H155" s="2">
         <v>45307</v>
       </c>
       <c r="I155" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J155" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="L155" s="4" t="str">
         <f t="shared" si="29"/>
         <v>-</v>
       </c>
       <c r="M155" s="4" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="156" spans="2:17" x14ac:dyDescent="0.3">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="156" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B156" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C156" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E156" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="H156" s="2">
         <v>45307</v>
       </c>
       <c r="I156" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J156" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="L156" s="4" t="str">
         <f t="shared" si="29"/>
         <v>-</v>
       </c>
       <c r="M156" s="4" t="s">
-        <v>154</v>
+        <v>222</v>
       </c>
     </row>
     <row r="157" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -8164,7 +8256,7 @@
         <v>34</v>
       </c>
       <c r="C157" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D157">
         <v>710</v>
@@ -8173,54 +8265,54 @@
         <v>8</v>
       </c>
       <c r="F157" s="5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="G157" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="H157" s="2">
         <v>45189</v>
       </c>
       <c r="I157" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J157" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="L157" s="4" t="str">
         <f t="shared" si="29"/>
         <v>-</v>
       </c>
       <c r="M157" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="N157" s="2">
         <v>45322</v>
       </c>
       <c r="P157" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="Q157" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="158" spans="2:17" x14ac:dyDescent="0.3">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="158" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B158" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C158" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D158">
         <v>708</v>
       </c>
       <c r="F158" s="5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="G158" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I158" s="4" t="str">
         <f t="shared" ca="1" si="27"/>
@@ -8235,24 +8327,27 @@
         <v>-</v>
       </c>
       <c r="M158" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="159" spans="2:17" x14ac:dyDescent="0.3">
+        <v>151</v>
+      </c>
+      <c r="O158" s="2">
+        <v>45329</v>
+      </c>
+    </row>
+    <row r="159" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B159" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C159" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D159">
         <v>767</v>
       </c>
       <c r="F159" s="5" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="G159" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="I159" s="4" t="str">
         <f t="shared" ca="1" si="27"/>
@@ -8267,24 +8362,24 @@
         <v>-</v>
       </c>
       <c r="M159" s="4" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="160" spans="2:17" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="160" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B160" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C160" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D160">
         <v>769</v>
       </c>
       <c r="F160" s="5" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="G160" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="I160" s="4" t="str">
         <f t="shared" ca="1" si="27"/>
@@ -8299,15 +8394,15 @@
         <v>-</v>
       </c>
       <c r="M160" s="4" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="161" spans="2:17" x14ac:dyDescent="0.3">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="161" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B161" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C161" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D161">
         <v>606</v>
@@ -8316,21 +8411,21 @@
         <v>8</v>
       </c>
       <c r="F161" s="5" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="G161" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H161" s="2">
         <v>45269</v>
       </c>
       <c r="I161" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J161" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="K161" s="2">
         <v>45301</v>
@@ -8340,15 +8435,15 @@
         <v>32</v>
       </c>
       <c r="M161" s="4" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="162" spans="2:17" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="162" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B162" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C162" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D162">
         <v>607</v>
@@ -8357,21 +8452,21 @@
         <v>8</v>
       </c>
       <c r="F162" s="5" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="G162" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H162" s="2">
         <v>45269</v>
       </c>
       <c r="I162" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J162" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="K162" s="2">
         <v>45301</v>
@@ -8381,35 +8476,35 @@
         <v>32</v>
       </c>
       <c r="M162" s="4" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
     </row>
     <row r="163" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B163" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C163" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D163">
         <v>608</v>
       </c>
       <c r="E163" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="G163" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H163" s="2">
         <v>45269</v>
       </c>
       <c r="I163" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J163" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="K163" s="2">
         <v>45301</v>
@@ -8419,21 +8514,21 @@
         <v>32</v>
       </c>
       <c r="M163" s="4" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="O163" s="2">
         <v>45321</v>
       </c>
       <c r="Q163" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="164" spans="2:17" x14ac:dyDescent="0.3">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="164" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B164" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C164" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D164">
         <v>609</v>
@@ -8442,21 +8537,21 @@
         <v>8</v>
       </c>
       <c r="F164" s="5" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="G164" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H164" s="2">
         <v>45269</v>
       </c>
       <c r="I164" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J164" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="K164" s="2">
         <v>45301</v>
@@ -8466,7 +8561,7 @@
         <v>32</v>
       </c>
       <c r="M164" s="4" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
     </row>
     <row r="165" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -8474,7 +8569,7 @@
         <v>34</v>
       </c>
       <c r="C165" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D165">
         <v>610</v>
@@ -8483,21 +8578,21 @@
         <v>8</v>
       </c>
       <c r="F165" s="5" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="G165" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H165" s="2">
         <v>45269</v>
       </c>
       <c r="I165" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J165" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="K165" s="2">
         <v>45301</v>
@@ -8507,24 +8602,24 @@
         <v>32</v>
       </c>
       <c r="M165" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="N165" s="2">
         <v>45322</v>
       </c>
       <c r="P165" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="Q165" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="166" spans="2:17" x14ac:dyDescent="0.3">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="166" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B166" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C166" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D166">
         <v>611</v>
@@ -8533,21 +8628,21 @@
         <v>8</v>
       </c>
       <c r="F166" s="5" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="G166" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H166" s="2">
         <v>45269</v>
       </c>
       <c r="I166" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J166" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="K166" s="2">
         <v>45301</v>
@@ -8557,10 +8652,10 @@
         <v>32</v>
       </c>
       <c r="M166" s="4" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="Q166" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
     </row>
     <row r="167" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -8568,40 +8663,40 @@
         <v>34</v>
       </c>
       <c r="C167" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D167">
         <v>708</v>
       </c>
       <c r="F167" s="5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="G167" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="H167" s="2">
         <v>45189</v>
       </c>
       <c r="I167" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J167" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="L167" s="4" t="str">
         <f t="shared" si="29"/>
         <v>-</v>
       </c>
       <c r="M167" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="N167" s="2">
         <v>45322</v>
       </c>
       <c r="P167" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
     </row>
     <row r="168" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -8609,40 +8704,40 @@
         <v>34</v>
       </c>
       <c r="C168" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D168">
         <v>709</v>
       </c>
       <c r="F168" s="5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="G168" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="H168" s="2">
         <v>45189</v>
       </c>
       <c r="I168" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J168" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="L168" s="4" t="str">
         <f t="shared" si="29"/>
         <v>-</v>
       </c>
       <c r="M168" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="N168" s="2">
         <v>45322</v>
       </c>
       <c r="P168" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
     </row>
     <row r="169" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -8650,40 +8745,40 @@
         <v>34</v>
       </c>
       <c r="C169" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D169">
         <v>711</v>
       </c>
       <c r="F169" s="5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="G169" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="H169" s="2">
         <v>45189</v>
       </c>
       <c r="I169" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J169" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="L169" s="4" t="str">
         <f t="shared" si="29"/>
         <v>-</v>
       </c>
       <c r="M169" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="N169" s="2">
         <v>45322</v>
       </c>
       <c r="P169" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
     </row>
     <row r="170" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -8691,7 +8786,7 @@
         <v>34</v>
       </c>
       <c r="C170" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D170">
         <v>601</v>
@@ -8700,21 +8795,21 @@
         <v>8</v>
       </c>
       <c r="F170" s="5" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="G170" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H170" s="2">
         <v>45269</v>
       </c>
       <c r="I170" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J170" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="K170" s="2">
         <v>45301</v>
@@ -8724,24 +8819,24 @@
         <v>32</v>
       </c>
       <c r="M170" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="N170" s="2">
         <v>45322</v>
       </c>
       <c r="P170" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="Q170" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="171" spans="2:17" x14ac:dyDescent="0.3">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="171" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B171" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C171" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D171">
         <v>602</v>
@@ -8750,21 +8845,21 @@
         <v>8</v>
       </c>
       <c r="F171" s="5" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="G171" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H171" s="2">
         <v>45269</v>
       </c>
       <c r="I171" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J171" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="K171" s="2">
         <v>45301</v>
@@ -8774,7 +8869,7 @@
         <v>32</v>
       </c>
       <c r="M171" s="4" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
     </row>
     <row r="172" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -8782,7 +8877,7 @@
         <v>34</v>
       </c>
       <c r="C172" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D172">
         <v>603</v>
@@ -8791,21 +8886,21 @@
         <v>8</v>
       </c>
       <c r="F172" s="5" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="G172" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="H172" s="2">
         <v>45269</v>
       </c>
       <c r="I172" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J172" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="K172" s="2">
         <v>45301</v>
@@ -8815,13 +8910,13 @@
         <v>32</v>
       </c>
       <c r="M172" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="N172" s="2">
         <v>45322</v>
       </c>
       <c r="P172" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
     </row>
     <row r="173" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -8829,7 +8924,7 @@
         <v>34</v>
       </c>
       <c r="C173" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D173">
         <v>604</v>
@@ -8838,21 +8933,21 @@
         <v>8</v>
       </c>
       <c r="F173" s="5" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="G173" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="H173" s="2">
         <v>45269</v>
       </c>
       <c r="I173" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J173" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="K173" s="2">
         <v>45301</v>
@@ -8862,13 +8957,13 @@
         <v>32</v>
       </c>
       <c r="M173" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="N173" s="2">
         <v>45322</v>
       </c>
       <c r="P173" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
     </row>
     <row r="174" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -8876,7 +8971,7 @@
         <v>34</v>
       </c>
       <c r="C174" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D174">
         <v>605</v>
@@ -8885,21 +8980,21 @@
         <v>8</v>
       </c>
       <c r="F174" s="5" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="G174" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="H174" s="2">
         <v>45269</v>
       </c>
       <c r="I174" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J174" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="K174" s="2">
         <v>45301</v>
@@ -8909,21 +9004,21 @@
         <v>32</v>
       </c>
       <c r="M174" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="N174" s="2">
         <v>45322</v>
       </c>
       <c r="P174" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="175" spans="2:17" x14ac:dyDescent="0.3">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="175" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B175" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C175" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D175">
         <v>649</v>
@@ -8932,28 +9027,28 @@
         <v>8</v>
       </c>
       <c r="F175" s="5" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="G175" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="H175" s="2">
         <v>45269</v>
       </c>
       <c r="I175" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J175" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="L175" s="4" t="str">
         <f t="shared" si="29"/>
         <v>-</v>
       </c>
       <c r="M175" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
     </row>
     <row r="176" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -8961,7 +9056,7 @@
         <v>34</v>
       </c>
       <c r="C176" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D176">
         <v>650</v>
@@ -8970,64 +9065,64 @@
         <v>8</v>
       </c>
       <c r="F176" s="5" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="G176" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="H176" s="2">
         <v>45269</v>
       </c>
       <c r="I176" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J176" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="L176" s="4" t="str">
         <f t="shared" si="29"/>
         <v>-</v>
       </c>
       <c r="M176" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="N176" s="2">
         <v>45322</v>
       </c>
       <c r="P176" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="Q176" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="177" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="177" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B177" t="s">
         <v>34</v>
       </c>
       <c r="C177" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E177" t="s">
         <v>16</v>
       </c>
       <c r="G177" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="H177" s="2">
         <v>45300</v>
       </c>
       <c r="I177" s="4">
         <f t="shared" ref="I177" ca="1" si="30">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H177), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H177), 7), "-")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J177" s="4">
         <f t="shared" ref="J177" ca="1" si="31">IF(_xlfn.DAYS(TODAY(),H177)&lt;10000, _xlfn.DAYS(TODAY(),H177), "-")</f>
-        <v>28</v>
-      </c>
-      <c r="K177" s="23">
+        <v>36</v>
+      </c>
+      <c r="K177" s="16">
         <v>45324</v>
       </c>
       <c r="L177" s="4">
@@ -9035,34 +9130,34 @@
         <v>24</v>
       </c>
       <c r="M177" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="178" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="178" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B178" t="s">
         <v>34</v>
       </c>
       <c r="C178" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E178" t="s">
         <v>16</v>
       </c>
       <c r="G178" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="H178" s="2">
         <v>45300</v>
       </c>
       <c r="I178" s="4">
         <f t="shared" ref="I178:I187" ca="1" si="33">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H178), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H178), 7), "-")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J178" s="4">
         <f t="shared" ref="J178:J187" ca="1" si="34">IF(_xlfn.DAYS(TODAY(),H178)&lt;10000, _xlfn.DAYS(TODAY(),H178), "-")</f>
-        <v>28</v>
-      </c>
-      <c r="K178" s="23">
+        <v>36</v>
+      </c>
+      <c r="K178" s="16">
         <v>45324</v>
       </c>
       <c r="L178" s="4">
@@ -9070,34 +9165,34 @@
         <v>24</v>
       </c>
       <c r="M178" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="179" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="179" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B179" t="s">
         <v>34</v>
       </c>
       <c r="C179" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E179" t="s">
         <v>16</v>
       </c>
       <c r="G179" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="H179" s="2">
         <v>45300</v>
       </c>
       <c r="I179" s="4">
         <f t="shared" ca="1" si="33"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J179" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>28</v>
-      </c>
-      <c r="K179" s="23">
+        <v>36</v>
+      </c>
+      <c r="K179" s="16">
         <v>45324</v>
       </c>
       <c r="L179" s="4">
@@ -9105,34 +9200,34 @@
         <v>24</v>
       </c>
       <c r="M179" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="180" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="180" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B180" t="s">
         <v>34</v>
       </c>
       <c r="C180" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E180" t="s">
         <v>16</v>
       </c>
       <c r="G180" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="H180" s="2">
         <v>45300</v>
       </c>
       <c r="I180" s="4">
         <f t="shared" ca="1" si="33"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J180" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>28</v>
-      </c>
-      <c r="K180" s="23">
+        <v>36</v>
+      </c>
+      <c r="K180" s="16">
         <v>45324</v>
       </c>
       <c r="L180" s="4">
@@ -9140,34 +9235,34 @@
         <v>24</v>
       </c>
       <c r="M180" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="181" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="181" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B181" t="s">
         <v>34</v>
       </c>
       <c r="C181" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E181" t="s">
         <v>16</v>
       </c>
       <c r="G181" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="H181" s="2">
         <v>45300</v>
       </c>
       <c r="I181" s="4">
         <f t="shared" ca="1" si="33"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J181" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>28</v>
-      </c>
-      <c r="K181" s="23">
+        <v>36</v>
+      </c>
+      <c r="K181" s="16">
         <v>45324</v>
       </c>
       <c r="L181" s="4">
@@ -9175,34 +9270,34 @@
         <v>24</v>
       </c>
       <c r="M181" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="182" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="182" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B182" t="s">
         <v>34</v>
       </c>
       <c r="C182" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E182" t="s">
         <v>16</v>
       </c>
       <c r="G182" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="H182" s="2">
         <v>45300</v>
       </c>
       <c r="I182" s="4">
         <f t="shared" ca="1" si="33"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J182" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>28</v>
-      </c>
-      <c r="K182" s="23">
+        <v>36</v>
+      </c>
+      <c r="K182" s="16">
         <v>45324</v>
       </c>
       <c r="L182" s="4">
@@ -9210,34 +9305,34 @@
         <v>24</v>
       </c>
       <c r="M182" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="183" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="183" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B183" t="s">
         <v>34</v>
       </c>
       <c r="C183" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E183" t="s">
         <v>16</v>
       </c>
       <c r="G183" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="H183" s="2">
         <v>45300</v>
       </c>
       <c r="I183" s="4">
         <f t="shared" ca="1" si="33"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J183" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>28</v>
-      </c>
-      <c r="K183" s="23">
+        <v>36</v>
+      </c>
+      <c r="K183" s="16">
         <v>45324</v>
       </c>
       <c r="L183" s="4">
@@ -9245,34 +9340,34 @@
         <v>24</v>
       </c>
       <c r="M183" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="184" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="184" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B184" t="s">
         <v>34</v>
       </c>
       <c r="C184" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E184" t="s">
         <v>16</v>
       </c>
       <c r="G184" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="H184" s="2">
         <v>45300</v>
       </c>
       <c r="I184" s="4">
         <f t="shared" ca="1" si="33"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J184" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>28</v>
-      </c>
-      <c r="K184" s="23">
+        <v>36</v>
+      </c>
+      <c r="K184" s="16">
         <v>45324</v>
       </c>
       <c r="L184" s="4">
@@ -9280,34 +9375,34 @@
         <v>24</v>
       </c>
       <c r="M184" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="185" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="185" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B185" t="s">
         <v>34</v>
       </c>
       <c r="C185" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E185" t="s">
         <v>16</v>
       </c>
       <c r="G185" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="H185" s="2">
         <v>45300</v>
       </c>
       <c r="I185" s="4">
         <f t="shared" ca="1" si="33"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J185" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>28</v>
-      </c>
-      <c r="K185" s="23">
+        <v>36</v>
+      </c>
+      <c r="K185" s="16">
         <v>45324</v>
       </c>
       <c r="L185" s="4">
@@ -9315,37 +9410,37 @@
         <v>24</v>
       </c>
       <c r="M185" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="186" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="186" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B186" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="C186" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="H186" s="2">
         <v>45324</v>
       </c>
       <c r="I186" s="4">
         <f t="shared" ca="1" si="33"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J186" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="M186" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="187" spans="2:13" x14ac:dyDescent="0.3">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="187" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B187" t="s">
         <v>5</v>
       </c>
       <c r="C187" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E187" t="s">
         <v>16</v>
@@ -9355,26 +9450,26 @@
       </c>
       <c r="I187" s="4">
         <f t="shared" ca="1" si="33"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J187" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L187" s="4" t="str">
         <f t="shared" ref="L187" si="36">IF(_xlfn.DAYS(K187,H187)&gt;0, _xlfn.DAYS(K187,H187), "-")</f>
         <v>-</v>
       </c>
       <c r="M187" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="188" spans="2:13" x14ac:dyDescent="0.3">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="188" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B188" t="s">
         <v>5</v>
       </c>
       <c r="C188" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E188" t="s">
         <v>16</v>
@@ -9383,27 +9478,27 @@
         <v>45327</v>
       </c>
       <c r="I188" s="4">
-        <f t="shared" ref="I188:I195" ca="1" si="37">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H188), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H188), 7), "-")</f>
-        <v>0</v>
+        <f t="shared" ref="I188:I194" ca="1" si="37">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H188), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H188), 7), "-")</f>
+        <v>1</v>
       </c>
       <c r="J188" s="4">
-        <f t="shared" ref="J188:J195" ca="1" si="38">IF(_xlfn.DAYS(TODAY(),H188)&lt;10000, _xlfn.DAYS(TODAY(),H188), "-")</f>
-        <v>1</v>
+        <f t="shared" ref="J188:J194" ca="1" si="38">IF(_xlfn.DAYS(TODAY(),H188)&lt;10000, _xlfn.DAYS(TODAY(),H188), "-")</f>
+        <v>9</v>
       </c>
       <c r="L188" s="4" t="str">
-        <f t="shared" ref="L188:L195" si="39">IF(_xlfn.DAYS(K188,H188)&gt;0, _xlfn.DAYS(K188,H188), "-")</f>
+        <f t="shared" ref="L188:L194" si="39">IF(_xlfn.DAYS(K188,H188)&gt;0, _xlfn.DAYS(K188,H188), "-")</f>
         <v>-</v>
       </c>
       <c r="M188" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="189" spans="2:13" x14ac:dyDescent="0.3">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="189" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B189" t="s">
         <v>5</v>
       </c>
       <c r="C189" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E189" s="2" t="s">
         <v>16</v>
@@ -9413,26 +9508,26 @@
       </c>
       <c r="I189" s="4">
         <f t="shared" ca="1" si="37"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J189" s="4">
         <f t="shared" ca="1" si="38"/>
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L189" s="4" t="str">
         <f t="shared" si="39"/>
         <v>-</v>
       </c>
       <c r="M189" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="190" spans="2:13" x14ac:dyDescent="0.3">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="190" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B190" t="s">
         <v>5</v>
       </c>
       <c r="C190" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E190" t="s">
         <v>16</v>
@@ -9442,26 +9537,26 @@
       </c>
       <c r="I190" s="4">
         <f t="shared" ca="1" si="37"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J190" s="4">
         <f t="shared" ca="1" si="38"/>
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L190" s="4" t="str">
         <f t="shared" si="39"/>
         <v>-</v>
       </c>
       <c r="M190" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="191" spans="2:13" x14ac:dyDescent="0.3">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="191" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B191" t="s">
         <v>5</v>
       </c>
       <c r="C191" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E191" t="s">
         <v>16</v>
@@ -9471,26 +9566,26 @@
       </c>
       <c r="I191" s="4">
         <f t="shared" ca="1" si="37"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J191" s="4">
         <f t="shared" ca="1" si="38"/>
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L191" s="4" t="str">
         <f t="shared" si="39"/>
         <v>-</v>
       </c>
       <c r="M191" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="192" spans="2:13" x14ac:dyDescent="0.3">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="192" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B192" t="s">
         <v>5</v>
       </c>
       <c r="C192" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E192" t="s">
         <v>16</v>
@@ -9500,26 +9595,26 @@
       </c>
       <c r="I192" s="4">
         <f t="shared" ca="1" si="37"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J192" s="4">
         <f t="shared" ca="1" si="38"/>
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L192" s="4" t="str">
         <f t="shared" si="39"/>
         <v>-</v>
       </c>
       <c r="M192" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="193" spans="2:17" x14ac:dyDescent="0.3">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="193" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B193" t="s">
         <v>5</v>
       </c>
       <c r="C193" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E193" t="s">
         <v>16</v>
@@ -9529,26 +9624,26 @@
       </c>
       <c r="I193" s="4">
         <f t="shared" ca="1" si="37"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J193" s="4">
         <f t="shared" ca="1" si="38"/>
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L193" s="4" t="str">
         <f t="shared" si="39"/>
         <v>-</v>
       </c>
       <c r="M193" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="194" spans="2:17" x14ac:dyDescent="0.3">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="194" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B194" t="s">
         <v>5</v>
       </c>
       <c r="C194" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E194" t="s">
         <v>16</v>
@@ -9558,198 +9653,174 @@
       </c>
       <c r="I194" s="4">
         <f t="shared" ca="1" si="37"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J194" s="4">
         <f t="shared" ca="1" si="38"/>
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L194" s="4" t="str">
         <f t="shared" si="39"/>
         <v>-</v>
       </c>
       <c r="M194" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="195" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B195" t="s">
+        <v>190</v>
+      </c>
+      <c r="C195" t="s">
+        <v>124</v>
+      </c>
+      <c r="D195">
+        <v>639</v>
+      </c>
+      <c r="E195" t="s">
+        <v>199</v>
+      </c>
+      <c r="F195" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="G195" t="s">
+        <v>198</v>
+      </c>
+      <c r="M195" s="4" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="196" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B196" t="s">
+        <v>190</v>
+      </c>
+      <c r="C196" t="s">
+        <v>124</v>
+      </c>
+      <c r="D196">
+        <v>640</v>
+      </c>
+      <c r="E196" t="s">
+        <v>199</v>
+      </c>
+      <c r="F196" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="G196" t="s">
+        <v>198</v>
+      </c>
+      <c r="M196" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q196" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="197" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B197" t="s">
+        <v>190</v>
+      </c>
+      <c r="C197" t="s">
+        <v>124</v>
+      </c>
+      <c r="D197">
+        <v>641</v>
+      </c>
+      <c r="E197" t="s">
+        <v>199</v>
+      </c>
+      <c r="F197" s="5" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="195" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B195" t="s">
-        <v>5</v>
-      </c>
-      <c r="C195" t="s">
-        <v>127</v>
-      </c>
-      <c r="H195" s="2">
-        <v>45327</v>
-      </c>
-      <c r="I195" s="4">
-        <f t="shared" ca="1" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="J195" s="4">
-        <f t="shared" ca="1" si="38"/>
-        <v>1</v>
-      </c>
-      <c r="L195" s="4" t="str">
-        <f t="shared" si="39"/>
-        <v>-</v>
-      </c>
-      <c r="M195" s="4" t="s">
+      <c r="G197" t="s">
+        <v>198</v>
+      </c>
+      <c r="M197" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="198" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B198" t="s">
+        <v>190</v>
+      </c>
+      <c r="C198" t="s">
+        <v>124</v>
+      </c>
+      <c r="D198">
+        <v>642</v>
+      </c>
+      <c r="E198" t="s">
+        <v>199</v>
+      </c>
+      <c r="F198" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="G198" t="s">
+        <v>198</v>
+      </c>
+      <c r="M198" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="199" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B199" t="s">
+        <v>190</v>
+      </c>
+      <c r="C199" t="s">
+        <v>124</v>
+      </c>
+      <c r="D199">
+        <v>643</v>
+      </c>
+      <c r="E199" t="s">
+        <v>199</v>
+      </c>
+      <c r="F199" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="G199" t="s">
+        <v>198</v>
+      </c>
+      <c r="M199" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="200" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B200" t="s">
+        <v>190</v>
+      </c>
+      <c r="C200" t="s">
+        <v>124</v>
+      </c>
+      <c r="D200">
+        <v>644</v>
+      </c>
+      <c r="E200" t="s">
+        <v>199</v>
+      </c>
+      <c r="F200" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="Q195" t="s">
+      <c r="G200" t="s">
+        <v>198</v>
+      </c>
+      <c r="M200" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="Q200" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="196" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B196" t="s">
-        <v>198</v>
-      </c>
-      <c r="C196" t="s">
-        <v>127</v>
-      </c>
-      <c r="D196">
-        <v>639</v>
-      </c>
-      <c r="E196" t="s">
-        <v>207</v>
-      </c>
-      <c r="F196" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="G196" t="s">
-        <v>206</v>
-      </c>
-      <c r="M196" s="4" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="197" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B197" t="s">
-        <v>198</v>
-      </c>
-      <c r="C197" t="s">
-        <v>127</v>
-      </c>
-      <c r="D197">
-        <v>640</v>
-      </c>
-      <c r="E197" t="s">
-        <v>207</v>
-      </c>
-      <c r="F197" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="G197" t="s">
-        <v>206</v>
-      </c>
-      <c r="M197" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="Q197" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="198" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B198" t="s">
-        <v>198</v>
-      </c>
-      <c r="C198" t="s">
-        <v>127</v>
-      </c>
-      <c r="D198">
-        <v>641</v>
-      </c>
-      <c r="E198" t="s">
-        <v>207</v>
-      </c>
-      <c r="F198" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="G198" t="s">
-        <v>206</v>
-      </c>
-      <c r="M198" s="4" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="199" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B199" t="s">
-        <v>198</v>
-      </c>
-      <c r="C199" t="s">
-        <v>127</v>
-      </c>
-      <c r="D199">
-        <v>642</v>
-      </c>
-      <c r="E199" t="s">
-        <v>207</v>
-      </c>
-      <c r="F199" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="G199" t="s">
-        <v>206</v>
-      </c>
-      <c r="M199" s="4" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="200" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B200" t="s">
-        <v>198</v>
-      </c>
-      <c r="C200" t="s">
-        <v>127</v>
-      </c>
-      <c r="D200">
-        <v>643</v>
-      </c>
-      <c r="E200" t="s">
-        <v>207</v>
-      </c>
-      <c r="F200" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="G200" t="s">
-        <v>206</v>
-      </c>
-      <c r="M200" s="4" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="201" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B201" t="s">
-        <v>198</v>
-      </c>
-      <c r="C201" t="s">
-        <v>127</v>
-      </c>
-      <c r="D201">
-        <v>644</v>
-      </c>
-      <c r="E201" t="s">
-        <v>207</v>
-      </c>
-      <c r="F201" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="G201" t="s">
-        <v>206</v>
-      </c>
-      <c r="M201" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="Q201" t="s">
-        <v>205</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="B1:Q201" xr:uid="{47ECCD65-6802-4B2B-901A-AED4A431A765}">
+  <autoFilter ref="B1:Q200" xr:uid="{47ECCD65-6802-4B2B-901A-AED4A431A765}">
     <filterColumn colId="0">
       <filters>
-        <filter val="SPF"/>
+        <filter val="5F"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Tmem119-CreERT2; Tsg101-flox"/>
       </filters>
     </filterColumn>
     <filterColumn colId="13">
@@ -9757,12 +9828,20 @@
     </filterColumn>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="M1:M1048576">
-    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text=".X">
+  <conditionalFormatting sqref="M1:M153 M155:M1048576">
+    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text=".X">
       <formula>NOT(ISERROR(SEARCH(".X",M1)))</formula>
     </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text=".B">
+      <formula>NOT(ISERROR(SEARCH(".B",M1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M154">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text=".X">
+      <formula>NOT(ISERROR(SEARCH(".X",M154)))</formula>
+    </cfRule>
     <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text=".B">
-      <formula>NOT(ISERROR(SEARCH(".B",M1)))</formula>
+      <formula>NOT(ISERROR(SEARCH(".B",M154)))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
@@ -9784,9 +9863,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EC7FBA1-B906-4440-9539-B905A5CA8161}">
   <dimension ref="C2:H4"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="27.75" customWidth="1"/>
+    <col min="3" max="3" width="27.625" customWidth="1"/>
     <col min="4" max="4" width="10.875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -9797,10 +9876,10 @@
       <c r="E2" t="s">
         <v>73</v>
       </c>
-      <c r="G2" s="24" t="s">
+      <c r="G2" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="H2" s="24"/>
+      <c r="H2" s="21"/>
     </row>
     <row r="3" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C3" t="s">
@@ -9844,4 +9923,207 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{204CD0B9-8C45-41F1-B207-9E51E4F55111}">
+  <dimension ref="A6:G17"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="28.625" customWidth="1"/>
+    <col min="6" max="6" width="72.375" customWidth="1"/>
+    <col min="7" max="7" width="30.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>211</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>220</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>211</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>218</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>3</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>211</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>212</v>
+      </c>
+      <c r="E8" s="20">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>4</v>
+      </c>
+      <c r="B9" t="s">
+        <v>98</v>
+      </c>
+      <c r="C9" t="s">
+        <v>211</v>
+      </c>
+      <c r="D9" t="s">
+        <v>216</v>
+      </c>
+      <c r="E9">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>215</v>
+      </c>
+      <c r="G9" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>5</v>
+      </c>
+      <c r="B10" t="s">
+        <v>99</v>
+      </c>
+      <c r="C10" t="s">
+        <v>211</v>
+      </c>
+      <c r="D10" t="s">
+        <v>213</v>
+      </c>
+      <c r="E10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>6</v>
+      </c>
+      <c r="B11" t="s">
+        <v>179</v>
+      </c>
+      <c r="C11" t="s">
+        <v>211</v>
+      </c>
+      <c r="D11" t="s">
+        <v>212</v>
+      </c>
+      <c r="E11">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>7</v>
+      </c>
+      <c r="B12" t="s">
+        <v>180</v>
+      </c>
+      <c r="C12" t="s">
+        <v>211</v>
+      </c>
+      <c r="D12" t="s">
+        <v>210</v>
+      </c>
+      <c r="E12">
+        <v>4</v>
+      </c>
+      <c r="F12" t="s">
+        <v>209</v>
+      </c>
+      <c r="G12" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>8</v>
+      </c>
+      <c r="B14" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>206</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>9</v>
+      </c>
+      <c r="B15" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>206</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>10</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>11</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="C17" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="D17" s="19" t="s">
+        <v>205</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Mouse 내역.xlsx
+++ b/Mouse 내역.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\heung\Dropbox\02. Lab. of Host Defenses\03. 동물실\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72AD19B1-BFFB-4408-BA85-3DA56D26BBF8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6F30E2B-F9E9-4366-9D52-837653D94A71}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="495" windowWidth="28800" windowHeight="16245" xr2:uid="{5A73A69A-2AFB-4F3E-AC64-070DD7700CB2}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="Sheet1 (2)" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$Q$200</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$Q$218</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1360" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1435" uniqueCount="231">
   <si>
     <t>Strain</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -916,6 +916,26 @@
   </si>
   <si>
     <t>Tmem119-CreERT2; Tsg101-flox</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A3.1.X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>G3.1.X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>N</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>몇마리인지 확인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Exp. 1-10-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1772,7 +1792,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D71A6DC-E91C-489F-8F50-989C4712FA7C}">
   <sheetPr filterMode="1"/>
-  <dimension ref="B1:Q200"/>
+  <dimension ref="B1:Q218"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="10.5" customWidth="1"/>
@@ -1860,11 +1880,11 @@
       </c>
       <c r="I2" s="4">
         <f ca="1">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H2), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H2), 7), "-")</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J2" s="4">
         <f ca="1">IF(_xlfn.DAYS(TODAY(),H2)&lt;10000, _xlfn.DAYS(TODAY(),H2), "-")</f>
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="L2" s="4" t="str">
         <f t="shared" ref="L2:L31" si="0">IF(_xlfn.DAYS(K2,H2)&gt;0, _xlfn.DAYS(K2,H2), "-")</f>
@@ -1878,7 +1898,7 @@
         <v>45299</v>
       </c>
     </row>
-    <row r="3" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>5</v>
       </c>
@@ -1899,11 +1919,11 @@
       </c>
       <c r="I3" s="4">
         <f t="shared" ref="I3:I65" ca="1" si="1">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H3), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H3), 7), "-")</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J3" s="4">
         <f t="shared" ref="J3:J31" ca="1" si="2">IF(_xlfn.DAYS(TODAY(),H3)&lt;10000, _xlfn.DAYS(TODAY(),H3), "-")</f>
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="L3" s="4" t="str">
         <f t="shared" si="0"/>
@@ -1915,7 +1935,7 @@
       <c r="N3" s="7"/>
       <c r="O3" s="7"/>
     </row>
-    <row r="4" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>5</v>
       </c>
@@ -1936,11 +1956,11 @@
       </c>
       <c r="I4" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J4" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="L4" s="4" t="str">
         <f t="shared" si="0"/>
@@ -1976,11 +1996,11 @@
       </c>
       <c r="I5" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J5" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="K5" s="2">
         <v>45293</v>
@@ -1997,7 +2017,7 @@
         <v>45309</v>
       </c>
     </row>
-    <row r="6" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>5</v>
       </c>
@@ -2021,11 +2041,11 @@
       </c>
       <c r="I6" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J6" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="K6" s="2">
         <v>45293</v>
@@ -2043,7 +2063,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="7" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>5</v>
       </c>
@@ -2067,11 +2087,11 @@
       </c>
       <c r="I7" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J7" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="K7" s="2">
         <v>45293</v>
@@ -2113,11 +2133,11 @@
       </c>
       <c r="I8" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J8" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="K8" s="2">
         <v>45293</v>
@@ -2137,7 +2157,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="9" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>5</v>
       </c>
@@ -2161,11 +2181,11 @@
       </c>
       <c r="I9" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J9" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="K9" s="2">
         <v>45293</v>
@@ -2204,11 +2224,11 @@
       </c>
       <c r="I10" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J10" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="K10" s="2">
         <v>45293</v>
@@ -2249,11 +2269,11 @@
       </c>
       <c r="I11" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J11" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="K11" s="2">
         <v>45293</v>
@@ -2291,11 +2311,11 @@
       </c>
       <c r="I12" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J12" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="L12" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2381,7 +2401,7 @@
         <v>45299</v>
       </c>
     </row>
-    <row r="15" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>5</v>
       </c>
@@ -2405,11 +2425,11 @@
       </c>
       <c r="I15" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J15" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="L15" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2421,7 +2441,7 @@
       <c r="N15" s="7"/>
       <c r="O15" s="7"/>
     </row>
-    <row r="16" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>5</v>
       </c>
@@ -2445,11 +2465,11 @@
       </c>
       <c r="I16" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J16" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="L16" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2461,7 +2481,7 @@
       <c r="N16" s="7"/>
       <c r="O16" s="7"/>
     </row>
-    <row r="17" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>5</v>
       </c>
@@ -2485,11 +2505,11 @@
       </c>
       <c r="I17" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J17" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="L17" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2523,11 +2543,11 @@
       </c>
       <c r="I18" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J18" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="L18" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2540,7 +2560,7 @@
         <v>45327</v>
       </c>
     </row>
-    <row r="19" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>5</v>
       </c>
@@ -2564,11 +2584,11 @@
       </c>
       <c r="I19" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J19" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="L19" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2599,11 +2619,11 @@
       </c>
       <c r="I20" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J20" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="L20" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2672,11 +2692,11 @@
       </c>
       <c r="I22" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J22" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="K22" s="2">
         <v>45112</v>
@@ -2713,11 +2733,11 @@
       </c>
       <c r="I23" s="4">
         <f ca="1">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H23), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H23), 7), "-")</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J23" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="K23" s="2">
         <v>45176</v>
@@ -2757,11 +2777,11 @@
       </c>
       <c r="I24" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J24" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="K24" s="2">
         <v>45176</v>
@@ -2801,11 +2821,11 @@
       </c>
       <c r="I25" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J25" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="K25" s="2">
         <v>45176</v>
@@ -2824,7 +2844,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="26" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>5</v>
       </c>
@@ -2845,11 +2865,11 @@
       </c>
       <c r="I26" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J26" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="K26" s="2">
         <v>45176</v>
@@ -2863,7 +2883,7 @@
       </c>
       <c r="Q26" s="2"/>
     </row>
-    <row r="27" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>5</v>
       </c>
@@ -2884,11 +2904,11 @@
       </c>
       <c r="I27" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J27" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="K27" s="2">
         <v>45176</v>
@@ -2923,11 +2943,11 @@
       </c>
       <c r="I28" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J28" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="K28" s="2">
         <v>45229</v>
@@ -2964,11 +2984,11 @@
       </c>
       <c r="I29" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J29" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="K29" s="2">
         <v>45229</v>
@@ -2984,7 +3004,7 @@
         <v>45310</v>
       </c>
     </row>
-    <row r="30" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>5</v>
       </c>
@@ -3005,11 +3025,11 @@
       </c>
       <c r="I30" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J30" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="K30" s="2">
         <v>45229</v>
@@ -3023,7 +3043,7 @@
       </c>
       <c r="Q30" s="2"/>
     </row>
-    <row r="31" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
         <v>5</v>
       </c>
@@ -3044,11 +3064,11 @@
       </c>
       <c r="I31" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J31" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="K31" s="2">
         <v>45229</v>
@@ -3062,7 +3082,7 @@
       </c>
       <c r="Q31" s="2"/>
     </row>
-    <row r="32" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
         <v>5</v>
       </c>
@@ -3083,11 +3103,11 @@
       </c>
       <c r="I32" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J32" s="4">
         <f t="shared" ref="J32:J38" ca="1" si="3">IF(_xlfn.DAYS(TODAY(),H32)&lt;10000, _xlfn.DAYS(TODAY(),H32), "-")</f>
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="K32" s="2">
         <v>45229</v>
@@ -3160,11 +3180,11 @@
       </c>
       <c r="I34" s="4">
         <f ca="1">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H34), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H34), 7), "-")</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J34" s="4">
         <f ca="1">IF(_xlfn.DAYS(TODAY(),H34)&lt;10000, _xlfn.DAYS(TODAY(),H34), "-")</f>
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="K34" s="2">
         <v>45257</v>
@@ -3283,11 +3303,11 @@
       </c>
       <c r="I37" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J37" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="K37" s="2">
         <v>45257</v>
@@ -3330,11 +3350,11 @@
       </c>
       <c r="I38" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J38" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="K38" s="2">
         <v>45257</v>
@@ -3377,11 +3397,11 @@
       </c>
       <c r="I39" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J39" s="4">
         <f t="shared" ref="J39:J41" ca="1" si="5">IF(_xlfn.DAYS(TODAY(),H39)&lt;10000, _xlfn.DAYS(TODAY(),H39), "-")</f>
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="K39" s="2">
         <v>45257</v>
@@ -3424,11 +3444,11 @@
       </c>
       <c r="I40" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J40" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="K40" s="2">
         <v>45257</v>
@@ -3468,11 +3488,11 @@
       </c>
       <c r="I41" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J41" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="K41" s="2">
         <v>45257</v>
@@ -3512,11 +3532,11 @@
       </c>
       <c r="I42" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J42" s="4">
         <f t="shared" ref="J42" ca="1" si="6">IF(_xlfn.DAYS(TODAY(),H42)&lt;10000, _xlfn.DAYS(TODAY(),H42), "-")</f>
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="L42" s="4" t="str">
         <f t="shared" si="4"/>
@@ -3529,7 +3549,7 @@
         <v>45309</v>
       </c>
     </row>
-    <row r="43" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B43" t="s">
         <v>5</v>
       </c>
@@ -3553,11 +3573,11 @@
       </c>
       <c r="I43" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J43" s="4">
         <f t="shared" ref="J43:J91" ca="1" si="7">IF(_xlfn.DAYS(TODAY(),H43)&lt;10000, _xlfn.DAYS(TODAY(),H43), "-")</f>
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="L43" s="4" t="str">
         <f t="shared" si="4"/>
@@ -3591,11 +3611,11 @@
       </c>
       <c r="I44" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J44" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="K44" s="2">
         <v>45293</v>
@@ -3635,11 +3655,11 @@
       </c>
       <c r="I45" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J45" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="K45" s="2">
         <v>45293</v>
@@ -3679,11 +3699,11 @@
       </c>
       <c r="I46" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J46" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="K46" s="2">
         <v>45293</v>
@@ -3726,11 +3746,11 @@
       </c>
       <c r="I47" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J47" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="K47" s="2">
         <v>45293</v>
@@ -3773,11 +3793,11 @@
       </c>
       <c r="I48" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J48" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="K48" s="2">
         <v>45293</v>
@@ -3796,7 +3816,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="49" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B49" t="s">
         <v>5</v>
       </c>
@@ -3820,11 +3840,11 @@
       </c>
       <c r="I49" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J49" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="K49" s="2">
         <v>45293</v>
@@ -3837,7 +3857,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="50" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B50" t="s">
         <v>5</v>
       </c>
@@ -3861,11 +3881,11 @@
       </c>
       <c r="I50" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J50" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="K50" s="2">
         <v>45293</v>
@@ -3902,11 +3922,11 @@
       </c>
       <c r="I51" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J51" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="K51" s="2">
         <v>45293</v>
@@ -3946,11 +3966,11 @@
       </c>
       <c r="I52" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J52" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="K52" s="2">
         <v>45293</v>
@@ -3966,7 +3986,7 @@
         <v>45309</v>
       </c>
     </row>
-    <row r="53" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B53" t="s">
         <v>5</v>
       </c>
@@ -3990,11 +4010,11 @@
       </c>
       <c r="I53" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J53" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="K53" s="2">
         <v>45293</v>
@@ -4007,7 +4027,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="54" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B54" t="s">
         <v>27</v>
       </c>
@@ -4031,11 +4051,11 @@
       </c>
       <c r="I54" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J54" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="K54" s="2">
         <v>45238</v>
@@ -4051,7 +4071,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="55" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B55" t="s">
         <v>27</v>
       </c>
@@ -4075,11 +4095,11 @@
       </c>
       <c r="I55" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J55" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="K55" s="2">
         <v>45238</v>
@@ -4095,7 +4115,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="56" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B56" t="s">
         <v>27</v>
       </c>
@@ -4119,11 +4139,11 @@
       </c>
       <c r="I56" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J56" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="K56" s="2">
         <v>45238</v>
@@ -4139,7 +4159,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="57" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B57" t="s">
         <v>27</v>
       </c>
@@ -4160,11 +4180,11 @@
       </c>
       <c r="I57" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J57" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="L57" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4177,7 +4197,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="58" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B58" t="s">
         <v>27</v>
       </c>
@@ -4198,11 +4218,11 @@
       </c>
       <c r="I58" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J58" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="L58" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4215,7 +4235,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="59" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B59" t="s">
         <v>27</v>
       </c>
@@ -4233,11 +4253,11 @@
       </c>
       <c r="I59" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J59" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="K59" s="2">
         <v>45295</v>
@@ -4253,7 +4273,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="60" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B60" t="s">
         <v>27</v>
       </c>
@@ -4271,11 +4291,11 @@
       </c>
       <c r="I60" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J60" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="K60" s="2">
         <v>45295</v>
@@ -4291,7 +4311,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="61" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B61" t="s">
         <v>27</v>
       </c>
@@ -4309,11 +4329,11 @@
       </c>
       <c r="I61" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J61" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="K61" s="2">
         <v>45295</v>
@@ -4326,7 +4346,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="62" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B62" t="s">
         <v>27</v>
       </c>
@@ -4344,11 +4364,11 @@
       </c>
       <c r="I62" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J62" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="K62" s="2">
         <v>45295</v>
@@ -4361,7 +4381,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="63" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B63" t="s">
         <v>27</v>
       </c>
@@ -4379,11 +4399,11 @@
       </c>
       <c r="I63" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J63" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="K63" s="2">
         <v>45295</v>
@@ -4392,11 +4412,14 @@
         <f t="shared" si="4"/>
         <v>28</v>
       </c>
-      <c r="M63" t="s">
+      <c r="M63" s="1" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="64" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="P63" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="64" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B64" t="s">
         <v>27</v>
       </c>
@@ -4414,11 +4437,11 @@
       </c>
       <c r="I64" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J64" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="K64" s="2">
         <v>45295</v>
@@ -4427,11 +4450,14 @@
         <f t="shared" si="4"/>
         <v>28</v>
       </c>
-      <c r="M64" t="s">
+      <c r="M64" s="1" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="P64" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B65" t="s">
         <v>27</v>
       </c>
@@ -4452,11 +4478,11 @@
       </c>
       <c r="I65" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J65" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="L65" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4469,7 +4495,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B66" t="s">
         <v>27</v>
       </c>
@@ -4490,11 +4516,11 @@
       </c>
       <c r="I66" s="4">
         <f t="shared" ref="I66:I91" ca="1" si="8">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H66), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H66), 7), "-")</f>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J66" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="L66" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4531,11 +4557,11 @@
       </c>
       <c r="I67" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J67" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="L67" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4581,11 +4607,11 @@
       </c>
       <c r="I68" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J68" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="L68" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4631,11 +4657,11 @@
       </c>
       <c r="I69" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J69" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="L69" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4681,11 +4707,11 @@
       </c>
       <c r="I70" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J70" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="L70" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4731,11 +4757,11 @@
       </c>
       <c r="I71" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J71" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="L71" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4781,11 +4807,11 @@
       </c>
       <c r="I72" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J72" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="L72" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4831,11 +4857,11 @@
       </c>
       <c r="I73" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J73" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="L73" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4881,11 +4907,11 @@
       </c>
       <c r="I74" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J74" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="L74" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4931,11 +4957,11 @@
       </c>
       <c r="I75" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J75" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="L75" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4981,11 +5007,11 @@
       </c>
       <c r="I76" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J76" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="L76" s="4" t="str">
         <f t="shared" si="4"/>
@@ -5031,11 +5057,11 @@
       </c>
       <c r="I77" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J77" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="L77" s="4" t="str">
         <f t="shared" si="4"/>
@@ -5081,11 +5107,11 @@
       </c>
       <c r="I78" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J78" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="L78" s="4" t="str">
         <f t="shared" si="4"/>
@@ -5131,11 +5157,11 @@
       </c>
       <c r="I79" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J79" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="L79" s="4" t="str">
         <f t="shared" si="4"/>
@@ -5181,11 +5207,11 @@
       </c>
       <c r="I80" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J80" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="L80" s="4" t="str">
         <f t="shared" si="4"/>
@@ -5231,11 +5257,11 @@
       </c>
       <c r="I81" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J81" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="L81" s="4" t="str">
         <f t="shared" si="4"/>
@@ -5281,11 +5307,11 @@
       </c>
       <c r="I82" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J82" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="L82" s="4" t="str">
         <f t="shared" si="4"/>
@@ -5331,11 +5357,11 @@
       </c>
       <c r="I83" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J83" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="L83" s="4" t="str">
         <f t="shared" si="4"/>
@@ -5381,11 +5407,11 @@
       </c>
       <c r="I84" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J84" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="L84" s="4" t="str">
         <f t="shared" si="4"/>
@@ -5431,11 +5457,11 @@
       </c>
       <c r="I85" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J85" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="L85" s="4" t="str">
         <f t="shared" si="4"/>
@@ -5481,11 +5507,11 @@
       </c>
       <c r="I86" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J86" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="L86" s="4" t="str">
         <f t="shared" si="4"/>
@@ -5531,11 +5557,11 @@
       </c>
       <c r="I87" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J87" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="K87" s="2">
         <v>45272</v>
@@ -5581,11 +5607,11 @@
       </c>
       <c r="I88" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J88" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="K88" s="2">
         <v>45273</v>
@@ -5631,11 +5657,11 @@
       </c>
       <c r="I89" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J89" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="K89" s="2">
         <v>45274</v>
@@ -5681,11 +5707,11 @@
       </c>
       <c r="I90" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J90" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="K90" s="2">
         <v>45275</v>
@@ -5731,11 +5757,11 @@
       </c>
       <c r="I91" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J91" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="K91" s="2">
         <v>45276</v>
@@ -5781,11 +5807,11 @@
       </c>
       <c r="I92" s="4">
         <f t="shared" ref="I92:I93" ca="1" si="9">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H92), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H92), 7), "-")</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J92" s="4">
         <f t="shared" ref="J92:J93" ca="1" si="10">IF(_xlfn.DAYS(TODAY(),H92)&lt;10000, _xlfn.DAYS(TODAY(),H92), "-")</f>
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="K92" s="2">
         <v>45277</v>
@@ -5831,11 +5857,11 @@
       </c>
       <c r="I93" s="4">
         <f t="shared" ca="1" si="9"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J93" s="4">
         <f t="shared" ca="1" si="10"/>
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="K93" s="2">
         <v>45278</v>
@@ -5881,11 +5907,11 @@
       </c>
       <c r="I94" s="4">
         <f t="shared" ref="I94" ca="1" si="11">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H94), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H94), 7), "-")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J94" s="4">
         <f t="shared" ref="J94" ca="1" si="12">IF(_xlfn.DAYS(TODAY(),H94)&lt;10000, _xlfn.DAYS(TODAY(),H94), "-")</f>
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="K94" s="2">
         <v>45223</v>
@@ -5931,11 +5957,11 @@
       </c>
       <c r="I95" s="4">
         <f t="shared" ref="I95:I117" ca="1" si="13">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H95), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H95), 7), "-")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J95" s="4">
         <f t="shared" ref="J95:J117" ca="1" si="14">IF(_xlfn.DAYS(TODAY(),H95)&lt;10000, _xlfn.DAYS(TODAY(),H95), "-")</f>
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="K95" s="2">
         <v>45223</v>
@@ -5981,11 +6007,11 @@
       </c>
       <c r="I96" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J96" s="4">
         <f t="shared" ca="1" si="14"/>
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="K96" s="2">
         <v>45223</v>
@@ -6031,11 +6057,11 @@
       </c>
       <c r="I97" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J97" s="4">
         <f t="shared" ca="1" si="14"/>
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="K97" s="2">
         <v>45223</v>
@@ -6081,11 +6107,11 @@
       </c>
       <c r="I98" s="4">
         <f t="shared" ref="I98:I107" ca="1" si="16">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H98), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H98), 7), "-")</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J98" s="4">
         <f t="shared" ref="J98:J107" ca="1" si="17">IF(_xlfn.DAYS(TODAY(),H98)&lt;10000, _xlfn.DAYS(TODAY(),H98), "-")</f>
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="K98" s="2">
         <v>45267</v>
@@ -6134,11 +6160,11 @@
       </c>
       <c r="I99" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J99" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="K99" s="2">
         <v>45267</v>
@@ -6187,11 +6213,11 @@
       </c>
       <c r="I100" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J100" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="K100" s="2">
         <v>45267</v>
@@ -6240,11 +6266,11 @@
       </c>
       <c r="I101" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J101" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="K101" s="2">
         <v>45267</v>
@@ -6293,11 +6319,11 @@
       </c>
       <c r="I102" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J102" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="K102" s="2">
         <v>45267</v>
@@ -6346,11 +6372,11 @@
       </c>
       <c r="I103" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J103" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="K103" s="2">
         <v>45267</v>
@@ -6399,11 +6425,11 @@
       </c>
       <c r="I104" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J104" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="K104" s="2">
         <v>45267</v>
@@ -6452,11 +6478,11 @@
       </c>
       <c r="I105" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J105" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="K105" s="2">
         <v>45267</v>
@@ -6505,11 +6531,11 @@
       </c>
       <c r="I106" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J106" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="K106" s="2">
         <v>45267</v>
@@ -6558,11 +6584,11 @@
       </c>
       <c r="I107" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J107" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="K107" s="2">
         <v>45267</v>
@@ -7082,7 +7108,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="120" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B120" t="s">
         <v>88</v>
       </c>
@@ -7106,11 +7132,11 @@
       </c>
       <c r="I120" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J120" s="4">
         <f t="shared" ca="1" si="19"/>
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="K120" s="2">
         <v>45315</v>
@@ -7123,7 +7149,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="121" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B121" t="s">
         <v>88</v>
       </c>
@@ -7147,11 +7173,11 @@
       </c>
       <c r="I121" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J121" s="4">
         <f t="shared" ca="1" si="19"/>
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="K121" s="2">
         <v>45315</v>
@@ -7167,7 +7193,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="122" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B122" t="s">
         <v>88</v>
       </c>
@@ -7191,11 +7217,11 @@
       </c>
       <c r="I122" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J122" s="4">
         <f t="shared" ca="1" si="19"/>
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="K122" s="2">
         <v>45315</v>
@@ -7208,7 +7234,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="123" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B123" t="s">
         <v>88</v>
       </c>
@@ -7232,11 +7258,11 @@
       </c>
       <c r="I123" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J123" s="4">
         <f t="shared" ca="1" si="19"/>
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="K123" s="2">
         <v>45315</v>
@@ -7249,7 +7275,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="124" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B124" t="s">
         <v>113</v>
       </c>
@@ -7264,11 +7290,11 @@
       </c>
       <c r="I124" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J124" s="4">
         <f t="shared" ca="1" si="19"/>
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="L124" s="4" t="str">
         <f t="shared" si="15"/>
@@ -7278,7 +7304,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="125" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B125" t="s">
         <v>113</v>
       </c>
@@ -7293,11 +7319,11 @@
       </c>
       <c r="I125" s="4">
         <f t="shared" ref="I125:I127" ca="1" si="20">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H125), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H125), 7), "-")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J125" s="4">
         <f t="shared" ref="J125:J127" ca="1" si="21">IF(_xlfn.DAYS(TODAY(),H125)&lt;10000, _xlfn.DAYS(TODAY(),H125), "-")</f>
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="L125" s="4" t="str">
         <f t="shared" si="15"/>
@@ -7307,7 +7333,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="126" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B126" t="s">
         <v>113</v>
       </c>
@@ -7322,11 +7348,11 @@
       </c>
       <c r="I126" s="4">
         <f t="shared" ca="1" si="20"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J126" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="L126" s="4" t="str">
         <f t="shared" si="15"/>
@@ -7336,7 +7362,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="127" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B127" t="s">
         <v>113</v>
       </c>
@@ -7351,11 +7377,11 @@
       </c>
       <c r="I127" s="4">
         <f t="shared" ca="1" si="20"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J127" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="L127" s="4" t="str">
         <f t="shared" si="15"/>
@@ -7365,7 +7391,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="128" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B128" t="s">
         <v>114</v>
       </c>
@@ -7380,11 +7406,11 @@
       </c>
       <c r="I128" s="4">
         <f t="shared" ref="I128:I130" ca="1" si="22">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H128), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H128), 7), "-")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J128" s="4">
         <f t="shared" ref="J128:J130" ca="1" si="23">IF(_xlfn.DAYS(TODAY(),H128)&lt;10000, _xlfn.DAYS(TODAY(),H128), "-")</f>
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="L128" s="4" t="str">
         <f t="shared" si="15"/>
@@ -7394,7 +7420,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="129" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B129" t="s">
         <v>114</v>
       </c>
@@ -7409,11 +7435,11 @@
       </c>
       <c r="I129" s="4">
         <f t="shared" ca="1" si="22"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J129" s="4">
         <f t="shared" ca="1" si="23"/>
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="L129" s="4" t="str">
         <f t="shared" si="15"/>
@@ -7423,7 +7449,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="130" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B130" t="s">
         <v>114</v>
       </c>
@@ -7438,11 +7464,11 @@
       </c>
       <c r="I130" s="4">
         <f t="shared" ca="1" si="22"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J130" s="4">
         <f t="shared" ca="1" si="23"/>
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="L130" s="4" t="str">
         <f t="shared" si="15"/>
@@ -7452,7 +7478,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="131" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B131" t="s">
         <v>5</v>
       </c>
@@ -7481,7 +7507,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="132" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B132" t="s">
         <v>5</v>
       </c>
@@ -7499,11 +7525,11 @@
       </c>
       <c r="I132" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J132" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="L132" s="4" t="str">
         <f t="shared" si="26"/>
@@ -7516,7 +7542,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="133" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B133" t="s">
         <v>5</v>
       </c>
@@ -7534,11 +7560,11 @@
       </c>
       <c r="I133" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J133" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="L133" s="4" t="str">
         <f t="shared" si="26"/>
@@ -7548,7 +7574,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="134" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B134" t="s">
         <v>5</v>
       </c>
@@ -7566,11 +7592,11 @@
       </c>
       <c r="I134" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J134" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="L134" s="4" t="str">
         <f t="shared" si="26"/>
@@ -7580,7 +7606,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="135" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B135" t="s">
         <v>5</v>
       </c>
@@ -7598,11 +7624,11 @@
       </c>
       <c r="I135" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J135" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="L135" s="4" t="str">
         <f t="shared" si="26"/>
@@ -7615,7 +7641,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="136" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B136" t="s">
         <v>5</v>
       </c>
@@ -7633,11 +7659,11 @@
       </c>
       <c r="I136" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J136" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="L136" s="4" t="str">
         <f t="shared" si="26"/>
@@ -7647,7 +7673,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="137" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B137" t="s">
         <v>5</v>
       </c>
@@ -7665,11 +7691,11 @@
       </c>
       <c r="I137" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J137" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="L137" s="4" t="str">
         <f t="shared" si="26"/>
@@ -7679,7 +7705,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="138" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B138" t="s">
         <v>141</v>
       </c>
@@ -7740,7 +7766,7 @@
         <v>45322</v>
       </c>
     </row>
-    <row r="140" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B140" t="s">
         <v>141</v>
       </c>
@@ -7769,7 +7795,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="141" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B141" t="s">
         <v>141</v>
       </c>
@@ -7784,11 +7810,11 @@
       </c>
       <c r="I141" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J141" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="L141" s="4" t="str">
         <f t="shared" si="26"/>
@@ -7801,7 +7827,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="142" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B142" t="s">
         <v>141</v>
       </c>
@@ -7816,11 +7842,11 @@
       </c>
       <c r="I142" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J142" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="L142" s="4" t="str">
         <f t="shared" si="26"/>
@@ -7833,7 +7859,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="143" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B143" t="s">
         <v>141</v>
       </c>
@@ -7848,11 +7874,11 @@
       </c>
       <c r="I143" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J143" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="L143" s="4" t="str">
         <f t="shared" si="26"/>
@@ -7865,7 +7891,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="144" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B144" t="s">
         <v>141</v>
       </c>
@@ -7880,11 +7906,11 @@
       </c>
       <c r="I144" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J144" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="L144" s="4" t="str">
         <f t="shared" si="26"/>
@@ -7897,7 +7923,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="145" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B145" t="s">
         <v>141</v>
       </c>
@@ -7912,11 +7938,11 @@
       </c>
       <c r="I145" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J145" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="L145" s="4" t="str">
         <f t="shared" si="26"/>
@@ -7929,7 +7955,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="146" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B146" t="s">
         <v>141</v>
       </c>
@@ -7944,11 +7970,11 @@
       </c>
       <c r="I146" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J146" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="L146" s="4" t="str">
         <f t="shared" si="26"/>
@@ -7961,7 +7987,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="147" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B147" t="s">
         <v>141</v>
       </c>
@@ -7990,7 +8016,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="148" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B148" t="s">
         <v>141</v>
       </c>
@@ -8019,7 +8045,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="149" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B149" t="s">
         <v>141</v>
       </c>
@@ -8048,7 +8074,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="150" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B150" t="s">
         <v>141</v>
       </c>
@@ -8077,7 +8103,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="151" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B151" t="s">
         <v>141</v>
       </c>
@@ -8092,11 +8118,11 @@
       </c>
       <c r="I151" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J151" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="L151" s="4" t="str">
         <f t="shared" si="29"/>
@@ -8106,7 +8132,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="152" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B152" t="s">
         <v>141</v>
       </c>
@@ -8121,11 +8147,11 @@
       </c>
       <c r="I152" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J152" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="L152" s="4" t="str">
         <f t="shared" si="29"/>
@@ -8135,7 +8161,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="153" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B153" t="s">
         <v>141</v>
       </c>
@@ -8150,11 +8176,11 @@
       </c>
       <c r="I153" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J153" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="L153" s="4" t="str">
         <f t="shared" si="29"/>
@@ -8164,7 +8190,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="154" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B154" t="s">
         <v>141</v>
       </c>
@@ -8179,11 +8205,11 @@
       </c>
       <c r="I154" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J154" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="L154" s="4" t="str">
         <f t="shared" si="29"/>
@@ -8193,7 +8219,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="155" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B155" t="s">
         <v>141</v>
       </c>
@@ -8208,11 +8234,11 @@
       </c>
       <c r="I155" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J155" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="L155" s="4" t="str">
         <f t="shared" si="29"/>
@@ -8222,7 +8248,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="156" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B156" t="s">
         <v>141</v>
       </c>
@@ -8237,11 +8263,11 @@
       </c>
       <c r="I156" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J156" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="L156" s="4" t="str">
         <f t="shared" si="29"/>
@@ -8275,11 +8301,11 @@
       </c>
       <c r="I157" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J157" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="L157" s="4" t="str">
         <f t="shared" si="29"/>
@@ -8333,7 +8359,7 @@
         <v>45329</v>
       </c>
     </row>
-    <row r="159" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B159" t="s">
         <v>141</v>
       </c>
@@ -8365,7 +8391,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="160" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B160" t="s">
         <v>141</v>
       </c>
@@ -8397,7 +8423,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="161" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B161" t="s">
         <v>141</v>
       </c>
@@ -8421,11 +8447,11 @@
       </c>
       <c r="I161" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J161" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="K161" s="2">
         <v>45301</v>
@@ -8438,7 +8464,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="162" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B162" t="s">
         <v>141</v>
       </c>
@@ -8462,11 +8488,11 @@
       </c>
       <c r="I162" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J162" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="K162" s="2">
         <v>45301</v>
@@ -8500,11 +8526,11 @@
       </c>
       <c r="I163" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J163" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="K163" s="2">
         <v>45301</v>
@@ -8523,7 +8549,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="164" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B164" t="s">
         <v>141</v>
       </c>
@@ -8547,11 +8573,11 @@
       </c>
       <c r="I164" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J164" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="K164" s="2">
         <v>45301</v>
@@ -8588,11 +8614,11 @@
       </c>
       <c r="I165" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J165" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="K165" s="2">
         <v>45301</v>
@@ -8614,7 +8640,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="166" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B166" t="s">
         <v>141</v>
       </c>
@@ -8638,11 +8664,11 @@
       </c>
       <c r="I166" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J166" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="K166" s="2">
         <v>45301</v>
@@ -8679,11 +8705,11 @@
       </c>
       <c r="I167" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J167" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="L167" s="4" t="str">
         <f t="shared" si="29"/>
@@ -8720,11 +8746,11 @@
       </c>
       <c r="I168" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J168" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="L168" s="4" t="str">
         <f t="shared" si="29"/>
@@ -8761,11 +8787,11 @@
       </c>
       <c r="I169" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J169" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="L169" s="4" t="str">
         <f t="shared" si="29"/>
@@ -8805,11 +8831,11 @@
       </c>
       <c r="I170" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J170" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="K170" s="2">
         <v>45301</v>
@@ -8831,7 +8857,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="171" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B171" t="s">
         <v>141</v>
       </c>
@@ -8855,11 +8881,11 @@
       </c>
       <c r="I171" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J171" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="K171" s="2">
         <v>45301</v>
@@ -8896,11 +8922,11 @@
       </c>
       <c r="I172" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J172" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="K172" s="2">
         <v>45301</v>
@@ -8943,11 +8969,11 @@
       </c>
       <c r="I173" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J173" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="K173" s="2">
         <v>45301</v>
@@ -8990,11 +9016,11 @@
       </c>
       <c r="I174" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J174" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="K174" s="2">
         <v>45301</v>
@@ -9013,7 +9039,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="175" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B175" t="s">
         <v>141</v>
       </c>
@@ -9037,11 +9063,11 @@
       </c>
       <c r="I175" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J175" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="L175" s="4" t="str">
         <f t="shared" si="29"/>
@@ -9075,11 +9101,11 @@
       </c>
       <c r="I176" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J176" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="L176" s="4" t="str">
         <f t="shared" si="29"/>
@@ -9098,7 +9124,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="177" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="177" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B177" t="s">
         <v>34</v>
       </c>
@@ -9116,11 +9142,11 @@
       </c>
       <c r="I177" s="4">
         <f t="shared" ref="I177" ca="1" si="30">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H177), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H177), 7), "-")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J177" s="4">
         <f t="shared" ref="J177" ca="1" si="31">IF(_xlfn.DAYS(TODAY(),H177)&lt;10000, _xlfn.DAYS(TODAY(),H177), "-")</f>
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="K177" s="16">
         <v>45324</v>
@@ -9133,7 +9159,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="178" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="178" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B178" t="s">
         <v>34</v>
       </c>
@@ -9151,11 +9177,11 @@
       </c>
       <c r="I178" s="4">
         <f t="shared" ref="I178:I187" ca="1" si="33">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H178), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H178), 7), "-")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J178" s="4">
         <f t="shared" ref="J178:J187" ca="1" si="34">IF(_xlfn.DAYS(TODAY(),H178)&lt;10000, _xlfn.DAYS(TODAY(),H178), "-")</f>
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="K178" s="16">
         <v>45324</v>
@@ -9168,7 +9194,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="179" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="179" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B179" t="s">
         <v>34</v>
       </c>
@@ -9186,11 +9212,11 @@
       </c>
       <c r="I179" s="4">
         <f t="shared" ca="1" si="33"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J179" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="K179" s="16">
         <v>45324</v>
@@ -9203,7 +9229,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="180" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="180" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B180" t="s">
         <v>34</v>
       </c>
@@ -9221,11 +9247,11 @@
       </c>
       <c r="I180" s="4">
         <f t="shared" ca="1" si="33"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J180" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="K180" s="16">
         <v>45324</v>
@@ -9238,7 +9264,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="181" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="181" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B181" t="s">
         <v>34</v>
       </c>
@@ -9256,11 +9282,11 @@
       </c>
       <c r="I181" s="4">
         <f t="shared" ca="1" si="33"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J181" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="K181" s="16">
         <v>45324</v>
@@ -9273,7 +9299,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="182" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="182" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B182" t="s">
         <v>34</v>
       </c>
@@ -9291,11 +9317,11 @@
       </c>
       <c r="I182" s="4">
         <f t="shared" ca="1" si="33"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J182" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="K182" s="16">
         <v>45324</v>
@@ -9308,7 +9334,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="183" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="183" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B183" t="s">
         <v>34</v>
       </c>
@@ -9326,11 +9352,11 @@
       </c>
       <c r="I183" s="4">
         <f t="shared" ca="1" si="33"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J183" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="K183" s="16">
         <v>45324</v>
@@ -9343,7 +9369,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="184" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="184" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B184" t="s">
         <v>34</v>
       </c>
@@ -9361,11 +9387,11 @@
       </c>
       <c r="I184" s="4">
         <f t="shared" ca="1" si="33"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J184" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="K184" s="16">
         <v>45324</v>
@@ -9378,7 +9404,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="185" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="185" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B185" t="s">
         <v>34</v>
       </c>
@@ -9396,11 +9422,11 @@
       </c>
       <c r="I185" s="4">
         <f t="shared" ca="1" si="33"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J185" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="K185" s="16">
         <v>45324</v>
@@ -9413,7 +9439,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="186" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="186" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B186" t="s">
         <v>183</v>
       </c>
@@ -9425,17 +9451,17 @@
       </c>
       <c r="I186" s="4">
         <f t="shared" ca="1" si="33"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J186" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="M186" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="187" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B187" t="s">
         <v>5</v>
       </c>
@@ -9450,11 +9476,11 @@
       </c>
       <c r="I187" s="4">
         <f t="shared" ca="1" si="33"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J187" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="L187" s="4" t="str">
         <f t="shared" ref="L187" si="36">IF(_xlfn.DAYS(K187,H187)&gt;0, _xlfn.DAYS(K187,H187), "-")</f>
@@ -9464,7 +9490,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="188" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B188" t="s">
         <v>5</v>
       </c>
@@ -9479,11 +9505,11 @@
       </c>
       <c r="I188" s="4">
         <f t="shared" ref="I188:I194" ca="1" si="37">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H188), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H188), 7), "-")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J188" s="4">
         <f t="shared" ref="J188:J194" ca="1" si="38">IF(_xlfn.DAYS(TODAY(),H188)&lt;10000, _xlfn.DAYS(TODAY(),H188), "-")</f>
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="L188" s="4" t="str">
         <f t="shared" ref="L188:L194" si="39">IF(_xlfn.DAYS(K188,H188)&gt;0, _xlfn.DAYS(K188,H188), "-")</f>
@@ -9493,7 +9519,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="189" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B189" t="s">
         <v>5</v>
       </c>
@@ -9508,11 +9534,11 @@
       </c>
       <c r="I189" s="4">
         <f t="shared" ca="1" si="37"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J189" s="4">
         <f t="shared" ca="1" si="38"/>
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="L189" s="4" t="str">
         <f t="shared" si="39"/>
@@ -9522,7 +9548,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="190" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B190" t="s">
         <v>5</v>
       </c>
@@ -9537,11 +9563,11 @@
       </c>
       <c r="I190" s="4">
         <f t="shared" ca="1" si="37"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J190" s="4">
         <f t="shared" ca="1" si="38"/>
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="L190" s="4" t="str">
         <f t="shared" si="39"/>
@@ -9551,7 +9577,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="191" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B191" t="s">
         <v>5</v>
       </c>
@@ -9566,11 +9592,11 @@
       </c>
       <c r="I191" s="4">
         <f t="shared" ca="1" si="37"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J191" s="4">
         <f t="shared" ca="1" si="38"/>
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="L191" s="4" t="str">
         <f t="shared" si="39"/>
@@ -9580,7 +9606,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="192" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B192" t="s">
         <v>5</v>
       </c>
@@ -9595,11 +9621,11 @@
       </c>
       <c r="I192" s="4">
         <f t="shared" ca="1" si="37"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J192" s="4">
         <f t="shared" ca="1" si="38"/>
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="L192" s="4" t="str">
         <f t="shared" si="39"/>
@@ -9609,7 +9635,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="193" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B193" t="s">
         <v>5</v>
       </c>
@@ -9624,11 +9650,11 @@
       </c>
       <c r="I193" s="4">
         <f t="shared" ca="1" si="37"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J193" s="4">
         <f t="shared" ca="1" si="38"/>
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="L193" s="4" t="str">
         <f t="shared" si="39"/>
@@ -9638,7 +9664,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="194" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B194" t="s">
         <v>5</v>
       </c>
@@ -9653,11 +9679,11 @@
       </c>
       <c r="I194" s="4">
         <f t="shared" ca="1" si="37"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J194" s="4">
         <f t="shared" ca="1" si="38"/>
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="L194" s="4" t="str">
         <f t="shared" si="39"/>
@@ -9667,7 +9693,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="195" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B195" t="s">
         <v>190</v>
       </c>
@@ -9690,7 +9716,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="196" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B196" t="s">
         <v>190</v>
       </c>
@@ -9716,7 +9742,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="197" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B197" t="s">
         <v>190</v>
       </c>
@@ -9739,7 +9765,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="198" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B198" t="s">
         <v>190</v>
       </c>
@@ -9762,7 +9788,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="199" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B199" t="s">
         <v>190</v>
       </c>
@@ -9785,7 +9811,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="200" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B200" t="s">
         <v>190</v>
       </c>
@@ -9811,16 +9837,521 @@
         <v>197</v>
       </c>
     </row>
+    <row r="201" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B201" t="s">
+        <v>5</v>
+      </c>
+      <c r="C201" t="s">
+        <v>125</v>
+      </c>
+      <c r="E201" t="s">
+        <v>15</v>
+      </c>
+      <c r="H201" s="2">
+        <v>45332</v>
+      </c>
+      <c r="I201" s="4">
+        <f t="shared" ref="I201" ca="1" si="40">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H201), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H201), 7), "-")</f>
+        <v>1</v>
+      </c>
+      <c r="J201" s="4">
+        <f t="shared" ref="J201" ca="1" si="41">IF(_xlfn.DAYS(TODAY(),H201)&lt;10000, _xlfn.DAYS(TODAY(),H201), "-")</f>
+        <v>11</v>
+      </c>
+      <c r="L201" s="4" t="str">
+        <f t="shared" ref="L201" si="42">IF(_xlfn.DAYS(K201,H201)&gt;0, _xlfn.DAYS(K201,H201), "-")</f>
+        <v>-</v>
+      </c>
+      <c r="M201" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="202" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B202" t="s">
+        <v>5</v>
+      </c>
+      <c r="C202" t="s">
+        <v>125</v>
+      </c>
+      <c r="E202" t="s">
+        <v>15</v>
+      </c>
+      <c r="H202" s="2">
+        <v>45332</v>
+      </c>
+      <c r="I202" s="4">
+        <f t="shared" ref="I202:I217" ca="1" si="43">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H202), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H202), 7), "-")</f>
+        <v>1</v>
+      </c>
+      <c r="J202" s="4">
+        <f t="shared" ref="J202:J217" ca="1" si="44">IF(_xlfn.DAYS(TODAY(),H202)&lt;10000, _xlfn.DAYS(TODAY(),H202), "-")</f>
+        <v>11</v>
+      </c>
+      <c r="L202" s="4" t="str">
+        <f t="shared" ref="L202:L217" si="45">IF(_xlfn.DAYS(K202,H202)&gt;0, _xlfn.DAYS(K202,H202), "-")</f>
+        <v>-</v>
+      </c>
+      <c r="M202" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="203" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B203" t="s">
+        <v>5</v>
+      </c>
+      <c r="C203" t="s">
+        <v>125</v>
+      </c>
+      <c r="E203" t="s">
+        <v>15</v>
+      </c>
+      <c r="H203" s="2">
+        <v>45332</v>
+      </c>
+      <c r="I203" s="4">
+        <f t="shared" ca="1" si="43"/>
+        <v>1</v>
+      </c>
+      <c r="J203" s="4">
+        <f t="shared" ca="1" si="44"/>
+        <v>11</v>
+      </c>
+      <c r="L203" s="4" t="str">
+        <f t="shared" si="45"/>
+        <v>-</v>
+      </c>
+      <c r="M203" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="204" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B204" t="s">
+        <v>5</v>
+      </c>
+      <c r="C204" t="s">
+        <v>125</v>
+      </c>
+      <c r="E204" t="s">
+        <v>15</v>
+      </c>
+      <c r="H204" s="2">
+        <v>45332</v>
+      </c>
+      <c r="I204" s="4">
+        <f t="shared" ca="1" si="43"/>
+        <v>1</v>
+      </c>
+      <c r="J204" s="4">
+        <f t="shared" ca="1" si="44"/>
+        <v>11</v>
+      </c>
+      <c r="L204" s="4" t="str">
+        <f t="shared" si="45"/>
+        <v>-</v>
+      </c>
+      <c r="M204" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="205" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B205" t="s">
+        <v>5</v>
+      </c>
+      <c r="C205" t="s">
+        <v>125</v>
+      </c>
+      <c r="E205" t="s">
+        <v>15</v>
+      </c>
+      <c r="H205" s="2">
+        <v>45332</v>
+      </c>
+      <c r="I205" s="4">
+        <f t="shared" ca="1" si="43"/>
+        <v>1</v>
+      </c>
+      <c r="J205" s="4">
+        <f t="shared" ca="1" si="44"/>
+        <v>11</v>
+      </c>
+      <c r="L205" s="4" t="str">
+        <f t="shared" si="45"/>
+        <v>-</v>
+      </c>
+      <c r="M205" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="206" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B206" t="s">
+        <v>5</v>
+      </c>
+      <c r="C206" t="s">
+        <v>125</v>
+      </c>
+      <c r="E206" t="s">
+        <v>15</v>
+      </c>
+      <c r="H206" s="2">
+        <v>45332</v>
+      </c>
+      <c r="I206" s="4">
+        <f t="shared" ca="1" si="43"/>
+        <v>1</v>
+      </c>
+      <c r="J206" s="4">
+        <f t="shared" ca="1" si="44"/>
+        <v>11</v>
+      </c>
+      <c r="L206" s="4" t="str">
+        <f t="shared" si="45"/>
+        <v>-</v>
+      </c>
+      <c r="M206" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="207" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B207" t="s">
+        <v>5</v>
+      </c>
+      <c r="C207" t="s">
+        <v>125</v>
+      </c>
+      <c r="E207" t="s">
+        <v>15</v>
+      </c>
+      <c r="H207" s="2">
+        <v>45332</v>
+      </c>
+      <c r="I207" s="4">
+        <f t="shared" ca="1" si="43"/>
+        <v>1</v>
+      </c>
+      <c r="J207" s="4">
+        <f t="shared" ca="1" si="44"/>
+        <v>11</v>
+      </c>
+      <c r="L207" s="4" t="str">
+        <f t="shared" si="45"/>
+        <v>-</v>
+      </c>
+      <c r="M207" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="208" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B208" t="s">
+        <v>5</v>
+      </c>
+      <c r="C208" t="s">
+        <v>125</v>
+      </c>
+      <c r="E208" t="s">
+        <v>15</v>
+      </c>
+      <c r="H208" s="2">
+        <v>45332</v>
+      </c>
+      <c r="I208" s="4">
+        <f t="shared" ca="1" si="43"/>
+        <v>1</v>
+      </c>
+      <c r="J208" s="4">
+        <f t="shared" ca="1" si="44"/>
+        <v>11</v>
+      </c>
+      <c r="L208" s="4" t="str">
+        <f t="shared" si="45"/>
+        <v>-</v>
+      </c>
+      <c r="M208" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="209" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B209" t="s">
+        <v>5</v>
+      </c>
+      <c r="C209" t="s">
+        <v>125</v>
+      </c>
+      <c r="E209" t="s">
+        <v>15</v>
+      </c>
+      <c r="H209" s="2">
+        <v>45332</v>
+      </c>
+      <c r="I209" s="4">
+        <f t="shared" ca="1" si="43"/>
+        <v>1</v>
+      </c>
+      <c r="J209" s="4">
+        <f t="shared" ca="1" si="44"/>
+        <v>11</v>
+      </c>
+      <c r="L209" s="4" t="str">
+        <f t="shared" si="45"/>
+        <v>-</v>
+      </c>
+      <c r="M209" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="210" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B210" t="s">
+        <v>5</v>
+      </c>
+      <c r="C210" t="s">
+        <v>125</v>
+      </c>
+      <c r="E210" t="s">
+        <v>15</v>
+      </c>
+      <c r="H210" s="2">
+        <v>45332</v>
+      </c>
+      <c r="I210" s="4">
+        <f t="shared" ca="1" si="43"/>
+        <v>1</v>
+      </c>
+      <c r="J210" s="4">
+        <f t="shared" ca="1" si="44"/>
+        <v>11</v>
+      </c>
+      <c r="L210" s="4" t="str">
+        <f t="shared" si="45"/>
+        <v>-</v>
+      </c>
+      <c r="M210" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="211" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B211" t="s">
+        <v>5</v>
+      </c>
+      <c r="C211" t="s">
+        <v>125</v>
+      </c>
+      <c r="E211" t="s">
+        <v>15</v>
+      </c>
+      <c r="H211" s="2">
+        <v>45337</v>
+      </c>
+      <c r="I211" s="4">
+        <f t="shared" ca="1" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="J211" s="4">
+        <f t="shared" ca="1" si="44"/>
+        <v>6</v>
+      </c>
+      <c r="L211" s="4" t="str">
+        <f t="shared" si="45"/>
+        <v>-</v>
+      </c>
+      <c r="M211" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="212" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B212" t="s">
+        <v>5</v>
+      </c>
+      <c r="C212" t="s">
+        <v>125</v>
+      </c>
+      <c r="E212" t="s">
+        <v>15</v>
+      </c>
+      <c r="H212" s="2">
+        <v>45337</v>
+      </c>
+      <c r="I212" s="4">
+        <f t="shared" ca="1" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="J212" s="4">
+        <f t="shared" ca="1" si="44"/>
+        <v>6</v>
+      </c>
+      <c r="L212" s="4" t="str">
+        <f t="shared" si="45"/>
+        <v>-</v>
+      </c>
+      <c r="M212" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="213" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B213" t="s">
+        <v>5</v>
+      </c>
+      <c r="C213" t="s">
+        <v>125</v>
+      </c>
+      <c r="E213" t="s">
+        <v>15</v>
+      </c>
+      <c r="H213" s="2">
+        <v>45337</v>
+      </c>
+      <c r="I213" s="4">
+        <f t="shared" ca="1" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="J213" s="4">
+        <f t="shared" ca="1" si="44"/>
+        <v>6</v>
+      </c>
+      <c r="L213" s="4" t="str">
+        <f t="shared" si="45"/>
+        <v>-</v>
+      </c>
+      <c r="M213" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="214" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B214" t="s">
+        <v>5</v>
+      </c>
+      <c r="C214" t="s">
+        <v>125</v>
+      </c>
+      <c r="E214" t="s">
+        <v>15</v>
+      </c>
+      <c r="H214" s="2">
+        <v>45337</v>
+      </c>
+      <c r="I214" s="4">
+        <f t="shared" ca="1" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="J214" s="4">
+        <f t="shared" ca="1" si="44"/>
+        <v>6</v>
+      </c>
+      <c r="L214" s="4" t="str">
+        <f t="shared" si="45"/>
+        <v>-</v>
+      </c>
+      <c r="M214" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="215" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B215" t="s">
+        <v>5</v>
+      </c>
+      <c r="C215" t="s">
+        <v>125</v>
+      </c>
+      <c r="E215" t="s">
+        <v>15</v>
+      </c>
+      <c r="H215" s="2">
+        <v>45337</v>
+      </c>
+      <c r="I215" s="4">
+        <f t="shared" ca="1" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="J215" s="4">
+        <f t="shared" ca="1" si="44"/>
+        <v>6</v>
+      </c>
+      <c r="L215" s="4" t="str">
+        <f t="shared" si="45"/>
+        <v>-</v>
+      </c>
+      <c r="M215" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="216" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B216" t="s">
+        <v>5</v>
+      </c>
+      <c r="C216" t="s">
+        <v>125</v>
+      </c>
+      <c r="E216" t="s">
+        <v>15</v>
+      </c>
+      <c r="H216" s="2">
+        <v>45337</v>
+      </c>
+      <c r="I216" s="4">
+        <f t="shared" ca="1" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="J216" s="4">
+        <f t="shared" ca="1" si="44"/>
+        <v>6</v>
+      </c>
+      <c r="L216" s="4" t="str">
+        <f t="shared" si="45"/>
+        <v>-</v>
+      </c>
+      <c r="M216" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="217" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B217" t="s">
+        <v>5</v>
+      </c>
+      <c r="C217" t="s">
+        <v>125</v>
+      </c>
+      <c r="E217" t="s">
+        <v>15</v>
+      </c>
+      <c r="H217" s="2">
+        <v>45337</v>
+      </c>
+      <c r="I217" s="4">
+        <f t="shared" ca="1" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="J217" s="4">
+        <f t="shared" ca="1" si="44"/>
+        <v>6</v>
+      </c>
+      <c r="L217" s="4" t="str">
+        <f t="shared" si="45"/>
+        <v>-</v>
+      </c>
+      <c r="M217" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="218" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B218" t="s">
+        <v>5</v>
+      </c>
+      <c r="C218" t="s">
+        <v>124</v>
+      </c>
+      <c r="E218" t="s">
+        <v>228</v>
+      </c>
+      <c r="M218" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="Q218" t="s">
+        <v>229</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="B1:Q200" xr:uid="{47ECCD65-6802-4B2B-901A-AED4A431A765}">
+  <autoFilter ref="B1:Q218" xr:uid="{47ECCD65-6802-4B2B-901A-AED4A431A765}">
     <filterColumn colId="0">
       <filters>
-        <filter val="5F"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="1">
-      <filters>
-        <filter val="Tmem119-CreERT2; Tsg101-flox"/>
+        <filter val="SPF"/>
       </filters>
     </filterColumn>
     <filterColumn colId="13">

--- a/Mouse 내역.xlsx
+++ b/Mouse 내역.xlsx
@@ -8,17 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\heung\Dropbox\02. Lab. of Host Defenses\03. 동물실\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6F30E2B-F9E9-4366-9D52-837653D94A71}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ADBE4D3-0F15-4DDE-BBD0-52A205F2E411}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="495" windowWidth="28800" windowHeight="16245" xr2:uid="{5A73A69A-2AFB-4F3E-AC64-070DD7700CB2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet1 (2)" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="4" r:id="rId3"/>
+    <sheet name="Sheet1 (2)" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$Q$218</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$Q$232</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1435" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1509" uniqueCount="236">
   <si>
     <t>Strain</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -679,14 +680,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>나중에 H3.B의 female과 breader?</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>geno</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>H5.B</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -755,10 +748,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Breader A4.B</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>A5.B</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -931,11 +920,43 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>몇마리인지 확인</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Exp. 1-10-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>H8.1.X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>H9.1.X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>N</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>죽임</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>weaning, genotyping</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>genotyping</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>genotyping</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>죽이기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>몇마리인지 확인, 주령도 확인</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1792,7 +1813,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D71A6DC-E91C-489F-8F50-989C4712FA7C}">
   <sheetPr filterMode="1"/>
-  <dimension ref="B1:Q218"/>
+  <dimension ref="B1:Q232"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="10.5" customWidth="1"/>
@@ -1880,11 +1901,11 @@
       </c>
       <c r="I2" s="4">
         <f ca="1">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H2), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H2), 7), "-")</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J2" s="4">
         <f ca="1">IF(_xlfn.DAYS(TODAY(),H2)&lt;10000, _xlfn.DAYS(TODAY(),H2), "-")</f>
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="L2" s="4" t="str">
         <f t="shared" ref="L2:L31" si="0">IF(_xlfn.DAYS(K2,H2)&gt;0, _xlfn.DAYS(K2,H2), "-")</f>
@@ -1898,7 +1919,7 @@
         <v>45299</v>
       </c>
     </row>
-    <row r="3" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>5</v>
       </c>
@@ -1919,11 +1940,11 @@
       </c>
       <c r="I3" s="4">
         <f t="shared" ref="I3:I65" ca="1" si="1">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H3), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H3), 7), "-")</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J3" s="4">
         <f t="shared" ref="J3:J31" ca="1" si="2">IF(_xlfn.DAYS(TODAY(),H3)&lt;10000, _xlfn.DAYS(TODAY(),H3), "-")</f>
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="L3" s="4" t="str">
         <f t="shared" si="0"/>
@@ -1935,7 +1956,7 @@
       <c r="N3" s="7"/>
       <c r="O3" s="7"/>
     </row>
-    <row r="4" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>5</v>
       </c>
@@ -1956,11 +1977,11 @@
       </c>
       <c r="I4" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J4" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="L4" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2000,7 +2021,7 @@
       </c>
       <c r="J5" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="K5" s="2">
         <v>45293</v>
@@ -2045,7 +2066,7 @@
       </c>
       <c r="J6" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="K6" s="2">
         <v>45293</v>
@@ -2063,7 +2084,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>5</v>
       </c>
@@ -2091,7 +2112,7 @@
       </c>
       <c r="J7" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="K7" s="2">
         <v>45293</v>
@@ -2101,13 +2122,10 @@
         <v>27</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="N7" s="7"/>
       <c r="O7" s="7"/>
-      <c r="Q7" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="8" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
@@ -2137,7 +2155,7 @@
       </c>
       <c r="J8" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="K8" s="2">
         <v>45293</v>
@@ -2157,7 +2175,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>5</v>
       </c>
@@ -2185,7 +2203,7 @@
       </c>
       <c r="J9" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="K9" s="2">
         <v>45293</v>
@@ -2228,7 +2246,7 @@
       </c>
       <c r="J10" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="K10" s="2">
         <v>45293</v>
@@ -2273,7 +2291,7 @@
       </c>
       <c r="J11" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="K11" s="2">
         <v>45293</v>
@@ -2311,11 +2329,11 @@
       </c>
       <c r="I12" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J12" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="L12" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2401,7 +2419,7 @@
         <v>45299</v>
       </c>
     </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>5</v>
       </c>
@@ -2425,11 +2443,11 @@
       </c>
       <c r="I15" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J15" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="L15" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2440,8 +2458,11 @@
       </c>
       <c r="N15" s="7"/>
       <c r="O15" s="7"/>
-    </row>
-    <row r="16" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="Q15" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="16" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>5</v>
       </c>
@@ -2465,11 +2486,11 @@
       </c>
       <c r="I16" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J16" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="L16" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2480,8 +2501,11 @@
       </c>
       <c r="N16" s="7"/>
       <c r="O16" s="7"/>
-    </row>
-    <row r="17" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="Q16" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="17" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>5</v>
       </c>
@@ -2505,11 +2529,11 @@
       </c>
       <c r="I17" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J17" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="L17" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2517,6 +2541,9 @@
       </c>
       <c r="M17" s="4" t="s">
         <v>51</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="18" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -2543,11 +2570,11 @@
       </c>
       <c r="I18" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J18" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="L18" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2560,7 +2587,7 @@
         <v>45327</v>
       </c>
     </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>5</v>
       </c>
@@ -2584,11 +2611,11 @@
       </c>
       <c r="I19" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J19" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="L19" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2596,6 +2623,9 @@
       </c>
       <c r="M19" s="4" t="s">
         <v>51</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="20" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -2623,7 +2653,7 @@
       </c>
       <c r="J20" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="L20" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2692,11 +2722,11 @@
       </c>
       <c r="I22" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J22" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="K22" s="2">
         <v>45112</v>
@@ -2737,7 +2767,7 @@
       </c>
       <c r="J23" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="K23" s="2">
         <v>45176</v>
@@ -2781,7 +2811,7 @@
       </c>
       <c r="J24" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="K24" s="2">
         <v>45176</v>
@@ -2825,7 +2855,7 @@
       </c>
       <c r="J25" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="K25" s="2">
         <v>45176</v>
@@ -2844,7 +2874,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="26" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>5</v>
       </c>
@@ -2869,7 +2899,7 @@
       </c>
       <c r="J26" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="K26" s="2">
         <v>45176</v>
@@ -2879,11 +2909,11 @@
         <v>22</v>
       </c>
       <c r="M26" s="4" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="Q26" s="2"/>
     </row>
-    <row r="27" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>5</v>
       </c>
@@ -2908,7 +2938,7 @@
       </c>
       <c r="J27" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="K27" s="2">
         <v>45176</v>
@@ -2918,7 +2948,7 @@
         <v>22</v>
       </c>
       <c r="M27" s="4" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="Q27" s="2"/>
     </row>
@@ -2947,7 +2977,7 @@
       </c>
       <c r="J28" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="K28" s="2">
         <v>45229</v>
@@ -2988,7 +3018,7 @@
       </c>
       <c r="J29" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="K29" s="2">
         <v>45229</v>
@@ -3004,7 +3034,7 @@
         <v>45310</v>
       </c>
     </row>
-    <row r="30" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>5</v>
       </c>
@@ -3029,7 +3059,7 @@
       </c>
       <c r="J30" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="K30" s="2">
         <v>45229</v>
@@ -3043,7 +3073,7 @@
       </c>
       <c r="Q30" s="2"/>
     </row>
-    <row r="31" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
         <v>5</v>
       </c>
@@ -3068,7 +3098,7 @@
       </c>
       <c r="J31" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="K31" s="2">
         <v>45229</v>
@@ -3082,7 +3112,7 @@
       </c>
       <c r="Q31" s="2"/>
     </row>
-    <row r="32" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
         <v>5</v>
       </c>
@@ -3107,7 +3137,7 @@
       </c>
       <c r="J32" s="4">
         <f t="shared" ref="J32:J38" ca="1" si="3">IF(_xlfn.DAYS(TODAY(),H32)&lt;10000, _xlfn.DAYS(TODAY(),H32), "-")</f>
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="K32" s="2">
         <v>45229</v>
@@ -3117,7 +3147,7 @@
         <v>26</v>
       </c>
       <c r="M32" s="4" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="Q32" s="2"/>
     </row>
@@ -3184,7 +3214,7 @@
       </c>
       <c r="J34" s="4">
         <f ca="1">IF(_xlfn.DAYS(TODAY(),H34)&lt;10000, _xlfn.DAYS(TODAY(),H34), "-")</f>
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="K34" s="2">
         <v>45257</v>
@@ -3307,7 +3337,7 @@
       </c>
       <c r="J37" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="K37" s="2">
         <v>45257</v>
@@ -3354,7 +3384,7 @@
       </c>
       <c r="J38" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="K38" s="2">
         <v>45257</v>
@@ -3401,7 +3431,7 @@
       </c>
       <c r="J39" s="4">
         <f t="shared" ref="J39:J41" ca="1" si="5">IF(_xlfn.DAYS(TODAY(),H39)&lt;10000, _xlfn.DAYS(TODAY(),H39), "-")</f>
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="K39" s="2">
         <v>45257</v>
@@ -3448,7 +3478,7 @@
       </c>
       <c r="J40" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="K40" s="2">
         <v>45257</v>
@@ -3492,7 +3522,7 @@
       </c>
       <c r="J41" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="K41" s="2">
         <v>45257</v>
@@ -3532,11 +3562,11 @@
       </c>
       <c r="I42" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J42" s="4">
         <f t="shared" ref="J42" ca="1" si="6">IF(_xlfn.DAYS(TODAY(),H42)&lt;10000, _xlfn.DAYS(TODAY(),H42), "-")</f>
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="L42" s="4" t="str">
         <f t="shared" si="4"/>
@@ -3549,7 +3579,7 @@
         <v>45309</v>
       </c>
     </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B43" t="s">
         <v>5</v>
       </c>
@@ -3573,18 +3603,18 @@
       </c>
       <c r="I43" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J43" s="4">
         <f t="shared" ref="J43:J91" ca="1" si="7">IF(_xlfn.DAYS(TODAY(),H43)&lt;10000, _xlfn.DAYS(TODAY(),H43), "-")</f>
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="L43" s="4" t="str">
         <f t="shared" si="4"/>
         <v>-</v>
       </c>
       <c r="M43" s="4" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="44" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -3611,11 +3641,11 @@
       </c>
       <c r="I44" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J44" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K44" s="2">
         <v>45293</v>
@@ -3655,11 +3685,11 @@
       </c>
       <c r="I45" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J45" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K45" s="2">
         <v>45293</v>
@@ -3699,11 +3729,11 @@
       </c>
       <c r="I46" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J46" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K46" s="2">
         <v>45293</v>
@@ -3746,11 +3776,11 @@
       </c>
       <c r="I47" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J47" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K47" s="2">
         <v>45293</v>
@@ -3793,11 +3823,11 @@
       </c>
       <c r="I48" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J48" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="K48" s="2">
         <v>45293</v>
@@ -3816,7 +3846,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="49" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B49" t="s">
         <v>5</v>
       </c>
@@ -3840,11 +3870,11 @@
       </c>
       <c r="I49" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J49" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K49" s="2">
         <v>45293</v>
@@ -3857,7 +3887,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="50" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B50" t="s">
         <v>5</v>
       </c>
@@ -3881,11 +3911,11 @@
       </c>
       <c r="I50" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J50" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K50" s="2">
         <v>45293</v>
@@ -3922,11 +3952,11 @@
       </c>
       <c r="I51" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J51" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K51" s="2">
         <v>45293</v>
@@ -3966,11 +3996,11 @@
       </c>
       <c r="I52" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J52" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="K52" s="2">
         <v>45293</v>
@@ -3986,7 +4016,7 @@
         <v>45309</v>
       </c>
     </row>
-    <row r="53" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B53" t="s">
         <v>5</v>
       </c>
@@ -4010,11 +4040,11 @@
       </c>
       <c r="I53" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J53" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="K53" s="2">
         <v>45293</v>
@@ -4051,11 +4081,11 @@
       </c>
       <c r="I54" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J54" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="K54" s="2">
         <v>45238</v>
@@ -4068,7 +4098,7 @@
         <v>42</v>
       </c>
       <c r="Q54" s="17" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="55" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -4095,11 +4125,11 @@
       </c>
       <c r="I55" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J55" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="K55" s="2">
         <v>45238</v>
@@ -4112,7 +4142,7 @@
         <v>42</v>
       </c>
       <c r="Q55" s="17" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="56" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -4139,11 +4169,11 @@
       </c>
       <c r="I56" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J56" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="K56" s="2">
         <v>45238</v>
@@ -4156,7 +4186,7 @@
         <v>42</v>
       </c>
       <c r="Q56" s="17" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="57" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -4184,7 +4214,7 @@
       </c>
       <c r="J57" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="L57" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4194,7 +4224,7 @@
         <v>43</v>
       </c>
       <c r="Q57" s="17" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="58" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -4222,7 +4252,7 @@
       </c>
       <c r="J58" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="L58" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4232,7 +4262,7 @@
         <v>43</v>
       </c>
       <c r="Q58" s="17" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="59" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -4253,11 +4283,11 @@
       </c>
       <c r="I59" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J59" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K59" s="2">
         <v>45295</v>
@@ -4270,7 +4300,7 @@
         <v>44</v>
       </c>
       <c r="Q59" s="17" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="60" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -4291,11 +4321,11 @@
       </c>
       <c r="I60" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J60" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K60" s="2">
         <v>45295</v>
@@ -4308,7 +4338,7 @@
         <v>98</v>
       </c>
       <c r="Q60" s="18" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="61" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -4329,11 +4359,11 @@
       </c>
       <c r="I61" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J61" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K61" s="2">
         <v>45295</v>
@@ -4364,11 +4394,11 @@
       </c>
       <c r="I62" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J62" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K62" s="2">
         <v>45295</v>
@@ -4386,7 +4416,7 @@
         <v>27</v>
       </c>
       <c r="C63" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E63" t="s">
         <v>26</v>
@@ -4399,11 +4429,11 @@
       </c>
       <c r="I63" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J63" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K63" s="2">
         <v>45295</v>
@@ -4416,7 +4446,7 @@
         <v>99</v>
       </c>
       <c r="P63" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
     </row>
     <row r="64" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -4437,11 +4467,11 @@
       </c>
       <c r="I64" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J64" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K64" s="2">
         <v>45295</v>
@@ -4454,7 +4484,7 @@
         <v>99</v>
       </c>
       <c r="P64" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
     </row>
     <row r="65" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -4482,7 +4512,7 @@
       </c>
       <c r="J65" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="L65" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4492,7 +4522,7 @@
         <v>44</v>
       </c>
       <c r="Q65" s="17" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="66" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -4520,7 +4550,7 @@
       </c>
       <c r="J66" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="L66" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4530,7 +4560,7 @@
         <v>44</v>
       </c>
       <c r="Q66" s="17" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="67" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -4561,7 +4591,7 @@
       </c>
       <c r="J67" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="L67" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4611,7 +4641,7 @@
       </c>
       <c r="J68" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="L68" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4661,7 +4691,7 @@
       </c>
       <c r="J69" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="L69" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4711,7 +4741,7 @@
       </c>
       <c r="J70" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="L70" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4761,7 +4791,7 @@
       </c>
       <c r="J71" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="L71" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4811,7 +4841,7 @@
       </c>
       <c r="J72" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="L72" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4861,7 +4891,7 @@
       </c>
       <c r="J73" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="L73" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4911,7 +4941,7 @@
       </c>
       <c r="J74" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="L74" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4961,7 +4991,7 @@
       </c>
       <c r="J75" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="L75" s="4" t="str">
         <f t="shared" si="4"/>
@@ -5011,7 +5041,7 @@
       </c>
       <c r="J76" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="L76" s="4" t="str">
         <f t="shared" si="4"/>
@@ -5061,7 +5091,7 @@
       </c>
       <c r="J77" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="L77" s="4" t="str">
         <f t="shared" si="4"/>
@@ -5111,7 +5141,7 @@
       </c>
       <c r="J78" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="L78" s="4" t="str">
         <f t="shared" si="4"/>
@@ -5161,7 +5191,7 @@
       </c>
       <c r="J79" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="L79" s="4" t="str">
         <f t="shared" si="4"/>
@@ -5211,7 +5241,7 @@
       </c>
       <c r="J80" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="L80" s="4" t="str">
         <f t="shared" si="4"/>
@@ -5261,7 +5291,7 @@
       </c>
       <c r="J81" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="L81" s="4" t="str">
         <f t="shared" si="4"/>
@@ -5311,7 +5341,7 @@
       </c>
       <c r="J82" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="L82" s="4" t="str">
         <f t="shared" si="4"/>
@@ -5361,7 +5391,7 @@
       </c>
       <c r="J83" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="L83" s="4" t="str">
         <f t="shared" si="4"/>
@@ -5411,7 +5441,7 @@
       </c>
       <c r="J84" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="L84" s="4" t="str">
         <f t="shared" si="4"/>
@@ -5461,7 +5491,7 @@
       </c>
       <c r="J85" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="L85" s="4" t="str">
         <f t="shared" si="4"/>
@@ -5511,7 +5541,7 @@
       </c>
       <c r="J86" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="L86" s="4" t="str">
         <f t="shared" si="4"/>
@@ -5561,7 +5591,7 @@
       </c>
       <c r="J87" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="K87" s="2">
         <v>45272</v>
@@ -5611,7 +5641,7 @@
       </c>
       <c r="J88" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="K88" s="2">
         <v>45273</v>
@@ -5661,7 +5691,7 @@
       </c>
       <c r="J89" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="K89" s="2">
         <v>45274</v>
@@ -5711,7 +5741,7 @@
       </c>
       <c r="J90" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="K90" s="2">
         <v>45275</v>
@@ -5761,7 +5791,7 @@
       </c>
       <c r="J91" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="K91" s="2">
         <v>45276</v>
@@ -5811,7 +5841,7 @@
       </c>
       <c r="J92" s="4">
         <f t="shared" ref="J92:J93" ca="1" si="10">IF(_xlfn.DAYS(TODAY(),H92)&lt;10000, _xlfn.DAYS(TODAY(),H92), "-")</f>
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="K92" s="2">
         <v>45277</v>
@@ -5861,7 +5891,7 @@
       </c>
       <c r="J93" s="4">
         <f t="shared" ca="1" si="10"/>
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="K93" s="2">
         <v>45278</v>
@@ -5907,11 +5937,11 @@
       </c>
       <c r="I94" s="4">
         <f t="shared" ref="I94" ca="1" si="11">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H94), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H94), 7), "-")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J94" s="4">
         <f t="shared" ref="J94" ca="1" si="12">IF(_xlfn.DAYS(TODAY(),H94)&lt;10000, _xlfn.DAYS(TODAY(),H94), "-")</f>
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="K94" s="2">
         <v>45223</v>
@@ -5957,11 +5987,11 @@
       </c>
       <c r="I95" s="4">
         <f t="shared" ref="I95:I117" ca="1" si="13">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H95), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H95), 7), "-")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J95" s="4">
         <f t="shared" ref="J95:J117" ca="1" si="14">IF(_xlfn.DAYS(TODAY(),H95)&lt;10000, _xlfn.DAYS(TODAY(),H95), "-")</f>
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="K95" s="2">
         <v>45223</v>
@@ -6007,11 +6037,11 @@
       </c>
       <c r="I96" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J96" s="4">
         <f t="shared" ca="1" si="14"/>
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="K96" s="2">
         <v>45223</v>
@@ -6057,11 +6087,11 @@
       </c>
       <c r="I97" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J97" s="4">
         <f t="shared" ca="1" si="14"/>
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="K97" s="2">
         <v>45223</v>
@@ -6107,11 +6137,11 @@
       </c>
       <c r="I98" s="4">
         <f t="shared" ref="I98:I107" ca="1" si="16">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H98), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H98), 7), "-")</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J98" s="4">
         <f t="shared" ref="J98:J107" ca="1" si="17">IF(_xlfn.DAYS(TODAY(),H98)&lt;10000, _xlfn.DAYS(TODAY(),H98), "-")</f>
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="K98" s="2">
         <v>45267</v>
@@ -6160,11 +6190,11 @@
       </c>
       <c r="I99" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J99" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="K99" s="2">
         <v>45267</v>
@@ -6213,11 +6243,11 @@
       </c>
       <c r="I100" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J100" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="K100" s="2">
         <v>45267</v>
@@ -6266,11 +6296,11 @@
       </c>
       <c r="I101" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J101" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="K101" s="2">
         <v>45267</v>
@@ -6319,11 +6349,11 @@
       </c>
       <c r="I102" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J102" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="K102" s="2">
         <v>45267</v>
@@ -6372,11 +6402,11 @@
       </c>
       <c r="I103" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J103" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="K103" s="2">
         <v>45267</v>
@@ -6425,11 +6455,11 @@
       </c>
       <c r="I104" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J104" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="K104" s="2">
         <v>45267</v>
@@ -6478,11 +6508,11 @@
       </c>
       <c r="I105" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J105" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="K105" s="2">
         <v>45267</v>
@@ -6531,11 +6561,11 @@
       </c>
       <c r="I106" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J106" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="K106" s="2">
         <v>45267</v>
@@ -6584,11 +6614,11 @@
       </c>
       <c r="I107" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J107" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="K107" s="2">
         <v>45267</v>
@@ -7108,7 +7138,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="120" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="120" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B120" t="s">
         <v>88</v>
       </c>
@@ -7132,11 +7162,11 @@
       </c>
       <c r="I120" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J120" s="4">
         <f t="shared" ca="1" si="19"/>
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="K120" s="2">
         <v>45315</v>
@@ -7149,7 +7179,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="121" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="121" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B121" t="s">
         <v>88</v>
       </c>
@@ -7173,11 +7203,11 @@
       </c>
       <c r="I121" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J121" s="4">
         <f t="shared" ca="1" si="19"/>
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="K121" s="2">
         <v>45315</v>
@@ -7187,13 +7217,10 @@
         <v>24</v>
       </c>
       <c r="M121" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="Q121" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="122" spans="2:17" x14ac:dyDescent="0.3">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="122" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B122" t="s">
         <v>88</v>
       </c>
@@ -7217,11 +7244,11 @@
       </c>
       <c r="I122" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J122" s="4">
         <f t="shared" ca="1" si="19"/>
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="K122" s="2">
         <v>45315</v>
@@ -7234,7 +7261,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="123" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="123" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B123" t="s">
         <v>88</v>
       </c>
@@ -7258,11 +7285,11 @@
       </c>
       <c r="I123" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J123" s="4">
         <f t="shared" ca="1" si="19"/>
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="K123" s="2">
         <v>45315</v>
@@ -7275,7 +7302,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="124" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="124" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B124" t="s">
         <v>113</v>
       </c>
@@ -7290,21 +7317,24 @@
       </c>
       <c r="I124" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J124" s="4">
         <f t="shared" ca="1" si="19"/>
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="L124" s="4" t="str">
         <f t="shared" si="15"/>
         <v>-</v>
       </c>
       <c r="M124" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="125" spans="2:17" x14ac:dyDescent="0.3">
+        <v>220</v>
+      </c>
+      <c r="Q124" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="125" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B125" t="s">
         <v>113</v>
       </c>
@@ -7319,21 +7349,24 @@
       </c>
       <c r="I125" s="4">
         <f t="shared" ref="I125:I127" ca="1" si="20">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H125), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H125), 7), "-")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J125" s="4">
         <f t="shared" ref="J125:J127" ca="1" si="21">IF(_xlfn.DAYS(TODAY(),H125)&lt;10000, _xlfn.DAYS(TODAY(),H125), "-")</f>
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="L125" s="4" t="str">
         <f t="shared" si="15"/>
         <v>-</v>
       </c>
       <c r="M125" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="126" spans="2:17" x14ac:dyDescent="0.3">
+        <v>220</v>
+      </c>
+      <c r="Q125" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="126" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B126" t="s">
         <v>113</v>
       </c>
@@ -7348,21 +7381,24 @@
       </c>
       <c r="I126" s="4">
         <f t="shared" ca="1" si="20"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J126" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="L126" s="4" t="str">
         <f t="shared" si="15"/>
         <v>-</v>
       </c>
       <c r="M126" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="127" spans="2:17" x14ac:dyDescent="0.3">
+        <v>221</v>
+      </c>
+      <c r="Q126" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="127" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B127" t="s">
         <v>113</v>
       </c>
@@ -7377,21 +7413,24 @@
       </c>
       <c r="I127" s="4">
         <f t="shared" ca="1" si="20"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J127" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="L127" s="4" t="str">
         <f t="shared" si="15"/>
         <v>-</v>
       </c>
       <c r="M127" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="128" spans="2:17" x14ac:dyDescent="0.3">
+        <v>221</v>
+      </c>
+      <c r="Q127" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="128" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B128" t="s">
         <v>114</v>
       </c>
@@ -7406,21 +7445,24 @@
       </c>
       <c r="I128" s="4">
         <f t="shared" ref="I128:I130" ca="1" si="22">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H128), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H128), 7), "-")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J128" s="4">
         <f t="shared" ref="J128:J130" ca="1" si="23">IF(_xlfn.DAYS(TODAY(),H128)&lt;10000, _xlfn.DAYS(TODAY(),H128), "-")</f>
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="L128" s="4" t="str">
         <f t="shared" si="15"/>
         <v>-</v>
       </c>
       <c r="M128" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="129" spans="2:17" x14ac:dyDescent="0.3">
+        <v>221</v>
+      </c>
+      <c r="Q128" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="129" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B129" t="s">
         <v>114</v>
       </c>
@@ -7435,21 +7477,24 @@
       </c>
       <c r="I129" s="4">
         <f t="shared" ca="1" si="22"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J129" s="4">
         <f t="shared" ca="1" si="23"/>
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="L129" s="4" t="str">
         <f t="shared" si="15"/>
         <v>-</v>
       </c>
       <c r="M129" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="130" spans="2:17" x14ac:dyDescent="0.3">
+        <v>221</v>
+      </c>
+      <c r="Q129" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="130" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B130" t="s">
         <v>114</v>
       </c>
@@ -7464,18 +7509,21 @@
       </c>
       <c r="I130" s="4">
         <f t="shared" ca="1" si="22"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J130" s="4">
         <f t="shared" ca="1" si="23"/>
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="L130" s="4" t="str">
         <f t="shared" si="15"/>
         <v>-</v>
       </c>
       <c r="M130" t="s">
-        <v>224</v>
+        <v>221</v>
+      </c>
+      <c r="Q130" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="131" spans="2:17" x14ac:dyDescent="0.3">
@@ -7486,7 +7534,7 @@
         <v>124</v>
       </c>
       <c r="F131" s="10" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="G131" t="s">
         <v>119</v>
@@ -7525,11 +7573,11 @@
       </c>
       <c r="I132" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J132" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="L132" s="4" t="str">
         <f t="shared" si="26"/>
@@ -7560,11 +7608,11 @@
       </c>
       <c r="I133" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J133" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="L133" s="4" t="str">
         <f t="shared" si="26"/>
@@ -7592,11 +7640,11 @@
       </c>
       <c r="I134" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J134" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="L134" s="4" t="str">
         <f t="shared" si="26"/>
@@ -7624,11 +7672,11 @@
       </c>
       <c r="I135" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J135" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="L135" s="4" t="str">
         <f t="shared" si="26"/>
@@ -7659,11 +7707,11 @@
       </c>
       <c r="I136" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J136" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="L136" s="4" t="str">
         <f t="shared" si="26"/>
@@ -7691,11 +7739,11 @@
       </c>
       <c r="I137" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J137" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="L137" s="4" t="str">
         <f t="shared" si="26"/>
@@ -7705,7 +7753,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="138" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="138" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B138" t="s">
         <v>141</v>
       </c>
@@ -7731,7 +7779,7 @@
         <v>-</v>
       </c>
       <c r="M138" s="4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="139" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -7766,7 +7814,7 @@
         <v>45322</v>
       </c>
     </row>
-    <row r="140" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="140" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B140" t="s">
         <v>141</v>
       </c>
@@ -7792,10 +7840,10 @@
         <v>-</v>
       </c>
       <c r="M140" s="4" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="141" spans="2:17" x14ac:dyDescent="0.3">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="141" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B141" t="s">
         <v>141</v>
       </c>
@@ -7814,20 +7862,20 @@
       </c>
       <c r="J141" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="L141" s="4" t="str">
         <f t="shared" si="26"/>
         <v>-</v>
       </c>
       <c r="M141" s="4" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="Q141" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="142" spans="2:17" x14ac:dyDescent="0.3">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="142" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B142" t="s">
         <v>141</v>
       </c>
@@ -7846,20 +7894,20 @@
       </c>
       <c r="J142" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="L142" s="4" t="str">
         <f t="shared" si="26"/>
         <v>-</v>
       </c>
       <c r="M142" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="Q142" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="143" spans="2:17" x14ac:dyDescent="0.3">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="143" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B143" t="s">
         <v>141</v>
       </c>
@@ -7878,20 +7926,20 @@
       </c>
       <c r="J143" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="L143" s="4" t="str">
         <f t="shared" si="26"/>
         <v>-</v>
       </c>
       <c r="M143" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="Q143" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="144" spans="2:17" x14ac:dyDescent="0.3">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="144" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B144" t="s">
         <v>141</v>
       </c>
@@ -7910,20 +7958,20 @@
       </c>
       <c r="J144" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="L144" s="4" t="str">
         <f t="shared" si="26"/>
         <v>-</v>
       </c>
       <c r="M144" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="Q144" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="145" spans="2:17" x14ac:dyDescent="0.3">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="145" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B145" t="s">
         <v>141</v>
       </c>
@@ -7942,20 +7990,20 @@
       </c>
       <c r="J145" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="L145" s="4" t="str">
         <f t="shared" si="26"/>
         <v>-</v>
       </c>
       <c r="M145" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="Q145" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="146" spans="2:17" x14ac:dyDescent="0.3">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="146" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B146" t="s">
         <v>141</v>
       </c>
@@ -7974,20 +8022,20 @@
       </c>
       <c r="J146" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="L146" s="4" t="str">
         <f t="shared" si="26"/>
         <v>-</v>
       </c>
       <c r="M146" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="Q146" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="147" spans="2:17" x14ac:dyDescent="0.3">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="147" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B147" t="s">
         <v>141</v>
       </c>
@@ -8016,7 +8064,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="148" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="148" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B148" t="s">
         <v>141</v>
       </c>
@@ -8042,10 +8090,10 @@
         <v>-</v>
       </c>
       <c r="M148" s="4" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="149" spans="2:17" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="149" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B149" t="s">
         <v>141</v>
       </c>
@@ -8074,7 +8122,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="150" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="150" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B150" t="s">
         <v>141</v>
       </c>
@@ -8103,7 +8151,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="151" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="151" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B151" t="s">
         <v>141</v>
       </c>
@@ -8118,21 +8166,21 @@
       </c>
       <c r="I151" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J151" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="L151" s="4" t="str">
         <f t="shared" si="29"/>
         <v>-</v>
       </c>
       <c r="M151" s="4" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="152" spans="2:17" x14ac:dyDescent="0.3">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="152" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B152" t="s">
         <v>141</v>
       </c>
@@ -8147,21 +8195,21 @@
       </c>
       <c r="I152" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J152" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="L152" s="4" t="str">
         <f t="shared" si="29"/>
         <v>-</v>
       </c>
       <c r="M152" s="4" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="153" spans="2:17" x14ac:dyDescent="0.3">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="153" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B153" t="s">
         <v>141</v>
       </c>
@@ -8176,21 +8224,21 @@
       </c>
       <c r="I153" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J153" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="L153" s="4" t="str">
         <f t="shared" si="29"/>
         <v>-</v>
       </c>
       <c r="M153" s="4" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="154" spans="2:17" x14ac:dyDescent="0.3">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="154" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B154" t="s">
         <v>141</v>
       </c>
@@ -8205,21 +8253,21 @@
       </c>
       <c r="I154" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J154" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="L154" s="4" t="str">
         <f t="shared" si="29"/>
         <v>-</v>
       </c>
       <c r="M154" s="4" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="155" spans="2:17" x14ac:dyDescent="0.3">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="155" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B155" t="s">
         <v>141</v>
       </c>
@@ -8234,21 +8282,21 @@
       </c>
       <c r="I155" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J155" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="L155" s="4" t="str">
         <f t="shared" si="29"/>
         <v>-</v>
       </c>
       <c r="M155" s="4" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="156" spans="2:17" x14ac:dyDescent="0.3">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="156" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B156" t="s">
         <v>141</v>
       </c>
@@ -8263,18 +8311,18 @@
       </c>
       <c r="I156" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J156" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="L156" s="4" t="str">
         <f t="shared" si="29"/>
         <v>-</v>
       </c>
       <c r="M156" s="4" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="157" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -8305,7 +8353,7 @@
       </c>
       <c r="J157" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="L157" s="4" t="str">
         <f t="shared" si="29"/>
@@ -8318,10 +8366,10 @@
         <v>45322</v>
       </c>
       <c r="P157" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="Q157" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="158" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -8359,7 +8407,7 @@
         <v>45329</v>
       </c>
     </row>
-    <row r="159" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="159" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B159" t="s">
         <v>141</v>
       </c>
@@ -8388,10 +8436,10 @@
         <v>-</v>
       </c>
       <c r="M159" s="4" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="160" spans="2:17" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="160" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B160" t="s">
         <v>141</v>
       </c>
@@ -8420,10 +8468,10 @@
         <v>-</v>
       </c>
       <c r="M160" s="4" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="161" spans="2:17" x14ac:dyDescent="0.3">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="161" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B161" t="s">
         <v>141</v>
       </c>
@@ -8447,11 +8495,11 @@
       </c>
       <c r="I161" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J161" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="K161" s="2">
         <v>45301</v>
@@ -8461,10 +8509,10 @@
         <v>32</v>
       </c>
       <c r="M161" s="4" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="162" spans="2:17" x14ac:dyDescent="0.3">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="162" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B162" t="s">
         <v>141</v>
       </c>
@@ -8488,11 +8536,11 @@
       </c>
       <c r="I162" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J162" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="K162" s="2">
         <v>45301</v>
@@ -8502,7 +8550,7 @@
         <v>32</v>
       </c>
       <c r="M162" s="4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="163" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -8526,11 +8574,11 @@
       </c>
       <c r="I163" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J163" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="K163" s="2">
         <v>45301</v>
@@ -8549,7 +8597,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="164" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="164" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B164" t="s">
         <v>141</v>
       </c>
@@ -8573,11 +8621,11 @@
       </c>
       <c r="I164" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J164" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="K164" s="2">
         <v>45301</v>
@@ -8587,7 +8635,7 @@
         <v>32</v>
       </c>
       <c r="M164" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="165" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -8614,11 +8662,11 @@
       </c>
       <c r="I165" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J165" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="K165" s="2">
         <v>45301</v>
@@ -8633,14 +8681,17 @@
       <c r="N165" s="2">
         <v>45322</v>
       </c>
+      <c r="O165" s="2">
+        <v>45335</v>
+      </c>
       <c r="P165" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="Q165" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="166" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="166" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B166" t="s">
         <v>141</v>
       </c>
@@ -8664,11 +8715,11 @@
       </c>
       <c r="I166" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J166" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="K166" s="2">
         <v>45301</v>
@@ -8681,7 +8732,7 @@
         <v>154</v>
       </c>
       <c r="Q166" t="s">
-        <v>166</v>
+        <v>230</v>
       </c>
     </row>
     <row r="167" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -8709,7 +8760,7 @@
       </c>
       <c r="J167" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="L167" s="4" t="str">
         <f t="shared" si="29"/>
@@ -8722,7 +8773,7 @@
         <v>45322</v>
       </c>
       <c r="P167" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="168" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -8750,7 +8801,7 @@
       </c>
       <c r="J168" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="L168" s="4" t="str">
         <f t="shared" si="29"/>
@@ -8763,7 +8814,7 @@
         <v>45322</v>
       </c>
       <c r="P168" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="169" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -8791,7 +8842,7 @@
       </c>
       <c r="J169" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="L169" s="4" t="str">
         <f t="shared" si="29"/>
@@ -8804,7 +8855,7 @@
         <v>45322</v>
       </c>
       <c r="P169" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="170" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -8831,11 +8882,11 @@
       </c>
       <c r="I170" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J170" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="K170" s="2">
         <v>45301</v>
@@ -8850,14 +8901,17 @@
       <c r="N170" s="2">
         <v>45322</v>
       </c>
+      <c r="O170" s="2">
+        <v>45335</v>
+      </c>
       <c r="P170" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="Q170" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="171" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="171" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B171" t="s">
         <v>141</v>
       </c>
@@ -8881,11 +8935,11 @@
       </c>
       <c r="I171" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J171" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="K171" s="2">
         <v>45301</v>
@@ -8895,7 +8949,7 @@
         <v>32</v>
       </c>
       <c r="M171" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="172" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -8922,11 +8976,11 @@
       </c>
       <c r="I172" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J172" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="K172" s="2">
         <v>45301</v>
@@ -8942,7 +8996,7 @@
         <v>45322</v>
       </c>
       <c r="P172" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="173" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -8969,11 +9023,11 @@
       </c>
       <c r="I173" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J173" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="K173" s="2">
         <v>45301</v>
@@ -8989,7 +9043,7 @@
         <v>45322</v>
       </c>
       <c r="P173" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="174" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -9016,11 +9070,11 @@
       </c>
       <c r="I174" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J174" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="K174" s="2">
         <v>45301</v>
@@ -9036,10 +9090,10 @@
         <v>45322</v>
       </c>
       <c r="P174" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="175" spans="2:17" x14ac:dyDescent="0.3">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="175" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B175" t="s">
         <v>141</v>
       </c>
@@ -9063,18 +9117,18 @@
       </c>
       <c r="I175" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J175" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="L175" s="4" t="str">
         <f t="shared" si="29"/>
         <v>-</v>
       </c>
       <c r="M175" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="176" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -9101,11 +9155,11 @@
       </c>
       <c r="I176" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J176" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="L176" s="4" t="str">
         <f t="shared" si="29"/>
@@ -9118,13 +9172,13 @@
         <v>45322</v>
       </c>
       <c r="P176" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="Q176" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="177" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="177" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B177" t="s">
         <v>34</v>
       </c>
@@ -9135,18 +9189,18 @@
         <v>16</v>
       </c>
       <c r="G177" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H177" s="2">
         <v>45300</v>
       </c>
       <c r="I177" s="4">
         <f t="shared" ref="I177" ca="1" si="30">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H177), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H177), 7), "-")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J177" s="4">
         <f t="shared" ref="J177" ca="1" si="31">IF(_xlfn.DAYS(TODAY(),H177)&lt;10000, _xlfn.DAYS(TODAY(),H177), "-")</f>
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="K177" s="16">
         <v>45324</v>
@@ -9156,10 +9210,10 @@
         <v>24</v>
       </c>
       <c r="M177" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="178" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="178" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B178" t="s">
         <v>34</v>
       </c>
@@ -9170,18 +9224,18 @@
         <v>16</v>
       </c>
       <c r="G178" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H178" s="2">
         <v>45300</v>
       </c>
       <c r="I178" s="4">
         <f t="shared" ref="I178:I187" ca="1" si="33">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H178), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H178), 7), "-")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J178" s="4">
         <f t="shared" ref="J178:J187" ca="1" si="34">IF(_xlfn.DAYS(TODAY(),H178)&lt;10000, _xlfn.DAYS(TODAY(),H178), "-")</f>
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="K178" s="16">
         <v>45324</v>
@@ -9191,10 +9245,10 @@
         <v>24</v>
       </c>
       <c r="M178" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="179" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="179" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B179" t="s">
         <v>34</v>
       </c>
@@ -9205,18 +9259,18 @@
         <v>16</v>
       </c>
       <c r="G179" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H179" s="2">
         <v>45300</v>
       </c>
       <c r="I179" s="4">
         <f t="shared" ca="1" si="33"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J179" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="K179" s="16">
         <v>45324</v>
@@ -9226,10 +9280,10 @@
         <v>24</v>
       </c>
       <c r="M179" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="180" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="180" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B180" t="s">
         <v>34</v>
       </c>
@@ -9240,18 +9294,18 @@
         <v>16</v>
       </c>
       <c r="G180" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H180" s="2">
         <v>45300</v>
       </c>
       <c r="I180" s="4">
         <f t="shared" ca="1" si="33"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J180" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="K180" s="16">
         <v>45324</v>
@@ -9261,10 +9315,10 @@
         <v>24</v>
       </c>
       <c r="M180" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="181" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="181" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B181" t="s">
         <v>34</v>
       </c>
@@ -9275,18 +9329,18 @@
         <v>16</v>
       </c>
       <c r="G181" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H181" s="2">
         <v>45300</v>
       </c>
       <c r="I181" s="4">
         <f t="shared" ca="1" si="33"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J181" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="K181" s="16">
         <v>45324</v>
@@ -9296,10 +9350,10 @@
         <v>24</v>
       </c>
       <c r="M181" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="182" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="182" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B182" t="s">
         <v>34</v>
       </c>
@@ -9310,18 +9364,18 @@
         <v>16</v>
       </c>
       <c r="G182" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H182" s="2">
         <v>45300</v>
       </c>
       <c r="I182" s="4">
         <f t="shared" ca="1" si="33"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J182" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="K182" s="16">
         <v>45324</v>
@@ -9331,10 +9385,10 @@
         <v>24</v>
       </c>
       <c r="M182" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="183" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="183" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B183" t="s">
         <v>34</v>
       </c>
@@ -9345,18 +9399,18 @@
         <v>16</v>
       </c>
       <c r="G183" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H183" s="2">
         <v>45300</v>
       </c>
       <c r="I183" s="4">
         <f t="shared" ca="1" si="33"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J183" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="K183" s="16">
         <v>45324</v>
@@ -9366,10 +9420,10 @@
         <v>24</v>
       </c>
       <c r="M183" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="184" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="184" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B184" t="s">
         <v>34</v>
       </c>
@@ -9380,18 +9434,18 @@
         <v>16</v>
       </c>
       <c r="G184" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H184" s="2">
         <v>45300</v>
       </c>
       <c r="I184" s="4">
         <f t="shared" ca="1" si="33"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J184" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="K184" s="16">
         <v>45324</v>
@@ -9401,10 +9455,10 @@
         <v>24</v>
       </c>
       <c r="M184" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="185" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="185" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B185" t="s">
         <v>34</v>
       </c>
@@ -9415,18 +9469,18 @@
         <v>16</v>
       </c>
       <c r="G185" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H185" s="2">
         <v>45300</v>
       </c>
       <c r="I185" s="4">
         <f t="shared" ca="1" si="33"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J185" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="K185" s="16">
         <v>45324</v>
@@ -9436,12 +9490,12 @@
         <v>24</v>
       </c>
       <c r="M185" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="186" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="186" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B186" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C186" t="s">
         <v>123</v>
@@ -9451,17 +9505,17 @@
       </c>
       <c r="I186" s="4">
         <f t="shared" ca="1" si="33"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J186" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="M186" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="187" spans="2:13" x14ac:dyDescent="0.3">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="187" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B187" t="s">
         <v>5</v>
       </c>
@@ -9476,21 +9530,24 @@
       </c>
       <c r="I187" s="4">
         <f t="shared" ca="1" si="33"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J187" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="L187" s="4" t="str">
         <f t="shared" ref="L187" si="36">IF(_xlfn.DAYS(K187,H187)&gt;0, _xlfn.DAYS(K187,H187), "-")</f>
         <v>-</v>
       </c>
       <c r="M187" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="188" spans="2:13" x14ac:dyDescent="0.3">
+        <v>186</v>
+      </c>
+      <c r="Q187" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="188" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B188" t="s">
         <v>5</v>
       </c>
@@ -9505,21 +9562,24 @@
       </c>
       <c r="I188" s="4">
         <f t="shared" ref="I188:I194" ca="1" si="37">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H188), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H188), 7), "-")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J188" s="4">
         <f t="shared" ref="J188:J194" ca="1" si="38">IF(_xlfn.DAYS(TODAY(),H188)&lt;10000, _xlfn.DAYS(TODAY(),H188), "-")</f>
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="L188" s="4" t="str">
         <f t="shared" ref="L188:L194" si="39">IF(_xlfn.DAYS(K188,H188)&gt;0, _xlfn.DAYS(K188,H188), "-")</f>
         <v>-</v>
       </c>
       <c r="M188" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="189" spans="2:13" x14ac:dyDescent="0.3">
+        <v>186</v>
+      </c>
+      <c r="Q188" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="189" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B189" t="s">
         <v>5</v>
       </c>
@@ -9534,21 +9594,24 @@
       </c>
       <c r="I189" s="4">
         <f t="shared" ca="1" si="37"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J189" s="4">
         <f t="shared" ca="1" si="38"/>
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="L189" s="4" t="str">
         <f t="shared" si="39"/>
         <v>-</v>
       </c>
       <c r="M189" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="190" spans="2:13" x14ac:dyDescent="0.3">
+        <v>186</v>
+      </c>
+      <c r="Q189" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="190" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B190" t="s">
         <v>5</v>
       </c>
@@ -9563,21 +9626,24 @@
       </c>
       <c r="I190" s="4">
         <f t="shared" ca="1" si="37"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J190" s="4">
         <f t="shared" ca="1" si="38"/>
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="L190" s="4" t="str">
         <f t="shared" si="39"/>
         <v>-</v>
       </c>
       <c r="M190" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="191" spans="2:13" x14ac:dyDescent="0.3">
+        <v>186</v>
+      </c>
+      <c r="Q190" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="191" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B191" t="s">
         <v>5</v>
       </c>
@@ -9592,21 +9658,24 @@
       </c>
       <c r="I191" s="4">
         <f t="shared" ca="1" si="37"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J191" s="4">
         <f t="shared" ca="1" si="38"/>
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="L191" s="4" t="str">
         <f t="shared" si="39"/>
         <v>-</v>
       </c>
       <c r="M191" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="192" spans="2:13" x14ac:dyDescent="0.3">
+        <v>186</v>
+      </c>
+      <c r="Q191" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="192" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B192" t="s">
         <v>5</v>
       </c>
@@ -9621,21 +9690,24 @@
       </c>
       <c r="I192" s="4">
         <f t="shared" ca="1" si="37"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J192" s="4">
         <f t="shared" ca="1" si="38"/>
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="L192" s="4" t="str">
         <f t="shared" si="39"/>
         <v>-</v>
       </c>
       <c r="M192" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="193" spans="2:17" x14ac:dyDescent="0.3">
+        <v>186</v>
+      </c>
+      <c r="Q192" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="193" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B193" t="s">
         <v>5</v>
       </c>
@@ -9650,21 +9722,24 @@
       </c>
       <c r="I193" s="4">
         <f t="shared" ca="1" si="37"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J193" s="4">
         <f t="shared" ca="1" si="38"/>
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="L193" s="4" t="str">
         <f t="shared" si="39"/>
         <v>-</v>
       </c>
       <c r="M193" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="194" spans="2:17" x14ac:dyDescent="0.3">
+        <v>186</v>
+      </c>
+      <c r="Q193" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="194" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B194" t="s">
         <v>5</v>
       </c>
@@ -9679,23 +9754,26 @@
       </c>
       <c r="I194" s="4">
         <f t="shared" ca="1" si="37"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J194" s="4">
         <f t="shared" ca="1" si="38"/>
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="L194" s="4" t="str">
         <f t="shared" si="39"/>
         <v>-</v>
       </c>
       <c r="M194" t="s">
-        <v>189</v>
+        <v>186</v>
+      </c>
+      <c r="Q194" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="195" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B195" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C195" t="s">
         <v>124</v>
@@ -9704,21 +9782,21 @@
         <v>639</v>
       </c>
       <c r="E195" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F195" s="5" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G195" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="M195" s="4" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="196" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B196" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C196" t="s">
         <v>124</v>
@@ -9727,24 +9805,24 @@
         <v>640</v>
       </c>
       <c r="E196" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F196" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="G196" t="s">
+        <v>195</v>
+      </c>
+      <c r="M196" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="Q196" t="s">
         <v>194</v>
-      </c>
-      <c r="G196" t="s">
-        <v>198</v>
-      </c>
-      <c r="M196" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="Q196" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="197" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B197" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C197" t="s">
         <v>124</v>
@@ -9753,21 +9831,21 @@
         <v>641</v>
       </c>
       <c r="E197" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F197" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="G197" t="s">
         <v>195</v>
       </c>
-      <c r="G197" t="s">
-        <v>198</v>
-      </c>
       <c r="M197" s="4" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="198" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B198" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C198" t="s">
         <v>124</v>
@@ -9776,21 +9854,21 @@
         <v>642</v>
       </c>
       <c r="E198" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F198" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="G198" t="s">
         <v>195</v>
       </c>
-      <c r="G198" t="s">
-        <v>198</v>
-      </c>
       <c r="M198" s="4" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="199" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B199" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C199" t="s">
         <v>124</v>
@@ -9799,21 +9877,21 @@
         <v>643</v>
       </c>
       <c r="E199" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F199" s="5" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="G199" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="M199" s="4" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="200" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B200" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C200" t="s">
         <v>124</v>
@@ -9822,22 +9900,22 @@
         <v>644</v>
       </c>
       <c r="E200" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F200" s="5" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="G200" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="M200" s="4" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="Q200" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="201" spans="2:17" x14ac:dyDescent="0.3">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="201" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B201" t="s">
         <v>5</v>
       </c>
@@ -9852,21 +9930,21 @@
       </c>
       <c r="I201" s="4">
         <f t="shared" ref="I201" ca="1" si="40">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H201), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H201), 7), "-")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J201" s="4">
         <f t="shared" ref="J201" ca="1" si="41">IF(_xlfn.DAYS(TODAY(),H201)&lt;10000, _xlfn.DAYS(TODAY(),H201), "-")</f>
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="L201" s="4" t="str">
         <f t="shared" ref="L201" si="42">IF(_xlfn.DAYS(K201,H201)&gt;0, _xlfn.DAYS(K201,H201), "-")</f>
         <v>-</v>
       </c>
       <c r="M201" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="202" spans="2:17" x14ac:dyDescent="0.3">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="202" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B202" t="s">
         <v>5</v>
       </c>
@@ -9881,21 +9959,21 @@
       </c>
       <c r="I202" s="4">
         <f t="shared" ref="I202:I217" ca="1" si="43">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H202), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H202), 7), "-")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J202" s="4">
         <f t="shared" ref="J202:J217" ca="1" si="44">IF(_xlfn.DAYS(TODAY(),H202)&lt;10000, _xlfn.DAYS(TODAY(),H202), "-")</f>
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="L202" s="4" t="str">
         <f t="shared" ref="L202:L217" si="45">IF(_xlfn.DAYS(K202,H202)&gt;0, _xlfn.DAYS(K202,H202), "-")</f>
         <v>-</v>
       </c>
       <c r="M202" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="203" spans="2:17" x14ac:dyDescent="0.3">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="203" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B203" t="s">
         <v>5</v>
       </c>
@@ -9910,21 +9988,21 @@
       </c>
       <c r="I203" s="4">
         <f t="shared" ca="1" si="43"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J203" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="L203" s="4" t="str">
         <f t="shared" si="45"/>
         <v>-</v>
       </c>
       <c r="M203" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="204" spans="2:17" x14ac:dyDescent="0.3">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="204" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B204" t="s">
         <v>5</v>
       </c>
@@ -9939,21 +10017,21 @@
       </c>
       <c r="I204" s="4">
         <f t="shared" ca="1" si="43"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J204" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="L204" s="4" t="str">
         <f t="shared" si="45"/>
         <v>-</v>
       </c>
       <c r="M204" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="205" spans="2:17" x14ac:dyDescent="0.3">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="205" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B205" t="s">
         <v>5</v>
       </c>
@@ -9968,21 +10046,21 @@
       </c>
       <c r="I205" s="4">
         <f t="shared" ca="1" si="43"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J205" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="L205" s="4" t="str">
         <f t="shared" si="45"/>
         <v>-</v>
       </c>
       <c r="M205" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="206" spans="2:17" x14ac:dyDescent="0.3">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="206" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B206" t="s">
         <v>5</v>
       </c>
@@ -9997,21 +10075,21 @@
       </c>
       <c r="I206" s="4">
         <f t="shared" ca="1" si="43"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J206" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="L206" s="4" t="str">
         <f t="shared" si="45"/>
         <v>-</v>
       </c>
       <c r="M206" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="207" spans="2:17" x14ac:dyDescent="0.3">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="207" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B207" t="s">
         <v>5</v>
       </c>
@@ -10026,21 +10104,21 @@
       </c>
       <c r="I207" s="4">
         <f t="shared" ca="1" si="43"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J207" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="L207" s="4" t="str">
         <f t="shared" si="45"/>
         <v>-</v>
       </c>
       <c r="M207" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="208" spans="2:17" x14ac:dyDescent="0.3">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="208" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B208" t="s">
         <v>5</v>
       </c>
@@ -10055,21 +10133,21 @@
       </c>
       <c r="I208" s="4">
         <f t="shared" ca="1" si="43"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J208" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="L208" s="4" t="str">
         <f t="shared" si="45"/>
         <v>-</v>
       </c>
       <c r="M208" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="209" spans="2:17" x14ac:dyDescent="0.3">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="209" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B209" t="s">
         <v>5</v>
       </c>
@@ -10084,21 +10162,21 @@
       </c>
       <c r="I209" s="4">
         <f t="shared" ca="1" si="43"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J209" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="L209" s="4" t="str">
         <f t="shared" si="45"/>
         <v>-</v>
       </c>
       <c r="M209" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="210" spans="2:17" x14ac:dyDescent="0.3">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="210" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B210" t="s">
         <v>5</v>
       </c>
@@ -10113,21 +10191,21 @@
       </c>
       <c r="I210" s="4">
         <f t="shared" ca="1" si="43"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J210" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="L210" s="4" t="str">
         <f t="shared" si="45"/>
         <v>-</v>
       </c>
       <c r="M210" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="211" spans="2:17" x14ac:dyDescent="0.3">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="211" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B211" t="s">
         <v>5</v>
       </c>
@@ -10142,21 +10220,21 @@
       </c>
       <c r="I211" s="4">
         <f t="shared" ca="1" si="43"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J211" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L211" s="4" t="str">
         <f t="shared" si="45"/>
         <v>-</v>
       </c>
       <c r="M211" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="212" spans="2:17" x14ac:dyDescent="0.3">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="212" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B212" t="s">
         <v>5</v>
       </c>
@@ -10171,21 +10249,21 @@
       </c>
       <c r="I212" s="4">
         <f t="shared" ca="1" si="43"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J212" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L212" s="4" t="str">
         <f t="shared" si="45"/>
         <v>-</v>
       </c>
       <c r="M212" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="213" spans="2:17" x14ac:dyDescent="0.3">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="213" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B213" t="s">
         <v>5</v>
       </c>
@@ -10200,21 +10278,21 @@
       </c>
       <c r="I213" s="4">
         <f t="shared" ca="1" si="43"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J213" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L213" s="4" t="str">
         <f t="shared" si="45"/>
         <v>-</v>
       </c>
       <c r="M213" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="214" spans="2:17" x14ac:dyDescent="0.3">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="214" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B214" t="s">
         <v>5</v>
       </c>
@@ -10229,21 +10307,21 @@
       </c>
       <c r="I214" s="4">
         <f t="shared" ca="1" si="43"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J214" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L214" s="4" t="str">
         <f t="shared" si="45"/>
         <v>-</v>
       </c>
       <c r="M214" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="215" spans="2:17" x14ac:dyDescent="0.3">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="215" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B215" t="s">
         <v>5</v>
       </c>
@@ -10258,21 +10336,21 @@
       </c>
       <c r="I215" s="4">
         <f t="shared" ca="1" si="43"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J215" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L215" s="4" t="str">
         <f t="shared" si="45"/>
         <v>-</v>
       </c>
       <c r="M215" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="216" spans="2:17" x14ac:dyDescent="0.3">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="216" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B216" t="s">
         <v>5</v>
       </c>
@@ -10287,21 +10365,21 @@
       </c>
       <c r="I216" s="4">
         <f t="shared" ca="1" si="43"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J216" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L216" s="4" t="str">
         <f t="shared" si="45"/>
         <v>-</v>
       </c>
       <c r="M216" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="217" spans="2:17" x14ac:dyDescent="0.3">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="217" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B217" t="s">
         <v>5</v>
       </c>
@@ -10316,18 +10394,18 @@
       </c>
       <c r="I217" s="4">
         <f t="shared" ca="1" si="43"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J217" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L217" s="4" t="str">
         <f t="shared" si="45"/>
         <v>-</v>
       </c>
       <c r="M217" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
     </row>
     <row r="218" spans="2:17" x14ac:dyDescent="0.3">
@@ -10338,20 +10416,431 @@
         <v>124</v>
       </c>
       <c r="E218" t="s">
+        <v>225</v>
+      </c>
+      <c r="M218" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="Q218" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="219" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B219" t="s">
+        <v>5</v>
+      </c>
+      <c r="C219" t="s">
+        <v>142</v>
+      </c>
+      <c r="E219" t="s">
+        <v>229</v>
+      </c>
+      <c r="H219" s="2">
+        <v>45343</v>
+      </c>
+      <c r="I219" s="4">
+        <f t="shared" ref="I219:I232" ca="1" si="46">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H219), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H219), 7), "-")</f>
+        <v>0</v>
+      </c>
+      <c r="J219" s="4">
+        <f t="shared" ref="J219:J232" ca="1" si="47">IF(_xlfn.DAYS(TODAY(),H219)&lt;10000, _xlfn.DAYS(TODAY(),H219), "-")</f>
+        <v>6</v>
+      </c>
+      <c r="L219" s="4" t="str">
+        <f t="shared" ref="L219:L232" si="48">IF(_xlfn.DAYS(K219,H219)&gt;0, _xlfn.DAYS(K219,H219), "-")</f>
+        <v>-</v>
+      </c>
+      <c r="M219" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="220" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B220" t="s">
+        <v>5</v>
+      </c>
+      <c r="C220" t="s">
+        <v>142</v>
+      </c>
+      <c r="E220" t="s">
+        <v>16</v>
+      </c>
+      <c r="H220" s="2">
+        <v>45343</v>
+      </c>
+      <c r="I220" s="4">
+        <f t="shared" ca="1" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="J220" s="4">
+        <f t="shared" ca="1" si="47"/>
+        <v>6</v>
+      </c>
+      <c r="L220" s="4" t="str">
+        <f t="shared" si="48"/>
+        <v>-</v>
+      </c>
+      <c r="M220" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="221" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B221" t="s">
+        <v>5</v>
+      </c>
+      <c r="C221" t="s">
+        <v>142</v>
+      </c>
+      <c r="E221" t="s">
+        <v>16</v>
+      </c>
+      <c r="H221" s="2">
+        <v>45343</v>
+      </c>
+      <c r="I221" s="4">
+        <f t="shared" ca="1" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="J221" s="4">
+        <f t="shared" ca="1" si="47"/>
+        <v>6</v>
+      </c>
+      <c r="L221" s="4" t="str">
+        <f t="shared" si="48"/>
+        <v>-</v>
+      </c>
+      <c r="M221" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="222" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B222" t="s">
+        <v>5</v>
+      </c>
+      <c r="C222" t="s">
+        <v>142</v>
+      </c>
+      <c r="E222" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H222" s="2">
+        <v>45343</v>
+      </c>
+      <c r="I222" s="4">
+        <f t="shared" ca="1" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="J222" s="4">
+        <f t="shared" ca="1" si="47"/>
+        <v>6</v>
+      </c>
+      <c r="L222" s="4" t="str">
+        <f t="shared" si="48"/>
+        <v>-</v>
+      </c>
+      <c r="M222" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="223" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B223" t="s">
+        <v>5</v>
+      </c>
+      <c r="C223" t="s">
+        <v>142</v>
+      </c>
+      <c r="E223" t="s">
+        <v>16</v>
+      </c>
+      <c r="H223" s="2">
+        <v>45343</v>
+      </c>
+      <c r="I223" s="4">
+        <f t="shared" ca="1" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="J223" s="4">
+        <f t="shared" ca="1" si="47"/>
+        <v>6</v>
+      </c>
+      <c r="L223" s="4" t="str">
+        <f t="shared" si="48"/>
+        <v>-</v>
+      </c>
+      <c r="M223" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="224" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B224" t="s">
+        <v>5</v>
+      </c>
+      <c r="C224" t="s">
+        <v>142</v>
+      </c>
+      <c r="E224" t="s">
+        <v>16</v>
+      </c>
+      <c r="H224" s="2">
+        <v>45343</v>
+      </c>
+      <c r="I224" s="4">
+        <f t="shared" ca="1" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="J224" s="4">
+        <f t="shared" ca="1" si="47"/>
+        <v>6</v>
+      </c>
+      <c r="L224" s="4" t="str">
+        <f t="shared" si="48"/>
+        <v>-</v>
+      </c>
+      <c r="M224" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="225" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B225" t="s">
+        <v>5</v>
+      </c>
+      <c r="C225" t="s">
+        <v>142</v>
+      </c>
+      <c r="E225" t="s">
+        <v>16</v>
+      </c>
+      <c r="H225" s="2">
+        <v>45343</v>
+      </c>
+      <c r="I225" s="4">
+        <f t="shared" ca="1" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="J225" s="4">
+        <f t="shared" ca="1" si="47"/>
+        <v>6</v>
+      </c>
+      <c r="L225" s="4" t="str">
+        <f t="shared" si="48"/>
+        <v>-</v>
+      </c>
+      <c r="M225" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="226" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B226" t="s">
+        <v>5</v>
+      </c>
+      <c r="C226" t="s">
+        <v>142</v>
+      </c>
+      <c r="E226" t="s">
+        <v>16</v>
+      </c>
+      <c r="H226" s="2">
+        <v>45343</v>
+      </c>
+      <c r="I226" s="4">
+        <f t="shared" ca="1" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="J226" s="4">
+        <f t="shared" ca="1" si="47"/>
+        <v>6</v>
+      </c>
+      <c r="L226" s="4" t="str">
+        <f t="shared" si="48"/>
+        <v>-</v>
+      </c>
+      <c r="M226" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="227" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B227" t="s">
+        <v>5</v>
+      </c>
+      <c r="C227" t="s">
+        <v>142</v>
+      </c>
+      <c r="E227" t="s">
+        <v>16</v>
+      </c>
+      <c r="H227" s="2">
+        <v>45343</v>
+      </c>
+      <c r="I227" s="4">
+        <f t="shared" ca="1" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="J227" s="4">
+        <f t="shared" ca="1" si="47"/>
+        <v>6</v>
+      </c>
+      <c r="L227" s="4" t="str">
+        <f t="shared" si="48"/>
+        <v>-</v>
+      </c>
+      <c r="M227" t="s">
         <v>228</v>
       </c>
-      <c r="M218" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="Q218" t="s">
-        <v>229</v>
+    </row>
+    <row r="228" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B228" t="s">
+        <v>5</v>
+      </c>
+      <c r="C228" t="s">
+        <v>142</v>
+      </c>
+      <c r="E228" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H228" s="2">
+        <v>45343</v>
+      </c>
+      <c r="I228" s="4">
+        <f t="shared" ca="1" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="J228" s="4">
+        <f t="shared" ca="1" si="47"/>
+        <v>6</v>
+      </c>
+      <c r="L228" s="4" t="str">
+        <f t="shared" si="48"/>
+        <v>-</v>
+      </c>
+      <c r="M228" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="229" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B229" t="s">
+        <v>5</v>
+      </c>
+      <c r="C229" t="s">
+        <v>142</v>
+      </c>
+      <c r="E229" t="s">
+        <v>16</v>
+      </c>
+      <c r="H229" s="2">
+        <v>45343</v>
+      </c>
+      <c r="I229" s="4">
+        <f t="shared" ca="1" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="J229" s="4">
+        <f t="shared" ca="1" si="47"/>
+        <v>6</v>
+      </c>
+      <c r="L229" s="4" t="str">
+        <f t="shared" si="48"/>
+        <v>-</v>
+      </c>
+      <c r="M229" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="230" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B230" t="s">
+        <v>5</v>
+      </c>
+      <c r="C230" t="s">
+        <v>142</v>
+      </c>
+      <c r="E230" t="s">
+        <v>16</v>
+      </c>
+      <c r="H230" s="2">
+        <v>45343</v>
+      </c>
+      <c r="I230" s="4">
+        <f t="shared" ca="1" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="J230" s="4">
+        <f t="shared" ca="1" si="47"/>
+        <v>6</v>
+      </c>
+      <c r="L230" s="4" t="str">
+        <f t="shared" si="48"/>
+        <v>-</v>
+      </c>
+      <c r="M230" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="231" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B231" t="s">
+        <v>5</v>
+      </c>
+      <c r="C231" t="s">
+        <v>142</v>
+      </c>
+      <c r="E231" t="s">
+        <v>16</v>
+      </c>
+      <c r="H231" s="2">
+        <v>45343</v>
+      </c>
+      <c r="I231" s="4">
+        <f t="shared" ca="1" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="J231" s="4">
+        <f t="shared" ca="1" si="47"/>
+        <v>6</v>
+      </c>
+      <c r="L231" s="4" t="str">
+        <f t="shared" si="48"/>
+        <v>-</v>
+      </c>
+      <c r="M231" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="232" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B232" t="s">
+        <v>5</v>
+      </c>
+      <c r="C232" t="s">
+        <v>142</v>
+      </c>
+      <c r="E232" t="s">
+        <v>16</v>
+      </c>
+      <c r="H232" s="2">
+        <v>45343</v>
+      </c>
+      <c r="I232" s="4">
+        <f t="shared" ca="1" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="J232" s="4">
+        <f t="shared" ca="1" si="47"/>
+        <v>6</v>
+      </c>
+      <c r="L232" s="4" t="str">
+        <f t="shared" si="48"/>
+        <v>-</v>
+      </c>
+      <c r="M232" t="s">
+        <v>228</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B1:Q218" xr:uid="{47ECCD65-6802-4B2B-901A-AED4A431A765}">
+  <autoFilter ref="B1:Q232" xr:uid="{47ECCD65-6802-4B2B-901A-AED4A431A765}">
     <filterColumn colId="0">
       <filters>
         <filter val="SPF"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Tmem119-CreERT2; Tsg101-flox"/>
       </filters>
     </filterColumn>
     <filterColumn colId="13">
@@ -10376,7 +10865,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E140 E142:E143 E145:E150 E152:E153 E155:E158 E160:E188 E190:E1048576" xr:uid="{939E2B39-E841-4A9F-AD11-00C266DB2690}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E140 E142:E143 E145:E150 E152:E153 E155:E158 E160:E188 E190:E221 E223:E227 E229:E1048576" xr:uid="{939E2B39-E841-4A9F-AD11-00C266DB2690}">
       <formula1>"Y, N"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1:G1048576" xr:uid="{2DE54AC7-5B92-48D6-98C4-E6203F87CDD0}">
@@ -10457,6 +10946,42 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{748D99E8-C5CF-4A6C-8EDC-A8EC4FAEDD12}">
+  <dimension ref="B7:E8"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="3" width="11.125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="2"/>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="2">
+        <v>45269</v>
+      </c>
+      <c r="C8" s="2">
+        <v>45329</v>
+      </c>
+      <c r="D8">
+        <f>_xlfn.DAYS(C8,B8)</f>
+        <v>60</v>
+      </c>
+      <c r="E8">
+        <f>QUOTIENT(D8, 7)</f>
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{204CD0B9-8C45-41F1-B207-9E51E4F55111}">
   <dimension ref="A6:G17"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -10474,13 +10999,13 @@
         <v>44</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E6" s="19" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -10491,13 +11016,13 @@
         <v>43</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -10508,10 +11033,10 @@
         <v>42</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E8" s="20">
         <v>17</v>
@@ -10525,19 +11050,19 @@
         <v>98</v>
       </c>
       <c r="C9" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D9" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E9">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="G9" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -10548,10 +11073,10 @@
         <v>99</v>
       </c>
       <c r="C10" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D10" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="E10">
         <v>8</v>
@@ -10562,13 +11087,13 @@
         <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C11" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D11" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E11">
         <v>4</v>
@@ -10579,22 +11104,22 @@
         <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C12" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D12" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E12">
         <v>4</v>
       </c>
       <c r="F12" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="G12" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -10605,10 +11130,10 @@
         <v>154</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="D14" s="20" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -10619,10 +11144,10 @@
         <v>156</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
@@ -10633,10 +11158,10 @@
         <v>155</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -10647,10 +11172,10 @@
         <v>157</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="D17" s="19" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>

--- a/Mouse 내역.xlsx
+++ b/Mouse 내역.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\heung\Dropbox\02. Lab. of Host Defenses\03. 동물실\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ADBE4D3-0F15-4DDE-BBD0-52A205F2E411}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{811241FC-8FA9-4B40-999C-94571474C7B8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="495" windowWidth="28800" windowHeight="16245" xr2:uid="{5A73A69A-2AFB-4F3E-AC64-070DD7700CB2}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <sheet name="Sheet1 (2)" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$Q$232</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$Q$234</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1509" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1553" uniqueCount="237">
   <si>
     <t>Strain</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -916,47 +916,51 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>Exp. 1-10-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>H8.1.X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>H9.1.X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>N</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Exp. 1-10-1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>H8.1.X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>H9.1.X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>N</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>죽임</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>weaning, genotyping</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>genotyping</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>genotyping</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>죽이기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>몇마리인지 확인, 주령도 확인</t>
+    <t>Cre/Cre</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cre/+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>+/+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Genotyping</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>H7.1.X</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1222,7 +1226,27 @@
     <cellStyle name="좋음" xfId="1" builtinId="26"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1813,7 +1837,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D71A6DC-E91C-489F-8F50-989C4712FA7C}">
   <sheetPr filterMode="1"/>
-  <dimension ref="B1:Q232"/>
+  <dimension ref="B1:Q238"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="10.5" customWidth="1"/>
@@ -1905,7 +1929,7 @@
       </c>
       <c r="J2" s="4">
         <f ca="1">IF(_xlfn.DAYS(TODAY(),H2)&lt;10000, _xlfn.DAYS(TODAY(),H2), "-")</f>
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L2" s="4" t="str">
         <f t="shared" ref="L2:L31" si="0">IF(_xlfn.DAYS(K2,H2)&gt;0, _xlfn.DAYS(K2,H2), "-")</f>
@@ -1944,7 +1968,7 @@
       </c>
       <c r="J3" s="4">
         <f t="shared" ref="J3:J31" ca="1" si="2">IF(_xlfn.DAYS(TODAY(),H3)&lt;10000, _xlfn.DAYS(TODAY(),H3), "-")</f>
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L3" s="4" t="str">
         <f t="shared" si="0"/>
@@ -1981,7 +2005,7 @@
       </c>
       <c r="J4" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L4" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2017,11 +2041,11 @@
       </c>
       <c r="I5" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J5" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K5" s="2">
         <v>45293</v>
@@ -2038,7 +2062,7 @@
         <v>45309</v>
       </c>
     </row>
-    <row r="6" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>5</v>
       </c>
@@ -2062,11 +2086,11 @@
       </c>
       <c r="I6" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J6" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K6" s="2">
         <v>45293</v>
@@ -2108,11 +2132,11 @@
       </c>
       <c r="I7" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J7" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K7" s="2">
         <v>45293</v>
@@ -2151,11 +2175,11 @@
       </c>
       <c r="I8" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J8" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K8" s="2">
         <v>45293</v>
@@ -2199,11 +2223,11 @@
       </c>
       <c r="I9" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J9" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K9" s="2">
         <v>45293</v>
@@ -2242,11 +2266,11 @@
       </c>
       <c r="I10" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J10" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K10" s="2">
         <v>45293</v>
@@ -2287,11 +2311,11 @@
       </c>
       <c r="I11" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J11" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K11" s="2">
         <v>45293</v>
@@ -2333,7 +2357,7 @@
       </c>
       <c r="J12" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L12" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2447,7 +2471,7 @@
       </c>
       <c r="J15" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="L15" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2457,9 +2481,11 @@
         <v>51</v>
       </c>
       <c r="N15" s="7"/>
-      <c r="O15" s="7"/>
+      <c r="O15" s="7">
+        <v>45349</v>
+      </c>
       <c r="Q15" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="16" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -2490,7 +2516,7 @@
       </c>
       <c r="J16" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="L16" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2500,9 +2526,11 @@
         <v>51</v>
       </c>
       <c r="N16" s="7"/>
-      <c r="O16" s="7"/>
+      <c r="O16" s="7">
+        <v>45349</v>
+      </c>
       <c r="Q16" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="17" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -2533,7 +2561,7 @@
       </c>
       <c r="J17" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="L17" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2542,8 +2570,11 @@
       <c r="M17" s="4" t="s">
         <v>51</v>
       </c>
+      <c r="O17" s="7">
+        <v>45349</v>
+      </c>
       <c r="Q17" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="18" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -2574,7 +2605,7 @@
       </c>
       <c r="J18" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="L18" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2615,7 +2646,7 @@
       </c>
       <c r="J19" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="L19" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2624,8 +2655,11 @@
       <c r="M19" s="4" t="s">
         <v>51</v>
       </c>
+      <c r="O19" s="7">
+        <v>45349</v>
+      </c>
       <c r="Q19" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="20" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -2649,11 +2683,11 @@
       </c>
       <c r="I20" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J20" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L20" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2726,7 +2760,7 @@
       </c>
       <c r="J22" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K22" s="2">
         <v>45112</v>
@@ -2763,11 +2797,11 @@
       </c>
       <c r="I23" s="4">
         <f ca="1">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H23), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H23), 7), "-")</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J23" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K23" s="2">
         <v>45176</v>
@@ -2807,11 +2841,11 @@
       </c>
       <c r="I24" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J24" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K24" s="2">
         <v>45176</v>
@@ -2851,11 +2885,11 @@
       </c>
       <c r="I25" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J25" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K25" s="2">
         <v>45176</v>
@@ -2895,11 +2929,11 @@
       </c>
       <c r="I26" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J26" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K26" s="2">
         <v>45176</v>
@@ -2934,11 +2968,11 @@
       </c>
       <c r="I27" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J27" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K27" s="2">
         <v>45176</v>
@@ -2973,11 +3007,11 @@
       </c>
       <c r="I28" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J28" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K28" s="2">
         <v>45229</v>
@@ -3014,11 +3048,11 @@
       </c>
       <c r="I29" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J29" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K29" s="2">
         <v>45229</v>
@@ -3055,11 +3089,11 @@
       </c>
       <c r="I30" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J30" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K30" s="2">
         <v>45229</v>
@@ -3094,11 +3128,11 @@
       </c>
       <c r="I31" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J31" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K31" s="2">
         <v>45229</v>
@@ -3133,11 +3167,11 @@
       </c>
       <c r="I32" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J32" s="4">
         <f t="shared" ref="J32:J38" ca="1" si="3">IF(_xlfn.DAYS(TODAY(),H32)&lt;10000, _xlfn.DAYS(TODAY(),H32), "-")</f>
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K32" s="2">
         <v>45229</v>
@@ -3210,11 +3244,11 @@
       </c>
       <c r="I34" s="4">
         <f ca="1">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H34), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H34), 7), "-")</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J34" s="4">
         <f ca="1">IF(_xlfn.DAYS(TODAY(),H34)&lt;10000, _xlfn.DAYS(TODAY(),H34), "-")</f>
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K34" s="2">
         <v>45257</v>
@@ -3333,11 +3367,11 @@
       </c>
       <c r="I37" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J37" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K37" s="2">
         <v>45257</v>
@@ -3380,11 +3414,11 @@
       </c>
       <c r="I38" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J38" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K38" s="2">
         <v>45257</v>
@@ -3427,11 +3461,11 @@
       </c>
       <c r="I39" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J39" s="4">
         <f t="shared" ref="J39:J41" ca="1" si="5">IF(_xlfn.DAYS(TODAY(),H39)&lt;10000, _xlfn.DAYS(TODAY(),H39), "-")</f>
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K39" s="2">
         <v>45257</v>
@@ -3474,11 +3508,11 @@
       </c>
       <c r="I40" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J40" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K40" s="2">
         <v>45257</v>
@@ -3518,11 +3552,11 @@
       </c>
       <c r="I41" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J41" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K41" s="2">
         <v>45257</v>
@@ -3566,7 +3600,7 @@
       </c>
       <c r="J42" s="4">
         <f t="shared" ref="J42" ca="1" si="6">IF(_xlfn.DAYS(TODAY(),H42)&lt;10000, _xlfn.DAYS(TODAY(),H42), "-")</f>
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L42" s="4" t="str">
         <f t="shared" si="4"/>
@@ -3607,7 +3641,7 @@
       </c>
       <c r="J43" s="4">
         <f t="shared" ref="J43:J91" ca="1" si="7">IF(_xlfn.DAYS(TODAY(),H43)&lt;10000, _xlfn.DAYS(TODAY(),H43), "-")</f>
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L43" s="4" t="str">
         <f t="shared" si="4"/>
@@ -3645,7 +3679,7 @@
       </c>
       <c r="J44" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K44" s="2">
         <v>45293</v>
@@ -3689,7 +3723,7 @@
       </c>
       <c r="J45" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K45" s="2">
         <v>45293</v>
@@ -3733,7 +3767,7 @@
       </c>
       <c r="J46" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K46" s="2">
         <v>45293</v>
@@ -3780,7 +3814,7 @@
       </c>
       <c r="J47" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K47" s="2">
         <v>45293</v>
@@ -3827,7 +3861,7 @@
       </c>
       <c r="J48" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K48" s="2">
         <v>45293</v>
@@ -3874,7 +3908,7 @@
       </c>
       <c r="J49" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K49" s="2">
         <v>45293</v>
@@ -3915,7 +3949,7 @@
       </c>
       <c r="J50" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K50" s="2">
         <v>45293</v>
@@ -3956,7 +3990,7 @@
       </c>
       <c r="J51" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K51" s="2">
         <v>45293</v>
@@ -4000,7 +4034,7 @@
       </c>
       <c r="J52" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K52" s="2">
         <v>45293</v>
@@ -4044,7 +4078,7 @@
       </c>
       <c r="J53" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K53" s="2">
         <v>45293</v>
@@ -4085,7 +4119,7 @@
       </c>
       <c r="J54" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K54" s="2">
         <v>45238</v>
@@ -4129,7 +4163,7 @@
       </c>
       <c r="J55" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K55" s="2">
         <v>45238</v>
@@ -4173,7 +4207,7 @@
       </c>
       <c r="J56" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K56" s="2">
         <v>45238</v>
@@ -4210,11 +4244,11 @@
       </c>
       <c r="I57" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J57" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L57" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4248,11 +4282,11 @@
       </c>
       <c r="I58" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J58" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L58" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4287,7 +4321,7 @@
       </c>
       <c r="J59" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K59" s="2">
         <v>45295</v>
@@ -4325,7 +4359,7 @@
       </c>
       <c r="J60" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K60" s="2">
         <v>45295</v>
@@ -4363,7 +4397,7 @@
       </c>
       <c r="J61" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K61" s="2">
         <v>45295</v>
@@ -4398,7 +4432,7 @@
       </c>
       <c r="J62" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K62" s="2">
         <v>45295</v>
@@ -4433,7 +4467,7 @@
       </c>
       <c r="J63" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K63" s="2">
         <v>45295</v>
@@ -4446,7 +4480,7 @@
         <v>99</v>
       </c>
       <c r="P63" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="64" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -4471,7 +4505,7 @@
       </c>
       <c r="J64" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K64" s="2">
         <v>45295</v>
@@ -4484,7 +4518,7 @@
         <v>99</v>
       </c>
       <c r="P64" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="65" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -4508,11 +4542,11 @@
       </c>
       <c r="I65" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J65" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L65" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4546,11 +4580,11 @@
       </c>
       <c r="I66" s="4">
         <f t="shared" ref="I66:I91" ca="1" si="8">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H66), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H66), 7), "-")</f>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J66" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L66" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4587,11 +4621,11 @@
       </c>
       <c r="I67" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J67" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L67" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4637,11 +4671,11 @@
       </c>
       <c r="I68" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J68" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L68" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4687,11 +4721,11 @@
       </c>
       <c r="I69" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J69" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L69" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4737,11 +4771,11 @@
       </c>
       <c r="I70" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J70" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L70" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4787,11 +4821,11 @@
       </c>
       <c r="I71" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J71" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L71" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4837,11 +4871,11 @@
       </c>
       <c r="I72" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J72" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L72" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4887,11 +4921,11 @@
       </c>
       <c r="I73" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J73" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L73" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4937,11 +4971,11 @@
       </c>
       <c r="I74" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J74" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L74" s="4" t="str">
         <f t="shared" si="4"/>
@@ -4987,11 +5021,11 @@
       </c>
       <c r="I75" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J75" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L75" s="4" t="str">
         <f t="shared" si="4"/>
@@ -5037,11 +5071,11 @@
       </c>
       <c r="I76" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J76" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L76" s="4" t="str">
         <f t="shared" si="4"/>
@@ -5087,11 +5121,11 @@
       </c>
       <c r="I77" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J77" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L77" s="4" t="str">
         <f t="shared" si="4"/>
@@ -5137,11 +5171,11 @@
       </c>
       <c r="I78" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J78" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L78" s="4" t="str">
         <f t="shared" si="4"/>
@@ -5187,11 +5221,11 @@
       </c>
       <c r="I79" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J79" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L79" s="4" t="str">
         <f t="shared" si="4"/>
@@ -5237,11 +5271,11 @@
       </c>
       <c r="I80" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J80" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L80" s="4" t="str">
         <f t="shared" si="4"/>
@@ -5287,11 +5321,11 @@
       </c>
       <c r="I81" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J81" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L81" s="4" t="str">
         <f t="shared" si="4"/>
@@ -5337,11 +5371,11 @@
       </c>
       <c r="I82" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J82" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L82" s="4" t="str">
         <f t="shared" si="4"/>
@@ -5387,11 +5421,11 @@
       </c>
       <c r="I83" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J83" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L83" s="4" t="str">
         <f t="shared" si="4"/>
@@ -5437,11 +5471,11 @@
       </c>
       <c r="I84" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J84" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L84" s="4" t="str">
         <f t="shared" si="4"/>
@@ -5487,11 +5521,11 @@
       </c>
       <c r="I85" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J85" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L85" s="4" t="str">
         <f t="shared" si="4"/>
@@ -5537,11 +5571,11 @@
       </c>
       <c r="I86" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J86" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L86" s="4" t="str">
         <f t="shared" si="4"/>
@@ -5587,11 +5621,11 @@
       </c>
       <c r="I87" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J87" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K87" s="2">
         <v>45272</v>
@@ -5637,11 +5671,11 @@
       </c>
       <c r="I88" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J88" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K88" s="2">
         <v>45273</v>
@@ -5687,11 +5721,11 @@
       </c>
       <c r="I89" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J89" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K89" s="2">
         <v>45274</v>
@@ -5737,11 +5771,11 @@
       </c>
       <c r="I90" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J90" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K90" s="2">
         <v>45275</v>
@@ -5787,11 +5821,11 @@
       </c>
       <c r="I91" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J91" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K91" s="2">
         <v>45276</v>
@@ -5837,11 +5871,11 @@
       </c>
       <c r="I92" s="4">
         <f t="shared" ref="I92:I93" ca="1" si="9">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H92), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H92), 7), "-")</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J92" s="4">
         <f t="shared" ref="J92:J93" ca="1" si="10">IF(_xlfn.DAYS(TODAY(),H92)&lt;10000, _xlfn.DAYS(TODAY(),H92), "-")</f>
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K92" s="2">
         <v>45277</v>
@@ -5887,11 +5921,11 @@
       </c>
       <c r="I93" s="4">
         <f t="shared" ca="1" si="9"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J93" s="4">
         <f t="shared" ca="1" si="10"/>
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K93" s="2">
         <v>45278</v>
@@ -5941,7 +5975,7 @@
       </c>
       <c r="J94" s="4">
         <f t="shared" ref="J94" ca="1" si="12">IF(_xlfn.DAYS(TODAY(),H94)&lt;10000, _xlfn.DAYS(TODAY(),H94), "-")</f>
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K94" s="2">
         <v>45223</v>
@@ -5991,7 +6025,7 @@
       </c>
       <c r="J95" s="4">
         <f t="shared" ref="J95:J117" ca="1" si="14">IF(_xlfn.DAYS(TODAY(),H95)&lt;10000, _xlfn.DAYS(TODAY(),H95), "-")</f>
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K95" s="2">
         <v>45223</v>
@@ -6041,7 +6075,7 @@
       </c>
       <c r="J96" s="4">
         <f t="shared" ca="1" si="14"/>
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K96" s="2">
         <v>45223</v>
@@ -6091,7 +6125,7 @@
       </c>
       <c r="J97" s="4">
         <f t="shared" ca="1" si="14"/>
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K97" s="2">
         <v>45223</v>
@@ -6141,7 +6175,7 @@
       </c>
       <c r="J98" s="4">
         <f t="shared" ref="J98:J107" ca="1" si="17">IF(_xlfn.DAYS(TODAY(),H98)&lt;10000, _xlfn.DAYS(TODAY(),H98), "-")</f>
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K98" s="2">
         <v>45267</v>
@@ -6194,7 +6228,7 @@
       </c>
       <c r="J99" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K99" s="2">
         <v>45267</v>
@@ -6247,7 +6281,7 @@
       </c>
       <c r="J100" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K100" s="2">
         <v>45267</v>
@@ -6300,7 +6334,7 @@
       </c>
       <c r="J101" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K101" s="2">
         <v>45267</v>
@@ -6353,7 +6387,7 @@
       </c>
       <c r="J102" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K102" s="2">
         <v>45267</v>
@@ -6406,7 +6440,7 @@
       </c>
       <c r="J103" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K103" s="2">
         <v>45267</v>
@@ -6459,7 +6493,7 @@
       </c>
       <c r="J104" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K104" s="2">
         <v>45267</v>
@@ -6512,7 +6546,7 @@
       </c>
       <c r="J105" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K105" s="2">
         <v>45267</v>
@@ -6565,7 +6599,7 @@
       </c>
       <c r="J106" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K106" s="2">
         <v>45267</v>
@@ -6618,7 +6652,7 @@
       </c>
       <c r="J107" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K107" s="2">
         <v>45267</v>
@@ -7166,7 +7200,7 @@
       </c>
       <c r="J120" s="4">
         <f t="shared" ca="1" si="19"/>
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K120" s="2">
         <v>45315</v>
@@ -7207,7 +7241,7 @@
       </c>
       <c r="J121" s="4">
         <f t="shared" ca="1" si="19"/>
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K121" s="2">
         <v>45315</v>
@@ -7248,7 +7282,7 @@
       </c>
       <c r="J122" s="4">
         <f t="shared" ca="1" si="19"/>
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K122" s="2">
         <v>45315</v>
@@ -7289,7 +7323,7 @@
       </c>
       <c r="J123" s="4">
         <f t="shared" ca="1" si="19"/>
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K123" s="2">
         <v>45315</v>
@@ -7309,8 +7343,14 @@
       <c r="C124" t="s">
         <v>125</v>
       </c>
+      <c r="D124">
+        <v>798</v>
+      </c>
       <c r="E124" t="s">
         <v>16</v>
+      </c>
+      <c r="F124" s="5" t="s">
+        <v>232</v>
       </c>
       <c r="H124" s="2">
         <v>45309</v>
@@ -7321,7 +7361,7 @@
       </c>
       <c r="J124" s="4">
         <f t="shared" ca="1" si="19"/>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L124" s="4" t="str">
         <f t="shared" si="15"/>
@@ -7331,7 +7371,7 @@
         <v>220</v>
       </c>
       <c r="Q124" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="125" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -7341,8 +7381,14 @@
       <c r="C125" t="s">
         <v>125</v>
       </c>
+      <c r="D125">
+        <v>797</v>
+      </c>
       <c r="E125" t="s">
         <v>16</v>
+      </c>
+      <c r="F125" s="5" t="s">
+        <v>233</v>
       </c>
       <c r="H125" s="2">
         <v>45309</v>
@@ -7353,7 +7399,7 @@
       </c>
       <c r="J125" s="4">
         <f t="shared" ref="J125:J127" ca="1" si="21">IF(_xlfn.DAYS(TODAY(),H125)&lt;10000, _xlfn.DAYS(TODAY(),H125), "-")</f>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L125" s="4" t="str">
         <f t="shared" si="15"/>
@@ -7363,7 +7409,7 @@
         <v>220</v>
       </c>
       <c r="Q125" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="126" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -7373,8 +7419,14 @@
       <c r="C126" t="s">
         <v>125</v>
       </c>
+      <c r="D126">
+        <v>796</v>
+      </c>
       <c r="E126" t="s">
         <v>16</v>
+      </c>
+      <c r="F126" s="5" t="s">
+        <v>232</v>
       </c>
       <c r="H126" s="2">
         <v>45309</v>
@@ -7385,7 +7437,7 @@
       </c>
       <c r="J126" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L126" s="4" t="str">
         <f t="shared" si="15"/>
@@ -7395,7 +7447,7 @@
         <v>221</v>
       </c>
       <c r="Q126" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="127" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -7405,8 +7457,14 @@
       <c r="C127" t="s">
         <v>125</v>
       </c>
+      <c r="D127">
+        <v>795</v>
+      </c>
       <c r="E127" t="s">
         <v>16</v>
+      </c>
+      <c r="F127" s="5" t="s">
+        <v>234</v>
       </c>
       <c r="H127" s="2">
         <v>45309</v>
@@ -7417,7 +7475,7 @@
       </c>
       <c r="J127" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L127" s="4" t="str">
         <f t="shared" si="15"/>
@@ -7427,7 +7485,7 @@
         <v>221</v>
       </c>
       <c r="Q127" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="128" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -7437,8 +7495,14 @@
       <c r="C128" t="s">
         <v>125</v>
       </c>
+      <c r="D128">
+        <v>794</v>
+      </c>
       <c r="E128" t="s">
         <v>16</v>
+      </c>
+      <c r="F128" s="5" t="s">
+        <v>233</v>
       </c>
       <c r="H128" s="2">
         <v>45309</v>
@@ -7449,7 +7513,7 @@
       </c>
       <c r="J128" s="4">
         <f t="shared" ref="J128:J130" ca="1" si="23">IF(_xlfn.DAYS(TODAY(),H128)&lt;10000, _xlfn.DAYS(TODAY(),H128), "-")</f>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L128" s="4" t="str">
         <f t="shared" si="15"/>
@@ -7459,7 +7523,7 @@
         <v>221</v>
       </c>
       <c r="Q128" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="129" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -7469,8 +7533,14 @@
       <c r="C129" t="s">
         <v>125</v>
       </c>
+      <c r="D129">
+        <v>793</v>
+      </c>
       <c r="E129" t="s">
         <v>16</v>
+      </c>
+      <c r="F129" s="5" t="s">
+        <v>233</v>
       </c>
       <c r="H129" s="2">
         <v>45309</v>
@@ -7481,7 +7551,7 @@
       </c>
       <c r="J129" s="4">
         <f t="shared" ca="1" si="23"/>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L129" s="4" t="str">
         <f t="shared" si="15"/>
@@ -7491,7 +7561,7 @@
         <v>221</v>
       </c>
       <c r="Q129" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="130" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -7501,8 +7571,14 @@
       <c r="C130" t="s">
         <v>125</v>
       </c>
+      <c r="D130">
+        <v>792</v>
+      </c>
       <c r="E130" t="s">
         <v>16</v>
+      </c>
+      <c r="F130" s="5" t="s">
+        <v>233</v>
       </c>
       <c r="H130" s="2">
         <v>45309</v>
@@ -7513,7 +7589,7 @@
       </c>
       <c r="J130" s="4">
         <f t="shared" ca="1" si="23"/>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L130" s="4" t="str">
         <f t="shared" si="15"/>
@@ -7523,10 +7599,10 @@
         <v>221</v>
       </c>
       <c r="Q130" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="131" spans="2:17" x14ac:dyDescent="0.3">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="131" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B131" t="s">
         <v>5</v>
       </c>
@@ -7555,7 +7631,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="132" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="132" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B132" t="s">
         <v>5</v>
       </c>
@@ -7577,7 +7653,7 @@
       </c>
       <c r="J132" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L132" s="4" t="str">
         <f t="shared" si="26"/>
@@ -7590,7 +7666,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="133" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="133" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B133" t="s">
         <v>5</v>
       </c>
@@ -7612,7 +7688,7 @@
       </c>
       <c r="J133" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="L133" s="4" t="str">
         <f t="shared" si="26"/>
@@ -7622,7 +7698,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="134" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="134" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B134" t="s">
         <v>5</v>
       </c>
@@ -7644,7 +7720,7 @@
       </c>
       <c r="J134" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="L134" s="4" t="str">
         <f t="shared" si="26"/>
@@ -7654,7 +7730,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="135" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="135" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B135" t="s">
         <v>5</v>
       </c>
@@ -7676,7 +7752,7 @@
       </c>
       <c r="J135" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L135" s="4" t="str">
         <f t="shared" si="26"/>
@@ -7689,7 +7765,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="136" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="136" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B136" t="s">
         <v>5</v>
       </c>
@@ -7711,7 +7787,7 @@
       </c>
       <c r="J136" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="L136" s="4" t="str">
         <f t="shared" si="26"/>
@@ -7721,7 +7797,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="137" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="137" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B137" t="s">
         <v>5</v>
       </c>
@@ -7743,7 +7819,7 @@
       </c>
       <c r="J137" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="L137" s="4" t="str">
         <f t="shared" si="26"/>
@@ -7753,7 +7829,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="138" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B138" t="s">
         <v>141</v>
       </c>
@@ -7780,6 +7856,9 @@
       </c>
       <c r="M138" s="4" t="s">
         <v>166</v>
+      </c>
+      <c r="Q138" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="139" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -7814,7 +7893,7 @@
         <v>45322</v>
       </c>
     </row>
-    <row r="140" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B140" t="s">
         <v>141</v>
       </c>
@@ -7842,27 +7921,36 @@
       <c r="M140" s="4" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="141" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q140" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="141" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B141" t="s">
         <v>141</v>
       </c>
       <c r="C141" t="s">
         <v>142</v>
       </c>
+      <c r="D141">
+        <v>791</v>
+      </c>
       <c r="E141" s="2" t="s">
         <v>150</v>
       </c>
+      <c r="F141" s="5" t="s">
+        <v>233</v>
+      </c>
       <c r="H141" s="2">
         <v>45301</v>
       </c>
       <c r="I141" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J141" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L141" s="4" t="str">
         <f t="shared" si="26"/>
@@ -7871,30 +7959,33 @@
       <c r="M141" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="Q141" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="142" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="142" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B142" t="s">
         <v>141</v>
       </c>
       <c r="C142" t="s">
         <v>142</v>
       </c>
+      <c r="D142">
+        <v>790</v>
+      </c>
       <c r="E142" t="s">
         <v>150</v>
       </c>
+      <c r="F142" s="5" t="s">
+        <v>233</v>
+      </c>
       <c r="H142" s="2">
         <v>45301</v>
       </c>
       <c r="I142" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J142" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L142" s="4" t="str">
         <f t="shared" si="26"/>
@@ -7903,30 +7994,33 @@
       <c r="M142" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="Q142" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="143" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="143" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B143" t="s">
         <v>141</v>
       </c>
       <c r="C143" t="s">
         <v>142</v>
       </c>
+      <c r="D143">
+        <v>789</v>
+      </c>
       <c r="E143" t="s">
         <v>150</v>
       </c>
+      <c r="F143" s="5" t="s">
+        <v>233</v>
+      </c>
       <c r="H143" s="2">
         <v>45301</v>
       </c>
       <c r="I143" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J143" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L143" s="4" t="str">
         <f t="shared" si="26"/>
@@ -7935,30 +8029,33 @@
       <c r="M143" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="Q143" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="144" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="144" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B144" t="s">
         <v>141</v>
       </c>
       <c r="C144" t="s">
         <v>142</v>
       </c>
+      <c r="D144">
+        <v>788</v>
+      </c>
       <c r="E144" s="2" t="s">
         <v>150</v>
       </c>
+      <c r="F144" s="5" t="s">
+        <v>233</v>
+      </c>
       <c r="H144" s="2">
         <v>45301</v>
       </c>
       <c r="I144" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J144" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L144" s="4" t="str">
         <f t="shared" si="26"/>
@@ -7967,30 +8064,33 @@
       <c r="M144" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="Q144" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="145" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="145" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B145" t="s">
         <v>141</v>
       </c>
       <c r="C145" t="s">
         <v>142</v>
       </c>
+      <c r="D145">
+        <v>787</v>
+      </c>
       <c r="E145" t="s">
         <v>150</v>
       </c>
+      <c r="F145" s="5" t="s">
+        <v>234</v>
+      </c>
       <c r="H145" s="2">
         <v>45301</v>
       </c>
       <c r="I145" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J145" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L145" s="4" t="str">
         <f t="shared" si="26"/>
@@ -7999,30 +8099,33 @@
       <c r="M145" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="Q145" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="146" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="146" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B146" t="s">
         <v>141</v>
       </c>
       <c r="C146" t="s">
         <v>142</v>
       </c>
+      <c r="D146">
+        <v>786</v>
+      </c>
       <c r="E146" t="s">
         <v>150</v>
       </c>
+      <c r="F146" s="5" t="s">
+        <v>233</v>
+      </c>
       <c r="H146" s="2">
         <v>45301</v>
       </c>
       <c r="I146" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J146" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L146" s="4" t="str">
         <f t="shared" si="26"/>
@@ -8031,11 +8134,8 @@
       <c r="M146" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="Q146" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="147" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="147" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B147" t="s">
         <v>141</v>
       </c>
@@ -8063,8 +8163,11 @@
       <c r="M147" s="4" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="148" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q147" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="148" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B148" t="s">
         <v>141</v>
       </c>
@@ -8092,8 +8195,11 @@
       <c r="M148" s="4" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="149" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q148" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="149" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B149" t="s">
         <v>141</v>
       </c>
@@ -8121,8 +8227,11 @@
       <c r="M149" s="4" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="150" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q149" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="150" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B150" t="s">
         <v>141</v>
       </c>
@@ -8150,16 +8259,25 @@
       <c r="M150" s="4" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="151" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q150" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="151" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B151" t="s">
         <v>141</v>
       </c>
       <c r="C151" t="s">
         <v>142</v>
       </c>
+      <c r="D151">
+        <v>785</v>
+      </c>
       <c r="E151" s="2" t="s">
         <v>150</v>
+      </c>
+      <c r="F151" s="5" t="s">
+        <v>233</v>
       </c>
       <c r="H151" s="2">
         <v>45307</v>
@@ -8170,7 +8288,7 @@
       </c>
       <c r="J151" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L151" s="4" t="str">
         <f t="shared" si="29"/>
@@ -8180,15 +8298,21 @@
         <v>218</v>
       </c>
     </row>
-    <row r="152" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B152" t="s">
         <v>141</v>
       </c>
       <c r="C152" t="s">
         <v>142</v>
       </c>
+      <c r="D152">
+        <v>784</v>
+      </c>
       <c r="E152" t="s">
         <v>150</v>
+      </c>
+      <c r="F152" s="5" t="s">
+        <v>234</v>
       </c>
       <c r="H152" s="2">
         <v>45307</v>
@@ -8199,7 +8323,7 @@
       </c>
       <c r="J152" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L152" s="4" t="str">
         <f t="shared" si="29"/>
@@ -8209,15 +8333,21 @@
         <v>218</v>
       </c>
     </row>
-    <row r="153" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B153" t="s">
         <v>141</v>
       </c>
       <c r="C153" t="s">
         <v>142</v>
       </c>
+      <c r="D153">
+        <v>783</v>
+      </c>
       <c r="E153" t="s">
         <v>150</v>
+      </c>
+      <c r="F153" s="5" t="s">
+        <v>232</v>
       </c>
       <c r="H153" s="2">
         <v>45307</v>
@@ -8228,7 +8358,7 @@
       </c>
       <c r="J153" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L153" s="4" t="str">
         <f t="shared" si="29"/>
@@ -8238,15 +8368,21 @@
         <v>218</v>
       </c>
     </row>
-    <row r="154" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B154" t="s">
         <v>141</v>
       </c>
       <c r="C154" t="s">
         <v>142</v>
       </c>
+      <c r="D154">
+        <v>782</v>
+      </c>
       <c r="E154" s="2" t="s">
         <v>150</v>
+      </c>
+      <c r="F154" s="5" t="s">
+        <v>232</v>
       </c>
       <c r="H154" s="2">
         <v>45307</v>
@@ -8257,7 +8393,7 @@
       </c>
       <c r="J154" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L154" s="4" t="str">
         <f t="shared" si="29"/>
@@ -8267,15 +8403,21 @@
         <v>218</v>
       </c>
     </row>
-    <row r="155" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B155" t="s">
         <v>141</v>
       </c>
       <c r="C155" t="s">
         <v>142</v>
       </c>
+      <c r="D155">
+        <v>781</v>
+      </c>
       <c r="E155" t="s">
         <v>150</v>
+      </c>
+      <c r="F155" s="5" t="s">
+        <v>233</v>
       </c>
       <c r="H155" s="2">
         <v>45307</v>
@@ -8286,7 +8428,7 @@
       </c>
       <c r="J155" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L155" s="4" t="str">
         <f t="shared" si="29"/>
@@ -8296,15 +8438,21 @@
         <v>218</v>
       </c>
     </row>
-    <row r="156" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B156" t="s">
         <v>141</v>
       </c>
       <c r="C156" t="s">
         <v>142</v>
       </c>
+      <c r="D156">
+        <v>780</v>
+      </c>
       <c r="E156" t="s">
         <v>150</v>
+      </c>
+      <c r="F156" s="5" t="s">
+        <v>233</v>
       </c>
       <c r="H156" s="2">
         <v>45307</v>
@@ -8315,7 +8463,7 @@
       </c>
       <c r="J156" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L156" s="4" t="str">
         <f t="shared" si="29"/>
@@ -8349,11 +8497,11 @@
       </c>
       <c r="I157" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J157" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L157" s="4" t="str">
         <f t="shared" si="29"/>
@@ -8407,7 +8555,7 @@
         <v>45329</v>
       </c>
     </row>
-    <row r="159" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B159" t="s">
         <v>141</v>
       </c>
@@ -8438,8 +8586,11 @@
       <c r="M159" s="4" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="160" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q159" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="160" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B160" t="s">
         <v>141</v>
       </c>
@@ -8470,8 +8621,11 @@
       <c r="M160" s="4" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="161" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q160" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="161" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B161" t="s">
         <v>141</v>
       </c>
@@ -8499,7 +8653,7 @@
       </c>
       <c r="J161" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K161" s="2">
         <v>45301</v>
@@ -8512,7 +8666,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="162" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B162" t="s">
         <v>141</v>
       </c>
@@ -8540,7 +8694,7 @@
       </c>
       <c r="J162" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K162" s="2">
         <v>45301</v>
@@ -8578,7 +8732,7 @@
       </c>
       <c r="J163" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K163" s="2">
         <v>45301</v>
@@ -8597,7 +8751,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="164" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B164" t="s">
         <v>141</v>
       </c>
@@ -8625,7 +8779,7 @@
       </c>
       <c r="J164" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K164" s="2">
         <v>45301</v>
@@ -8666,7 +8820,7 @@
       </c>
       <c r="J165" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K165" s="2">
         <v>45301</v>
@@ -8719,7 +8873,7 @@
       </c>
       <c r="J166" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K166" s="2">
         <v>45301</v>
@@ -8731,8 +8885,11 @@
       <c r="M166" s="4" t="s">
         <v>154</v>
       </c>
+      <c r="O166" s="2">
+        <v>45350</v>
+      </c>
       <c r="Q166" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="167" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -8756,11 +8913,11 @@
       </c>
       <c r="I167" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J167" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L167" s="4" t="str">
         <f t="shared" si="29"/>
@@ -8797,11 +8954,11 @@
       </c>
       <c r="I168" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J168" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L168" s="4" t="str">
         <f t="shared" si="29"/>
@@ -8838,11 +8995,11 @@
       </c>
       <c r="I169" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J169" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L169" s="4" t="str">
         <f t="shared" si="29"/>
@@ -8886,7 +9043,7 @@
       </c>
       <c r="J170" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K170" s="2">
         <v>45301</v>
@@ -8911,7 +9068,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="171" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B171" t="s">
         <v>141</v>
       </c>
@@ -8939,7 +9096,7 @@
       </c>
       <c r="J171" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K171" s="2">
         <v>45301</v>
@@ -8980,7 +9137,7 @@
       </c>
       <c r="J172" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K172" s="2">
         <v>45301</v>
@@ -9027,7 +9184,7 @@
       </c>
       <c r="J173" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K173" s="2">
         <v>45301</v>
@@ -9074,7 +9231,7 @@
       </c>
       <c r="J174" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K174" s="2">
         <v>45301</v>
@@ -9093,7 +9250,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="175" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B175" t="s">
         <v>141</v>
       </c>
@@ -9121,7 +9278,7 @@
       </c>
       <c r="J175" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L175" s="4" t="str">
         <f t="shared" si="29"/>
@@ -9159,7 +9316,7 @@
       </c>
       <c r="J176" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L176" s="4" t="str">
         <f t="shared" si="29"/>
@@ -9200,7 +9357,7 @@
       </c>
       <c r="J177" s="4">
         <f t="shared" ref="J177" ca="1" si="31">IF(_xlfn.DAYS(TODAY(),H177)&lt;10000, _xlfn.DAYS(TODAY(),H177), "-")</f>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K177" s="16">
         <v>45324</v>
@@ -9235,7 +9392,7 @@
       </c>
       <c r="J178" s="4">
         <f t="shared" ref="J178:J187" ca="1" si="34">IF(_xlfn.DAYS(TODAY(),H178)&lt;10000, _xlfn.DAYS(TODAY(),H178), "-")</f>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K178" s="16">
         <v>45324</v>
@@ -9270,7 +9427,7 @@
       </c>
       <c r="J179" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K179" s="16">
         <v>45324</v>
@@ -9305,7 +9462,7 @@
       </c>
       <c r="J180" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K180" s="16">
         <v>45324</v>
@@ -9340,7 +9497,7 @@
       </c>
       <c r="J181" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K181" s="16">
         <v>45324</v>
@@ -9375,7 +9532,7 @@
       </c>
       <c r="J182" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K182" s="16">
         <v>45324</v>
@@ -9410,7 +9567,7 @@
       </c>
       <c r="J183" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K183" s="16">
         <v>45324</v>
@@ -9445,7 +9602,7 @@
       </c>
       <c r="J184" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K184" s="16">
         <v>45324</v>
@@ -9480,7 +9637,7 @@
       </c>
       <c r="J185" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K185" s="16">
         <v>45324</v>
@@ -9509,13 +9666,13 @@
       </c>
       <c r="J186" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M186" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="187" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B187" t="s">
         <v>5</v>
       </c>
@@ -9534,7 +9691,7 @@
       </c>
       <c r="J187" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L187" s="4" t="str">
         <f t="shared" ref="L187" si="36">IF(_xlfn.DAYS(K187,H187)&gt;0, _xlfn.DAYS(K187,H187), "-")</f>
@@ -9544,10 +9701,10 @@
         <v>186</v>
       </c>
       <c r="Q187" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="188" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="188" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B188" t="s">
         <v>5</v>
       </c>
@@ -9566,7 +9723,7 @@
       </c>
       <c r="J188" s="4">
         <f t="shared" ref="J188:J194" ca="1" si="38">IF(_xlfn.DAYS(TODAY(),H188)&lt;10000, _xlfn.DAYS(TODAY(),H188), "-")</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L188" s="4" t="str">
         <f t="shared" ref="L188:L194" si="39">IF(_xlfn.DAYS(K188,H188)&gt;0, _xlfn.DAYS(K188,H188), "-")</f>
@@ -9576,10 +9733,10 @@
         <v>186</v>
       </c>
       <c r="Q188" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="189" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="189" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B189" t="s">
         <v>5</v>
       </c>
@@ -9598,7 +9755,7 @@
       </c>
       <c r="J189" s="4">
         <f t="shared" ca="1" si="38"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L189" s="4" t="str">
         <f t="shared" si="39"/>
@@ -9608,10 +9765,10 @@
         <v>186</v>
       </c>
       <c r="Q189" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="190" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="190" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B190" t="s">
         <v>5</v>
       </c>
@@ -9630,7 +9787,7 @@
       </c>
       <c r="J190" s="4">
         <f t="shared" ca="1" si="38"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L190" s="4" t="str">
         <f t="shared" si="39"/>
@@ -9640,10 +9797,10 @@
         <v>186</v>
       </c>
       <c r="Q190" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="191" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="191" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B191" t="s">
         <v>5</v>
       </c>
@@ -9662,7 +9819,7 @@
       </c>
       <c r="J191" s="4">
         <f t="shared" ca="1" si="38"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L191" s="4" t="str">
         <f t="shared" si="39"/>
@@ -9672,10 +9829,10 @@
         <v>186</v>
       </c>
       <c r="Q191" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="192" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="192" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B192" t="s">
         <v>5</v>
       </c>
@@ -9694,7 +9851,7 @@
       </c>
       <c r="J192" s="4">
         <f t="shared" ca="1" si="38"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L192" s="4" t="str">
         <f t="shared" si="39"/>
@@ -9704,10 +9861,10 @@
         <v>186</v>
       </c>
       <c r="Q192" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="193" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="193" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B193" t="s">
         <v>5</v>
       </c>
@@ -9726,7 +9883,7 @@
       </c>
       <c r="J193" s="4">
         <f t="shared" ca="1" si="38"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L193" s="4" t="str">
         <f t="shared" si="39"/>
@@ -9736,10 +9893,10 @@
         <v>186</v>
       </c>
       <c r="Q193" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="194" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="194" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B194" t="s">
         <v>5</v>
       </c>
@@ -9758,7 +9915,7 @@
       </c>
       <c r="J194" s="4">
         <f t="shared" ca="1" si="38"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L194" s="4" t="str">
         <f t="shared" si="39"/>
@@ -9768,10 +9925,10 @@
         <v>186</v>
       </c>
       <c r="Q194" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="195" spans="2:17" x14ac:dyDescent="0.3">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="195" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B195" t="s">
         <v>187</v>
       </c>
@@ -9794,7 +9951,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="196" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="196" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B196" t="s">
         <v>187</v>
       </c>
@@ -9820,7 +9977,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="197" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="197" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B197" t="s">
         <v>187</v>
       </c>
@@ -9843,7 +10000,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="198" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="198" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B198" t="s">
         <v>187</v>
       </c>
@@ -9866,7 +10023,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="199" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="199" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B199" t="s">
         <v>187</v>
       </c>
@@ -9889,7 +10046,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="200" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="200" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B200" t="s">
         <v>187</v>
       </c>
@@ -9934,7 +10091,7 @@
       </c>
       <c r="J201" s="4">
         <f t="shared" ref="J201" ca="1" si="41">IF(_xlfn.DAYS(TODAY(),H201)&lt;10000, _xlfn.DAYS(TODAY(),H201), "-")</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L201" s="4" t="str">
         <f t="shared" ref="L201" si="42">IF(_xlfn.DAYS(K201,H201)&gt;0, _xlfn.DAYS(K201,H201), "-")</f>
@@ -9963,7 +10120,7 @@
       </c>
       <c r="J202" s="4">
         <f t="shared" ref="J202:J217" ca="1" si="44">IF(_xlfn.DAYS(TODAY(),H202)&lt;10000, _xlfn.DAYS(TODAY(),H202), "-")</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L202" s="4" t="str">
         <f t="shared" ref="L202:L217" si="45">IF(_xlfn.DAYS(K202,H202)&gt;0, _xlfn.DAYS(K202,H202), "-")</f>
@@ -9992,7 +10149,7 @@
       </c>
       <c r="J203" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L203" s="4" t="str">
         <f t="shared" si="45"/>
@@ -10021,7 +10178,7 @@
       </c>
       <c r="J204" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L204" s="4" t="str">
         <f t="shared" si="45"/>
@@ -10050,7 +10207,7 @@
       </c>
       <c r="J205" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L205" s="4" t="str">
         <f t="shared" si="45"/>
@@ -10079,7 +10236,7 @@
       </c>
       <c r="J206" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L206" s="4" t="str">
         <f t="shared" si="45"/>
@@ -10108,7 +10265,7 @@
       </c>
       <c r="J207" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L207" s="4" t="str">
         <f t="shared" si="45"/>
@@ -10137,7 +10294,7 @@
       </c>
       <c r="J208" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L208" s="4" t="str">
         <f t="shared" si="45"/>
@@ -10147,7 +10304,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="209" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B209" t="s">
         <v>5</v>
       </c>
@@ -10166,7 +10323,7 @@
       </c>
       <c r="J209" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L209" s="4" t="str">
         <f t="shared" si="45"/>
@@ -10176,7 +10333,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="210" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B210" t="s">
         <v>5</v>
       </c>
@@ -10195,7 +10352,7 @@
       </c>
       <c r="J210" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L210" s="4" t="str">
         <f t="shared" si="45"/>
@@ -10205,7 +10362,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="211" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B211" t="s">
         <v>5</v>
       </c>
@@ -10224,7 +10381,7 @@
       </c>
       <c r="J211" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L211" s="4" t="str">
         <f t="shared" si="45"/>
@@ -10234,7 +10391,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="212" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B212" t="s">
         <v>5</v>
       </c>
@@ -10253,7 +10410,7 @@
       </c>
       <c r="J212" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L212" s="4" t="str">
         <f t="shared" si="45"/>
@@ -10263,7 +10420,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="213" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B213" t="s">
         <v>5</v>
       </c>
@@ -10282,7 +10439,7 @@
       </c>
       <c r="J213" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L213" s="4" t="str">
         <f t="shared" si="45"/>
@@ -10292,7 +10449,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="214" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B214" t="s">
         <v>5</v>
       </c>
@@ -10311,7 +10468,7 @@
       </c>
       <c r="J214" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L214" s="4" t="str">
         <f t="shared" si="45"/>
@@ -10321,7 +10478,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="215" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B215" t="s">
         <v>5</v>
       </c>
@@ -10340,7 +10497,7 @@
       </c>
       <c r="J215" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L215" s="4" t="str">
         <f t="shared" si="45"/>
@@ -10350,7 +10507,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="216" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B216" t="s">
         <v>5</v>
       </c>
@@ -10369,7 +10526,7 @@
       </c>
       <c r="J216" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L216" s="4" t="str">
         <f t="shared" si="45"/>
@@ -10379,7 +10536,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="217" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B217" t="s">
         <v>5</v>
       </c>
@@ -10398,7 +10555,7 @@
       </c>
       <c r="J217" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L217" s="4" t="str">
         <f t="shared" si="45"/>
@@ -10408,24 +10565,36 @@
         <v>223</v>
       </c>
     </row>
-    <row r="218" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="218" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B218" t="s">
         <v>5</v>
       </c>
       <c r="C218" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="E218" t="s">
-        <v>225</v>
-      </c>
-      <c r="M218" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="Q218" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="219" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+        <v>228</v>
+      </c>
+      <c r="H218" s="2">
+        <v>45343</v>
+      </c>
+      <c r="I218" s="4">
+        <f t="shared" ref="I218:I235" ca="1" si="46">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H218), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H218), 7), "-")</f>
+        <v>1</v>
+      </c>
+      <c r="J218" s="4">
+        <f t="shared" ref="J218:J235" ca="1" si="47">IF(_xlfn.DAYS(TODAY(),H218)&lt;10000, _xlfn.DAYS(TODAY(),H218), "-")</f>
+        <v>7</v>
+      </c>
+      <c r="L218" s="4" t="str">
+        <f t="shared" ref="L218:L235" si="48">IF(_xlfn.DAYS(K218,H218)&gt;0, _xlfn.DAYS(K218,H218), "-")</f>
+        <v>-</v>
+      </c>
+      <c r="M218" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="219" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B219" t="s">
         <v>5</v>
       </c>
@@ -10433,28 +10602,28 @@
         <v>142</v>
       </c>
       <c r="E219" t="s">
-        <v>229</v>
+        <v>16</v>
       </c>
       <c r="H219" s="2">
         <v>45343</v>
       </c>
       <c r="I219" s="4">
-        <f t="shared" ref="I219:I232" ca="1" si="46">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H219), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H219), 7), "-")</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="46"/>
+        <v>1</v>
       </c>
       <c r="J219" s="4">
-        <f t="shared" ref="J219:J232" ca="1" si="47">IF(_xlfn.DAYS(TODAY(),H219)&lt;10000, _xlfn.DAYS(TODAY(),H219), "-")</f>
-        <v>6</v>
+        <f t="shared" ca="1" si="47"/>
+        <v>7</v>
       </c>
       <c r="L219" s="4" t="str">
-        <f t="shared" ref="L219:L232" si="48">IF(_xlfn.DAYS(K219,H219)&gt;0, _xlfn.DAYS(K219,H219), "-")</f>
+        <f t="shared" si="48"/>
         <v>-</v>
       </c>
       <c r="M219" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="220" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="220" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B220" t="s">
         <v>5</v>
       </c>
@@ -10469,28 +10638,28 @@
       </c>
       <c r="I220" s="4">
         <f t="shared" ca="1" si="46"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J220" s="4">
         <f t="shared" ca="1" si="47"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L220" s="4" t="str">
         <f t="shared" si="48"/>
         <v>-</v>
       </c>
       <c r="M220" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="221" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="221" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B221" t="s">
         <v>5</v>
       </c>
       <c r="C221" t="s">
         <v>142</v>
       </c>
-      <c r="E221" t="s">
+      <c r="E221" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H221" s="2">
@@ -10498,28 +10667,28 @@
       </c>
       <c r="I221" s="4">
         <f t="shared" ca="1" si="46"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J221" s="4">
         <f t="shared" ca="1" si="47"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L221" s="4" t="str">
         <f t="shared" si="48"/>
         <v>-</v>
       </c>
       <c r="M221" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="222" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="222" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B222" t="s">
         <v>5</v>
       </c>
       <c r="C222" t="s">
         <v>142</v>
       </c>
-      <c r="E222" s="2" t="s">
+      <c r="E222" t="s">
         <v>16</v>
       </c>
       <c r="H222" s="2">
@@ -10527,21 +10696,21 @@
       </c>
       <c r="I222" s="4">
         <f t="shared" ca="1" si="46"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J222" s="4">
         <f t="shared" ca="1" si="47"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L222" s="4" t="str">
         <f t="shared" si="48"/>
         <v>-</v>
       </c>
       <c r="M222" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="223" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="223" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B223" t="s">
         <v>5</v>
       </c>
@@ -10556,21 +10725,21 @@
       </c>
       <c r="I223" s="4">
         <f t="shared" ca="1" si="46"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J223" s="4">
         <f t="shared" ca="1" si="47"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L223" s="4" t="str">
         <f t="shared" si="48"/>
         <v>-</v>
       </c>
       <c r="M223" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="224" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="224" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B224" t="s">
         <v>5</v>
       </c>
@@ -10585,21 +10754,21 @@
       </c>
       <c r="I224" s="4">
         <f t="shared" ca="1" si="46"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J224" s="4">
         <f t="shared" ca="1" si="47"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L224" s="4" t="str">
         <f t="shared" si="48"/>
         <v>-</v>
       </c>
       <c r="M224" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="225" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="225" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B225" t="s">
         <v>5</v>
       </c>
@@ -10614,21 +10783,21 @@
       </c>
       <c r="I225" s="4">
         <f t="shared" ca="1" si="46"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J225" s="4">
         <f t="shared" ca="1" si="47"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L225" s="4" t="str">
         <f t="shared" si="48"/>
         <v>-</v>
       </c>
       <c r="M225" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="226" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="226" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B226" t="s">
         <v>5</v>
       </c>
@@ -10643,11 +10812,11 @@
       </c>
       <c r="I226" s="4">
         <f t="shared" ca="1" si="46"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J226" s="4">
         <f t="shared" ca="1" si="47"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L226" s="4" t="str">
         <f t="shared" si="48"/>
@@ -10657,14 +10826,14 @@
         <v>227</v>
       </c>
     </row>
-    <row r="227" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B227" t="s">
         <v>5</v>
       </c>
       <c r="C227" t="s">
         <v>142</v>
       </c>
-      <c r="E227" t="s">
+      <c r="E227" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H227" s="2">
@@ -10672,28 +10841,28 @@
       </c>
       <c r="I227" s="4">
         <f t="shared" ca="1" si="46"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J227" s="4">
         <f t="shared" ca="1" si="47"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L227" s="4" t="str">
         <f t="shared" si="48"/>
         <v>-</v>
       </c>
       <c r="M227" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="228" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="228" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B228" t="s">
         <v>5</v>
       </c>
       <c r="C228" t="s">
         <v>142</v>
       </c>
-      <c r="E228" s="2" t="s">
+      <c r="E228" t="s">
         <v>16</v>
       </c>
       <c r="H228" s="2">
@@ -10701,21 +10870,21 @@
       </c>
       <c r="I228" s="4">
         <f t="shared" ca="1" si="46"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J228" s="4">
         <f t="shared" ca="1" si="47"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L228" s="4" t="str">
         <f t="shared" si="48"/>
         <v>-</v>
       </c>
       <c r="M228" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="229" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="229" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B229" t="s">
         <v>5</v>
       </c>
@@ -10730,21 +10899,21 @@
       </c>
       <c r="I229" s="4">
         <f t="shared" ca="1" si="46"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J229" s="4">
         <f t="shared" ca="1" si="47"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L229" s="4" t="str">
         <f t="shared" si="48"/>
         <v>-</v>
       </c>
       <c r="M229" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="230" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="230" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B230" t="s">
         <v>5</v>
       </c>
@@ -10759,21 +10928,21 @@
       </c>
       <c r="I230" s="4">
         <f t="shared" ca="1" si="46"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J230" s="4">
         <f t="shared" ca="1" si="47"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L230" s="4" t="str">
         <f t="shared" si="48"/>
         <v>-</v>
       </c>
       <c r="M230" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="231" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="231" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B231" t="s">
         <v>5</v>
       </c>
@@ -10788,18 +10957,18 @@
       </c>
       <c r="I231" s="4">
         <f t="shared" ca="1" si="46"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J231" s="4">
         <f t="shared" ca="1" si="47"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L231" s="4" t="str">
         <f t="shared" si="48"/>
         <v>-</v>
       </c>
       <c r="M231" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="232" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
@@ -10807,32 +10976,206 @@
         <v>5</v>
       </c>
       <c r="C232" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="E232" t="s">
         <v>16</v>
       </c>
       <c r="H232" s="2">
-        <v>45343</v>
+        <v>45337</v>
       </c>
       <c r="I232" s="4">
         <f t="shared" ca="1" si="46"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J232" s="4">
         <f t="shared" ca="1" si="47"/>
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="L232" s="4" t="str">
         <f t="shared" si="48"/>
         <v>-</v>
       </c>
-      <c r="M232" t="s">
-        <v>228</v>
+      <c r="M232" s="4" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="233" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B233" t="s">
+        <v>5</v>
+      </c>
+      <c r="C233" t="s">
+        <v>124</v>
+      </c>
+      <c r="E233" t="s">
+        <v>16</v>
+      </c>
+      <c r="H233" s="2">
+        <v>45337</v>
+      </c>
+      <c r="I233" s="4">
+        <f t="shared" ca="1" si="46"/>
+        <v>1</v>
+      </c>
+      <c r="J233" s="4">
+        <f t="shared" ca="1" si="47"/>
+        <v>13</v>
+      </c>
+      <c r="L233" s="4" t="str">
+        <f t="shared" si="48"/>
+        <v>-</v>
+      </c>
+      <c r="M233" s="4" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="234" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B234" t="s">
+        <v>5</v>
+      </c>
+      <c r="C234" t="s">
+        <v>124</v>
+      </c>
+      <c r="E234" t="s">
+        <v>16</v>
+      </c>
+      <c r="H234" s="2">
+        <v>45337</v>
+      </c>
+      <c r="I234" s="4">
+        <f t="shared" ca="1" si="46"/>
+        <v>1</v>
+      </c>
+      <c r="J234" s="4">
+        <f t="shared" ca="1" si="47"/>
+        <v>13</v>
+      </c>
+      <c r="L234" s="4" t="str">
+        <f t="shared" si="48"/>
+        <v>-</v>
+      </c>
+      <c r="M234" s="4" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="235" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B235" t="s">
+        <v>5</v>
+      </c>
+      <c r="C235" t="s">
+        <v>142</v>
+      </c>
+      <c r="E235" t="s">
+        <v>16</v>
+      </c>
+      <c r="H235" s="2">
+        <v>45349</v>
+      </c>
+      <c r="I235" s="4">
+        <f t="shared" ca="1" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="J235" s="4">
+        <f t="shared" ca="1" si="47"/>
+        <v>1</v>
+      </c>
+      <c r="L235" s="4" t="str">
+        <f t="shared" si="48"/>
+        <v>-</v>
+      </c>
+      <c r="M235" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="236" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B236" t="s">
+        <v>5</v>
+      </c>
+      <c r="C236" t="s">
+        <v>142</v>
+      </c>
+      <c r="E236" t="s">
+        <v>16</v>
+      </c>
+      <c r="H236" s="2">
+        <v>45349</v>
+      </c>
+      <c r="I236" s="4">
+        <f t="shared" ref="I236:I238" ca="1" si="49">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H236), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H236), 7), "-")</f>
+        <v>0</v>
+      </c>
+      <c r="J236" s="4">
+        <f t="shared" ref="J236:J238" ca="1" si="50">IF(_xlfn.DAYS(TODAY(),H236)&lt;10000, _xlfn.DAYS(TODAY(),H236), "-")</f>
+        <v>1</v>
+      </c>
+      <c r="L236" s="4" t="str">
+        <f t="shared" ref="L236:L238" si="51">IF(_xlfn.DAYS(K236,H236)&gt;0, _xlfn.DAYS(K236,H236), "-")</f>
+        <v>-</v>
+      </c>
+      <c r="M236" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="237" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B237" t="s">
+        <v>5</v>
+      </c>
+      <c r="C237" t="s">
+        <v>142</v>
+      </c>
+      <c r="E237" t="s">
+        <v>16</v>
+      </c>
+      <c r="H237" s="2">
+        <v>45349</v>
+      </c>
+      <c r="I237" s="4">
+        <f t="shared" ca="1" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="J237" s="4">
+        <f t="shared" ca="1" si="50"/>
+        <v>1</v>
+      </c>
+      <c r="L237" s="4" t="str">
+        <f t="shared" si="51"/>
+        <v>-</v>
+      </c>
+      <c r="M237" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="238" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B238" t="s">
+        <v>5</v>
+      </c>
+      <c r="C238" t="s">
+        <v>142</v>
+      </c>
+      <c r="E238" t="s">
+        <v>16</v>
+      </c>
+      <c r="H238" s="2">
+        <v>45349</v>
+      </c>
+      <c r="I238" s="4">
+        <f t="shared" ca="1" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="J238" s="4">
+        <f t="shared" ca="1" si="50"/>
+        <v>1</v>
+      </c>
+      <c r="L238" s="4" t="str">
+        <f t="shared" si="51"/>
+        <v>-</v>
+      </c>
+      <c r="M238" t="s">
+        <v>236</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B1:Q232" xr:uid="{47ECCD65-6802-4B2B-901A-AED4A431A765}">
+  <autoFilter ref="B1:Q234" xr:uid="{47ECCD65-6802-4B2B-901A-AED4A431A765}">
     <filterColumn colId="0">
       <filters>
         <filter val="SPF"/>
@@ -10840,7 +11183,7 @@
     </filterColumn>
     <filterColumn colId="1">
       <filters>
-        <filter val="Tmem119-CreERT2; Tsg101-flox"/>
+        <filter val="Tcrd-CreER; Tsg101-flox"/>
       </filters>
     </filterColumn>
     <filterColumn colId="13">
@@ -10848,24 +11191,32 @@
     </filterColumn>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="M1:M153 M155:M1048576">
-    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text=".X">
+  <conditionalFormatting sqref="M1:M153 M155:M233 M235:M1048576">
+    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text=".X">
       <formula>NOT(ISERROR(SEARCH(".X",M1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text=".B">
+    <cfRule type="containsText" dxfId="4" priority="6" operator="containsText" text=".B">
       <formula>NOT(ISERROR(SEARCH(".B",M1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M154">
-    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text=".X">
+    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text=".X">
       <formula>NOT(ISERROR(SEARCH(".X",M154)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text=".B">
+    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text=".B">
       <formula>NOT(ISERROR(SEARCH(".B",M154)))</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="M234">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text=".X">
+      <formula>NOT(ISERROR(SEARCH(".X",M234)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text=".B">
+      <formula>NOT(ISERROR(SEARCH(".B",M234)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E140 E142:E143 E145:E150 E152:E153 E155:E158 E160:E188 E190:E221 E223:E227 E229:E1048576" xr:uid="{939E2B39-E841-4A9F-AD11-00C266DB2690}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E140 E142:E143 E145:E150 E152:E153 E155:E158 E160:E188 E222:E226 E190:E220 E228:E1048576" xr:uid="{939E2B39-E841-4A9F-AD11-00C266DB2690}">
       <formula1>"Y, N"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1:G1048576" xr:uid="{2DE54AC7-5B92-48D6-98C4-E6203F87CDD0}">

--- a/Mouse 내역.xlsx
+++ b/Mouse 내역.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\heung\Dropbox\02. Lab. of Host Defenses\03. 동물실\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{957B8BDB-844D-4AB7-90FD-F6523A508F4B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80CF19A2-F297-49D9-8DC7-39429809C744}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="495" windowWidth="28800" windowHeight="16245" xr2:uid="{5A73A69A-2AFB-4F3E-AC64-070DD7700CB2}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1593" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1597" uniqueCount="239">
   <si>
     <t>Strain</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -962,6 +962,10 @@
   </si>
   <si>
     <t>weaning, genotyping (ear punch)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>새끼/임신 확인</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3265,7 +3269,9 @@
       <c r="M28" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="Q28" s="2"/>
+      <c r="Q28" s="2" t="s">
+        <v>238</v>
+      </c>
       <c r="R28" t="s">
         <v>219</v>
       </c>
@@ -3310,7 +3316,9 @@
       <c r="M29" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="Q29" s="2"/>
+      <c r="Q29" s="2" t="s">
+        <v>238</v>
+      </c>
       <c r="R29" t="s">
         <v>219</v>
       </c>
@@ -7518,6 +7526,9 @@
         <v>221</v>
       </c>
       <c r="O124"/>
+      <c r="Q124" s="2" t="s">
+        <v>238</v>
+      </c>
       <c r="R124" t="s">
         <v>222</v>
       </c>
@@ -7558,6 +7569,9 @@
       </c>
       <c r="M125" t="s">
         <v>221</v>
+      </c>
+      <c r="Q125" s="2" t="s">
+        <v>238</v>
       </c>
       <c r="R125" t="s">
         <v>220</v>

--- a/Mouse 내역.xlsx
+++ b/Mouse 내역.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\heung\Dropbox\02. Lab. of Host Defenses\03. 동물실\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80CF19A2-F297-49D9-8DC7-39429809C744}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77514458-ACAD-48ED-A595-95ACAAD60324}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="495" windowWidth="28800" windowHeight="16245" xr2:uid="{5A73A69A-2AFB-4F3E-AC64-070DD7700CB2}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <sheet name="Sheet1 (2)" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$R$238</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$R$230</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1597" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1567" uniqueCount="253">
   <si>
     <t>Strain</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -399,9 +399,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Weaned; or Provisino date</t>
-  </si>
-  <si>
     <t>Cre/+; f/+</t>
   </si>
   <si>
@@ -684,10 +681,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>H6.1.X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>SPF</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -890,10 +883,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>임신?</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>from A2.3.M</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -941,10 +930,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>weaning하기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Tmem119-CreERT2; Cd36-flox</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -953,19 +938,91 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>데려오고 Tam or corn oil 찌르기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>weaning, genotyping</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>weaning, genotyping (ear punch)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>새끼/임신 확인</t>
+    <t>죽이기 (새끼 있어서 못죽임)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>데려오고 Tam or corn oil 찌르기 (6, 7주도 가능)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>H6.1.F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>H6.1.M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A3.1.M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A3.1.F1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A3.1.F2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>L1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>L2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R1L1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R1L2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SPF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>N</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>H10.1.X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>H10.B cage가 없는데? 확인 필요. 여러마리 있으니 일주일 정도 후에 개체수 확인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>genotyping</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>weaning하기, 몇마리인지 세기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Weaned; or Provision date</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>+/+; +/+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cre/+; +/+</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -973,9 +1030,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
-  </numFmts>
   <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1154,7 +1208,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1201,9 +1255,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="4" applyFont="1">
@@ -2068,7 +2119,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D71A6DC-E91C-489F-8F50-989C4712FA7C}">
   <sheetPr filterMode="1"/>
-  <dimension ref="B1:R238"/>
+  <dimension ref="B1:R230"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="10.5" customWidth="1"/>
@@ -2084,7 +2135,7 @@
     <col min="14" max="14" width="13.125" style="2" customWidth="1"/>
     <col min="15" max="15" width="12.625" style="2" customWidth="1"/>
     <col min="16" max="16" width="13.125" customWidth="1"/>
-    <col min="17" max="17" width="23.125" customWidth="1"/>
+    <col min="17" max="17" width="25.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:18" x14ac:dyDescent="0.3">
@@ -2116,7 +2167,7 @@
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>93</v>
+        <v>250</v>
       </c>
       <c r="L1" s="8" t="s">
         <v>14</v>
@@ -2134,10 +2185,10 @@
         <v>60</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="R1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="2" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -2145,13 +2196,13 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G2" t="s">
         <v>11</v>
@@ -2165,7 +2216,7 @@
       </c>
       <c r="J2" s="4">
         <f ca="1">IF(_xlfn.DAYS(TODAY(),H2)&lt;10000, _xlfn.DAYS(TODAY(),H2), "-")</f>
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L2" s="4" t="str">
         <f t="shared" ref="L2:L29" si="0">IF(_xlfn.DAYS(K2,H2)&gt;0, _xlfn.DAYS(K2,H2), "-")</f>
@@ -2184,13 +2235,13 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G3" t="s">
         <v>13</v>
@@ -2204,7 +2255,7 @@
       </c>
       <c r="J3" s="4">
         <f t="shared" ref="J3:J29" ca="1" si="2">IF(_xlfn.DAYS(TODAY(),H3)&lt;10000, _xlfn.DAYS(TODAY(),H3), "-")</f>
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L3" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2218,7 +2269,7 @@
         <v>45351</v>
       </c>
       <c r="Q3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="4" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -2226,13 +2277,13 @@
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G4" t="s">
         <v>13</v>
@@ -2246,7 +2297,7 @@
       </c>
       <c r="J4" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L4" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2260,7 +2311,7 @@
         <v>45351</v>
       </c>
       <c r="Q4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="5" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -2268,7 +2319,7 @@
         <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D5">
         <v>871</v>
@@ -2291,7 +2342,7 @@
       </c>
       <c r="J5" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K5" s="2">
         <v>45293</v>
@@ -2313,7 +2364,7 @@
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D6">
         <v>688</v>
@@ -2336,7 +2387,7 @@
       </c>
       <c r="J6" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K6" s="2">
         <v>45293</v>
@@ -2353,7 +2404,7 @@
         <v>45315</v>
       </c>
       <c r="Q6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.3">
@@ -2361,7 +2412,7 @@
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D7">
         <v>921</v>
@@ -2384,7 +2435,7 @@
       </c>
       <c r="J7" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K7" s="2">
         <v>45293</v>
@@ -2404,7 +2455,7 @@
         <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D8">
         <v>922</v>
@@ -2427,7 +2478,7 @@
       </c>
       <c r="J8" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K8" s="2">
         <v>45293</v>
@@ -2449,7 +2500,7 @@
         <v>5</v>
       </c>
       <c r="C9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D9">
         <v>923</v>
@@ -2472,7 +2523,7 @@
       </c>
       <c r="J9" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K9" s="2">
         <v>45293</v>
@@ -2494,13 +2545,13 @@
         <v>5</v>
       </c>
       <c r="C10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E10" t="s">
         <v>7</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G10" t="s">
         <v>10</v>
@@ -2514,7 +2565,7 @@
       </c>
       <c r="J10" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L10" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2533,13 +2584,13 @@
         <v>5</v>
       </c>
       <c r="C11" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E11" t="s">
         <v>7</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G11" t="s">
         <v>12</v>
@@ -2569,13 +2620,13 @@
         <v>5</v>
       </c>
       <c r="C12" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E12" t="s">
         <v>7</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G12" t="s">
         <v>12</v>
@@ -2605,7 +2656,7 @@
         <v>5</v>
       </c>
       <c r="C13" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D13">
         <v>972</v>
@@ -2614,7 +2665,7 @@
         <v>7</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G13" t="s">
         <v>11</v>
@@ -2628,7 +2679,7 @@
       </c>
       <c r="J13" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L13" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2642,7 +2693,7 @@
         <v>45349</v>
       </c>
       <c r="Q13" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="14" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -2650,7 +2701,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D14">
         <v>973</v>
@@ -2659,7 +2710,7 @@
         <v>7</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G14" t="s">
         <v>11</v>
@@ -2673,7 +2724,7 @@
       </c>
       <c r="J14" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L14" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2687,7 +2738,7 @@
         <v>45349</v>
       </c>
       <c r="Q14" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="15" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -2695,7 +2746,7 @@
         <v>5</v>
       </c>
       <c r="C15" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D15">
         <v>974</v>
@@ -2704,7 +2755,7 @@
         <v>7</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G15" t="s">
         <v>11</v>
@@ -2718,7 +2769,7 @@
       </c>
       <c r="J15" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L15" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2731,7 +2782,7 @@
         <v>45349</v>
       </c>
       <c r="Q15" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="16" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -2739,7 +2790,7 @@
         <v>5</v>
       </c>
       <c r="C16" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D16">
         <v>975</v>
@@ -2748,7 +2799,7 @@
         <v>7</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G16" t="s">
         <v>11</v>
@@ -2762,25 +2813,25 @@
       </c>
       <c r="J16" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L16" s="4" t="str">
         <f t="shared" si="0"/>
         <v>-</v>
       </c>
       <c r="M16" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O16" s="2">
         <v>45327</v>
       </c>
     </row>
-    <row r="17" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>5</v>
       </c>
       <c r="C17" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D17">
         <v>970</v>
@@ -2789,7 +2840,7 @@
         <v>7</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G17" t="s">
         <v>11</v>
@@ -2803,7 +2854,7 @@
       </c>
       <c r="J17" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L17" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2816,21 +2867,21 @@
         <v>45349</v>
       </c>
       <c r="Q17" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="18" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="18" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>5</v>
       </c>
       <c r="C18" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E18" t="s">
         <v>7</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G18" t="s">
         <v>11</v>
@@ -2844,7 +2895,7 @@
       </c>
       <c r="J18" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L18" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2857,18 +2908,18 @@
         <v>45299</v>
       </c>
     </row>
-    <row r="19" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>5</v>
       </c>
       <c r="C19" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E19" t="s">
         <v>7</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G19" t="s">
         <v>13</v>
@@ -2892,18 +2943,18 @@
         <v>45299</v>
       </c>
     </row>
-    <row r="20" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>5</v>
       </c>
       <c r="C20" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G20" t="s">
         <v>13</v>
@@ -2917,7 +2968,7 @@
       </c>
       <c r="J20" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K20" s="2">
         <v>45112</v>
@@ -2933,12 +2984,12 @@
         <v>45299</v>
       </c>
     </row>
-    <row r="21" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>5</v>
       </c>
       <c r="C21" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E21" t="s">
         <v>7</v>
@@ -2958,7 +3009,7 @@
       </c>
       <c r="J21" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K21" s="2">
         <v>45176</v>
@@ -2974,15 +3025,15 @@
         <v>45306</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="22" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="22" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>5</v>
       </c>
       <c r="C22" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E22" t="s">
         <v>7</v>
@@ -3002,7 +3053,7 @@
       </c>
       <c r="J22" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K22" s="2">
         <v>45176</v>
@@ -3018,15 +3069,15 @@
         <v>45306</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="23" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="23" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>5</v>
       </c>
       <c r="C23" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E23" t="s">
         <v>7</v>
@@ -3046,7 +3097,7 @@
       </c>
       <c r="J23" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K23" s="2">
         <v>45176</v>
@@ -3062,21 +3113,21 @@
         <v>45306</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="24" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="24" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>5</v>
       </c>
       <c r="C24" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G24" t="s">
         <v>11</v>
@@ -3090,7 +3141,7 @@
       </c>
       <c r="J24" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K24" s="2">
         <v>45229</v>
@@ -3106,18 +3157,18 @@
         <v>45310</v>
       </c>
     </row>
-    <row r="25" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>5</v>
       </c>
       <c r="C25" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G25" t="s">
         <v>11</v>
@@ -3131,7 +3182,7 @@
       </c>
       <c r="J25" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K25" s="2">
         <v>45229</v>
@@ -3147,12 +3198,12 @@
         <v>45310</v>
       </c>
     </row>
-    <row r="26" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>5</v>
       </c>
       <c r="C26" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -3172,7 +3223,7 @@
       </c>
       <c r="J26" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K26" s="2">
         <v>45229</v>
@@ -3182,18 +3233,18 @@
         <v>26</v>
       </c>
       <c r="M26" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="Q26" s="2" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="27" spans="2:18" x14ac:dyDescent="0.3">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="27" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>5</v>
       </c>
       <c r="C27" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
@@ -3213,7 +3264,7 @@
       </c>
       <c r="J27" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K27" s="2">
         <v>45229</v>
@@ -3223,18 +3274,18 @@
         <v>26</v>
       </c>
       <c r="M27" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="Q27" s="2" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="28" spans="2:18" x14ac:dyDescent="0.3">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="28" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>5</v>
       </c>
       <c r="C28" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D28">
         <v>687</v>
@@ -3257,7 +3308,7 @@
       </c>
       <c r="J28" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K28" s="2">
         <v>45293</v>
@@ -3267,21 +3318,16 @@
         <v>27</v>
       </c>
       <c r="M28" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="Q28" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="R28" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="29" spans="2:18" x14ac:dyDescent="0.3">
+        <v>164</v>
+      </c>
+      <c r="Q28" s="2"/>
+    </row>
+    <row r="29" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
         <v>5</v>
       </c>
       <c r="C29" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D29">
         <v>646</v>
@@ -3304,7 +3350,7 @@
       </c>
       <c r="J29" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K29" s="2">
         <v>45315</v>
@@ -3314,21 +3360,16 @@
         <v>24</v>
       </c>
       <c r="M29" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="Q29" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="R29" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="30" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+        <v>164</v>
+      </c>
+      <c r="Q29" s="2"/>
+    </row>
+    <row r="30" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>5</v>
       </c>
       <c r="C30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E30" t="s">
         <v>7</v>
@@ -3348,7 +3389,7 @@
       </c>
       <c r="J30" s="4">
         <f t="shared" ref="J30" ca="1" si="4">IF(_xlfn.DAYS(TODAY(),H30)&lt;10000, _xlfn.DAYS(TODAY(),H30), "-")</f>
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K30" s="2">
         <v>45176</v>
@@ -3358,27 +3399,27 @@
         <v>22</v>
       </c>
       <c r="M30" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="O30" s="2">
         <v>45351</v>
       </c>
       <c r="Q30" s="2" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="31" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="31" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
         <v>5</v>
       </c>
       <c r="C31" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
       </c>
       <c r="F31" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G31" t="s">
         <v>13</v>
@@ -3392,7 +3433,7 @@
       </c>
       <c r="J31" s="4">
         <f t="shared" ref="J31:J37" ca="1" si="6">IF(_xlfn.DAYS(TODAY(),H31)&lt;10000, _xlfn.DAYS(TODAY(),H31), "-")</f>
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K31" s="2">
         <v>45229</v>
@@ -3402,27 +3443,27 @@
         <v>26</v>
       </c>
       <c r="M31" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="O31" s="2">
         <v>45351</v>
       </c>
       <c r="Q31" s="2" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="32" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="32" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
         <v>5</v>
       </c>
       <c r="C32" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G32" t="s">
         <v>11</v>
@@ -3451,7 +3492,7 @@
         <v>5</v>
       </c>
       <c r="C33" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D33" t="s">
         <v>24</v>
@@ -3474,7 +3515,7 @@
       </c>
       <c r="J33" s="4">
         <f ca="1">IF(_xlfn.DAYS(TODAY(),H33)&lt;10000, _xlfn.DAYS(TODAY(),H33), "-")</f>
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K33" s="2">
         <v>45257</v>
@@ -3490,7 +3531,7 @@
         <v>45306</v>
       </c>
       <c r="Q33" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="34" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -3498,13 +3539,13 @@
         <v>5</v>
       </c>
       <c r="C34" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G34" t="s">
         <v>13</v>
@@ -3528,7 +3569,7 @@
         <v>45306</v>
       </c>
       <c r="Q34" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="35" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -3536,13 +3577,13 @@
         <v>5</v>
       </c>
       <c r="C35" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G35" t="s">
         <v>13</v>
@@ -3566,7 +3607,7 @@
         <v>45306</v>
       </c>
       <c r="Q35" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="36" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -3574,7 +3615,7 @@
         <v>5</v>
       </c>
       <c r="C36" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D36" t="s">
         <v>23</v>
@@ -3597,7 +3638,7 @@
       </c>
       <c r="J36" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K36" s="2">
         <v>45257</v>
@@ -3613,7 +3654,7 @@
         <v>45306</v>
       </c>
       <c r="Q36" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="37" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -3621,7 +3662,7 @@
         <v>5</v>
       </c>
       <c r="C37" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D37" t="s">
         <v>24</v>
@@ -3644,7 +3685,7 @@
       </c>
       <c r="J37" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K37" s="2">
         <v>45257</v>
@@ -3660,7 +3701,7 @@
         <v>45306</v>
       </c>
       <c r="Q37" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="38" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -3668,7 +3709,7 @@
         <v>5</v>
       </c>
       <c r="C38" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D38" t="s">
         <v>25</v>
@@ -3691,7 +3732,7 @@
       </c>
       <c r="J38" s="4">
         <f t="shared" ref="J38:J40" ca="1" si="8">IF(_xlfn.DAYS(TODAY(),H38)&lt;10000, _xlfn.DAYS(TODAY(),H38), "-")</f>
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K38" s="2">
         <v>45257</v>
@@ -3707,7 +3748,7 @@
         <v>45306</v>
       </c>
       <c r="Q38" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="39" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -3715,7 +3756,7 @@
         <v>5</v>
       </c>
       <c r="C39" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D39" t="s">
         <v>23</v>
@@ -3724,7 +3765,7 @@
         <v>8</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G39" t="s">
         <v>11</v>
@@ -3738,7 +3779,7 @@
       </c>
       <c r="J39" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K39" s="2">
         <v>45257</v>
@@ -3759,7 +3800,7 @@
         <v>5</v>
       </c>
       <c r="C40" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D40" t="s">
         <v>25</v>
@@ -3782,7 +3823,7 @@
       </c>
       <c r="J40" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K40" s="2">
         <v>45257</v>
@@ -3803,7 +3844,7 @@
         <v>5</v>
       </c>
       <c r="C41" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D41">
         <v>798</v>
@@ -3812,7 +3853,7 @@
         <v>8</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G41" t="s">
         <v>13</v>
@@ -3826,7 +3867,7 @@
       </c>
       <c r="J41" s="4">
         <f t="shared" ref="J41:J42" ca="1" si="9">IF(_xlfn.DAYS(TODAY(),H41)&lt;10000, _xlfn.DAYS(TODAY(),H41), "-")</f>
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L41" s="4" t="str">
         <f t="shared" si="7"/>
@@ -3839,12 +3880,12 @@
         <v>45309</v>
       </c>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B42" t="s">
         <v>5</v>
       </c>
       <c r="C42" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E42" t="s">
         <v>7</v>
@@ -3864,7 +3905,7 @@
       </c>
       <c r="J42" s="4">
         <f t="shared" ca="1" si="9"/>
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K42" s="2">
         <v>45176</v>
@@ -3874,19 +3915,21 @@
         <v>22</v>
       </c>
       <c r="M42" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="O42" s="7"/>
+        <v>165</v>
+      </c>
+      <c r="O42" s="7">
+        <v>45355</v>
+      </c>
       <c r="Q42" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.3">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B43" t="s">
         <v>5</v>
       </c>
       <c r="C43" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D43">
         <v>799</v>
@@ -3895,7 +3938,7 @@
         <v>8</v>
       </c>
       <c r="F43" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G43" t="s">
         <v>13</v>
@@ -3909,17 +3952,20 @@
       </c>
       <c r="J43" s="4">
         <f t="shared" ref="J43:J91" ca="1" si="11">IF(_xlfn.DAYS(TODAY(),H43)&lt;10000, _xlfn.DAYS(TODAY(),H43), "-")</f>
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L43" s="4" t="str">
         <f t="shared" si="7"/>
         <v>-</v>
       </c>
       <c r="M43" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
+      </c>
+      <c r="O43" s="2">
+        <v>45355</v>
       </c>
       <c r="Q43" s="2" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
     </row>
     <row r="44" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -3927,7 +3973,7 @@
         <v>5</v>
       </c>
       <c r="C44" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D44">
         <v>815</v>
@@ -3950,7 +3996,7 @@
       </c>
       <c r="J44" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K44" s="2">
         <v>45293</v>
@@ -3971,7 +4017,7 @@
         <v>5</v>
       </c>
       <c r="C45" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D45">
         <v>816</v>
@@ -3994,7 +4040,7 @@
       </c>
       <c r="J45" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K45" s="2">
         <v>45293</v>
@@ -4015,7 +4061,7 @@
         <v>5</v>
       </c>
       <c r="C46" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D46">
         <v>817</v>
@@ -4038,7 +4084,7 @@
       </c>
       <c r="J46" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K46" s="2">
         <v>45293</v>
@@ -4054,7 +4100,7 @@
         <v>45306</v>
       </c>
       <c r="Q46" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="47" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -4062,7 +4108,7 @@
         <v>5</v>
       </c>
       <c r="C47" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D47">
         <v>819</v>
@@ -4085,7 +4131,7 @@
       </c>
       <c r="J47" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K47" s="2">
         <v>45293</v>
@@ -4101,7 +4147,7 @@
         <v>45306</v>
       </c>
       <c r="Q47" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="48" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -4109,7 +4155,7 @@
         <v>5</v>
       </c>
       <c r="C48" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D48">
         <v>820</v>
@@ -4132,7 +4178,7 @@
       </c>
       <c r="J48" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K48" s="2">
         <v>45293</v>
@@ -4148,7 +4194,7 @@
         <v>45306</v>
       </c>
       <c r="Q48" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="49" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -4156,7 +4202,7 @@
         <v>5</v>
       </c>
       <c r="C49" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D49">
         <v>821</v>
@@ -4165,7 +4211,7 @@
         <v>8</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G49" t="s">
         <v>72</v>
@@ -4179,7 +4225,7 @@
       </c>
       <c r="J49" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K49" s="2">
         <v>45293</v>
@@ -4195,7 +4241,7 @@
         <v>45351</v>
       </c>
       <c r="Q49" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="50" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -4203,7 +4249,7 @@
         <v>5</v>
       </c>
       <c r="C50" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D50">
         <v>822</v>
@@ -4212,7 +4258,7 @@
         <v>8</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G50" t="s">
         <v>72</v>
@@ -4226,7 +4272,7 @@
       </c>
       <c r="J50" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K50" s="2">
         <v>45293</v>
@@ -4242,7 +4288,7 @@
         <v>45351</v>
       </c>
       <c r="Q50" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="51" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -4250,7 +4296,7 @@
         <v>5</v>
       </c>
       <c r="C51" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D51">
         <v>823</v>
@@ -4273,7 +4319,7 @@
       </c>
       <c r="J51" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K51" s="2">
         <v>45293</v>
@@ -4294,7 +4340,7 @@
         <v>5</v>
       </c>
       <c r="C52" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D52">
         <v>824</v>
@@ -4317,7 +4363,7 @@
       </c>
       <c r="J52" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K52" s="2">
         <v>45293</v>
@@ -4338,7 +4384,7 @@
         <v>5</v>
       </c>
       <c r="C53" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D53">
         <v>825</v>
@@ -4347,7 +4393,7 @@
         <v>8</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G53" t="s">
         <v>72</v>
@@ -4361,7 +4407,7 @@
       </c>
       <c r="J53" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K53" s="2">
         <v>45293</v>
@@ -4377,7 +4423,7 @@
         <v>45351</v>
       </c>
       <c r="Q53" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="54" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -4385,7 +4431,7 @@
         <v>27</v>
       </c>
       <c r="C54" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D54" t="s">
         <v>28</v>
@@ -4394,7 +4440,7 @@
         <v>31</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G54" t="s">
         <v>32</v>
@@ -4408,7 +4454,7 @@
       </c>
       <c r="J54" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K54" s="2">
         <v>45238</v>
@@ -4423,8 +4469,8 @@
       <c r="O54" s="2">
         <v>45351</v>
       </c>
-      <c r="Q54" s="17" t="s">
-        <v>179</v>
+      <c r="Q54" s="16" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="55" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -4432,7 +4478,7 @@
         <v>27</v>
       </c>
       <c r="C55" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D55" t="s">
         <v>30</v>
@@ -4441,7 +4487,7 @@
         <v>31</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G55" t="s">
         <v>32</v>
@@ -4455,7 +4501,7 @@
       </c>
       <c r="J55" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K55" s="2">
         <v>45238</v>
@@ -4468,7 +4514,7 @@
         <v>40</v>
       </c>
       <c r="Q55" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
     </row>
     <row r="56" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -4476,7 +4522,7 @@
         <v>27</v>
       </c>
       <c r="C56" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D56" t="s">
         <v>29</v>
@@ -4485,7 +4531,7 @@
         <v>31</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G56" t="s">
         <v>32</v>
@@ -4499,7 +4545,7 @@
       </c>
       <c r="J56" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K56" s="2">
         <v>45238</v>
@@ -4512,7 +4558,7 @@
         <v>40</v>
       </c>
       <c r="Q56" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
     </row>
     <row r="57" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -4520,13 +4566,13 @@
         <v>27</v>
       </c>
       <c r="C57" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E57" t="s">
         <v>31</v>
       </c>
       <c r="F57" s="14" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G57" t="s">
         <v>33</v>
@@ -4540,7 +4586,7 @@
       </c>
       <c r="J57" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L57" s="4" t="str">
         <f t="shared" si="7"/>
@@ -4550,7 +4596,7 @@
         <v>41</v>
       </c>
       <c r="Q57" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
     </row>
     <row r="58" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -4558,13 +4604,13 @@
         <v>27</v>
       </c>
       <c r="C58" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E58" t="s">
         <v>31</v>
       </c>
       <c r="F58" s="14" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G58" t="s">
         <v>32</v>
@@ -4578,7 +4624,7 @@
       </c>
       <c r="J58" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L58" s="4" t="str">
         <f t="shared" si="7"/>
@@ -4588,7 +4634,7 @@
         <v>41</v>
       </c>
       <c r="Q58" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
     </row>
     <row r="59" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -4596,7 +4642,7 @@
         <v>27</v>
       </c>
       <c r="C59" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E59" t="s">
         <v>26</v>
@@ -4613,7 +4659,7 @@
       </c>
       <c r="J59" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K59" s="2">
         <v>45295</v>
@@ -4631,7 +4677,7 @@
         <v>27</v>
       </c>
       <c r="C60" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E60" t="s">
         <v>26</v>
@@ -4648,7 +4694,7 @@
       </c>
       <c r="J60" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K60" s="2">
         <v>45295</v>
@@ -4661,7 +4707,7 @@
         <v>90</v>
       </c>
       <c r="Q60" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="61" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -4669,7 +4715,7 @@
         <v>27</v>
       </c>
       <c r="C61" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E61" t="s">
         <v>26</v>
@@ -4686,7 +4732,7 @@
       </c>
       <c r="J61" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K61" s="2">
         <v>45295</v>
@@ -4699,7 +4745,7 @@
         <v>90</v>
       </c>
       <c r="Q61" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="62" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -4707,7 +4753,7 @@
         <v>27</v>
       </c>
       <c r="C62" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E62" t="s">
         <v>26</v>
@@ -4724,7 +4770,7 @@
       </c>
       <c r="J62" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K62" s="2">
         <v>45295</v>
@@ -4737,7 +4783,7 @@
         <v>90</v>
       </c>
       <c r="Q62" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
     </row>
     <row r="63" spans="2:17" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
@@ -4745,7 +4791,7 @@
         <v>27</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E63" s="4" t="s">
         <v>26</v>
@@ -4763,7 +4809,7 @@
       </c>
       <c r="J63" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K63" s="7">
         <v>45295</v>
@@ -4780,7 +4826,7 @@
         <v>45345</v>
       </c>
       <c r="Q63" s="4" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="64" spans="2:17" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
@@ -4788,7 +4834,7 @@
         <v>27</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E64" s="4" t="s">
         <v>26</v>
@@ -4806,7 +4852,7 @@
       </c>
       <c r="J64" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K64" s="7">
         <v>45295</v>
@@ -4823,7 +4869,7 @@
         <v>45345</v>
       </c>
       <c r="Q64" s="4" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="65" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -4831,13 +4877,13 @@
         <v>27</v>
       </c>
       <c r="C65" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E65" t="s">
         <v>31</v>
       </c>
       <c r="F65" s="14" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G65" t="s">
         <v>32</v>
@@ -4851,7 +4897,7 @@
       </c>
       <c r="J65" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L65" s="4" t="str">
         <f t="shared" si="7"/>
@@ -4861,7 +4907,7 @@
         <v>42</v>
       </c>
       <c r="Q65" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
     </row>
     <row r="66" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -4869,13 +4915,13 @@
         <v>27</v>
       </c>
       <c r="C66" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E66" t="s">
         <v>31</v>
       </c>
       <c r="F66" s="14" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G66" t="s">
         <v>32</v>
@@ -4889,7 +4935,7 @@
       </c>
       <c r="J66" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L66" s="4" t="str">
         <f t="shared" si="7"/>
@@ -4899,7 +4945,7 @@
         <v>42</v>
       </c>
       <c r="Q66" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
     </row>
     <row r="67" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -4930,7 +4976,7 @@
       </c>
       <c r="J67" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L67" s="4" t="str">
         <f t="shared" si="7"/>
@@ -4977,7 +5023,7 @@
       </c>
       <c r="J68" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L68" s="4" t="str">
         <f t="shared" si="7"/>
@@ -5024,7 +5070,7 @@
       </c>
       <c r="J69" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L69" s="4" t="str">
         <f t="shared" si="7"/>
@@ -5071,7 +5117,7 @@
       </c>
       <c r="J70" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L70" s="4" t="str">
         <f t="shared" si="7"/>
@@ -5118,7 +5164,7 @@
       </c>
       <c r="J71" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L71" s="4" t="str">
         <f t="shared" si="7"/>
@@ -5165,7 +5211,7 @@
       </c>
       <c r="J72" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L72" s="4" t="str">
         <f t="shared" si="7"/>
@@ -5212,7 +5258,7 @@
       </c>
       <c r="J73" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L73" s="4" t="str">
         <f t="shared" si="7"/>
@@ -5259,7 +5305,7 @@
       </c>
       <c r="J74" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L74" s="4" t="str">
         <f t="shared" si="7"/>
@@ -5306,7 +5352,7 @@
       </c>
       <c r="J75" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L75" s="4" t="str">
         <f t="shared" si="7"/>
@@ -5353,7 +5399,7 @@
       </c>
       <c r="J76" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L76" s="4" t="str">
         <f t="shared" si="7"/>
@@ -5400,7 +5446,7 @@
       </c>
       <c r="J77" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L77" s="4" t="str">
         <f t="shared" si="7"/>
@@ -5447,7 +5493,7 @@
       </c>
       <c r="J78" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L78" s="4" t="str">
         <f t="shared" si="7"/>
@@ -5494,7 +5540,7 @@
       </c>
       <c r="J79" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L79" s="4" t="str">
         <f t="shared" si="7"/>
@@ -5541,7 +5587,7 @@
       </c>
       <c r="J80" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L80" s="4" t="str">
         <f t="shared" si="7"/>
@@ -5588,7 +5634,7 @@
       </c>
       <c r="J81" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L81" s="4" t="str">
         <f t="shared" si="7"/>
@@ -5635,7 +5681,7 @@
       </c>
       <c r="J82" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L82" s="4" t="str">
         <f t="shared" si="7"/>
@@ -5682,7 +5728,7 @@
       </c>
       <c r="J83" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L83" s="4" t="str">
         <f t="shared" si="7"/>
@@ -5729,7 +5775,7 @@
       </c>
       <c r="J84" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L84" s="4" t="str">
         <f t="shared" si="7"/>
@@ -5776,7 +5822,7 @@
       </c>
       <c r="J85" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L85" s="4" t="str">
         <f t="shared" si="7"/>
@@ -5823,7 +5869,7 @@
       </c>
       <c r="J86" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L86" s="4" t="str">
         <f t="shared" si="7"/>
@@ -5847,7 +5893,7 @@
         <v>27</v>
       </c>
       <c r="C87" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D87" t="s">
         <v>28</v>
@@ -5856,7 +5902,7 @@
         <v>31</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G87" t="s">
         <v>33</v>
@@ -5870,7 +5916,7 @@
       </c>
       <c r="J87" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K87" s="2">
         <v>45272</v>
@@ -5880,13 +5926,13 @@
         <v>34</v>
       </c>
       <c r="M87" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O87" s="2">
         <v>45323</v>
       </c>
       <c r="Q87" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="88" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -5894,7 +5940,7 @@
         <v>34</v>
       </c>
       <c r="C88" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D88" t="s">
         <v>30</v>
@@ -5903,7 +5949,7 @@
         <v>31</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G88" t="s">
         <v>33</v>
@@ -5917,7 +5963,7 @@
       </c>
       <c r="J88" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K88" s="2">
         <v>45273</v>
@@ -5927,13 +5973,13 @@
         <v>35</v>
       </c>
       <c r="M88" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O88" s="2">
         <v>45323</v>
       </c>
       <c r="Q88" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="89" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -5941,7 +5987,7 @@
         <v>34</v>
       </c>
       <c r="C89" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D89" t="s">
         <v>29</v>
@@ -5950,7 +5996,7 @@
         <v>31</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G89" t="s">
         <v>33</v>
@@ -5964,7 +6010,7 @@
       </c>
       <c r="J89" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K89" s="2">
         <v>45274</v>
@@ -5974,13 +6020,13 @@
         <v>36</v>
       </c>
       <c r="M89" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O89" s="2">
         <v>45323</v>
       </c>
       <c r="Q89" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="90" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -5988,7 +6034,7 @@
         <v>27</v>
       </c>
       <c r="C90" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D90" t="s">
         <v>28</v>
@@ -5997,7 +6043,7 @@
         <v>31</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G90" t="s">
         <v>32</v>
@@ -6011,7 +6057,7 @@
       </c>
       <c r="J90" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K90" s="2">
         <v>45275</v>
@@ -6021,13 +6067,13 @@
         <v>37</v>
       </c>
       <c r="M90" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O90" s="2">
         <v>45323</v>
       </c>
       <c r="Q90" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="91" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -6035,7 +6081,7 @@
         <v>27</v>
       </c>
       <c r="C91" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D91" t="s">
         <v>30</v>
@@ -6044,7 +6090,7 @@
         <v>31</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G91" t="s">
         <v>32</v>
@@ -6058,7 +6104,7 @@
       </c>
       <c r="J91" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K91" s="2">
         <v>45276</v>
@@ -6068,13 +6114,13 @@
         <v>38</v>
       </c>
       <c r="M91" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O91" s="2">
         <v>45323</v>
       </c>
       <c r="Q91" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="92" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -6082,7 +6128,7 @@
         <v>27</v>
       </c>
       <c r="C92" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D92" t="s">
         <v>29</v>
@@ -6091,7 +6137,7 @@
         <v>31</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G92" t="s">
         <v>32</v>
@@ -6105,7 +6151,7 @@
       </c>
       <c r="J92" s="4">
         <f t="shared" ref="J92:J93" ca="1" si="14">IF(_xlfn.DAYS(TODAY(),H92)&lt;10000, _xlfn.DAYS(TODAY(),H92), "-")</f>
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K92" s="2">
         <v>45277</v>
@@ -6115,13 +6161,13 @@
         <v>39</v>
       </c>
       <c r="M92" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O92" s="2">
         <v>45323</v>
       </c>
       <c r="Q92" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="93" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -6129,7 +6175,7 @@
         <v>34</v>
       </c>
       <c r="C93" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D93" t="s">
         <v>35</v>
@@ -6138,7 +6184,7 @@
         <v>31</v>
       </c>
       <c r="F93" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G93" t="s">
         <v>32</v>
@@ -6152,7 +6198,7 @@
       </c>
       <c r="J93" s="4">
         <f t="shared" ca="1" si="14"/>
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K93" s="2">
         <v>45278</v>
@@ -6162,13 +6208,13 @@
         <v>40</v>
       </c>
       <c r="M93" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O93" s="2">
         <v>45323</v>
       </c>
       <c r="Q93" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="94" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -6176,7 +6222,7 @@
         <v>34</v>
       </c>
       <c r="C94" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D94">
         <v>615</v>
@@ -6185,7 +6231,7 @@
         <v>31</v>
       </c>
       <c r="F94" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G94" t="s">
         <v>33</v>
@@ -6195,11 +6241,11 @@
       </c>
       <c r="I94" s="4">
         <f t="shared" ref="I94" ca="1" si="15">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H94), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H94), 7), "-")</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J94" s="4">
         <f t="shared" ref="J94" ca="1" si="16">IF(_xlfn.DAYS(TODAY(),H94)&lt;10000, _xlfn.DAYS(TODAY(),H94), "-")</f>
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K94" s="2">
         <v>45223</v>
@@ -6215,7 +6261,7 @@
         <v>45301</v>
       </c>
       <c r="Q94" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="95" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -6223,7 +6269,7 @@
         <v>34</v>
       </c>
       <c r="C95" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D95">
         <v>616</v>
@@ -6232,7 +6278,7 @@
         <v>31</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G95" t="s">
         <v>33</v>
@@ -6242,11 +6288,11 @@
       </c>
       <c r="I95" s="4">
         <f t="shared" ref="I95:I117" ca="1" si="17">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H95), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H95), 7), "-")</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J95" s="4">
         <f t="shared" ref="J95:J117" ca="1" si="18">IF(_xlfn.DAYS(TODAY(),H95)&lt;10000, _xlfn.DAYS(TODAY(),H95), "-")</f>
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K95" s="2">
         <v>45223</v>
@@ -6262,7 +6308,7 @@
         <v>45301</v>
       </c>
       <c r="Q95" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="96" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -6270,7 +6316,7 @@
         <v>34</v>
       </c>
       <c r="C96" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D96">
         <v>617</v>
@@ -6279,7 +6325,7 @@
         <v>31</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G96" t="s">
         <v>33</v>
@@ -6289,11 +6335,11 @@
       </c>
       <c r="I96" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J96" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K96" s="2">
         <v>45223</v>
@@ -6309,7 +6355,7 @@
         <v>45301</v>
       </c>
       <c r="Q96" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="97" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -6317,7 +6363,7 @@
         <v>34</v>
       </c>
       <c r="C97" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D97">
         <v>618</v>
@@ -6326,7 +6372,7 @@
         <v>31</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G97" t="s">
         <v>33</v>
@@ -6336,11 +6382,11 @@
       </c>
       <c r="I97" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J97" s="4">
         <f t="shared" ca="1" si="18"/>
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K97" s="2">
         <v>45223</v>
@@ -6356,7 +6402,7 @@
         <v>45301</v>
       </c>
       <c r="Q97" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="98" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -6387,7 +6433,7 @@
       </c>
       <c r="J98" s="4">
         <f t="shared" ref="J98:J107" ca="1" si="21">IF(_xlfn.DAYS(TODAY(),H98)&lt;10000, _xlfn.DAYS(TODAY(),H98), "-")</f>
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K98" s="2">
         <v>45267</v>
@@ -6437,7 +6483,7 @@
       </c>
       <c r="J99" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K99" s="2">
         <v>45267</v>
@@ -6487,7 +6533,7 @@
       </c>
       <c r="J100" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K100" s="2">
         <v>45267</v>
@@ -6537,7 +6583,7 @@
       </c>
       <c r="J101" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K101" s="2">
         <v>45267</v>
@@ -6587,7 +6633,7 @@
       </c>
       <c r="J102" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K102" s="2">
         <v>45267</v>
@@ -6637,7 +6683,7 @@
       </c>
       <c r="J103" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K103" s="2">
         <v>45267</v>
@@ -6687,7 +6733,7 @@
       </c>
       <c r="J104" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K104" s="2">
         <v>45267</v>
@@ -6737,7 +6783,7 @@
       </c>
       <c r="J105" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K105" s="2">
         <v>45267</v>
@@ -6787,7 +6833,7 @@
       </c>
       <c r="J106" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K106" s="2">
         <v>45267</v>
@@ -6837,7 +6883,7 @@
       </c>
       <c r="J107" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K107" s="2">
         <v>45267</v>
@@ -7142,7 +7188,7 @@
         <v>56</v>
       </c>
       <c r="G115" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I115" s="4" t="str">
         <f t="shared" ca="1" si="17"/>
@@ -7323,7 +7369,7 @@
         <v>80</v>
       </c>
       <c r="C120" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D120">
         <v>645</v>
@@ -7332,10 +7378,10 @@
         <v>81</v>
       </c>
       <c r="F120" s="14" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G120" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H120" s="2">
         <v>45291</v>
@@ -7346,7 +7392,7 @@
       </c>
       <c r="J120" s="4">
         <f t="shared" ca="1" si="23"/>
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K120" s="2">
         <v>45315</v>
@@ -7356,7 +7402,7 @@
         <v>24</v>
       </c>
       <c r="M120" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O120" s="2">
         <v>45351</v>
@@ -7367,7 +7413,7 @@
         <v>80</v>
       </c>
       <c r="C121" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D121">
         <v>647</v>
@@ -7376,10 +7422,10 @@
         <v>81</v>
       </c>
       <c r="F121" s="14" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G121" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H121" s="2">
         <v>45291</v>
@@ -7390,7 +7436,7 @@
       </c>
       <c r="J121" s="4">
         <f t="shared" ca="1" si="23"/>
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K121" s="2">
         <v>45315</v>
@@ -7400,7 +7446,7 @@
         <v>24</v>
       </c>
       <c r="M121" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O121" s="2">
         <v>45351</v>
@@ -7411,7 +7457,7 @@
         <v>80</v>
       </c>
       <c r="C122" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D122">
         <v>648</v>
@@ -7423,7 +7469,7 @@
         <v>84</v>
       </c>
       <c r="G122" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H122" s="2">
         <v>45291</v>
@@ -7434,7 +7480,7 @@
       </c>
       <c r="J122" s="4">
         <f t="shared" ca="1" si="23"/>
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K122" s="2">
         <v>45315</v>
@@ -7444,18 +7490,18 @@
         <v>24</v>
       </c>
       <c r="M122" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O122" s="2">
         <v>45351</v>
       </c>
     </row>
-    <row r="123" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="123" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B123" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C123" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D123">
         <v>798</v>
@@ -7467,7 +7513,7 @@
         <v>85</v>
       </c>
       <c r="G123" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H123" s="2">
         <v>45309</v>
@@ -7478,17 +7524,20 @@
       </c>
       <c r="J123" s="4">
         <f t="shared" ca="1" si="23"/>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L123" s="4" t="str">
         <f t="shared" si="19"/>
         <v>-</v>
       </c>
       <c r="M123" t="s">
-        <v>198</v>
+        <v>196</v>
+      </c>
+      <c r="O123" s="2">
+        <v>45355</v>
       </c>
       <c r="Q123" s="2" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
     </row>
     <row r="124" spans="2:18" x14ac:dyDescent="0.3">
@@ -7496,7 +7545,7 @@
         <v>5</v>
       </c>
       <c r="C124" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D124">
         <v>795</v>
@@ -7520,25 +7569,23 @@
         <v>42</v>
       </c>
       <c r="L124" s="4" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="M124" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="O124"/>
-      <c r="Q124" s="2" t="s">
-        <v>238</v>
-      </c>
+      <c r="Q124" s="2"/>
       <c r="R124" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="125" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B125" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C125" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D125">
         <v>797</v>
@@ -7550,7 +7597,7 @@
         <v>86</v>
       </c>
       <c r="G125" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H125" s="2">
         <v>45309</v>
@@ -7561,28 +7608,26 @@
       </c>
       <c r="J125" s="4">
         <f t="shared" ref="J125:J126" ca="1" si="25">IF(_xlfn.DAYS(TODAY(),H125)&lt;10000, _xlfn.DAYS(TODAY(),H125), "-")</f>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L125" s="4" t="str">
         <f t="shared" si="19"/>
         <v>-</v>
       </c>
       <c r="M125" t="s">
-        <v>221</v>
-      </c>
-      <c r="Q125" s="2" t="s">
-        <v>238</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="Q125" s="2"/>
       <c r="R125" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="126" spans="2:18" x14ac:dyDescent="0.3">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="126" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B126" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C126" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="D126">
         <v>796</v>
@@ -7594,7 +7639,7 @@
         <v>85</v>
       </c>
       <c r="G126" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="H126" s="2">
         <v>45309</v>
@@ -7605,17 +7650,20 @@
       </c>
       <c r="J126" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L126" s="4" t="str">
         <f t="shared" si="19"/>
         <v>-</v>
       </c>
       <c r="M126" t="s">
-        <v>199</v>
+        <v>197</v>
+      </c>
+      <c r="O126" s="2">
+        <v>45355</v>
       </c>
       <c r="Q126" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
     </row>
     <row r="127" spans="2:18" x14ac:dyDescent="0.3">
@@ -7623,7 +7671,7 @@
         <v>5</v>
       </c>
       <c r="C127" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>83</v>
@@ -7641,22 +7689,22 @@
         <v>196</v>
       </c>
       <c r="L127" s="4" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="M127" s="4" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="O127"/>
       <c r="R127" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
     </row>
     <row r="128" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B128" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C128" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D128">
         <v>794</v>
@@ -7668,7 +7716,7 @@
         <v>84</v>
       </c>
       <c r="G128" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="H128" s="2">
         <v>45309</v>
@@ -7679,25 +7727,25 @@
       </c>
       <c r="J128" s="4">
         <f t="shared" ref="J128:J131" ca="1" si="27">IF(_xlfn.DAYS(TODAY(),H128)&lt;10000, _xlfn.DAYS(TODAY(),H128), "-")</f>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L128" s="4" t="str">
         <f t="shared" si="19"/>
         <v>-</v>
       </c>
       <c r="M128" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="R128" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="129" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B129" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C129" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D129">
         <v>793</v>
@@ -7709,7 +7757,7 @@
         <v>84</v>
       </c>
       <c r="G129" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="H129" s="2">
         <v>45309</v>
@@ -7720,17 +7768,17 @@
       </c>
       <c r="J129" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L129" s="4" t="str">
         <f t="shared" si="19"/>
         <v>-</v>
       </c>
       <c r="M129" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="R129" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="130" spans="2:18" x14ac:dyDescent="0.3">
@@ -7738,7 +7786,7 @@
         <v>5</v>
       </c>
       <c r="C130" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F130" s="10" t="s">
         <v>83</v>
@@ -7755,25 +7803,25 @@
       </c>
       <c r="J130" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L130" s="4" t="str">
         <f t="shared" si="19"/>
         <v>-</v>
       </c>
       <c r="M130" s="4" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="R130" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="131" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B131" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C131" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D131">
         <v>792</v>
@@ -7785,7 +7833,7 @@
         <v>84</v>
       </c>
       <c r="G131" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="H131" s="2">
         <v>45309</v>
@@ -7796,17 +7844,17 @@
       </c>
       <c r="J131" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L131" s="4" t="str">
         <f t="shared" si="19"/>
         <v>-</v>
       </c>
       <c r="M131" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="R131" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="132" spans="2:18" x14ac:dyDescent="0.3">
@@ -7814,7 +7862,7 @@
         <v>5</v>
       </c>
       <c r="C132" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D132">
         <v>686</v>
@@ -7844,12 +7892,12 @@
         <v>27</v>
       </c>
       <c r="M132" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="N132" s="7"/>
       <c r="O132"/>
       <c r="R132" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="133" spans="2:18" x14ac:dyDescent="0.3">
@@ -7857,13 +7905,13 @@
         <v>5</v>
       </c>
       <c r="C133" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F133" s="10" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="G133" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I133" s="4" t="str">
         <f t="shared" ref="I133:I144" ca="1" si="28">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H133), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H133), 7), "-")</f>
@@ -7878,7 +7926,7 @@
         <v>-</v>
       </c>
       <c r="M133" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="134" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -7886,13 +7934,13 @@
         <v>5</v>
       </c>
       <c r="C134" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F134" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G134" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H134" s="2">
         <v>44885</v>
@@ -7903,14 +7951,14 @@
       </c>
       <c r="J134" s="4">
         <f t="shared" ca="1" si="29"/>
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="L134" s="4" t="str">
         <f t="shared" si="30"/>
         <v>-</v>
       </c>
       <c r="M134" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="O134" s="2">
         <v>45351</v>
@@ -7921,13 +7969,13 @@
         <v>5</v>
       </c>
       <c r="C135" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F135" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G135" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H135" s="2">
         <v>44885</v>
@@ -7938,14 +7986,14 @@
       </c>
       <c r="J135" s="4">
         <f t="shared" ca="1" si="29"/>
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="L135" s="4" t="str">
         <f t="shared" si="30"/>
         <v>-</v>
       </c>
       <c r="M135" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="O135" s="2">
         <v>45351</v>
@@ -7956,13 +8004,13 @@
         <v>5</v>
       </c>
       <c r="C136" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F136" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G136" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H136" s="2">
         <v>44885</v>
@@ -7973,14 +8021,14 @@
       </c>
       <c r="J136" s="4">
         <f t="shared" ca="1" si="29"/>
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="L136" s="4" t="str">
         <f t="shared" si="30"/>
         <v>-</v>
       </c>
       <c r="M136" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O136" s="2">
         <v>45351</v>
@@ -7991,13 +8039,13 @@
         <v>5</v>
       </c>
       <c r="C137" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F137" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G137" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H137" s="2">
         <v>44885</v>
@@ -8008,14 +8056,14 @@
       </c>
       <c r="J137" s="4">
         <f t="shared" ca="1" si="29"/>
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="L137" s="4" t="str">
         <f t="shared" si="30"/>
         <v>-</v>
       </c>
       <c r="M137" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O137" s="2">
         <v>45351</v>
@@ -8023,16 +8071,16 @@
     </row>
     <row r="138" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B138" t="s">
+        <v>126</v>
+      </c>
+      <c r="C138" t="s">
         <v>127</v>
       </c>
-      <c r="C138" t="s">
-        <v>128</v>
-      </c>
       <c r="F138" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G138" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I138" s="4" t="str">
         <f t="shared" ca="1" si="28"/>
@@ -8047,7 +8095,7 @@
         <v>-</v>
       </c>
       <c r="M138" s="15" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="O138" s="2">
         <v>45322</v>
@@ -8055,10 +8103,10 @@
     </row>
     <row r="139" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B139" t="s">
+        <v>126</v>
+      </c>
+      <c r="C139" t="s">
         <v>127</v>
-      </c>
-      <c r="C139" t="s">
-        <v>128</v>
       </c>
       <c r="D139">
         <v>791</v>
@@ -8081,22 +8129,22 @@
       </c>
       <c r="J139" s="4">
         <f t="shared" ca="1" si="29"/>
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L139" s="4" t="str">
         <f t="shared" si="30"/>
         <v>-</v>
       </c>
       <c r="M139" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="140" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B140" t="s">
+        <v>126</v>
+      </c>
+      <c r="C140" t="s">
         <v>127</v>
-      </c>
-      <c r="C140" t="s">
-        <v>128</v>
       </c>
       <c r="D140">
         <v>790</v>
@@ -8108,7 +8156,7 @@
         <v>86</v>
       </c>
       <c r="G140" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H140" s="2">
         <v>45301</v>
@@ -8119,22 +8167,22 @@
       </c>
       <c r="J140" s="4">
         <f t="shared" ca="1" si="29"/>
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L140" s="4" t="str">
         <f t="shared" si="30"/>
         <v>-</v>
       </c>
       <c r="M140" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="141" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B141" t="s">
+        <v>126</v>
+      </c>
+      <c r="C141" t="s">
         <v>127</v>
-      </c>
-      <c r="C141" t="s">
-        <v>128</v>
       </c>
       <c r="D141">
         <v>789</v>
@@ -8146,7 +8194,7 @@
         <v>86</v>
       </c>
       <c r="G141" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H141" s="2">
         <v>45301</v>
@@ -8157,22 +8205,22 @@
       </c>
       <c r="J141" s="4">
         <f t="shared" ca="1" si="29"/>
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L141" s="4" t="str">
         <f t="shared" si="30"/>
         <v>-</v>
       </c>
       <c r="M141" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="142" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B142" t="s">
+        <v>126</v>
+      </c>
+      <c r="C142" t="s">
         <v>127</v>
-      </c>
-      <c r="C142" t="s">
-        <v>128</v>
       </c>
       <c r="D142">
         <v>788</v>
@@ -8184,7 +8232,7 @@
         <v>86</v>
       </c>
       <c r="G142" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H142" s="2">
         <v>45301</v>
@@ -8195,22 +8243,22 @@
       </c>
       <c r="J142" s="4">
         <f t="shared" ca="1" si="29"/>
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L142" s="4" t="str">
         <f t="shared" si="30"/>
         <v>-</v>
       </c>
       <c r="M142" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="143" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B143" t="s">
+        <v>126</v>
+      </c>
+      <c r="C143" t="s">
         <v>127</v>
-      </c>
-      <c r="C143" t="s">
-        <v>128</v>
       </c>
       <c r="D143">
         <v>787</v>
@@ -8222,7 +8270,7 @@
         <v>87</v>
       </c>
       <c r="G143" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H143" s="2">
         <v>45301</v>
@@ -8233,14 +8281,14 @@
       </c>
       <c r="J143" s="4">
         <f t="shared" ca="1" si="29"/>
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L143" s="4" t="str">
         <f t="shared" si="30"/>
         <v>-</v>
       </c>
       <c r="M143" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O143" s="2">
         <v>45351</v>
@@ -8248,10 +8296,10 @@
     </row>
     <row r="144" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B144" t="s">
+        <v>126</v>
+      </c>
+      <c r="C144" t="s">
         <v>127</v>
-      </c>
-      <c r="C144" t="s">
-        <v>128</v>
       </c>
       <c r="D144">
         <v>786</v>
@@ -8263,7 +8311,7 @@
         <v>86</v>
       </c>
       <c r="G144" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H144" s="2">
         <v>45301</v>
@@ -8274,28 +8322,28 @@
       </c>
       <c r="J144" s="4">
         <f t="shared" ca="1" si="29"/>
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L144" s="4" t="str">
         <f t="shared" si="30"/>
         <v>-</v>
       </c>
       <c r="M144" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="145" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B145" t="s">
+        <v>126</v>
+      </c>
+      <c r="C145" t="s">
         <v>127</v>
       </c>
-      <c r="C145" t="s">
-        <v>128</v>
-      </c>
       <c r="F145" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G145" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I145" s="4" t="str">
         <f t="shared" ref="I145:I176" ca="1" si="31">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H145), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H145), 7), "-")</f>
@@ -8310,7 +8358,7 @@
         <v>-</v>
       </c>
       <c r="M145" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O145" s="2">
         <v>45351</v>
@@ -8318,16 +8366,16 @@
     </row>
     <row r="146" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B146" t="s">
+        <v>126</v>
+      </c>
+      <c r="C146" t="s">
         <v>127</v>
       </c>
-      <c r="C146" t="s">
-        <v>128</v>
-      </c>
       <c r="F146" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G146" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I146" s="4" t="str">
         <f t="shared" ca="1" si="31"/>
@@ -8342,7 +8390,7 @@
         <v>-</v>
       </c>
       <c r="M146" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="O146" s="2">
         <v>45351</v>
@@ -8350,16 +8398,16 @@
     </row>
     <row r="147" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B147" t="s">
+        <v>126</v>
+      </c>
+      <c r="C147" t="s">
         <v>127</v>
       </c>
-      <c r="C147" t="s">
-        <v>128</v>
-      </c>
       <c r="F147" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G147" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I147" s="4" t="str">
         <f t="shared" ca="1" si="31"/>
@@ -8374,7 +8422,7 @@
         <v>-</v>
       </c>
       <c r="M147" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="O147" s="2">
         <v>45351</v>
@@ -8382,10 +8430,10 @@
     </row>
     <row r="148" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B148" t="s">
+        <v>126</v>
+      </c>
+      <c r="C148" t="s">
         <v>127</v>
-      </c>
-      <c r="C148" t="s">
-        <v>128</v>
       </c>
       <c r="D148">
         <v>785</v>
@@ -8397,39 +8445,39 @@
         <v>86</v>
       </c>
       <c r="G148" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H148" s="2">
         <v>45307</v>
       </c>
       <c r="I148" s="4">
         <f t="shared" ca="1" si="31"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J148" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L148" s="4" t="str">
         <f t="shared" si="33"/>
         <v>-</v>
       </c>
       <c r="M148" s="4" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="P148" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="Q148" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="149" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B149" t="s">
+        <v>126</v>
+      </c>
+      <c r="C149" t="s">
         <v>127</v>
-      </c>
-      <c r="C149" t="s">
-        <v>128</v>
       </c>
       <c r="D149">
         <v>784</v>
@@ -8441,25 +8489,25 @@
         <v>87</v>
       </c>
       <c r="G149" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H149" s="2">
         <v>45307</v>
       </c>
       <c r="I149" s="4">
         <f t="shared" ca="1" si="31"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J149" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L149" s="4" t="str">
         <f t="shared" si="33"/>
         <v>-</v>
       </c>
       <c r="M149" s="4" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="O149" s="2">
         <v>45351</v>
@@ -8467,10 +8515,10 @@
     </row>
     <row r="150" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B150" t="s">
+        <v>126</v>
+      </c>
+      <c r="C150" t="s">
         <v>127</v>
-      </c>
-      <c r="C150" t="s">
-        <v>128</v>
       </c>
       <c r="D150">
         <v>783</v>
@@ -8479,28 +8527,28 @@
         <v>8</v>
       </c>
       <c r="F150" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G150" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H150" s="2">
         <v>45307</v>
       </c>
       <c r="I150" s="4">
         <f t="shared" ca="1" si="31"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J150" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L150" s="4" t="str">
         <f t="shared" si="33"/>
         <v>-</v>
       </c>
       <c r="M150" s="4" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="O150" s="2">
         <v>45351</v>
@@ -8508,10 +8556,10 @@
     </row>
     <row r="151" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B151" t="s">
+        <v>126</v>
+      </c>
+      <c r="C151" t="s">
         <v>127</v>
-      </c>
-      <c r="C151" t="s">
-        <v>128</v>
       </c>
       <c r="D151">
         <v>782</v>
@@ -8520,28 +8568,28 @@
         <v>8</v>
       </c>
       <c r="F151" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G151" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H151" s="2">
         <v>45307</v>
       </c>
       <c r="I151" s="4">
         <f t="shared" ca="1" si="31"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J151" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L151" s="4" t="str">
         <f t="shared" si="33"/>
         <v>-</v>
       </c>
       <c r="M151" s="4" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="O151" s="2">
         <v>45351</v>
@@ -8549,10 +8597,10 @@
     </row>
     <row r="152" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B152" t="s">
+        <v>126</v>
+      </c>
+      <c r="C152" t="s">
         <v>127</v>
-      </c>
-      <c r="C152" t="s">
-        <v>128</v>
       </c>
       <c r="D152">
         <v>781</v>
@@ -8564,39 +8612,39 @@
         <v>86</v>
       </c>
       <c r="G152" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H152" s="2">
         <v>45307</v>
       </c>
       <c r="I152" s="4">
         <f t="shared" ca="1" si="31"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J152" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L152" s="4" t="str">
         <f t="shared" si="33"/>
         <v>-</v>
       </c>
       <c r="M152" s="4" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="P152" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="Q152" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="153" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B153" t="s">
+        <v>126</v>
+      </c>
+      <c r="C153" t="s">
         <v>127</v>
-      </c>
-      <c r="C153" t="s">
-        <v>128</v>
       </c>
       <c r="D153">
         <v>780</v>
@@ -8608,25 +8656,25 @@
         <v>86</v>
       </c>
       <c r="G153" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="H153" s="2">
         <v>45307</v>
       </c>
       <c r="I153" s="4">
         <f t="shared" ca="1" si="31"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J153" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L153" s="4" t="str">
         <f t="shared" si="33"/>
         <v>-</v>
       </c>
       <c r="M153" s="4" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="154" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -8634,7 +8682,7 @@
         <v>34</v>
       </c>
       <c r="C154" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D154">
         <v>710</v>
@@ -8643,10 +8691,10 @@
         <v>8</v>
       </c>
       <c r="F154" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G154" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H154" s="2">
         <v>45189</v>
@@ -8657,14 +8705,14 @@
       </c>
       <c r="J154" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L154" s="4" t="str">
         <f t="shared" si="33"/>
         <v>-</v>
       </c>
       <c r="M154" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="N154" s="2">
         <v>45322</v>
@@ -8673,24 +8721,24 @@
         <v>45336</v>
       </c>
       <c r="Q154" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="155" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B155" t="s">
+        <v>126</v>
+      </c>
+      <c r="C155" t="s">
         <v>127</v>
-      </c>
-      <c r="C155" t="s">
-        <v>128</v>
       </c>
       <c r="D155">
         <v>708</v>
       </c>
       <c r="F155" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G155" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I155" s="4" t="str">
         <f t="shared" ca="1" si="31"/>
@@ -8705,7 +8753,7 @@
         <v>-</v>
       </c>
       <c r="M155" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O155" s="2">
         <v>45329</v>
@@ -8716,7 +8764,7 @@
         <v>5</v>
       </c>
       <c r="C156" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F156" s="10" t="s">
         <v>86</v>
@@ -8737,24 +8785,24 @@
         <v>-</v>
       </c>
       <c r="M156" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="157" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B157" t="s">
+        <v>126</v>
+      </c>
+      <c r="C157" t="s">
         <v>127</v>
-      </c>
-      <c r="C157" t="s">
-        <v>128</v>
       </c>
       <c r="D157">
         <v>767</v>
       </c>
       <c r="F157" s="10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G157" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I157" s="4" t="str">
         <f t="shared" ca="1" si="31"/>
@@ -8769,7 +8817,7 @@
         <v>-</v>
       </c>
       <c r="M157" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="158" spans="2:17" x14ac:dyDescent="0.3">
@@ -8777,7 +8825,7 @@
         <v>5</v>
       </c>
       <c r="C158" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F158" s="10" t="s">
         <v>86</v>
@@ -8798,15 +8846,15 @@
         <v>-</v>
       </c>
       <c r="M158" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="159" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B159" t="s">
+        <v>126</v>
+      </c>
+      <c r="C159" t="s">
         <v>127</v>
-      </c>
-      <c r="C159" t="s">
-        <v>128</v>
       </c>
       <c r="D159">
         <v>606</v>
@@ -8815,10 +8863,10 @@
         <v>8</v>
       </c>
       <c r="F159" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G159" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H159" s="2">
         <v>45269</v>
@@ -8829,7 +8877,7 @@
       </c>
       <c r="J159" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K159" s="2">
         <v>45301</v>
@@ -8839,7 +8887,7 @@
         <v>32</v>
       </c>
       <c r="M159" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="160" spans="2:17" x14ac:dyDescent="0.3">
@@ -8847,7 +8895,7 @@
         <v>5</v>
       </c>
       <c r="C160" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F160" s="10" t="s">
         <v>86</v>
@@ -8868,15 +8916,15 @@
         <v>-</v>
       </c>
       <c r="M160" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="161" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B161" t="s">
+        <v>126</v>
+      </c>
+      <c r="C161" t="s">
         <v>127</v>
-      </c>
-      <c r="C161" t="s">
-        <v>128</v>
       </c>
       <c r="D161">
         <v>607</v>
@@ -8885,10 +8933,10 @@
         <v>8</v>
       </c>
       <c r="F161" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G161" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H161" s="2">
         <v>45269</v>
@@ -8899,7 +8947,7 @@
       </c>
       <c r="J161" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K161" s="2">
         <v>45301</v>
@@ -8909,24 +8957,24 @@
         <v>32</v>
       </c>
       <c r="M161" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="162" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B162" t="s">
+        <v>126</v>
+      </c>
+      <c r="C162" t="s">
         <v>127</v>
-      </c>
-      <c r="C162" t="s">
-        <v>128</v>
       </c>
       <c r="D162">
         <v>608</v>
       </c>
       <c r="E162" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G162" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H162" s="2">
         <v>45269</v>
@@ -8937,7 +8985,7 @@
       </c>
       <c r="J162" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K162" s="2">
         <v>45301</v>
@@ -8947,7 +8995,7 @@
         <v>32</v>
       </c>
       <c r="M162" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O162" s="2">
         <v>45321</v>
@@ -8955,10 +9003,10 @@
     </row>
     <row r="163" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B163" t="s">
+        <v>126</v>
+      </c>
+      <c r="C163" t="s">
         <v>127</v>
-      </c>
-      <c r="C163" t="s">
-        <v>128</v>
       </c>
       <c r="D163">
         <v>609</v>
@@ -8967,10 +9015,10 @@
         <v>8</v>
       </c>
       <c r="F163" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G163" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H163" s="2">
         <v>45269</v>
@@ -8981,7 +9029,7 @@
       </c>
       <c r="J163" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K163" s="2">
         <v>45301</v>
@@ -8991,7 +9039,7 @@
         <v>32</v>
       </c>
       <c r="M163" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="164" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -8999,7 +9047,7 @@
         <v>34</v>
       </c>
       <c r="C164" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D164">
         <v>610</v>
@@ -9008,10 +9056,10 @@
         <v>8</v>
       </c>
       <c r="F164" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G164" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H164" s="2">
         <v>45269</v>
@@ -9022,7 +9070,7 @@
       </c>
       <c r="J164" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K164" s="2">
         <v>45301</v>
@@ -9032,7 +9080,7 @@
         <v>32</v>
       </c>
       <c r="M164" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="N164" s="2">
         <v>45322</v>
@@ -9041,15 +9089,15 @@
         <v>45335</v>
       </c>
       <c r="Q164" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="165" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B165" t="s">
+        <v>126</v>
+      </c>
+      <c r="C165" t="s">
         <v>127</v>
-      </c>
-      <c r="C165" t="s">
-        <v>128</v>
       </c>
       <c r="D165">
         <v>611</v>
@@ -9058,10 +9106,10 @@
         <v>8</v>
       </c>
       <c r="F165" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G165" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H165" s="2">
         <v>45269</v>
@@ -9072,7 +9120,7 @@
       </c>
       <c r="J165" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K165" s="2">
         <v>45301</v>
@@ -9082,7 +9130,7 @@
         <v>32</v>
       </c>
       <c r="M165" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="O165" s="2">
         <v>45350</v>
@@ -9093,16 +9141,16 @@
         <v>34</v>
       </c>
       <c r="C166" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D166">
         <v>708</v>
       </c>
       <c r="F166" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G166" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H166" s="2">
         <v>45189</v>
@@ -9113,14 +9161,14 @@
       </c>
       <c r="J166" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L166" s="4" t="str">
         <f t="shared" si="33"/>
         <v>-</v>
       </c>
       <c r="M166" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="N166" s="2">
         <v>45322</v>
@@ -9129,7 +9177,7 @@
         <v>45336</v>
       </c>
       <c r="Q166" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="167" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -9137,16 +9185,16 @@
         <v>34</v>
       </c>
       <c r="C167" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D167">
         <v>709</v>
       </c>
       <c r="F167" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G167" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H167" s="2">
         <v>45189</v>
@@ -9157,23 +9205,23 @@
       </c>
       <c r="J167" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L167" s="4" t="str">
         <f t="shared" si="33"/>
         <v>-</v>
       </c>
       <c r="M167" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="N167" s="2">
         <v>45322</v>
       </c>
       <c r="Q167" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="R167" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="168" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -9181,16 +9229,16 @@
         <v>34</v>
       </c>
       <c r="C168" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D168">
         <v>711</v>
       </c>
       <c r="F168" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G168" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H168" s="2">
         <v>45189</v>
@@ -9201,23 +9249,23 @@
       </c>
       <c r="J168" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L168" s="4" t="str">
         <f t="shared" si="33"/>
         <v>-</v>
       </c>
       <c r="M168" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="N168" s="2">
         <v>45322</v>
       </c>
       <c r="Q168" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="R168" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="169" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -9225,7 +9273,7 @@
         <v>34</v>
       </c>
       <c r="C169" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D169">
         <v>601</v>
@@ -9234,10 +9282,10 @@
         <v>8</v>
       </c>
       <c r="F169" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G169" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H169" s="2">
         <v>45269</v>
@@ -9248,7 +9296,7 @@
       </c>
       <c r="J169" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K169" s="2">
         <v>45301</v>
@@ -9258,7 +9306,7 @@
         <v>32</v>
       </c>
       <c r="M169" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="N169" s="2">
         <v>45322</v>
@@ -9267,7 +9315,7 @@
         <v>45335</v>
       </c>
       <c r="Q169" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="170" spans="2:18" x14ac:dyDescent="0.3">
@@ -9275,7 +9323,7 @@
         <v>5</v>
       </c>
       <c r="C170" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D170">
         <v>649</v>
@@ -9298,14 +9346,14 @@
       </c>
       <c r="J170" s="4">
         <f t="shared" ref="J170:J171" ca="1" si="38">IF(_xlfn.DAYS(TODAY(),H170)&lt;10000, _xlfn.DAYS(TODAY(),H170), "-")</f>
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L170" s="4" t="str">
         <f t="shared" ref="L170:L171" si="39">IF(_xlfn.DAYS(K170,H170)&gt;0, _xlfn.DAYS(K170,H170), "-")</f>
         <v>-</v>
       </c>
       <c r="M170" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="171" spans="2:18" x14ac:dyDescent="0.3">
@@ -9313,7 +9361,7 @@
         <v>5</v>
       </c>
       <c r="C171" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D171">
         <v>769</v>
@@ -9337,15 +9385,15 @@
         <v>-</v>
       </c>
       <c r="M171" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="172" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B172" t="s">
+        <v>126</v>
+      </c>
+      <c r="C172" t="s">
         <v>127</v>
-      </c>
-      <c r="C172" t="s">
-        <v>128</v>
       </c>
       <c r="D172">
         <v>602</v>
@@ -9354,10 +9402,10 @@
         <v>8</v>
       </c>
       <c r="F172" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G172" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H172" s="2">
         <v>45269</v>
@@ -9368,7 +9416,7 @@
       </c>
       <c r="J172" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K172" s="2">
         <v>45301</v>
@@ -9378,7 +9426,7 @@
         <v>32</v>
       </c>
       <c r="M172" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="173" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -9386,7 +9434,7 @@
         <v>34</v>
       </c>
       <c r="C173" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D173">
         <v>603</v>
@@ -9395,10 +9443,10 @@
         <v>8</v>
       </c>
       <c r="F173" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G173" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H173" s="2">
         <v>45269</v>
@@ -9409,7 +9457,7 @@
       </c>
       <c r="J173" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K173" s="2">
         <v>45301</v>
@@ -9419,16 +9467,16 @@
         <v>32</v>
       </c>
       <c r="M173" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="N173" s="2">
         <v>45322</v>
       </c>
       <c r="Q173" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="R173" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="174" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -9436,7 +9484,7 @@
         <v>34</v>
       </c>
       <c r="C174" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D174">
         <v>604</v>
@@ -9445,10 +9493,10 @@
         <v>8</v>
       </c>
       <c r="F174" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G174" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H174" s="2">
         <v>45269</v>
@@ -9459,7 +9507,7 @@
       </c>
       <c r="J174" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K174" s="2">
         <v>45301</v>
@@ -9469,16 +9517,16 @@
         <v>32</v>
       </c>
       <c r="M174" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="N174" s="2">
         <v>45322</v>
       </c>
       <c r="Q174" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="R174" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="175" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -9486,7 +9534,7 @@
         <v>34</v>
       </c>
       <c r="C175" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D175">
         <v>605</v>
@@ -9495,10 +9543,10 @@
         <v>8</v>
       </c>
       <c r="F175" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G175" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H175" s="2">
         <v>45269</v>
@@ -9509,7 +9557,7 @@
       </c>
       <c r="J175" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K175" s="2">
         <v>45301</v>
@@ -9519,16 +9567,16 @@
         <v>32</v>
       </c>
       <c r="M175" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="N175" s="2">
         <v>45322</v>
       </c>
       <c r="Q175" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="R175" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="176" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -9536,7 +9584,7 @@
         <v>34</v>
       </c>
       <c r="C176" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D176">
         <v>650</v>
@@ -9545,10 +9593,10 @@
         <v>8</v>
       </c>
       <c r="F176" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G176" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H176" s="2">
         <v>45269</v>
@@ -9559,23 +9607,23 @@
       </c>
       <c r="J176" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L176" s="4" t="str">
         <f t="shared" si="33"/>
         <v>-</v>
       </c>
       <c r="M176" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="N176" s="2">
         <v>45322</v>
       </c>
       <c r="Q176" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="R176" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="177" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -9583,26 +9631,26 @@
         <v>34</v>
       </c>
       <c r="C177" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E177" t="s">
         <v>16</v>
       </c>
       <c r="G177" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H177" s="2">
         <v>45300</v>
       </c>
       <c r="I177" s="4">
         <f t="shared" ref="I177" ca="1" si="40">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H177), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H177), 7), "-")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J177" s="4">
         <f t="shared" ref="J177" ca="1" si="41">IF(_xlfn.DAYS(TODAY(),H177)&lt;10000, _xlfn.DAYS(TODAY(),H177), "-")</f>
-        <v>55</v>
-      </c>
-      <c r="K177" s="16">
+        <v>56</v>
+      </c>
+      <c r="K177" s="7">
         <v>45324</v>
       </c>
       <c r="L177" s="4">
@@ -9610,10 +9658,10 @@
         <v>24</v>
       </c>
       <c r="M177" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Q177" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="178" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -9621,26 +9669,26 @@
         <v>34</v>
       </c>
       <c r="C178" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E178" t="s">
         <v>16</v>
       </c>
       <c r="G178" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H178" s="2">
         <v>45300</v>
       </c>
       <c r="I178" s="4">
         <f t="shared" ref="I178:I187" ca="1" si="43">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H178), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H178), 7), "-")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J178" s="4">
         <f t="shared" ref="J178:J187" ca="1" si="44">IF(_xlfn.DAYS(TODAY(),H178)&lt;10000, _xlfn.DAYS(TODAY(),H178), "-")</f>
-        <v>55</v>
-      </c>
-      <c r="K178" s="16">
+        <v>56</v>
+      </c>
+      <c r="K178" s="7">
         <v>45324</v>
       </c>
       <c r="L178" s="4">
@@ -9648,10 +9696,10 @@
         <v>24</v>
       </c>
       <c r="M178" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Q178" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="179" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -9659,26 +9707,26 @@
         <v>34</v>
       </c>
       <c r="C179" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E179" t="s">
         <v>16</v>
       </c>
       <c r="G179" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H179" s="2">
         <v>45300</v>
       </c>
       <c r="I179" s="4">
         <f t="shared" ca="1" si="43"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J179" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>55</v>
-      </c>
-      <c r="K179" s="16">
+        <v>56</v>
+      </c>
+      <c r="K179" s="7">
         <v>45324</v>
       </c>
       <c r="L179" s="4">
@@ -9686,10 +9734,10 @@
         <v>24</v>
       </c>
       <c r="M179" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Q179" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="180" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -9697,26 +9745,26 @@
         <v>34</v>
       </c>
       <c r="C180" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E180" t="s">
         <v>16</v>
       </c>
       <c r="G180" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H180" s="2">
         <v>45300</v>
       </c>
       <c r="I180" s="4">
         <f t="shared" ca="1" si="43"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J180" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>55</v>
-      </c>
-      <c r="K180" s="16">
+        <v>56</v>
+      </c>
+      <c r="K180" s="7">
         <v>45324</v>
       </c>
       <c r="L180" s="4">
@@ -9724,7 +9772,7 @@
         <v>24</v>
       </c>
       <c r="M180" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="181" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -9732,26 +9780,26 @@
         <v>34</v>
       </c>
       <c r="C181" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E181" t="s">
         <v>16</v>
       </c>
       <c r="G181" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H181" s="2">
         <v>45300</v>
       </c>
       <c r="I181" s="4">
         <f t="shared" ca="1" si="43"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J181" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>55</v>
-      </c>
-      <c r="K181" s="16">
+        <v>56</v>
+      </c>
+      <c r="K181" s="7">
         <v>45324</v>
       </c>
       <c r="L181" s="4">
@@ -9759,7 +9807,7 @@
         <v>24</v>
       </c>
       <c r="M181" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="182" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -9767,26 +9815,26 @@
         <v>34</v>
       </c>
       <c r="C182" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E182" t="s">
         <v>16</v>
       </c>
       <c r="G182" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H182" s="2">
         <v>45300</v>
       </c>
       <c r="I182" s="4">
         <f t="shared" ca="1" si="43"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J182" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>55</v>
-      </c>
-      <c r="K182" s="16">
+        <v>56</v>
+      </c>
+      <c r="K182" s="7">
         <v>45324</v>
       </c>
       <c r="L182" s="4">
@@ -9794,7 +9842,7 @@
         <v>24</v>
       </c>
       <c r="M182" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="183" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -9802,26 +9850,26 @@
         <v>34</v>
       </c>
       <c r="C183" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E183" t="s">
         <v>16</v>
       </c>
       <c r="G183" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H183" s="2">
         <v>45300</v>
       </c>
       <c r="I183" s="4">
         <f t="shared" ca="1" si="43"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J183" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>55</v>
-      </c>
-      <c r="K183" s="16">
+        <v>56</v>
+      </c>
+      <c r="K183" s="7">
         <v>45324</v>
       </c>
       <c r="L183" s="4">
@@ -9829,7 +9877,7 @@
         <v>24</v>
       </c>
       <c r="M183" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="184" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -9837,26 +9885,26 @@
         <v>34</v>
       </c>
       <c r="C184" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E184" t="s">
         <v>16</v>
       </c>
       <c r="G184" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H184" s="2">
         <v>45300</v>
       </c>
       <c r="I184" s="4">
         <f t="shared" ca="1" si="43"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J184" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>55</v>
-      </c>
-      <c r="K184" s="16">
+        <v>56</v>
+      </c>
+      <c r="K184" s="7">
         <v>45324</v>
       </c>
       <c r="L184" s="4">
@@ -9864,7 +9912,7 @@
         <v>24</v>
       </c>
       <c r="M184" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="185" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -9872,26 +9920,26 @@
         <v>34</v>
       </c>
       <c r="C185" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E185" t="s">
         <v>16</v>
       </c>
       <c r="G185" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H185" s="2">
         <v>45300</v>
       </c>
       <c r="I185" s="4">
         <f t="shared" ca="1" si="43"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J185" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>55</v>
-      </c>
-      <c r="K185" s="16">
+        <v>56</v>
+      </c>
+      <c r="K185" s="7">
         <v>45324</v>
       </c>
       <c r="L185" s="4">
@@ -9899,15 +9947,18 @@
         <v>24</v>
       </c>
       <c r="M185" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="186" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B186" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C186" t="s">
-        <v>111</v>
+        <v>110</v>
+      </c>
+      <c r="E186" t="s">
+        <v>16</v>
       </c>
       <c r="H186" s="2">
         <v>45324</v>
@@ -9918,13 +9969,13 @@
       </c>
       <c r="J186" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M186" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="Q186" t="s">
-        <v>232</v>
+        <v>249</v>
       </c>
     </row>
     <row r="187" spans="2:18" x14ac:dyDescent="0.3">
@@ -9932,7 +9983,7 @@
         <v>5</v>
       </c>
       <c r="C187" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E187" t="s">
         <v>16</v>
@@ -9946,20 +9997,20 @@
       </c>
       <c r="J187" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L187" s="4" t="str">
         <f t="shared" ref="L187" si="46">IF(_xlfn.DAYS(K187,H187)&gt;0, _xlfn.DAYS(K187,H187), "-")</f>
         <v>-</v>
       </c>
       <c r="M187" t="s">
-        <v>167</v>
+        <v>233</v>
       </c>
       <c r="Q187" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="R187" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="188" spans="2:18" x14ac:dyDescent="0.3">
@@ -9967,7 +10018,7 @@
         <v>5</v>
       </c>
       <c r="C188" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E188" t="s">
         <v>16</v>
@@ -9976,25 +10027,25 @@
         <v>45327</v>
       </c>
       <c r="I188" s="4">
-        <f t="shared" ref="I188:I194" ca="1" si="47">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H188), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H188), 7), "-")</f>
+        <f t="shared" ref="I188:I192" ca="1" si="47">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H188), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H188), 7), "-")</f>
         <v>4</v>
       </c>
       <c r="J188" s="4">
-        <f t="shared" ref="J188:J194" ca="1" si="48">IF(_xlfn.DAYS(TODAY(),H188)&lt;10000, _xlfn.DAYS(TODAY(),H188), "-")</f>
-        <v>28</v>
+        <f t="shared" ref="J188:J192" ca="1" si="48">IF(_xlfn.DAYS(TODAY(),H188)&lt;10000, _xlfn.DAYS(TODAY(),H188), "-")</f>
+        <v>29</v>
       </c>
       <c r="L188" s="4" t="str">
-        <f t="shared" ref="L188:L194" si="49">IF(_xlfn.DAYS(K188,H188)&gt;0, _xlfn.DAYS(K188,H188), "-")</f>
+        <f t="shared" ref="L188:L192" si="49">IF(_xlfn.DAYS(K188,H188)&gt;0, _xlfn.DAYS(K188,H188), "-")</f>
         <v>-</v>
       </c>
       <c r="M188" t="s">
-        <v>167</v>
+        <v>233</v>
       </c>
       <c r="Q188" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="R188" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="189" spans="2:18" x14ac:dyDescent="0.3">
@@ -10002,7 +10053,7 @@
         <v>5</v>
       </c>
       <c r="C189" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E189" s="2" t="s">
         <v>16</v>
@@ -10016,20 +10067,20 @@
       </c>
       <c r="J189" s="4">
         <f t="shared" ca="1" si="48"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L189" s="4" t="str">
         <f t="shared" si="49"/>
         <v>-</v>
       </c>
       <c r="M189" t="s">
-        <v>167</v>
+        <v>233</v>
       </c>
       <c r="Q189" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="R189" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="190" spans="2:18" x14ac:dyDescent="0.3">
@@ -10037,7 +10088,7 @@
         <v>5</v>
       </c>
       <c r="C190" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E190" t="s">
         <v>16</v>
@@ -10051,20 +10102,20 @@
       </c>
       <c r="J190" s="4">
         <f t="shared" ca="1" si="48"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L190" s="4" t="str">
         <f t="shared" si="49"/>
         <v>-</v>
       </c>
       <c r="M190" t="s">
-        <v>167</v>
+        <v>233</v>
       </c>
       <c r="Q190" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="R190" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="191" spans="2:18" x14ac:dyDescent="0.3">
@@ -10072,7 +10123,7 @@
         <v>5</v>
       </c>
       <c r="C191" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E191" t="s">
         <v>16</v>
@@ -10086,20 +10137,20 @@
       </c>
       <c r="J191" s="4">
         <f t="shared" ca="1" si="48"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L191" s="4" t="str">
         <f t="shared" si="49"/>
         <v>-</v>
       </c>
       <c r="M191" t="s">
-        <v>167</v>
+        <v>234</v>
       </c>
       <c r="Q191" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="R191" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="192" spans="2:18" x14ac:dyDescent="0.3">
@@ -10107,7 +10158,7 @@
         <v>5</v>
       </c>
       <c r="C192" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E192" t="s">
         <v>16</v>
@@ -10121,234 +10172,246 @@
       </c>
       <c r="J192" s="4">
         <f t="shared" ca="1" si="48"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L192" s="4" t="str">
         <f t="shared" si="49"/>
         <v>-</v>
       </c>
       <c r="M192" t="s">
-        <v>167</v>
+        <v>234</v>
       </c>
       <c r="Q192" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="R192" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="193" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B193" t="s">
-        <v>5</v>
+        <v>166</v>
       </c>
       <c r="C193" t="s">
-        <v>128</v>
+        <v>111</v>
+      </c>
+      <c r="D193">
+        <v>639</v>
       </c>
       <c r="E193" t="s">
-        <v>16</v>
-      </c>
-      <c r="H193" s="2">
-        <v>45327</v>
-      </c>
-      <c r="I193" s="4">
-        <f t="shared" ca="1" si="47"/>
-        <v>4</v>
-      </c>
-      <c r="J193" s="4">
-        <f t="shared" ca="1" si="48"/>
-        <v>28</v>
-      </c>
-      <c r="L193" s="4" t="str">
-        <f t="shared" si="49"/>
-        <v>-</v>
-      </c>
-      <c r="M193" t="s">
+        <v>175</v>
+      </c>
+      <c r="F193" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="G193" t="s">
+        <v>174</v>
+      </c>
+      <c r="M193" s="4" t="s">
         <v>167</v>
-      </c>
-      <c r="Q193" t="s">
-        <v>236</v>
-      </c>
-      <c r="R193" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="194" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B194" t="s">
-        <v>5</v>
+        <v>166</v>
       </c>
       <c r="C194" t="s">
-        <v>128</v>
+        <v>111</v>
+      </c>
+      <c r="D194">
+        <v>640</v>
       </c>
       <c r="E194" t="s">
-        <v>16</v>
-      </c>
-      <c r="H194" s="2">
-        <v>45327</v>
-      </c>
-      <c r="I194" s="4">
-        <f t="shared" ca="1" si="47"/>
-        <v>4</v>
-      </c>
-      <c r="J194" s="4">
-        <f t="shared" ca="1" si="48"/>
-        <v>28</v>
-      </c>
-      <c r="L194" s="4" t="str">
-        <f t="shared" si="49"/>
-        <v>-</v>
-      </c>
-      <c r="M194" t="s">
+        <v>175</v>
+      </c>
+      <c r="F194" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="G194" t="s">
+        <v>174</v>
+      </c>
+      <c r="M194" s="4" t="s">
         <v>167</v>
       </c>
       <c r="Q194" t="s">
-        <v>236</v>
-      </c>
-      <c r="R194" t="s">
-        <v>217</v>
+        <v>173</v>
       </c>
     </row>
     <row r="195" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B195" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C195" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D195">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="E195" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F195" s="5" t="s">
         <v>171</v>
       </c>
       <c r="G195" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="M195" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="196" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B196" t="s">
+        <v>166</v>
+      </c>
+      <c r="C196" t="s">
+        <v>111</v>
+      </c>
+      <c r="D196">
+        <v>642</v>
+      </c>
+      <c r="E196" t="s">
+        <v>175</v>
+      </c>
+      <c r="F196" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="G196" t="s">
+        <v>174</v>
+      </c>
+      <c r="M196" s="4" t="s">
         <v>168</v>
-      </c>
-      <c r="C196" t="s">
-        <v>112</v>
-      </c>
-      <c r="D196">
-        <v>640</v>
-      </c>
-      <c r="E196" t="s">
-        <v>177</v>
-      </c>
-      <c r="F196" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="G196" t="s">
-        <v>176</v>
-      </c>
-      <c r="M196" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="Q196" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="197" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B197" t="s">
+        <v>166</v>
+      </c>
+      <c r="C197" t="s">
+        <v>111</v>
+      </c>
+      <c r="D197">
+        <v>643</v>
+      </c>
+      <c r="E197" t="s">
+        <v>175</v>
+      </c>
+      <c r="F197" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="G197" t="s">
+        <v>174</v>
+      </c>
+      <c r="M197" s="4" t="s">
         <v>168</v>
-      </c>
-      <c r="C197" t="s">
-        <v>112</v>
-      </c>
-      <c r="D197">
-        <v>641</v>
-      </c>
-      <c r="E197" t="s">
-        <v>177</v>
-      </c>
-      <c r="F197" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="G197" t="s">
-        <v>176</v>
-      </c>
-      <c r="M197" s="4" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="198" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B198" t="s">
+        <v>166</v>
+      </c>
+      <c r="C198" t="s">
+        <v>111</v>
+      </c>
+      <c r="D198">
+        <v>644</v>
+      </c>
+      <c r="E198" t="s">
+        <v>175</v>
+      </c>
+      <c r="F198" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="G198" t="s">
+        <v>174</v>
+      </c>
+      <c r="M198" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="C198" t="s">
-        <v>112</v>
-      </c>
-      <c r="D198">
-        <v>642</v>
-      </c>
-      <c r="E198" t="s">
-        <v>177</v>
-      </c>
-      <c r="F198" s="5" t="s">
+      <c r="Q198" t="s">
         <v>173</v>
-      </c>
-      <c r="G198" t="s">
-        <v>176</v>
-      </c>
-      <c r="M198" s="4" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="199" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B199" t="s">
-        <v>168</v>
+        <v>5</v>
       </c>
       <c r="C199" t="s">
         <v>112</v>
       </c>
-      <c r="D199">
-        <v>643</v>
+      <c r="D199" t="s">
+        <v>238</v>
       </c>
       <c r="E199" t="s">
-        <v>177</v>
+        <v>7</v>
       </c>
       <c r="F199" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="G199" t="s">
-        <v>176</v>
-      </c>
-      <c r="M199" s="4" t="s">
-        <v>170</v>
+        <v>251</v>
+      </c>
+      <c r="H199" s="2">
+        <v>45332</v>
+      </c>
+      <c r="I199" s="4">
+        <f t="shared" ref="I199" ca="1" si="50">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H199), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H199), 7), "-")</f>
+        <v>3</v>
+      </c>
+      <c r="J199" s="4">
+        <f t="shared" ref="J199" ca="1" si="51">IF(_xlfn.DAYS(TODAY(),H199)&lt;10000, _xlfn.DAYS(TODAY(),H199), "-")</f>
+        <v>24</v>
+      </c>
+      <c r="L199" s="4" t="str">
+        <f t="shared" ref="L199" si="52">IF(_xlfn.DAYS(K199,H199)&gt;0, _xlfn.DAYS(K199,H199), "-")</f>
+        <v>-</v>
+      </c>
+      <c r="M199" t="s">
+        <v>235</v>
+      </c>
+      <c r="Q199" t="s">
+        <v>173</v>
+      </c>
+      <c r="R199" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="200" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B200" t="s">
-        <v>168</v>
+        <v>5</v>
       </c>
       <c r="C200" t="s">
         <v>112</v>
       </c>
-      <c r="D200">
-        <v>644</v>
+      <c r="D200" t="s">
+        <v>239</v>
       </c>
       <c r="E200" t="s">
-        <v>177</v>
+        <v>8</v>
       </c>
       <c r="F200" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="G200" t="s">
-        <v>176</v>
-      </c>
-      <c r="M200" s="4" t="s">
-        <v>170</v>
+        <v>252</v>
+      </c>
+      <c r="H200" s="2">
+        <v>45332</v>
+      </c>
+      <c r="I200" s="4">
+        <f t="shared" ref="I200:I214" ca="1" si="53">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H200), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H200), 7), "-")</f>
+        <v>3</v>
+      </c>
+      <c r="J200" s="4">
+        <f t="shared" ref="J200:J214" ca="1" si="54">IF(_xlfn.DAYS(TODAY(),H200)&lt;10000, _xlfn.DAYS(TODAY(),H200), "-")</f>
+        <v>24</v>
+      </c>
+      <c r="L200" s="4" t="str">
+        <f t="shared" ref="L200:L214" si="55">IF(_xlfn.DAYS(K200,H200)&gt;0, _xlfn.DAYS(K200,H200), "-")</f>
+        <v>-</v>
+      </c>
+      <c r="M200" t="s">
+        <v>235</v>
       </c>
       <c r="Q200" t="s">
-        <v>175</v>
+        <v>173</v>
+      </c>
+      <c r="R200" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="201" spans="2:18" x14ac:dyDescent="0.3">
@@ -10356,34 +10419,40 @@
         <v>5</v>
       </c>
       <c r="C201" t="s">
-        <v>113</v>
+        <v>112</v>
+      </c>
+      <c r="D201" t="s">
+        <v>240</v>
       </c>
       <c r="E201" t="s">
-        <v>15</v>
+        <v>8</v>
+      </c>
+      <c r="F201" s="5" t="s">
+        <v>252</v>
       </c>
       <c r="H201" s="2">
         <v>45332</v>
       </c>
       <c r="I201" s="4">
-        <f t="shared" ref="I201" ca="1" si="50">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H201), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H201), 7), "-")</f>
+        <f t="shared" ca="1" si="53"/>
         <v>3</v>
       </c>
       <c r="J201" s="4">
-        <f t="shared" ref="J201" ca="1" si="51">IF(_xlfn.DAYS(TODAY(),H201)&lt;10000, _xlfn.DAYS(TODAY(),H201), "-")</f>
-        <v>23</v>
+        <f t="shared" ca="1" si="54"/>
+        <v>24</v>
       </c>
       <c r="L201" s="4" t="str">
-        <f t="shared" ref="L201" si="52">IF(_xlfn.DAYS(K201,H201)&gt;0, _xlfn.DAYS(K201,H201), "-")</f>
+        <f t="shared" si="55"/>
         <v>-</v>
       </c>
       <c r="M201" t="s">
-        <v>201</v>
+        <v>235</v>
       </c>
       <c r="Q201" t="s">
-        <v>237</v>
+        <v>173</v>
       </c>
       <c r="R201" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="202" spans="2:18" x14ac:dyDescent="0.3">
@@ -10391,34 +10460,40 @@
         <v>5</v>
       </c>
       <c r="C202" t="s">
-        <v>113</v>
+        <v>112</v>
+      </c>
+      <c r="D202" t="s">
+        <v>238</v>
       </c>
       <c r="E202" t="s">
-        <v>15</v>
+        <v>8</v>
+      </c>
+      <c r="F202" s="5" t="s">
+        <v>252</v>
       </c>
       <c r="H202" s="2">
         <v>45332</v>
       </c>
       <c r="I202" s="4">
-        <f t="shared" ref="I202:I217" ca="1" si="53">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H202), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H202), 7), "-")</f>
+        <f t="shared" ca="1" si="53"/>
         <v>3</v>
       </c>
       <c r="J202" s="4">
-        <f t="shared" ref="J202:J217" ca="1" si="54">IF(_xlfn.DAYS(TODAY(),H202)&lt;10000, _xlfn.DAYS(TODAY(),H202), "-")</f>
-        <v>23</v>
+        <f t="shared" ca="1" si="54"/>
+        <v>24</v>
       </c>
       <c r="L202" s="4" t="str">
-        <f t="shared" ref="L202:L217" si="55">IF(_xlfn.DAYS(K202,H202)&gt;0, _xlfn.DAYS(K202,H202), "-")</f>
+        <f t="shared" si="55"/>
         <v>-</v>
       </c>
       <c r="M202" t="s">
-        <v>201</v>
+        <v>236</v>
       </c>
       <c r="Q202" t="s">
-        <v>237</v>
+        <v>173</v>
       </c>
       <c r="R202" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="203" spans="2:18" x14ac:dyDescent="0.3">
@@ -10426,10 +10501,16 @@
         <v>5</v>
       </c>
       <c r="C203" t="s">
-        <v>113</v>
+        <v>112</v>
+      </c>
+      <c r="D203" t="s">
+        <v>239</v>
       </c>
       <c r="E203" t="s">
-        <v>15</v>
+        <v>8</v>
+      </c>
+      <c r="F203" s="5" t="s">
+        <v>252</v>
       </c>
       <c r="H203" s="2">
         <v>45332</v>
@@ -10440,20 +10521,20 @@
       </c>
       <c r="J203" s="4">
         <f t="shared" ca="1" si="54"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L203" s="4" t="str">
         <f t="shared" si="55"/>
         <v>-</v>
       </c>
       <c r="M203" t="s">
-        <v>201</v>
+        <v>236</v>
       </c>
       <c r="Q203" t="s">
-        <v>237</v>
+        <v>173</v>
       </c>
       <c r="R203" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="204" spans="2:18" x14ac:dyDescent="0.3">
@@ -10461,10 +10542,16 @@
         <v>5</v>
       </c>
       <c r="C204" t="s">
-        <v>113</v>
+        <v>112</v>
+      </c>
+      <c r="D204" t="s">
+        <v>240</v>
       </c>
       <c r="E204" t="s">
-        <v>15</v>
+        <v>7</v>
+      </c>
+      <c r="F204" s="5" t="s">
+        <v>252</v>
       </c>
       <c r="H204" s="2">
         <v>45332</v>
@@ -10475,20 +10562,20 @@
       </c>
       <c r="J204" s="4">
         <f t="shared" ca="1" si="54"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L204" s="4" t="str">
         <f t="shared" si="55"/>
         <v>-</v>
       </c>
       <c r="M204" t="s">
-        <v>201</v>
+        <v>236</v>
       </c>
       <c r="Q204" t="s">
-        <v>237</v>
+        <v>173</v>
       </c>
       <c r="R204" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="205" spans="2:18" x14ac:dyDescent="0.3">
@@ -10496,10 +10583,16 @@
         <v>5</v>
       </c>
       <c r="C205" t="s">
-        <v>113</v>
+        <v>112</v>
+      </c>
+      <c r="D205" t="s">
+        <v>241</v>
       </c>
       <c r="E205" t="s">
-        <v>15</v>
+        <v>7</v>
+      </c>
+      <c r="F205" s="5" t="s">
+        <v>252</v>
       </c>
       <c r="H205" s="2">
         <v>45332</v>
@@ -10510,20 +10603,20 @@
       </c>
       <c r="J205" s="4">
         <f t="shared" ca="1" si="54"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L205" s="4" t="str">
         <f t="shared" si="55"/>
         <v>-</v>
       </c>
       <c r="M205" t="s">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="Q205" t="s">
-        <v>237</v>
+        <v>173</v>
       </c>
       <c r="R205" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="206" spans="2:18" x14ac:dyDescent="0.3">
@@ -10531,10 +10624,16 @@
         <v>5</v>
       </c>
       <c r="C206" t="s">
-        <v>113</v>
+        <v>112</v>
+      </c>
+      <c r="D206" t="s">
+        <v>242</v>
       </c>
       <c r="E206" t="s">
-        <v>15</v>
+        <v>7</v>
+      </c>
+      <c r="F206" s="5" t="s">
+        <v>251</v>
       </c>
       <c r="H206" s="2">
         <v>45332</v>
@@ -10545,20 +10644,20 @@
       </c>
       <c r="J206" s="4">
         <f t="shared" ca="1" si="54"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L206" s="4" t="str">
         <f t="shared" si="55"/>
         <v>-</v>
       </c>
       <c r="M206" t="s">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="Q206" t="s">
-        <v>237</v>
+        <v>173</v>
       </c>
       <c r="R206" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="207" spans="2:18" x14ac:dyDescent="0.3">
@@ -10566,10 +10665,16 @@
         <v>5</v>
       </c>
       <c r="C207" t="s">
-        <v>113</v>
+        <v>112</v>
+      </c>
+      <c r="D207" t="s">
+        <v>243</v>
       </c>
       <c r="E207" t="s">
-        <v>15</v>
+        <v>7</v>
+      </c>
+      <c r="F207" s="5" t="s">
+        <v>251</v>
       </c>
       <c r="H207" s="2">
         <v>45332</v>
@@ -10580,20 +10685,20 @@
       </c>
       <c r="J207" s="4">
         <f t="shared" ca="1" si="54"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L207" s="4" t="str">
         <f t="shared" si="55"/>
         <v>-</v>
       </c>
       <c r="M207" t="s">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="Q207" t="s">
-        <v>237</v>
+        <v>173</v>
       </c>
       <c r="R207" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="208" spans="2:18" x14ac:dyDescent="0.3">
@@ -10601,34 +10706,31 @@
         <v>5</v>
       </c>
       <c r="C208" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E208" t="s">
         <v>15</v>
       </c>
       <c r="H208" s="2">
-        <v>45332</v>
+        <v>45337</v>
       </c>
       <c r="I208" s="4">
         <f t="shared" ca="1" si="53"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J208" s="4">
         <f t="shared" ca="1" si="54"/>
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="L208" s="4" t="str">
         <f t="shared" si="55"/>
         <v>-</v>
       </c>
       <c r="M208" t="s">
-        <v>201</v>
-      </c>
-      <c r="Q208" t="s">
-        <v>237</v>
+        <v>199</v>
       </c>
       <c r="R208" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="209" spans="2:18" x14ac:dyDescent="0.3">
@@ -10636,34 +10738,31 @@
         <v>5</v>
       </c>
       <c r="C209" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E209" t="s">
         <v>15</v>
       </c>
       <c r="H209" s="2">
-        <v>45332</v>
+        <v>45337</v>
       </c>
       <c r="I209" s="4">
         <f t="shared" ca="1" si="53"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J209" s="4">
         <f t="shared" ca="1" si="54"/>
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="L209" s="4" t="str">
         <f t="shared" si="55"/>
         <v>-</v>
       </c>
       <c r="M209" t="s">
-        <v>201</v>
-      </c>
-      <c r="Q209" t="s">
-        <v>237</v>
+        <v>199</v>
       </c>
       <c r="R209" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="210" spans="2:18" x14ac:dyDescent="0.3">
@@ -10671,34 +10770,31 @@
         <v>5</v>
       </c>
       <c r="C210" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E210" t="s">
         <v>15</v>
       </c>
       <c r="H210" s="2">
-        <v>45332</v>
+        <v>45337</v>
       </c>
       <c r="I210" s="4">
         <f t="shared" ca="1" si="53"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J210" s="4">
         <f t="shared" ca="1" si="54"/>
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="L210" s="4" t="str">
         <f t="shared" si="55"/>
         <v>-</v>
       </c>
       <c r="M210" t="s">
-        <v>201</v>
-      </c>
-      <c r="Q210" t="s">
-        <v>237</v>
+        <v>199</v>
       </c>
       <c r="R210" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="211" spans="2:18" x14ac:dyDescent="0.3">
@@ -10706,7 +10802,7 @@
         <v>5</v>
       </c>
       <c r="C211" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E211" t="s">
         <v>15</v>
@@ -10720,17 +10816,17 @@
       </c>
       <c r="J211" s="4">
         <f t="shared" ca="1" si="54"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L211" s="4" t="str">
         <f t="shared" si="55"/>
         <v>-</v>
       </c>
       <c r="M211" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="R211" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="212" spans="2:18" x14ac:dyDescent="0.3">
@@ -10738,7 +10834,7 @@
         <v>5</v>
       </c>
       <c r="C212" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E212" t="s">
         <v>15</v>
@@ -10752,17 +10848,17 @@
       </c>
       <c r="J212" s="4">
         <f t="shared" ca="1" si="54"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L212" s="4" t="str">
         <f t="shared" si="55"/>
         <v>-</v>
       </c>
       <c r="M212" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="R212" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="213" spans="2:18" x14ac:dyDescent="0.3">
@@ -10770,7 +10866,7 @@
         <v>5</v>
       </c>
       <c r="C213" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E213" t="s">
         <v>15</v>
@@ -10784,17 +10880,17 @@
       </c>
       <c r="J213" s="4">
         <f t="shared" ca="1" si="54"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L213" s="4" t="str">
         <f t="shared" si="55"/>
         <v>-</v>
       </c>
       <c r="M213" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="R213" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="214" spans="2:18" x14ac:dyDescent="0.3">
@@ -10802,7 +10898,7 @@
         <v>5</v>
       </c>
       <c r="C214" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E214" t="s">
         <v>15</v>
@@ -10816,17 +10912,17 @@
       </c>
       <c r="J214" s="4">
         <f t="shared" ca="1" si="54"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L214" s="4" t="str">
         <f t="shared" si="55"/>
         <v>-</v>
       </c>
       <c r="M214" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="R214" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="215" spans="2:18" x14ac:dyDescent="0.3">
@@ -10834,31 +10930,31 @@
         <v>5</v>
       </c>
       <c r="C215" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="E215" t="s">
-        <v>15</v>
+        <v>204</v>
       </c>
       <c r="H215" s="2">
-        <v>45337</v>
+        <v>45343</v>
       </c>
       <c r="I215" s="4">
-        <f t="shared" ca="1" si="53"/>
-        <v>2</v>
+        <f t="shared" ref="I215:I226" ca="1" si="56">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H215), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H215), 7), "-")</f>
+        <v>1</v>
       </c>
       <c r="J215" s="4">
-        <f t="shared" ca="1" si="54"/>
-        <v>18</v>
+        <f t="shared" ref="J215:J226" ca="1" si="57">IF(_xlfn.DAYS(TODAY(),H215)&lt;10000, _xlfn.DAYS(TODAY(),H215), "-")</f>
+        <v>13</v>
       </c>
       <c r="L215" s="4" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" ref="L215:L226" si="58">IF(_xlfn.DAYS(K215,H215)&gt;0, _xlfn.DAYS(K215,H215), "-")</f>
         <v>-</v>
       </c>
       <c r="M215" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="R215" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="216" spans="2:18" x14ac:dyDescent="0.3">
@@ -10866,31 +10962,31 @@
         <v>5</v>
       </c>
       <c r="C216" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="E216" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H216" s="2">
-        <v>45337</v>
+        <v>45343</v>
       </c>
       <c r="I216" s="4">
-        <f t="shared" ca="1" si="53"/>
-        <v>2</v>
+        <f t="shared" ca="1" si="56"/>
+        <v>1</v>
       </c>
       <c r="J216" s="4">
-        <f t="shared" ca="1" si="54"/>
-        <v>18</v>
+        <f t="shared" ca="1" si="57"/>
+        <v>13</v>
       </c>
       <c r="L216" s="4" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="58"/>
         <v>-</v>
       </c>
       <c r="M216" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="R216" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="217" spans="2:18" x14ac:dyDescent="0.3">
@@ -10898,31 +10994,31 @@
         <v>5</v>
       </c>
       <c r="C217" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="E217" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H217" s="2">
-        <v>45337</v>
+        <v>45343</v>
       </c>
       <c r="I217" s="4">
-        <f t="shared" ca="1" si="53"/>
-        <v>2</v>
+        <f t="shared" ca="1" si="56"/>
+        <v>1</v>
       </c>
       <c r="J217" s="4">
-        <f t="shared" ca="1" si="54"/>
-        <v>18</v>
+        <f t="shared" ca="1" si="57"/>
+        <v>13</v>
       </c>
       <c r="L217" s="4" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="58"/>
         <v>-</v>
       </c>
       <c r="M217" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="R217" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="218" spans="2:18" x14ac:dyDescent="0.3">
@@ -10930,31 +11026,31 @@
         <v>5</v>
       </c>
       <c r="C218" t="s">
-        <v>128</v>
-      </c>
-      <c r="E218" t="s">
-        <v>206</v>
+        <v>127</v>
+      </c>
+      <c r="E218" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="H218" s="2">
         <v>45343</v>
       </c>
       <c r="I218" s="4">
-        <f t="shared" ref="I218:I235" ca="1" si="56">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H218), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H218), 7), "-")</f>
+        <f t="shared" ca="1" si="56"/>
         <v>1</v>
       </c>
       <c r="J218" s="4">
-        <f t="shared" ref="J218:J235" ca="1" si="57">IF(_xlfn.DAYS(TODAY(),H218)&lt;10000, _xlfn.DAYS(TODAY(),H218), "-")</f>
-        <v>12</v>
+        <f t="shared" ca="1" si="57"/>
+        <v>13</v>
       </c>
       <c r="L218" s="4" t="str">
-        <f t="shared" ref="L218:L235" si="58">IF(_xlfn.DAYS(K218,H218)&gt;0, _xlfn.DAYS(K218,H218), "-")</f>
+        <f t="shared" si="58"/>
         <v>-</v>
       </c>
       <c r="M218" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="R218" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="219" spans="2:18" x14ac:dyDescent="0.3">
@@ -10962,7 +11058,7 @@
         <v>5</v>
       </c>
       <c r="C219" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E219" t="s">
         <v>16</v>
@@ -10976,17 +11072,17 @@
       </c>
       <c r="J219" s="4">
         <f t="shared" ca="1" si="57"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L219" s="4" t="str">
         <f t="shared" si="58"/>
         <v>-</v>
       </c>
       <c r="M219" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="R219" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="220" spans="2:18" x14ac:dyDescent="0.3">
@@ -10994,7 +11090,7 @@
         <v>5</v>
       </c>
       <c r="C220" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E220" t="s">
         <v>16</v>
@@ -11008,17 +11104,17 @@
       </c>
       <c r="J220" s="4">
         <f t="shared" ca="1" si="57"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L220" s="4" t="str">
         <f t="shared" si="58"/>
         <v>-</v>
       </c>
       <c r="M220" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="R220" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="221" spans="2:18" x14ac:dyDescent="0.3">
@@ -11026,7 +11122,7 @@
         <v>5</v>
       </c>
       <c r="C221" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E221" s="2" t="s">
         <v>16</v>
@@ -11040,17 +11136,17 @@
       </c>
       <c r="J221" s="4">
         <f t="shared" ca="1" si="57"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L221" s="4" t="str">
         <f t="shared" si="58"/>
         <v>-</v>
       </c>
       <c r="M221" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="R221" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="222" spans="2:18" x14ac:dyDescent="0.3">
@@ -11058,7 +11154,7 @@
         <v>5</v>
       </c>
       <c r="C222" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E222" t="s">
         <v>16</v>
@@ -11072,17 +11168,17 @@
       </c>
       <c r="J222" s="4">
         <f t="shared" ca="1" si="57"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L222" s="4" t="str">
         <f t="shared" si="58"/>
         <v>-</v>
       </c>
       <c r="M222" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="R222" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="223" spans="2:18" x14ac:dyDescent="0.3">
@@ -11090,28 +11186,28 @@
         <v>5</v>
       </c>
       <c r="C223" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="E223" t="s">
         <v>16</v>
       </c>
       <c r="H223" s="2">
-        <v>45343</v>
+        <v>45337</v>
       </c>
       <c r="I223" s="4">
         <f t="shared" ca="1" si="56"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J223" s="4">
         <f t="shared" ca="1" si="57"/>
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="L223" s="4" t="str">
         <f t="shared" si="58"/>
         <v>-</v>
       </c>
-      <c r="M223" t="s">
-        <v>204</v>
+      <c r="M223" s="4" t="s">
+        <v>200</v>
       </c>
       <c r="R223" t="s">
         <v>209</v>
@@ -11122,28 +11218,28 @@
         <v>5</v>
       </c>
       <c r="C224" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="E224" t="s">
         <v>16</v>
       </c>
       <c r="H224" s="2">
-        <v>45343</v>
+        <v>45337</v>
       </c>
       <c r="I224" s="4">
         <f t="shared" ca="1" si="56"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J224" s="4">
         <f t="shared" ca="1" si="57"/>
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="L224" s="4" t="str">
         <f t="shared" si="58"/>
         <v>-</v>
       </c>
-      <c r="M224" t="s">
-        <v>204</v>
+      <c r="M224" s="4" t="s">
+        <v>200</v>
       </c>
       <c r="R224" t="s">
         <v>209</v>
@@ -11154,28 +11250,28 @@
         <v>5</v>
       </c>
       <c r="C225" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="E225" t="s">
         <v>16</v>
       </c>
       <c r="H225" s="2">
-        <v>45343</v>
+        <v>45337</v>
       </c>
       <c r="I225" s="4">
         <f t="shared" ca="1" si="56"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J225" s="4">
         <f t="shared" ca="1" si="57"/>
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="L225" s="4" t="str">
         <f t="shared" si="58"/>
         <v>-</v>
       </c>
-      <c r="M225" t="s">
-        <v>204</v>
+      <c r="M225" s="4" t="s">
+        <v>200</v>
       </c>
       <c r="R225" t="s">
         <v>209</v>
@@ -11186,13 +11282,13 @@
         <v>5</v>
       </c>
       <c r="C226" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E226" t="s">
         <v>16</v>
       </c>
       <c r="H226" s="2">
-        <v>45343</v>
+        <v>45349</v>
       </c>
       <c r="I226" s="4">
         <f t="shared" ca="1" si="56"/>
@@ -11200,17 +11296,17 @@
       </c>
       <c r="J226" s="4">
         <f t="shared" ca="1" si="57"/>
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="L226" s="4" t="str">
         <f t="shared" si="58"/>
         <v>-</v>
       </c>
       <c r="M226" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="R226" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="227" spans="2:18" x14ac:dyDescent="0.3">
@@ -11218,31 +11314,31 @@
         <v>5</v>
       </c>
       <c r="C227" t="s">
-        <v>128</v>
-      </c>
-      <c r="E227" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E227" t="s">
         <v>16</v>
       </c>
       <c r="H227" s="2">
-        <v>45343</v>
+        <v>45349</v>
       </c>
       <c r="I227" s="4">
-        <f t="shared" ca="1" si="56"/>
+        <f t="shared" ref="I227:I230" ca="1" si="59">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H227), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H227), 7), "-")</f>
         <v>1</v>
       </c>
       <c r="J227" s="4">
-        <f t="shared" ca="1" si="57"/>
-        <v>12</v>
+        <f t="shared" ref="J227:J230" ca="1" si="60">IF(_xlfn.DAYS(TODAY(),H227)&lt;10000, _xlfn.DAYS(TODAY(),H227), "-")</f>
+        <v>7</v>
       </c>
       <c r="L227" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" ref="L227:L230" si="61">IF(_xlfn.DAYS(K227,H227)&gt;0, _xlfn.DAYS(K227,H227), "-")</f>
         <v>-</v>
       </c>
       <c r="M227" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="R227" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="228" spans="2:18" x14ac:dyDescent="0.3">
@@ -11250,31 +11346,31 @@
         <v>5</v>
       </c>
       <c r="C228" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E228" t="s">
         <v>16</v>
       </c>
       <c r="H228" s="2">
-        <v>45343</v>
+        <v>45349</v>
       </c>
       <c r="I228" s="4">
-        <f t="shared" ca="1" si="56"/>
+        <f t="shared" ca="1" si="59"/>
         <v>1</v>
       </c>
       <c r="J228" s="4">
-        <f t="shared" ca="1" si="57"/>
-        <v>12</v>
+        <f t="shared" ca="1" si="60"/>
+        <v>7</v>
       </c>
       <c r="L228" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="61"/>
         <v>-</v>
       </c>
       <c r="M228" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="R228" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="229" spans="2:18" x14ac:dyDescent="0.3">
@@ -11282,323 +11378,67 @@
         <v>5</v>
       </c>
       <c r="C229" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E229" t="s">
         <v>16</v>
       </c>
       <c r="H229" s="2">
-        <v>45343</v>
+        <v>45349</v>
       </c>
       <c r="I229" s="4">
-        <f t="shared" ca="1" si="56"/>
+        <f t="shared" ca="1" si="59"/>
         <v>1</v>
       </c>
       <c r="J229" s="4">
-        <f t="shared" ca="1" si="57"/>
-        <v>12</v>
+        <f t="shared" ca="1" si="60"/>
+        <v>7</v>
       </c>
       <c r="L229" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="61"/>
         <v>-</v>
       </c>
       <c r="M229" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="R229" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="230" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B230" t="s">
-        <v>5</v>
+        <v>244</v>
       </c>
       <c r="C230" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E230" t="s">
-        <v>16</v>
+        <v>245</v>
       </c>
       <c r="H230" s="2">
-        <v>45343</v>
+        <v>45355</v>
       </c>
       <c r="I230" s="4">
-        <f t="shared" ca="1" si="56"/>
-        <v>1</v>
-      </c>
-      <c r="J230" s="4">
-        <f t="shared" ca="1" si="57"/>
-        <v>12</v>
-      </c>
-      <c r="L230" s="4" t="str">
-        <f t="shared" si="58"/>
-        <v>-</v>
-      </c>
-      <c r="M230" t="s">
-        <v>205</v>
-      </c>
-      <c r="R230" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="231" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B231" t="s">
-        <v>5</v>
-      </c>
-      <c r="C231" t="s">
-        <v>128</v>
-      </c>
-      <c r="E231" t="s">
-        <v>16</v>
-      </c>
-      <c r="H231" s="2">
-        <v>45343</v>
-      </c>
-      <c r="I231" s="4">
-        <f t="shared" ca="1" si="56"/>
-        <v>1</v>
-      </c>
-      <c r="J231" s="4">
-        <f t="shared" ca="1" si="57"/>
-        <v>12</v>
-      </c>
-      <c r="L231" s="4" t="str">
-        <f t="shared" si="58"/>
-        <v>-</v>
-      </c>
-      <c r="M231" t="s">
-        <v>205</v>
-      </c>
-      <c r="R231" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="232" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B232" t="s">
-        <v>5</v>
-      </c>
-      <c r="C232" t="s">
-        <v>112</v>
-      </c>
-      <c r="E232" t="s">
-        <v>16</v>
-      </c>
-      <c r="H232" s="2">
-        <v>45337</v>
-      </c>
-      <c r="I232" s="4">
-        <f t="shared" ca="1" si="56"/>
-        <v>2</v>
-      </c>
-      <c r="J232" s="4">
-        <f t="shared" ca="1" si="57"/>
-        <v>18</v>
-      </c>
-      <c r="L232" s="4" t="str">
-        <f t="shared" si="58"/>
-        <v>-</v>
-      </c>
-      <c r="M232" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="R232" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="233" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B233" t="s">
-        <v>5</v>
-      </c>
-      <c r="C233" t="s">
-        <v>112</v>
-      </c>
-      <c r="E233" t="s">
-        <v>16</v>
-      </c>
-      <c r="H233" s="2">
-        <v>45337</v>
-      </c>
-      <c r="I233" s="4">
-        <f t="shared" ca="1" si="56"/>
-        <v>2</v>
-      </c>
-      <c r="J233" s="4">
-        <f t="shared" ca="1" si="57"/>
-        <v>18</v>
-      </c>
-      <c r="L233" s="4" t="str">
-        <f t="shared" si="58"/>
-        <v>-</v>
-      </c>
-      <c r="M233" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="R233" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="234" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B234" t="s">
-        <v>5</v>
-      </c>
-      <c r="C234" t="s">
-        <v>112</v>
-      </c>
-      <c r="E234" t="s">
-        <v>16</v>
-      </c>
-      <c r="H234" s="2">
-        <v>45337</v>
-      </c>
-      <c r="I234" s="4">
-        <f t="shared" ca="1" si="56"/>
-        <v>2</v>
-      </c>
-      <c r="J234" s="4">
-        <f t="shared" ca="1" si="57"/>
-        <v>18</v>
-      </c>
-      <c r="L234" s="4" t="str">
-        <f t="shared" si="58"/>
-        <v>-</v>
-      </c>
-      <c r="M234" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="R234" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="235" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B235" t="s">
-        <v>5</v>
-      </c>
-      <c r="C235" t="s">
-        <v>128</v>
-      </c>
-      <c r="E235" t="s">
-        <v>16</v>
-      </c>
-      <c r="H235" s="2">
-        <v>45349</v>
-      </c>
-      <c r="I235" s="4">
-        <f t="shared" ca="1" si="56"/>
-        <v>0</v>
-      </c>
-      <c r="J235" s="4">
-        <f t="shared" ca="1" si="57"/>
-        <v>6</v>
-      </c>
-      <c r="L235" s="4" t="str">
-        <f t="shared" si="58"/>
-        <v>-</v>
-      </c>
-      <c r="M235" t="s">
-        <v>208</v>
-      </c>
-      <c r="R235" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="236" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B236" t="s">
-        <v>5</v>
-      </c>
-      <c r="C236" t="s">
-        <v>128</v>
-      </c>
-      <c r="E236" t="s">
-        <v>16</v>
-      </c>
-      <c r="H236" s="2">
-        <v>45349</v>
-      </c>
-      <c r="I236" s="4">
-        <f t="shared" ref="I236:I238" ca="1" si="59">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H236), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H236), 7), "-")</f>
-        <v>0</v>
-      </c>
-      <c r="J236" s="4">
-        <f t="shared" ref="J236:J238" ca="1" si="60">IF(_xlfn.DAYS(TODAY(),H236)&lt;10000, _xlfn.DAYS(TODAY(),H236), "-")</f>
-        <v>6</v>
-      </c>
-      <c r="L236" s="4" t="str">
-        <f t="shared" ref="L236:L238" si="61">IF(_xlfn.DAYS(K236,H236)&gt;0, _xlfn.DAYS(K236,H236), "-")</f>
-        <v>-</v>
-      </c>
-      <c r="M236" t="s">
-        <v>208</v>
-      </c>
-      <c r="R236" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="237" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B237" t="s">
-        <v>5</v>
-      </c>
-      <c r="C237" t="s">
-        <v>128</v>
-      </c>
-      <c r="E237" t="s">
-        <v>16</v>
-      </c>
-      <c r="H237" s="2">
-        <v>45349</v>
-      </c>
-      <c r="I237" s="4">
         <f t="shared" ca="1" si="59"/>
         <v>0</v>
       </c>
-      <c r="J237" s="4">
+      <c r="J230" s="4">
         <f t="shared" ca="1" si="60"/>
-        <v>6</v>
-      </c>
-      <c r="L237" s="4" t="str">
+        <v>1</v>
+      </c>
+      <c r="L230" s="4" t="str">
         <f t="shared" si="61"/>
         <v>-</v>
       </c>
-      <c r="M237" t="s">
-        <v>208</v>
-      </c>
-      <c r="R237" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="238" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B238" t="s">
-        <v>5</v>
-      </c>
-      <c r="C238" t="s">
-        <v>128</v>
-      </c>
-      <c r="E238" t="s">
-        <v>16</v>
-      </c>
-      <c r="H238" s="2">
-        <v>45349</v>
-      </c>
-      <c r="I238" s="4">
-        <f t="shared" ca="1" si="59"/>
-        <v>0</v>
-      </c>
-      <c r="J238" s="4">
-        <f t="shared" ca="1" si="60"/>
-        <v>6</v>
-      </c>
-      <c r="L238" s="4" t="str">
-        <f t="shared" si="61"/>
-        <v>-</v>
-      </c>
-      <c r="M238" t="s">
-        <v>208</v>
-      </c>
-      <c r="R238" t="s">
-        <v>209</v>
+      <c r="M230" t="s">
+        <v>246</v>
+      </c>
+      <c r="Q230" t="s">
+        <v>247</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B1:R238" xr:uid="{8D08DEC4-803F-4130-9E5E-30A83401A29D}">
+  <autoFilter ref="B1:R230" xr:uid="{8D08DEC4-803F-4130-9E5E-30A83401A29D}">
     <filterColumn colId="0">
       <filters>
         <filter val="SPF"/>
@@ -11609,7 +11449,7 @@
     </filterColumn>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="M152:M155 M235:M1048576 M157 M159 M161:M169 M172:M233 M31:M41 M43:M123 M1:M27 M125:M126 M128:M129 M131 M133:M150">
+  <conditionalFormatting sqref="M152:M155 M226:M1048576 M157 M159 M161:M169 M31:M41 M43:M123 M1:M27 M125:M126 M128:M129 M131 M133:M150 M172:M224">
     <cfRule type="containsText" dxfId="39" priority="43" operator="containsText" text=".X">
       <formula>NOT(ISERROR(SEARCH(".X",M1)))</formula>
     </cfRule>
@@ -11625,12 +11465,12 @@
       <formula>NOT(ISERROR(SEARCH(".B",M151)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M234">
+  <conditionalFormatting sqref="M225">
     <cfRule type="containsText" dxfId="35" priority="39" operator="containsText" text=".X">
-      <formula>NOT(ISERROR(SEARCH(".X",M234)))</formula>
+      <formula>NOT(ISERROR(SEARCH(".X",M225)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="34" priority="40" operator="containsText" text=".B">
-      <formula>NOT(ISERROR(SEARCH(".B",M234)))</formula>
+      <formula>NOT(ISERROR(SEARCH(".B",M225)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M156">
@@ -11770,7 +11610,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E154:E156 E145:E147 E228:E1048576 E158:E188 E222:E226 E190:E220 E1:E138" xr:uid="{939E2B39-E841-4A9F-AD11-00C266DB2690}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E154:E156 E145:E147 E222:E1048576 E1:E138 E158:E188 E219:E220 E190:E217" xr:uid="{939E2B39-E841-4A9F-AD11-00C266DB2690}">
       <formula1>"Y, N"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1:G1048576" xr:uid="{2DE54AC7-5B92-48D6-98C4-E6203F87CDD0}">
@@ -11801,10 +11641,10 @@
       <c r="E2" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="21" t="s">
+      <c r="G2" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="H2" s="21"/>
+      <c r="H2" s="20"/>
     </row>
     <row r="3" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C3" t="s">
@@ -11866,7 +11706,7 @@
       <c r="C7" s="2"/>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="20">
+      <c r="B8" s="19">
         <v>45313</v>
       </c>
       <c r="C8" s="2">
@@ -11901,50 +11741,50 @@
       <c r="A6">
         <v>1</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="18" t="s">
-        <v>186</v>
-      </c>
-      <c r="D6" s="18" t="s">
-        <v>195</v>
-      </c>
-      <c r="E6" s="18" t="s">
-        <v>194</v>
+      <c r="C6" s="17" t="s">
+        <v>184</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>2</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="C7" s="18" t="s">
-        <v>186</v>
-      </c>
-      <c r="D7" s="18" t="s">
-        <v>193</v>
-      </c>
-      <c r="E7" s="18" t="s">
-        <v>192</v>
+      <c r="C7" s="17" t="s">
+        <v>184</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>191</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>3</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="19" t="s">
-        <v>186</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>187</v>
-      </c>
-      <c r="E8" s="19">
+      <c r="C8" s="18" t="s">
+        <v>184</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>185</v>
+      </c>
+      <c r="E8" s="18">
         <v>17</v>
       </c>
     </row>
@@ -11956,19 +11796,19 @@
         <v>90</v>
       </c>
       <c r="C9" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D9" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E9">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G9" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -11979,10 +11819,10 @@
         <v>91</v>
       </c>
       <c r="C10" t="s">
+        <v>184</v>
+      </c>
+      <c r="D10" t="s">
         <v>186</v>
-      </c>
-      <c r="D10" t="s">
-        <v>188</v>
       </c>
       <c r="E10">
         <v>8</v>
@@ -11993,13 +11833,13 @@
         <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C11" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D11" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E11">
         <v>4</v>
@@ -12010,78 +11850,78 @@
         <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C12" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D12" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E12">
         <v>4</v>
       </c>
       <c r="F12" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G12" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>8</v>
       </c>
-      <c r="B14" s="19" t="s">
-        <v>140</v>
-      </c>
-      <c r="C14" s="19" t="s">
-        <v>181</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>182</v>
+      <c r="B14" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>179</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>9</v>
       </c>
-      <c r="B15" s="19" t="s">
-        <v>142</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>181</v>
-      </c>
-      <c r="D15" s="19" t="s">
-        <v>182</v>
+      <c r="B15" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>179</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>10</v>
       </c>
-      <c r="B16" s="18" t="s">
-        <v>141</v>
-      </c>
-      <c r="C16" s="18" t="s">
-        <v>181</v>
-      </c>
-      <c r="D16" s="18" t="s">
-        <v>180</v>
+      <c r="B16" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>179</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>11</v>
       </c>
-      <c r="B17" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="C17" s="18" t="s">
-        <v>181</v>
-      </c>
-      <c r="D17" s="18" t="s">
-        <v>180</v>
+      <c r="B17" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>179</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>178</v>
       </c>
     </row>
   </sheetData>

--- a/Mouse 내역.xlsx
+++ b/Mouse 내역.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\heung\Dropbox\02. Lab. of Host Defenses\03. 동물실\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C792697-D542-44CD-8744-711FBCE0963E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F2D288F-A971-4D9C-9BC9-73619A284476}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="495" windowWidth="28800" windowHeight="16245" xr2:uid="{5A73A69A-2AFB-4F3E-AC64-070DD7700CB2}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <sheet name="Sheet1 (2)" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$R$255</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$R$263</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1710" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1804" uniqueCount="277">
   <si>
     <t>Strain</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -805,14 +805,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>A3.1.X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>G3.1.X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Exp. 1-10-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -926,10 +918,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>죽이기 (새끼 있어서 못죽임)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>H6.1.F</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -986,10 +974,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>H10.B cage가 없는데? 확인 필요. 여러마리 있으니 일주일 정도 후에 개체수 확인</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>genotyping</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1082,7 +1066,59 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>.</t>
+    <t>Exp. 4-4-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A3.2.M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A3.2.F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>genotyping</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>G3.1.F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cre/+; f/f</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>+/+; f/f</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>H10.B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>H9.2.X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>N</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>개체수 확인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>weaning, genotyping</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2439,7 +2475,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D71A6DC-E91C-489F-8F50-989C4712FA7C}">
   <sheetPr filterMode="1"/>
-  <dimension ref="B1:R255"/>
+  <dimension ref="B1:R263"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="10.5" customWidth="1"/>
@@ -2488,7 +2524,7 @@
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="L1" s="8" t="s">
         <v>14</v>
@@ -2506,10 +2542,10 @@
         <v>60</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="R1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="2" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -2537,7 +2573,7 @@
       </c>
       <c r="J2" s="4">
         <f ca="1">IF(_xlfn.DAYS(TODAY(),H2)&lt;10000, _xlfn.DAYS(TODAY(),H2), "-")</f>
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L2" s="4" t="str">
         <f t="shared" ref="L2:L29" si="0">IF(_xlfn.DAYS(K2,H2)&gt;0, _xlfn.DAYS(K2,H2), "-")</f>
@@ -2577,7 +2613,7 @@
       </c>
       <c r="J3" s="4">
         <f t="shared" ref="J3:J29" ca="1" si="2">IF(_xlfn.DAYS(TODAY(),H3)&lt;10000, _xlfn.DAYS(TODAY(),H3), "-")</f>
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L3" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2592,7 +2628,7 @@
       </c>
       <c r="P3"/>
       <c r="Q3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="4" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -2620,7 +2656,7 @@
       </c>
       <c r="J4" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L4" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2635,7 +2671,7 @@
       </c>
       <c r="P4"/>
       <c r="Q4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -2662,11 +2698,11 @@
       </c>
       <c r="I5" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J5" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K5" s="2">
         <v>45293</v>
@@ -2708,11 +2744,11 @@
       </c>
       <c r="I6" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J6" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K6" s="2">
         <v>45293</v>
@@ -2757,11 +2793,11 @@
       </c>
       <c r="I7" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J7" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K7" s="2">
         <v>45293</v>
@@ -2801,11 +2837,11 @@
       </c>
       <c r="I8" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J8" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K8" s="2">
         <v>45293</v>
@@ -2847,11 +2883,11 @@
       </c>
       <c r="I9" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J9" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K9" s="2">
         <v>45293</v>
@@ -2894,7 +2930,7 @@
       </c>
       <c r="J10" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L10" s="4" t="str">
         <f t="shared" si="0"/>
@@ -3011,7 +3047,7 @@
       </c>
       <c r="J13" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L13" s="4" t="str">
         <f t="shared" si="0"/>
@@ -3026,7 +3062,7 @@
       </c>
       <c r="P13"/>
       <c r="Q13" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="14" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -3057,7 +3093,7 @@
       </c>
       <c r="J14" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L14" s="4" t="str">
         <f t="shared" si="0"/>
@@ -3072,7 +3108,7 @@
       </c>
       <c r="P14"/>
       <c r="Q14" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="15" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -3103,7 +3139,7 @@
       </c>
       <c r="J15" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L15" s="4" t="str">
         <f t="shared" si="0"/>
@@ -3117,7 +3153,7 @@
       </c>
       <c r="P15"/>
       <c r="Q15" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="16" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -3148,7 +3184,7 @@
       </c>
       <c r="J16" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L16" s="4" t="str">
         <f t="shared" si="0"/>
@@ -3190,7 +3226,7 @@
       </c>
       <c r="J17" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L17" s="4" t="str">
         <f t="shared" si="0"/>
@@ -3204,7 +3240,7 @@
       </c>
       <c r="P17"/>
       <c r="Q17" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="18" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -3228,11 +3264,11 @@
       </c>
       <c r="I18" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J18" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L18" s="4" t="str">
         <f t="shared" si="0"/>
@@ -3307,7 +3343,7 @@
       </c>
       <c r="J20" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K20" s="2">
         <v>45112</v>
@@ -3345,11 +3381,11 @@
       </c>
       <c r="I21" s="4">
         <f ca="1">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H21), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H21), 7), "-")</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J21" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K21" s="2">
         <v>45176</v>
@@ -3390,11 +3426,11 @@
       </c>
       <c r="I22" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J22" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K22" s="2">
         <v>45176</v>
@@ -3435,11 +3471,11 @@
       </c>
       <c r="I23" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J23" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K23" s="2">
         <v>45176</v>
@@ -3480,11 +3516,11 @@
       </c>
       <c r="I24" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J24" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K24" s="2">
         <v>45229</v>
@@ -3522,11 +3558,11 @@
       </c>
       <c r="I25" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J25" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K25" s="2">
         <v>45229</v>
@@ -3564,11 +3600,11 @@
       </c>
       <c r="I26" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J26" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K26" s="2">
         <v>45229</v>
@@ -3582,7 +3618,7 @@
       </c>
       <c r="P26"/>
       <c r="Q26" s="2" t="s">
-        <v>228</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="2:17" x14ac:dyDescent="0.3">
@@ -3606,11 +3642,11 @@
       </c>
       <c r="I27" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J27" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K27" s="2">
         <v>45229</v>
@@ -3624,7 +3660,7 @@
       </c>
       <c r="P27"/>
       <c r="Q27" s="2" t="s">
-        <v>228</v>
+        <v>171</v>
       </c>
     </row>
     <row r="28" spans="2:17" x14ac:dyDescent="0.3">
@@ -3651,11 +3687,11 @@
       </c>
       <c r="I28" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J28" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K28" s="2">
         <v>45293</v>
@@ -3698,7 +3734,7 @@
       </c>
       <c r="J29" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K29" s="2">
         <v>45315</v>
@@ -3734,11 +3770,11 @@
       </c>
       <c r="I30" s="4">
         <f t="shared" ref="I30" ca="1" si="3">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H30), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H30), 7), "-")</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J30" s="4">
         <f t="shared" ref="J30" ca="1" si="4">IF(_xlfn.DAYS(TODAY(),H30)&lt;10000, _xlfn.DAYS(TODAY(),H30), "-")</f>
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K30" s="2">
         <v>45176</v>
@@ -3755,7 +3791,7 @@
       </c>
       <c r="P30"/>
       <c r="Q30" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="31" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -3779,11 +3815,11 @@
       </c>
       <c r="I31" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J31" s="4">
         <f t="shared" ref="J31:J37" ca="1" si="6">IF(_xlfn.DAYS(TODAY(),H31)&lt;10000, _xlfn.DAYS(TODAY(),H31), "-")</f>
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K31" s="2">
         <v>45229</v>
@@ -3800,7 +3836,7 @@
       </c>
       <c r="P31"/>
       <c r="Q31" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="32" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -3863,11 +3899,11 @@
       </c>
       <c r="I33" s="4">
         <f ca="1">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H33), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H33), 7), "-")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J33" s="4">
         <f ca="1">IF(_xlfn.DAYS(TODAY(),H33)&lt;10000, _xlfn.DAYS(TODAY(),H33), "-")</f>
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K33" s="2">
         <v>45257</v>
@@ -3989,11 +4025,11 @@
       </c>
       <c r="I36" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J36" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K36" s="2">
         <v>45257</v>
@@ -4037,11 +4073,11 @@
       </c>
       <c r="I37" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J37" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K37" s="2">
         <v>45257</v>
@@ -4085,11 +4121,11 @@
       </c>
       <c r="I38" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J38" s="4">
         <f t="shared" ref="J38:J40" ca="1" si="8">IF(_xlfn.DAYS(TODAY(),H38)&lt;10000, _xlfn.DAYS(TODAY(),H38), "-")</f>
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K38" s="2">
         <v>45257</v>
@@ -4133,11 +4169,11 @@
       </c>
       <c r="I39" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J39" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K39" s="2">
         <v>45257</v>
@@ -4178,11 +4214,11 @@
       </c>
       <c r="I40" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J40" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K40" s="2">
         <v>45257</v>
@@ -4227,7 +4263,7 @@
       </c>
       <c r="J41" s="4">
         <f t="shared" ref="J41:J42" ca="1" si="9">IF(_xlfn.DAYS(TODAY(),H41)&lt;10000, _xlfn.DAYS(TODAY(),H41), "-")</f>
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L41" s="4" t="str">
         <f t="shared" si="7"/>
@@ -4262,11 +4298,11 @@
       </c>
       <c r="I42" s="4">
         <f t="shared" ref="I42" ca="1" si="10">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H42), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H42), 7), "-")</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J42" s="4">
         <f t="shared" ca="1" si="9"/>
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K42" s="2">
         <v>45176</v>
@@ -4283,7 +4319,7 @@
       </c>
       <c r="P42"/>
       <c r="Q42" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="43" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -4314,7 +4350,7 @@
       </c>
       <c r="J43" s="4">
         <f t="shared" ref="J43:J94" ca="1" si="11">IF(_xlfn.DAYS(TODAY(),H43)&lt;10000, _xlfn.DAYS(TODAY(),H43), "-")</f>
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L43" s="4" t="str">
         <f t="shared" si="7"/>
@@ -4328,7 +4364,7 @@
       </c>
       <c r="P43"/>
       <c r="Q43" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="44" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -4359,7 +4395,7 @@
       </c>
       <c r="J44" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K44" s="2">
         <v>45293</v>
@@ -4404,7 +4440,7 @@
       </c>
       <c r="J45" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K45" s="2">
         <v>45293</v>
@@ -4449,7 +4485,7 @@
       </c>
       <c r="J46" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K46" s="2">
         <v>45293</v>
@@ -4497,7 +4533,7 @@
       </c>
       <c r="J47" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K47" s="2">
         <v>45293</v>
@@ -4545,7 +4581,7 @@
       </c>
       <c r="J48" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K48" s="2">
         <v>45293</v>
@@ -4593,7 +4629,7 @@
       </c>
       <c r="J49" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K49" s="2">
         <v>45293</v>
@@ -4610,7 +4646,7 @@
       </c>
       <c r="P49"/>
       <c r="Q49" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="50" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -4641,7 +4677,7 @@
       </c>
       <c r="J50" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K50" s="2">
         <v>45293</v>
@@ -4658,7 +4694,7 @@
       </c>
       <c r="P50"/>
       <c r="Q50" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="51" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -4689,7 +4725,7 @@
       </c>
       <c r="J51" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K51" s="2">
         <v>45293</v>
@@ -4734,7 +4770,7 @@
       </c>
       <c r="J52" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K52" s="2">
         <v>45293</v>
@@ -4779,7 +4815,7 @@
       </c>
       <c r="J53" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K53" s="2">
         <v>45293</v>
@@ -4796,7 +4832,7 @@
       </c>
       <c r="P53"/>
       <c r="Q53" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="54" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -4827,7 +4863,7 @@
       </c>
       <c r="J54" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K54" s="2">
         <v>45238</v>
@@ -4875,7 +4911,7 @@
       </c>
       <c r="J55" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K55" s="2">
         <v>45238</v>
@@ -4892,7 +4928,7 @@
       </c>
       <c r="P55"/>
       <c r="Q55" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="56" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -4923,7 +4959,7 @@
       </c>
       <c r="J56" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K56" s="2">
         <v>45238</v>
@@ -4940,7 +4976,7 @@
       </c>
       <c r="P56"/>
       <c r="Q56" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="57" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -4964,11 +5000,11 @@
       </c>
       <c r="I57" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J57" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L57" s="4" t="str">
         <f t="shared" si="7"/>
@@ -4982,7 +5018,7 @@
       </c>
       <c r="P57"/>
       <c r="Q57" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="58" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -5006,11 +5042,11 @@
       </c>
       <c r="I58" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J58" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L58" s="4" t="str">
         <f t="shared" si="7"/>
@@ -5024,7 +5060,7 @@
       </c>
       <c r="P58"/>
       <c r="Q58" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="59" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -5049,7 +5085,7 @@
       </c>
       <c r="J59" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K59" s="2">
         <v>45295</v>
@@ -5087,11 +5123,11 @@
       </c>
       <c r="I60" s="4">
         <f t="shared" ref="I60:I61" ca="1" si="12">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H60), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H60), 7), "-")</f>
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J60" s="4">
         <f t="shared" ref="J60:J61" ca="1" si="13">IF(_xlfn.DAYS(TODAY(),H60)&lt;10000, _xlfn.DAYS(TODAY(),H60), "-")</f>
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L60" s="4" t="str">
         <f t="shared" ref="L60:L61" si="14">IF(_xlfn.DAYS(K60,H60)&gt;0, _xlfn.DAYS(K60,H60), "-")</f>
@@ -5101,7 +5137,7 @@
         <v>42</v>
       </c>
       <c r="Q60" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
     </row>
     <row r="61" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -5125,11 +5161,11 @@
       </c>
       <c r="I61" s="4">
         <f t="shared" ca="1" si="12"/>
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J61" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L61" s="4" t="str">
         <f t="shared" si="14"/>
@@ -5139,7 +5175,7 @@
         <v>42</v>
       </c>
       <c r="Q61" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
     </row>
     <row r="62" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -5152,6 +5188,9 @@
       <c r="E62" t="s">
         <v>26</v>
       </c>
+      <c r="F62" s="14" t="s">
+        <v>97</v>
+      </c>
       <c r="G62" t="s">
         <v>88</v>
       </c>
@@ -5164,7 +5203,7 @@
       </c>
       <c r="J62" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K62" s="2">
         <v>45295</v>
@@ -5174,10 +5213,10 @@
         <v>28</v>
       </c>
       <c r="M62" s="4" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="R62" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="63" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -5190,6 +5229,9 @@
       <c r="E63" t="s">
         <v>16</v>
       </c>
+      <c r="F63" s="14" t="s">
+        <v>97</v>
+      </c>
       <c r="G63" t="s">
         <v>13</v>
       </c>
@@ -5202,7 +5244,7 @@
       </c>
       <c r="J63" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K63" s="7">
         <v>45324</v>
@@ -5212,10 +5254,10 @@
         <v>24</v>
       </c>
       <c r="M63" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="R63" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
     </row>
     <row r="64" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -5228,6 +5270,9 @@
       <c r="E64" t="s">
         <v>16</v>
       </c>
+      <c r="F64" s="14" t="s">
+        <v>97</v>
+      </c>
       <c r="G64" t="s">
         <v>13</v>
       </c>
@@ -5240,7 +5285,7 @@
       </c>
       <c r="J64" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K64" s="7">
         <v>45324</v>
@@ -5250,10 +5295,10 @@
         <v>24</v>
       </c>
       <c r="M64" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="R64" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
     </row>
     <row r="65" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -5266,6 +5311,9 @@
       <c r="E65" t="s">
         <v>26</v>
       </c>
+      <c r="F65" s="14" t="s">
+        <v>97</v>
+      </c>
       <c r="G65" t="s">
         <v>88</v>
       </c>
@@ -5278,7 +5326,7 @@
       </c>
       <c r="J65" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K65" s="2">
         <v>45295</v>
@@ -5288,10 +5336,10 @@
         <v>28</v>
       </c>
       <c r="M65" s="4" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="R65" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="66" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -5316,7 +5364,7 @@
       </c>
       <c r="J66" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K66" s="2">
         <v>45295</v>
@@ -5333,7 +5381,7 @@
       </c>
       <c r="P66"/>
       <c r="Q66" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="67" spans="2:18" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
@@ -5359,7 +5407,7 @@
       </c>
       <c r="J67" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K67" s="7">
         <v>45295</v>
@@ -5376,7 +5424,7 @@
         <v>45345</v>
       </c>
       <c r="Q67" s="4" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="68" spans="2:18" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
@@ -5402,7 +5450,7 @@
       </c>
       <c r="J68" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K68" s="7">
         <v>45295</v>
@@ -5419,7 +5467,7 @@
         <v>45345</v>
       </c>
       <c r="Q68" s="4" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="69" spans="2:18" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
@@ -5433,7 +5481,9 @@
       <c r="E69" t="s">
         <v>16</v>
       </c>
-      <c r="F69" s="5"/>
+      <c r="F69" s="14" t="s">
+        <v>97</v>
+      </c>
       <c r="G69" t="s">
         <v>13</v>
       </c>
@@ -5446,7 +5496,7 @@
       </c>
       <c r="J69" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K69" s="7">
         <v>45324</v>
@@ -5456,14 +5506,14 @@
         <v>24</v>
       </c>
       <c r="M69" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" s="5"/>
       <c r="Q69"/>
       <c r="R69" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
     </row>
     <row r="70" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -5490,11 +5540,11 @@
       </c>
       <c r="I70" s="4">
         <f t="shared" ref="I70:I94" ca="1" si="15">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H70), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H70), 7), "-")</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J70" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L70" s="4" t="str">
         <f t="shared" si="7"/>
@@ -5538,11 +5588,11 @@
       </c>
       <c r="I71" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J71" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L71" s="4" t="str">
         <f t="shared" si="7"/>
@@ -5586,11 +5636,11 @@
       </c>
       <c r="I72" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J72" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L72" s="4" t="str">
         <f t="shared" si="7"/>
@@ -5634,11 +5684,11 @@
       </c>
       <c r="I73" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J73" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L73" s="4" t="str">
         <f t="shared" si="7"/>
@@ -5682,11 +5732,11 @@
       </c>
       <c r="I74" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J74" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L74" s="4" t="str">
         <f t="shared" si="7"/>
@@ -5730,11 +5780,11 @@
       </c>
       <c r="I75" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J75" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L75" s="4" t="str">
         <f t="shared" si="7"/>
@@ -5778,11 +5828,11 @@
       </c>
       <c r="I76" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J76" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L76" s="4" t="str">
         <f t="shared" si="7"/>
@@ -5826,11 +5876,11 @@
       </c>
       <c r="I77" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J77" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L77" s="4" t="str">
         <f t="shared" si="7"/>
@@ -5874,11 +5924,11 @@
       </c>
       <c r="I78" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J78" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L78" s="4" t="str">
         <f t="shared" si="7"/>
@@ -5922,11 +5972,11 @@
       </c>
       <c r="I79" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J79" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L79" s="4" t="str">
         <f t="shared" si="7"/>
@@ -5970,11 +6020,11 @@
       </c>
       <c r="I80" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J80" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L80" s="4" t="str">
         <f t="shared" si="7"/>
@@ -6018,11 +6068,11 @@
       </c>
       <c r="I81" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J81" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L81" s="4" t="str">
         <f t="shared" si="7"/>
@@ -6066,11 +6116,11 @@
       </c>
       <c r="I82" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J82" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L82" s="4" t="str">
         <f t="shared" si="7"/>
@@ -6114,11 +6164,11 @@
       </c>
       <c r="I83" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J83" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L83" s="4" t="str">
         <f t="shared" si="7"/>
@@ -6162,11 +6212,11 @@
       </c>
       <c r="I84" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J84" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L84" s="4" t="str">
         <f t="shared" si="7"/>
@@ -6210,11 +6260,11 @@
       </c>
       <c r="I85" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J85" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L85" s="4" t="str">
         <f t="shared" si="7"/>
@@ -6258,11 +6308,11 @@
       </c>
       <c r="I86" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J86" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L86" s="4" t="str">
         <f t="shared" si="7"/>
@@ -6306,11 +6356,11 @@
       </c>
       <c r="I87" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J87" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L87" s="4" t="str">
         <f t="shared" si="7"/>
@@ -6354,11 +6404,11 @@
       </c>
       <c r="I88" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J88" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L88" s="4" t="str">
         <f t="shared" si="7"/>
@@ -6402,11 +6452,11 @@
       </c>
       <c r="I89" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J89" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L89" s="4" t="str">
         <f t="shared" si="7"/>
@@ -6450,11 +6500,11 @@
       </c>
       <c r="I90" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J90" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K90" s="2">
         <v>45272</v>
@@ -6498,11 +6548,11 @@
       </c>
       <c r="I91" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J91" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K91" s="2">
         <v>45273</v>
@@ -6546,11 +6596,11 @@
       </c>
       <c r="I92" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J92" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K92" s="2">
         <v>45274</v>
@@ -6594,11 +6644,11 @@
       </c>
       <c r="I93" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J93" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K93" s="2">
         <v>45275</v>
@@ -6642,11 +6692,11 @@
       </c>
       <c r="I94" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J94" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K94" s="2">
         <v>45276</v>
@@ -6690,11 +6740,11 @@
       </c>
       <c r="I95" s="4">
         <f t="shared" ref="I95:I96" ca="1" si="16">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H95), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H95), 7), "-")</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J95" s="4">
         <f t="shared" ref="J95:J96" ca="1" si="17">IF(_xlfn.DAYS(TODAY(),H95)&lt;10000, _xlfn.DAYS(TODAY(),H95), "-")</f>
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K95" s="2">
         <v>45277</v>
@@ -6738,11 +6788,11 @@
       </c>
       <c r="I96" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J96" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K96" s="2">
         <v>45278</v>
@@ -6790,7 +6840,7 @@
       </c>
       <c r="J97" s="4">
         <f t="shared" ref="J97" ca="1" si="19">IF(_xlfn.DAYS(TODAY(),H97)&lt;10000, _xlfn.DAYS(TODAY(),H97), "-")</f>
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K97" s="2">
         <v>45223</v>
@@ -6838,7 +6888,7 @@
       </c>
       <c r="J98" s="4">
         <f t="shared" ref="J98:J120" ca="1" si="21">IF(_xlfn.DAYS(TODAY(),H98)&lt;10000, _xlfn.DAYS(TODAY(),H98), "-")</f>
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K98" s="2">
         <v>45223</v>
@@ -6886,7 +6936,7 @@
       </c>
       <c r="J99" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K99" s="2">
         <v>45223</v>
@@ -6934,7 +6984,7 @@
       </c>
       <c r="J100" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K100" s="2">
         <v>45223</v>
@@ -6982,7 +7032,7 @@
       </c>
       <c r="J101" s="4">
         <f t="shared" ref="J101:J110" ca="1" si="24">IF(_xlfn.DAYS(TODAY(),H101)&lt;10000, _xlfn.DAYS(TODAY(),H101), "-")</f>
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K101" s="2">
         <v>45267</v>
@@ -7033,7 +7083,7 @@
       </c>
       <c r="J102" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K102" s="2">
         <v>45267</v>
@@ -7084,7 +7134,7 @@
       </c>
       <c r="J103" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K103" s="2">
         <v>45267</v>
@@ -7135,7 +7185,7 @@
       </c>
       <c r="J104" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K104" s="2">
         <v>45267</v>
@@ -7186,7 +7236,7 @@
       </c>
       <c r="J105" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K105" s="2">
         <v>45267</v>
@@ -7237,7 +7287,7 @@
       </c>
       <c r="J106" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K106" s="2">
         <v>45267</v>
@@ -7288,7 +7338,7 @@
       </c>
       <c r="J107" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K107" s="2">
         <v>45267</v>
@@ -7339,7 +7389,7 @@
       </c>
       <c r="J108" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K108" s="2">
         <v>45267</v>
@@ -7390,7 +7440,7 @@
       </c>
       <c r="J109" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K109" s="2">
         <v>45267</v>
@@ -7441,7 +7491,7 @@
       </c>
       <c r="J110" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K110" s="2">
         <v>45267</v>
@@ -7963,7 +8013,7 @@
       </c>
       <c r="J123" s="4">
         <f t="shared" ca="1" si="26"/>
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K123" s="2">
         <v>45315</v>
@@ -8008,7 +8058,7 @@
       </c>
       <c r="J124" s="4">
         <f t="shared" ca="1" si="26"/>
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K124" s="2">
         <v>45315</v>
@@ -8053,7 +8103,7 @@
       </c>
       <c r="J125" s="4">
         <f t="shared" ca="1" si="26"/>
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K125" s="2">
         <v>45315</v>
@@ -8087,7 +8137,7 @@
         <v>85</v>
       </c>
       <c r="G126" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="H126" s="2">
         <v>45309</v>
@@ -8098,7 +8148,7 @@
       </c>
       <c r="J126" s="4">
         <f t="shared" ca="1" si="26"/>
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L126" s="4" t="str">
         <f t="shared" si="22"/>
@@ -8112,7 +8162,7 @@
       </c>
       <c r="P126"/>
       <c r="Q126" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="127" spans="2:18" x14ac:dyDescent="0.3">
@@ -8144,16 +8194,16 @@
         <v>42</v>
       </c>
       <c r="L127" s="4" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="M127" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="O127"/>
       <c r="P127"/>
       <c r="Q127" s="2"/>
       <c r="R127" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="128" spans="2:18" x14ac:dyDescent="0.3">
@@ -8173,7 +8223,7 @@
         <v>86</v>
       </c>
       <c r="G128" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="H128" s="2">
         <v>45309</v>
@@ -8184,19 +8234,19 @@
       </c>
       <c r="J128" s="4">
         <f t="shared" ref="J128:J129" ca="1" si="28">IF(_xlfn.DAYS(TODAY(),H128)&lt;10000, _xlfn.DAYS(TODAY(),H128), "-")</f>
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L128" s="4" t="str">
         <f t="shared" si="22"/>
         <v>-</v>
       </c>
       <c r="M128" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="P128"/>
       <c r="Q128" s="2"/>
       <c r="R128" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="129" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -8204,7 +8254,7 @@
         <v>100</v>
       </c>
       <c r="C129" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D129">
         <v>796</v>
@@ -8216,7 +8266,7 @@
         <v>85</v>
       </c>
       <c r="G129" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H129" s="2">
         <v>45309</v>
@@ -8227,7 +8277,7 @@
       </c>
       <c r="J129" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L129" s="4" t="str">
         <f t="shared" si="22"/>
@@ -8241,10 +8291,10 @@
       </c>
       <c r="P129"/>
       <c r="Q129" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="130" spans="2:18" x14ac:dyDescent="0.3">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="130" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B130" t="s">
         <v>5</v>
       </c>
@@ -8267,18 +8317,18 @@
         <v>196</v>
       </c>
       <c r="L130" s="4" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="M130" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="O130"/>
       <c r="P130"/>
       <c r="R130" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="131" spans="2:18" x14ac:dyDescent="0.3">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="131" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B131" t="s">
         <v>101</v>
       </c>
@@ -8295,7 +8345,7 @@
         <v>84</v>
       </c>
       <c r="G131" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H131" s="2">
         <v>45309</v>
@@ -8306,21 +8356,21 @@
       </c>
       <c r="J131" s="4">
         <f t="shared" ref="J131:J134" ca="1" si="30">IF(_xlfn.DAYS(TODAY(),H131)&lt;10000, _xlfn.DAYS(TODAY(),H131), "-")</f>
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L131" s="4" t="str">
         <f t="shared" si="22"/>
         <v>-</v>
       </c>
       <c r="M131" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="P131"/>
       <c r="R131" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="132" spans="2:18" x14ac:dyDescent="0.3">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="132" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B132" t="s">
         <v>101</v>
       </c>
@@ -8337,7 +8387,7 @@
         <v>84</v>
       </c>
       <c r="G132" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H132" s="2">
         <v>45309</v>
@@ -8348,21 +8398,21 @@
       </c>
       <c r="J132" s="4">
         <f t="shared" ca="1" si="30"/>
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L132" s="4" t="str">
         <f t="shared" si="22"/>
         <v>-</v>
       </c>
       <c r="M132" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="P132"/>
       <c r="R132" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="133" spans="2:18" x14ac:dyDescent="0.3">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="133" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B133" t="s">
         <v>5</v>
       </c>
@@ -8384,21 +8434,21 @@
       </c>
       <c r="J133" s="4">
         <f t="shared" ca="1" si="30"/>
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L133" s="4" t="str">
         <f t="shared" si="22"/>
         <v>-</v>
       </c>
       <c r="M133" s="4" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="P133"/>
       <c r="R133" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="134" spans="2:18" x14ac:dyDescent="0.3">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="134" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B134" t="s">
         <v>101</v>
       </c>
@@ -8415,7 +8465,7 @@
         <v>84</v>
       </c>
       <c r="G134" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H134" s="2">
         <v>45309</v>
@@ -8426,21 +8476,21 @@
       </c>
       <c r="J134" s="4">
         <f t="shared" ca="1" si="30"/>
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L134" s="4" t="str">
         <f t="shared" si="22"/>
         <v>-</v>
       </c>
       <c r="M134" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="P134"/>
       <c r="R134" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="135" spans="2:18" x14ac:dyDescent="0.3">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="135" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B135" t="s">
         <v>5</v>
       </c>
@@ -8484,7 +8534,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="136" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="136" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B136" t="s">
         <v>5</v>
       </c>
@@ -8536,7 +8586,7 @@
       </c>
       <c r="J137" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="L137" s="4" t="str">
         <f t="shared" si="33"/>
@@ -8572,7 +8622,7 @@
       </c>
       <c r="J138" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="L138" s="4" t="str">
         <f t="shared" si="33"/>
@@ -8608,7 +8658,7 @@
       </c>
       <c r="J139" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="L139" s="4" t="str">
         <f t="shared" si="33"/>
@@ -8644,7 +8694,7 @@
       </c>
       <c r="J140" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="L140" s="4" t="str">
         <f t="shared" si="33"/>
@@ -8715,11 +8765,11 @@
       </c>
       <c r="I142" s="4">
         <f t="shared" ca="1" si="31"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J142" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L142" s="4" t="str">
         <f t="shared" si="33"/>
@@ -8730,9 +8780,9 @@
       </c>
       <c r="P142"/>
     </row>
-    <row r="143" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="143" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B143" t="s">
-        <v>126</v>
+        <v>27</v>
       </c>
       <c r="C143" t="s">
         <v>127</v>
@@ -8747,18 +8797,18 @@
         <v>86</v>
       </c>
       <c r="G143" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="H143" s="2">
         <v>45301</v>
       </c>
       <c r="I143" s="4">
         <f t="shared" ca="1" si="31"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J143" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L143" s="4" t="str">
         <f t="shared" si="33"/>
@@ -8767,13 +8817,16 @@
       <c r="M143" s="4" t="s">
         <v>150</v>
       </c>
+      <c r="N143" s="2">
+        <v>45363</v>
+      </c>
       <c r="P143" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="144" spans="2:18" x14ac:dyDescent="0.3">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="144" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B144" t="s">
-        <v>126</v>
+        <v>27</v>
       </c>
       <c r="C144" t="s">
         <v>127</v>
@@ -8788,18 +8841,18 @@
         <v>86</v>
       </c>
       <c r="G144" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="H144" s="2">
         <v>45301</v>
       </c>
       <c r="I144" s="4">
         <f t="shared" ca="1" si="31"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J144" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L144" s="4" t="str">
         <f t="shared" si="33"/>
@@ -8808,13 +8861,16 @@
       <c r="M144" s="4" t="s">
         <v>150</v>
       </c>
+      <c r="N144" s="2">
+        <v>45363</v>
+      </c>
       <c r="P144" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="145" spans="2:18" x14ac:dyDescent="0.3">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="145" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B145" t="s">
-        <v>126</v>
+        <v>27</v>
       </c>
       <c r="C145" t="s">
         <v>127</v>
@@ -8829,18 +8885,18 @@
         <v>86</v>
       </c>
       <c r="G145" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="H145" s="2">
         <v>45301</v>
       </c>
       <c r="I145" s="4">
         <f t="shared" ca="1" si="31"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J145" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L145" s="4" t="str">
         <f t="shared" si="33"/>
@@ -8849,8 +8905,11 @@
       <c r="M145" s="4" t="s">
         <v>150</v>
       </c>
+      <c r="N145" s="2">
+        <v>45363</v>
+      </c>
       <c r="P145" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
     </row>
     <row r="146" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -8870,18 +8929,18 @@
         <v>87</v>
       </c>
       <c r="G146" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="H146" s="2">
         <v>45301</v>
       </c>
       <c r="I146" s="4">
         <f t="shared" ca="1" si="31"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J146" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L146" s="4" t="str">
         <f t="shared" si="33"/>
@@ -8895,9 +8954,9 @@
       </c>
       <c r="P146"/>
     </row>
-    <row r="147" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="147" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B147" t="s">
-        <v>126</v>
+        <v>27</v>
       </c>
       <c r="C147" t="s">
         <v>127</v>
@@ -8912,18 +8971,18 @@
         <v>86</v>
       </c>
       <c r="G147" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="H147" s="2">
         <v>45301</v>
       </c>
       <c r="I147" s="4">
         <f t="shared" ca="1" si="31"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J147" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L147" s="4" t="str">
         <f t="shared" si="33"/>
@@ -8932,8 +8991,11 @@
       <c r="M147" s="4" t="s">
         <v>150</v>
       </c>
+      <c r="N147" s="2">
+        <v>45363</v>
+      </c>
       <c r="P147" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
     </row>
     <row r="148" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -9052,7 +9114,7 @@
         <v>86</v>
       </c>
       <c r="G151" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="H151" s="2">
         <v>45307</v>
@@ -9063,7 +9125,7 @@
       </c>
       <c r="J151" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L151" s="4" t="str">
         <f t="shared" si="36"/>
@@ -9076,10 +9138,10 @@
         <v>45357</v>
       </c>
       <c r="P151" s="5" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="R151" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="152" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -9099,7 +9161,7 @@
         <v>87</v>
       </c>
       <c r="G152" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="H152" s="2">
         <v>45307</v>
@@ -9110,7 +9172,7 @@
       </c>
       <c r="J152" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L152" s="4" t="str">
         <f t="shared" si="36"/>
@@ -9141,7 +9203,7 @@
         <v>134</v>
       </c>
       <c r="G153" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="H153" s="2">
         <v>45307</v>
@@ -9152,7 +9214,7 @@
       </c>
       <c r="J153" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L153" s="4" t="str">
         <f t="shared" si="36"/>
@@ -9183,7 +9245,7 @@
         <v>134</v>
       </c>
       <c r="G154" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="H154" s="2">
         <v>45307</v>
@@ -9194,7 +9256,7 @@
       </c>
       <c r="J154" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L154" s="4" t="str">
         <f t="shared" si="36"/>
@@ -9225,7 +9287,7 @@
         <v>86</v>
       </c>
       <c r="G155" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="H155" s="2">
         <v>45307</v>
@@ -9236,7 +9298,7 @@
       </c>
       <c r="J155" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L155" s="4" t="str">
         <f t="shared" si="36"/>
@@ -9249,10 +9311,10 @@
         <v>45357</v>
       </c>
       <c r="P155" s="5" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="R155" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
     </row>
     <row r="156" spans="2:18" x14ac:dyDescent="0.3">
@@ -9272,7 +9334,7 @@
         <v>86</v>
       </c>
       <c r="G156" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H156" s="2">
         <v>45307</v>
@@ -9283,7 +9345,7 @@
       </c>
       <c r="J156" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L156" s="4" t="str">
         <f t="shared" si="36"/>
@@ -9318,11 +9380,11 @@
       </c>
       <c r="I157" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J157" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L157" s="4" t="str">
         <f t="shared" si="36"/>
@@ -9499,7 +9561,7 @@
       </c>
       <c r="J162" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K162" s="2">
         <v>45301</v>
@@ -9571,7 +9633,7 @@
       </c>
       <c r="J164" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K164" s="2">
         <v>45301</v>
@@ -9610,7 +9672,7 @@
       </c>
       <c r="J165" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K165" s="2">
         <v>45301</v>
@@ -9655,7 +9717,7 @@
       </c>
       <c r="J166" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K166" s="2">
         <v>45301</v>
@@ -9697,7 +9759,7 @@
       </c>
       <c r="J167" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K167" s="2">
         <v>45301</v>
@@ -9748,7 +9810,7 @@
       </c>
       <c r="J168" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K168" s="2">
         <v>45301</v>
@@ -9786,11 +9848,11 @@
       </c>
       <c r="I169" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J169" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L169" s="4" t="str">
         <f t="shared" si="36"/>
@@ -9831,11 +9893,11 @@
       </c>
       <c r="I170" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J170" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L170" s="4" t="str">
         <f t="shared" si="36"/>
@@ -9851,7 +9913,7 @@
         <v>156</v>
       </c>
       <c r="R170" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="171" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -9875,11 +9937,11 @@
       </c>
       <c r="I171" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J171" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L171" s="4" t="str">
         <f t="shared" si="36"/>
@@ -9891,11 +9953,14 @@
       <c r="N171" s="2">
         <v>45322</v>
       </c>
+      <c r="O171" s="2">
+        <v>45361</v>
+      </c>
       <c r="P171" s="5" t="s">
         <v>156</v>
       </c>
       <c r="R171" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="172" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -9926,7 +9991,7 @@
       </c>
       <c r="J172" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K172" s="2">
         <v>45301</v>
@@ -9976,7 +10041,7 @@
       </c>
       <c r="J173" s="4">
         <f t="shared" ref="J173:J174" ca="1" si="41">IF(_xlfn.DAYS(TODAY(),H173)&lt;10000, _xlfn.DAYS(TODAY(),H173), "-")</f>
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L173" s="4" t="str">
         <f t="shared" ref="L173:L174" si="42">IF(_xlfn.DAYS(K173,H173)&gt;0, _xlfn.DAYS(K173,H173), "-")</f>
@@ -10048,7 +10113,7 @@
       </c>
       <c r="J175" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K175" s="2">
         <v>45301</v>
@@ -10090,7 +10155,7 @@
       </c>
       <c r="J176" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K176" s="2">
         <v>45301</v>
@@ -10105,11 +10170,14 @@
       <c r="N176" s="2">
         <v>45322</v>
       </c>
+      <c r="O176" s="2">
+        <v>45359</v>
+      </c>
       <c r="P176" s="5" t="s">
         <v>156</v>
       </c>
       <c r="R176" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="177" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -10140,7 +10208,7 @@
       </c>
       <c r="J177" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K177" s="2">
         <v>45301</v>
@@ -10159,7 +10227,7 @@
         <v>156</v>
       </c>
       <c r="R177" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="178" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -10190,7 +10258,7 @@
       </c>
       <c r="J178" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K178" s="2">
         <v>45301</v>
@@ -10209,7 +10277,7 @@
         <v>156</v>
       </c>
       <c r="R178" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="179" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -10240,7 +10308,7 @@
       </c>
       <c r="J179" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L179" s="4" t="str">
         <f t="shared" si="36"/>
@@ -10256,7 +10324,7 @@
         <v>156</v>
       </c>
       <c r="R179" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="180" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -10269,6 +10337,9 @@
       <c r="E180" t="s">
         <v>16</v>
       </c>
+      <c r="F180" s="5" t="s">
+        <v>134</v>
+      </c>
       <c r="G180" t="s">
         <v>159</v>
       </c>
@@ -10276,12 +10347,12 @@
         <v>45300</v>
       </c>
       <c r="I180" s="4">
-        <f t="shared" ref="I180:I187" ca="1" si="43">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H180), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H180), 7), "-")</f>
+        <f t="shared" ref="I180:I189" ca="1" si="43">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H180), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H180), 7), "-")</f>
         <v>9</v>
       </c>
       <c r="J180" s="4">
-        <f t="shared" ref="J180:J187" ca="1" si="44">IF(_xlfn.DAYS(TODAY(),H180)&lt;10000, _xlfn.DAYS(TODAY(),H180), "-")</f>
-        <v>63</v>
+        <f t="shared" ref="J180:J189" ca="1" si="44">IF(_xlfn.DAYS(TODAY(),H180)&lt;10000, _xlfn.DAYS(TODAY(),H180), "-")</f>
+        <v>64</v>
       </c>
       <c r="K180" s="7">
         <v>45324</v>
@@ -10304,6 +10375,9 @@
       <c r="E181" t="s">
         <v>16</v>
       </c>
+      <c r="F181" s="5" t="s">
+        <v>134</v>
+      </c>
       <c r="G181" t="s">
         <v>159</v>
       </c>
@@ -10316,7 +10390,7 @@
       </c>
       <c r="J181" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K181" s="7">
         <v>45324</v>
@@ -10339,6 +10413,9 @@
       <c r="E182" t="s">
         <v>16</v>
       </c>
+      <c r="F182" s="5" t="s">
+        <v>134</v>
+      </c>
       <c r="G182" t="s">
         <v>159</v>
       </c>
@@ -10351,7 +10428,7 @@
       </c>
       <c r="J182" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K182" s="7">
         <v>45324</v>
@@ -10374,6 +10451,9 @@
       <c r="E183" t="s">
         <v>16</v>
       </c>
+      <c r="F183" s="5" t="s">
+        <v>134</v>
+      </c>
       <c r="G183" t="s">
         <v>159</v>
       </c>
@@ -10386,7 +10466,7 @@
       </c>
       <c r="J183" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K183" s="7">
         <v>45324</v>
@@ -10409,6 +10489,9 @@
       <c r="E184" t="s">
         <v>16</v>
       </c>
+      <c r="F184" s="5" t="s">
+        <v>134</v>
+      </c>
       <c r="G184" t="s">
         <v>159</v>
       </c>
@@ -10421,7 +10504,7 @@
       </c>
       <c r="J184" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K184" s="7">
         <v>45324</v>
@@ -10444,6 +10527,9 @@
       <c r="E185" t="s">
         <v>16</v>
       </c>
+      <c r="F185" s="5" t="s">
+        <v>134</v>
+      </c>
       <c r="G185" t="s">
         <v>159</v>
       </c>
@@ -10456,7 +10542,7 @@
       </c>
       <c r="J185" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K185" s="7">
         <v>45324</v>
@@ -10479,8 +10565,11 @@
       <c r="E186" t="s">
         <v>16</v>
       </c>
+      <c r="F186" s="5" t="s">
+        <v>134</v>
+      </c>
       <c r="G186" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="H186" s="2">
         <v>45324</v>
@@ -10491,7 +10580,7 @@
       </c>
       <c r="J186" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K186" s="2">
         <v>45357</v>
@@ -10501,7 +10590,7 @@
         <v>33</v>
       </c>
       <c r="M186" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
     </row>
     <row r="187" spans="2:18" x14ac:dyDescent="0.3">
@@ -10511,33 +10600,26 @@
       <c r="C187" t="s">
         <v>127</v>
       </c>
-      <c r="E187" t="s">
-        <v>16</v>
-      </c>
-      <c r="H187" s="2">
-        <v>45327</v>
-      </c>
-      <c r="I187" s="4">
-        <f t="shared" ca="1" si="43"/>
-        <v>5</v>
-      </c>
-      <c r="J187" s="4">
-        <f t="shared" ca="1" si="44"/>
-        <v>36</v>
+      <c r="F187" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="G187" t="s">
+        <v>268</v>
+      </c>
+      <c r="I187" s="4" t="str">
+        <f t="shared" ref="I187" ca="1" si="46">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H187), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H187), 7), "-")</f>
+        <v>-</v>
+      </c>
+      <c r="J187" s="4" t="str">
+        <f t="shared" ref="J187" ca="1" si="47">IF(_xlfn.DAYS(TODAY(),H187)&lt;10000, _xlfn.DAYS(TODAY(),H187), "-")</f>
+        <v>-</v>
       </c>
       <c r="L187" s="4" t="str">
-        <f t="shared" ref="L187" si="46">IF(_xlfn.DAYS(K187,H187)&gt;0, _xlfn.DAYS(K187,H187), "-")</f>
-        <v>-</v>
-      </c>
-      <c r="M187" t="s">
-        <v>229</v>
-      </c>
-      <c r="P187"/>
-      <c r="Q187" t="s">
-        <v>244</v>
-      </c>
-      <c r="R187" t="s">
-        <v>213</v>
+        <f t="shared" ref="L187:L189" si="48">IF(_xlfn.DAYS(K187,H187)&gt;0, _xlfn.DAYS(K187,H187), "-")</f>
+        <v>-</v>
+      </c>
+      <c r="M187" s="4" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="188" spans="2:18" x14ac:dyDescent="0.3">
@@ -10547,33 +10629,29 @@
       <c r="C188" t="s">
         <v>127</v>
       </c>
-      <c r="E188" t="s">
-        <v>16</v>
+      <c r="F188" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="G188" t="s">
+        <v>269</v>
       </c>
       <c r="H188" s="2">
-        <v>45327</v>
+        <v>45269</v>
       </c>
       <c r="I188" s="4">
-        <f t="shared" ref="I188:I192" ca="1" si="47">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H188), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H188), 7), "-")</f>
-        <v>5</v>
+        <f t="shared" ca="1" si="43"/>
+        <v>13</v>
       </c>
       <c r="J188" s="4">
-        <f t="shared" ref="J188:J192" ca="1" si="48">IF(_xlfn.DAYS(TODAY(),H188)&lt;10000, _xlfn.DAYS(TODAY(),H188), "-")</f>
-        <v>36</v>
+        <f t="shared" ca="1" si="44"/>
+        <v>95</v>
       </c>
       <c r="L188" s="4" t="str">
-        <f t="shared" ref="L188:L192" si="49">IF(_xlfn.DAYS(K188,H188)&gt;0, _xlfn.DAYS(K188,H188), "-")</f>
-        <v>-</v>
-      </c>
-      <c r="M188" t="s">
-        <v>229</v>
-      </c>
-      <c r="P188"/>
-      <c r="Q188" t="s">
-        <v>244</v>
-      </c>
-      <c r="R188" t="s">
-        <v>213</v>
+        <f t="shared" si="48"/>
+        <v>-</v>
+      </c>
+      <c r="M188" s="4" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="189" spans="2:18" x14ac:dyDescent="0.3">
@@ -10583,33 +10661,36 @@
       <c r="C189" t="s">
         <v>127</v>
       </c>
-      <c r="E189" s="2" t="s">
+      <c r="E189" t="s">
         <v>16</v>
+      </c>
+      <c r="G189" t="s">
+        <v>268</v>
       </c>
       <c r="H189" s="2">
         <v>45327</v>
       </c>
       <c r="I189" s="4">
-        <f t="shared" ca="1" si="47"/>
+        <f t="shared" ca="1" si="43"/>
         <v>5</v>
       </c>
       <c r="J189" s="4">
-        <f t="shared" ca="1" si="48"/>
-        <v>36</v>
+        <f t="shared" ca="1" si="44"/>
+        <v>37</v>
       </c>
       <c r="L189" s="4" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>-</v>
       </c>
       <c r="M189" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="P189"/>
       <c r="Q189" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="R189" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="190" spans="2:18" x14ac:dyDescent="0.3">
@@ -10622,30 +10703,33 @@
       <c r="E190" t="s">
         <v>16</v>
       </c>
+      <c r="G190" t="s">
+        <v>268</v>
+      </c>
       <c r="H190" s="2">
         <v>45327</v>
       </c>
       <c r="I190" s="4">
-        <f t="shared" ca="1" si="47"/>
+        <f t="shared" ref="I190:I194" ca="1" si="49">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H190), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H190), 7), "-")</f>
         <v>5</v>
       </c>
       <c r="J190" s="4">
-        <f t="shared" ca="1" si="48"/>
-        <v>36</v>
+        <f t="shared" ref="J190:J194" ca="1" si="50">IF(_xlfn.DAYS(TODAY(),H190)&lt;10000, _xlfn.DAYS(TODAY(),H190), "-")</f>
+        <v>37</v>
       </c>
       <c r="L190" s="4" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" ref="L190:L194" si="51">IF(_xlfn.DAYS(K190,H190)&gt;0, _xlfn.DAYS(K190,H190), "-")</f>
         <v>-</v>
       </c>
       <c r="M190" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="P190"/>
       <c r="Q190" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="R190" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="191" spans="2:18" x14ac:dyDescent="0.3">
@@ -10655,33 +10739,36 @@
       <c r="C191" t="s">
         <v>127</v>
       </c>
-      <c r="E191" t="s">
+      <c r="E191" s="2" t="s">
         <v>16</v>
+      </c>
+      <c r="G191" t="s">
+        <v>268</v>
       </c>
       <c r="H191" s="2">
         <v>45327</v>
       </c>
       <c r="I191" s="4">
-        <f t="shared" ca="1" si="47"/>
+        <f t="shared" ca="1" si="49"/>
         <v>5</v>
       </c>
       <c r="J191" s="4">
-        <f t="shared" ca="1" si="48"/>
-        <v>36</v>
+        <f t="shared" ca="1" si="50"/>
+        <v>37</v>
       </c>
       <c r="L191" s="4" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>-</v>
       </c>
       <c r="M191" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="P191"/>
       <c r="Q191" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="R191" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="192" spans="2:18" x14ac:dyDescent="0.3">
@@ -10694,84 +10781,114 @@
       <c r="E192" t="s">
         <v>16</v>
       </c>
+      <c r="G192" t="s">
+        <v>268</v>
+      </c>
       <c r="H192" s="2">
         <v>45327</v>
       </c>
       <c r="I192" s="4">
-        <f t="shared" ca="1" si="47"/>
+        <f t="shared" ca="1" si="49"/>
         <v>5</v>
       </c>
       <c r="J192" s="4">
-        <f t="shared" ca="1" si="48"/>
-        <v>36</v>
+        <f t="shared" ca="1" si="50"/>
+        <v>37</v>
       </c>
       <c r="L192" s="4" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>-</v>
       </c>
       <c r="M192" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="P192"/>
       <c r="Q192" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="R192" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="193" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B193" t="s">
-        <v>164</v>
+        <v>5</v>
       </c>
       <c r="C193" t="s">
-        <v>111</v>
-      </c>
-      <c r="D193">
-        <v>639</v>
+        <v>127</v>
       </c>
       <c r="E193" t="s">
-        <v>173</v>
-      </c>
-      <c r="F193" s="5" t="s">
-        <v>167</v>
+        <v>16</v>
       </c>
       <c r="G193" t="s">
-        <v>172</v>
-      </c>
-      <c r="M193" s="4" t="s">
-        <v>165</v>
+        <v>269</v>
+      </c>
+      <c r="H193" s="2">
+        <v>45327</v>
+      </c>
+      <c r="I193" s="4">
+        <f t="shared" ca="1" si="49"/>
+        <v>5</v>
+      </c>
+      <c r="J193" s="4">
+        <f t="shared" ca="1" si="50"/>
+        <v>37</v>
+      </c>
+      <c r="L193" s="4" t="str">
+        <f t="shared" si="51"/>
+        <v>-</v>
+      </c>
+      <c r="M193" t="s">
+        <v>227</v>
       </c>
       <c r="P193"/>
+      <c r="Q193" t="s">
+        <v>240</v>
+      </c>
+      <c r="R193" t="s">
+        <v>211</v>
+      </c>
     </row>
     <row r="194" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B194" t="s">
-        <v>164</v>
+        <v>5</v>
       </c>
       <c r="C194" t="s">
-        <v>111</v>
-      </c>
-      <c r="D194">
-        <v>640</v>
+        <v>127</v>
       </c>
       <c r="E194" t="s">
-        <v>173</v>
-      </c>
-      <c r="F194" s="5" t="s">
-        <v>168</v>
+        <v>16</v>
       </c>
       <c r="G194" t="s">
-        <v>172</v>
-      </c>
-      <c r="M194" s="4" t="s">
-        <v>165</v>
+        <v>269</v>
+      </c>
+      <c r="H194" s="2">
+        <v>45327</v>
+      </c>
+      <c r="I194" s="4">
+        <f t="shared" ca="1" si="49"/>
+        <v>5</v>
+      </c>
+      <c r="J194" s="4">
+        <f t="shared" ca="1" si="50"/>
+        <v>37</v>
+      </c>
+      <c r="L194" s="4" t="str">
+        <f t="shared" si="51"/>
+        <v>-</v>
+      </c>
+      <c r="M194" t="s">
+        <v>227</v>
       </c>
       <c r="P194"/>
       <c r="Q194" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="195" spans="2:18" x14ac:dyDescent="0.3">
+        <v>240</v>
+      </c>
+      <c r="R194" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="195" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B195" t="s">
         <v>164</v>
       </c>
@@ -10779,23 +10896,35 @@
         <v>111</v>
       </c>
       <c r="D195">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="E195" t="s">
         <v>173</v>
       </c>
       <c r="F195" s="5" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G195" t="s">
         <v>172</v>
       </c>
+      <c r="I195" s="4" t="str">
+        <f t="shared" ref="I195:I200" ca="1" si="52">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H195), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H195), 7), "-")</f>
+        <v>-</v>
+      </c>
+      <c r="J195" s="4" t="str">
+        <f t="shared" ref="J195:J200" ca="1" si="53">IF(_xlfn.DAYS(TODAY(),H195)&lt;10000, _xlfn.DAYS(TODAY(),H195), "-")</f>
+        <v>-</v>
+      </c>
+      <c r="L195" s="4" t="str">
+        <f t="shared" ref="L195:L200" si="54">IF(_xlfn.DAYS(K195,H195)&gt;0, _xlfn.DAYS(K195,H195), "-")</f>
+        <v>-</v>
+      </c>
       <c r="M195" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P195"/>
     </row>
-    <row r="196" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="196" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B196" t="s">
         <v>164</v>
       </c>
@@ -10803,23 +10932,38 @@
         <v>111</v>
       </c>
       <c r="D196">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="E196" t="s">
         <v>173</v>
       </c>
       <c r="F196" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G196" t="s">
         <v>172</v>
       </c>
+      <c r="I196" s="4" t="str">
+        <f t="shared" ca="1" si="52"/>
+        <v>-</v>
+      </c>
+      <c r="J196" s="4" t="str">
+        <f t="shared" ca="1" si="53"/>
+        <v>-</v>
+      </c>
+      <c r="L196" s="4" t="str">
+        <f t="shared" si="54"/>
+        <v>-</v>
+      </c>
       <c r="M196" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P196"/>
-    </row>
-    <row r="197" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="Q196" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="197" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B197" t="s">
         <v>164</v>
       </c>
@@ -10827,23 +10971,35 @@
         <v>111</v>
       </c>
       <c r="D197">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="E197" t="s">
         <v>173</v>
       </c>
       <c r="F197" s="5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G197" t="s">
         <v>172</v>
       </c>
+      <c r="I197" s="4" t="str">
+        <f t="shared" ca="1" si="52"/>
+        <v>-</v>
+      </c>
+      <c r="J197" s="4" t="str">
+        <f t="shared" ca="1" si="53"/>
+        <v>-</v>
+      </c>
+      <c r="L197" s="4" t="str">
+        <f t="shared" si="54"/>
+        <v>-</v>
+      </c>
       <c r="M197" s="4" t="s">
         <v>166</v>
       </c>
       <c r="P197"/>
     </row>
-    <row r="198" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="198" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B198" t="s">
         <v>164</v>
       </c>
@@ -10851,108 +11007,108 @@
         <v>111</v>
       </c>
       <c r="D198">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="E198" t="s">
         <v>173</v>
       </c>
       <c r="F198" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G198" t="s">
         <v>172</v>
       </c>
+      <c r="I198" s="4" t="str">
+        <f t="shared" ca="1" si="52"/>
+        <v>-</v>
+      </c>
+      <c r="J198" s="4" t="str">
+        <f t="shared" ca="1" si="53"/>
+        <v>-</v>
+      </c>
+      <c r="L198" s="4" t="str">
+        <f t="shared" si="54"/>
+        <v>-</v>
+      </c>
       <c r="M198" s="4" t="s">
         <v>166</v>
       </c>
       <c r="P198"/>
-      <c r="Q198" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="199" spans="2:18" x14ac:dyDescent="0.3">
+    </row>
+    <row r="199" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B199" t="s">
-        <v>5</v>
+        <v>164</v>
       </c>
       <c r="C199" t="s">
-        <v>112</v>
-      </c>
-      <c r="D199" t="s">
-        <v>234</v>
+        <v>111</v>
+      </c>
+      <c r="D199">
+        <v>643</v>
       </c>
       <c r="E199" t="s">
-        <v>7</v>
+        <v>173</v>
       </c>
       <c r="F199" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="H199" s="2">
-        <v>45332</v>
-      </c>
-      <c r="I199" s="4">
-        <f t="shared" ref="I199" ca="1" si="50">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H199), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H199), 7), "-")</f>
-        <v>4</v>
-      </c>
-      <c r="J199" s="4">
-        <f t="shared" ref="J199" ca="1" si="51">IF(_xlfn.DAYS(TODAY(),H199)&lt;10000, _xlfn.DAYS(TODAY(),H199), "-")</f>
-        <v>31</v>
+        <v>168</v>
+      </c>
+      <c r="G199" t="s">
+        <v>172</v>
+      </c>
+      <c r="I199" s="4" t="str">
+        <f t="shared" ca="1" si="52"/>
+        <v>-</v>
+      </c>
+      <c r="J199" s="4" t="str">
+        <f t="shared" ca="1" si="53"/>
+        <v>-</v>
       </c>
       <c r="L199" s="4" t="str">
-        <f t="shared" ref="L199" si="52">IF(_xlfn.DAYS(K199,H199)&gt;0, _xlfn.DAYS(K199,H199), "-")</f>
-        <v>-</v>
-      </c>
-      <c r="M199" t="s">
-        <v>231</v>
+        <f t="shared" si="54"/>
+        <v>-</v>
+      </c>
+      <c r="M199" s="4" t="s">
+        <v>166</v>
       </c>
       <c r="P199"/>
-      <c r="Q199" t="s">
-        <v>171</v>
-      </c>
-      <c r="R199" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="200" spans="2:18" x14ac:dyDescent="0.3">
+    </row>
+    <row r="200" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B200" t="s">
-        <v>5</v>
+        <v>164</v>
       </c>
       <c r="C200" t="s">
-        <v>112</v>
-      </c>
-      <c r="D200" t="s">
-        <v>235</v>
+        <v>111</v>
+      </c>
+      <c r="D200">
+        <v>644</v>
       </c>
       <c r="E200" t="s">
-        <v>8</v>
+        <v>173</v>
       </c>
       <c r="F200" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="H200" s="2">
-        <v>45332</v>
-      </c>
-      <c r="I200" s="4">
-        <f t="shared" ref="I200:I214" ca="1" si="53">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H200), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H200), 7), "-")</f>
-        <v>4</v>
-      </c>
-      <c r="J200" s="4">
-        <f t="shared" ref="J200:J214" ca="1" si="54">IF(_xlfn.DAYS(TODAY(),H200)&lt;10000, _xlfn.DAYS(TODAY(),H200), "-")</f>
-        <v>31</v>
+        <v>170</v>
+      </c>
+      <c r="G200" t="s">
+        <v>172</v>
+      </c>
+      <c r="I200" s="4" t="str">
+        <f t="shared" ca="1" si="52"/>
+        <v>-</v>
+      </c>
+      <c r="J200" s="4" t="str">
+        <f t="shared" ca="1" si="53"/>
+        <v>-</v>
       </c>
       <c r="L200" s="4" t="str">
-        <f t="shared" ref="L200:L214" si="55">IF(_xlfn.DAYS(K200,H200)&gt;0, _xlfn.DAYS(K200,H200), "-")</f>
-        <v>-</v>
-      </c>
-      <c r="M200" t="s">
-        <v>231</v>
+        <f t="shared" si="54"/>
+        <v>-</v>
+      </c>
+      <c r="M200" s="4" t="s">
+        <v>166</v>
       </c>
       <c r="P200"/>
       <c r="Q200" t="s">
         <v>171</v>
       </c>
-      <c r="R200" t="s">
-        <v>206</v>
-      </c>
     </row>
     <row r="201" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B201" t="s">
@@ -10962,38 +11118,41 @@
         <v>112</v>
       </c>
       <c r="D201" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="E201" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F201" s="5" t="s">
-        <v>247</v>
+        <v>242</v>
+      </c>
+      <c r="G201" t="s">
+        <v>269</v>
       </c>
       <c r="H201" s="2">
         <v>45332</v>
       </c>
       <c r="I201" s="4">
-        <f t="shared" ca="1" si="53"/>
+        <f t="shared" ref="I201" ca="1" si="55">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H201), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H201), 7), "-")</f>
         <v>4</v>
       </c>
       <c r="J201" s="4">
-        <f t="shared" ca="1" si="54"/>
-        <v>31</v>
+        <f t="shared" ref="J201" ca="1" si="56">IF(_xlfn.DAYS(TODAY(),H201)&lt;10000, _xlfn.DAYS(TODAY(),H201), "-")</f>
+        <v>32</v>
       </c>
       <c r="L201" s="4" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" ref="L201" si="57">IF(_xlfn.DAYS(K201,H201)&gt;0, _xlfn.DAYS(K201,H201), "-")</f>
         <v>-</v>
       </c>
       <c r="M201" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="P201"/>
       <c r="Q201" t="s">
         <v>171</v>
       </c>
       <c r="R201" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="202" spans="2:18" x14ac:dyDescent="0.3">
@@ -11004,38 +11163,41 @@
         <v>112</v>
       </c>
       <c r="D202" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E202" t="s">
         <v>8</v>
       </c>
       <c r="F202" s="5" t="s">
-        <v>247</v>
+        <v>243</v>
+      </c>
+      <c r="G202" t="s">
+        <v>269</v>
       </c>
       <c r="H202" s="2">
         <v>45332</v>
       </c>
       <c r="I202" s="4">
-        <f t="shared" ca="1" si="53"/>
+        <f t="shared" ref="I202:I216" ca="1" si="58">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H202), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H202), 7), "-")</f>
         <v>4</v>
       </c>
       <c r="J202" s="4">
-        <f t="shared" ca="1" si="54"/>
-        <v>31</v>
+        <f t="shared" ref="J202:J216" ca="1" si="59">IF(_xlfn.DAYS(TODAY(),H202)&lt;10000, _xlfn.DAYS(TODAY(),H202), "-")</f>
+        <v>32</v>
       </c>
       <c r="L202" s="4" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" ref="L202:L216" si="60">IF(_xlfn.DAYS(K202,H202)&gt;0, _xlfn.DAYS(K202,H202), "-")</f>
         <v>-</v>
       </c>
       <c r="M202" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="P202"/>
       <c r="Q202" t="s">
         <v>171</v>
       </c>
       <c r="R202" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="203" spans="2:18" x14ac:dyDescent="0.3">
@@ -11046,38 +11208,41 @@
         <v>112</v>
       </c>
       <c r="D203" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E203" t="s">
         <v>8</v>
       </c>
       <c r="F203" s="5" t="s">
-        <v>247</v>
+        <v>243</v>
+      </c>
+      <c r="G203" t="s">
+        <v>269</v>
       </c>
       <c r="H203" s="2">
         <v>45332</v>
       </c>
       <c r="I203" s="4">
-        <f t="shared" ca="1" si="53"/>
+        <f t="shared" ca="1" si="58"/>
         <v>4</v>
       </c>
       <c r="J203" s="4">
-        <f t="shared" ca="1" si="54"/>
-        <v>31</v>
+        <f t="shared" ca="1" si="59"/>
+        <v>32</v>
       </c>
       <c r="L203" s="4" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="60"/>
         <v>-</v>
       </c>
       <c r="M203" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="P203"/>
       <c r="Q203" t="s">
         <v>171</v>
       </c>
       <c r="R203" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="204" spans="2:18" x14ac:dyDescent="0.3">
@@ -11088,38 +11253,41 @@
         <v>112</v>
       </c>
       <c r="D204" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="E204" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F204" s="5" t="s">
-        <v>247</v>
+        <v>243</v>
+      </c>
+      <c r="G204" t="s">
+        <v>268</v>
       </c>
       <c r="H204" s="2">
         <v>45332</v>
       </c>
       <c r="I204" s="4">
-        <f t="shared" ca="1" si="53"/>
+        <f t="shared" ca="1" si="58"/>
         <v>4</v>
       </c>
       <c r="J204" s="4">
-        <f t="shared" ca="1" si="54"/>
-        <v>31</v>
+        <f t="shared" ca="1" si="59"/>
+        <v>32</v>
       </c>
       <c r="L204" s="4" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="60"/>
         <v>-</v>
       </c>
       <c r="M204" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="P204"/>
       <c r="Q204" t="s">
         <v>171</v>
       </c>
       <c r="R204" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="205" spans="2:18" x14ac:dyDescent="0.3">
@@ -11130,38 +11298,41 @@
         <v>112</v>
       </c>
       <c r="D205" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E205" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F205" s="5" t="s">
-        <v>247</v>
+        <v>243</v>
+      </c>
+      <c r="G205" t="s">
+        <v>268</v>
       </c>
       <c r="H205" s="2">
         <v>45332</v>
       </c>
       <c r="I205" s="4">
-        <f t="shared" ca="1" si="53"/>
+        <f t="shared" ca="1" si="58"/>
         <v>4</v>
       </c>
       <c r="J205" s="4">
-        <f t="shared" ca="1" si="54"/>
-        <v>31</v>
+        <f t="shared" ca="1" si="59"/>
+        <v>32</v>
       </c>
       <c r="L205" s="4" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="60"/>
         <v>-</v>
       </c>
       <c r="M205" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="P205"/>
       <c r="Q205" t="s">
         <v>171</v>
       </c>
       <c r="R205" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="206" spans="2:18" x14ac:dyDescent="0.3">
@@ -11172,38 +11343,41 @@
         <v>112</v>
       </c>
       <c r="D206" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="E206" t="s">
         <v>7</v>
       </c>
       <c r="F206" s="5" t="s">
-        <v>246</v>
+        <v>243</v>
+      </c>
+      <c r="G206" t="s">
+        <v>268</v>
       </c>
       <c r="H206" s="2">
         <v>45332</v>
       </c>
       <c r="I206" s="4">
-        <f t="shared" ca="1" si="53"/>
+        <f t="shared" ca="1" si="58"/>
         <v>4</v>
       </c>
       <c r="J206" s="4">
-        <f t="shared" ca="1" si="54"/>
-        <v>31</v>
+        <f t="shared" ca="1" si="59"/>
+        <v>32</v>
       </c>
       <c r="L206" s="4" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="60"/>
         <v>-</v>
       </c>
       <c r="M206" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="P206"/>
       <c r="Q206" t="s">
         <v>171</v>
       </c>
       <c r="R206" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="207" spans="2:18" x14ac:dyDescent="0.3">
@@ -11214,38 +11388,41 @@
         <v>112</v>
       </c>
       <c r="D207" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="E207" t="s">
         <v>7</v>
       </c>
       <c r="F207" s="5" t="s">
-        <v>246</v>
+        <v>243</v>
+      </c>
+      <c r="G207" t="s">
+        <v>268</v>
       </c>
       <c r="H207" s="2">
         <v>45332</v>
       </c>
       <c r="I207" s="4">
-        <f t="shared" ca="1" si="53"/>
+        <f t="shared" ca="1" si="58"/>
         <v>4</v>
       </c>
       <c r="J207" s="4">
-        <f t="shared" ca="1" si="54"/>
-        <v>31</v>
+        <f t="shared" ca="1" si="59"/>
+        <v>32</v>
       </c>
       <c r="L207" s="4" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="60"/>
         <v>-</v>
       </c>
       <c r="M207" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="P207"/>
       <c r="Q207" t="s">
         <v>171</v>
       </c>
       <c r="R207" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="208" spans="2:18" x14ac:dyDescent="0.3">
@@ -11255,30 +11432,42 @@
       <c r="C208" t="s">
         <v>112</v>
       </c>
+      <c r="D208" t="s">
+        <v>235</v>
+      </c>
       <c r="E208" t="s">
-        <v>15</v>
+        <v>7</v>
+      </c>
+      <c r="F208" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="G208" t="s">
+        <v>268</v>
       </c>
       <c r="H208" s="2">
-        <v>45337</v>
+        <v>45332</v>
       </c>
       <c r="I208" s="4">
-        <f t="shared" ca="1" si="53"/>
-        <v>3</v>
+        <f t="shared" ca="1" si="58"/>
+        <v>4</v>
       </c>
       <c r="J208" s="4">
-        <f t="shared" ca="1" si="54"/>
-        <v>26</v>
+        <f t="shared" ca="1" si="59"/>
+        <v>32</v>
       </c>
       <c r="L208" s="4" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="60"/>
         <v>-</v>
       </c>
       <c r="M208" t="s">
-        <v>197</v>
+        <v>230</v>
       </c>
       <c r="P208"/>
+      <c r="Q208" t="s">
+        <v>171</v>
+      </c>
       <c r="R208" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="209" spans="2:18" x14ac:dyDescent="0.3">
@@ -11288,30 +11477,42 @@
       <c r="C209" t="s">
         <v>112</v>
       </c>
+      <c r="D209" t="s">
+        <v>236</v>
+      </c>
       <c r="E209" t="s">
-        <v>15</v>
+        <v>7</v>
+      </c>
+      <c r="F209" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="G209" t="s">
+        <v>268</v>
       </c>
       <c r="H209" s="2">
-        <v>45337</v>
+        <v>45332</v>
       </c>
       <c r="I209" s="4">
-        <f t="shared" ca="1" si="53"/>
-        <v>3</v>
+        <f t="shared" ca="1" si="58"/>
+        <v>4</v>
       </c>
       <c r="J209" s="4">
-        <f t="shared" ca="1" si="54"/>
-        <v>26</v>
+        <f t="shared" ca="1" si="59"/>
+        <v>32</v>
       </c>
       <c r="L209" s="4" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="60"/>
         <v>-</v>
       </c>
       <c r="M209" t="s">
-        <v>197</v>
+        <v>230</v>
       </c>
       <c r="P209"/>
+      <c r="Q209" t="s">
+        <v>171</v>
+      </c>
       <c r="R209" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="210" spans="2:18" x14ac:dyDescent="0.3">
@@ -11324,27 +11525,36 @@
       <c r="E210" t="s">
         <v>15</v>
       </c>
+      <c r="G210" t="s">
+        <v>268</v>
+      </c>
       <c r="H210" s="2">
         <v>45337</v>
       </c>
       <c r="I210" s="4">
-        <f t="shared" ca="1" si="53"/>
+        <f t="shared" ca="1" si="58"/>
         <v>3</v>
       </c>
       <c r="J210" s="4">
-        <f t="shared" ca="1" si="54"/>
+        <f t="shared" ca="1" si="59"/>
+        <v>27</v>
+      </c>
+      <c r="K210" s="2">
+        <v>45363</v>
+      </c>
+      <c r="L210" s="4">
+        <f t="shared" si="60"/>
         <v>26</v>
       </c>
-      <c r="L210" s="4" t="str">
-        <f t="shared" si="55"/>
-        <v>-</v>
-      </c>
       <c r="M210" t="s">
-        <v>197</v>
+        <v>265</v>
       </c>
       <c r="P210"/>
+      <c r="Q210" t="s">
+        <v>266</v>
+      </c>
       <c r="R210" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="211" spans="2:18" x14ac:dyDescent="0.3">
@@ -11357,27 +11567,36 @@
       <c r="E211" t="s">
         <v>15</v>
       </c>
+      <c r="G211" t="s">
+        <v>268</v>
+      </c>
       <c r="H211" s="2">
         <v>45337</v>
       </c>
       <c r="I211" s="4">
-        <f t="shared" ca="1" si="53"/>
+        <f t="shared" ca="1" si="58"/>
         <v>3</v>
       </c>
       <c r="J211" s="4">
-        <f t="shared" ca="1" si="54"/>
+        <f t="shared" ca="1" si="59"/>
+        <v>27</v>
+      </c>
+      <c r="K211" s="2">
+        <v>45363</v>
+      </c>
+      <c r="L211" s="4">
+        <f t="shared" si="60"/>
         <v>26</v>
       </c>
-      <c r="L211" s="4" t="str">
-        <f t="shared" si="55"/>
-        <v>-</v>
-      </c>
       <c r="M211" t="s">
-        <v>197</v>
+        <v>265</v>
       </c>
       <c r="P211"/>
+      <c r="Q211" t="s">
+        <v>266</v>
+      </c>
       <c r="R211" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="212" spans="2:18" x14ac:dyDescent="0.3">
@@ -11390,27 +11609,36 @@
       <c r="E212" t="s">
         <v>15</v>
       </c>
+      <c r="G212" t="s">
+        <v>268</v>
+      </c>
       <c r="H212" s="2">
         <v>45337</v>
       </c>
       <c r="I212" s="4">
-        <f t="shared" ca="1" si="53"/>
+        <f t="shared" ca="1" si="58"/>
         <v>3</v>
       </c>
       <c r="J212" s="4">
-        <f t="shared" ca="1" si="54"/>
+        <f t="shared" ca="1" si="59"/>
+        <v>27</v>
+      </c>
+      <c r="K212" s="2">
+        <v>45363</v>
+      </c>
+      <c r="L212" s="4">
+        <f t="shared" si="60"/>
         <v>26</v>
       </c>
-      <c r="L212" s="4" t="str">
-        <f t="shared" si="55"/>
-        <v>-</v>
-      </c>
       <c r="M212" t="s">
-        <v>197</v>
+        <v>265</v>
       </c>
       <c r="P212"/>
+      <c r="Q212" t="s">
+        <v>266</v>
+      </c>
       <c r="R212" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="213" spans="2:18" x14ac:dyDescent="0.3">
@@ -11423,27 +11651,36 @@
       <c r="E213" t="s">
         <v>15</v>
       </c>
+      <c r="G213" t="s">
+        <v>268</v>
+      </c>
       <c r="H213" s="2">
         <v>45337</v>
       </c>
       <c r="I213" s="4">
-        <f t="shared" ca="1" si="53"/>
+        <f t="shared" ca="1" si="58"/>
         <v>3</v>
       </c>
       <c r="J213" s="4">
-        <f t="shared" ca="1" si="54"/>
+        <f t="shared" ca="1" si="59"/>
+        <v>27</v>
+      </c>
+      <c r="K213" s="2">
+        <v>45363</v>
+      </c>
+      <c r="L213" s="4">
+        <f t="shared" si="60"/>
         <v>26</v>
       </c>
-      <c r="L213" s="4" t="str">
-        <f t="shared" si="55"/>
-        <v>-</v>
-      </c>
       <c r="M213" t="s">
-        <v>197</v>
+        <v>265</v>
       </c>
       <c r="P213"/>
+      <c r="Q213" t="s">
+        <v>266</v>
+      </c>
       <c r="R213" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="214" spans="2:18" x14ac:dyDescent="0.3">
@@ -11456,27 +11693,36 @@
       <c r="E214" t="s">
         <v>15</v>
       </c>
+      <c r="G214" t="s">
+        <v>268</v>
+      </c>
       <c r="H214" s="2">
         <v>45337</v>
       </c>
       <c r="I214" s="4">
-        <f t="shared" ca="1" si="53"/>
+        <f t="shared" ca="1" si="58"/>
         <v>3</v>
       </c>
       <c r="J214" s="4">
-        <f t="shared" ca="1" si="54"/>
+        <f t="shared" ca="1" si="59"/>
+        <v>27</v>
+      </c>
+      <c r="K214" s="2">
+        <v>45363</v>
+      </c>
+      <c r="L214" s="4">
+        <f t="shared" si="60"/>
         <v>26</v>
       </c>
-      <c r="L214" s="4" t="str">
-        <f t="shared" si="55"/>
-        <v>-</v>
-      </c>
       <c r="M214" t="s">
-        <v>197</v>
+        <v>265</v>
       </c>
       <c r="P214"/>
+      <c r="Q214" t="s">
+        <v>266</v>
+      </c>
       <c r="R214" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="215" spans="2:18" x14ac:dyDescent="0.3">
@@ -11484,32 +11730,41 @@
         <v>5</v>
       </c>
       <c r="C215" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="E215" t="s">
-        <v>202</v>
+        <v>15</v>
+      </c>
+      <c r="G215" t="s">
+        <v>269</v>
       </c>
       <c r="H215" s="2">
-        <v>45343</v>
+        <v>45337</v>
       </c>
       <c r="I215" s="4">
-        <f t="shared" ref="I215:I226" ca="1" si="56">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H215), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H215), 7), "-")</f>
-        <v>2</v>
+        <f t="shared" ca="1" si="58"/>
+        <v>3</v>
       </c>
       <c r="J215" s="4">
-        <f t="shared" ref="J215:J226" ca="1" si="57">IF(_xlfn.DAYS(TODAY(),H215)&lt;10000, _xlfn.DAYS(TODAY(),H215), "-")</f>
-        <v>20</v>
-      </c>
-      <c r="L215" s="4" t="str">
-        <f t="shared" ref="L215:L226" si="58">IF(_xlfn.DAYS(K215,H215)&gt;0, _xlfn.DAYS(K215,H215), "-")</f>
-        <v>-</v>
+        <f t="shared" ca="1" si="59"/>
+        <v>27</v>
+      </c>
+      <c r="K215" s="2">
+        <v>45363</v>
+      </c>
+      <c r="L215" s="4">
+        <f t="shared" si="60"/>
+        <v>26</v>
       </c>
       <c r="M215" t="s">
-        <v>200</v>
+        <v>264</v>
       </c>
       <c r="P215"/>
+      <c r="Q215" t="s">
+        <v>266</v>
+      </c>
       <c r="R215" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="216" spans="2:18" x14ac:dyDescent="0.3">
@@ -11517,32 +11772,41 @@
         <v>5</v>
       </c>
       <c r="C216" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="E216" t="s">
-        <v>16</v>
+        <v>15</v>
+      </c>
+      <c r="G216" t="s">
+        <v>269</v>
       </c>
       <c r="H216" s="2">
-        <v>45343</v>
+        <v>45337</v>
       </c>
       <c r="I216" s="4">
-        <f t="shared" ca="1" si="56"/>
-        <v>2</v>
+        <f t="shared" ca="1" si="58"/>
+        <v>3</v>
       </c>
       <c r="J216" s="4">
-        <f t="shared" ca="1" si="57"/>
-        <v>20</v>
-      </c>
-      <c r="L216" s="4" t="str">
-        <f t="shared" si="58"/>
-        <v>-</v>
+        <f t="shared" ca="1" si="59"/>
+        <v>27</v>
+      </c>
+      <c r="K216" s="2">
+        <v>45363</v>
+      </c>
+      <c r="L216" s="4">
+        <f t="shared" si="60"/>
+        <v>26</v>
       </c>
       <c r="M216" t="s">
-        <v>200</v>
+        <v>264</v>
       </c>
       <c r="P216"/>
+      <c r="Q216" t="s">
+        <v>266</v>
+      </c>
       <c r="R216" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="217" spans="2:18" x14ac:dyDescent="0.3">
@@ -11553,29 +11817,32 @@
         <v>127</v>
       </c>
       <c r="E217" t="s">
-        <v>16</v>
+        <v>200</v>
       </c>
       <c r="H217" s="2">
         <v>45343</v>
       </c>
       <c r="I217" s="4">
-        <f t="shared" ca="1" si="56"/>
-        <v>2</v>
+        <f t="shared" ref="I217:I228" ca="1" si="61">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H217), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H217), 7), "-")</f>
+        <v>3</v>
       </c>
       <c r="J217" s="4">
-        <f t="shared" ca="1" si="57"/>
-        <v>20</v>
+        <f t="shared" ref="J217:J228" ca="1" si="62">IF(_xlfn.DAYS(TODAY(),H217)&lt;10000, _xlfn.DAYS(TODAY(),H217), "-")</f>
+        <v>21</v>
       </c>
       <c r="L217" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" ref="L217:L228" si="63">IF(_xlfn.DAYS(K217,H217)&gt;0, _xlfn.DAYS(K217,H217), "-")</f>
         <v>-</v>
       </c>
       <c r="M217" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="P217"/>
+      <c r="Q217" t="s">
+        <v>276</v>
+      </c>
       <c r="R217" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="218" spans="2:18" x14ac:dyDescent="0.3">
@@ -11585,30 +11852,33 @@
       <c r="C218" t="s">
         <v>127</v>
       </c>
-      <c r="E218" s="2" t="s">
+      <c r="E218" t="s">
         <v>16</v>
       </c>
       <c r="H218" s="2">
         <v>45343</v>
       </c>
       <c r="I218" s="4">
-        <f t="shared" ca="1" si="56"/>
-        <v>2</v>
+        <f t="shared" ca="1" si="61"/>
+        <v>3</v>
       </c>
       <c r="J218" s="4">
-        <f t="shared" ca="1" si="57"/>
-        <v>20</v>
+        <f t="shared" ca="1" si="62"/>
+        <v>21</v>
       </c>
       <c r="L218" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="63"/>
         <v>-</v>
       </c>
       <c r="M218" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="P218"/>
+      <c r="Q218" t="s">
+        <v>276</v>
+      </c>
       <c r="R218" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="219" spans="2:18" x14ac:dyDescent="0.3">
@@ -11625,23 +11895,26 @@
         <v>45343</v>
       </c>
       <c r="I219" s="4">
-        <f t="shared" ca="1" si="56"/>
-        <v>2</v>
+        <f t="shared" ca="1" si="61"/>
+        <v>3</v>
       </c>
       <c r="J219" s="4">
-        <f t="shared" ca="1" si="57"/>
-        <v>20</v>
+        <f t="shared" ca="1" si="62"/>
+        <v>21</v>
       </c>
       <c r="L219" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="63"/>
         <v>-</v>
       </c>
       <c r="M219" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="P219"/>
+      <c r="Q219" t="s">
+        <v>276</v>
+      </c>
       <c r="R219" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="220" spans="2:18" x14ac:dyDescent="0.3">
@@ -11651,30 +11924,33 @@
       <c r="C220" t="s">
         <v>127</v>
       </c>
-      <c r="E220" t="s">
+      <c r="E220" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H220" s="2">
         <v>45343</v>
       </c>
       <c r="I220" s="4">
-        <f t="shared" ca="1" si="56"/>
-        <v>2</v>
+        <f t="shared" ca="1" si="61"/>
+        <v>3</v>
       </c>
       <c r="J220" s="4">
-        <f t="shared" ca="1" si="57"/>
-        <v>20</v>
+        <f t="shared" ca="1" si="62"/>
+        <v>21</v>
       </c>
       <c r="L220" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="63"/>
         <v>-</v>
       </c>
       <c r="M220" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="P220"/>
+      <c r="Q220" t="s">
+        <v>276</v>
+      </c>
       <c r="R220" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="221" spans="2:18" x14ac:dyDescent="0.3">
@@ -11684,30 +11960,33 @@
       <c r="C221" t="s">
         <v>127</v>
       </c>
-      <c r="E221" s="2" t="s">
+      <c r="E221" t="s">
         <v>16</v>
       </c>
       <c r="H221" s="2">
         <v>45343</v>
       </c>
       <c r="I221" s="4">
-        <f t="shared" ca="1" si="56"/>
-        <v>2</v>
+        <f t="shared" ca="1" si="61"/>
+        <v>3</v>
       </c>
       <c r="J221" s="4">
-        <f t="shared" ca="1" si="57"/>
-        <v>20</v>
+        <f t="shared" ca="1" si="62"/>
+        <v>21</v>
       </c>
       <c r="L221" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="63"/>
         <v>-</v>
       </c>
       <c r="M221" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="P221"/>
+      <c r="Q221" t="s">
+        <v>276</v>
+      </c>
       <c r="R221" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="222" spans="2:18" x14ac:dyDescent="0.3">
@@ -11724,23 +12003,26 @@
         <v>45343</v>
       </c>
       <c r="I222" s="4">
-        <f t="shared" ca="1" si="56"/>
-        <v>2</v>
+        <f t="shared" ca="1" si="61"/>
+        <v>3</v>
       </c>
       <c r="J222" s="4">
-        <f t="shared" ca="1" si="57"/>
-        <v>20</v>
+        <f t="shared" ca="1" si="62"/>
+        <v>21</v>
       </c>
       <c r="L222" s="4" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="63"/>
         <v>-</v>
       </c>
       <c r="M222" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="P222"/>
+      <c r="Q222" t="s">
+        <v>276</v>
+      </c>
       <c r="R222" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="223" spans="2:18" x14ac:dyDescent="0.3">
@@ -11748,32 +12030,35 @@
         <v>5</v>
       </c>
       <c r="C223" t="s">
-        <v>111</v>
-      </c>
-      <c r="E223" t="s">
+        <v>127</v>
+      </c>
+      <c r="E223" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H223" s="2">
-        <v>45337</v>
+        <v>45343</v>
       </c>
       <c r="I223" s="4">
-        <f t="shared" ca="1" si="56"/>
+        <f t="shared" ca="1" si="61"/>
         <v>3</v>
       </c>
       <c r="J223" s="4">
-        <f t="shared" ca="1" si="57"/>
-        <v>26</v>
+        <f t="shared" ca="1" si="62"/>
+        <v>21</v>
       </c>
       <c r="L223" s="4" t="str">
-        <f t="shared" si="58"/>
-        <v>-</v>
-      </c>
-      <c r="M223" s="4" t="s">
-        <v>198</v>
+        <f t="shared" si="63"/>
+        <v>-</v>
+      </c>
+      <c r="M223" t="s">
+        <v>199</v>
       </c>
       <c r="P223"/>
+      <c r="Q223" t="s">
+        <v>276</v>
+      </c>
       <c r="R223" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
     </row>
     <row r="224" spans="2:18" x14ac:dyDescent="0.3">
@@ -11781,35 +12066,38 @@
         <v>5</v>
       </c>
       <c r="C224" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="E224" t="s">
         <v>16</v>
       </c>
       <c r="H224" s="2">
-        <v>45337</v>
+        <v>45343</v>
       </c>
       <c r="I224" s="4">
-        <f t="shared" ca="1" si="56"/>
+        <f t="shared" ca="1" si="61"/>
         <v>3</v>
       </c>
       <c r="J224" s="4">
-        <f t="shared" ca="1" si="57"/>
-        <v>26</v>
+        <f t="shared" ca="1" si="62"/>
+        <v>21</v>
       </c>
       <c r="L224" s="4" t="str">
-        <f t="shared" si="58"/>
-        <v>-</v>
-      </c>
-      <c r="M224" s="4" t="s">
-        <v>198</v>
+        <f t="shared" si="63"/>
+        <v>-</v>
+      </c>
+      <c r="M224" t="s">
+        <v>199</v>
       </c>
       <c r="P224"/>
+      <c r="Q224" t="s">
+        <v>276</v>
+      </c>
       <c r="R224" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="225" spans="2:18" x14ac:dyDescent="0.3">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="225" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B225" t="s">
         <v>5</v>
       </c>
@@ -11819,91 +12107,118 @@
       <c r="E225" t="s">
         <v>16</v>
       </c>
+      <c r="G225" t="s">
+        <v>268</v>
+      </c>
       <c r="H225" s="2">
         <v>45337</v>
       </c>
       <c r="I225" s="4">
-        <f t="shared" ca="1" si="56"/>
+        <f t="shared" ca="1" si="61"/>
         <v>3</v>
       </c>
       <c r="J225" s="4">
-        <f t="shared" ca="1" si="57"/>
+        <f t="shared" ca="1" si="62"/>
+        <v>27</v>
+      </c>
+      <c r="K225" s="2">
+        <v>45363</v>
+      </c>
+      <c r="L225" s="4">
+        <f t="shared" si="63"/>
         <v>26</v>
       </c>
-      <c r="L225" s="4" t="str">
-        <f t="shared" si="58"/>
-        <v>-</v>
-      </c>
       <c r="M225" s="4" t="s">
-        <v>198</v>
+        <v>267</v>
       </c>
       <c r="P225"/>
+      <c r="Q225" t="s">
+        <v>266</v>
+      </c>
       <c r="R225" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="226" spans="2:18" x14ac:dyDescent="0.3">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="226" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B226" t="s">
         <v>5</v>
       </c>
       <c r="C226" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="E226" t="s">
         <v>16</v>
       </c>
+      <c r="G226" t="s">
+        <v>268</v>
+      </c>
       <c r="H226" s="2">
-        <v>45349</v>
+        <v>45337</v>
       </c>
       <c r="I226" s="4">
-        <f t="shared" ca="1" si="56"/>
-        <v>2</v>
+        <f t="shared" ca="1" si="61"/>
+        <v>3</v>
       </c>
       <c r="J226" s="4">
-        <f t="shared" ca="1" si="57"/>
-        <v>14</v>
-      </c>
-      <c r="L226" s="4" t="str">
-        <f t="shared" si="58"/>
-        <v>-</v>
-      </c>
-      <c r="M226" t="s">
-        <v>204</v>
+        <f t="shared" ca="1" si="62"/>
+        <v>27</v>
+      </c>
+      <c r="K226" s="2">
+        <v>45363</v>
+      </c>
+      <c r="L226" s="4">
+        <f t="shared" si="63"/>
+        <v>26</v>
+      </c>
+      <c r="M226" s="4" t="s">
+        <v>267</v>
       </c>
       <c r="P226"/>
+      <c r="Q226" t="s">
+        <v>266</v>
+      </c>
       <c r="R226" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="227" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="227" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B227" t="s">
         <v>5</v>
       </c>
       <c r="C227" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="E227" t="s">
         <v>16</v>
       </c>
+      <c r="G227" t="s">
+        <v>268</v>
+      </c>
       <c r="H227" s="2">
-        <v>45349</v>
+        <v>45337</v>
       </c>
       <c r="I227" s="4">
-        <f t="shared" ref="I227:I235" ca="1" si="59">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H227), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H227), 7), "-")</f>
-        <v>2</v>
+        <f t="shared" ca="1" si="61"/>
+        <v>3</v>
       </c>
       <c r="J227" s="4">
-        <f t="shared" ref="J227:J235" ca="1" si="60">IF(_xlfn.DAYS(TODAY(),H227)&lt;10000, _xlfn.DAYS(TODAY(),H227), "-")</f>
-        <v>14</v>
-      </c>
-      <c r="L227" s="4" t="str">
-        <f t="shared" ref="L227:L235" si="61">IF(_xlfn.DAYS(K227,H227)&gt;0, _xlfn.DAYS(K227,H227), "-")</f>
-        <v>-</v>
-      </c>
-      <c r="M227" t="s">
-        <v>204</v>
+        <f t="shared" ca="1" si="62"/>
+        <v>27</v>
+      </c>
+      <c r="K227" s="2">
+        <v>45363</v>
+      </c>
+      <c r="L227" s="4">
+        <f t="shared" si="63"/>
+        <v>26</v>
+      </c>
+      <c r="M227" s="4" t="s">
+        <v>267</v>
       </c>
       <c r="P227"/>
+      <c r="Q227" t="s">
+        <v>266</v>
+      </c>
       <c r="R227" t="s">
         <v>205</v>
       </c>
@@ -11922,23 +12237,23 @@
         <v>45349</v>
       </c>
       <c r="I228" s="4">
-        <f t="shared" ca="1" si="59"/>
+        <f t="shared" ca="1" si="61"/>
         <v>2</v>
       </c>
       <c r="J228" s="4">
-        <f t="shared" ca="1" si="60"/>
-        <v>14</v>
+        <f t="shared" ca="1" si="62"/>
+        <v>15</v>
       </c>
       <c r="L228" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v>-</v>
       </c>
       <c r="M228" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="P228"/>
       <c r="R228" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="229" spans="2:18" x14ac:dyDescent="0.3">
@@ -11955,126 +12270,122 @@
         <v>45349</v>
       </c>
       <c r="I229" s="4">
-        <f t="shared" ca="1" si="59"/>
+        <f t="shared" ref="I229:I237" ca="1" si="64">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H229), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H229), 7), "-")</f>
         <v>2</v>
       </c>
       <c r="J229" s="4">
-        <f t="shared" ca="1" si="60"/>
-        <v>14</v>
+        <f t="shared" ref="J229:J237" ca="1" si="65">IF(_xlfn.DAYS(TODAY(),H229)&lt;10000, _xlfn.DAYS(TODAY(),H229), "-")</f>
+        <v>15</v>
       </c>
       <c r="L229" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" ref="L229:L237" si="66">IF(_xlfn.DAYS(K229,H229)&gt;0, _xlfn.DAYS(K229,H229), "-")</f>
         <v>-</v>
       </c>
       <c r="M229" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="P229"/>
       <c r="R229" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="230" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B230" t="s">
-        <v>240</v>
+        <v>5</v>
       </c>
       <c r="C230" t="s">
         <v>127</v>
       </c>
       <c r="E230" t="s">
-        <v>241</v>
+        <v>16</v>
       </c>
       <c r="H230" s="2">
-        <v>45355</v>
+        <v>45349</v>
       </c>
       <c r="I230" s="4">
-        <f t="shared" ca="1" si="59"/>
-        <v>1</v>
+        <f t="shared" ca="1" si="64"/>
+        <v>2</v>
       </c>
       <c r="J230" s="4">
-        <f t="shared" ca="1" si="60"/>
-        <v>8</v>
+        <f t="shared" ca="1" si="65"/>
+        <v>15</v>
       </c>
       <c r="L230" s="4" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="66"/>
         <v>-</v>
       </c>
       <c r="M230" t="s">
-        <v>242</v>
+        <v>202</v>
       </c>
       <c r="P230"/>
-      <c r="Q230" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="231" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R230" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="231" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B231" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="C231" t="s">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="E231" t="s">
         <v>16</v>
       </c>
-      <c r="G231" t="s">
-        <v>255</v>
-      </c>
       <c r="H231" s="2">
-        <v>45324</v>
+        <v>45349</v>
       </c>
       <c r="I231" s="4">
-        <f t="shared" ca="1" si="59"/>
-        <v>5</v>
+        <f t="shared" ca="1" si="64"/>
+        <v>2</v>
       </c>
       <c r="J231" s="4">
-        <f t="shared" ca="1" si="60"/>
-        <v>39</v>
-      </c>
-      <c r="K231" s="2">
-        <v>45357</v>
-      </c>
-      <c r="L231" s="4">
-        <f t="shared" si="61"/>
-        <v>33</v>
+        <f t="shared" ca="1" si="65"/>
+        <v>15</v>
+      </c>
+      <c r="L231" s="4" t="str">
+        <f t="shared" si="66"/>
+        <v>-</v>
       </c>
       <c r="M231" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="232" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+        <v>202</v>
+      </c>
+      <c r="P231"/>
+      <c r="R231" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="232" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B232" t="s">
-        <v>34</v>
+        <v>237</v>
       </c>
       <c r="C232" t="s">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="E232" t="s">
-        <v>16</v>
-      </c>
-      <c r="G232" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
       <c r="H232" s="2">
-        <v>45324</v>
+        <v>45355</v>
       </c>
       <c r="I232" s="4">
-        <f t="shared" ca="1" si="59"/>
-        <v>5</v>
+        <f t="shared" ca="1" si="64"/>
+        <v>1</v>
       </c>
       <c r="J232" s="4">
-        <f t="shared" ca="1" si="60"/>
-        <v>39</v>
-      </c>
-      <c r="K232" s="2">
-        <v>45357</v>
-      </c>
-      <c r="L232" s="4">
-        <f t="shared" si="61"/>
-        <v>33</v>
+        <f t="shared" ca="1" si="65"/>
+        <v>9</v>
+      </c>
+      <c r="L232" s="4" t="str">
+        <f t="shared" si="66"/>
+        <v>-</v>
       </c>
       <c r="M232" t="s">
-        <v>253</v>
+        <v>239</v>
+      </c>
+      <c r="P232"/>
+      <c r="Q232" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="233" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -12087,29 +12398,32 @@
       <c r="E233" t="s">
         <v>16</v>
       </c>
+      <c r="F233" s="5" t="s">
+        <v>134</v>
+      </c>
       <c r="G233" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="H233" s="2">
         <v>45324</v>
       </c>
       <c r="I233" s="4">
-        <f t="shared" ca="1" si="59"/>
+        <f t="shared" ca="1" si="64"/>
         <v>5</v>
       </c>
       <c r="J233" s="4">
-        <f t="shared" ca="1" si="60"/>
-        <v>39</v>
+        <f t="shared" ca="1" si="65"/>
+        <v>40</v>
       </c>
       <c r="K233" s="2">
         <v>45357</v>
       </c>
       <c r="L233" s="4">
-        <f t="shared" si="61"/>
+        <f t="shared" si="66"/>
         <v>33</v>
       </c>
       <c r="M233" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
     </row>
     <row r="234" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -12122,29 +12436,32 @@
       <c r="E234" t="s">
         <v>16</v>
       </c>
+      <c r="F234" s="5" t="s">
+        <v>134</v>
+      </c>
       <c r="G234" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="H234" s="2">
         <v>45324</v>
       </c>
       <c r="I234" s="4">
-        <f t="shared" ca="1" si="59"/>
+        <f t="shared" ca="1" si="64"/>
         <v>5</v>
       </c>
       <c r="J234" s="4">
-        <f t="shared" ca="1" si="60"/>
-        <v>39</v>
+        <f t="shared" ca="1" si="65"/>
+        <v>40</v>
       </c>
       <c r="K234" s="2">
         <v>45357</v>
       </c>
       <c r="L234" s="4">
-        <f t="shared" si="61"/>
+        <f t="shared" si="66"/>
         <v>33</v>
       </c>
       <c r="M234" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
     </row>
     <row r="235" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -12157,29 +12474,32 @@
       <c r="E235" t="s">
         <v>16</v>
       </c>
+      <c r="F235" s="5" t="s">
+        <v>134</v>
+      </c>
       <c r="G235" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="H235" s="2">
         <v>45324</v>
       </c>
       <c r="I235" s="4">
-        <f t="shared" ca="1" si="59"/>
+        <f t="shared" ca="1" si="64"/>
         <v>5</v>
       </c>
       <c r="J235" s="4">
-        <f t="shared" ca="1" si="60"/>
-        <v>39</v>
+        <f t="shared" ca="1" si="65"/>
+        <v>40</v>
       </c>
       <c r="K235" s="2">
         <v>45357</v>
       </c>
       <c r="L235" s="4">
-        <f t="shared" si="61"/>
+        <f t="shared" si="66"/>
         <v>33</v>
       </c>
       <c r="M235" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
     </row>
     <row r="236" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -12192,25 +12512,33 @@
       <c r="E236" t="s">
         <v>16</v>
       </c>
+      <c r="F236" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="G236" t="s">
+        <v>251</v>
+      </c>
       <c r="H236" s="2">
         <v>45324</v>
       </c>
       <c r="I236" s="4">
-        <v>4</v>
+        <f t="shared" ca="1" si="64"/>
+        <v>5</v>
       </c>
       <c r="J236" s="4">
-        <v>34</v>
+        <f t="shared" ca="1" si="65"/>
+        <v>40</v>
       </c>
       <c r="K236" s="2">
         <v>45357</v>
       </c>
+      <c r="L236" s="4">
+        <f t="shared" si="66"/>
+        <v>33</v>
+      </c>
       <c r="M236" t="s">
-        <v>254</v>
-      </c>
-      <c r="O236" s="2">
-        <v>45357</v>
-      </c>
-      <c r="P236"/>
+        <v>249</v>
+      </c>
     </row>
     <row r="237" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B237" t="s">
@@ -12222,26 +12550,32 @@
       <c r="E237" t="s">
         <v>16</v>
       </c>
+      <c r="F237" s="5" t="s">
+        <v>134</v>
+      </c>
       <c r="G237" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="H237" s="2">
-        <v>45350</v>
+        <v>45324</v>
       </c>
       <c r="I237" s="4">
-        <f t="shared" ref="I237" ca="1" si="62">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H237), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H237), 7), "-")</f>
-        <v>1</v>
+        <f t="shared" ca="1" si="64"/>
+        <v>5</v>
       </c>
       <c r="J237" s="4">
-        <f t="shared" ref="J237" ca="1" si="63">IF(_xlfn.DAYS(TODAY(),H237)&lt;10000, _xlfn.DAYS(TODAY(),H237), "-")</f>
-        <v>13</v>
-      </c>
-      <c r="L237" s="4" t="str">
-        <f t="shared" ref="L237" si="64">IF(_xlfn.DAYS(K237,H237)&gt;0, _xlfn.DAYS(K237,H237), "-")</f>
-        <v>-</v>
+        <f t="shared" ca="1" si="65"/>
+        <v>40</v>
+      </c>
+      <c r="K237" s="2">
+        <v>45357</v>
+      </c>
+      <c r="L237" s="4">
+        <f t="shared" si="66"/>
+        <v>33</v>
       </c>
       <c r="M237" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
     </row>
     <row r="238" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -12254,27 +12588,25 @@
       <c r="E238" t="s">
         <v>16</v>
       </c>
-      <c r="G238" t="s">
-        <v>255</v>
-      </c>
       <c r="H238" s="2">
-        <v>45350</v>
+        <v>45324</v>
       </c>
       <c r="I238" s="4">
-        <f t="shared" ref="I238" ca="1" si="65">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H238), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H238), 7), "-")</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J238" s="4">
-        <f t="shared" ref="J238" ca="1" si="66">IF(_xlfn.DAYS(TODAY(),H238)&lt;10000, _xlfn.DAYS(TODAY(),H238), "-")</f>
-        <v>13</v>
-      </c>
-      <c r="L238" s="4" t="str">
-        <f t="shared" ref="L238" si="67">IF(_xlfn.DAYS(K238,H238)&gt;0, _xlfn.DAYS(K238,H238), "-")</f>
-        <v>-</v>
+        <v>34</v>
+      </c>
+      <c r="K238" s="2">
+        <v>45357</v>
       </c>
       <c r="M238" t="s">
-        <v>256</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="O238" s="2">
+        <v>45357</v>
+      </c>
+      <c r="P238"/>
     </row>
     <row r="239" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B239" t="s">
@@ -12287,25 +12619,25 @@
         <v>16</v>
       </c>
       <c r="G239" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="H239" s="2">
         <v>45350</v>
       </c>
       <c r="I239" s="4">
-        <f t="shared" ref="I239:I241" ca="1" si="68">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H239), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H239), 7), "-")</f>
-        <v>1</v>
+        <f t="shared" ref="I239" ca="1" si="67">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H239), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H239), 7), "-")</f>
+        <v>2</v>
       </c>
       <c r="J239" s="4">
-        <f t="shared" ref="J239:J241" ca="1" si="69">IF(_xlfn.DAYS(TODAY(),H239)&lt;10000, _xlfn.DAYS(TODAY(),H239), "-")</f>
-        <v>13</v>
+        <f t="shared" ref="J239" ca="1" si="68">IF(_xlfn.DAYS(TODAY(),H239)&lt;10000, _xlfn.DAYS(TODAY(),H239), "-")</f>
+        <v>14</v>
       </c>
       <c r="L239" s="4" t="str">
-        <f t="shared" ref="L239:L255" si="70">IF(_xlfn.DAYS(K239,H239)&gt;0, _xlfn.DAYS(K239,H239), "-")</f>
+        <f t="shared" ref="L239" si="69">IF(_xlfn.DAYS(K239,H239)&gt;0, _xlfn.DAYS(K239,H239), "-")</f>
         <v>-</v>
       </c>
       <c r="M239" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
     </row>
     <row r="240" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -12319,25 +12651,25 @@
         <v>16</v>
       </c>
       <c r="G240" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="H240" s="2">
         <v>45350</v>
       </c>
       <c r="I240" s="4">
-        <f t="shared" ca="1" si="68"/>
-        <v>1</v>
+        <f t="shared" ref="I240" ca="1" si="70">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H240), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H240), 7), "-")</f>
+        <v>2</v>
       </c>
       <c r="J240" s="4">
-        <f t="shared" ca="1" si="69"/>
-        <v>13</v>
+        <f t="shared" ref="J240" ca="1" si="71">IF(_xlfn.DAYS(TODAY(),H240)&lt;10000, _xlfn.DAYS(TODAY(),H240), "-")</f>
+        <v>14</v>
       </c>
       <c r="L240" s="4" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" ref="L240" si="72">IF(_xlfn.DAYS(K240,H240)&gt;0, _xlfn.DAYS(K240,H240), "-")</f>
         <v>-</v>
       </c>
       <c r="M240" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
     </row>
     <row r="241" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -12345,40 +12677,31 @@
         <v>34</v>
       </c>
       <c r="C241" t="s">
-        <v>257</v>
+        <v>110</v>
+      </c>
+      <c r="E241" t="s">
+        <v>16</v>
       </c>
       <c r="G241" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="H241" s="2">
-        <v>45313</v>
+        <v>45350</v>
       </c>
       <c r="I241" s="4">
-        <f t="shared" ca="1" si="68"/>
-        <v>7</v>
+        <f t="shared" ref="I241:I243" ca="1" si="73">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H241), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H241), 7), "-")</f>
+        <v>2</v>
       </c>
       <c r="J241" s="4">
-        <f t="shared" ca="1" si="69"/>
-        <v>50</v>
-      </c>
-      <c r="K241" s="2">
-        <v>45350</v>
-      </c>
-      <c r="L241" s="4">
-        <f t="shared" si="70"/>
-        <v>37</v>
+        <f t="shared" ref="J241:J243" ca="1" si="74">IF(_xlfn.DAYS(TODAY(),H241)&lt;10000, _xlfn.DAYS(TODAY(),H241), "-")</f>
+        <v>14</v>
+      </c>
+      <c r="L241" s="4" t="str">
+        <f t="shared" ref="L241:L258" si="75">IF(_xlfn.DAYS(K241,H241)&gt;0, _xlfn.DAYS(K241,H241), "-")</f>
+        <v>-</v>
       </c>
       <c r="M241" t="s">
-        <v>262</v>
-      </c>
-      <c r="N241" s="2">
-        <v>45353</v>
-      </c>
-      <c r="P241" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="R241" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
     </row>
     <row r="242" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -12386,40 +12709,31 @@
         <v>34</v>
       </c>
       <c r="C242" t="s">
-        <v>257</v>
+        <v>110</v>
+      </c>
+      <c r="E242" t="s">
+        <v>16</v>
       </c>
       <c r="G242" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="H242" s="2">
-        <v>45313</v>
+        <v>45350</v>
       </c>
       <c r="I242" s="4">
-        <f t="shared" ref="I242:I255" ca="1" si="71">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H242), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H242), 7), "-")</f>
-        <v>7</v>
+        <f t="shared" ca="1" si="73"/>
+        <v>2</v>
       </c>
       <c r="J242" s="4">
-        <f t="shared" ref="J242:J255" ca="1" si="72">IF(_xlfn.DAYS(TODAY(),H242)&lt;10000, _xlfn.DAYS(TODAY(),H242), "-")</f>
-        <v>50</v>
-      </c>
-      <c r="K242" s="2">
-        <v>45350</v>
-      </c>
-      <c r="L242" s="4">
-        <f t="shared" si="70"/>
-        <v>37</v>
+        <f t="shared" ca="1" si="74"/>
+        <v>14</v>
+      </c>
+      <c r="L242" s="4" t="str">
+        <f t="shared" si="75"/>
+        <v>-</v>
       </c>
       <c r="M242" t="s">
-        <v>262</v>
-      </c>
-      <c r="N242" s="2">
-        <v>45353</v>
-      </c>
-      <c r="P242" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="R242" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
     </row>
     <row r="243" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -12427,40 +12741,40 @@
         <v>34</v>
       </c>
       <c r="C243" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="G243" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="H243" s="2">
         <v>45313</v>
       </c>
       <c r="I243" s="4">
-        <f t="shared" ca="1" si="71"/>
+        <f t="shared" ca="1" si="73"/>
         <v>7</v>
       </c>
       <c r="J243" s="4">
-        <f t="shared" ca="1" si="72"/>
-        <v>50</v>
+        <f t="shared" ca="1" si="74"/>
+        <v>51</v>
       </c>
       <c r="K243" s="2">
         <v>45350</v>
       </c>
       <c r="L243" s="4">
-        <f t="shared" si="70"/>
+        <f t="shared" si="75"/>
         <v>37</v>
       </c>
       <c r="M243" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="N243" s="2">
         <v>45353</v>
       </c>
       <c r="P243" s="5" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="R243" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
     </row>
     <row r="244" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -12468,40 +12782,40 @@
         <v>34</v>
       </c>
       <c r="C244" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="G244" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="H244" s="2">
         <v>45313</v>
       </c>
       <c r="I244" s="4">
-        <f t="shared" ca="1" si="71"/>
+        <f t="shared" ref="I244:I258" ca="1" si="76">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H244), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H244), 7), "-")</f>
         <v>7</v>
       </c>
       <c r="J244" s="4">
-        <f t="shared" ca="1" si="72"/>
-        <v>50</v>
+        <f t="shared" ref="J244:J258" ca="1" si="77">IF(_xlfn.DAYS(TODAY(),H244)&lt;10000, _xlfn.DAYS(TODAY(),H244), "-")</f>
+        <v>51</v>
       </c>
       <c r="K244" s="2">
         <v>45350</v>
       </c>
       <c r="L244" s="4">
-        <f t="shared" si="70"/>
+        <f t="shared" si="75"/>
         <v>37</v>
       </c>
       <c r="M244" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="N244" s="2">
         <v>45353</v>
       </c>
       <c r="P244" s="5" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="R244" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
     </row>
     <row r="245" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -12509,40 +12823,40 @@
         <v>34</v>
       </c>
       <c r="C245" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="G245" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="H245" s="2">
         <v>45313</v>
       </c>
       <c r="I245" s="4">
-        <f t="shared" ca="1" si="71"/>
+        <f t="shared" ca="1" si="76"/>
         <v>7</v>
       </c>
       <c r="J245" s="4">
-        <f t="shared" ca="1" si="72"/>
-        <v>50</v>
+        <f t="shared" ca="1" si="77"/>
+        <v>51</v>
       </c>
       <c r="K245" s="2">
         <v>45350</v>
       </c>
       <c r="L245" s="4">
-        <f t="shared" si="70"/>
+        <f t="shared" si="75"/>
         <v>37</v>
       </c>
       <c r="M245" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="N245" s="2">
         <v>45353</v>
       </c>
       <c r="P245" s="5" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="R245" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
     </row>
     <row r="246" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -12550,40 +12864,40 @@
         <v>34</v>
       </c>
       <c r="C246" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="G246" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="H246" s="2">
         <v>45313</v>
       </c>
       <c r="I246" s="4">
-        <f t="shared" ca="1" si="71"/>
+        <f t="shared" ca="1" si="76"/>
         <v>7</v>
       </c>
       <c r="J246" s="4">
-        <f t="shared" ca="1" si="72"/>
-        <v>50</v>
+        <f t="shared" ca="1" si="77"/>
+        <v>51</v>
       </c>
       <c r="K246" s="2">
         <v>45350</v>
       </c>
       <c r="L246" s="4">
-        <f t="shared" si="70"/>
+        <f t="shared" si="75"/>
         <v>37</v>
       </c>
       <c r="M246" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="N246" s="2">
         <v>45353</v>
       </c>
       <c r="P246" s="5" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="R246" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
     </row>
     <row r="247" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -12591,40 +12905,40 @@
         <v>34</v>
       </c>
       <c r="C247" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="G247" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="H247" s="2">
         <v>45313</v>
       </c>
       <c r="I247" s="4">
-        <f t="shared" ca="1" si="71"/>
+        <f t="shared" ca="1" si="76"/>
         <v>7</v>
       </c>
       <c r="J247" s="4">
-        <f t="shared" ca="1" si="72"/>
-        <v>50</v>
+        <f t="shared" ca="1" si="77"/>
+        <v>51</v>
       </c>
       <c r="K247" s="2">
         <v>45350</v>
       </c>
       <c r="L247" s="4">
-        <f t="shared" si="70"/>
+        <f t="shared" si="75"/>
         <v>37</v>
       </c>
       <c r="M247" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="N247" s="2">
         <v>45353</v>
       </c>
       <c r="P247" s="5" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="R247" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
     </row>
     <row r="248" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -12632,40 +12946,40 @@
         <v>34</v>
       </c>
       <c r="C248" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="G248" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="H248" s="2">
         <v>45313</v>
       </c>
       <c r="I248" s="4">
-        <f t="shared" ca="1" si="71"/>
+        <f t="shared" ca="1" si="76"/>
         <v>7</v>
       </c>
       <c r="J248" s="4">
-        <f t="shared" ca="1" si="72"/>
-        <v>50</v>
+        <f t="shared" ca="1" si="77"/>
+        <v>51</v>
       </c>
       <c r="K248" s="2">
         <v>45350</v>
       </c>
       <c r="L248" s="4">
-        <f t="shared" si="70"/>
+        <f t="shared" si="75"/>
         <v>37</v>
       </c>
       <c r="M248" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="N248" s="2">
         <v>45353</v>
       </c>
       <c r="P248" s="5" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="R248" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
     </row>
     <row r="249" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -12673,40 +12987,40 @@
         <v>34</v>
       </c>
       <c r="C249" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="G249" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="H249" s="2">
         <v>45313</v>
       </c>
       <c r="I249" s="4">
-        <f t="shared" ca="1" si="71"/>
+        <f t="shared" ca="1" si="76"/>
         <v>7</v>
       </c>
       <c r="J249" s="4">
-        <f t="shared" ca="1" si="72"/>
-        <v>50</v>
+        <f t="shared" ca="1" si="77"/>
+        <v>51</v>
       </c>
       <c r="K249" s="2">
         <v>45350</v>
       </c>
       <c r="L249" s="4">
-        <f t="shared" si="70"/>
+        <f t="shared" si="75"/>
         <v>37</v>
       </c>
       <c r="M249" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="N249" s="2">
         <v>45353</v>
       </c>
       <c r="P249" s="5" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="R249" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
     </row>
     <row r="250" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -12714,40 +13028,40 @@
         <v>34</v>
       </c>
       <c r="C250" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="G250" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="H250" s="2">
         <v>45313</v>
       </c>
       <c r="I250" s="4">
-        <f t="shared" ca="1" si="71"/>
+        <f t="shared" ca="1" si="76"/>
         <v>7</v>
       </c>
       <c r="J250" s="4">
-        <f t="shared" ca="1" si="72"/>
-        <v>50</v>
+        <f t="shared" ca="1" si="77"/>
+        <v>51</v>
       </c>
       <c r="K250" s="2">
         <v>45350</v>
       </c>
       <c r="L250" s="4">
-        <f t="shared" si="70"/>
+        <f t="shared" si="75"/>
         <v>37</v>
       </c>
       <c r="M250" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="N250" s="2">
         <v>45353</v>
       </c>
       <c r="P250" s="5" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="R250" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
     </row>
     <row r="251" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -12755,40 +13069,40 @@
         <v>34</v>
       </c>
       <c r="C251" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="G251" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="H251" s="2">
         <v>45313</v>
       </c>
       <c r="I251" s="4">
-        <f t="shared" ca="1" si="71"/>
+        <f t="shared" ca="1" si="76"/>
         <v>7</v>
       </c>
       <c r="J251" s="4">
-        <f t="shared" ca="1" si="72"/>
-        <v>50</v>
+        <f t="shared" ca="1" si="77"/>
+        <v>51</v>
       </c>
       <c r="K251" s="2">
         <v>45350</v>
       </c>
       <c r="L251" s="4">
-        <f t="shared" si="70"/>
+        <f t="shared" si="75"/>
         <v>37</v>
       </c>
       <c r="M251" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="N251" s="2">
         <v>45353</v>
       </c>
       <c r="P251" s="5" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="R251" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
     </row>
     <row r="252" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -12796,40 +13110,40 @@
         <v>34</v>
       </c>
       <c r="C252" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="G252" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="H252" s="2">
         <v>45313</v>
       </c>
       <c r="I252" s="4">
-        <f t="shared" ca="1" si="71"/>
+        <f t="shared" ca="1" si="76"/>
         <v>7</v>
       </c>
       <c r="J252" s="4">
-        <f t="shared" ca="1" si="72"/>
-        <v>50</v>
+        <f t="shared" ca="1" si="77"/>
+        <v>51</v>
       </c>
       <c r="K252" s="2">
         <v>45350</v>
       </c>
       <c r="L252" s="4">
-        <f t="shared" si="70"/>
+        <f t="shared" si="75"/>
         <v>37</v>
       </c>
       <c r="M252" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="N252" s="2">
         <v>45353</v>
       </c>
       <c r="P252" s="5" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="R252" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
     </row>
     <row r="253" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -12837,40 +13151,40 @@
         <v>34</v>
       </c>
       <c r="C253" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="G253" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="H253" s="2">
         <v>45313</v>
       </c>
       <c r="I253" s="4">
-        <f t="shared" ca="1" si="71"/>
+        <f t="shared" ca="1" si="76"/>
         <v>7</v>
       </c>
       <c r="J253" s="4">
-        <f t="shared" ca="1" si="72"/>
-        <v>50</v>
+        <f t="shared" ca="1" si="77"/>
+        <v>51</v>
       </c>
       <c r="K253" s="2">
         <v>45350</v>
       </c>
       <c r="L253" s="4">
-        <f t="shared" si="70"/>
+        <f t="shared" si="75"/>
         <v>37</v>
       </c>
       <c r="M253" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="N253" s="2">
         <v>45353</v>
       </c>
       <c r="P253" s="5" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="R253" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
     </row>
     <row r="254" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -12878,40 +13192,40 @@
         <v>34</v>
       </c>
       <c r="C254" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="G254" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="H254" s="2">
         <v>45313</v>
       </c>
       <c r="I254" s="4">
-        <f t="shared" ca="1" si="71"/>
+        <f t="shared" ca="1" si="76"/>
         <v>7</v>
       </c>
       <c r="J254" s="4">
-        <f t="shared" ca="1" si="72"/>
-        <v>50</v>
+        <f t="shared" ca="1" si="77"/>
+        <v>51</v>
       </c>
       <c r="K254" s="2">
         <v>45350</v>
       </c>
       <c r="L254" s="4">
-        <f t="shared" si="70"/>
+        <f t="shared" si="75"/>
         <v>37</v>
       </c>
       <c r="M254" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="N254" s="2">
         <v>45353</v>
       </c>
       <c r="P254" s="5" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="R254" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
     </row>
     <row r="255" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -12919,47 +13233,309 @@
         <v>34</v>
       </c>
       <c r="C255" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="G255" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="H255" s="2">
         <v>45313</v>
       </c>
       <c r="I255" s="4">
-        <f t="shared" ca="1" si="71"/>
+        <f t="shared" ca="1" si="76"/>
         <v>7</v>
       </c>
       <c r="J255" s="4">
-        <f t="shared" ca="1" si="72"/>
-        <v>50</v>
+        <f t="shared" ca="1" si="77"/>
+        <v>51</v>
       </c>
       <c r="K255" s="2">
         <v>45350</v>
       </c>
       <c r="L255" s="4">
-        <f t="shared" si="70"/>
+        <f t="shared" si="75"/>
         <v>37</v>
       </c>
       <c r="M255" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="N255" s="2">
         <v>45353</v>
       </c>
       <c r="P255" s="5" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="R255" t="s">
-        <v>261</v>
+        <v>257</v>
+      </c>
+    </row>
+    <row r="256" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B256" t="s">
+        <v>34</v>
+      </c>
+      <c r="C256" t="s">
+        <v>253</v>
+      </c>
+      <c r="G256" t="s">
+        <v>251</v>
+      </c>
+      <c r="H256" s="2">
+        <v>45313</v>
+      </c>
+      <c r="I256" s="4">
+        <f t="shared" ca="1" si="76"/>
+        <v>7</v>
+      </c>
+      <c r="J256" s="4">
+        <f t="shared" ca="1" si="77"/>
+        <v>51</v>
+      </c>
+      <c r="K256" s="2">
+        <v>45350</v>
+      </c>
+      <c r="L256" s="4">
+        <f t="shared" si="75"/>
+        <v>37</v>
+      </c>
+      <c r="M256" t="s">
+        <v>260</v>
+      </c>
+      <c r="N256" s="2">
+        <v>45353</v>
+      </c>
+      <c r="P256" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="R256" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="257" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B257" t="s">
+        <v>34</v>
+      </c>
+      <c r="C257" t="s">
+        <v>253</v>
+      </c>
+      <c r="G257" t="s">
+        <v>251</v>
+      </c>
+      <c r="H257" s="2">
+        <v>45313</v>
+      </c>
+      <c r="I257" s="4">
+        <f t="shared" ca="1" si="76"/>
+        <v>7</v>
+      </c>
+      <c r="J257" s="4">
+        <f t="shared" ca="1" si="77"/>
+        <v>51</v>
+      </c>
+      <c r="K257" s="2">
+        <v>45350</v>
+      </c>
+      <c r="L257" s="4">
+        <f t="shared" si="75"/>
+        <v>37</v>
+      </c>
+      <c r="M257" t="s">
+        <v>260</v>
+      </c>
+      <c r="N257" s="2">
+        <v>45353</v>
+      </c>
+      <c r="P257" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="R257" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="258" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B258" t="s">
+        <v>5</v>
+      </c>
+      <c r="C258" t="s">
+        <v>127</v>
+      </c>
+      <c r="E258" t="s">
+        <v>16</v>
+      </c>
+      <c r="H258" s="2">
+        <v>45363</v>
+      </c>
+      <c r="I258" s="4">
+        <f t="shared" ca="1" si="76"/>
+        <v>0</v>
+      </c>
+      <c r="J258" s="4">
+        <f t="shared" ca="1" si="77"/>
+        <v>1</v>
+      </c>
+      <c r="L258" s="4" t="str">
+        <f t="shared" si="75"/>
+        <v>-</v>
+      </c>
+      <c r="M258" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="259" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B259" t="s">
+        <v>5</v>
+      </c>
+      <c r="C259" t="s">
+        <v>127</v>
+      </c>
+      <c r="E259" t="s">
+        <v>16</v>
+      </c>
+      <c r="H259" s="2">
+        <v>45363</v>
+      </c>
+      <c r="I259" s="4">
+        <f t="shared" ref="I259:I263" ca="1" si="78">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H259), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H259), 7), "-")</f>
+        <v>0</v>
+      </c>
+      <c r="J259" s="4">
+        <f t="shared" ref="J259:J263" ca="1" si="79">IF(_xlfn.DAYS(TODAY(),H259)&lt;10000, _xlfn.DAYS(TODAY(),H259), "-")</f>
+        <v>1</v>
+      </c>
+      <c r="L259" s="4" t="str">
+        <f t="shared" ref="L259:L263" si="80">IF(_xlfn.DAYS(K259,H259)&gt;0, _xlfn.DAYS(K259,H259), "-")</f>
+        <v>-</v>
+      </c>
+      <c r="M259" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="260" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B260" t="s">
+        <v>5</v>
+      </c>
+      <c r="C260" t="s">
+        <v>127</v>
+      </c>
+      <c r="E260" t="s">
+        <v>16</v>
+      </c>
+      <c r="H260" s="2">
+        <v>45363</v>
+      </c>
+      <c r="I260" s="4">
+        <f t="shared" ca="1" si="78"/>
+        <v>0</v>
+      </c>
+      <c r="J260" s="4">
+        <f t="shared" ca="1" si="79"/>
+        <v>1</v>
+      </c>
+      <c r="L260" s="4" t="str">
+        <f t="shared" si="80"/>
+        <v>-</v>
+      </c>
+      <c r="M260" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="261" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B261" t="s">
+        <v>5</v>
+      </c>
+      <c r="C261" t="s">
+        <v>127</v>
+      </c>
+      <c r="E261" t="s">
+        <v>16</v>
+      </c>
+      <c r="H261" s="2">
+        <v>45363</v>
+      </c>
+      <c r="I261" s="4">
+        <f t="shared" ca="1" si="78"/>
+        <v>0</v>
+      </c>
+      <c r="J261" s="4">
+        <f t="shared" ca="1" si="79"/>
+        <v>1</v>
+      </c>
+      <c r="L261" s="4" t="str">
+        <f t="shared" si="80"/>
+        <v>-</v>
+      </c>
+      <c r="M261" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="262" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B262" t="s">
+        <v>5</v>
+      </c>
+      <c r="C262" t="s">
+        <v>127</v>
+      </c>
+      <c r="E262" t="s">
+        <v>274</v>
+      </c>
+      <c r="H262" s="2">
+        <v>45363</v>
+      </c>
+      <c r="I262" s="4">
+        <f t="shared" ca="1" si="78"/>
+        <v>0</v>
+      </c>
+      <c r="J262" s="4">
+        <f t="shared" ca="1" si="79"/>
+        <v>1</v>
+      </c>
+      <c r="L262" s="4" t="str">
+        <f t="shared" si="80"/>
+        <v>-</v>
+      </c>
+      <c r="M262" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="263" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B263" t="s">
+        <v>5</v>
+      </c>
+      <c r="C263" t="s">
+        <v>127</v>
+      </c>
+      <c r="E263" t="s">
+        <v>274</v>
+      </c>
+      <c r="H263" s="2">
+        <v>45363</v>
+      </c>
+      <c r="I263" s="4">
+        <f t="shared" ca="1" si="78"/>
+        <v>0</v>
+      </c>
+      <c r="J263" s="4">
+        <f t="shared" ca="1" si="79"/>
+        <v>1</v>
+      </c>
+      <c r="L263" s="4" t="str">
+        <f t="shared" si="80"/>
+        <v>-</v>
+      </c>
+      <c r="M263" t="s">
+        <v>273</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B1:R255" xr:uid="{8D08DEC4-803F-4130-9E5E-30A83401A29D}">
+  <autoFilter ref="B1:R263" xr:uid="{8D08DEC4-803F-4130-9E5E-30A83401A29D}">
     <filterColumn colId="0">
       <filters>
         <filter val="SPF"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Tcrd-CreER; Tsg101-flox"/>
+        <filter val="Tmem119-CreERT2; Cd36-flox"/>
       </filters>
     </filterColumn>
     <filterColumn colId="13">
@@ -12967,272 +13543,272 @@
     </filterColumn>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="M155:M158 M226:M230 M160 M162 M164:M172 M31:M41 M43:M59 M1:M27 M128:M129 M131:M132 M134 M136:M153 M65:M68 M175:M224 M62 M70:M126 M241:M1048576">
-    <cfRule type="containsText" dxfId="65" priority="71" operator="containsText" text=".X">
+  <conditionalFormatting sqref="M155:M158 M228:M232 M160 M162 M164:M172 M31:M41 M43:M59 M1:M27 M128:M129 M131:M132 M134 M136:M153 M65:M68 M62 M70:M126 M175:M226 M243:M1048576">
+    <cfRule type="containsText" dxfId="65" priority="73" operator="containsText" text=".X">
       <formula>NOT(ISERROR(SEARCH(".X",M1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="64" priority="72" operator="containsText" text=".B">
+    <cfRule type="containsText" dxfId="64" priority="74" operator="containsText" text=".B">
       <formula>NOT(ISERROR(SEARCH(".B",M1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M154">
-    <cfRule type="containsText" dxfId="63" priority="69" operator="containsText" text=".X">
+    <cfRule type="containsText" dxfId="63" priority="71" operator="containsText" text=".X">
       <formula>NOT(ISERROR(SEARCH(".X",M154)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="62" priority="70" operator="containsText" text=".B">
+    <cfRule type="containsText" dxfId="62" priority="72" operator="containsText" text=".B">
       <formula>NOT(ISERROR(SEARCH(".B",M154)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M225">
+  <conditionalFormatting sqref="M159">
     <cfRule type="containsText" dxfId="61" priority="67" operator="containsText" text=".X">
-      <formula>NOT(ISERROR(SEARCH(".X",M225)))</formula>
+      <formula>NOT(ISERROR(SEARCH(".X",M159)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="60" priority="68" operator="containsText" text=".B">
-      <formula>NOT(ISERROR(SEARCH(".B",M225)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M159">
-    <cfRule type="containsText" dxfId="59" priority="65" operator="containsText" text=".X">
-      <formula>NOT(ISERROR(SEARCH(".X",M159)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="58" priority="66" operator="containsText" text=".B">
       <formula>NOT(ISERROR(SEARCH(".B",M159)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M161">
-    <cfRule type="containsText" dxfId="57" priority="63" operator="containsText" text=".X">
+    <cfRule type="containsText" dxfId="59" priority="65" operator="containsText" text=".X">
       <formula>NOT(ISERROR(SEARCH(".X",M161)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="56" priority="64" operator="containsText" text=".B">
+    <cfRule type="containsText" dxfId="58" priority="66" operator="containsText" text=".B">
       <formula>NOT(ISERROR(SEARCH(".B",M161)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M163">
-    <cfRule type="containsText" dxfId="55" priority="61" operator="containsText" text=".X">
+    <cfRule type="containsText" dxfId="57" priority="63" operator="containsText" text=".X">
       <formula>NOT(ISERROR(SEARCH(".X",M163)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="54" priority="62" operator="containsText" text=".B">
+    <cfRule type="containsText" dxfId="56" priority="64" operator="containsText" text=".B">
       <formula>NOT(ISERROR(SEARCH(".B",M163)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M173">
-    <cfRule type="containsText" dxfId="53" priority="59" operator="containsText" text=".X">
+    <cfRule type="containsText" dxfId="55" priority="61" operator="containsText" text=".X">
       <formula>NOT(ISERROR(SEARCH(".X",M173)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="52" priority="60" operator="containsText" text=".B">
+    <cfRule type="containsText" dxfId="54" priority="62" operator="containsText" text=".B">
       <formula>NOT(ISERROR(SEARCH(".B",M173)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M174">
-    <cfRule type="containsText" dxfId="51" priority="57" operator="containsText" text=".X">
+    <cfRule type="containsText" dxfId="53" priority="59" operator="containsText" text=".X">
       <formula>NOT(ISERROR(SEARCH(".X",M174)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="50" priority="58" operator="containsText" text=".B">
+    <cfRule type="containsText" dxfId="52" priority="60" operator="containsText" text=".B">
       <formula>NOT(ISERROR(SEARCH(".B",M174)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M30">
-    <cfRule type="containsText" dxfId="49" priority="53" operator="containsText" text=".X">
+    <cfRule type="containsText" dxfId="51" priority="55" operator="containsText" text=".X">
       <formula>NOT(ISERROR(SEARCH(".X",M30)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="48" priority="54" operator="containsText" text=".B">
+    <cfRule type="containsText" dxfId="50" priority="56" operator="containsText" text=".B">
       <formula>NOT(ISERROR(SEARCH(".B",M30)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M42">
-    <cfRule type="containsText" dxfId="47" priority="51" operator="containsText" text=".X">
+    <cfRule type="containsText" dxfId="49" priority="53" operator="containsText" text=".X">
       <formula>NOT(ISERROR(SEARCH(".X",M42)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="46" priority="52" operator="containsText" text=".B">
+    <cfRule type="containsText" dxfId="48" priority="54" operator="containsText" text=".B">
       <formula>NOT(ISERROR(SEARCH(".B",M42)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M29">
-    <cfRule type="containsText" dxfId="45" priority="49" operator="containsText" text=".X">
+    <cfRule type="containsText" dxfId="47" priority="51" operator="containsText" text=".X">
       <formula>NOT(ISERROR(SEARCH(".X",M29)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="44" priority="50" operator="containsText" text=".B">
+    <cfRule type="containsText" dxfId="46" priority="52" operator="containsText" text=".B">
       <formula>NOT(ISERROR(SEARCH(".B",M29)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M28">
-    <cfRule type="containsText" dxfId="43" priority="47" operator="containsText" text=".X">
+    <cfRule type="containsText" dxfId="45" priority="49" operator="containsText" text=".X">
       <formula>NOT(ISERROR(SEARCH(".X",M28)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="42" priority="48" operator="containsText" text=".B">
+    <cfRule type="containsText" dxfId="44" priority="50" operator="containsText" text=".B">
       <formula>NOT(ISERROR(SEARCH(".B",M28)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R131">
-    <cfRule type="containsText" dxfId="41" priority="43" operator="containsText" text=".X">
+    <cfRule type="containsText" dxfId="43" priority="45" operator="containsText" text=".X">
       <formula>NOT(ISERROR(SEARCH(".X",R131)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="40" priority="44" operator="containsText" text=".B">
+    <cfRule type="containsText" dxfId="42" priority="46" operator="containsText" text=".B">
       <formula>NOT(ISERROR(SEARCH(".B",R131)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R132">
-    <cfRule type="containsText" dxfId="39" priority="41" operator="containsText" text=".X">
+    <cfRule type="containsText" dxfId="41" priority="43" operator="containsText" text=".X">
       <formula>NOT(ISERROR(SEARCH(".X",R132)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="38" priority="42" operator="containsText" text=".B">
+    <cfRule type="containsText" dxfId="40" priority="44" operator="containsText" text=".B">
       <formula>NOT(ISERROR(SEARCH(".B",R132)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R134:R135">
-    <cfRule type="containsText" dxfId="37" priority="39" operator="containsText" text=".X">
+    <cfRule type="containsText" dxfId="39" priority="41" operator="containsText" text=".X">
       <formula>NOT(ISERROR(SEARCH(".X",R134)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="36" priority="40" operator="containsText" text=".B">
+    <cfRule type="containsText" dxfId="38" priority="42" operator="containsText" text=".B">
       <formula>NOT(ISERROR(SEARCH(".B",R134)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M135">
-    <cfRule type="containsText" dxfId="35" priority="37" operator="containsText" text=".X">
+    <cfRule type="containsText" dxfId="37" priority="39" operator="containsText" text=".X">
       <formula>NOT(ISERROR(SEARCH(".X",M135)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="34" priority="38" operator="containsText" text=".B">
+    <cfRule type="containsText" dxfId="36" priority="40" operator="containsText" text=".B">
       <formula>NOT(ISERROR(SEARCH(".B",M135)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M127">
-    <cfRule type="containsText" dxfId="33" priority="35" operator="containsText" text=".X">
+    <cfRule type="containsText" dxfId="35" priority="37" operator="containsText" text=".X">
       <formula>NOT(ISERROR(SEARCH(".X",M127)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="32" priority="36" operator="containsText" text=".B">
+    <cfRule type="containsText" dxfId="34" priority="38" operator="containsText" text=".B">
       <formula>NOT(ISERROR(SEARCH(".B",M127)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R127">
-    <cfRule type="containsText" dxfId="31" priority="33" operator="containsText" text=".X">
+    <cfRule type="containsText" dxfId="33" priority="35" operator="containsText" text=".X">
       <formula>NOT(ISERROR(SEARCH(".X",R127)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="30" priority="34" operator="containsText" text=".B">
+    <cfRule type="containsText" dxfId="32" priority="36" operator="containsText" text=".B">
       <formula>NOT(ISERROR(SEARCH(".B",R127)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M130">
-    <cfRule type="containsText" dxfId="29" priority="31" operator="containsText" text=".X">
+    <cfRule type="containsText" dxfId="31" priority="33" operator="containsText" text=".X">
       <formula>NOT(ISERROR(SEARCH(".X",M130)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="28" priority="32" operator="containsText" text=".B">
+    <cfRule type="containsText" dxfId="30" priority="34" operator="containsText" text=".B">
       <formula>NOT(ISERROR(SEARCH(".B",M130)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M133">
-    <cfRule type="containsText" dxfId="27" priority="29" operator="containsText" text=".X">
+    <cfRule type="containsText" dxfId="29" priority="31" operator="containsText" text=".X">
       <formula>NOT(ISERROR(SEARCH(".X",M133)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="26" priority="30" operator="containsText" text=".B">
+    <cfRule type="containsText" dxfId="28" priority="32" operator="containsText" text=".B">
       <formula>NOT(ISERROR(SEARCH(".B",M133)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M63:M64">
-    <cfRule type="containsText" dxfId="25" priority="27" operator="containsText" text=".X">
+    <cfRule type="containsText" dxfId="27" priority="29" operator="containsText" text=".X">
       <formula>NOT(ISERROR(SEARCH(".X",M63)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="24" priority="28" operator="containsText" text=".B">
+    <cfRule type="containsText" dxfId="26" priority="30" operator="containsText" text=".B">
       <formula>NOT(ISERROR(SEARCH(".B",M63)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M69">
-    <cfRule type="containsText" dxfId="23" priority="25" operator="containsText" text=".X">
+    <cfRule type="containsText" dxfId="25" priority="27" operator="containsText" text=".X">
       <formula>NOT(ISERROR(SEARCH(".X",M69)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="22" priority="26" operator="containsText" text=".B">
+    <cfRule type="containsText" dxfId="24" priority="28" operator="containsText" text=".B">
       <formula>NOT(ISERROR(SEARCH(".B",M69)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M60:M61">
-    <cfRule type="containsText" dxfId="21" priority="23" operator="containsText" text=".X">
+    <cfRule type="containsText" dxfId="23" priority="25" operator="containsText" text=".X">
       <formula>NOT(ISERROR(SEARCH(".X",M60)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="20" priority="24" operator="containsText" text=".B">
+    <cfRule type="containsText" dxfId="22" priority="26" operator="containsText" text=".B">
       <formula>NOT(ISERROR(SEARCH(".B",M60)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M231">
-    <cfRule type="containsText" dxfId="19" priority="19" operator="containsText" text=".X">
-      <formula>NOT(ISERROR(SEARCH(".X",M231)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="18" priority="20" operator="containsText" text=".B">
-      <formula>NOT(ISERROR(SEARCH(".B",M231)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M232">
-    <cfRule type="containsText" dxfId="17" priority="17" operator="containsText" text=".X">
-      <formula>NOT(ISERROR(SEARCH(".X",M232)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="16" priority="18" operator="containsText" text=".B">
-      <formula>NOT(ISERROR(SEARCH(".B",M232)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="M233">
-    <cfRule type="containsText" dxfId="15" priority="15" operator="containsText" text=".X">
+    <cfRule type="containsText" dxfId="21" priority="21" operator="containsText" text=".X">
       <formula>NOT(ISERROR(SEARCH(".X",M233)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="14" priority="16" operator="containsText" text=".B">
+    <cfRule type="containsText" dxfId="20" priority="22" operator="containsText" text=".B">
       <formula>NOT(ISERROR(SEARCH(".B",M233)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M234">
-    <cfRule type="containsText" dxfId="13" priority="13" operator="containsText" text=".X">
+    <cfRule type="containsText" dxfId="19" priority="19" operator="containsText" text=".X">
       <formula>NOT(ISERROR(SEARCH(".X",M234)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="14" operator="containsText" text=".B">
+    <cfRule type="containsText" dxfId="18" priority="20" operator="containsText" text=".B">
       <formula>NOT(ISERROR(SEARCH(".B",M234)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M235">
-    <cfRule type="containsText" dxfId="11" priority="11" operator="containsText" text=".X">
+    <cfRule type="containsText" dxfId="17" priority="17" operator="containsText" text=".X">
       <formula>NOT(ISERROR(SEARCH(".X",M235)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="10" priority="12" operator="containsText" text=".B">
+    <cfRule type="containsText" dxfId="16" priority="18" operator="containsText" text=".B">
       <formula>NOT(ISERROR(SEARCH(".B",M235)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M236">
-    <cfRule type="containsText" dxfId="9" priority="9" operator="containsText" text=".X">
+    <cfRule type="containsText" dxfId="15" priority="15" operator="containsText" text=".X">
       <formula>NOT(ISERROR(SEARCH(".X",M236)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="10" operator="containsText" text=".B">
+    <cfRule type="containsText" dxfId="14" priority="16" operator="containsText" text=".B">
       <formula>NOT(ISERROR(SEARCH(".B",M236)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M237">
-    <cfRule type="containsText" dxfId="7" priority="7" operator="containsText" text=".X">
+    <cfRule type="containsText" dxfId="13" priority="13" operator="containsText" text=".X">
       <formula>NOT(ISERROR(SEARCH(".X",M237)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="8" operator="containsText" text=".B">
+    <cfRule type="containsText" dxfId="12" priority="14" operator="containsText" text=".B">
       <formula>NOT(ISERROR(SEARCH(".B",M237)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M238">
-    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text=".X">
+    <cfRule type="containsText" dxfId="11" priority="11" operator="containsText" text=".X">
       <formula>NOT(ISERROR(SEARCH(".X",M238)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="6" operator="containsText" text=".B">
+    <cfRule type="containsText" dxfId="10" priority="12" operator="containsText" text=".B">
       <formula>NOT(ISERROR(SEARCH(".B",M238)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M239">
-    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text=".X">
+    <cfRule type="containsText" dxfId="9" priority="9" operator="containsText" text=".X">
       <formula>NOT(ISERROR(SEARCH(".X",M239)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text=".B">
+    <cfRule type="containsText" dxfId="8" priority="10" operator="containsText" text=".B">
       <formula>NOT(ISERROR(SEARCH(".B",M239)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M240">
-    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text=".X">
+    <cfRule type="containsText" dxfId="7" priority="7" operator="containsText" text=".X">
       <formula>NOT(ISERROR(SEARCH(".X",M240)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text=".B">
+    <cfRule type="containsText" dxfId="6" priority="8" operator="containsText" text=".B">
       <formula>NOT(ISERROR(SEARCH(".B",M240)))</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="M241">
+    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text=".X">
+      <formula>NOT(ISERROR(SEARCH(".X",M241)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="6" operator="containsText" text=".B">
+      <formula>NOT(ISERROR(SEARCH(".B",M241)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M242">
+    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text=".X">
+      <formula>NOT(ISERROR(SEARCH(".X",M242)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text=".B">
+      <formula>NOT(ISERROR(SEARCH(".B",M242)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M227">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text=".X">
+      <formula>NOT(ISERROR(SEARCH(".X",M227)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text=".B">
+      <formula>NOT(ISERROR(SEARCH(".B",M227)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E157:E159 E148:E150 E1:E141 E190:E217 E219:E220 E161:E188 E222:E1048576" xr:uid="{939E2B39-E841-4A9F-AD11-00C266DB2690}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E157:E159 E148:E150 E1:E141 E192:E219 E221:E222 E161:E190 E224:E1048576" xr:uid="{939E2B39-E841-4A9F-AD11-00C266DB2690}">
       <formula1>"Y, N"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1:G1048576" xr:uid="{2DE54AC7-5B92-48D6-98C4-E6203F87CDD0}">

--- a/Mouse 내역.xlsx
+++ b/Mouse 내역.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\heung\Dropbox\02. Lab. of Host Defenses\03. 동물실\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F2D288F-A971-4D9C-9BC9-73619A284476}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{350CD658-6ACF-4146-9DDF-71B584CA6BF6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="495" windowWidth="28800" windowHeight="16245" xr2:uid="{5A73A69A-2AFB-4F3E-AC64-070DD7700CB2}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1804" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1841" uniqueCount="291">
   <si>
     <t>Strain</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1058,10 +1058,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Control</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Tamoxifen</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1119,6 +1115,66 @@
   </si>
   <si>
     <t>weaning, genotyping</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>L1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>L2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R1L1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Exp. 1-11-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>L1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>L2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R1L1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>corn oil</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tamoxifen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Corn oil</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1126,6 +1182,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
+  </numFmts>
   <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1304,7 +1363,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1363,6 +1422,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2488,7 +2550,7 @@
     <col min="9" max="10" width="9" customWidth="1"/>
     <col min="11" max="11" width="11.125" style="2" customWidth="1"/>
     <col min="12" max="12" width="8.125" customWidth="1"/>
-    <col min="14" max="14" width="11.375" style="2" customWidth="1"/>
+    <col min="14" max="14" width="11.375" style="2" hidden="1" customWidth="1"/>
     <col min="15" max="15" width="12.625" style="2" customWidth="1"/>
     <col min="16" max="16" width="13.125" style="5" customWidth="1"/>
     <col min="17" max="17" width="23.75" customWidth="1"/>
@@ -2569,11 +2631,11 @@
       </c>
       <c r="I2" s="4">
         <f ca="1">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H2), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H2), 7), "-")</f>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J2" s="4">
         <f ca="1">IF(_xlfn.DAYS(TODAY(),H2)&lt;10000, _xlfn.DAYS(TODAY(),H2), "-")</f>
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="L2" s="4" t="str">
         <f t="shared" ref="L2:L29" si="0">IF(_xlfn.DAYS(K2,H2)&gt;0, _xlfn.DAYS(K2,H2), "-")</f>
@@ -2609,11 +2671,11 @@
       </c>
       <c r="I3" s="4">
         <f t="shared" ref="I3:I69" ca="1" si="1">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H3), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H3), 7), "-")</f>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J3" s="4">
         <f t="shared" ref="J3:J29" ca="1" si="2">IF(_xlfn.DAYS(TODAY(),H3)&lt;10000, _xlfn.DAYS(TODAY(),H3), "-")</f>
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="L3" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2652,11 +2714,11 @@
       </c>
       <c r="I4" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J4" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="L4" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2702,7 +2764,7 @@
       </c>
       <c r="J5" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="K5" s="2">
         <v>45293</v>
@@ -2748,7 +2810,7 @@
       </c>
       <c r="J6" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="K6" s="2">
         <v>45293</v>
@@ -2769,7 +2831,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="7" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>5</v>
       </c>
@@ -2797,7 +2859,7 @@
       </c>
       <c r="J7" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="K7" s="2">
         <v>45293</v>
@@ -2841,7 +2903,7 @@
       </c>
       <c r="J8" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="K8" s="2">
         <v>45293</v>
@@ -2887,7 +2949,7 @@
       </c>
       <c r="J9" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="K9" s="2">
         <v>45293</v>
@@ -2926,11 +2988,11 @@
       </c>
       <c r="I10" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J10" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="L10" s="4" t="str">
         <f t="shared" si="0"/>
@@ -3047,7 +3109,7 @@
       </c>
       <c r="J13" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="L13" s="4" t="str">
         <f t="shared" si="0"/>
@@ -3093,7 +3155,7 @@
       </c>
       <c r="J14" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="L14" s="4" t="str">
         <f t="shared" si="0"/>
@@ -3139,7 +3201,7 @@
       </c>
       <c r="J15" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="L15" s="4" t="str">
         <f t="shared" si="0"/>
@@ -3184,7 +3246,7 @@
       </c>
       <c r="J16" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="L16" s="4" t="str">
         <f t="shared" si="0"/>
@@ -3226,7 +3288,7 @@
       </c>
       <c r="J17" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="L17" s="4" t="str">
         <f t="shared" si="0"/>
@@ -3268,7 +3330,7 @@
       </c>
       <c r="J18" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="L18" s="4" t="str">
         <f t="shared" si="0"/>
@@ -3339,11 +3401,11 @@
       </c>
       <c r="I20" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J20" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="K20" s="2">
         <v>45112</v>
@@ -3385,7 +3447,7 @@
       </c>
       <c r="J21" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="K21" s="2">
         <v>45176</v>
@@ -3430,7 +3492,7 @@
       </c>
       <c r="J22" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="K22" s="2">
         <v>45176</v>
@@ -3475,7 +3537,7 @@
       </c>
       <c r="J23" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="K23" s="2">
         <v>45176</v>
@@ -3520,7 +3582,7 @@
       </c>
       <c r="J24" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="K24" s="2">
         <v>45229</v>
@@ -3562,7 +3624,7 @@
       </c>
       <c r="J25" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="K25" s="2">
         <v>45229</v>
@@ -3579,7 +3641,7 @@
       </c>
       <c r="P25"/>
     </row>
-    <row r="26" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>5</v>
       </c>
@@ -3604,7 +3666,7 @@
       </c>
       <c r="J26" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="K26" s="2">
         <v>45229</v>
@@ -3616,12 +3678,15 @@
       <c r="M26" s="4" t="s">
         <v>102</v>
       </c>
+      <c r="O26" s="2">
+        <v>45364</v>
+      </c>
       <c r="P26"/>
       <c r="Q26" s="2" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="27" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>5</v>
       </c>
@@ -3646,7 +3711,7 @@
       </c>
       <c r="J27" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="K27" s="2">
         <v>45229</v>
@@ -3658,12 +3723,15 @@
       <c r="M27" s="4" t="s">
         <v>102</v>
       </c>
+      <c r="O27" s="2">
+        <v>45364</v>
+      </c>
       <c r="P27"/>
       <c r="Q27" s="2" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="28" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>5</v>
       </c>
@@ -3691,7 +3759,7 @@
       </c>
       <c r="J28" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="K28" s="2">
         <v>45293</v>
@@ -3706,7 +3774,7 @@
       <c r="P28"/>
       <c r="Q28" s="2"/>
     </row>
-    <row r="29" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
         <v>5</v>
       </c>
@@ -3730,11 +3798,11 @@
       </c>
       <c r="I29" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J29" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="K29" s="2">
         <v>45315</v>
@@ -3774,7 +3842,7 @@
       </c>
       <c r="J30" s="4">
         <f t="shared" ref="J30" ca="1" si="4">IF(_xlfn.DAYS(TODAY(),H30)&lt;10000, _xlfn.DAYS(TODAY(),H30), "-")</f>
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="K30" s="2">
         <v>45176</v>
@@ -3819,7 +3887,7 @@
       </c>
       <c r="J31" s="4">
         <f t="shared" ref="J31:J37" ca="1" si="6">IF(_xlfn.DAYS(TODAY(),H31)&lt;10000, _xlfn.DAYS(TODAY(),H31), "-")</f>
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="K31" s="2">
         <v>45229</v>
@@ -3903,7 +3971,7 @@
       </c>
       <c r="J33" s="4">
         <f ca="1">IF(_xlfn.DAYS(TODAY(),H33)&lt;10000, _xlfn.DAYS(TODAY(),H33), "-")</f>
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K33" s="2">
         <v>45257</v>
@@ -4029,7 +4097,7 @@
       </c>
       <c r="J36" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K36" s="2">
         <v>45257</v>
@@ -4077,7 +4145,7 @@
       </c>
       <c r="J37" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K37" s="2">
         <v>45257</v>
@@ -4125,7 +4193,7 @@
       </c>
       <c r="J38" s="4">
         <f t="shared" ref="J38:J40" ca="1" si="8">IF(_xlfn.DAYS(TODAY(),H38)&lt;10000, _xlfn.DAYS(TODAY(),H38), "-")</f>
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K38" s="2">
         <v>45257</v>
@@ -4173,7 +4241,7 @@
       </c>
       <c r="J39" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K39" s="2">
         <v>45257</v>
@@ -4218,7 +4286,7 @@
       </c>
       <c r="J40" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K40" s="2">
         <v>45257</v>
@@ -4259,11 +4327,11 @@
       </c>
       <c r="I41" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J41" s="4">
         <f t="shared" ref="J41:J42" ca="1" si="9">IF(_xlfn.DAYS(TODAY(),H41)&lt;10000, _xlfn.DAYS(TODAY(),H41), "-")</f>
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="L41" s="4" t="str">
         <f t="shared" si="7"/>
@@ -4302,7 +4370,7 @@
       </c>
       <c r="J42" s="4">
         <f t="shared" ca="1" si="9"/>
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="K42" s="2">
         <v>45176</v>
@@ -4346,11 +4414,11 @@
       </c>
       <c r="I43" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J43" s="4">
         <f t="shared" ref="J43:J94" ca="1" si="11">IF(_xlfn.DAYS(TODAY(),H43)&lt;10000, _xlfn.DAYS(TODAY(),H43), "-")</f>
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="L43" s="4" t="str">
         <f t="shared" si="7"/>
@@ -4391,11 +4459,11 @@
       </c>
       <c r="I44" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J44" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="K44" s="2">
         <v>45293</v>
@@ -4436,11 +4504,11 @@
       </c>
       <c r="I45" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J45" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="K45" s="2">
         <v>45293</v>
@@ -4481,11 +4549,11 @@
       </c>
       <c r="I46" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J46" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="K46" s="2">
         <v>45293</v>
@@ -4529,11 +4597,11 @@
       </c>
       <c r="I47" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J47" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="K47" s="2">
         <v>45293</v>
@@ -4581,7 +4649,7 @@
       </c>
       <c r="J48" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="K48" s="2">
         <v>45293</v>
@@ -4625,11 +4693,11 @@
       </c>
       <c r="I49" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J49" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="K49" s="2">
         <v>45293</v>
@@ -4673,11 +4741,11 @@
       </c>
       <c r="I50" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J50" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="K50" s="2">
         <v>45293</v>
@@ -4721,11 +4789,11 @@
       </c>
       <c r="I51" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J51" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="K51" s="2">
         <v>45293</v>
@@ -4770,7 +4838,7 @@
       </c>
       <c r="J52" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="K52" s="2">
         <v>45293</v>
@@ -4815,7 +4883,7 @@
       </c>
       <c r="J53" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="K53" s="2">
         <v>45293</v>
@@ -4863,7 +4931,7 @@
       </c>
       <c r="J54" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="K54" s="2">
         <v>45238</v>
@@ -4911,7 +4979,7 @@
       </c>
       <c r="J55" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="K55" s="2">
         <v>45238</v>
@@ -4959,7 +5027,7 @@
       </c>
       <c r="J56" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="K56" s="2">
         <v>45238</v>
@@ -5004,7 +5072,7 @@
       </c>
       <c r="J57" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="L57" s="4" t="str">
         <f t="shared" si="7"/>
@@ -5046,7 +5114,7 @@
       </c>
       <c r="J58" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="L58" s="4" t="str">
         <f t="shared" si="7"/>
@@ -5081,11 +5149,11 @@
       </c>
       <c r="I59" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J59" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="K59" s="2">
         <v>45295</v>
@@ -5127,7 +5195,7 @@
       </c>
       <c r="J60" s="4">
         <f t="shared" ref="J60:J61" ca="1" si="13">IF(_xlfn.DAYS(TODAY(),H60)&lt;10000, _xlfn.DAYS(TODAY(),H60), "-")</f>
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="L60" s="4" t="str">
         <f t="shared" ref="L60:L61" si="14">IF(_xlfn.DAYS(K60,H60)&gt;0, _xlfn.DAYS(K60,H60), "-")</f>
@@ -5165,7 +5233,7 @@
       </c>
       <c r="J61" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="L61" s="4" t="str">
         <f t="shared" si="14"/>
@@ -5199,11 +5267,11 @@
       </c>
       <c r="I62" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J62" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="K62" s="2">
         <v>45295</v>
@@ -5244,7 +5312,7 @@
       </c>
       <c r="J63" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K63" s="7">
         <v>45324</v>
@@ -5285,7 +5353,7 @@
       </c>
       <c r="J64" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K64" s="7">
         <v>45324</v>
@@ -5322,11 +5390,11 @@
       </c>
       <c r="I65" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J65" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="K65" s="2">
         <v>45295</v>
@@ -5360,11 +5428,11 @@
       </c>
       <c r="I66" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J66" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="K66" s="2">
         <v>45295</v>
@@ -5403,11 +5471,11 @@
       </c>
       <c r="I67" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J67" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="K67" s="7">
         <v>45295</v>
@@ -5446,11 +5514,11 @@
       </c>
       <c r="I68" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J68" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="K68" s="7">
         <v>45295</v>
@@ -5496,7 +5564,7 @@
       </c>
       <c r="J69" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K69" s="7">
         <v>45324</v>
@@ -5544,7 +5612,7 @@
       </c>
       <c r="J70" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="L70" s="4" t="str">
         <f t="shared" si="7"/>
@@ -5592,7 +5660,7 @@
       </c>
       <c r="J71" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="L71" s="4" t="str">
         <f t="shared" si="7"/>
@@ -5640,7 +5708,7 @@
       </c>
       <c r="J72" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="L72" s="4" t="str">
         <f t="shared" si="7"/>
@@ -5688,7 +5756,7 @@
       </c>
       <c r="J73" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="L73" s="4" t="str">
         <f t="shared" si="7"/>
@@ -5736,7 +5804,7 @@
       </c>
       <c r="J74" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="L74" s="4" t="str">
         <f t="shared" si="7"/>
@@ -5784,7 +5852,7 @@
       </c>
       <c r="J75" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="L75" s="4" t="str">
         <f t="shared" si="7"/>
@@ -5832,7 +5900,7 @@
       </c>
       <c r="J76" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="L76" s="4" t="str">
         <f t="shared" si="7"/>
@@ -5880,7 +5948,7 @@
       </c>
       <c r="J77" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="L77" s="4" t="str">
         <f t="shared" si="7"/>
@@ -5928,7 +5996,7 @@
       </c>
       <c r="J78" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="L78" s="4" t="str">
         <f t="shared" si="7"/>
@@ -5976,7 +6044,7 @@
       </c>
       <c r="J79" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="L79" s="4" t="str">
         <f t="shared" si="7"/>
@@ -6024,7 +6092,7 @@
       </c>
       <c r="J80" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="L80" s="4" t="str">
         <f t="shared" si="7"/>
@@ -6072,7 +6140,7 @@
       </c>
       <c r="J81" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="L81" s="4" t="str">
         <f t="shared" si="7"/>
@@ -6120,7 +6188,7 @@
       </c>
       <c r="J82" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="L82" s="4" t="str">
         <f t="shared" si="7"/>
@@ -6168,7 +6236,7 @@
       </c>
       <c r="J83" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="L83" s="4" t="str">
         <f t="shared" si="7"/>
@@ -6216,7 +6284,7 @@
       </c>
       <c r="J84" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="L84" s="4" t="str">
         <f t="shared" si="7"/>
@@ -6264,7 +6332,7 @@
       </c>
       <c r="J85" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="L85" s="4" t="str">
         <f t="shared" si="7"/>
@@ -6312,7 +6380,7 @@
       </c>
       <c r="J86" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="L86" s="4" t="str">
         <f t="shared" si="7"/>
@@ -6360,7 +6428,7 @@
       </c>
       <c r="J87" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="L87" s="4" t="str">
         <f t="shared" si="7"/>
@@ -6408,7 +6476,7 @@
       </c>
       <c r="J88" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="L88" s="4" t="str">
         <f t="shared" si="7"/>
@@ -6456,7 +6524,7 @@
       </c>
       <c r="J89" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="L89" s="4" t="str">
         <f t="shared" si="7"/>
@@ -6504,7 +6572,7 @@
       </c>
       <c r="J90" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="K90" s="2">
         <v>45272</v>
@@ -6552,7 +6620,7 @@
       </c>
       <c r="J91" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="K91" s="2">
         <v>45273</v>
@@ -6600,7 +6668,7 @@
       </c>
       <c r="J92" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="K92" s="2">
         <v>45274</v>
@@ -6648,7 +6716,7 @@
       </c>
       <c r="J93" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="K93" s="2">
         <v>45275</v>
@@ -6696,7 +6764,7 @@
       </c>
       <c r="J94" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="K94" s="2">
         <v>45276</v>
@@ -6744,7 +6812,7 @@
       </c>
       <c r="J95" s="4">
         <f t="shared" ref="J95:J96" ca="1" si="17">IF(_xlfn.DAYS(TODAY(),H95)&lt;10000, _xlfn.DAYS(TODAY(),H95), "-")</f>
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="K95" s="2">
         <v>45277</v>
@@ -6792,7 +6860,7 @@
       </c>
       <c r="J96" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="K96" s="2">
         <v>45278</v>
@@ -6840,7 +6908,7 @@
       </c>
       <c r="J97" s="4">
         <f t="shared" ref="J97" ca="1" si="19">IF(_xlfn.DAYS(TODAY(),H97)&lt;10000, _xlfn.DAYS(TODAY(),H97), "-")</f>
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="K97" s="2">
         <v>45223</v>
@@ -6888,7 +6956,7 @@
       </c>
       <c r="J98" s="4">
         <f t="shared" ref="J98:J120" ca="1" si="21">IF(_xlfn.DAYS(TODAY(),H98)&lt;10000, _xlfn.DAYS(TODAY(),H98), "-")</f>
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="K98" s="2">
         <v>45223</v>
@@ -6936,7 +7004,7 @@
       </c>
       <c r="J99" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="K99" s="2">
         <v>45223</v>
@@ -6984,7 +7052,7 @@
       </c>
       <c r="J100" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="K100" s="2">
         <v>45223</v>
@@ -7032,7 +7100,7 @@
       </c>
       <c r="J101" s="4">
         <f t="shared" ref="J101:J110" ca="1" si="24">IF(_xlfn.DAYS(TODAY(),H101)&lt;10000, _xlfn.DAYS(TODAY(),H101), "-")</f>
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="K101" s="2">
         <v>45267</v>
@@ -7083,7 +7151,7 @@
       </c>
       <c r="J102" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="K102" s="2">
         <v>45267</v>
@@ -7134,7 +7202,7 @@
       </c>
       <c r="J103" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="K103" s="2">
         <v>45267</v>
@@ -7185,7 +7253,7 @@
       </c>
       <c r="J104" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="K104" s="2">
         <v>45267</v>
@@ -7236,7 +7304,7 @@
       </c>
       <c r="J105" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="K105" s="2">
         <v>45267</v>
@@ -7287,7 +7355,7 @@
       </c>
       <c r="J106" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="K106" s="2">
         <v>45267</v>
@@ -7338,7 +7406,7 @@
       </c>
       <c r="J107" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="K107" s="2">
         <v>45267</v>
@@ -7389,7 +7457,7 @@
       </c>
       <c r="J108" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="K108" s="2">
         <v>45267</v>
@@ -7440,7 +7508,7 @@
       </c>
       <c r="J109" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="K109" s="2">
         <v>45267</v>
@@ -7491,7 +7559,7 @@
       </c>
       <c r="J110" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="K110" s="2">
         <v>45267</v>
@@ -8009,11 +8077,11 @@
       </c>
       <c r="I123" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J123" s="4">
         <f t="shared" ca="1" si="26"/>
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="K123" s="2">
         <v>45315</v>
@@ -8054,11 +8122,11 @@
       </c>
       <c r="I124" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J124" s="4">
         <f t="shared" ca="1" si="26"/>
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="K124" s="2">
         <v>45315</v>
@@ -8099,11 +8167,11 @@
       </c>
       <c r="I125" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J125" s="4">
         <f t="shared" ca="1" si="26"/>
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="K125" s="2">
         <v>45315</v>
@@ -8144,11 +8212,11 @@
       </c>
       <c r="I126" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J126" s="4">
         <f t="shared" ca="1" si="26"/>
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="L126" s="4" t="str">
         <f t="shared" si="22"/>
@@ -8165,7 +8233,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="127" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="127" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B127" t="s">
         <v>5</v>
       </c>
@@ -8206,7 +8274,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="128" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="128" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B128" t="s">
         <v>100</v>
       </c>
@@ -8230,11 +8298,11 @@
       </c>
       <c r="I128" s="4">
         <f t="shared" ref="I128:I129" ca="1" si="27">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H128), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H128), 7), "-")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J128" s="4">
         <f t="shared" ref="J128:J129" ca="1" si="28">IF(_xlfn.DAYS(TODAY(),H128)&lt;10000, _xlfn.DAYS(TODAY(),H128), "-")</f>
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="L128" s="4" t="str">
         <f t="shared" si="22"/>
@@ -8273,11 +8341,11 @@
       </c>
       <c r="I129" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J129" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="L129" s="4" t="str">
         <f t="shared" si="22"/>
@@ -8352,11 +8420,11 @@
       </c>
       <c r="I131" s="4">
         <f t="shared" ref="I131:I134" ca="1" si="29">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H131), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H131), 7), "-")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J131" s="4">
         <f t="shared" ref="J131:J134" ca="1" si="30">IF(_xlfn.DAYS(TODAY(),H131)&lt;10000, _xlfn.DAYS(TODAY(),H131), "-")</f>
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="L131" s="4" t="str">
         <f t="shared" si="22"/>
@@ -8394,11 +8462,11 @@
       </c>
       <c r="I132" s="4">
         <f t="shared" ca="1" si="29"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J132" s="4">
         <f t="shared" ca="1" si="30"/>
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="L132" s="4" t="str">
         <f t="shared" si="22"/>
@@ -8430,11 +8498,11 @@
       </c>
       <c r="I133" s="4">
         <f t="shared" ca="1" si="29"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J133" s="4">
         <f t="shared" ca="1" si="30"/>
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="L133" s="4" t="str">
         <f t="shared" si="22"/>
@@ -8472,11 +8540,11 @@
       </c>
       <c r="I134" s="4">
         <f t="shared" ca="1" si="29"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J134" s="4">
         <f t="shared" ca="1" si="30"/>
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="L134" s="4" t="str">
         <f t="shared" si="22"/>
@@ -8582,11 +8650,11 @@
       </c>
       <c r="I137" s="4">
         <f t="shared" ca="1" si="31"/>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J137" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="L137" s="4" t="str">
         <f t="shared" si="33"/>
@@ -8618,11 +8686,11 @@
       </c>
       <c r="I138" s="4">
         <f t="shared" ca="1" si="31"/>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J138" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="L138" s="4" t="str">
         <f t="shared" si="33"/>
@@ -8654,11 +8722,11 @@
       </c>
       <c r="I139" s="4">
         <f t="shared" ca="1" si="31"/>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J139" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="L139" s="4" t="str">
         <f t="shared" si="33"/>
@@ -8690,11 +8758,11 @@
       </c>
       <c r="I140" s="4">
         <f t="shared" ca="1" si="31"/>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J140" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="L140" s="4" t="str">
         <f t="shared" si="33"/>
@@ -8741,7 +8809,7 @@
       </c>
       <c r="P141"/>
     </row>
-    <row r="142" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="142" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B142" t="s">
         <v>126</v>
       </c>
@@ -8769,7 +8837,7 @@
       </c>
       <c r="J142" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="L142" s="4" t="str">
         <f t="shared" si="33"/>
@@ -8780,7 +8848,7 @@
       </c>
       <c r="P142"/>
     </row>
-    <row r="143" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B143" t="s">
         <v>27</v>
       </c>
@@ -8808,7 +8876,7 @@
       </c>
       <c r="J143" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="L143" s="4" t="str">
         <f t="shared" si="33"/>
@@ -8821,10 +8889,13 @@
         <v>45363</v>
       </c>
       <c r="P143" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="144" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+        <v>262</v>
+      </c>
+      <c r="R143" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="144" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B144" t="s">
         <v>27</v>
       </c>
@@ -8852,7 +8923,7 @@
       </c>
       <c r="J144" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="L144" s="4" t="str">
         <f t="shared" si="33"/>
@@ -8865,10 +8936,13 @@
         <v>45363</v>
       </c>
       <c r="P144" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="145" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+        <v>262</v>
+      </c>
+      <c r="R144" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="145" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B145" t="s">
         <v>27</v>
       </c>
@@ -8896,7 +8970,7 @@
       </c>
       <c r="J145" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="L145" s="4" t="str">
         <f t="shared" si="33"/>
@@ -8909,7 +8983,10 @@
         <v>45363</v>
       </c>
       <c r="P145" t="s">
-        <v>263</v>
+        <v>262</v>
+      </c>
+      <c r="R145" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="146" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -8940,7 +9017,7 @@
       </c>
       <c r="J146" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="L146" s="4" t="str">
         <f t="shared" si="33"/>
@@ -8954,7 +9031,7 @@
       </c>
       <c r="P146"/>
     </row>
-    <row r="147" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B147" t="s">
         <v>27</v>
       </c>
@@ -8982,7 +9059,7 @@
       </c>
       <c r="J147" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="L147" s="4" t="str">
         <f t="shared" si="33"/>
@@ -8995,7 +9072,10 @@
         <v>45363</v>
       </c>
       <c r="P147" t="s">
-        <v>263</v>
+        <v>262</v>
+      </c>
+      <c r="R147" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="148" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -9097,7 +9177,7 @@
       </c>
       <c r="P150"/>
     </row>
-    <row r="151" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B151" t="s">
         <v>27</v>
       </c>
@@ -9125,7 +9205,7 @@
       </c>
       <c r="J151" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="L151" s="4" t="str">
         <f t="shared" si="36"/>
@@ -9141,7 +9221,7 @@
         <v>225</v>
       </c>
       <c r="R151" t="s">
-        <v>261</v>
+        <v>222</v>
       </c>
     </row>
     <row r="152" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -9172,7 +9252,7 @@
       </c>
       <c r="J152" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="L152" s="4" t="str">
         <f t="shared" si="36"/>
@@ -9214,7 +9294,7 @@
       </c>
       <c r="J153" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="L153" s="4" t="str">
         <f t="shared" si="36"/>
@@ -9256,7 +9336,7 @@
       </c>
       <c r="J154" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="L154" s="4" t="str">
         <f t="shared" si="36"/>
@@ -9270,7 +9350,7 @@
       </c>
       <c r="P154"/>
     </row>
-    <row r="155" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B155" t="s">
         <v>27</v>
       </c>
@@ -9298,7 +9378,7 @@
       </c>
       <c r="J155" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="L155" s="4" t="str">
         <f t="shared" si="36"/>
@@ -9314,10 +9394,10 @@
         <v>225</v>
       </c>
       <c r="R155" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="156" spans="2:18" x14ac:dyDescent="0.3">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="156" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B156" t="s">
         <v>126</v>
       </c>
@@ -9345,7 +9425,7 @@
       </c>
       <c r="J156" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="L156" s="4" t="str">
         <f t="shared" si="36"/>
@@ -9384,7 +9464,7 @@
       </c>
       <c r="J157" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="L157" s="4" t="str">
         <f t="shared" si="36"/>
@@ -9440,7 +9520,7 @@
       </c>
       <c r="P158"/>
     </row>
-    <row r="159" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="159" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B159" t="s">
         <v>5</v>
       </c>
@@ -9470,7 +9550,7 @@
       </c>
       <c r="P159"/>
     </row>
-    <row r="160" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="160" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B160" t="s">
         <v>126</v>
       </c>
@@ -9503,7 +9583,7 @@
       </c>
       <c r="P160"/>
     </row>
-    <row r="161" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="161" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B161" t="s">
         <v>5</v>
       </c>
@@ -9533,7 +9613,7 @@
       </c>
       <c r="P161"/>
     </row>
-    <row r="162" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="162" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B162" t="s">
         <v>126</v>
       </c>
@@ -9557,11 +9637,11 @@
       </c>
       <c r="I162" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J162" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K162" s="2">
         <v>45301</v>
@@ -9575,7 +9655,7 @@
       </c>
       <c r="P162"/>
     </row>
-    <row r="163" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="163" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B163" t="s">
         <v>5</v>
       </c>
@@ -9605,7 +9685,7 @@
       </c>
       <c r="P163"/>
     </row>
-    <row r="164" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="164" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B164" t="s">
         <v>126</v>
       </c>
@@ -9629,11 +9709,11 @@
       </c>
       <c r="I164" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J164" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K164" s="2">
         <v>45301</v>
@@ -9668,11 +9748,11 @@
       </c>
       <c r="I165" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J165" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K165" s="2">
         <v>45301</v>
@@ -9689,7 +9769,7 @@
       </c>
       <c r="P165"/>
     </row>
-    <row r="166" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="166" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B166" t="s">
         <v>126</v>
       </c>
@@ -9713,11 +9793,11 @@
       </c>
       <c r="I166" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J166" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K166" s="2">
         <v>45301</v>
@@ -9755,11 +9835,11 @@
       </c>
       <c r="I167" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J167" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K167" s="2">
         <v>45301</v>
@@ -9806,11 +9886,11 @@
       </c>
       <c r="I168" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J168" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K168" s="2">
         <v>45301</v>
@@ -9852,7 +9932,7 @@
       </c>
       <c r="J169" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="L169" s="4" t="str">
         <f t="shared" si="36"/>
@@ -9897,7 +9977,7 @@
       </c>
       <c r="J170" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="L170" s="4" t="str">
         <f t="shared" si="36"/>
@@ -9909,9 +9989,13 @@
       <c r="N170" s="2">
         <v>45322</v>
       </c>
+      <c r="O170" s="2">
+        <v>45365</v>
+      </c>
       <c r="P170" s="5" t="s">
         <v>156</v>
       </c>
+      <c r="Q170" s="20"/>
       <c r="R170" t="s">
         <v>221</v>
       </c>
@@ -9941,7 +10025,7 @@
       </c>
       <c r="J171" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="L171" s="4" t="str">
         <f t="shared" si="36"/>
@@ -9987,11 +10071,11 @@
       </c>
       <c r="I172" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J172" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K172" s="2">
         <v>45301</v>
@@ -10013,7 +10097,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="173" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="173" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B173" t="s">
         <v>5</v>
       </c>
@@ -10037,11 +10121,11 @@
       </c>
       <c r="I173" s="4">
         <f t="shared" ref="I173:I174" ca="1" si="40">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H173), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H173), 7), "-")</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J173" s="4">
         <f t="shared" ref="J173:J174" ca="1" si="41">IF(_xlfn.DAYS(TODAY(),H173)&lt;10000, _xlfn.DAYS(TODAY(),H173), "-")</f>
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="L173" s="4" t="str">
         <f t="shared" ref="L173:L174" si="42">IF(_xlfn.DAYS(K173,H173)&gt;0, _xlfn.DAYS(K173,H173), "-")</f>
@@ -10052,7 +10136,7 @@
       </c>
       <c r="P173"/>
     </row>
-    <row r="174" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="174" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B174" t="s">
         <v>5</v>
       </c>
@@ -10085,7 +10169,7 @@
       </c>
       <c r="P174"/>
     </row>
-    <row r="175" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="175" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B175" t="s">
         <v>126</v>
       </c>
@@ -10109,11 +10193,11 @@
       </c>
       <c r="I175" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J175" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K175" s="2">
         <v>45301</v>
@@ -10151,11 +10235,11 @@
       </c>
       <c r="I176" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J176" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K176" s="2">
         <v>45301</v>
@@ -10204,11 +10288,11 @@
       </c>
       <c r="I177" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J177" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K177" s="2">
         <v>45301</v>
@@ -10223,6 +10307,9 @@
       <c r="N177" s="2">
         <v>45322</v>
       </c>
+      <c r="O177" s="2">
+        <v>45365</v>
+      </c>
       <c r="P177" s="5" t="s">
         <v>156</v>
       </c>
@@ -10254,11 +10341,11 @@
       </c>
       <c r="I178" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J178" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K178" s="2">
         <v>45301</v>
@@ -10273,6 +10360,9 @@
       <c r="N178" s="2">
         <v>45322</v>
       </c>
+      <c r="O178" s="2">
+        <v>45365</v>
+      </c>
       <c r="P178" s="5" t="s">
         <v>156</v>
       </c>
@@ -10304,11 +10394,11 @@
       </c>
       <c r="I179" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J179" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="L179" s="4" t="str">
         <f t="shared" si="36"/>
@@ -10319,6 +10409,9 @@
       </c>
       <c r="N179" s="2">
         <v>45322</v>
+      </c>
+      <c r="O179" s="2">
+        <v>45365</v>
       </c>
       <c r="P179" s="5" t="s">
         <v>156</v>
@@ -10334,6 +10427,9 @@
       <c r="C180" t="s">
         <v>110</v>
       </c>
+      <c r="D180" t="s">
+        <v>282</v>
+      </c>
       <c r="E180" t="s">
         <v>16</v>
       </c>
@@ -10352,7 +10448,7 @@
       </c>
       <c r="J180" s="4">
         <f t="shared" ref="J180:J189" ca="1" si="44">IF(_xlfn.DAYS(TODAY(),H180)&lt;10000, _xlfn.DAYS(TODAY(),H180), "-")</f>
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K180" s="7">
         <v>45324</v>
@@ -10364,6 +10460,12 @@
       <c r="M180" t="s">
         <v>158</v>
       </c>
+      <c r="P180" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="R180" t="s">
+        <v>288</v>
+      </c>
     </row>
     <row r="181" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B181" t="s">
@@ -10372,6 +10474,9 @@
       <c r="C181" t="s">
         <v>110</v>
       </c>
+      <c r="D181" t="s">
+        <v>283</v>
+      </c>
       <c r="E181" t="s">
         <v>16</v>
       </c>
@@ -10390,7 +10495,7 @@
       </c>
       <c r="J181" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K181" s="7">
         <v>45324</v>
@@ -10402,6 +10507,12 @@
       <c r="M181" t="s">
         <v>158</v>
       </c>
+      <c r="P181" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="R181" t="s">
+        <v>288</v>
+      </c>
     </row>
     <row r="182" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B182" t="s">
@@ -10410,6 +10521,9 @@
       <c r="C182" t="s">
         <v>110</v>
       </c>
+      <c r="D182" t="s">
+        <v>284</v>
+      </c>
       <c r="E182" t="s">
         <v>16</v>
       </c>
@@ -10428,7 +10542,7 @@
       </c>
       <c r="J182" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K182" s="7">
         <v>45324</v>
@@ -10440,6 +10554,12 @@
       <c r="M182" t="s">
         <v>158</v>
       </c>
+      <c r="P182" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="R182" t="s">
+        <v>288</v>
+      </c>
     </row>
     <row r="183" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B183" t="s">
@@ -10448,6 +10568,9 @@
       <c r="C183" t="s">
         <v>110</v>
       </c>
+      <c r="D183" t="s">
+        <v>285</v>
+      </c>
       <c r="E183" t="s">
         <v>16</v>
       </c>
@@ -10466,7 +10589,7 @@
       </c>
       <c r="J183" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K183" s="7">
         <v>45324</v>
@@ -10478,6 +10601,12 @@
       <c r="M183" t="s">
         <v>158</v>
       </c>
+      <c r="P183" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="R183" t="s">
+        <v>289</v>
+      </c>
     </row>
     <row r="184" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B184" t="s">
@@ -10486,6 +10615,9 @@
       <c r="C184" t="s">
         <v>110</v>
       </c>
+      <c r="D184" t="s">
+        <v>286</v>
+      </c>
       <c r="E184" t="s">
         <v>16</v>
       </c>
@@ -10504,7 +10636,7 @@
       </c>
       <c r="J184" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K184" s="7">
         <v>45324</v>
@@ -10516,6 +10648,12 @@
       <c r="M184" t="s">
         <v>158</v>
       </c>
+      <c r="P184" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="R184" t="s">
+        <v>289</v>
+      </c>
     </row>
     <row r="185" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B185" t="s">
@@ -10524,6 +10662,9 @@
       <c r="C185" t="s">
         <v>110</v>
       </c>
+      <c r="D185" t="s">
+        <v>287</v>
+      </c>
       <c r="E185" t="s">
         <v>16</v>
       </c>
@@ -10542,7 +10683,7 @@
       </c>
       <c r="J185" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K185" s="7">
         <v>45324</v>
@@ -10554,6 +10695,12 @@
       <c r="M185" t="s">
         <v>158</v>
       </c>
+      <c r="P185" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="R185" t="s">
+        <v>289</v>
+      </c>
     </row>
     <row r="186" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B186" t="s">
@@ -10576,11 +10723,11 @@
       </c>
       <c r="I186" s="4">
         <f t="shared" ca="1" si="43"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J186" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="K186" s="2">
         <v>45357</v>
@@ -10593,7 +10740,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="187" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="187" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B187" t="s">
         <v>5</v>
       </c>
@@ -10601,10 +10748,10 @@
         <v>127</v>
       </c>
       <c r="F187" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G187" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="I187" s="4" t="str">
         <f t="shared" ref="I187" ca="1" si="46">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H187), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H187), 7), "-")</f>
@@ -10619,10 +10766,10 @@
         <v>-</v>
       </c>
       <c r="M187" s="4" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="188" spans="2:18" x14ac:dyDescent="0.3">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="188" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B188" t="s">
         <v>5</v>
       </c>
@@ -10630,31 +10777,31 @@
         <v>127</v>
       </c>
       <c r="F188" s="5" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G188" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H188" s="2">
         <v>45269</v>
       </c>
       <c r="I188" s="4">
         <f t="shared" ca="1" si="43"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J188" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="L188" s="4" t="str">
         <f t="shared" si="48"/>
         <v>-</v>
       </c>
       <c r="M188" s="4" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="189" spans="2:18" x14ac:dyDescent="0.3">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="189" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B189" t="s">
         <v>5</v>
       </c>
@@ -10665,7 +10812,7 @@
         <v>16</v>
       </c>
       <c r="G189" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H189" s="2">
         <v>45327</v>
@@ -10676,7 +10823,7 @@
       </c>
       <c r="J189" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="L189" s="4" t="str">
         <f t="shared" si="48"/>
@@ -10693,7 +10840,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="190" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="190" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B190" t="s">
         <v>5</v>
       </c>
@@ -10704,7 +10851,7 @@
         <v>16</v>
       </c>
       <c r="G190" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H190" s="2">
         <v>45327</v>
@@ -10715,7 +10862,7 @@
       </c>
       <c r="J190" s="4">
         <f t="shared" ref="J190:J194" ca="1" si="50">IF(_xlfn.DAYS(TODAY(),H190)&lt;10000, _xlfn.DAYS(TODAY(),H190), "-")</f>
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="L190" s="4" t="str">
         <f t="shared" ref="L190:L194" si="51">IF(_xlfn.DAYS(K190,H190)&gt;0, _xlfn.DAYS(K190,H190), "-")</f>
@@ -10732,7 +10879,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="191" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="191" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B191" t="s">
         <v>5</v>
       </c>
@@ -10743,7 +10890,7 @@
         <v>16</v>
       </c>
       <c r="G191" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H191" s="2">
         <v>45327</v>
@@ -10754,7 +10901,7 @@
       </c>
       <c r="J191" s="4">
         <f t="shared" ca="1" si="50"/>
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="L191" s="4" t="str">
         <f t="shared" si="51"/>
@@ -10771,7 +10918,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="192" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="192" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B192" t="s">
         <v>5</v>
       </c>
@@ -10782,7 +10929,7 @@
         <v>16</v>
       </c>
       <c r="G192" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H192" s="2">
         <v>45327</v>
@@ -10793,7 +10940,7 @@
       </c>
       <c r="J192" s="4">
         <f t="shared" ca="1" si="50"/>
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="L192" s="4" t="str">
         <f t="shared" si="51"/>
@@ -10810,7 +10957,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="193" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="193" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B193" t="s">
         <v>5</v>
       </c>
@@ -10821,7 +10968,7 @@
         <v>16</v>
       </c>
       <c r="G193" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H193" s="2">
         <v>45327</v>
@@ -10832,7 +10979,7 @@
       </c>
       <c r="J193" s="4">
         <f t="shared" ca="1" si="50"/>
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="L193" s="4" t="str">
         <f t="shared" si="51"/>
@@ -10849,7 +10996,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="194" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="194" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B194" t="s">
         <v>5</v>
       </c>
@@ -10860,7 +11007,7 @@
         <v>16</v>
       </c>
       <c r="G194" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H194" s="2">
         <v>45327</v>
@@ -10871,7 +11018,7 @@
       </c>
       <c r="J194" s="4">
         <f t="shared" ca="1" si="50"/>
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="L194" s="4" t="str">
         <f t="shared" si="51"/>
@@ -11110,7 +11257,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="201" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="201" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B201" t="s">
         <v>5</v>
       </c>
@@ -11127,18 +11274,18 @@
         <v>242</v>
       </c>
       <c r="G201" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H201" s="2">
         <v>45332</v>
       </c>
       <c r="I201" s="4">
         <f t="shared" ref="I201" ca="1" si="55">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H201), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H201), 7), "-")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J201" s="4">
         <f t="shared" ref="J201" ca="1" si="56">IF(_xlfn.DAYS(TODAY(),H201)&lt;10000, _xlfn.DAYS(TODAY(),H201), "-")</f>
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L201" s="4" t="str">
         <f t="shared" ref="L201" si="57">IF(_xlfn.DAYS(K201,H201)&gt;0, _xlfn.DAYS(K201,H201), "-")</f>
@@ -11146,6 +11293,9 @@
       </c>
       <c r="M201" t="s">
         <v>228</v>
+      </c>
+      <c r="O201" s="2">
+        <v>45364</v>
       </c>
       <c r="P201"/>
       <c r="Q201" t="s">
@@ -11155,7 +11305,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="202" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="202" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B202" t="s">
         <v>5</v>
       </c>
@@ -11172,18 +11322,18 @@
         <v>243</v>
       </c>
       <c r="G202" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H202" s="2">
         <v>45332</v>
       </c>
       <c r="I202" s="4">
         <f t="shared" ref="I202:I216" ca="1" si="58">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H202), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H202), 7), "-")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J202" s="4">
         <f t="shared" ref="J202:J216" ca="1" si="59">IF(_xlfn.DAYS(TODAY(),H202)&lt;10000, _xlfn.DAYS(TODAY(),H202), "-")</f>
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L202" s="4" t="str">
         <f t="shared" ref="L202:L216" si="60">IF(_xlfn.DAYS(K202,H202)&gt;0, _xlfn.DAYS(K202,H202), "-")</f>
@@ -11191,6 +11341,9 @@
       </c>
       <c r="M202" t="s">
         <v>228</v>
+      </c>
+      <c r="O202" s="2">
+        <v>45364</v>
       </c>
       <c r="P202"/>
       <c r="Q202" t="s">
@@ -11200,7 +11353,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="203" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="203" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B203" t="s">
         <v>5</v>
       </c>
@@ -11217,18 +11370,18 @@
         <v>243</v>
       </c>
       <c r="G203" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H203" s="2">
         <v>45332</v>
       </c>
       <c r="I203" s="4">
         <f t="shared" ca="1" si="58"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J203" s="4">
         <f t="shared" ca="1" si="59"/>
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L203" s="4" t="str">
         <f t="shared" si="60"/>
@@ -11236,6 +11389,9 @@
       </c>
       <c r="M203" t="s">
         <v>228</v>
+      </c>
+      <c r="O203" s="2">
+        <v>45364</v>
       </c>
       <c r="P203"/>
       <c r="Q203" t="s">
@@ -11245,7 +11401,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="204" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="204" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B204" t="s">
         <v>5</v>
       </c>
@@ -11262,18 +11418,18 @@
         <v>243</v>
       </c>
       <c r="G204" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H204" s="2">
         <v>45332</v>
       </c>
       <c r="I204" s="4">
         <f t="shared" ca="1" si="58"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J204" s="4">
         <f t="shared" ca="1" si="59"/>
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L204" s="4" t="str">
         <f t="shared" si="60"/>
@@ -11281,6 +11437,9 @@
       </c>
       <c r="M204" t="s">
         <v>229</v>
+      </c>
+      <c r="O204" s="2">
+        <v>45364</v>
       </c>
       <c r="P204"/>
       <c r="Q204" t="s">
@@ -11290,7 +11449,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="205" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="205" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B205" t="s">
         <v>5</v>
       </c>
@@ -11307,18 +11466,18 @@
         <v>243</v>
       </c>
       <c r="G205" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H205" s="2">
         <v>45332</v>
       </c>
       <c r="I205" s="4">
         <f t="shared" ca="1" si="58"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J205" s="4">
         <f t="shared" ca="1" si="59"/>
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L205" s="4" t="str">
         <f t="shared" si="60"/>
@@ -11326,6 +11485,9 @@
       </c>
       <c r="M205" t="s">
         <v>229</v>
+      </c>
+      <c r="O205" s="2">
+        <v>45364</v>
       </c>
       <c r="P205"/>
       <c r="Q205" t="s">
@@ -11335,7 +11497,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="206" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="206" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B206" t="s">
         <v>5</v>
       </c>
@@ -11352,18 +11514,18 @@
         <v>243</v>
       </c>
       <c r="G206" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H206" s="2">
         <v>45332</v>
       </c>
       <c r="I206" s="4">
         <f t="shared" ca="1" si="58"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J206" s="4">
         <f t="shared" ca="1" si="59"/>
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L206" s="4" t="str">
         <f t="shared" si="60"/>
@@ -11371,6 +11533,9 @@
       </c>
       <c r="M206" t="s">
         <v>229</v>
+      </c>
+      <c r="O206" s="2">
+        <v>45364</v>
       </c>
       <c r="P206"/>
       <c r="Q206" t="s">
@@ -11380,7 +11545,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="207" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="207" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B207" t="s">
         <v>5</v>
       </c>
@@ -11397,18 +11562,18 @@
         <v>243</v>
       </c>
       <c r="G207" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H207" s="2">
         <v>45332</v>
       </c>
       <c r="I207" s="4">
         <f t="shared" ca="1" si="58"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J207" s="4">
         <f t="shared" ca="1" si="59"/>
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L207" s="4" t="str">
         <f t="shared" si="60"/>
@@ -11416,6 +11581,9 @@
       </c>
       <c r="M207" t="s">
         <v>230</v>
+      </c>
+      <c r="O207" s="2">
+        <v>45364</v>
       </c>
       <c r="P207"/>
       <c r="Q207" t="s">
@@ -11425,7 +11593,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="208" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="208" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B208" t="s">
         <v>5</v>
       </c>
@@ -11442,18 +11610,18 @@
         <v>242</v>
       </c>
       <c r="G208" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H208" s="2">
         <v>45332</v>
       </c>
       <c r="I208" s="4">
         <f t="shared" ca="1" si="58"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J208" s="4">
         <f t="shared" ca="1" si="59"/>
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L208" s="4" t="str">
         <f t="shared" si="60"/>
@@ -11461,6 +11629,9 @@
       </c>
       <c r="M208" t="s">
         <v>230</v>
+      </c>
+      <c r="O208" s="2">
+        <v>45364</v>
       </c>
       <c r="P208"/>
       <c r="Q208" t="s">
@@ -11470,7 +11641,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="209" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="209" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B209" t="s">
         <v>5</v>
       </c>
@@ -11487,18 +11658,18 @@
         <v>242</v>
       </c>
       <c r="G209" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H209" s="2">
         <v>45332</v>
       </c>
       <c r="I209" s="4">
         <f t="shared" ca="1" si="58"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J209" s="4">
         <f t="shared" ca="1" si="59"/>
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L209" s="4" t="str">
         <f t="shared" si="60"/>
@@ -11506,6 +11677,9 @@
       </c>
       <c r="M209" t="s">
         <v>230</v>
+      </c>
+      <c r="O209" s="2">
+        <v>45364</v>
       </c>
       <c r="P209"/>
       <c r="Q209" t="s">
@@ -11515,29 +11689,32 @@
         <v>204</v>
       </c>
     </row>
-    <row r="210" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="210" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B210" t="s">
         <v>5</v>
       </c>
       <c r="C210" t="s">
         <v>112</v>
       </c>
+      <c r="D210" t="s">
+        <v>276</v>
+      </c>
       <c r="E210" t="s">
         <v>15</v>
       </c>
       <c r="G210" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H210" s="2">
         <v>45337</v>
       </c>
       <c r="I210" s="4">
         <f t="shared" ca="1" si="58"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J210" s="4">
         <f t="shared" ca="1" si="59"/>
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K210" s="2">
         <v>45363</v>
@@ -11547,39 +11724,39 @@
         <v>26</v>
       </c>
       <c r="M210" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="P210"/>
-      <c r="Q210" t="s">
-        <v>266</v>
-      </c>
       <c r="R210" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="211" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="211" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B211" t="s">
         <v>5</v>
       </c>
       <c r="C211" t="s">
         <v>112</v>
       </c>
+      <c r="D211" t="s">
+        <v>277</v>
+      </c>
       <c r="E211" t="s">
         <v>15</v>
       </c>
       <c r="G211" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H211" s="2">
         <v>45337</v>
       </c>
       <c r="I211" s="4">
         <f t="shared" ca="1" si="58"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J211" s="4">
         <f t="shared" ca="1" si="59"/>
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K211" s="2">
         <v>45363</v>
@@ -11589,39 +11766,39 @@
         <v>26</v>
       </c>
       <c r="M211" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="P211"/>
-      <c r="Q211" t="s">
-        <v>266</v>
-      </c>
       <c r="R211" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="212" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="212" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B212" t="s">
         <v>5</v>
       </c>
       <c r="C212" t="s">
         <v>112</v>
       </c>
+      <c r="D212" t="s">
+        <v>278</v>
+      </c>
       <c r="E212" t="s">
         <v>15</v>
       </c>
       <c r="G212" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H212" s="2">
         <v>45337</v>
       </c>
       <c r="I212" s="4">
         <f t="shared" ca="1" si="58"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J212" s="4">
         <f t="shared" ca="1" si="59"/>
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K212" s="2">
         <v>45363</v>
@@ -11631,39 +11808,39 @@
         <v>26</v>
       </c>
       <c r="M212" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="P212"/>
-      <c r="Q212" t="s">
-        <v>266</v>
-      </c>
       <c r="R212" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="213" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="213" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B213" t="s">
         <v>5</v>
       </c>
       <c r="C213" t="s">
         <v>112</v>
       </c>
+      <c r="D213" t="s">
+        <v>279</v>
+      </c>
       <c r="E213" t="s">
         <v>15</v>
       </c>
       <c r="G213" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H213" s="2">
         <v>45337</v>
       </c>
       <c r="I213" s="4">
         <f t="shared" ca="1" si="58"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J213" s="4">
         <f t="shared" ca="1" si="59"/>
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K213" s="2">
         <v>45363</v>
@@ -11673,39 +11850,39 @@
         <v>26</v>
       </c>
       <c r="M213" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="P213"/>
-      <c r="Q213" t="s">
-        <v>266</v>
-      </c>
       <c r="R213" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="214" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="214" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B214" t="s">
         <v>5</v>
       </c>
       <c r="C214" t="s">
         <v>112</v>
       </c>
+      <c r="D214" t="s">
+        <v>280</v>
+      </c>
       <c r="E214" t="s">
         <v>15</v>
       </c>
       <c r="G214" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H214" s="2">
         <v>45337</v>
       </c>
       <c r="I214" s="4">
         <f t="shared" ca="1" si="58"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J214" s="4">
         <f t="shared" ca="1" si="59"/>
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K214" s="2">
         <v>45363</v>
@@ -11715,39 +11892,39 @@
         <v>26</v>
       </c>
       <c r="M214" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="P214"/>
-      <c r="Q214" t="s">
-        <v>266</v>
-      </c>
       <c r="R214" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="215" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="215" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B215" t="s">
         <v>5</v>
       </c>
       <c r="C215" t="s">
         <v>112</v>
       </c>
+      <c r="D215" t="s">
+        <v>276</v>
+      </c>
       <c r="E215" t="s">
         <v>15</v>
       </c>
       <c r="G215" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H215" s="2">
         <v>45337</v>
       </c>
       <c r="I215" s="4">
         <f t="shared" ca="1" si="58"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J215" s="4">
         <f t="shared" ca="1" si="59"/>
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K215" s="2">
         <v>45363</v>
@@ -11757,39 +11934,39 @@
         <v>26</v>
       </c>
       <c r="M215" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="P215"/>
-      <c r="Q215" t="s">
-        <v>266</v>
-      </c>
       <c r="R215" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="216" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="216" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B216" t="s">
         <v>5</v>
       </c>
       <c r="C216" t="s">
         <v>112</v>
       </c>
+      <c r="D216" t="s">
+        <v>278</v>
+      </c>
       <c r="E216" t="s">
         <v>15</v>
       </c>
       <c r="G216" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H216" s="2">
         <v>45337</v>
       </c>
       <c r="I216" s="4">
         <f t="shared" ca="1" si="58"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J216" s="4">
         <f t="shared" ca="1" si="59"/>
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K216" s="2">
         <v>45363</v>
@@ -11799,17 +11976,14 @@
         <v>26</v>
       </c>
       <c r="M216" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="P216"/>
-      <c r="Q216" t="s">
-        <v>266</v>
-      </c>
       <c r="R216" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="217" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="217" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B217" t="s">
         <v>5</v>
       </c>
@@ -11828,7 +12002,7 @@
       </c>
       <c r="J217" s="4">
         <f t="shared" ref="J217:J228" ca="1" si="62">IF(_xlfn.DAYS(TODAY(),H217)&lt;10000, _xlfn.DAYS(TODAY(),H217), "-")</f>
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L217" s="4" t="str">
         <f t="shared" ref="L217:L228" si="63">IF(_xlfn.DAYS(K217,H217)&gt;0, _xlfn.DAYS(K217,H217), "-")</f>
@@ -11839,13 +12013,13 @@
       </c>
       <c r="P217"/>
       <c r="Q217" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="R217" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="218" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="218" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B218" t="s">
         <v>5</v>
       </c>
@@ -11864,7 +12038,7 @@
       </c>
       <c r="J218" s="4">
         <f t="shared" ca="1" si="62"/>
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L218" s="4" t="str">
         <f t="shared" si="63"/>
@@ -11875,13 +12049,13 @@
       </c>
       <c r="P218"/>
       <c r="Q218" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="R218" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="219" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="219" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B219" t="s">
         <v>5</v>
       </c>
@@ -11900,7 +12074,7 @@
       </c>
       <c r="J219" s="4">
         <f t="shared" ca="1" si="62"/>
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L219" s="4" t="str">
         <f t="shared" si="63"/>
@@ -11911,13 +12085,13 @@
       </c>
       <c r="P219"/>
       <c r="Q219" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="R219" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="220" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="220" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B220" t="s">
         <v>5</v>
       </c>
@@ -11936,7 +12110,7 @@
       </c>
       <c r="J220" s="4">
         <f t="shared" ca="1" si="62"/>
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L220" s="4" t="str">
         <f t="shared" si="63"/>
@@ -11947,13 +12121,13 @@
       </c>
       <c r="P220"/>
       <c r="Q220" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="R220" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="221" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="221" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B221" t="s">
         <v>5</v>
       </c>
@@ -11972,7 +12146,7 @@
       </c>
       <c r="J221" s="4">
         <f t="shared" ca="1" si="62"/>
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L221" s="4" t="str">
         <f t="shared" si="63"/>
@@ -11983,13 +12157,13 @@
       </c>
       <c r="P221"/>
       <c r="Q221" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="R221" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="222" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="222" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B222" t="s">
         <v>5</v>
       </c>
@@ -12008,7 +12182,7 @@
       </c>
       <c r="J222" s="4">
         <f t="shared" ca="1" si="62"/>
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L222" s="4" t="str">
         <f t="shared" si="63"/>
@@ -12019,13 +12193,13 @@
       </c>
       <c r="P222"/>
       <c r="Q222" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="R222" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="223" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="223" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B223" t="s">
         <v>5</v>
       </c>
@@ -12044,7 +12218,7 @@
       </c>
       <c r="J223" s="4">
         <f t="shared" ca="1" si="62"/>
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L223" s="4" t="str">
         <f t="shared" si="63"/>
@@ -12055,13 +12229,13 @@
       </c>
       <c r="P223"/>
       <c r="Q223" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="R223" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="224" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="224" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B224" t="s">
         <v>5</v>
       </c>
@@ -12080,7 +12254,7 @@
       </c>
       <c r="J224" s="4">
         <f t="shared" ca="1" si="62"/>
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L224" s="4" t="str">
         <f t="shared" si="63"/>
@@ -12091,7 +12265,7 @@
       </c>
       <c r="P224"/>
       <c r="Q224" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="R224" t="s">
         <v>203</v>
@@ -12108,18 +12282,18 @@
         <v>16</v>
       </c>
       <c r="G225" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H225" s="2">
         <v>45337</v>
       </c>
       <c r="I225" s="4">
         <f t="shared" ca="1" si="61"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J225" s="4">
         <f t="shared" ca="1" si="62"/>
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K225" s="2">
         <v>45363</v>
@@ -12129,11 +12303,11 @@
         <v>26</v>
       </c>
       <c r="M225" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P225"/>
       <c r="Q225" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="R225" t="s">
         <v>205</v>
@@ -12150,18 +12324,18 @@
         <v>16</v>
       </c>
       <c r="G226" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H226" s="2">
         <v>45337</v>
       </c>
       <c r="I226" s="4">
         <f t="shared" ca="1" si="61"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J226" s="4">
         <f t="shared" ca="1" si="62"/>
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K226" s="2">
         <v>45363</v>
@@ -12171,11 +12345,11 @@
         <v>26</v>
       </c>
       <c r="M226" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P226"/>
       <c r="Q226" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="R226" t="s">
         <v>205</v>
@@ -12192,18 +12366,18 @@
         <v>16</v>
       </c>
       <c r="G227" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H227" s="2">
         <v>45337</v>
       </c>
       <c r="I227" s="4">
         <f t="shared" ca="1" si="61"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J227" s="4">
         <f t="shared" ca="1" si="62"/>
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K227" s="2">
         <v>45363</v>
@@ -12213,17 +12387,17 @@
         <v>26</v>
       </c>
       <c r="M227" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P227"/>
       <c r="Q227" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="R227" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="228" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="228" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B228" t="s">
         <v>5</v>
       </c>
@@ -12242,7 +12416,7 @@
       </c>
       <c r="J228" s="4">
         <f t="shared" ca="1" si="62"/>
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="L228" s="4" t="str">
         <f t="shared" si="63"/>
@@ -12256,7 +12430,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="229" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="229" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B229" t="s">
         <v>5</v>
       </c>
@@ -12275,7 +12449,7 @@
       </c>
       <c r="J229" s="4">
         <f t="shared" ref="J229:J237" ca="1" si="65">IF(_xlfn.DAYS(TODAY(),H229)&lt;10000, _xlfn.DAYS(TODAY(),H229), "-")</f>
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="L229" s="4" t="str">
         <f t="shared" ref="L229:L237" si="66">IF(_xlfn.DAYS(K229,H229)&gt;0, _xlfn.DAYS(K229,H229), "-")</f>
@@ -12289,7 +12463,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="230" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="230" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B230" t="s">
         <v>5</v>
       </c>
@@ -12308,7 +12482,7 @@
       </c>
       <c r="J230" s="4">
         <f t="shared" ca="1" si="65"/>
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="L230" s="4" t="str">
         <f t="shared" si="66"/>
@@ -12322,7 +12496,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="231" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="231" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B231" t="s">
         <v>5</v>
       </c>
@@ -12341,7 +12515,7 @@
       </c>
       <c r="J231" s="4">
         <f t="shared" ca="1" si="65"/>
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="L231" s="4" t="str">
         <f t="shared" si="66"/>
@@ -12355,7 +12529,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="232" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="232" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B232" t="s">
         <v>237</v>
       </c>
@@ -12374,7 +12548,7 @@
       </c>
       <c r="J232" s="4">
         <f t="shared" ca="1" si="65"/>
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L232" s="4" t="str">
         <f t="shared" si="66"/>
@@ -12385,7 +12559,7 @@
       </c>
       <c r="P232"/>
       <c r="Q232" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="233" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -12409,11 +12583,11 @@
       </c>
       <c r="I233" s="4">
         <f t="shared" ca="1" si="64"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J233" s="4">
         <f t="shared" ca="1" si="65"/>
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="K233" s="2">
         <v>45357</v>
@@ -12447,11 +12621,11 @@
       </c>
       <c r="I234" s="4">
         <f t="shared" ca="1" si="64"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J234" s="4">
         <f t="shared" ca="1" si="65"/>
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="K234" s="2">
         <v>45357</v>
@@ -12485,11 +12659,11 @@
       </c>
       <c r="I235" s="4">
         <f t="shared" ca="1" si="64"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J235" s="4">
         <f t="shared" ca="1" si="65"/>
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="K235" s="2">
         <v>45357</v>
@@ -12523,11 +12697,11 @@
       </c>
       <c r="I236" s="4">
         <f t="shared" ca="1" si="64"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J236" s="4">
         <f t="shared" ca="1" si="65"/>
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="K236" s="2">
         <v>45357</v>
@@ -12561,11 +12735,11 @@
       </c>
       <c r="I237" s="4">
         <f t="shared" ca="1" si="64"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J237" s="4">
         <f t="shared" ca="1" si="65"/>
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="K237" s="2">
         <v>45357</v>
@@ -12630,7 +12804,7 @@
       </c>
       <c r="J239" s="4">
         <f t="shared" ref="J239" ca="1" si="68">IF(_xlfn.DAYS(TODAY(),H239)&lt;10000, _xlfn.DAYS(TODAY(),H239), "-")</f>
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="L239" s="4" t="str">
         <f t="shared" ref="L239" si="69">IF(_xlfn.DAYS(K239,H239)&gt;0, _xlfn.DAYS(K239,H239), "-")</f>
@@ -12662,7 +12836,7 @@
       </c>
       <c r="J240" s="4">
         <f t="shared" ref="J240" ca="1" si="71">IF(_xlfn.DAYS(TODAY(),H240)&lt;10000, _xlfn.DAYS(TODAY(),H240), "-")</f>
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="L240" s="4" t="str">
         <f t="shared" ref="L240" si="72">IF(_xlfn.DAYS(K240,H240)&gt;0, _xlfn.DAYS(K240,H240), "-")</f>
@@ -12694,7 +12868,7 @@
       </c>
       <c r="J241" s="4">
         <f t="shared" ref="J241:J243" ca="1" si="74">IF(_xlfn.DAYS(TODAY(),H241)&lt;10000, _xlfn.DAYS(TODAY(),H241), "-")</f>
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="L241" s="4" t="str">
         <f t="shared" ref="L241:L258" si="75">IF(_xlfn.DAYS(K241,H241)&gt;0, _xlfn.DAYS(K241,H241), "-")</f>
@@ -12726,7 +12900,7 @@
       </c>
       <c r="J242" s="4">
         <f t="shared" ca="1" si="74"/>
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="L242" s="4" t="str">
         <f t="shared" si="75"/>
@@ -12743,6 +12917,9 @@
       <c r="C243" t="s">
         <v>253</v>
       </c>
+      <c r="D243" t="s">
+        <v>282</v>
+      </c>
       <c r="G243" t="s">
         <v>251</v>
       </c>
@@ -12755,7 +12932,7 @@
       </c>
       <c r="J243" s="4">
         <f t="shared" ca="1" si="74"/>
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="K243" s="2">
         <v>45350</v>
@@ -12784,6 +12961,9 @@
       <c r="C244" t="s">
         <v>253</v>
       </c>
+      <c r="D244" t="s">
+        <v>283</v>
+      </c>
       <c r="G244" t="s">
         <v>251</v>
       </c>
@@ -12796,7 +12976,7 @@
       </c>
       <c r="J244" s="4">
         <f t="shared" ref="J244:J258" ca="1" si="77">IF(_xlfn.DAYS(TODAY(),H244)&lt;10000, _xlfn.DAYS(TODAY(),H244), "-")</f>
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="K244" s="2">
         <v>45350</v>
@@ -12825,6 +13005,9 @@
       <c r="C245" t="s">
         <v>253</v>
       </c>
+      <c r="D245" t="s">
+        <v>284</v>
+      </c>
       <c r="G245" t="s">
         <v>251</v>
       </c>
@@ -12837,7 +13020,7 @@
       </c>
       <c r="J245" s="4">
         <f t="shared" ca="1" si="77"/>
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="K245" s="2">
         <v>45350</v>
@@ -12866,6 +13049,9 @@
       <c r="C246" t="s">
         <v>253</v>
       </c>
+      <c r="D246" t="s">
+        <v>285</v>
+      </c>
       <c r="G246" t="s">
         <v>251</v>
       </c>
@@ -12878,7 +13064,7 @@
       </c>
       <c r="J246" s="4">
         <f t="shared" ca="1" si="77"/>
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="K246" s="2">
         <v>45350</v>
@@ -12907,6 +13093,9 @@
       <c r="C247" t="s">
         <v>253</v>
       </c>
+      <c r="D247" t="s">
+        <v>286</v>
+      </c>
       <c r="G247" t="s">
         <v>251</v>
       </c>
@@ -12919,7 +13108,7 @@
       </c>
       <c r="J247" s="4">
         <f t="shared" ca="1" si="77"/>
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="K247" s="2">
         <v>45350</v>
@@ -12948,6 +13137,9 @@
       <c r="C248" t="s">
         <v>253</v>
       </c>
+      <c r="D248" t="s">
+        <v>282</v>
+      </c>
       <c r="G248" t="s">
         <v>251</v>
       </c>
@@ -12960,7 +13152,7 @@
       </c>
       <c r="J248" s="4">
         <f t="shared" ca="1" si="77"/>
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="K248" s="2">
         <v>45350</v>
@@ -12989,6 +13181,9 @@
       <c r="C249" t="s">
         <v>253</v>
       </c>
+      <c r="D249" t="s">
+        <v>283</v>
+      </c>
       <c r="G249" t="s">
         <v>251</v>
       </c>
@@ -13001,7 +13196,7 @@
       </c>
       <c r="J249" s="4">
         <f t="shared" ca="1" si="77"/>
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="K249" s="2">
         <v>45350</v>
@@ -13030,6 +13225,9 @@
       <c r="C250" t="s">
         <v>253</v>
       </c>
+      <c r="D250" t="s">
+        <v>284</v>
+      </c>
       <c r="G250" t="s">
         <v>251</v>
       </c>
@@ -13042,7 +13240,7 @@
       </c>
       <c r="J250" s="4">
         <f t="shared" ca="1" si="77"/>
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="K250" s="2">
         <v>45350</v>
@@ -13071,6 +13269,9 @@
       <c r="C251" t="s">
         <v>253</v>
       </c>
+      <c r="D251" t="s">
+        <v>285</v>
+      </c>
       <c r="G251" t="s">
         <v>251</v>
       </c>
@@ -13083,7 +13284,7 @@
       </c>
       <c r="J251" s="4">
         <f t="shared" ca="1" si="77"/>
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="K251" s="2">
         <v>45350</v>
@@ -13112,6 +13313,9 @@
       <c r="C252" t="s">
         <v>253</v>
       </c>
+      <c r="D252" t="s">
+        <v>286</v>
+      </c>
       <c r="G252" t="s">
         <v>251</v>
       </c>
@@ -13124,7 +13328,7 @@
       </c>
       <c r="J252" s="4">
         <f t="shared" ca="1" si="77"/>
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="K252" s="2">
         <v>45350</v>
@@ -13153,6 +13357,9 @@
       <c r="C253" t="s">
         <v>253</v>
       </c>
+      <c r="D253" t="s">
+        <v>282</v>
+      </c>
       <c r="G253" t="s">
         <v>251</v>
       </c>
@@ -13165,7 +13372,7 @@
       </c>
       <c r="J253" s="4">
         <f t="shared" ca="1" si="77"/>
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="K253" s="2">
         <v>45350</v>
@@ -13194,6 +13401,9 @@
       <c r="C254" t="s">
         <v>253</v>
       </c>
+      <c r="D254" t="s">
+        <v>283</v>
+      </c>
       <c r="G254" t="s">
         <v>251</v>
       </c>
@@ -13206,7 +13416,7 @@
       </c>
       <c r="J254" s="4">
         <f t="shared" ca="1" si="77"/>
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="K254" s="2">
         <v>45350</v>
@@ -13235,6 +13445,9 @@
       <c r="C255" t="s">
         <v>253</v>
       </c>
+      <c r="D255" t="s">
+        <v>284</v>
+      </c>
       <c r="G255" t="s">
         <v>251</v>
       </c>
@@ -13247,7 +13460,7 @@
       </c>
       <c r="J255" s="4">
         <f t="shared" ca="1" si="77"/>
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="K255" s="2">
         <v>45350</v>
@@ -13276,6 +13489,9 @@
       <c r="C256" t="s">
         <v>253</v>
       </c>
+      <c r="D256" t="s">
+        <v>285</v>
+      </c>
       <c r="G256" t="s">
         <v>251</v>
       </c>
@@ -13288,7 +13504,7 @@
       </c>
       <c r="J256" s="4">
         <f t="shared" ca="1" si="77"/>
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="K256" s="2">
         <v>45350</v>
@@ -13317,6 +13533,9 @@
       <c r="C257" t="s">
         <v>253</v>
       </c>
+      <c r="D257" t="s">
+        <v>286</v>
+      </c>
       <c r="G257" t="s">
         <v>251</v>
       </c>
@@ -13329,7 +13548,7 @@
       </c>
       <c r="J257" s="4">
         <f t="shared" ca="1" si="77"/>
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="K257" s="2">
         <v>45350</v>
@@ -13351,7 +13570,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="258" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="258" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B258" t="s">
         <v>5</v>
       </c>
@@ -13370,17 +13589,17 @@
       </c>
       <c r="J258" s="4">
         <f t="shared" ca="1" si="77"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L258" s="4" t="str">
         <f t="shared" si="75"/>
         <v>-</v>
       </c>
       <c r="M258" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="259" spans="2:18" x14ac:dyDescent="0.3">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="259" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B259" t="s">
         <v>5</v>
       </c>
@@ -13399,17 +13618,17 @@
       </c>
       <c r="J259" s="4">
         <f t="shared" ref="J259:J263" ca="1" si="79">IF(_xlfn.DAYS(TODAY(),H259)&lt;10000, _xlfn.DAYS(TODAY(),H259), "-")</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L259" s="4" t="str">
         <f t="shared" ref="L259:L263" si="80">IF(_xlfn.DAYS(K259,H259)&gt;0, _xlfn.DAYS(K259,H259), "-")</f>
         <v>-</v>
       </c>
       <c r="M259" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="260" spans="2:18" x14ac:dyDescent="0.3">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="260" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B260" t="s">
         <v>5</v>
       </c>
@@ -13428,17 +13647,17 @@
       </c>
       <c r="J260" s="4">
         <f t="shared" ca="1" si="79"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L260" s="4" t="str">
         <f t="shared" si="80"/>
         <v>-</v>
       </c>
       <c r="M260" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="261" spans="2:18" x14ac:dyDescent="0.3">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="261" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B261" t="s">
         <v>5</v>
       </c>
@@ -13457,17 +13676,17 @@
       </c>
       <c r="J261" s="4">
         <f t="shared" ca="1" si="79"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L261" s="4" t="str">
         <f t="shared" si="80"/>
         <v>-</v>
       </c>
       <c r="M261" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="262" spans="2:18" x14ac:dyDescent="0.3">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="262" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B262" t="s">
         <v>5</v>
       </c>
@@ -13475,7 +13694,7 @@
         <v>127</v>
       </c>
       <c r="E262" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H262" s="2">
         <v>45363</v>
@@ -13486,17 +13705,17 @@
       </c>
       <c r="J262" s="4">
         <f t="shared" ca="1" si="79"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L262" s="4" t="str">
         <f t="shared" si="80"/>
         <v>-</v>
       </c>
       <c r="M262" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="263" spans="2:18" x14ac:dyDescent="0.3">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="263" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B263" t="s">
         <v>5</v>
       </c>
@@ -13504,7 +13723,7 @@
         <v>127</v>
       </c>
       <c r="E263" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H263" s="2">
         <v>45363</v>
@@ -13515,27 +13734,26 @@
       </c>
       <c r="J263" s="4">
         <f t="shared" ca="1" si="79"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L263" s="4" t="str">
         <f t="shared" si="80"/>
         <v>-</v>
       </c>
       <c r="M263" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="B1:R263" xr:uid="{8D08DEC4-803F-4130-9E5E-30A83401A29D}">
     <filterColumn colId="0">
       <filters>
-        <filter val="SPF"/>
+        <filter val="5F"/>
       </filters>
     </filterColumn>
     <filterColumn colId="1">
       <filters>
         <filter val="Tcrd-CreER; Tsg101-flox"/>
-        <filter val="Tmem119-CreERT2; Cd36-flox"/>
       </filters>
     </filterColumn>
     <filterColumn colId="13">
@@ -13839,10 +14057,10 @@
       <c r="E2" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="20" t="s">
+      <c r="G2" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="H2" s="20"/>
+      <c r="H2" s="21"/>
     </row>
     <row r="3" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C3" t="s">
@@ -13905,18 +14123,18 @@
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B8" s="19">
-        <v>45313</v>
+        <v>45301</v>
       </c>
       <c r="C8" s="2">
-        <v>45355</v>
+        <v>45363</v>
       </c>
       <c r="D8">
         <f>_xlfn.DAYS(C8,B8)</f>
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="E8">
         <f>QUOTIENT(D8, 7)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/Mouse 내역.xlsx
+++ b/Mouse 내역.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20407"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20408"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\heung\Dropbox\02. Lab. of Host Defenses\03. 동물실\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{350CD658-6ACF-4146-9DDF-71B584CA6BF6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7540AF2-730E-4419-B9C7-D758119D5D53}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="495" windowWidth="28800" windowHeight="16245" xr2:uid="{5A73A69A-2AFB-4F3E-AC64-070DD7700CB2}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <sheet name="Sheet1 (2)" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$R$263</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$R$265</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1841" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1874" uniqueCount="297">
   <si>
     <t>Strain</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -809,14 +809,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>H8.1.X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>H9.1.X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>N</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -962,219 +954,250 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>H10.1.X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>genotyping</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Weaned; or Provision date</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>+/+; +/+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cre/+; +/+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>from E1.2.M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D2.B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D3.B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>from D1.3.F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>새끼 다 자라면 죽이기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E1.3.M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E1.3.F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D1.4.X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WT B6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Exp. 2-7-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GL261-pLV</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GL261-CTACK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GL261-MYDGF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2-7-1-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2-7-1-2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2-7-1-3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tamoxifen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Exp. 4-4-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A3.2.M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A3.2.F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>genotyping</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>G3.1.F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cre/+; f/f</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>+/+; f/f</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>H10.B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>L1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>L2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R1L1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Exp. 1-11-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>L1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>L2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R1L1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>corn oil</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tamoxifen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Corn oil</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>H9.1.F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>H9.1.M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(Cre/+; f/f x +/+; f/f)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(Cre/+; f/f x +/+; f/f) from H9.B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(Cre/+; f/f x +/+; f/f) from H8.B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>SPF</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>N</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>H10.1.X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>genotyping</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Weaned; or Provision date</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>+/+; +/+</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Cre/+; +/+</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>from E1.2.M</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>D2.B</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>D3.B</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>from D1.3.F</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>새끼 다 자라면 죽이기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>E1.3.M</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>E1.3.F</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>D1.4.X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>WT B6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Exp. 2-7-1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GL261-pLV</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GL261-CTACK</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GL261-MYDGF</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2-7-1-1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2-7-1-2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2-7-1-3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tamoxifen</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Exp. 4-4-1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>A3.2.M</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>A3.2.F</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>genotyping</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>G3.1.F</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>F</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Cre/+; f/f</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>+/+; f/f</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>H10.B</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>H9.2.X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>N</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>개체수 확인</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>weaning, genotyping</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>R1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>R2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>L1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>L2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>R1L1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Exp. 1-11-1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NA</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>R1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>R2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>L1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>L2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>R1L1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>corn oil</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tamoxifen</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Corn oil</t>
+  </si>
+  <si>
+    <t>A7.1.X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4/1 이후 개체수 확인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wt/ho x he/ho</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D2.1.X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>마리수 확인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Weaning</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1185,7 +1208,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1262,15 +1285,6 @@
     </font>
     <font>
       <strike/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
@@ -1363,7 +1377,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1421,9 +1435,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
@@ -1438,7 +1449,47 @@
     <cellStyle name="좋음" xfId="1" builtinId="26"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="66">
+  <dxfs count="70">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2537,7 +2588,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D71A6DC-E91C-489F-8F50-989C4712FA7C}">
   <sheetPr filterMode="1"/>
-  <dimension ref="B1:R263"/>
+  <dimension ref="B1:R267"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="10.5" customWidth="1"/>
@@ -2550,7 +2601,7 @@
     <col min="9" max="10" width="9" customWidth="1"/>
     <col min="11" max="11" width="11.125" style="2" customWidth="1"/>
     <col min="12" max="12" width="8.125" customWidth="1"/>
-    <col min="14" max="14" width="11.375" style="2" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="11.375" style="2" customWidth="1"/>
     <col min="15" max="15" width="12.625" style="2" customWidth="1"/>
     <col min="16" max="16" width="13.125" style="5" customWidth="1"/>
     <col min="17" max="17" width="23.75" customWidth="1"/>
@@ -2586,7 +2637,7 @@
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="L1" s="8" t="s">
         <v>14</v>
@@ -2604,10 +2655,10 @@
         <v>60</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="R1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="2" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -2631,11 +2682,11 @@
       </c>
       <c r="I2" s="4">
         <f ca="1">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H2), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H2), 7), "-")</f>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J2" s="4">
         <f ca="1">IF(_xlfn.DAYS(TODAY(),H2)&lt;10000, _xlfn.DAYS(TODAY(),H2), "-")</f>
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="L2" s="4" t="str">
         <f t="shared" ref="L2:L29" si="0">IF(_xlfn.DAYS(K2,H2)&gt;0, _xlfn.DAYS(K2,H2), "-")</f>
@@ -2671,11 +2722,11 @@
       </c>
       <c r="I3" s="4">
         <f t="shared" ref="I3:I69" ca="1" si="1">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H3), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H3), 7), "-")</f>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J3" s="4">
         <f t="shared" ref="J3:J29" ca="1" si="2">IF(_xlfn.DAYS(TODAY(),H3)&lt;10000, _xlfn.DAYS(TODAY(),H3), "-")</f>
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="L3" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2690,7 +2741,7 @@
       </c>
       <c r="P3"/>
       <c r="Q3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="4" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -2714,11 +2765,11 @@
       </c>
       <c r="I4" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J4" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="L4" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2733,7 +2784,7 @@
       </c>
       <c r="P4"/>
       <c r="Q4" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="5" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -2760,11 +2811,11 @@
       </c>
       <c r="I5" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J5" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="K5" s="2">
         <v>45293</v>
@@ -2806,11 +2857,11 @@
       </c>
       <c r="I6" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J6" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="K6" s="2">
         <v>45293</v>
@@ -2855,11 +2906,11 @@
       </c>
       <c r="I7" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J7" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="K7" s="2">
         <v>45293</v>
@@ -2899,11 +2950,11 @@
       </c>
       <c r="I8" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J8" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="K8" s="2">
         <v>45293</v>
@@ -2945,11 +2996,11 @@
       </c>
       <c r="I9" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J9" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="K9" s="2">
         <v>45293</v>
@@ -2988,11 +3039,11 @@
       </c>
       <c r="I10" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J10" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="L10" s="4" t="str">
         <f t="shared" si="0"/>
@@ -3105,11 +3156,11 @@
       </c>
       <c r="I13" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J13" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="L13" s="4" t="str">
         <f t="shared" si="0"/>
@@ -3124,7 +3175,7 @@
       </c>
       <c r="P13"/>
       <c r="Q13" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="14" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -3151,11 +3202,11 @@
       </c>
       <c r="I14" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J14" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="L14" s="4" t="str">
         <f t="shared" si="0"/>
@@ -3170,7 +3221,7 @@
       </c>
       <c r="P14"/>
       <c r="Q14" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="15" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -3197,11 +3248,11 @@
       </c>
       <c r="I15" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J15" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="L15" s="4" t="str">
         <f t="shared" si="0"/>
@@ -3215,7 +3266,7 @@
       </c>
       <c r="P15"/>
       <c r="Q15" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="16" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -3242,11 +3293,11 @@
       </c>
       <c r="I16" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J16" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="L16" s="4" t="str">
         <f t="shared" si="0"/>
@@ -3284,11 +3335,11 @@
       </c>
       <c r="I17" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J17" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="L17" s="4" t="str">
         <f t="shared" si="0"/>
@@ -3302,7 +3353,7 @@
       </c>
       <c r="P17"/>
       <c r="Q17" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="18" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -3326,11 +3377,11 @@
       </c>
       <c r="I18" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J18" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="L18" s="4" t="str">
         <f t="shared" si="0"/>
@@ -3401,11 +3452,11 @@
       </c>
       <c r="I20" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J20" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="K20" s="2">
         <v>45112</v>
@@ -3443,11 +3494,11 @@
       </c>
       <c r="I21" s="4">
         <f ca="1">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H21), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H21), 7), "-")</f>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J21" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="K21" s="2">
         <v>45176</v>
@@ -3488,11 +3539,11 @@
       </c>
       <c r="I22" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J22" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="K22" s="2">
         <v>45176</v>
@@ -3533,11 +3584,11 @@
       </c>
       <c r="I23" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J23" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="K23" s="2">
         <v>45176</v>
@@ -3578,11 +3629,11 @@
       </c>
       <c r="I24" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J24" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="K24" s="2">
         <v>45229</v>
@@ -3620,11 +3671,11 @@
       </c>
       <c r="I25" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J25" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="K25" s="2">
         <v>45229</v>
@@ -3662,11 +3713,11 @@
       </c>
       <c r="I26" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J26" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="K26" s="2">
         <v>45229</v>
@@ -3707,11 +3758,11 @@
       </c>
       <c r="I27" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J27" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="K27" s="2">
         <v>45229</v>
@@ -3755,11 +3806,11 @@
       </c>
       <c r="I28" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J28" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="K28" s="2">
         <v>45293</v>
@@ -3798,11 +3849,11 @@
       </c>
       <c r="I29" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J29" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="K29" s="2">
         <v>45315</v>
@@ -3838,11 +3889,11 @@
       </c>
       <c r="I30" s="4">
         <f t="shared" ref="I30" ca="1" si="3">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H30), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H30), 7), "-")</f>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J30" s="4">
         <f t="shared" ref="J30" ca="1" si="4">IF(_xlfn.DAYS(TODAY(),H30)&lt;10000, _xlfn.DAYS(TODAY(),H30), "-")</f>
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="K30" s="2">
         <v>45176</v>
@@ -3859,7 +3910,7 @@
       </c>
       <c r="P30"/>
       <c r="Q30" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="31" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -3883,11 +3934,11 @@
       </c>
       <c r="I31" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J31" s="4">
         <f t="shared" ref="J31:J37" ca="1" si="6">IF(_xlfn.DAYS(TODAY(),H31)&lt;10000, _xlfn.DAYS(TODAY(),H31), "-")</f>
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="K31" s="2">
         <v>45229</v>
@@ -3904,7 +3955,7 @@
       </c>
       <c r="P31"/>
       <c r="Q31" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="32" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -3967,11 +4018,11 @@
       </c>
       <c r="I33" s="4">
         <f ca="1">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H33), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H33), 7), "-")</f>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J33" s="4">
         <f ca="1">IF(_xlfn.DAYS(TODAY(),H33)&lt;10000, _xlfn.DAYS(TODAY(),H33), "-")</f>
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="K33" s="2">
         <v>45257</v>
@@ -4093,11 +4144,11 @@
       </c>
       <c r="I36" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J36" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="K36" s="2">
         <v>45257</v>
@@ -4141,11 +4192,11 @@
       </c>
       <c r="I37" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J37" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="K37" s="2">
         <v>45257</v>
@@ -4189,11 +4240,11 @@
       </c>
       <c r="I38" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J38" s="4">
         <f t="shared" ref="J38:J40" ca="1" si="8">IF(_xlfn.DAYS(TODAY(),H38)&lt;10000, _xlfn.DAYS(TODAY(),H38), "-")</f>
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="K38" s="2">
         <v>45257</v>
@@ -4237,11 +4288,11 @@
       </c>
       <c r="I39" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J39" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="K39" s="2">
         <v>45257</v>
@@ -4282,11 +4333,11 @@
       </c>
       <c r="I40" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J40" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="K40" s="2">
         <v>45257</v>
@@ -4327,11 +4378,11 @@
       </c>
       <c r="I41" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J41" s="4">
         <f t="shared" ref="J41:J42" ca="1" si="9">IF(_xlfn.DAYS(TODAY(),H41)&lt;10000, _xlfn.DAYS(TODAY(),H41), "-")</f>
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="L41" s="4" t="str">
         <f t="shared" si="7"/>
@@ -4366,11 +4417,11 @@
       </c>
       <c r="I42" s="4">
         <f t="shared" ref="I42" ca="1" si="10">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H42), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H42), 7), "-")</f>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J42" s="4">
         <f t="shared" ca="1" si="9"/>
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="K42" s="2">
         <v>45176</v>
@@ -4387,7 +4438,7 @@
       </c>
       <c r="P42"/>
       <c r="Q42" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="43" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -4414,11 +4465,11 @@
       </c>
       <c r="I43" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J43" s="4">
         <f t="shared" ref="J43:J94" ca="1" si="11">IF(_xlfn.DAYS(TODAY(),H43)&lt;10000, _xlfn.DAYS(TODAY(),H43), "-")</f>
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="L43" s="4" t="str">
         <f t="shared" si="7"/>
@@ -4432,7 +4483,7 @@
       </c>
       <c r="P43"/>
       <c r="Q43" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="44" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
@@ -4459,11 +4510,11 @@
       </c>
       <c r="I44" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J44" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="K44" s="2">
         <v>45293</v>
@@ -4504,11 +4555,11 @@
       </c>
       <c r="I45" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J45" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="K45" s="2">
         <v>45293</v>
@@ -4549,11 +4600,11 @@
       </c>
       <c r="I46" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J46" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="K46" s="2">
         <v>45293</v>
@@ -4597,11 +4648,11 @@
       </c>
       <c r="I47" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J47" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="K47" s="2">
         <v>45293</v>
@@ -4645,11 +4696,11 @@
       </c>
       <c r="I48" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J48" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="K48" s="2">
         <v>45293</v>
@@ -4693,11 +4744,11 @@
       </c>
       <c r="I49" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J49" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="K49" s="2">
         <v>45293</v>
@@ -4714,7 +4765,7 @@
       </c>
       <c r="P49"/>
       <c r="Q49" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="50" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -4741,11 +4792,11 @@
       </c>
       <c r="I50" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J50" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="K50" s="2">
         <v>45293</v>
@@ -4762,7 +4813,7 @@
       </c>
       <c r="P50"/>
       <c r="Q50" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="51" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -4789,11 +4840,11 @@
       </c>
       <c r="I51" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J51" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="K51" s="2">
         <v>45293</v>
@@ -4834,11 +4885,11 @@
       </c>
       <c r="I52" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J52" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="K52" s="2">
         <v>45293</v>
@@ -4879,11 +4930,11 @@
       </c>
       <c r="I53" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J53" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="K53" s="2">
         <v>45293</v>
@@ -4900,7 +4951,7 @@
       </c>
       <c r="P53"/>
       <c r="Q53" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="54" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -4927,11 +4978,11 @@
       </c>
       <c r="I54" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J54" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="K54" s="2">
         <v>45238</v>
@@ -4975,11 +5026,11 @@
       </c>
       <c r="I55" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J55" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="K55" s="2">
         <v>45238</v>
@@ -4996,7 +5047,7 @@
       </c>
       <c r="P55"/>
       <c r="Q55" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="56" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -5023,11 +5074,11 @@
       </c>
       <c r="I56" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J56" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="K56" s="2">
         <v>45238</v>
@@ -5044,7 +5095,7 @@
       </c>
       <c r="P56"/>
       <c r="Q56" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="57" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -5068,11 +5119,11 @@
       </c>
       <c r="I57" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="J57" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="L57" s="4" t="str">
         <f t="shared" si="7"/>
@@ -5086,7 +5137,7 @@
       </c>
       <c r="P57"/>
       <c r="Q57" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="58" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -5110,11 +5161,11 @@
       </c>
       <c r="I58" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="J58" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="L58" s="4" t="str">
         <f t="shared" si="7"/>
@@ -5128,7 +5179,7 @@
       </c>
       <c r="P58"/>
       <c r="Q58" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="59" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -5149,11 +5200,11 @@
       </c>
       <c r="I59" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J59" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="K59" s="2">
         <v>45295</v>
@@ -5170,7 +5221,7 @@
       </c>
       <c r="P59"/>
     </row>
-    <row r="60" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B60" t="s">
         <v>27</v>
       </c>
@@ -5191,11 +5242,11 @@
       </c>
       <c r="I60" s="4">
         <f t="shared" ref="I60:I61" ca="1" si="12">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H60), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H60), 7), "-")</f>
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="J60" s="4">
         <f t="shared" ref="J60:J61" ca="1" si="13">IF(_xlfn.DAYS(TODAY(),H60)&lt;10000, _xlfn.DAYS(TODAY(),H60), "-")</f>
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="L60" s="4" t="str">
         <f t="shared" ref="L60:L61" si="14">IF(_xlfn.DAYS(K60,H60)&gt;0, _xlfn.DAYS(K60,H60), "-")</f>
@@ -5205,10 +5256,10 @@
         <v>42</v>
       </c>
       <c r="Q60" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="61" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="61" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B61" t="s">
         <v>27</v>
       </c>
@@ -5229,11 +5280,11 @@
       </c>
       <c r="I61" s="4">
         <f t="shared" ca="1" si="12"/>
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="J61" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="L61" s="4" t="str">
         <f t="shared" si="14"/>
@@ -5243,10 +5294,10 @@
         <v>42</v>
       </c>
       <c r="Q61" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="62" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="62" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B62" t="s">
         <v>27</v>
       </c>
@@ -5267,11 +5318,11 @@
       </c>
       <c r="I62" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J62" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="K62" s="2">
         <v>45295</v>
@@ -5281,13 +5332,13 @@
         <v>28</v>
       </c>
       <c r="M62" s="4" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="R62" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="63" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="63" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B63" t="s">
         <v>34</v>
       </c>
@@ -5308,11 +5359,11 @@
       </c>
       <c r="I63" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J63" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="K63" s="7">
         <v>45324</v>
@@ -5322,13 +5373,13 @@
         <v>24</v>
       </c>
       <c r="M63" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="R63" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="64" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="64" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B64" t="s">
         <v>34</v>
       </c>
@@ -5349,11 +5400,11 @@
       </c>
       <c r="I64" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J64" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="K64" s="7">
         <v>45324</v>
@@ -5363,13 +5414,13 @@
         <v>24</v>
       </c>
       <c r="M64" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="R64" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="65" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B65" t="s">
         <v>27</v>
       </c>
@@ -5390,11 +5441,11 @@
       </c>
       <c r="I65" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J65" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="K65" s="2">
         <v>45295</v>
@@ -5404,10 +5455,10 @@
         <v>28</v>
       </c>
       <c r="M65" s="4" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="R65" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
     </row>
     <row r="66" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -5428,11 +5479,11 @@
       </c>
       <c r="I66" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J66" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="K66" s="2">
         <v>45295</v>
@@ -5449,7 +5500,7 @@
       </c>
       <c r="P66"/>
       <c r="Q66" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="67" spans="2:18" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
@@ -5471,11 +5522,11 @@
       </c>
       <c r="I67" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J67" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="K67" s="7">
         <v>45295</v>
@@ -5514,11 +5565,11 @@
       </c>
       <c r="I68" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J68" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="K68" s="7">
         <v>45295</v>
@@ -5538,7 +5589,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="69" spans="2:18" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:18" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B69" t="s">
         <v>34</v>
       </c>
@@ -5560,11 +5611,11 @@
       </c>
       <c r="I69" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J69" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="K69" s="7">
         <v>45324</v>
@@ -5574,14 +5625,14 @@
         <v>24</v>
       </c>
       <c r="M69" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" s="5"/>
       <c r="Q69"/>
       <c r="R69" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
     </row>
     <row r="70" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -5608,11 +5659,11 @@
       </c>
       <c r="I70" s="4">
         <f t="shared" ref="I70:I94" ca="1" si="15">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H70), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H70), 7), "-")</f>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J70" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="L70" s="4" t="str">
         <f t="shared" si="7"/>
@@ -5656,11 +5707,11 @@
       </c>
       <c r="I71" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J71" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="L71" s="4" t="str">
         <f t="shared" si="7"/>
@@ -5704,11 +5755,11 @@
       </c>
       <c r="I72" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J72" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="L72" s="4" t="str">
         <f t="shared" si="7"/>
@@ -5752,11 +5803,11 @@
       </c>
       <c r="I73" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J73" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="L73" s="4" t="str">
         <f t="shared" si="7"/>
@@ -5800,11 +5851,11 @@
       </c>
       <c r="I74" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J74" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="L74" s="4" t="str">
         <f t="shared" si="7"/>
@@ -5848,11 +5899,11 @@
       </c>
       <c r="I75" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J75" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="L75" s="4" t="str">
         <f t="shared" si="7"/>
@@ -5896,11 +5947,11 @@
       </c>
       <c r="I76" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J76" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="L76" s="4" t="str">
         <f t="shared" si="7"/>
@@ -5944,11 +5995,11 @@
       </c>
       <c r="I77" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J77" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="L77" s="4" t="str">
         <f t="shared" si="7"/>
@@ -5992,11 +6043,11 @@
       </c>
       <c r="I78" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J78" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="L78" s="4" t="str">
         <f t="shared" si="7"/>
@@ -6040,11 +6091,11 @@
       </c>
       <c r="I79" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J79" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="L79" s="4" t="str">
         <f t="shared" si="7"/>
@@ -6088,11 +6139,11 @@
       </c>
       <c r="I80" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J80" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="L80" s="4" t="str">
         <f t="shared" si="7"/>
@@ -6136,11 +6187,11 @@
       </c>
       <c r="I81" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J81" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="L81" s="4" t="str">
         <f t="shared" si="7"/>
@@ -6184,11 +6235,11 @@
       </c>
       <c r="I82" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J82" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="L82" s="4" t="str">
         <f t="shared" si="7"/>
@@ -6232,11 +6283,11 @@
       </c>
       <c r="I83" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J83" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="L83" s="4" t="str">
         <f t="shared" si="7"/>
@@ -6280,11 +6331,11 @@
       </c>
       <c r="I84" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J84" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="L84" s="4" t="str">
         <f t="shared" si="7"/>
@@ -6328,11 +6379,11 @@
       </c>
       <c r="I85" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J85" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="L85" s="4" t="str">
         <f t="shared" si="7"/>
@@ -6376,11 +6427,11 @@
       </c>
       <c r="I86" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J86" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="L86" s="4" t="str">
         <f t="shared" si="7"/>
@@ -6424,11 +6475,11 @@
       </c>
       <c r="I87" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J87" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="L87" s="4" t="str">
         <f t="shared" si="7"/>
@@ -6472,11 +6523,11 @@
       </c>
       <c r="I88" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J88" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="L88" s="4" t="str">
         <f t="shared" si="7"/>
@@ -6520,11 +6571,11 @@
       </c>
       <c r="I89" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J89" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="L89" s="4" t="str">
         <f t="shared" si="7"/>
@@ -6568,11 +6619,11 @@
       </c>
       <c r="I90" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J90" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="K90" s="2">
         <v>45272</v>
@@ -6616,11 +6667,11 @@
       </c>
       <c r="I91" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J91" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="K91" s="2">
         <v>45273</v>
@@ -6664,11 +6715,11 @@
       </c>
       <c r="I92" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J92" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="K92" s="2">
         <v>45274</v>
@@ -6712,11 +6763,11 @@
       </c>
       <c r="I93" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J93" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="K93" s="2">
         <v>45275</v>
@@ -6760,11 +6811,11 @@
       </c>
       <c r="I94" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J94" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="K94" s="2">
         <v>45276</v>
@@ -6808,11 +6859,11 @@
       </c>
       <c r="I95" s="4">
         <f t="shared" ref="I95:I96" ca="1" si="16">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H95), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H95), 7), "-")</f>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J95" s="4">
         <f t="shared" ref="J95:J96" ca="1" si="17">IF(_xlfn.DAYS(TODAY(),H95)&lt;10000, _xlfn.DAYS(TODAY(),H95), "-")</f>
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="K95" s="2">
         <v>45277</v>
@@ -6856,11 +6907,11 @@
       </c>
       <c r="I96" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J96" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="K96" s="2">
         <v>45278</v>
@@ -6904,11 +6955,11 @@
       </c>
       <c r="I97" s="4">
         <f t="shared" ref="I97" ca="1" si="18">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H97), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H97), 7), "-")</f>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J97" s="4">
         <f t="shared" ref="J97" ca="1" si="19">IF(_xlfn.DAYS(TODAY(),H97)&lt;10000, _xlfn.DAYS(TODAY(),H97), "-")</f>
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="K97" s="2">
         <v>45223</v>
@@ -6952,11 +7003,11 @@
       </c>
       <c r="I98" s="4">
         <f t="shared" ref="I98:I120" ca="1" si="20">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H98), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H98), 7), "-")</f>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J98" s="4">
         <f t="shared" ref="J98:J120" ca="1" si="21">IF(_xlfn.DAYS(TODAY(),H98)&lt;10000, _xlfn.DAYS(TODAY(),H98), "-")</f>
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="K98" s="2">
         <v>45223</v>
@@ -7000,11 +7051,11 @@
       </c>
       <c r="I99" s="4">
         <f t="shared" ca="1" si="20"/>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J99" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="K99" s="2">
         <v>45223</v>
@@ -7048,11 +7099,11 @@
       </c>
       <c r="I100" s="4">
         <f t="shared" ca="1" si="20"/>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J100" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="K100" s="2">
         <v>45223</v>
@@ -7096,11 +7147,11 @@
       </c>
       <c r="I101" s="4">
         <f t="shared" ref="I101:I110" ca="1" si="23">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H101), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H101), 7), "-")</f>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J101" s="4">
         <f t="shared" ref="J101:J110" ca="1" si="24">IF(_xlfn.DAYS(TODAY(),H101)&lt;10000, _xlfn.DAYS(TODAY(),H101), "-")</f>
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="K101" s="2">
         <v>45267</v>
@@ -7147,11 +7198,11 @@
       </c>
       <c r="I102" s="4">
         <f t="shared" ca="1" si="23"/>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J102" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="K102" s="2">
         <v>45267</v>
@@ -7198,11 +7249,11 @@
       </c>
       <c r="I103" s="4">
         <f t="shared" ca="1" si="23"/>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J103" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="K103" s="2">
         <v>45267</v>
@@ -7249,11 +7300,11 @@
       </c>
       <c r="I104" s="4">
         <f t="shared" ca="1" si="23"/>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J104" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="K104" s="2">
         <v>45267</v>
@@ -7300,11 +7351,11 @@
       </c>
       <c r="I105" s="4">
         <f t="shared" ca="1" si="23"/>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J105" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="K105" s="2">
         <v>45267</v>
@@ -7351,11 +7402,11 @@
       </c>
       <c r="I106" s="4">
         <f t="shared" ca="1" si="23"/>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J106" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="K106" s="2">
         <v>45267</v>
@@ -7402,11 +7453,11 @@
       </c>
       <c r="I107" s="4">
         <f t="shared" ca="1" si="23"/>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J107" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="K107" s="2">
         <v>45267</v>
@@ -7453,11 +7504,11 @@
       </c>
       <c r="I108" s="4">
         <f t="shared" ca="1" si="23"/>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J108" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="K108" s="2">
         <v>45267</v>
@@ -7504,11 +7555,11 @@
       </c>
       <c r="I109" s="4">
         <f t="shared" ca="1" si="23"/>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J109" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="K109" s="2">
         <v>45267</v>
@@ -7555,11 +7606,11 @@
       </c>
       <c r="I110" s="4">
         <f t="shared" ca="1" si="23"/>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J110" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="K110" s="2">
         <v>45267</v>
@@ -8077,11 +8128,11 @@
       </c>
       <c r="I123" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J123" s="4">
         <f t="shared" ca="1" si="26"/>
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="K123" s="2">
         <v>45315</v>
@@ -8122,11 +8173,11 @@
       </c>
       <c r="I124" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J124" s="4">
         <f t="shared" ca="1" si="26"/>
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="K124" s="2">
         <v>45315</v>
@@ -8167,11 +8218,11 @@
       </c>
       <c r="I125" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J125" s="4">
         <f t="shared" ca="1" si="26"/>
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="K125" s="2">
         <v>45315</v>
@@ -8205,18 +8256,18 @@
         <v>85</v>
       </c>
       <c r="G126" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="H126" s="2">
         <v>45309</v>
       </c>
       <c r="I126" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J126" s="4">
         <f t="shared" ca="1" si="26"/>
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="L126" s="4" t="str">
         <f t="shared" si="22"/>
@@ -8230,7 +8281,7 @@
       </c>
       <c r="P126"/>
       <c r="Q126" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="127" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -8262,16 +8313,16 @@
         <v>42</v>
       </c>
       <c r="L127" s="4" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="M127" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="O127"/>
       <c r="P127"/>
       <c r="Q127" s="2"/>
       <c r="R127" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="128" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -8291,30 +8342,30 @@
         <v>86</v>
       </c>
       <c r="G128" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="H128" s="2">
         <v>45309</v>
       </c>
       <c r="I128" s="4">
         <f t="shared" ref="I128:I129" ca="1" si="27">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H128), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H128), 7), "-")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J128" s="4">
         <f t="shared" ref="J128:J129" ca="1" si="28">IF(_xlfn.DAYS(TODAY(),H128)&lt;10000, _xlfn.DAYS(TODAY(),H128), "-")</f>
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="L128" s="4" t="str">
         <f t="shared" si="22"/>
         <v>-</v>
       </c>
       <c r="M128" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="P128"/>
       <c r="Q128" s="2"/>
       <c r="R128" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="129" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -8322,7 +8373,7 @@
         <v>100</v>
       </c>
       <c r="C129" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D129">
         <v>796</v>
@@ -8334,18 +8385,18 @@
         <v>85</v>
       </c>
       <c r="G129" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="H129" s="2">
         <v>45309</v>
       </c>
       <c r="I129" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J129" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="L129" s="4" t="str">
         <f t="shared" si="22"/>
@@ -8359,7 +8410,7 @@
       </c>
       <c r="P129"/>
       <c r="Q129" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="130" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -8385,15 +8436,15 @@
         <v>196</v>
       </c>
       <c r="L130" s="4" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="M130" s="4" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="O130"/>
       <c r="P130"/>
       <c r="R130" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="131" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -8413,29 +8464,29 @@
         <v>84</v>
       </c>
       <c r="G131" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="H131" s="2">
         <v>45309</v>
       </c>
       <c r="I131" s="4">
         <f t="shared" ref="I131:I134" ca="1" si="29">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H131), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H131), 7), "-")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J131" s="4">
         <f t="shared" ref="J131:J134" ca="1" si="30">IF(_xlfn.DAYS(TODAY(),H131)&lt;10000, _xlfn.DAYS(TODAY(),H131), "-")</f>
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="L131" s="4" t="str">
         <f t="shared" si="22"/>
         <v>-</v>
       </c>
       <c r="M131" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="P131"/>
       <c r="R131" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="132" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -8455,29 +8506,29 @@
         <v>84</v>
       </c>
       <c r="G132" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="H132" s="2">
         <v>45309</v>
       </c>
       <c r="I132" s="4">
         <f t="shared" ca="1" si="29"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J132" s="4">
         <f t="shared" ca="1" si="30"/>
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="L132" s="4" t="str">
         <f t="shared" si="22"/>
         <v>-</v>
       </c>
       <c r="M132" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="P132"/>
       <c r="R132" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="133" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -8498,22 +8549,22 @@
       </c>
       <c r="I133" s="4">
         <f t="shared" ca="1" si="29"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J133" s="4">
         <f t="shared" ca="1" si="30"/>
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="L133" s="4" t="str">
         <f t="shared" si="22"/>
         <v>-</v>
       </c>
       <c r="M133" s="4" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="P133"/>
       <c r="R133" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="134" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -8533,29 +8584,29 @@
         <v>84</v>
       </c>
       <c r="G134" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="H134" s="2">
         <v>45309</v>
       </c>
       <c r="I134" s="4">
         <f t="shared" ca="1" si="29"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J134" s="4">
         <f t="shared" ca="1" si="30"/>
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="L134" s="4" t="str">
         <f t="shared" si="22"/>
         <v>-</v>
       </c>
       <c r="M134" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="P134"/>
       <c r="R134" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="135" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -8650,11 +8701,11 @@
       </c>
       <c r="I137" s="4">
         <f t="shared" ca="1" si="31"/>
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J137" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>483</v>
+        <v>493</v>
       </c>
       <c r="L137" s="4" t="str">
         <f t="shared" si="33"/>
@@ -8686,11 +8737,11 @@
       </c>
       <c r="I138" s="4">
         <f t="shared" ca="1" si="31"/>
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J138" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>483</v>
+        <v>493</v>
       </c>
       <c r="L138" s="4" t="str">
         <f t="shared" si="33"/>
@@ -8722,11 +8773,11 @@
       </c>
       <c r="I139" s="4">
         <f t="shared" ca="1" si="31"/>
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J139" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>483</v>
+        <v>493</v>
       </c>
       <c r="L139" s="4" t="str">
         <f t="shared" si="33"/>
@@ -8758,11 +8809,11 @@
       </c>
       <c r="I140" s="4">
         <f t="shared" ca="1" si="31"/>
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J140" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>483</v>
+        <v>493</v>
       </c>
       <c r="L140" s="4" t="str">
         <f t="shared" si="33"/>
@@ -8833,11 +8884,11 @@
       </c>
       <c r="I142" s="4">
         <f t="shared" ca="1" si="31"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J142" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="L142" s="4" t="str">
         <f t="shared" si="33"/>
@@ -8848,7 +8899,7 @@
       </c>
       <c r="P142"/>
     </row>
-    <row r="143" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="143" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B143" t="s">
         <v>27</v>
       </c>
@@ -8865,18 +8916,18 @@
         <v>86</v>
       </c>
       <c r="G143" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="H143" s="2">
         <v>45301</v>
       </c>
       <c r="I143" s="4">
         <f t="shared" ca="1" si="31"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J143" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="L143" s="4" t="str">
         <f t="shared" si="33"/>
@@ -8889,13 +8940,13 @@
         <v>45363</v>
       </c>
       <c r="P143" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="R143" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="144" spans="2:18" x14ac:dyDescent="0.3">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="144" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B144" t="s">
         <v>27</v>
       </c>
@@ -8912,18 +8963,18 @@
         <v>86</v>
       </c>
       <c r="G144" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="H144" s="2">
         <v>45301</v>
       </c>
       <c r="I144" s="4">
         <f t="shared" ca="1" si="31"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J144" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="L144" s="4" t="str">
         <f t="shared" si="33"/>
@@ -8936,13 +8987,13 @@
         <v>45363</v>
       </c>
       <c r="P144" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="R144" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="145" spans="2:18" x14ac:dyDescent="0.3">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="145" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B145" t="s">
         <v>27</v>
       </c>
@@ -8959,18 +9010,18 @@
         <v>86</v>
       </c>
       <c r="G145" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="H145" s="2">
         <v>45301</v>
       </c>
       <c r="I145" s="4">
         <f t="shared" ca="1" si="31"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J145" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="L145" s="4" t="str">
         <f t="shared" si="33"/>
@@ -8983,10 +9034,10 @@
         <v>45363</v>
       </c>
       <c r="P145" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="R145" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
     </row>
     <row r="146" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -9006,18 +9057,18 @@
         <v>87</v>
       </c>
       <c r="G146" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="H146" s="2">
         <v>45301</v>
       </c>
       <c r="I146" s="4">
         <f t="shared" ca="1" si="31"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J146" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="L146" s="4" t="str">
         <f t="shared" si="33"/>
@@ -9031,7 +9082,7 @@
       </c>
       <c r="P146"/>
     </row>
-    <row r="147" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="147" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B147" t="s">
         <v>27</v>
       </c>
@@ -9048,18 +9099,18 @@
         <v>86</v>
       </c>
       <c r="G147" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="H147" s="2">
         <v>45301</v>
       </c>
       <c r="I147" s="4">
         <f t="shared" ca="1" si="31"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J147" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="L147" s="4" t="str">
         <f t="shared" si="33"/>
@@ -9072,10 +9123,10 @@
         <v>45363</v>
       </c>
       <c r="P147" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="R147" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
     </row>
     <row r="148" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -9177,7 +9228,7 @@
       </c>
       <c r="P150"/>
     </row>
-    <row r="151" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="151" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B151" t="s">
         <v>27</v>
       </c>
@@ -9194,18 +9245,18 @@
         <v>86</v>
       </c>
       <c r="G151" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="H151" s="2">
         <v>45307</v>
       </c>
       <c r="I151" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J151" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="L151" s="4" t="str">
         <f t="shared" si="36"/>
@@ -9218,10 +9269,10 @@
         <v>45357</v>
       </c>
       <c r="P151" s="5" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="R151" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="152" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -9241,18 +9292,18 @@
         <v>87</v>
       </c>
       <c r="G152" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="H152" s="2">
         <v>45307</v>
       </c>
       <c r="I152" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J152" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="L152" s="4" t="str">
         <f t="shared" si="36"/>
@@ -9283,18 +9334,18 @@
         <v>134</v>
       </c>
       <c r="G153" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="H153" s="2">
         <v>45307</v>
       </c>
       <c r="I153" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J153" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="L153" s="4" t="str">
         <f t="shared" si="36"/>
@@ -9325,18 +9376,18 @@
         <v>134</v>
       </c>
       <c r="G154" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="H154" s="2">
         <v>45307</v>
       </c>
       <c r="I154" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J154" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="L154" s="4" t="str">
         <f t="shared" si="36"/>
@@ -9350,7 +9401,7 @@
       </c>
       <c r="P154"/>
     </row>
-    <row r="155" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="155" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B155" t="s">
         <v>27</v>
       </c>
@@ -9367,18 +9418,18 @@
         <v>86</v>
       </c>
       <c r="G155" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="H155" s="2">
         <v>45307</v>
       </c>
       <c r="I155" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J155" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="L155" s="4" t="str">
         <f t="shared" si="36"/>
@@ -9391,10 +9442,10 @@
         <v>45357</v>
       </c>
       <c r="P155" s="5" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="R155" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
     </row>
     <row r="156" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -9414,18 +9465,18 @@
         <v>86</v>
       </c>
       <c r="G156" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="H156" s="2">
         <v>45307</v>
       </c>
       <c r="I156" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J156" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="L156" s="4" t="str">
         <f t="shared" si="36"/>
@@ -9460,11 +9511,11 @@
       </c>
       <c r="I157" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J157" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="L157" s="4" t="str">
         <f t="shared" si="36"/>
@@ -9637,11 +9688,11 @@
       </c>
       <c r="I162" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J162" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="K162" s="2">
         <v>45301</v>
@@ -9709,11 +9760,11 @@
       </c>
       <c r="I164" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J164" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="K164" s="2">
         <v>45301</v>
@@ -9748,11 +9799,11 @@
       </c>
       <c r="I165" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J165" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="K165" s="2">
         <v>45301</v>
@@ -9793,11 +9844,11 @@
       </c>
       <c r="I166" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J166" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="K166" s="2">
         <v>45301</v>
@@ -9835,11 +9886,11 @@
       </c>
       <c r="I167" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J167" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="K167" s="2">
         <v>45301</v>
@@ -9886,11 +9937,11 @@
       </c>
       <c r="I168" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J168" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="K168" s="2">
         <v>45301</v>
@@ -9928,11 +9979,11 @@
       </c>
       <c r="I169" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J169" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="L169" s="4" t="str">
         <f t="shared" si="36"/>
@@ -9973,11 +10024,11 @@
       </c>
       <c r="I170" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J170" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="L170" s="4" t="str">
         <f t="shared" si="36"/>
@@ -9995,9 +10046,9 @@
       <c r="P170" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="Q170" s="20"/>
+      <c r="Q170" s="19"/>
       <c r="R170" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="171" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -10021,11 +10072,11 @@
       </c>
       <c r="I171" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J171" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="L171" s="4" t="str">
         <f t="shared" si="36"/>
@@ -10044,7 +10095,7 @@
         <v>156</v>
       </c>
       <c r="R171" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="172" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -10071,11 +10122,11 @@
       </c>
       <c r="I172" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J172" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="K172" s="2">
         <v>45301</v>
@@ -10121,11 +10172,11 @@
       </c>
       <c r="I173" s="4">
         <f t="shared" ref="I173:I174" ca="1" si="40">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H173), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H173), 7), "-")</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J173" s="4">
         <f t="shared" ref="J173:J174" ca="1" si="41">IF(_xlfn.DAYS(TODAY(),H173)&lt;10000, _xlfn.DAYS(TODAY(),H173), "-")</f>
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="L173" s="4" t="str">
         <f t="shared" ref="L173:L174" si="42">IF(_xlfn.DAYS(K173,H173)&gt;0, _xlfn.DAYS(K173,H173), "-")</f>
@@ -10193,11 +10244,11 @@
       </c>
       <c r="I175" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J175" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="K175" s="2">
         <v>45301</v>
@@ -10235,11 +10286,11 @@
       </c>
       <c r="I176" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J176" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="K176" s="2">
         <v>45301</v>
@@ -10261,7 +10312,7 @@
         <v>156</v>
       </c>
       <c r="R176" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="177" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -10288,11 +10339,11 @@
       </c>
       <c r="I177" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J177" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="K177" s="2">
         <v>45301</v>
@@ -10314,7 +10365,7 @@
         <v>156</v>
       </c>
       <c r="R177" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="178" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -10341,11 +10392,11 @@
       </c>
       <c r="I178" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J178" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="K178" s="2">
         <v>45301</v>
@@ -10367,7 +10418,7 @@
         <v>156</v>
       </c>
       <c r="R178" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="179" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -10394,11 +10445,11 @@
       </c>
       <c r="I179" s="4">
         <f t="shared" ca="1" si="34"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J179" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="L179" s="4" t="str">
         <f t="shared" si="36"/>
@@ -10417,7 +10468,7 @@
         <v>156</v>
       </c>
       <c r="R179" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="180" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -10428,7 +10479,7 @@
         <v>110</v>
       </c>
       <c r="D180" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="E180" t="s">
         <v>16</v>
@@ -10444,11 +10495,11 @@
       </c>
       <c r="I180" s="4">
         <f t="shared" ref="I180:I189" ca="1" si="43">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H180), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H180), 7), "-")</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J180" s="4">
         <f t="shared" ref="J180:J189" ca="1" si="44">IF(_xlfn.DAYS(TODAY(),H180)&lt;10000, _xlfn.DAYS(TODAY(),H180), "-")</f>
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="K180" s="7">
         <v>45324</v>
@@ -10460,11 +10511,14 @@
       <c r="M180" t="s">
         <v>158</v>
       </c>
+      <c r="O180" s="2">
+        <v>45370</v>
+      </c>
       <c r="P180" s="5" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="R180" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
     </row>
     <row r="181" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -10475,7 +10529,7 @@
         <v>110</v>
       </c>
       <c r="D181" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="E181" t="s">
         <v>16</v>
@@ -10491,11 +10545,11 @@
       </c>
       <c r="I181" s="4">
         <f t="shared" ca="1" si="43"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J181" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="K181" s="7">
         <v>45324</v>
@@ -10507,11 +10561,14 @@
       <c r="M181" t="s">
         <v>158</v>
       </c>
+      <c r="O181" s="2">
+        <v>45370</v>
+      </c>
       <c r="P181" s="5" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="R181" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
     </row>
     <row r="182" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -10522,7 +10579,7 @@
         <v>110</v>
       </c>
       <c r="D182" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="E182" t="s">
         <v>16</v>
@@ -10538,11 +10595,11 @@
       </c>
       <c r="I182" s="4">
         <f t="shared" ca="1" si="43"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J182" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="K182" s="7">
         <v>45324</v>
@@ -10554,11 +10611,14 @@
       <c r="M182" t="s">
         <v>158</v>
       </c>
+      <c r="O182" s="2">
+        <v>45370</v>
+      </c>
       <c r="P182" s="5" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="R182" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
     </row>
     <row r="183" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -10569,7 +10629,7 @@
         <v>110</v>
       </c>
       <c r="D183" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="E183" t="s">
         <v>16</v>
@@ -10585,11 +10645,11 @@
       </c>
       <c r="I183" s="4">
         <f t="shared" ca="1" si="43"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J183" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="K183" s="7">
         <v>45324</v>
@@ -10601,11 +10661,14 @@
       <c r="M183" t="s">
         <v>158</v>
       </c>
+      <c r="O183" s="2">
+        <v>45370</v>
+      </c>
       <c r="P183" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="R183" t="s">
         <v>281</v>
-      </c>
-      <c r="R183" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="184" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -10616,7 +10679,7 @@
         <v>110</v>
       </c>
       <c r="D184" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="E184" t="s">
         <v>16</v>
@@ -10632,11 +10695,11 @@
       </c>
       <c r="I184" s="4">
         <f t="shared" ca="1" si="43"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J184" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="K184" s="7">
         <v>45324</v>
@@ -10648,11 +10711,14 @@
       <c r="M184" t="s">
         <v>158</v>
       </c>
+      <c r="O184" s="2">
+        <v>45370</v>
+      </c>
       <c r="P184" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="R184" t="s">
         <v>281</v>
-      </c>
-      <c r="R184" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="185" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -10663,7 +10729,7 @@
         <v>110</v>
       </c>
       <c r="D185" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="E185" t="s">
         <v>16</v>
@@ -10679,11 +10745,11 @@
       </c>
       <c r="I185" s="4">
         <f t="shared" ca="1" si="43"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J185" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="K185" s="7">
         <v>45324</v>
@@ -10695,14 +10761,17 @@
       <c r="M185" t="s">
         <v>158</v>
       </c>
+      <c r="O185" s="2">
+        <v>45370</v>
+      </c>
       <c r="P185" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="R185" t="s">
         <v>281</v>
       </c>
-      <c r="R185" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="186" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="186" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B186" t="s">
         <v>160</v>
       </c>
@@ -10716,18 +10785,18 @@
         <v>134</v>
       </c>
       <c r="G186" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="H186" s="2">
         <v>45324</v>
       </c>
       <c r="I186" s="4">
         <f t="shared" ca="1" si="43"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J186" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="K186" s="2">
         <v>45357</v>
@@ -10737,7 +10806,7 @@
         <v>33</v>
       </c>
       <c r="M186" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
     </row>
     <row r="187" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -10748,10 +10817,10 @@
         <v>127</v>
       </c>
       <c r="F187" s="5" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="G187" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="I187" s="4" t="str">
         <f t="shared" ref="I187" ca="1" si="46">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H187), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H187), 7), "-")</f>
@@ -10766,7 +10835,7 @@
         <v>-</v>
       </c>
       <c r="M187" s="4" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
     </row>
     <row r="188" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -10777,28 +10846,28 @@
         <v>127</v>
       </c>
       <c r="F188" s="5" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="G188" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="H188" s="2">
         <v>45269</v>
       </c>
       <c r="I188" s="4">
         <f t="shared" ca="1" si="43"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J188" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="L188" s="4" t="str">
         <f t="shared" si="48"/>
         <v>-</v>
       </c>
       <c r="M188" s="4" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
     </row>
     <row r="189" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -10812,32 +10881,32 @@
         <v>16</v>
       </c>
       <c r="G189" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="H189" s="2">
         <v>45327</v>
       </c>
       <c r="I189" s="4">
         <f t="shared" ca="1" si="43"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J189" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="L189" s="4" t="str">
         <f t="shared" si="48"/>
         <v>-</v>
       </c>
       <c r="M189" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="P189"/>
       <c r="Q189" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="R189" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="190" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -10851,32 +10920,32 @@
         <v>16</v>
       </c>
       <c r="G190" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="H190" s="2">
         <v>45327</v>
       </c>
       <c r="I190" s="4">
         <f t="shared" ref="I190:I194" ca="1" si="49">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H190), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H190), 7), "-")</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J190" s="4">
         <f t="shared" ref="J190:J194" ca="1" si="50">IF(_xlfn.DAYS(TODAY(),H190)&lt;10000, _xlfn.DAYS(TODAY(),H190), "-")</f>
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="L190" s="4" t="str">
         <f t="shared" ref="L190:L194" si="51">IF(_xlfn.DAYS(K190,H190)&gt;0, _xlfn.DAYS(K190,H190), "-")</f>
         <v>-</v>
       </c>
       <c r="M190" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="P190"/>
       <c r="Q190" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="R190" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="191" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -10890,32 +10959,32 @@
         <v>16</v>
       </c>
       <c r="G191" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="H191" s="2">
         <v>45327</v>
       </c>
       <c r="I191" s="4">
         <f t="shared" ca="1" si="49"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J191" s="4">
         <f t="shared" ca="1" si="50"/>
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="L191" s="4" t="str">
         <f t="shared" si="51"/>
         <v>-</v>
       </c>
       <c r="M191" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="P191"/>
       <c r="Q191" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="R191" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="192" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -10929,32 +10998,32 @@
         <v>16</v>
       </c>
       <c r="G192" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="H192" s="2">
         <v>45327</v>
       </c>
       <c r="I192" s="4">
         <f t="shared" ca="1" si="49"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J192" s="4">
         <f t="shared" ca="1" si="50"/>
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="L192" s="4" t="str">
         <f t="shared" si="51"/>
         <v>-</v>
       </c>
       <c r="M192" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="P192"/>
       <c r="Q192" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="R192" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="193" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -10968,32 +11037,32 @@
         <v>16</v>
       </c>
       <c r="G193" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="H193" s="2">
         <v>45327</v>
       </c>
       <c r="I193" s="4">
         <f t="shared" ca="1" si="49"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J193" s="4">
         <f t="shared" ca="1" si="50"/>
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="L193" s="4" t="str">
         <f t="shared" si="51"/>
         <v>-</v>
       </c>
       <c r="M193" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P193"/>
       <c r="Q193" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="R193" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="194" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -11007,32 +11076,32 @@
         <v>16</v>
       </c>
       <c r="G194" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="H194" s="2">
         <v>45327</v>
       </c>
       <c r="I194" s="4">
         <f t="shared" ca="1" si="49"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J194" s="4">
         <f t="shared" ca="1" si="50"/>
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="L194" s="4" t="str">
         <f t="shared" si="51"/>
         <v>-</v>
       </c>
       <c r="M194" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P194"/>
       <c r="Q194" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="R194" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="195" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -11265,34 +11334,34 @@
         <v>112</v>
       </c>
       <c r="D201" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E201" t="s">
         <v>7</v>
       </c>
       <c r="F201" s="5" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="G201" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="H201" s="2">
         <v>45332</v>
       </c>
       <c r="I201" s="4">
         <f t="shared" ref="I201" ca="1" si="55">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H201), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H201), 7), "-")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J201" s="4">
         <f t="shared" ref="J201" ca="1" si="56">IF(_xlfn.DAYS(TODAY(),H201)&lt;10000, _xlfn.DAYS(TODAY(),H201), "-")</f>
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="L201" s="4" t="str">
         <f t="shared" ref="L201" si="57">IF(_xlfn.DAYS(K201,H201)&gt;0, _xlfn.DAYS(K201,H201), "-")</f>
         <v>-</v>
       </c>
       <c r="M201" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="O201" s="2">
         <v>45364</v>
@@ -11302,7 +11371,7 @@
         <v>171</v>
       </c>
       <c r="R201" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="202" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -11313,34 +11382,34 @@
         <v>112</v>
       </c>
       <c r="D202" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E202" t="s">
         <v>8</v>
       </c>
       <c r="F202" s="5" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G202" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="H202" s="2">
         <v>45332</v>
       </c>
       <c r="I202" s="4">
         <f t="shared" ref="I202:I216" ca="1" si="58">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H202), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H202), 7), "-")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J202" s="4">
         <f t="shared" ref="J202:J216" ca="1" si="59">IF(_xlfn.DAYS(TODAY(),H202)&lt;10000, _xlfn.DAYS(TODAY(),H202), "-")</f>
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="L202" s="4" t="str">
         <f t="shared" ref="L202:L216" si="60">IF(_xlfn.DAYS(K202,H202)&gt;0, _xlfn.DAYS(K202,H202), "-")</f>
         <v>-</v>
       </c>
       <c r="M202" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="O202" s="2">
         <v>45364</v>
@@ -11350,7 +11419,7 @@
         <v>171</v>
       </c>
       <c r="R202" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="203" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -11361,34 +11430,34 @@
         <v>112</v>
       </c>
       <c r="D203" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E203" t="s">
         <v>8</v>
       </c>
       <c r="F203" s="5" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G203" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="H203" s="2">
         <v>45332</v>
       </c>
       <c r="I203" s="4">
         <f t="shared" ca="1" si="58"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J203" s="4">
         <f t="shared" ca="1" si="59"/>
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="L203" s="4" t="str">
         <f t="shared" si="60"/>
         <v>-</v>
       </c>
       <c r="M203" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="O203" s="2">
         <v>45364</v>
@@ -11398,7 +11467,7 @@
         <v>171</v>
       </c>
       <c r="R203" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="204" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -11409,34 +11478,34 @@
         <v>112</v>
       </c>
       <c r="D204" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E204" t="s">
         <v>8</v>
       </c>
       <c r="F204" s="5" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G204" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="H204" s="2">
         <v>45332</v>
       </c>
       <c r="I204" s="4">
         <f t="shared" ca="1" si="58"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J204" s="4">
         <f t="shared" ca="1" si="59"/>
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="L204" s="4" t="str">
         <f t="shared" si="60"/>
         <v>-</v>
       </c>
       <c r="M204" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="O204" s="2">
         <v>45364</v>
@@ -11446,7 +11515,7 @@
         <v>171</v>
       </c>
       <c r="R204" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="205" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -11457,34 +11526,34 @@
         <v>112</v>
       </c>
       <c r="D205" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E205" t="s">
         <v>8</v>
       </c>
       <c r="F205" s="5" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G205" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="H205" s="2">
         <v>45332</v>
       </c>
       <c r="I205" s="4">
         <f t="shared" ca="1" si="58"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J205" s="4">
         <f t="shared" ca="1" si="59"/>
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="L205" s="4" t="str">
         <f t="shared" si="60"/>
         <v>-</v>
       </c>
       <c r="M205" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="O205" s="2">
         <v>45364</v>
@@ -11494,7 +11563,7 @@
         <v>171</v>
       </c>
       <c r="R205" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="206" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -11505,34 +11574,34 @@
         <v>112</v>
       </c>
       <c r="D206" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E206" t="s">
         <v>7</v>
       </c>
       <c r="F206" s="5" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G206" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="H206" s="2">
         <v>45332</v>
       </c>
       <c r="I206" s="4">
         <f t="shared" ca="1" si="58"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J206" s="4">
         <f t="shared" ca="1" si="59"/>
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="L206" s="4" t="str">
         <f t="shared" si="60"/>
         <v>-</v>
       </c>
       <c r="M206" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="O206" s="2">
         <v>45364</v>
@@ -11542,7 +11611,7 @@
         <v>171</v>
       </c>
       <c r="R206" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="207" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -11553,34 +11622,34 @@
         <v>112</v>
       </c>
       <c r="D207" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E207" t="s">
         <v>7</v>
       </c>
       <c r="F207" s="5" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G207" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="H207" s="2">
         <v>45332</v>
       </c>
       <c r="I207" s="4">
         <f t="shared" ca="1" si="58"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J207" s="4">
         <f t="shared" ca="1" si="59"/>
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="L207" s="4" t="str">
         <f t="shared" si="60"/>
         <v>-</v>
       </c>
       <c r="M207" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="O207" s="2">
         <v>45364</v>
@@ -11590,7 +11659,7 @@
         <v>171</v>
       </c>
       <c r="R207" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="208" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -11601,34 +11670,34 @@
         <v>112</v>
       </c>
       <c r="D208" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E208" t="s">
         <v>7</v>
       </c>
       <c r="F208" s="5" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="G208" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="H208" s="2">
         <v>45332</v>
       </c>
       <c r="I208" s="4">
         <f t="shared" ca="1" si="58"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J208" s="4">
         <f t="shared" ca="1" si="59"/>
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="L208" s="4" t="str">
         <f t="shared" si="60"/>
         <v>-</v>
       </c>
       <c r="M208" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="O208" s="2">
         <v>45364</v>
@@ -11638,7 +11707,7 @@
         <v>171</v>
       </c>
       <c r="R208" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="209" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -11649,34 +11718,34 @@
         <v>112</v>
       </c>
       <c r="D209" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E209" t="s">
         <v>7</v>
       </c>
       <c r="F209" s="5" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="G209" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="H209" s="2">
         <v>45332</v>
       </c>
       <c r="I209" s="4">
         <f t="shared" ca="1" si="58"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J209" s="4">
         <f t="shared" ca="1" si="59"/>
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="L209" s="4" t="str">
         <f t="shared" si="60"/>
         <v>-</v>
       </c>
       <c r="M209" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="O209" s="2">
         <v>45364</v>
@@ -11686,7 +11755,7 @@
         <v>171</v>
       </c>
       <c r="R209" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="210" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -11697,24 +11766,24 @@
         <v>112</v>
       </c>
       <c r="D210" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="E210" t="s">
         <v>15</v>
       </c>
       <c r="G210" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="H210" s="2">
         <v>45337</v>
       </c>
       <c r="I210" s="4">
         <f t="shared" ca="1" si="58"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J210" s="4">
         <f t="shared" ca="1" si="59"/>
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="K210" s="2">
         <v>45363</v>
@@ -11724,11 +11793,11 @@
         <v>26</v>
       </c>
       <c r="M210" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="P210"/>
       <c r="R210" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="211" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -11739,24 +11808,24 @@
         <v>112</v>
       </c>
       <c r="D211" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="E211" t="s">
         <v>15</v>
       </c>
       <c r="G211" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="H211" s="2">
         <v>45337</v>
       </c>
       <c r="I211" s="4">
         <f t="shared" ca="1" si="58"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J211" s="4">
         <f t="shared" ca="1" si="59"/>
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="K211" s="2">
         <v>45363</v>
@@ -11766,11 +11835,11 @@
         <v>26</v>
       </c>
       <c r="M211" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="P211"/>
       <c r="R211" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="212" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -11781,24 +11850,24 @@
         <v>112</v>
       </c>
       <c r="D212" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="E212" t="s">
         <v>15</v>
       </c>
       <c r="G212" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="H212" s="2">
         <v>45337</v>
       </c>
       <c r="I212" s="4">
         <f t="shared" ca="1" si="58"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J212" s="4">
         <f t="shared" ca="1" si="59"/>
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="K212" s="2">
         <v>45363</v>
@@ -11808,11 +11877,11 @@
         <v>26</v>
       </c>
       <c r="M212" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="P212"/>
       <c r="R212" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="213" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -11823,24 +11892,24 @@
         <v>112</v>
       </c>
       <c r="D213" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="E213" t="s">
         <v>15</v>
       </c>
       <c r="G213" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="H213" s="2">
         <v>45337</v>
       </c>
       <c r="I213" s="4">
         <f t="shared" ca="1" si="58"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J213" s="4">
         <f t="shared" ca="1" si="59"/>
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="K213" s="2">
         <v>45363</v>
@@ -11850,11 +11919,11 @@
         <v>26</v>
       </c>
       <c r="M213" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="P213"/>
       <c r="R213" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="214" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -11865,24 +11934,24 @@
         <v>112</v>
       </c>
       <c r="D214" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="E214" t="s">
         <v>15</v>
       </c>
       <c r="G214" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="H214" s="2">
         <v>45337</v>
       </c>
       <c r="I214" s="4">
         <f t="shared" ca="1" si="58"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J214" s="4">
         <f t="shared" ca="1" si="59"/>
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="K214" s="2">
         <v>45363</v>
@@ -11892,11 +11961,11 @@
         <v>26</v>
       </c>
       <c r="M214" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="P214"/>
       <c r="R214" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="215" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -11907,24 +11976,24 @@
         <v>112</v>
       </c>
       <c r="D215" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="E215" t="s">
         <v>15</v>
       </c>
       <c r="G215" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="H215" s="2">
         <v>45337</v>
       </c>
       <c r="I215" s="4">
         <f t="shared" ca="1" si="58"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J215" s="4">
         <f t="shared" ca="1" si="59"/>
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="K215" s="2">
         <v>45363</v>
@@ -11934,11 +12003,11 @@
         <v>26</v>
       </c>
       <c r="M215" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="P215"/>
       <c r="R215" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="216" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -11949,24 +12018,24 @@
         <v>112</v>
       </c>
       <c r="D216" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="E216" t="s">
         <v>15</v>
       </c>
       <c r="G216" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="H216" s="2">
         <v>45337</v>
       </c>
       <c r="I216" s="4">
         <f t="shared" ca="1" si="58"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J216" s="4">
         <f t="shared" ca="1" si="59"/>
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="K216" s="2">
         <v>45363</v>
@@ -11976,11 +12045,11 @@
         <v>26</v>
       </c>
       <c r="M216" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="P216"/>
       <c r="R216" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="217" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -11991,32 +12060,35 @@
         <v>127</v>
       </c>
       <c r="E217" t="s">
-        <v>200</v>
+        <v>198</v>
+      </c>
+      <c r="G217" t="s">
+        <v>288</v>
       </c>
       <c r="H217" s="2">
         <v>45343</v>
       </c>
       <c r="I217" s="4">
-        <f t="shared" ref="I217:I228" ca="1" si="61">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H217), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H217), 7), "-")</f>
-        <v>3</v>
+        <f t="shared" ref="I217:I227" ca="1" si="61">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H217), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H217), 7), "-")</f>
+        <v>5</v>
       </c>
       <c r="J217" s="4">
-        <f t="shared" ref="J217:J228" ca="1" si="62">IF(_xlfn.DAYS(TODAY(),H217)&lt;10000, _xlfn.DAYS(TODAY(),H217), "-")</f>
-        <v>25</v>
+        <f t="shared" ref="J217:J227" ca="1" si="62">IF(_xlfn.DAYS(TODAY(),H217)&lt;10000, _xlfn.DAYS(TODAY(),H217), "-")</f>
+        <v>35</v>
       </c>
       <c r="L217" s="4" t="str">
-        <f t="shared" ref="L217:L228" si="63">IF(_xlfn.DAYS(K217,H217)&gt;0, _xlfn.DAYS(K217,H217), "-")</f>
+        <f t="shared" ref="L217:L227" si="63">IF(_xlfn.DAYS(K217,H217)&gt;0, _xlfn.DAYS(K217,H217), "-")</f>
         <v>-</v>
       </c>
       <c r="M217" t="s">
-        <v>198</v>
+        <v>283</v>
       </c>
       <c r="P217"/>
       <c r="Q217" t="s">
-        <v>275</v>
+        <v>236</v>
       </c>
       <c r="R217" t="s">
-        <v>203</v>
+        <v>286</v>
       </c>
     </row>
     <row r="218" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -12029,30 +12101,33 @@
       <c r="E218" t="s">
         <v>16</v>
       </c>
+      <c r="G218" t="s">
+        <v>288</v>
+      </c>
       <c r="H218" s="2">
         <v>45343</v>
       </c>
       <c r="I218" s="4">
-        <f t="shared" ca="1" si="61"/>
-        <v>3</v>
+        <f t="shared" ref="I218" ca="1" si="64">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H218), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H218), 7), "-")</f>
+        <v>5</v>
       </c>
       <c r="J218" s="4">
-        <f t="shared" ca="1" si="62"/>
-        <v>25</v>
+        <f t="shared" ref="J218" ca="1" si="65">IF(_xlfn.DAYS(TODAY(),H218)&lt;10000, _xlfn.DAYS(TODAY(),H218), "-")</f>
+        <v>35</v>
       </c>
       <c r="L218" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" ref="L218" si="66">IF(_xlfn.DAYS(K218,H218)&gt;0, _xlfn.DAYS(K218,H218), "-")</f>
         <v>-</v>
       </c>
       <c r="M218" t="s">
-        <v>198</v>
+        <v>283</v>
       </c>
       <c r="P218"/>
       <c r="Q218" t="s">
-        <v>275</v>
+        <v>236</v>
       </c>
       <c r="R218" t="s">
-        <v>203</v>
+        <v>286</v>
       </c>
     </row>
     <row r="219" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -12065,30 +12140,33 @@
       <c r="E219" t="s">
         <v>16</v>
       </c>
+      <c r="G219" t="s">
+        <v>288</v>
+      </c>
       <c r="H219" s="2">
         <v>45343</v>
       </c>
       <c r="I219" s="4">
         <f t="shared" ca="1" si="61"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J219" s="4">
         <f t="shared" ca="1" si="62"/>
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="L219" s="4" t="str">
         <f t="shared" si="63"/>
         <v>-</v>
       </c>
       <c r="M219" t="s">
-        <v>198</v>
+        <v>283</v>
       </c>
       <c r="P219"/>
       <c r="Q219" t="s">
-        <v>275</v>
+        <v>236</v>
       </c>
       <c r="R219" t="s">
-        <v>203</v>
+        <v>287</v>
       </c>
     </row>
     <row r="220" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -12098,33 +12176,36 @@
       <c r="C220" t="s">
         <v>127</v>
       </c>
-      <c r="E220" s="2" t="s">
+      <c r="E220" t="s">
         <v>16</v>
+      </c>
+      <c r="G220" t="s">
+        <v>289</v>
       </c>
       <c r="H220" s="2">
         <v>45343</v>
       </c>
       <c r="I220" s="4">
         <f t="shared" ca="1" si="61"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J220" s="4">
         <f t="shared" ca="1" si="62"/>
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="L220" s="4" t="str">
         <f t="shared" si="63"/>
         <v>-</v>
       </c>
       <c r="M220" t="s">
-        <v>198</v>
+        <v>284</v>
       </c>
       <c r="P220"/>
       <c r="Q220" t="s">
-        <v>275</v>
+        <v>236</v>
       </c>
       <c r="R220" t="s">
-        <v>203</v>
+        <v>287</v>
       </c>
     </row>
     <row r="221" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -12134,33 +12215,36 @@
       <c r="C221" t="s">
         <v>127</v>
       </c>
-      <c r="E221" t="s">
+      <c r="E221" s="2" t="s">
         <v>16</v>
+      </c>
+      <c r="G221" t="s">
+        <v>289</v>
       </c>
       <c r="H221" s="2">
         <v>45343</v>
       </c>
       <c r="I221" s="4">
         <f t="shared" ca="1" si="61"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J221" s="4">
         <f t="shared" ca="1" si="62"/>
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="L221" s="4" t="str">
         <f t="shared" si="63"/>
         <v>-</v>
       </c>
       <c r="M221" t="s">
-        <v>198</v>
+        <v>284</v>
       </c>
       <c r="P221"/>
       <c r="Q221" t="s">
-        <v>275</v>
+        <v>236</v>
       </c>
       <c r="R221" t="s">
-        <v>203</v>
+        <v>287</v>
       </c>
     </row>
     <row r="222" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -12173,30 +12257,33 @@
       <c r="E222" t="s">
         <v>16</v>
       </c>
+      <c r="G222" t="s">
+        <v>289</v>
+      </c>
       <c r="H222" s="2">
         <v>45343</v>
       </c>
       <c r="I222" s="4">
         <f t="shared" ca="1" si="61"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J222" s="4">
         <f t="shared" ca="1" si="62"/>
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="L222" s="4" t="str">
         <f t="shared" si="63"/>
         <v>-</v>
       </c>
       <c r="M222" t="s">
-        <v>199</v>
+        <v>284</v>
       </c>
       <c r="P222"/>
       <c r="Q222" t="s">
-        <v>275</v>
+        <v>236</v>
       </c>
       <c r="R222" t="s">
-        <v>203</v>
+        <v>287</v>
       </c>
     </row>
     <row r="223" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -12206,33 +12293,36 @@
       <c r="C223" t="s">
         <v>127</v>
       </c>
-      <c r="E223" s="2" t="s">
+      <c r="E223" t="s">
         <v>16</v>
+      </c>
+      <c r="G223" t="s">
+        <v>289</v>
       </c>
       <c r="H223" s="2">
         <v>45343</v>
       </c>
       <c r="I223" s="4">
         <f t="shared" ca="1" si="61"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J223" s="4">
         <f t="shared" ca="1" si="62"/>
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="L223" s="4" t="str">
         <f t="shared" si="63"/>
         <v>-</v>
       </c>
       <c r="M223" t="s">
-        <v>199</v>
+        <v>284</v>
       </c>
       <c r="P223"/>
       <c r="Q223" t="s">
-        <v>275</v>
+        <v>236</v>
       </c>
       <c r="R223" t="s">
-        <v>203</v>
+        <v>287</v>
       </c>
     </row>
     <row r="224" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -12240,32 +12330,38 @@
         <v>5</v>
       </c>
       <c r="C224" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="E224" t="s">
         <v>16</v>
       </c>
+      <c r="G224" t="s">
+        <v>263</v>
+      </c>
       <c r="H224" s="2">
-        <v>45343</v>
+        <v>45337</v>
       </c>
       <c r="I224" s="4">
         <f t="shared" ca="1" si="61"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J224" s="4">
         <f t="shared" ca="1" si="62"/>
-        <v>25</v>
-      </c>
-      <c r="L224" s="4" t="str">
+        <v>41</v>
+      </c>
+      <c r="K224" s="2">
+        <v>45363</v>
+      </c>
+      <c r="L224" s="4">
         <f t="shared" si="63"/>
-        <v>-</v>
-      </c>
-      <c r="M224" t="s">
-        <v>199</v>
+        <v>26</v>
+      </c>
+      <c r="M224" s="4" t="s">
+        <v>262</v>
       </c>
       <c r="P224"/>
       <c r="Q224" t="s">
-        <v>275</v>
+        <v>261</v>
       </c>
       <c r="R224" t="s">
         <v>203</v>
@@ -12282,18 +12378,18 @@
         <v>16</v>
       </c>
       <c r="G225" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="H225" s="2">
         <v>45337</v>
       </c>
       <c r="I225" s="4">
         <f t="shared" ca="1" si="61"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J225" s="4">
         <f t="shared" ca="1" si="62"/>
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="K225" s="2">
         <v>45363</v>
@@ -12303,14 +12399,14 @@
         <v>26</v>
       </c>
       <c r="M225" s="4" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="P225"/>
       <c r="Q225" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="R225" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="226" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -12324,18 +12420,18 @@
         <v>16</v>
       </c>
       <c r="G226" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="H226" s="2">
         <v>45337</v>
       </c>
       <c r="I226" s="4">
         <f t="shared" ca="1" si="61"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J226" s="4">
         <f t="shared" ca="1" si="62"/>
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="K226" s="2">
         <v>45363</v>
@@ -12345,14 +12441,14 @@
         <v>26</v>
       </c>
       <c r="M226" s="4" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="P226"/>
       <c r="Q226" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="R226" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="227" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -12360,16 +12456,13 @@
         <v>5</v>
       </c>
       <c r="C227" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="E227" t="s">
         <v>16</v>
       </c>
-      <c r="G227" t="s">
-        <v>267</v>
-      </c>
       <c r="H227" s="2">
-        <v>45337</v>
+        <v>45349</v>
       </c>
       <c r="I227" s="4">
         <f t="shared" ca="1" si="61"/>
@@ -12377,24 +12470,18 @@
       </c>
       <c r="J227" s="4">
         <f t="shared" ca="1" si="62"/>
-        <v>31</v>
-      </c>
-      <c r="K227" s="2">
-        <v>45363</v>
-      </c>
-      <c r="L227" s="4">
+        <v>29</v>
+      </c>
+      <c r="L227" s="4" t="str">
         <f t="shared" si="63"/>
-        <v>26</v>
-      </c>
-      <c r="M227" s="4" t="s">
-        <v>266</v>
+        <v>-</v>
+      </c>
+      <c r="M227" t="s">
+        <v>200</v>
       </c>
       <c r="P227"/>
-      <c r="Q227" t="s">
-        <v>265</v>
-      </c>
       <c r="R227" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
     </row>
     <row r="228" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -12411,23 +12498,23 @@
         <v>45349</v>
       </c>
       <c r="I228" s="4">
-        <f t="shared" ca="1" si="61"/>
-        <v>2</v>
+        <f t="shared" ref="I228:I235" ca="1" si="67">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H228), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H228), 7), "-")</f>
+        <v>4</v>
       </c>
       <c r="J228" s="4">
-        <f t="shared" ca="1" si="62"/>
-        <v>19</v>
+        <f t="shared" ref="J228:J235" ca="1" si="68">IF(_xlfn.DAYS(TODAY(),H228)&lt;10000, _xlfn.DAYS(TODAY(),H228), "-")</f>
+        <v>29</v>
       </c>
       <c r="L228" s="4" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" ref="L228:L235" si="69">IF(_xlfn.DAYS(K228,H228)&gt;0, _xlfn.DAYS(K228,H228), "-")</f>
         <v>-</v>
       </c>
       <c r="M228" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="P228"/>
       <c r="R228" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="229" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -12444,23 +12531,23 @@
         <v>45349</v>
       </c>
       <c r="I229" s="4">
-        <f t="shared" ref="I229:I237" ca="1" si="64">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H229), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H229), 7), "-")</f>
-        <v>2</v>
+        <f t="shared" ca="1" si="67"/>
+        <v>4</v>
       </c>
       <c r="J229" s="4">
-        <f t="shared" ref="J229:J237" ca="1" si="65">IF(_xlfn.DAYS(TODAY(),H229)&lt;10000, _xlfn.DAYS(TODAY(),H229), "-")</f>
-        <v>19</v>
+        <f t="shared" ca="1" si="68"/>
+        <v>29</v>
       </c>
       <c r="L229" s="4" t="str">
-        <f t="shared" ref="L229:L237" si="66">IF(_xlfn.DAYS(K229,H229)&gt;0, _xlfn.DAYS(K229,H229), "-")</f>
+        <f t="shared" si="69"/>
         <v>-</v>
       </c>
       <c r="M229" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="P229"/>
       <c r="R229" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="230" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -12477,92 +12564,102 @@
         <v>45349</v>
       </c>
       <c r="I230" s="4">
-        <f t="shared" ca="1" si="64"/>
-        <v>2</v>
+        <f t="shared" ca="1" si="67"/>
+        <v>4</v>
       </c>
       <c r="J230" s="4">
-        <f t="shared" ca="1" si="65"/>
-        <v>19</v>
+        <f t="shared" ca="1" si="68"/>
+        <v>29</v>
       </c>
       <c r="L230" s="4" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="69"/>
         <v>-</v>
       </c>
       <c r="M230" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="P230"/>
       <c r="R230" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="231" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="231" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B231" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="C231" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="E231" t="s">
         <v>16</v>
       </c>
+      <c r="F231" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="G231" t="s">
+        <v>247</v>
+      </c>
       <c r="H231" s="2">
-        <v>45349</v>
+        <v>45324</v>
       </c>
       <c r="I231" s="4">
-        <f t="shared" ca="1" si="64"/>
-        <v>2</v>
+        <f t="shared" ca="1" si="67"/>
+        <v>7</v>
       </c>
       <c r="J231" s="4">
-        <f t="shared" ca="1" si="65"/>
-        <v>19</v>
-      </c>
-      <c r="L231" s="4" t="str">
-        <f t="shared" si="66"/>
-        <v>-</v>
+        <f t="shared" ca="1" si="68"/>
+        <v>54</v>
+      </c>
+      <c r="K231" s="2">
+        <v>45357</v>
+      </c>
+      <c r="L231" s="4">
+        <f t="shared" si="69"/>
+        <v>33</v>
       </c>
       <c r="M231" t="s">
-        <v>202</v>
-      </c>
-      <c r="P231"/>
-      <c r="R231" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="232" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="232" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B232" t="s">
-        <v>237</v>
+        <v>34</v>
       </c>
       <c r="C232" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="E232" t="s">
-        <v>238</v>
+        <v>16</v>
+      </c>
+      <c r="F232" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="G232" t="s">
+        <v>247</v>
       </c>
       <c r="H232" s="2">
-        <v>45355</v>
+        <v>45324</v>
       </c>
       <c r="I232" s="4">
-        <f t="shared" ca="1" si="64"/>
-        <v>1</v>
+        <f t="shared" ca="1" si="67"/>
+        <v>7</v>
       </c>
       <c r="J232" s="4">
-        <f t="shared" ca="1" si="65"/>
-        <v>13</v>
-      </c>
-      <c r="L232" s="4" t="str">
-        <f t="shared" si="66"/>
-        <v>-</v>
+        <f t="shared" ca="1" si="68"/>
+        <v>54</v>
+      </c>
+      <c r="K232" s="2">
+        <v>45357</v>
+      </c>
+      <c r="L232" s="4">
+        <f t="shared" si="69"/>
+        <v>33</v>
       </c>
       <c r="M232" t="s">
-        <v>239</v>
-      </c>
-      <c r="P232"/>
-      <c r="Q232" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="233" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="233" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B233" t="s">
         <v>34</v>
       </c>
@@ -12576,31 +12673,31 @@
         <v>134</v>
       </c>
       <c r="G233" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="H233" s="2">
         <v>45324</v>
       </c>
       <c r="I233" s="4">
-        <f t="shared" ca="1" si="64"/>
-        <v>6</v>
+        <f t="shared" ca="1" si="67"/>
+        <v>7</v>
       </c>
       <c r="J233" s="4">
-        <f t="shared" ca="1" si="65"/>
-        <v>44</v>
+        <f t="shared" ca="1" si="68"/>
+        <v>54</v>
       </c>
       <c r="K233" s="2">
         <v>45357</v>
       </c>
       <c r="L233" s="4">
-        <f t="shared" si="66"/>
+        <f t="shared" si="69"/>
         <v>33</v>
       </c>
       <c r="M233" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="234" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="234" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B234" t="s">
         <v>34</v>
       </c>
@@ -12614,31 +12711,31 @@
         <v>134</v>
       </c>
       <c r="G234" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="H234" s="2">
         <v>45324</v>
       </c>
       <c r="I234" s="4">
-        <f t="shared" ca="1" si="64"/>
-        <v>6</v>
+        <f t="shared" ca="1" si="67"/>
+        <v>7</v>
       </c>
       <c r="J234" s="4">
-        <f t="shared" ca="1" si="65"/>
-        <v>44</v>
+        <f t="shared" ca="1" si="68"/>
+        <v>54</v>
       </c>
       <c r="K234" s="2">
         <v>45357</v>
       </c>
       <c r="L234" s="4">
-        <f t="shared" si="66"/>
+        <f t="shared" si="69"/>
         <v>33</v>
       </c>
       <c r="M234" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="235" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="235" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B235" t="s">
         <v>34</v>
       </c>
@@ -12652,28 +12749,28 @@
         <v>134</v>
       </c>
       <c r="G235" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="H235" s="2">
         <v>45324</v>
       </c>
       <c r="I235" s="4">
-        <f t="shared" ca="1" si="64"/>
-        <v>6</v>
+        <f t="shared" ca="1" si="67"/>
+        <v>7</v>
       </c>
       <c r="J235" s="4">
-        <f t="shared" ca="1" si="65"/>
-        <v>44</v>
+        <f t="shared" ca="1" si="68"/>
+        <v>54</v>
       </c>
       <c r="K235" s="2">
         <v>45357</v>
       </c>
       <c r="L235" s="4">
-        <f t="shared" si="66"/>
+        <f t="shared" si="69"/>
         <v>33</v>
       </c>
       <c r="M235" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
     </row>
     <row r="236" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -12686,35 +12783,27 @@
       <c r="E236" t="s">
         <v>16</v>
       </c>
-      <c r="F236" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="G236" t="s">
-        <v>251</v>
-      </c>
       <c r="H236" s="2">
         <v>45324</v>
       </c>
       <c r="I236" s="4">
-        <f t="shared" ca="1" si="64"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J236" s="4">
-        <f t="shared" ca="1" si="65"/>
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="K236" s="2">
         <v>45357</v>
       </c>
-      <c r="L236" s="4">
-        <f t="shared" si="66"/>
-        <v>33</v>
-      </c>
       <c r="M236" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="237" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+        <v>246</v>
+      </c>
+      <c r="O236" s="2">
+        <v>45357</v>
+      </c>
+      <c r="P236"/>
+    </row>
+    <row r="237" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B237" t="s">
         <v>34</v>
       </c>
@@ -12724,35 +12813,32 @@
       <c r="E237" t="s">
         <v>16</v>
       </c>
-      <c r="F237" s="5" t="s">
-        <v>134</v>
-      </c>
       <c r="G237" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="H237" s="2">
-        <v>45324</v>
+        <v>45350</v>
       </c>
       <c r="I237" s="4">
-        <f t="shared" ca="1" si="64"/>
-        <v>6</v>
+        <f t="shared" ref="I237" ca="1" si="70">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H237), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H237), 7), "-")</f>
+        <v>4</v>
       </c>
       <c r="J237" s="4">
-        <f t="shared" ca="1" si="65"/>
-        <v>44</v>
-      </c>
-      <c r="K237" s="2">
-        <v>45357</v>
-      </c>
-      <c r="L237" s="4">
-        <f t="shared" si="66"/>
-        <v>33</v>
+        <f t="shared" ref="J237" ca="1" si="71">IF(_xlfn.DAYS(TODAY(),H237)&lt;10000, _xlfn.DAYS(TODAY(),H237), "-")</f>
+        <v>28</v>
+      </c>
+      <c r="L237" s="4" t="str">
+        <f t="shared" ref="L237" si="72">IF(_xlfn.DAYS(K237,H237)&gt;0, _xlfn.DAYS(K237,H237), "-")</f>
+        <v>-</v>
       </c>
       <c r="M237" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="238" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+        <v>248</v>
+      </c>
+      <c r="Q237" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="238" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B238" t="s">
         <v>34</v>
       </c>
@@ -12762,27 +12848,32 @@
       <c r="E238" t="s">
         <v>16</v>
       </c>
+      <c r="G238" t="s">
+        <v>247</v>
+      </c>
       <c r="H238" s="2">
-        <v>45324</v>
+        <v>45350</v>
       </c>
       <c r="I238" s="4">
+        <f t="shared" ref="I238" ca="1" si="73">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H238), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H238), 7), "-")</f>
         <v>4</v>
       </c>
       <c r="J238" s="4">
-        <v>34</v>
-      </c>
-      <c r="K238" s="2">
-        <v>45357</v>
+        <f t="shared" ref="J238" ca="1" si="74">IF(_xlfn.DAYS(TODAY(),H238)&lt;10000, _xlfn.DAYS(TODAY(),H238), "-")</f>
+        <v>28</v>
+      </c>
+      <c r="L238" s="4" t="str">
+        <f t="shared" ref="L238" si="75">IF(_xlfn.DAYS(K238,H238)&gt;0, _xlfn.DAYS(K238,H238), "-")</f>
+        <v>-</v>
       </c>
       <c r="M238" t="s">
-        <v>250</v>
-      </c>
-      <c r="O238" s="2">
-        <v>45357</v>
-      </c>
-      <c r="P238"/>
-    </row>
-    <row r="239" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+        <v>248</v>
+      </c>
+      <c r="Q238" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="239" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B239" t="s">
         <v>34</v>
       </c>
@@ -12793,28 +12884,31 @@
         <v>16</v>
       </c>
       <c r="G239" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="H239" s="2">
         <v>45350</v>
       </c>
       <c r="I239" s="4">
-        <f t="shared" ref="I239" ca="1" si="67">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H239), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H239), 7), "-")</f>
-        <v>2</v>
+        <f t="shared" ref="I239:I241" ca="1" si="76">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H239), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H239), 7), "-")</f>
+        <v>4</v>
       </c>
       <c r="J239" s="4">
-        <f t="shared" ref="J239" ca="1" si="68">IF(_xlfn.DAYS(TODAY(),H239)&lt;10000, _xlfn.DAYS(TODAY(),H239), "-")</f>
-        <v>18</v>
+        <f t="shared" ref="J239:J241" ca="1" si="77">IF(_xlfn.DAYS(TODAY(),H239)&lt;10000, _xlfn.DAYS(TODAY(),H239), "-")</f>
+        <v>28</v>
       </c>
       <c r="L239" s="4" t="str">
-        <f t="shared" ref="L239" si="69">IF(_xlfn.DAYS(K239,H239)&gt;0, _xlfn.DAYS(K239,H239), "-")</f>
+        <f t="shared" ref="L239:L255" si="78">IF(_xlfn.DAYS(K239,H239)&gt;0, _xlfn.DAYS(K239,H239), "-")</f>
         <v>-</v>
       </c>
       <c r="M239" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="240" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+        <v>248</v>
+      </c>
+      <c r="Q239" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="240" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B240" t="s">
         <v>34</v>
       </c>
@@ -12825,25 +12919,28 @@
         <v>16</v>
       </c>
       <c r="G240" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="H240" s="2">
         <v>45350</v>
       </c>
       <c r="I240" s="4">
-        <f t="shared" ref="I240" ca="1" si="70">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H240), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H240), 7), "-")</f>
-        <v>2</v>
+        <f t="shared" ca="1" si="76"/>
+        <v>4</v>
       </c>
       <c r="J240" s="4">
-        <f t="shared" ref="J240" ca="1" si="71">IF(_xlfn.DAYS(TODAY(),H240)&lt;10000, _xlfn.DAYS(TODAY(),H240), "-")</f>
-        <v>18</v>
+        <f t="shared" ca="1" si="77"/>
+        <v>28</v>
       </c>
       <c r="L240" s="4" t="str">
-        <f t="shared" ref="L240" si="72">IF(_xlfn.DAYS(K240,H240)&gt;0, _xlfn.DAYS(K240,H240), "-")</f>
+        <f t="shared" si="78"/>
         <v>-</v>
       </c>
       <c r="M240" t="s">
-        <v>252</v>
+        <v>248</v>
+      </c>
+      <c r="Q240" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="241" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -12851,31 +12948,43 @@
         <v>34</v>
       </c>
       <c r="C241" t="s">
-        <v>110</v>
-      </c>
-      <c r="E241" t="s">
-        <v>16</v>
+        <v>249</v>
+      </c>
+      <c r="D241" t="s">
+        <v>274</v>
       </c>
       <c r="G241" t="s">
+        <v>247</v>
+      </c>
+      <c r="H241" s="2">
+        <v>45313</v>
+      </c>
+      <c r="I241" s="4">
+        <f t="shared" ca="1" si="76"/>
+        <v>9</v>
+      </c>
+      <c r="J241" s="4">
+        <f t="shared" ca="1" si="77"/>
+        <v>65</v>
+      </c>
+      <c r="K241" s="2">
+        <v>45350</v>
+      </c>
+      <c r="L241" s="4">
+        <f t="shared" si="78"/>
+        <v>37</v>
+      </c>
+      <c r="M241" t="s">
+        <v>254</v>
+      </c>
+      <c r="N241" s="2">
+        <v>45353</v>
+      </c>
+      <c r="P241" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="R241" t="s">
         <v>251</v>
-      </c>
-      <c r="H241" s="2">
-        <v>45350</v>
-      </c>
-      <c r="I241" s="4">
-        <f t="shared" ref="I241:I243" ca="1" si="73">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H241), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H241), 7), "-")</f>
-        <v>2</v>
-      </c>
-      <c r="J241" s="4">
-        <f t="shared" ref="J241:J243" ca="1" si="74">IF(_xlfn.DAYS(TODAY(),H241)&lt;10000, _xlfn.DAYS(TODAY(),H241), "-")</f>
-        <v>18</v>
-      </c>
-      <c r="L241" s="4" t="str">
-        <f t="shared" ref="L241:L258" si="75">IF(_xlfn.DAYS(K241,H241)&gt;0, _xlfn.DAYS(K241,H241), "-")</f>
-        <v>-</v>
-      </c>
-      <c r="M241" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="242" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -12883,31 +12992,43 @@
         <v>34</v>
       </c>
       <c r="C242" t="s">
-        <v>110</v>
-      </c>
-      <c r="E242" t="s">
-        <v>16</v>
+        <v>249</v>
+      </c>
+      <c r="D242" t="s">
+        <v>275</v>
       </c>
       <c r="G242" t="s">
+        <v>247</v>
+      </c>
+      <c r="H242" s="2">
+        <v>45313</v>
+      </c>
+      <c r="I242" s="4">
+        <f t="shared" ref="I242:I255" ca="1" si="79">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H242), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H242), 7), "-")</f>
+        <v>9</v>
+      </c>
+      <c r="J242" s="4">
+        <f t="shared" ref="J242:J255" ca="1" si="80">IF(_xlfn.DAYS(TODAY(),H242)&lt;10000, _xlfn.DAYS(TODAY(),H242), "-")</f>
+        <v>65</v>
+      </c>
+      <c r="K242" s="2">
+        <v>45350</v>
+      </c>
+      <c r="L242" s="4">
+        <f t="shared" si="78"/>
+        <v>37</v>
+      </c>
+      <c r="M242" t="s">
+        <v>254</v>
+      </c>
+      <c r="N242" s="2">
+        <v>45353</v>
+      </c>
+      <c r="P242" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="R242" t="s">
         <v>251</v>
-      </c>
-      <c r="H242" s="2">
-        <v>45350</v>
-      </c>
-      <c r="I242" s="4">
-        <f t="shared" ca="1" si="73"/>
-        <v>2</v>
-      </c>
-      <c r="J242" s="4">
-        <f t="shared" ca="1" si="74"/>
-        <v>18</v>
-      </c>
-      <c r="L242" s="4" t="str">
-        <f t="shared" si="75"/>
-        <v>-</v>
-      </c>
-      <c r="M242" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="243" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -12915,43 +13036,43 @@
         <v>34</v>
       </c>
       <c r="C243" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="D243" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="G243" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="H243" s="2">
         <v>45313</v>
       </c>
       <c r="I243" s="4">
-        <f t="shared" ca="1" si="73"/>
-        <v>7</v>
+        <f t="shared" ca="1" si="79"/>
+        <v>9</v>
       </c>
       <c r="J243" s="4">
-        <f t="shared" ca="1" si="74"/>
-        <v>55</v>
+        <f t="shared" ca="1" si="80"/>
+        <v>65</v>
       </c>
       <c r="K243" s="2">
         <v>45350</v>
       </c>
       <c r="L243" s="4">
-        <f t="shared" si="75"/>
+        <f t="shared" si="78"/>
         <v>37</v>
       </c>
       <c r="M243" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="N243" s="2">
         <v>45353</v>
       </c>
       <c r="P243" s="5" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="R243" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
     </row>
     <row r="244" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -12959,43 +13080,43 @@
         <v>34</v>
       </c>
       <c r="C244" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="D244" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="G244" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="H244" s="2">
         <v>45313</v>
       </c>
       <c r="I244" s="4">
-        <f t="shared" ref="I244:I258" ca="1" si="76">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H244), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H244), 7), "-")</f>
-        <v>7</v>
+        <f t="shared" ca="1" si="79"/>
+        <v>9</v>
       </c>
       <c r="J244" s="4">
-        <f t="shared" ref="J244:J258" ca="1" si="77">IF(_xlfn.DAYS(TODAY(),H244)&lt;10000, _xlfn.DAYS(TODAY(),H244), "-")</f>
-        <v>55</v>
+        <f t="shared" ca="1" si="80"/>
+        <v>65</v>
       </c>
       <c r="K244" s="2">
         <v>45350</v>
       </c>
       <c r="L244" s="4">
-        <f t="shared" si="75"/>
+        <f t="shared" si="78"/>
         <v>37</v>
       </c>
       <c r="M244" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="N244" s="2">
         <v>45353</v>
       </c>
       <c r="P244" s="5" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="R244" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
     </row>
     <row r="245" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -13003,43 +13124,43 @@
         <v>34</v>
       </c>
       <c r="C245" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="D245" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="G245" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="H245" s="2">
         <v>45313</v>
       </c>
       <c r="I245" s="4">
-        <f t="shared" ca="1" si="76"/>
-        <v>7</v>
+        <f t="shared" ca="1" si="79"/>
+        <v>9</v>
       </c>
       <c r="J245" s="4">
-        <f t="shared" ca="1" si="77"/>
-        <v>55</v>
+        <f t="shared" ca="1" si="80"/>
+        <v>65</v>
       </c>
       <c r="K245" s="2">
         <v>45350</v>
       </c>
       <c r="L245" s="4">
-        <f t="shared" si="75"/>
+        <f t="shared" si="78"/>
         <v>37</v>
       </c>
       <c r="M245" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="N245" s="2">
         <v>45353</v>
       </c>
       <c r="P245" s="5" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="R245" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
     </row>
     <row r="246" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -13047,43 +13168,43 @@
         <v>34</v>
       </c>
       <c r="C246" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="D246" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="G246" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="H246" s="2">
         <v>45313</v>
       </c>
       <c r="I246" s="4">
-        <f t="shared" ca="1" si="76"/>
-        <v>7</v>
+        <f t="shared" ca="1" si="79"/>
+        <v>9</v>
       </c>
       <c r="J246" s="4">
-        <f t="shared" ca="1" si="77"/>
-        <v>55</v>
+        <f t="shared" ca="1" si="80"/>
+        <v>65</v>
       </c>
       <c r="K246" s="2">
         <v>45350</v>
       </c>
       <c r="L246" s="4">
-        <f t="shared" si="75"/>
+        <f t="shared" si="78"/>
         <v>37</v>
       </c>
       <c r="M246" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="N246" s="2">
         <v>45353</v>
       </c>
       <c r="P246" s="5" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="R246" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
     </row>
     <row r="247" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -13091,43 +13212,43 @@
         <v>34</v>
       </c>
       <c r="C247" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="D247" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="G247" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="H247" s="2">
         <v>45313</v>
       </c>
       <c r="I247" s="4">
-        <f t="shared" ca="1" si="76"/>
-        <v>7</v>
+        <f t="shared" ca="1" si="79"/>
+        <v>9</v>
       </c>
       <c r="J247" s="4">
-        <f t="shared" ca="1" si="77"/>
-        <v>55</v>
+        <f t="shared" ca="1" si="80"/>
+        <v>65</v>
       </c>
       <c r="K247" s="2">
         <v>45350</v>
       </c>
       <c r="L247" s="4">
-        <f t="shared" si="75"/>
+        <f t="shared" si="78"/>
         <v>37</v>
       </c>
       <c r="M247" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="N247" s="2">
         <v>45353</v>
       </c>
       <c r="P247" s="5" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="R247" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
     </row>
     <row r="248" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -13135,43 +13256,43 @@
         <v>34</v>
       </c>
       <c r="C248" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="D248" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="G248" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="H248" s="2">
         <v>45313</v>
       </c>
       <c r="I248" s="4">
-        <f t="shared" ca="1" si="76"/>
-        <v>7</v>
+        <f t="shared" ca="1" si="79"/>
+        <v>9</v>
       </c>
       <c r="J248" s="4">
-        <f t="shared" ca="1" si="77"/>
-        <v>55</v>
+        <f t="shared" ca="1" si="80"/>
+        <v>65</v>
       </c>
       <c r="K248" s="2">
         <v>45350</v>
       </c>
       <c r="L248" s="4">
-        <f t="shared" si="75"/>
+        <f t="shared" si="78"/>
         <v>37</v>
       </c>
       <c r="M248" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="N248" s="2">
         <v>45353</v>
       </c>
       <c r="P248" s="5" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="R248" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
     </row>
     <row r="249" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -13179,43 +13300,43 @@
         <v>34</v>
       </c>
       <c r="C249" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="D249" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="G249" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="H249" s="2">
         <v>45313</v>
       </c>
       <c r="I249" s="4">
-        <f t="shared" ca="1" si="76"/>
-        <v>7</v>
+        <f t="shared" ca="1" si="79"/>
+        <v>9</v>
       </c>
       <c r="J249" s="4">
-        <f t="shared" ca="1" si="77"/>
-        <v>55</v>
+        <f t="shared" ca="1" si="80"/>
+        <v>65</v>
       </c>
       <c r="K249" s="2">
         <v>45350</v>
       </c>
       <c r="L249" s="4">
-        <f t="shared" si="75"/>
+        <f t="shared" si="78"/>
         <v>37</v>
       </c>
       <c r="M249" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="N249" s="2">
         <v>45353</v>
       </c>
       <c r="P249" s="5" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="R249" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
     </row>
     <row r="250" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -13223,43 +13344,43 @@
         <v>34</v>
       </c>
       <c r="C250" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="D250" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="G250" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="H250" s="2">
         <v>45313</v>
       </c>
       <c r="I250" s="4">
-        <f t="shared" ca="1" si="76"/>
-        <v>7</v>
+        <f t="shared" ca="1" si="79"/>
+        <v>9</v>
       </c>
       <c r="J250" s="4">
-        <f t="shared" ca="1" si="77"/>
-        <v>55</v>
+        <f t="shared" ca="1" si="80"/>
+        <v>65</v>
       </c>
       <c r="K250" s="2">
         <v>45350</v>
       </c>
       <c r="L250" s="4">
-        <f t="shared" si="75"/>
+        <f t="shared" si="78"/>
         <v>37</v>
       </c>
       <c r="M250" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="N250" s="2">
         <v>45353</v>
       </c>
       <c r="P250" s="5" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="R250" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
     </row>
     <row r="251" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -13267,43 +13388,43 @@
         <v>34</v>
       </c>
       <c r="C251" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="D251" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="G251" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="H251" s="2">
         <v>45313</v>
       </c>
       <c r="I251" s="4">
-        <f t="shared" ca="1" si="76"/>
-        <v>7</v>
+        <f t="shared" ca="1" si="79"/>
+        <v>9</v>
       </c>
       <c r="J251" s="4">
-        <f t="shared" ca="1" si="77"/>
-        <v>55</v>
+        <f t="shared" ca="1" si="80"/>
+        <v>65</v>
       </c>
       <c r="K251" s="2">
         <v>45350</v>
       </c>
       <c r="L251" s="4">
-        <f t="shared" si="75"/>
+        <f t="shared" si="78"/>
         <v>37</v>
       </c>
       <c r="M251" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="N251" s="2">
         <v>45353</v>
       </c>
       <c r="P251" s="5" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="R251" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
     </row>
     <row r="252" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -13311,43 +13432,43 @@
         <v>34</v>
       </c>
       <c r="C252" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="D252" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="G252" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="H252" s="2">
         <v>45313</v>
       </c>
       <c r="I252" s="4">
-        <f t="shared" ca="1" si="76"/>
-        <v>7</v>
+        <f t="shared" ca="1" si="79"/>
+        <v>9</v>
       </c>
       <c r="J252" s="4">
-        <f t="shared" ca="1" si="77"/>
-        <v>55</v>
+        <f t="shared" ca="1" si="80"/>
+        <v>65</v>
       </c>
       <c r="K252" s="2">
         <v>45350</v>
       </c>
       <c r="L252" s="4">
-        <f t="shared" si="75"/>
+        <f t="shared" si="78"/>
         <v>37</v>
       </c>
       <c r="M252" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="N252" s="2">
         <v>45353</v>
       </c>
       <c r="P252" s="5" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="R252" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
     </row>
     <row r="253" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -13355,43 +13476,43 @@
         <v>34</v>
       </c>
       <c r="C253" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="D253" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="G253" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="H253" s="2">
         <v>45313</v>
       </c>
       <c r="I253" s="4">
-        <f t="shared" ca="1" si="76"/>
-        <v>7</v>
+        <f t="shared" ca="1" si="79"/>
+        <v>9</v>
       </c>
       <c r="J253" s="4">
-        <f t="shared" ca="1" si="77"/>
-        <v>55</v>
+        <f t="shared" ca="1" si="80"/>
+        <v>65</v>
       </c>
       <c r="K253" s="2">
         <v>45350</v>
       </c>
       <c r="L253" s="4">
-        <f t="shared" si="75"/>
+        <f t="shared" si="78"/>
         <v>37</v>
       </c>
       <c r="M253" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="N253" s="2">
         <v>45353</v>
       </c>
       <c r="P253" s="5" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="R253" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
     </row>
     <row r="254" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -13399,43 +13520,43 @@
         <v>34</v>
       </c>
       <c r="C254" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="D254" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="G254" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="H254" s="2">
         <v>45313</v>
       </c>
       <c r="I254" s="4">
-        <f t="shared" ca="1" si="76"/>
-        <v>7</v>
+        <f t="shared" ca="1" si="79"/>
+        <v>9</v>
       </c>
       <c r="J254" s="4">
-        <f t="shared" ca="1" si="77"/>
-        <v>55</v>
+        <f t="shared" ca="1" si="80"/>
+        <v>65</v>
       </c>
       <c r="K254" s="2">
         <v>45350</v>
       </c>
       <c r="L254" s="4">
-        <f t="shared" si="75"/>
+        <f t="shared" si="78"/>
         <v>37</v>
       </c>
       <c r="M254" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="N254" s="2">
         <v>45353</v>
       </c>
       <c r="P254" s="5" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="R254" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
     </row>
     <row r="255" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -13443,131 +13564,108 @@
         <v>34</v>
       </c>
       <c r="C255" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="D255" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="G255" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="H255" s="2">
         <v>45313</v>
       </c>
       <c r="I255" s="4">
-        <f t="shared" ca="1" si="76"/>
-        <v>7</v>
+        <f t="shared" ca="1" si="79"/>
+        <v>9</v>
       </c>
       <c r="J255" s="4">
-        <f t="shared" ca="1" si="77"/>
-        <v>55</v>
+        <f t="shared" ca="1" si="80"/>
+        <v>65</v>
       </c>
       <c r="K255" s="2">
         <v>45350</v>
       </c>
       <c r="L255" s="4">
-        <f t="shared" si="75"/>
+        <f t="shared" si="78"/>
         <v>37</v>
       </c>
       <c r="M255" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="N255" s="2">
         <v>45353</v>
       </c>
       <c r="P255" s="5" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="R255" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
     </row>
     <row r="256" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B256" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="C256" t="s">
-        <v>253</v>
-      </c>
-      <c r="D256" t="s">
+        <v>127</v>
+      </c>
+      <c r="E256" t="s">
+        <v>16</v>
+      </c>
+      <c r="H256" s="2">
+        <v>45355</v>
+      </c>
+      <c r="I256" s="4">
+        <f t="shared" ref="I256" ca="1" si="81">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H256), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H256), 7), "-")</f>
+        <v>3</v>
+      </c>
+      <c r="J256" s="4">
+        <f t="shared" ref="J256" ca="1" si="82">IF(_xlfn.DAYS(TODAY(),H256)&lt;10000, _xlfn.DAYS(TODAY(),H256), "-")</f>
+        <v>23</v>
+      </c>
+      <c r="L256" s="4" t="str">
+        <f t="shared" ref="L256" si="83">IF(_xlfn.DAYS(K256,H256)&gt;0, _xlfn.DAYS(K256,H256), "-")</f>
+        <v>-</v>
+      </c>
+      <c r="M256" t="s">
+        <v>235</v>
+      </c>
+      <c r="P256"/>
+      <c r="R256" t="s">
         <v>285</v>
-      </c>
-      <c r="G256" t="s">
-        <v>251</v>
-      </c>
-      <c r="H256" s="2">
-        <v>45313</v>
-      </c>
-      <c r="I256" s="4">
-        <f t="shared" ca="1" si="76"/>
-        <v>7</v>
-      </c>
-      <c r="J256" s="4">
-        <f t="shared" ca="1" si="77"/>
-        <v>55</v>
-      </c>
-      <c r="K256" s="2">
-        <v>45350</v>
-      </c>
-      <c r="L256" s="4">
-        <f t="shared" si="75"/>
-        <v>37</v>
-      </c>
-      <c r="M256" t="s">
-        <v>260</v>
-      </c>
-      <c r="N256" s="2">
-        <v>45353</v>
-      </c>
-      <c r="P256" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="R256" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="257" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B257" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="C257" t="s">
-        <v>253</v>
-      </c>
-      <c r="D257" t="s">
-        <v>286</v>
-      </c>
-      <c r="G257" t="s">
-        <v>251</v>
+        <v>127</v>
+      </c>
+      <c r="E257" t="s">
+        <v>16</v>
       </c>
       <c r="H257" s="2">
-        <v>45313</v>
+        <v>45355</v>
       </c>
       <c r="I257" s="4">
-        <f t="shared" ca="1" si="76"/>
-        <v>7</v>
+        <f t="shared" ref="I257:I266" ca="1" si="84">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H257), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H257), 7), "-")</f>
+        <v>3</v>
       </c>
       <c r="J257" s="4">
-        <f t="shared" ca="1" si="77"/>
-        <v>55</v>
-      </c>
-      <c r="K257" s="2">
-        <v>45350</v>
-      </c>
-      <c r="L257" s="4">
-        <f t="shared" si="75"/>
-        <v>37</v>
+        <f t="shared" ref="J257:J266" ca="1" si="85">IF(_xlfn.DAYS(TODAY(),H257)&lt;10000, _xlfn.DAYS(TODAY(),H257), "-")</f>
+        <v>23</v>
+      </c>
+      <c r="L257" s="4" t="str">
+        <f t="shared" ref="L257:L266" si="86">IF(_xlfn.DAYS(K257,H257)&gt;0, _xlfn.DAYS(K257,H257), "-")</f>
+        <v>-</v>
       </c>
       <c r="M257" t="s">
-        <v>260</v>
-      </c>
-      <c r="N257" s="2">
-        <v>45353</v>
-      </c>
-      <c r="P257" s="5" t="s">
-        <v>254</v>
+        <v>235</v>
       </c>
       <c r="R257" t="s">
-        <v>257</v>
+        <v>285</v>
       </c>
     </row>
     <row r="258" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -13581,22 +13679,25 @@
         <v>16</v>
       </c>
       <c r="H258" s="2">
-        <v>45363</v>
+        <v>45355</v>
       </c>
       <c r="I258" s="4">
-        <f t="shared" ca="1" si="76"/>
-        <v>0</v>
+        <f t="shared" ca="1" si="84"/>
+        <v>3</v>
       </c>
       <c r="J258" s="4">
-        <f t="shared" ca="1" si="77"/>
-        <v>5</v>
+        <f t="shared" ca="1" si="85"/>
+        <v>23</v>
       </c>
       <c r="L258" s="4" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="86"/>
         <v>-</v>
       </c>
       <c r="M258" t="s">
-        <v>272</v>
+        <v>235</v>
+      </c>
+      <c r="R258" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="259" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -13610,22 +13711,25 @@
         <v>16</v>
       </c>
       <c r="H259" s="2">
-        <v>45363</v>
+        <v>45355</v>
       </c>
       <c r="I259" s="4">
-        <f t="shared" ref="I259:I263" ca="1" si="78">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H259), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H259), 7), "-")</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="84"/>
+        <v>3</v>
       </c>
       <c r="J259" s="4">
-        <f t="shared" ref="J259:J263" ca="1" si="79">IF(_xlfn.DAYS(TODAY(),H259)&lt;10000, _xlfn.DAYS(TODAY(),H259), "-")</f>
-        <v>5</v>
+        <f t="shared" ca="1" si="85"/>
+        <v>23</v>
       </c>
       <c r="L259" s="4" t="str">
-        <f t="shared" ref="L259:L263" si="80">IF(_xlfn.DAYS(K259,H259)&gt;0, _xlfn.DAYS(K259,H259), "-")</f>
+        <f t="shared" si="86"/>
         <v>-</v>
       </c>
       <c r="M259" t="s">
-        <v>272</v>
+        <v>235</v>
+      </c>
+      <c r="R259" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="260" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -13639,22 +13743,25 @@
         <v>16</v>
       </c>
       <c r="H260" s="2">
-        <v>45363</v>
+        <v>45355</v>
       </c>
       <c r="I260" s="4">
-        <f t="shared" ca="1" si="78"/>
-        <v>0</v>
+        <f t="shared" ca="1" si="84"/>
+        <v>3</v>
       </c>
       <c r="J260" s="4">
-        <f t="shared" ca="1" si="79"/>
-        <v>5</v>
+        <f t="shared" ca="1" si="85"/>
+        <v>23</v>
       </c>
       <c r="L260" s="4" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="86"/>
         <v>-</v>
       </c>
       <c r="M260" t="s">
-        <v>272</v>
+        <v>235</v>
+      </c>
+      <c r="R260" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="261" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -13668,22 +13775,25 @@
         <v>16</v>
       </c>
       <c r="H261" s="2">
-        <v>45363</v>
+        <v>45355</v>
       </c>
       <c r="I261" s="4">
-        <f t="shared" ca="1" si="78"/>
-        <v>0</v>
+        <f t="shared" ca="1" si="84"/>
+        <v>3</v>
       </c>
       <c r="J261" s="4">
-        <f t="shared" ca="1" si="79"/>
-        <v>5</v>
+        <f t="shared" ca="1" si="85"/>
+        <v>23</v>
       </c>
       <c r="L261" s="4" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="86"/>
         <v>-</v>
       </c>
       <c r="M261" t="s">
-        <v>272</v>
+        <v>235</v>
+      </c>
+      <c r="R261" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="262" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -13694,25 +13804,28 @@
         <v>127</v>
       </c>
       <c r="E262" t="s">
-        <v>273</v>
+        <v>16</v>
       </c>
       <c r="H262" s="2">
-        <v>45363</v>
+        <v>45355</v>
       </c>
       <c r="I262" s="4">
-        <f t="shared" ca="1" si="78"/>
-        <v>0</v>
+        <f t="shared" ca="1" si="84"/>
+        <v>3</v>
       </c>
       <c r="J262" s="4">
-        <f t="shared" ca="1" si="79"/>
-        <v>5</v>
+        <f t="shared" ca="1" si="85"/>
+        <v>23</v>
       </c>
       <c r="L262" s="4" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="86"/>
         <v>-</v>
       </c>
       <c r="M262" t="s">
-        <v>272</v>
+        <v>235</v>
+      </c>
+      <c r="R262" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="263" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
@@ -13723,29 +13836,139 @@
         <v>127</v>
       </c>
       <c r="E263" t="s">
-        <v>273</v>
+        <v>16</v>
       </c>
       <c r="H263" s="2">
-        <v>45363</v>
+        <v>45355</v>
       </c>
       <c r="I263" s="4">
-        <f t="shared" ca="1" si="78"/>
+        <f t="shared" ca="1" si="84"/>
+        <v>3</v>
+      </c>
+      <c r="J263" s="4">
+        <f t="shared" ca="1" si="85"/>
+        <v>23</v>
+      </c>
+      <c r="L263" s="4" t="str">
+        <f t="shared" si="86"/>
+        <v>-</v>
+      </c>
+      <c r="M263" t="s">
+        <v>235</v>
+      </c>
+      <c r="R263" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="264" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B264" t="s">
+        <v>5</v>
+      </c>
+      <c r="C264" t="s">
+        <v>127</v>
+      </c>
+      <c r="E264" t="s">
+        <v>16</v>
+      </c>
+      <c r="H264" s="2">
+        <v>45355</v>
+      </c>
+      <c r="I264" s="4">
+        <f t="shared" ca="1" si="84"/>
+        <v>3</v>
+      </c>
+      <c r="J264" s="4">
+        <f t="shared" ca="1" si="85"/>
+        <v>23</v>
+      </c>
+      <c r="L264" s="4" t="str">
+        <f t="shared" si="86"/>
+        <v>-</v>
+      </c>
+      <c r="M264" t="s">
+        <v>235</v>
+      </c>
+      <c r="R264" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="265" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B265" t="s">
+        <v>290</v>
+      </c>
+      <c r="C265" t="s">
+        <v>112</v>
+      </c>
+      <c r="E265" t="s">
+        <v>15</v>
+      </c>
+      <c r="H265" s="2">
+        <v>45372</v>
+      </c>
+      <c r="I265" s="4">
+        <f t="shared" ca="1" si="84"/>
         <v>0</v>
       </c>
-      <c r="J263" s="4">
-        <f t="shared" ca="1" si="79"/>
-        <v>5</v>
-      </c>
-      <c r="L263" s="4" t="str">
-        <f t="shared" si="80"/>
-        <v>-</v>
-      </c>
-      <c r="M263" t="s">
-        <v>272</v>
-      </c>
+      <c r="J265" s="4">
+        <f t="shared" ca="1" si="85"/>
+        <v>6</v>
+      </c>
+      <c r="L265" s="4" t="str">
+        <f t="shared" si="86"/>
+        <v>-</v>
+      </c>
+      <c r="M265" t="s">
+        <v>291</v>
+      </c>
+      <c r="Q265" t="s">
+        <v>292</v>
+      </c>
+      <c r="R265" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="266" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B266" t="s">
+        <v>34</v>
+      </c>
+      <c r="C266" t="s">
+        <v>110</v>
+      </c>
+      <c r="E266" t="s">
+        <v>16</v>
+      </c>
+      <c r="G266" t="s">
+        <v>11</v>
+      </c>
+      <c r="H266" s="2">
+        <v>45378</v>
+      </c>
+      <c r="I266" s="4">
+        <f t="shared" ca="1" si="84"/>
+        <v>0</v>
+      </c>
+      <c r="J266" s="4">
+        <f t="shared" ca="1" si="85"/>
+        <v>0</v>
+      </c>
+      <c r="L266" s="4" t="str">
+        <f t="shared" si="86"/>
+        <v>-</v>
+      </c>
+      <c r="M266" t="s">
+        <v>294</v>
+      </c>
+      <c r="Q266" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="267" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="I267" s="4"/>
+      <c r="J267" s="4"/>
+      <c r="L267" s="4"/>
     </row>
   </sheetData>
-  <autoFilter ref="B1:R263" xr:uid="{8D08DEC4-803F-4130-9E5E-30A83401A29D}">
+  <autoFilter ref="B1:R265" xr:uid="{8D08DEC4-803F-4130-9E5E-30A83401A29D}">
     <filterColumn colId="0">
       <filters>
         <filter val="5F"/>
@@ -13753,7 +13976,7 @@
     </filterColumn>
     <filterColumn colId="1">
       <filters>
-        <filter val="Tcrd-CreER; Tsg101-flox"/>
+        <filter val="Tmem119-CreERT2; Tsg101-flox"/>
       </filters>
     </filterColumn>
     <filterColumn colId="13">
@@ -13761,180 +13984,196 @@
     </filterColumn>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="M155:M158 M228:M232 M160 M162 M164:M172 M31:M41 M43:M59 M1:M27 M128:M129 M131:M132 M134 M136:M153 M65:M68 M62 M70:M126 M175:M226 M243:M1048576">
-    <cfRule type="containsText" dxfId="65" priority="73" operator="containsText" text=".X">
+  <conditionalFormatting sqref="M155:M158 M227:M230 M160 M162 M164:M172 M31:M41 M43:M59 M1:M27 M128:M129 M131:M132 M134 M136:M153 M65:M68 M62 M70:M126 M241:M255 M175:M217 M219:M225 M268:M1048576">
+    <cfRule type="containsText" dxfId="69" priority="77" operator="containsText" text=".X">
       <formula>NOT(ISERROR(SEARCH(".X",M1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="64" priority="74" operator="containsText" text=".B">
+    <cfRule type="containsText" dxfId="68" priority="78" operator="containsText" text=".B">
       <formula>NOT(ISERROR(SEARCH(".B",M1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M154">
-    <cfRule type="containsText" dxfId="63" priority="71" operator="containsText" text=".X">
+    <cfRule type="containsText" dxfId="67" priority="75" operator="containsText" text=".X">
       <formula>NOT(ISERROR(SEARCH(".X",M154)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="62" priority="72" operator="containsText" text=".B">
+    <cfRule type="containsText" dxfId="66" priority="76" operator="containsText" text=".B">
       <formula>NOT(ISERROR(SEARCH(".B",M154)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M159">
-    <cfRule type="containsText" dxfId="61" priority="67" operator="containsText" text=".X">
+    <cfRule type="containsText" dxfId="65" priority="71" operator="containsText" text=".X">
       <formula>NOT(ISERROR(SEARCH(".X",M159)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="60" priority="68" operator="containsText" text=".B">
+    <cfRule type="containsText" dxfId="64" priority="72" operator="containsText" text=".B">
       <formula>NOT(ISERROR(SEARCH(".B",M159)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M161">
-    <cfRule type="containsText" dxfId="59" priority="65" operator="containsText" text=".X">
+    <cfRule type="containsText" dxfId="63" priority="69" operator="containsText" text=".X">
       <formula>NOT(ISERROR(SEARCH(".X",M161)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="58" priority="66" operator="containsText" text=".B">
+    <cfRule type="containsText" dxfId="62" priority="70" operator="containsText" text=".B">
       <formula>NOT(ISERROR(SEARCH(".B",M161)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M163">
-    <cfRule type="containsText" dxfId="57" priority="63" operator="containsText" text=".X">
+    <cfRule type="containsText" dxfId="61" priority="67" operator="containsText" text=".X">
       <formula>NOT(ISERROR(SEARCH(".X",M163)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="56" priority="64" operator="containsText" text=".B">
+    <cfRule type="containsText" dxfId="60" priority="68" operator="containsText" text=".B">
       <formula>NOT(ISERROR(SEARCH(".B",M163)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M173">
-    <cfRule type="containsText" dxfId="55" priority="61" operator="containsText" text=".X">
+    <cfRule type="containsText" dxfId="59" priority="65" operator="containsText" text=".X">
       <formula>NOT(ISERROR(SEARCH(".X",M173)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="54" priority="62" operator="containsText" text=".B">
+    <cfRule type="containsText" dxfId="58" priority="66" operator="containsText" text=".B">
       <formula>NOT(ISERROR(SEARCH(".B",M173)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M174">
-    <cfRule type="containsText" dxfId="53" priority="59" operator="containsText" text=".X">
+    <cfRule type="containsText" dxfId="57" priority="63" operator="containsText" text=".X">
       <formula>NOT(ISERROR(SEARCH(".X",M174)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="52" priority="60" operator="containsText" text=".B">
+    <cfRule type="containsText" dxfId="56" priority="64" operator="containsText" text=".B">
       <formula>NOT(ISERROR(SEARCH(".B",M174)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M30">
-    <cfRule type="containsText" dxfId="51" priority="55" operator="containsText" text=".X">
+    <cfRule type="containsText" dxfId="55" priority="59" operator="containsText" text=".X">
       <formula>NOT(ISERROR(SEARCH(".X",M30)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="50" priority="56" operator="containsText" text=".B">
+    <cfRule type="containsText" dxfId="54" priority="60" operator="containsText" text=".B">
       <formula>NOT(ISERROR(SEARCH(".B",M30)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M42">
-    <cfRule type="containsText" dxfId="49" priority="53" operator="containsText" text=".X">
+    <cfRule type="containsText" dxfId="53" priority="57" operator="containsText" text=".X">
       <formula>NOT(ISERROR(SEARCH(".X",M42)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="48" priority="54" operator="containsText" text=".B">
+    <cfRule type="containsText" dxfId="52" priority="58" operator="containsText" text=".B">
       <formula>NOT(ISERROR(SEARCH(".B",M42)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M29">
-    <cfRule type="containsText" dxfId="47" priority="51" operator="containsText" text=".X">
+    <cfRule type="containsText" dxfId="51" priority="55" operator="containsText" text=".X">
       <formula>NOT(ISERROR(SEARCH(".X",M29)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="46" priority="52" operator="containsText" text=".B">
+    <cfRule type="containsText" dxfId="50" priority="56" operator="containsText" text=".B">
       <formula>NOT(ISERROR(SEARCH(".B",M29)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M28">
-    <cfRule type="containsText" dxfId="45" priority="49" operator="containsText" text=".X">
+    <cfRule type="containsText" dxfId="49" priority="53" operator="containsText" text=".X">
       <formula>NOT(ISERROR(SEARCH(".X",M28)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="44" priority="50" operator="containsText" text=".B">
+    <cfRule type="containsText" dxfId="48" priority="54" operator="containsText" text=".B">
       <formula>NOT(ISERROR(SEARCH(".B",M28)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R131">
-    <cfRule type="containsText" dxfId="43" priority="45" operator="containsText" text=".X">
+    <cfRule type="containsText" dxfId="47" priority="49" operator="containsText" text=".X">
       <formula>NOT(ISERROR(SEARCH(".X",R131)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="42" priority="46" operator="containsText" text=".B">
+    <cfRule type="containsText" dxfId="46" priority="50" operator="containsText" text=".B">
       <formula>NOT(ISERROR(SEARCH(".B",R131)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R132">
-    <cfRule type="containsText" dxfId="41" priority="43" operator="containsText" text=".X">
+    <cfRule type="containsText" dxfId="45" priority="47" operator="containsText" text=".X">
       <formula>NOT(ISERROR(SEARCH(".X",R132)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="40" priority="44" operator="containsText" text=".B">
+    <cfRule type="containsText" dxfId="44" priority="48" operator="containsText" text=".B">
       <formula>NOT(ISERROR(SEARCH(".B",R132)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R134:R135">
-    <cfRule type="containsText" dxfId="39" priority="41" operator="containsText" text=".X">
+    <cfRule type="containsText" dxfId="43" priority="45" operator="containsText" text=".X">
       <formula>NOT(ISERROR(SEARCH(".X",R134)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="38" priority="42" operator="containsText" text=".B">
+    <cfRule type="containsText" dxfId="42" priority="46" operator="containsText" text=".B">
       <formula>NOT(ISERROR(SEARCH(".B",R134)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M135">
-    <cfRule type="containsText" dxfId="37" priority="39" operator="containsText" text=".X">
+    <cfRule type="containsText" dxfId="41" priority="43" operator="containsText" text=".X">
       <formula>NOT(ISERROR(SEARCH(".X",M135)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="36" priority="40" operator="containsText" text=".B">
+    <cfRule type="containsText" dxfId="40" priority="44" operator="containsText" text=".B">
       <formula>NOT(ISERROR(SEARCH(".B",M135)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M127">
-    <cfRule type="containsText" dxfId="35" priority="37" operator="containsText" text=".X">
+    <cfRule type="containsText" dxfId="39" priority="41" operator="containsText" text=".X">
       <formula>NOT(ISERROR(SEARCH(".X",M127)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="34" priority="38" operator="containsText" text=".B">
+    <cfRule type="containsText" dxfId="38" priority="42" operator="containsText" text=".B">
       <formula>NOT(ISERROR(SEARCH(".B",M127)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R127">
-    <cfRule type="containsText" dxfId="33" priority="35" operator="containsText" text=".X">
+    <cfRule type="containsText" dxfId="37" priority="39" operator="containsText" text=".X">
       <formula>NOT(ISERROR(SEARCH(".X",R127)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="32" priority="36" operator="containsText" text=".B">
+    <cfRule type="containsText" dxfId="36" priority="40" operator="containsText" text=".B">
       <formula>NOT(ISERROR(SEARCH(".B",R127)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M130">
-    <cfRule type="containsText" dxfId="31" priority="33" operator="containsText" text=".X">
+    <cfRule type="containsText" dxfId="35" priority="37" operator="containsText" text=".X">
       <formula>NOT(ISERROR(SEARCH(".X",M130)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="30" priority="34" operator="containsText" text=".B">
+    <cfRule type="containsText" dxfId="34" priority="38" operator="containsText" text=".B">
       <formula>NOT(ISERROR(SEARCH(".B",M130)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M133">
-    <cfRule type="containsText" dxfId="29" priority="31" operator="containsText" text=".X">
+    <cfRule type="containsText" dxfId="33" priority="35" operator="containsText" text=".X">
       <formula>NOT(ISERROR(SEARCH(".X",M133)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="28" priority="32" operator="containsText" text=".B">
+    <cfRule type="containsText" dxfId="32" priority="36" operator="containsText" text=".B">
       <formula>NOT(ISERROR(SEARCH(".B",M133)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M63:M64">
-    <cfRule type="containsText" dxfId="27" priority="29" operator="containsText" text=".X">
+    <cfRule type="containsText" dxfId="31" priority="33" operator="containsText" text=".X">
       <formula>NOT(ISERROR(SEARCH(".X",M63)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="26" priority="30" operator="containsText" text=".B">
+    <cfRule type="containsText" dxfId="30" priority="34" operator="containsText" text=".B">
       <formula>NOT(ISERROR(SEARCH(".B",M63)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M69">
-    <cfRule type="containsText" dxfId="25" priority="27" operator="containsText" text=".X">
+    <cfRule type="containsText" dxfId="29" priority="31" operator="containsText" text=".X">
       <formula>NOT(ISERROR(SEARCH(".X",M69)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="24" priority="28" operator="containsText" text=".B">
+    <cfRule type="containsText" dxfId="28" priority="32" operator="containsText" text=".B">
       <formula>NOT(ISERROR(SEARCH(".B",M69)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M60:M61">
-    <cfRule type="containsText" dxfId="23" priority="25" operator="containsText" text=".X">
+    <cfRule type="containsText" dxfId="27" priority="29" operator="containsText" text=".X">
       <formula>NOT(ISERROR(SEARCH(".X",M60)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="22" priority="26" operator="containsText" text=".B">
+    <cfRule type="containsText" dxfId="26" priority="30" operator="containsText" text=".B">
       <formula>NOT(ISERROR(SEARCH(".B",M60)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M231">
+    <cfRule type="containsText" dxfId="25" priority="25" operator="containsText" text=".X">
+      <formula>NOT(ISERROR(SEARCH(".X",M231)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="24" priority="26" operator="containsText" text=".B">
+      <formula>NOT(ISERROR(SEARCH(".B",M231)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M232">
+    <cfRule type="containsText" dxfId="23" priority="23" operator="containsText" text=".X">
+      <formula>NOT(ISERROR(SEARCH(".X",M232)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="22" priority="24" operator="containsText" text=".B">
+      <formula>NOT(ISERROR(SEARCH(".B",M232)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M233">
@@ -14001,32 +14240,32 @@
       <formula>NOT(ISERROR(SEARCH(".B",M240)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M241">
+  <conditionalFormatting sqref="M226">
     <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text=".X">
-      <formula>NOT(ISERROR(SEARCH(".X",M241)))</formula>
+      <formula>NOT(ISERROR(SEARCH(".X",M226)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="4" priority="6" operator="containsText" text=".B">
-      <formula>NOT(ISERROR(SEARCH(".B",M241)))</formula>
+      <formula>NOT(ISERROR(SEARCH(".B",M226)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M242">
+  <conditionalFormatting sqref="M218">
     <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text=".X">
-      <formula>NOT(ISERROR(SEARCH(".X",M242)))</formula>
+      <formula>NOT(ISERROR(SEARCH(".X",M218)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text=".B">
-      <formula>NOT(ISERROR(SEARCH(".B",M242)))</formula>
+      <formula>NOT(ISERROR(SEARCH(".B",M218)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M227">
+  <conditionalFormatting sqref="M256:M267">
     <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text=".X">
-      <formula>NOT(ISERROR(SEARCH(".X",M227)))</formula>
+      <formula>NOT(ISERROR(SEARCH(".X",M256)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text=".B">
-      <formula>NOT(ISERROR(SEARCH(".B",M227)))</formula>
+      <formula>NOT(ISERROR(SEARCH(".B",M256)))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E157:E159 E148:E150 E1:E141 E192:E219 E221:E222 E161:E190 E224:E1048576" xr:uid="{939E2B39-E841-4A9F-AD11-00C266DB2690}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E157:E159 E148:E150 E1:E141 E192:E220 E161:E190 E222:E1048576" xr:uid="{939E2B39-E841-4A9F-AD11-00C266DB2690}">
       <formula1>"Y, N"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1:G1048576" xr:uid="{2DE54AC7-5B92-48D6-98C4-E6203F87CDD0}">
@@ -14057,10 +14296,10 @@
       <c r="E2" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="21" t="s">
+      <c r="G2" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="H2" s="21"/>
+      <c r="H2" s="20"/>
     </row>
     <row r="3" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C3" t="s">
@@ -14122,19 +14361,19 @@
       <c r="C7" s="2"/>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="19">
-        <v>45301</v>
+      <c r="B8" s="2">
+        <v>45300</v>
       </c>
       <c r="C8" s="2">
-        <v>45363</v>
+        <v>45365</v>
       </c>
       <c r="D8">
         <f>_xlfn.DAYS(C8,B8)</f>
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E8">
         <f>QUOTIENT(D8, 7)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/Mouse 내역.xlsx
+++ b/Mouse 내역.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\heung\Dropbox\02. Lab. of Host Defenses\03. 동물실\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7540AF2-730E-4419-B9C7-D758119D5D53}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC22D869-F5B3-45EC-AA88-F3944FA5ADD7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="495" windowWidth="28800" windowHeight="16245" xr2:uid="{5A73A69A-2AFB-4F3E-AC64-070DD7700CB2}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <sheet name="Sheet1 (2)" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$R$265</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$R$266</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1874" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1887" uniqueCount="298">
   <si>
     <t>Strain</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1198,6 +1198,10 @@
   </si>
   <si>
     <t>Weaning</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Weaning/geno</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2686,7 +2690,7 @@
       </c>
       <c r="J2" s="4">
         <f ca="1">IF(_xlfn.DAYS(TODAY(),H2)&lt;10000, _xlfn.DAYS(TODAY(),H2), "-")</f>
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L2" s="4" t="str">
         <f t="shared" ref="L2:L29" si="0">IF(_xlfn.DAYS(K2,H2)&gt;0, _xlfn.DAYS(K2,H2), "-")</f>
@@ -2726,7 +2730,7 @@
       </c>
       <c r="J3" s="4">
         <f t="shared" ref="J3:J29" ca="1" si="2">IF(_xlfn.DAYS(TODAY(),H3)&lt;10000, _xlfn.DAYS(TODAY(),H3), "-")</f>
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L3" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2769,7 +2773,7 @@
       </c>
       <c r="J4" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L4" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2815,7 +2819,7 @@
       </c>
       <c r="J5" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K5" s="2">
         <v>45293</v>
@@ -2861,7 +2865,7 @@
       </c>
       <c r="J6" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K6" s="2">
         <v>45293</v>
@@ -2882,7 +2886,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="7" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>5</v>
       </c>
@@ -2910,7 +2914,7 @@
       </c>
       <c r="J7" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K7" s="2">
         <v>45293</v>
@@ -2954,7 +2958,7 @@
       </c>
       <c r="J8" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K8" s="2">
         <v>45293</v>
@@ -3000,7 +3004,7 @@
       </c>
       <c r="J9" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K9" s="2">
         <v>45293</v>
@@ -3043,7 +3047,7 @@
       </c>
       <c r="J10" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L10" s="4" t="str">
         <f t="shared" si="0"/>
@@ -3160,7 +3164,7 @@
       </c>
       <c r="J13" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L13" s="4" t="str">
         <f t="shared" si="0"/>
@@ -3206,7 +3210,7 @@
       </c>
       <c r="J14" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L14" s="4" t="str">
         <f t="shared" si="0"/>
@@ -3252,7 +3256,7 @@
       </c>
       <c r="J15" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L15" s="4" t="str">
         <f t="shared" si="0"/>
@@ -3297,7 +3301,7 @@
       </c>
       <c r="J16" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L16" s="4" t="str">
         <f t="shared" si="0"/>
@@ -3339,7 +3343,7 @@
       </c>
       <c r="J17" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L17" s="4" t="str">
         <f t="shared" si="0"/>
@@ -3381,7 +3385,7 @@
       </c>
       <c r="J18" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L18" s="4" t="str">
         <f t="shared" si="0"/>
@@ -3456,7 +3460,7 @@
       </c>
       <c r="J20" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K20" s="2">
         <v>45112</v>
@@ -3498,7 +3502,7 @@
       </c>
       <c r="J21" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K21" s="2">
         <v>45176</v>
@@ -3543,7 +3547,7 @@
       </c>
       <c r="J22" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K22" s="2">
         <v>45176</v>
@@ -3588,7 +3592,7 @@
       </c>
       <c r="J23" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K23" s="2">
         <v>45176</v>
@@ -3633,7 +3637,7 @@
       </c>
       <c r="J24" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K24" s="2">
         <v>45229</v>
@@ -3675,7 +3679,7 @@
       </c>
       <c r="J25" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K25" s="2">
         <v>45229</v>
@@ -3717,7 +3721,7 @@
       </c>
       <c r="J26" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K26" s="2">
         <v>45229</v>
@@ -3762,7 +3766,7 @@
       </c>
       <c r="J27" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K27" s="2">
         <v>45229</v>
@@ -3782,7 +3786,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="28" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>5</v>
       </c>
@@ -3810,7 +3814,7 @@
       </c>
       <c r="J28" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K28" s="2">
         <v>45293</v>
@@ -3825,7 +3829,7 @@
       <c r="P28"/>
       <c r="Q28" s="2"/>
     </row>
-    <row r="29" spans="2:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
         <v>5</v>
       </c>
@@ -3853,7 +3857,7 @@
       </c>
       <c r="J29" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K29" s="2">
         <v>45315</v>
@@ -3893,7 +3897,7 @@
       </c>
       <c r="J30" s="4">
         <f t="shared" ref="J30" ca="1" si="4">IF(_xlfn.DAYS(TODAY(),H30)&lt;10000, _xlfn.DAYS(TODAY(),H30), "-")</f>
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K30" s="2">
         <v>45176</v>
@@ -3938,7 +3942,7 @@
       </c>
       <c r="J31" s="4">
         <f t="shared" ref="J31:J37" ca="1" si="6">IF(_xlfn.DAYS(TODAY(),H31)&lt;10000, _xlfn.DAYS(TODAY(),H31), "-")</f>
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K31" s="2">
         <v>45229</v>
@@ -4022,7 +4026,7 @@
       </c>
       <c r="J33" s="4">
         <f ca="1">IF(_xlfn.DAYS(TODAY(),H33)&lt;10000, _xlfn.DAYS(TODAY(),H33), "-")</f>
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K33" s="2">
         <v>45257</v>
@@ -4148,7 +4152,7 @@
       </c>
       <c r="J36" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K36" s="2">
         <v>45257</v>
@@ -4196,7 +4200,7 @@
       </c>
       <c r="J37" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K37" s="2">
         <v>45257</v>
@@ -4244,7 +4248,7 @@
       </c>
       <c r="J38" s="4">
         <f t="shared" ref="J38:J40" ca="1" si="8">IF(_xlfn.DAYS(TODAY(),H38)&lt;10000, _xlfn.DAYS(TODAY(),H38), "-")</f>
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K38" s="2">
         <v>45257</v>
@@ -4292,7 +4296,7 @@
       </c>
       <c r="J39" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K39" s="2">
         <v>45257</v>
@@ -4337,7 +4341,7 @@
       </c>
       <c r="J40" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K40" s="2">
         <v>45257</v>
@@ -4382,7 +4386,7 @@
       </c>
       <c r="J41" s="4">
         <f t="shared" ref="J41:J42" ca="1" si="9">IF(_xlfn.DAYS(TODAY(),H41)&lt;10000, _xlfn.DAYS(TODAY(),H41), "-")</f>
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L41" s="4" t="str">
         <f t="shared" si="7"/>
@@ -4421,7 +4425,7 @@
       </c>
       <c r="J42" s="4">
         <f t="shared" ca="1" si="9"/>
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K42" s="2">
         <v>45176</v>
@@ -4469,7 +4473,7 @@
       </c>
       <c r="J43" s="4">
         <f t="shared" ref="J43:J94" ca="1" si="11">IF(_xlfn.DAYS(TODAY(),H43)&lt;10000, _xlfn.DAYS(TODAY(),H43), "-")</f>
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L43" s="4" t="str">
         <f t="shared" si="7"/>
@@ -4510,11 +4514,11 @@
       </c>
       <c r="I44" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J44" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K44" s="2">
         <v>45293</v>
@@ -4555,11 +4559,11 @@
       </c>
       <c r="I45" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J45" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K45" s="2">
         <v>45293</v>
@@ -4600,11 +4604,11 @@
       </c>
       <c r="I46" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J46" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K46" s="2">
         <v>45293</v>
@@ -4648,11 +4652,11 @@
       </c>
       <c r="I47" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J47" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K47" s="2">
         <v>45293</v>
@@ -4700,7 +4704,7 @@
       </c>
       <c r="J48" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K48" s="2">
         <v>45293</v>
@@ -4744,11 +4748,11 @@
       </c>
       <c r="I49" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J49" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K49" s="2">
         <v>45293</v>
@@ -4792,11 +4796,11 @@
       </c>
       <c r="I50" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J50" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K50" s="2">
         <v>45293</v>
@@ -4840,11 +4844,11 @@
       </c>
       <c r="I51" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J51" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K51" s="2">
         <v>45293</v>
@@ -4889,7 +4893,7 @@
       </c>
       <c r="J52" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K52" s="2">
         <v>45293</v>
@@ -4934,7 +4938,7 @@
       </c>
       <c r="J53" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K53" s="2">
         <v>45293</v>
@@ -4982,7 +4986,7 @@
       </c>
       <c r="J54" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K54" s="2">
         <v>45238</v>
@@ -5030,7 +5034,7 @@
       </c>
       <c r="J55" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K55" s="2">
         <v>45238</v>
@@ -5078,7 +5082,7 @@
       </c>
       <c r="J56" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K56" s="2">
         <v>45238</v>
@@ -5123,7 +5127,7 @@
       </c>
       <c r="J57" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="L57" s="4" t="str">
         <f t="shared" si="7"/>
@@ -5165,7 +5169,7 @@
       </c>
       <c r="J58" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="L58" s="4" t="str">
         <f t="shared" si="7"/>
@@ -5200,11 +5204,11 @@
       </c>
       <c r="I59" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J59" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K59" s="2">
         <v>45295</v>
@@ -5221,7 +5225,7 @@
       </c>
       <c r="P59"/>
     </row>
-    <row r="60" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B60" t="s">
         <v>27</v>
       </c>
@@ -5246,7 +5250,7 @@
       </c>
       <c r="J60" s="4">
         <f t="shared" ref="J60:J61" ca="1" si="13">IF(_xlfn.DAYS(TODAY(),H60)&lt;10000, _xlfn.DAYS(TODAY(),H60), "-")</f>
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="L60" s="4" t="str">
         <f t="shared" ref="L60:L61" si="14">IF(_xlfn.DAYS(K60,H60)&gt;0, _xlfn.DAYS(K60,H60), "-")</f>
@@ -5259,7 +5263,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="61" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B61" t="s">
         <v>27</v>
       </c>
@@ -5284,7 +5288,7 @@
       </c>
       <c r="J61" s="4">
         <f t="shared" ca="1" si="13"/>
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="L61" s="4" t="str">
         <f t="shared" si="14"/>
@@ -5297,7 +5301,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="62" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B62" t="s">
         <v>27</v>
       </c>
@@ -5318,11 +5322,11 @@
       </c>
       <c r="I62" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J62" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K62" s="2">
         <v>45295</v>
@@ -5338,7 +5342,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="63" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B63" t="s">
         <v>34</v>
       </c>
@@ -5363,7 +5367,7 @@
       </c>
       <c r="J63" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K63" s="7">
         <v>45324</v>
@@ -5379,7 +5383,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="64" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B64" t="s">
         <v>34</v>
       </c>
@@ -5404,7 +5408,7 @@
       </c>
       <c r="J64" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K64" s="7">
         <v>45324</v>
@@ -5420,7 +5424,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B65" t="s">
         <v>27</v>
       </c>
@@ -5441,11 +5445,11 @@
       </c>
       <c r="I65" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J65" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K65" s="2">
         <v>45295</v>
@@ -5479,11 +5483,11 @@
       </c>
       <c r="I66" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J66" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K66" s="2">
         <v>45295</v>
@@ -5522,11 +5526,11 @@
       </c>
       <c r="I67" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J67" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K67" s="7">
         <v>45295</v>
@@ -5565,11 +5569,11 @@
       </c>
       <c r="I68" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J68" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K68" s="7">
         <v>45295</v>
@@ -5589,7 +5593,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="69" spans="2:18" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:18" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="B69" t="s">
         <v>34</v>
       </c>
@@ -5615,7 +5619,7 @@
       </c>
       <c r="J69" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K69" s="7">
         <v>45324</v>
@@ -5663,7 +5667,7 @@
       </c>
       <c r="J70" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L70" s="4" t="str">
         <f t="shared" si="7"/>
@@ -5711,7 +5715,7 @@
       </c>
       <c r="J71" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L71" s="4" t="str">
         <f t="shared" si="7"/>
@@ -5759,7 +5763,7 @@
       </c>
       <c r="J72" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L72" s="4" t="str">
         <f t="shared" si="7"/>
@@ -5807,7 +5811,7 @@
       </c>
       <c r="J73" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L73" s="4" t="str">
         <f t="shared" si="7"/>
@@ -5855,7 +5859,7 @@
       </c>
       <c r="J74" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L74" s="4" t="str">
         <f t="shared" si="7"/>
@@ -5903,7 +5907,7 @@
       </c>
       <c r="J75" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L75" s="4" t="str">
         <f t="shared" si="7"/>
@@ -5951,7 +5955,7 @@
       </c>
       <c r="J76" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L76" s="4" t="str">
         <f t="shared" si="7"/>
@@ -5999,7 +6003,7 @@
       </c>
       <c r="J77" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L77" s="4" t="str">
         <f t="shared" si="7"/>
@@ -6047,7 +6051,7 @@
       </c>
       <c r="J78" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L78" s="4" t="str">
         <f t="shared" si="7"/>
@@ -6095,7 +6099,7 @@
       </c>
       <c r="J79" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L79" s="4" t="str">
         <f t="shared" si="7"/>
@@ -6143,7 +6147,7 @@
       </c>
       <c r="J80" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L80" s="4" t="str">
         <f t="shared" si="7"/>
@@ -6191,7 +6195,7 @@
       </c>
       <c r="J81" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L81" s="4" t="str">
         <f t="shared" si="7"/>
@@ -6239,7 +6243,7 @@
       </c>
       <c r="J82" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L82" s="4" t="str">
         <f t="shared" si="7"/>
@@ -6287,7 +6291,7 @@
       </c>
       <c r="J83" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L83" s="4" t="str">
         <f t="shared" si="7"/>
@@ -6335,7 +6339,7 @@
       </c>
       <c r="J84" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L84" s="4" t="str">
         <f t="shared" si="7"/>
@@ -6383,7 +6387,7 @@
       </c>
       <c r="J85" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L85" s="4" t="str">
         <f t="shared" si="7"/>
@@ -6431,7 +6435,7 @@
       </c>
       <c r="J86" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L86" s="4" t="str">
         <f t="shared" si="7"/>
@@ -6479,7 +6483,7 @@
       </c>
       <c r="J87" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L87" s="4" t="str">
         <f t="shared" si="7"/>
@@ -6527,7 +6531,7 @@
       </c>
       <c r="J88" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L88" s="4" t="str">
         <f t="shared" si="7"/>
@@ -6575,7 +6579,7 @@
       </c>
       <c r="J89" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L89" s="4" t="str">
         <f t="shared" si="7"/>
@@ -6623,7 +6627,7 @@
       </c>
       <c r="J90" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K90" s="2">
         <v>45272</v>
@@ -6671,7 +6675,7 @@
       </c>
       <c r="J91" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K91" s="2">
         <v>45273</v>
@@ -6719,7 +6723,7 @@
       </c>
       <c r="J92" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K92" s="2">
         <v>45274</v>
@@ -6767,7 +6771,7 @@
       </c>
       <c r="J93" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K93" s="2">
         <v>45275</v>
@@ -6815,7 +6819,7 @@
       </c>
       <c r="J94" s="4">
         <f t="shared" ca="1" si="11"/>
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K94" s="2">
         <v>45276</v>
@@ -6863,7 +6867,7 @@
       </c>
       <c r="J95" s="4">
         <f t="shared" ref="J95:J96" ca="1" si="17">IF(_xlfn.DAYS(TODAY(),H95)&lt;10000, _xlfn.DAYS(TODAY(),H95), "-")</f>
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K95" s="2">
         <v>45277</v>
@@ -6911,7 +6915,7 @@
       </c>
       <c r="J96" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K96" s="2">
         <v>45278</v>
@@ -6959,7 +6963,7 @@
       </c>
       <c r="J97" s="4">
         <f t="shared" ref="J97" ca="1" si="19">IF(_xlfn.DAYS(TODAY(),H97)&lt;10000, _xlfn.DAYS(TODAY(),H97), "-")</f>
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K97" s="2">
         <v>45223</v>
@@ -7007,7 +7011,7 @@
       </c>
       <c r="J98" s="4">
         <f t="shared" ref="J98:J120" ca="1" si="21">IF(_xlfn.DAYS(TODAY(),H98)&lt;10000, _xlfn.DAYS(TODAY(),H98), "-")</f>
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K98" s="2">
         <v>45223</v>
@@ -7055,7 +7059,7 @@
       </c>
       <c r="J99" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K99" s="2">
         <v>45223</v>
@@ -7103,7 +7107,7 @@
       </c>
       <c r="J100" s="4">
         <f t="shared" ca="1" si="21"/>
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K100" s="2">
         <v>45223</v>
@@ -7151,7 +7155,7 @@
       </c>
       <c r="J101" s="4">
         <f t="shared" ref="J101:J110" ca="1" si="24">IF(_xlfn.DAYS(TODAY(),H101)&lt;10000, _xlfn.DAYS(TODAY(),H101), "-")</f>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K101" s="2">
         <v>45267</v>
@@ -7202,7 +7206,7 @@
       </c>
       <c r="J102" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K102" s="2">
         <v>45267</v>
@@ -7253,7 +7257,7 @@
       </c>
       <c r="J103" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K103" s="2">
         <v>45267</v>
@@ -7304,7 +7308,7 @@
       </c>
       <c r="J104" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K104" s="2">
         <v>45267</v>
@@ -7355,7 +7359,7 @@
       </c>
       <c r="J105" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K105" s="2">
         <v>45267</v>
@@ -7406,7 +7410,7 @@
       </c>
       <c r="J106" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K106" s="2">
         <v>45267</v>
@@ -7457,7 +7461,7 @@
       </c>
       <c r="J107" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K107" s="2">
         <v>45267</v>
@@ -7508,7 +7512,7 @@
       </c>
       <c r="J108" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K108" s="2">
         <v>45267</v>
@@ -7559,7 +7563,7 @@
       </c>
       <c r="J109" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K109" s="2">
         <v>45267</v>
@@ -7610,7 +7614,7 @@
       </c>
       <c r="J110" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K110" s="2">
         <v>45267</v>
@@ -8132,7 +8136,7 @@
       </c>
       <c r="J123" s="4">
         <f t="shared" ca="1" si="26"/>
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K123" s="2">
         <v>45315</v>
@@ -8177,7 +8181,7 @@
       </c>
       <c r="J124" s="4">
         <f t="shared" ca="1" si="26"/>
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K124" s="2">
         <v>45315</v>
@@ -8222,7 +8226,7 @@
       </c>
       <c r="J125" s="4">
         <f t="shared" ca="1" si="26"/>
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K125" s="2">
         <v>45315</v>
@@ -8263,11 +8267,11 @@
       </c>
       <c r="I126" s="4">
         <f t="shared" ca="1" si="25"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J126" s="4">
         <f t="shared" ca="1" si="26"/>
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L126" s="4" t="str">
         <f t="shared" si="22"/>
@@ -8284,7 +8288,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="127" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B127" t="s">
         <v>5</v>
       </c>
@@ -8325,7 +8329,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="128" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B128" t="s">
         <v>100</v>
       </c>
@@ -8349,11 +8353,11 @@
       </c>
       <c r="I128" s="4">
         <f t="shared" ref="I128:I129" ca="1" si="27">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H128), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H128), 7), "-")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J128" s="4">
         <f t="shared" ref="J128:J129" ca="1" si="28">IF(_xlfn.DAYS(TODAY(),H128)&lt;10000, _xlfn.DAYS(TODAY(),H128), "-")</f>
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L128" s="4" t="str">
         <f t="shared" si="22"/>
@@ -8392,11 +8396,11 @@
       </c>
       <c r="I129" s="4">
         <f t="shared" ca="1" si="27"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J129" s="4">
         <f t="shared" ca="1" si="28"/>
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L129" s="4" t="str">
         <f t="shared" si="22"/>
@@ -8413,7 +8417,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="130" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B130" t="s">
         <v>5</v>
       </c>
@@ -8447,7 +8451,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="131" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B131" t="s">
         <v>101</v>
       </c>
@@ -8471,11 +8475,11 @@
       </c>
       <c r="I131" s="4">
         <f t="shared" ref="I131:I134" ca="1" si="29">IF(QUOTIENT(_xlfn.DAYS(TODAY(),H131), 7)&lt;1000, QUOTIENT(_xlfn.DAYS(TODAY(),H131), 7), "-")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J131" s="4">
         <f t="shared" ref="J131:J134" ca="1" si="30">IF(_xlfn.DAYS(TODAY(),H131)&lt;10000, _xlfn.DAYS(TODAY(),H131), "-")</f>
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L131" s="4" t="str">
         <f t="shared" si="22"/>
@@ -8489,7 +8493,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="132" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B132" t="s">
         <v>101</v>
       </c>
@@ -8513,11 +8517,11 @@
       </c>
       <c r="I132" s="4">
         <f t="shared" ca="1" si="29"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J132" s="4">
         <f t="shared" ca="1" si="30"/>
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L132" s="4" t="str">
         <f t="shared" si="22"/>
@@ -8531,7 +8535,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="133" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B133" t="s">
         <v>5</v>
       </c>
@@ -8549,11 +8553,11 @@
       </c>
       <c r="I133" s="4">
         <f t="shared" ca="1" si="29"/>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J133" s="4">
         <f t="shared" ca="1" si="30"/>
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L133" s="4" t="str">
         <f t="shared" si="22"/>
@@ -8567,7 +8571,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="134" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B134" t="s">
         <v>101</v>
       </c>
@@ -8591,11 +8595,11 @@
       </c>
       <c r="I134" s="4">
         <f t="shared" ca="1" si="29"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J134" s="4">
         <f t="shared" ca="1" si="30"/>
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L134" s="4" t="str">
         <f t="shared" si="22"/>
@@ -8609,7 +8613,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="135" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B135" t="s">
         <v>5</v>
       </c>
@@ -8653,7 +8657,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="136" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B136" t="s">
         <v>5</v>
       </c>
@@ -8705,7 +8709,7 @@
       </c>
       <c r="J137" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="L137" s="4" t="str">
         <f t="shared" si="33"/>
@@ -8741,7 +8745,7 @@
       </c>
       <c r="J138" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="L138" s="4" t="str">
         <f t="shared" si="33"/>
@@ -8777,7 +8781,7 @@
       </c>
       <c r="J139" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="L139" s="4" t="str">
         <f t="shared" si="33"/>
@@ -8813,7 +8817,7 @@
       </c>
       <c r="J140" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="L140" s="4" t="str">
         <f t="shared" si="33"/>
@@ -8860,7 +8864,7 @@
       </c>
       <c r="P141"/>
     </row>
-    <row r="142" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B142" t="s">
         <v>126</v>
       </c>
@@ -8888,7 +8892,7 @@
       </c>
       <c r="J142" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L142" s="4" t="str">
         <f t="shared" si="33"/>
@@ -8927,7 +8931,7 @@
       </c>
       <c r="J143" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L143" s="4" t="str">
         <f t="shared" si="33"/>
@@ -8974,7 +8978,7 @@
       </c>
       <c r="J144" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L144" s="4" t="str">
         <f t="shared" si="33"/>
@@ -9021,7 +9025,7 @@
       </c>
       <c r="J145" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L145" s="4" t="str">
         <f t="shared" si="33"/>
@@ -9068,7 +9072,7 @@
       </c>
       <c r="J146" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L146" s="4" t="str">
         <f t="shared" si="33"/>
@@ -9110,7 +9114,7 @@
       </c>
       <c r="J147" s="4">
         <f t="shared" ca="1" si="32"/>
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L147" s="4" t="str">
         <f t="shared" si="33"/>
@@ -9256,7 +9260,7 @@
       </c>
       <c r="J151" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L151" s="4" t="str">
         <f t="shared" si="36"/>
@@ -9303,7 +9307,7 @@
       </c>
       <c r="J152" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L152" s="4" t="str">
         <f t="shared" si="36"/>
@@ -9345,7 +9349,7 @@
       </c>
       <c r="J153" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L153" s="4" t="str">
         <f t="shared" si="36"/>
@@ -9387,7 +9391,7 @@
       </c>
       <c r="J154" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L154" s="4" t="str">
         <f t="shared" si="36"/>
@@ -9429,7 +9433,7 @@
       </c>
       <c r="J155" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L155" s="4" t="str">
         <f t="shared" si="36"/>
@@ -9448,7 +9452,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="156" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B156" t="s">
         <v>126</v>
       </c>
@@ -9476,7 +9480,7 @@
       </c>
       <c r="J156" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L156" s="4" t="str">
         <f t="shared" si="36"/>
@@ -9515,7 +9519,7 @@
       </c>
       <c r="J157" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L157" s="4" t="str">
         <f t="shared" si="36"/>
@@ -9571,7 +9575,7 @@
       </c>
       <c r="P158"/>
     </row>
-    <row r="159" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B159" t="s">
         <v>5</v>
       </c>
@@ -9601,7 +9605,7 @@
       </c>
       <c r="P159"/>
     </row>
-    <row r="160" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B160" t="s">
         <v>126</v>
       </c>
@@ -9634,7 +9638,7 @@
       </c>
       <c r="P160"/>
     </row>
-    <row r="161" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B161" t="s">
         <v>5</v>
       </c>
@@ -9664,7 +9668,7 @@
       </c>
       <c r="P161"/>
     </row>
-    <row r="162" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B162" t="s">
         <v>126</v>
       </c>
@@ -9692,7 +9696,7 @@
       </c>
       <c r="J162" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K162" s="2">
         <v>45301</v>
@@ -9706,7 +9710,7 @@
       </c>
       <c r="P162"/>
     </row>
-    <row r="163" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B163" t="s">
         <v>5</v>
       </c>
@@ -9736,7 +9740,7 @@
       </c>
       <c r="P163"/>
     </row>
-    <row r="164" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B164" t="s">
         <v>126</v>
       </c>
@@ -9764,7 +9768,7 @@
       </c>
       <c r="J164" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K164" s="2">
         <v>45301</v>
@@ -9803,7 +9807,7 @@
       </c>
       <c r="J165" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K165" s="2">
         <v>45301</v>
@@ -9820,7 +9824,7 @@
       </c>
       <c r="P165"/>
     </row>
-    <row r="166" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B166" t="s">
         <v>126</v>
       </c>
@@ -9848,7 +9852,7 @@
       </c>
       <c r="J166" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K166" s="2">
         <v>45301</v>
@@ -9890,7 +9894,7 @@
       </c>
       <c r="J167" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K167" s="2">
         <v>45301</v>
@@ -9941,7 +9945,7 @@
       </c>
       <c r="J168" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K168" s="2">
         <v>45301</v>
@@ -9983,7 +9987,7 @@
       </c>
       <c r="J169" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L169" s="4" t="str">
         <f t="shared" si="36"/>
@@ -10028,7 +10032,7 @@
       </c>
       <c r="J170" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L170" s="4" t="str">
         <f t="shared" si="36"/>
@@ -10076,7 +10080,7 @@
       </c>
       <c r="J171" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L171" s="4" t="str">
         <f t="shared" si="36"/>
@@ -10126,7 +10130,7 @@
       </c>
       <c r="J172" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K172" s="2">
         <v>45301</v>
@@ -10148,7 +10152,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="173" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B173" t="s">
         <v>5</v>
       </c>
@@ -10176,7 +10180,7 @@
       </c>
       <c r="J173" s="4">
         <f t="shared" ref="J173:J174" ca="1" si="41">IF(_xlfn.DAYS(TODAY(),H173)&lt;10000, _xlfn.DAYS(TODAY(),H173), "-")</f>
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L173" s="4" t="str">
         <f t="shared" ref="L173:L174" si="42">IF(_xlfn.DAYS(K173,H173)&gt;0, _xlfn.DAYS(K173,H173), "-")</f>
@@ -10187,7 +10191,7 @@
       </c>
       <c r="P173"/>
     </row>
-    <row r="174" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B174" t="s">
         <v>5</v>
       </c>
@@ -10220,7 +10224,7 @@
       </c>
       <c r="P174"/>
     </row>
-    <row r="175" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B175" t="s">
         <v>126</v>
       </c>
@@ -10248,7 +10252,7 @@
       </c>
       <c r="J175" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K175" s="2">
         <v>45301</v>
@@ -10290,7 +10294,7 @@
       </c>
       <c r="J176" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K176" s="2">
         <v>45301</v>
@@ -10343,7 +10347,7 @@
       </c>
       <c r="J177" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K177" s="2">
         <v>45301</v>
@@ -10396,7 +10400,7 @@
       </c>
       <c r="J178" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K178" s="2">
         <v>45301</v>
@@ -10449,7 +10453,7 @@
       </c>
       <c r="J179" s="4">
         <f t="shared" ca="1" si="35"/>
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L179" s="4" t="str">
         <f t="shared" si="36"/>
@@ -10499,7 +10503,7 @@
       </c>
       <c r="J180" s="4">
         <f t="shared" ref="J180:J189" ca="1" si="44">IF(_xlfn.DAYS(TODAY(),H180)&lt;10000, _xlfn.DAYS(TODAY(),H180), "-")</f>
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K180" s="7">
         <v>45324</v>
@@ -10549,7 +10553,7 @@
       </c>
       <c r="J181" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K181" s="7">
         <v>45324</v>
@@ -10599,7 +10603,7 @@
       </c>
       <c r="J182" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K182" s="7">
         <v>45324</v>
@@ -10649,7 +10653,7 @@
       </c>
       <c r="J183" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K183" s="7">
         <v>45324</v>
@@ -10699,7 +10703,7 @@
       </c>
       <c r="J184" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K184" s="7">
         <v>45324</v>
@@ -10749,7 +10753,7 @@
       </c>
       <c r="J185" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K185" s="7">
         <v>45324</v>
@@ -10771,7 +10775,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="186" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="186" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B186" t="s">
         <v>160</v>
       </c>
@@ -10796,7 +10800,7 @@
       </c>
       <c r="J186" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K186" s="2">
         <v>45357</v>
@@ -10809,7 +10813,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="187" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B187" t="s">
         <v>5</v>
       </c>
@@ -10838,7 +10842,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="188" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B188" t="s">
         <v>5</v>
       </c>
@@ -10860,7 +10864,7 @@
       </c>
       <c r="J188" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L188" s="4" t="str">
         <f t="shared" si="48"/>
@@ -10870,7 +10874,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="189" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B189" t="s">
         <v>5</v>
       </c>
@@ -10892,7 +10896,7 @@
       </c>
       <c r="J189" s="4">
         <f t="shared" ca="1" si="44"/>
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L189" s="4" t="str">
         <f t="shared" si="48"/>
@@ -10909,7 +10913,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="190" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B190" t="s">
         <v>5</v>
       </c>
@@ -10931,7 +10935,7 @@
       </c>
       <c r="J190" s="4">
         <f t="shared" ref="J190:J194" ca="1" si="50">IF(_xlfn.DAYS(TODAY(),H190)&lt;10000, _xlfn.DAYS(TODAY(),H190), "-")</f>
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L190" s="4" t="str">
         <f t="shared" ref="L190:L194" si="51">IF(_xlfn.DAYS(K190,H190)&gt;0, _xlfn.DAYS(K190,H190), "-")</f>
@@ -10948,7 +10952,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="191" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B191" t="s">
         <v>5</v>
       </c>
@@ -10970,7 +10974,7 @@
       </c>
       <c r="J191" s="4">
         <f t="shared" ca="1" si="50"/>
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L191" s="4" t="str">
         <f t="shared" si="51"/>
@@ -10987,7 +10991,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="192" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B192" t="s">
         <v>5</v>
       </c>
@@ -11009,7 +11013,7 @@
       </c>
       <c r="J192" s="4">
         <f t="shared" ca="1" si="50"/>
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L192" s="4" t="str">
         <f t="shared" si="51"/>
@@ -11026,7 +11030,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="193" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B193" t="s">
         <v>5</v>
       </c>
@@ -11048,7 +11052,7 @@
       </c>
       <c r="J193" s="4">
         <f t="shared" ca="1" si="50"/>
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L193" s="4" t="str">
         <f t="shared" si="51"/>
@@ -11065,7 +11069,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="194" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B194" t="s">
         <v>5</v>
       </c>
@@ -11087,7 +11091,7 @@
       </c>
       <c r="J194" s="4">
         <f t="shared" ca="1" si="50"/>
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L194" s="4" t="str">
         <f t="shared" si="51"/>
@@ -11104,7 +11108,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="195" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B195" t="s">
         <v>164</v>
       </c>
@@ -11140,7 +11144,7 @@
       </c>
       <c r="P195"/>
     </row>
-    <row r="196" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B196" t="s">
         <v>164</v>
       </c>
@@ -11179,7 +11183,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="197" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B197" t="s">
         <v>164</v>
       </c>
@@ -11215,7 +11219,7 @@
       </c>
       <c r="P197"/>
     </row>
-    <row r="198" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B198" t="s">
         <v>164</v>
       </c>
@@ -11251,7 +11255,7 @@
       </c>
       <c r="P198"/>
     </row>
-    <row r="199" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B199" t="s">
         <v>164</v>
       </c>
@@ -11287,7 +11291,7 @@
       </c>
       <c r="P199"/>
     </row>
-    <row r="200" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B200" t="s">
         <v>164</v>
       </c>
@@ -11354,7 +11358,7 @@
       </c>
       <c r="J201" s="4">
         <f t="shared" ref="J201" ca="1" si="56">IF(_xlfn.DAYS(TODAY(),H201)&lt;10000, _xlfn.DAYS(TODAY(),H201), "-")</f>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L201" s="4" t="str">
         <f t="shared" ref="L201" si="57">IF(_xlfn.DAYS(K201,H201)&gt;0, _xlfn.DAYS(K201,H201), "-")</f>
@@ -11402,7 +11406,7 @@
       </c>
       <c r="J202" s="4">
         <f t="shared" ref="J202:J216" ca="1" si="59">IF(_xlfn.DAYS(TODAY(),H202)&lt;10000, _xlfn.DAYS(TODAY(),H202), "-")</f>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L202" s="4" t="str">
         <f t="shared" ref="L202:L216" si="60">IF(_xlfn.DAYS(K202,H202)&gt;0, _xlfn.DAYS(K202,H202), "-")</f>
@@ -11450,7 +11454,7 @@
       </c>
       <c r="J203" s="4">
         <f t="shared" ca="1" si="59"/>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L203" s="4" t="str">
         <f t="shared" si="60"/>
@@ -11498,7 +11502,7 @@
       </c>
       <c r="J204" s="4">
         <f t="shared" ca="1" si="59"/>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L204" s="4" t="str">
         <f t="shared" si="60"/>
@@ -11546,7 +11550,7 @@
       </c>
       <c r="J205" s="4">
         <f t="shared" ca="1" si="59"/>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L205" s="4" t="str">
         <f t="shared" si="60"/>
@@ -11594,7 +11598,7 @@
       </c>
       <c r="J206" s="4">
         <f t="shared" ca="1" si="59"/>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L206" s="4" t="str">
         <f t="shared" si="60"/>
@@ -11642,7 +11646,7 @@
       </c>
       <c r="J207" s="4">
         <f t="shared" ca="1" si="59"/>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L207" s="4" t="str">
         <f t="shared" si="60"/>
@@ -11690,7 +11694,7 @@
       </c>
       <c r="J208" s="4">
         <f t="shared" ca="1" si="59"/>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L208" s="4" t="str">
         <f t="shared" si="60"/>
@@ -11738,7 +11742,7 @@
       </c>
       <c r="J209" s="4">
         <f t="shared" ca="1" si="59"/>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L209" s="4" t="str">
         <f t="shared" si="60"/>
@@ -11758,7 +11762,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="210" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B210" t="s">
         <v>5</v>
       </c>
@@ -11779,11 +11783,11 @@
       </c>
       <c r="I210" s="4">
         <f t="shared" ca="1" si="58"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J210" s="4">
         <f t="shared" ca="1" si="59"/>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K210" s="2">
         <v>45363</v>
@@ -11800,7 +11804,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="211" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B211" t="s">
         <v>5</v>
       </c>
@@ -11821,11 +11825,11 @@
       </c>
       <c r="I211" s="4">
         <f t="shared" ca="1" si="58"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J211" s="4">
         <f t="shared" ca="1" si="59"/>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K211" s="2">
         <v>45363</v>
@@ -11842,7 +11846,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="212" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B212" t="s">
         <v>5</v>
       </c>
@@ -11863,11 +11867,11 @@
       </c>
       <c r="I212" s="4">
         <f t="shared" ca="1" si="58"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J212" s="4">
         <f t="shared" ca="1" si="59"/>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K212" s="2">
         <v>45363</v>
@@ -11884,7 +11888,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="213" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B213" t="s">
         <v>5</v>
       </c>
@@ -11905,11 +11909,11 @@
       </c>
       <c r="I213" s="4">
         <f t="shared" ca="1" si="58"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J213" s="4">
         <f t="shared" ca="1" si="59"/>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K213" s="2">
         <v>45363</v>
@@ -11926,7 +11930,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="214" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B214" t="s">
         <v>5</v>
       </c>
@@ -11947,11 +11951,11 @@
       </c>
       <c r="I214" s="4">
         <f t="shared" ca="1" si="58"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J214" s="4">
         <f t="shared" ca="1" si="59"/>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K214" s="2">
         <v>45363</v>
@@ -11968,7 +11972,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="215" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B215" t="s">
         <v>5</v>
       </c>
@@ -11989,11 +11993,11 @@
       </c>
       <c r="I215" s="4">
         <f t="shared" ca="1" si="58"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J215" s="4">
         <f t="shared" ca="1" si="59"/>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K215" s="2">
         <v>45363</v>
@@ -12010,7 +12014,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="216" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B216" t="s">
         <v>5</v>
       </c>
@@ -12031,11 +12035,11 @@
       </c>
       <c r="I216" s="4">
         <f t="shared" ca="1" si="58"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J216" s="4">
         <f t="shared" ca="1" si="59"/>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K216" s="2">
         <v>45363</v>
@@ -12052,7 +12056,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="217" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B217" t="s">
         <v>5</v>
       </c>
@@ -12074,7 +12078,7 @@
       </c>
       <c r="J217" s="4">
         <f t="shared" ref="J217:J227" ca="1" si="62">IF(_xlfn.DAYS(TODAY(),H217)&lt;10000, _xlfn.DAYS(TODAY(),H217), "-")</f>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L217" s="4" t="str">
         <f t="shared" ref="L217:L227" si="63">IF(_xlfn.DAYS(K217,H217)&gt;0, _xlfn.DAYS(K217,H217), "-")</f>
@@ -12091,7 +12095,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="218" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B218" t="s">
         <v>5</v>
       </c>
@@ -12113,7 +12117,7 @@
       </c>
       <c r="J218" s="4">
         <f t="shared" ref="J218" ca="1" si="65">IF(_xlfn.DAYS(TODAY(),H218)&lt;10000, _xlfn.DAYS(TODAY(),H218), "-")</f>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L218" s="4" t="str">
         <f t="shared" ref="L218" si="66">IF(_xlfn.DAYS(K218,H218)&gt;0, _xlfn.DAYS(K218,H218), "-")</f>
@@ -12130,7 +12134,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="219" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B219" t="s">
         <v>5</v>
       </c>
@@ -12152,7 +12156,7 @@
       </c>
       <c r="J219" s="4">
         <f t="shared" ca="1" si="62"/>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L219" s="4" t="str">
         <f t="shared" si="63"/>
@@ -12169,7 +12173,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="220" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B220" t="s">
         <v>5</v>
       </c>
@@ -12191,7 +12195,7 @@
       </c>
       <c r="J220" s="4">
         <f t="shared" ca="1" si="62"/>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L220" s="4" t="str">
         <f t="shared" si="63"/>
@@ -12208,7 +12212,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="221" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B221" t="s">
         <v>5</v>
       </c>
@@ -12230,7 +12234,7 @@
       </c>
       <c r="J221" s="4">
         <f t="shared" ca="1" si="62"/>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L221" s="4" t="str">
         <f t="shared" si="63"/>
@@ -12247,7 +12251,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="222" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B222" t="s">
         <v>5</v>
       </c>
@@ -12269,7 +12273,7 @@
       </c>
       <c r="J222" s="4">
         <f t="shared" ca="1" si="62"/>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L222" s="4" t="str">
         <f t="shared" si="63"/>
@@ -12286,7 +12290,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="223" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B223" t="s">
         <v>5</v>
       </c>
@@ -12308,7 +12312,7 @@
       </c>
       <c r="J223" s="4">
         <f t="shared" ca="1" si="62"/>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L223" s="4" t="str">
         <f t="shared" si="63"/>
@@ -12325,7 +12329,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="224" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B224" t="s">
         <v>5</v>
       </c>
@@ -12343,11 +12347,11 @@
       </c>
       <c r="I224" s="4">
         <f t="shared" ca="1" si="61"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J224" s="4">
         <f t="shared" ca="1" si="62"/>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K224" s="2">
         <v>45363</v>
@@ -12367,7 +12371,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="225" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B225" t="s">
         <v>5</v>
       </c>
@@ -12385,11 +12389,11 @@
       </c>
       <c r="I225" s="4">
         <f t="shared" ca="1" si="61"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J225" s="4">
         <f t="shared" ca="1" si="62"/>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K225" s="2">
         <v>45363</v>
@@ -12409,7 +12413,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="226" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B226" t="s">
         <v>5</v>
       </c>
@@ -12427,11 +12431,11 @@
       </c>
       <c r="I226" s="4">
         <f t="shared" ca="1" si="61"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J226" s="4">
         <f t="shared" ca="1" si="62"/>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K226" s="2">
         <v>45363</v>
@@ -12451,7 +12455,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="227" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B227" t="s">
         <v>5</v>
       </c>
@@ -12470,7 +12474,7 @@
       </c>
       <c r="J227" s="4">
         <f t="shared" ca="1" si="62"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L227" s="4" t="str">
         <f t="shared" si="63"/>
@@ -12480,11 +12484,14 @@
         <v>200</v>
       </c>
       <c r="P227"/>
+      <c r="Q227" t="s">
+        <v>297</v>
+      </c>
       <c r="R227" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="228" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B228" t="s">
         <v>5</v>
       </c>
@@ -12503,7 +12510,7 @@
       </c>
       <c r="J228" s="4">
         <f t="shared" ref="J228:J235" ca="1" si="68">IF(_xlfn.DAYS(TODAY(),H228)&lt;10000, _xlfn.DAYS(TODAY(),H228), "-")</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L228" s="4" t="str">
         <f t="shared" ref="L228:L235" si="69">IF(_xlfn.DAYS(K228,H228)&gt;0, _xlfn.DAYS(K228,H228), "-")</f>
@@ -12513,11 +12520,14 @@
         <v>200</v>
       </c>
       <c r="P228"/>
+      <c r="Q228" t="s">
+        <v>297</v>
+      </c>
       <c r="R228" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="229" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B229" t="s">
         <v>5</v>
       </c>
@@ -12536,7 +12546,7 @@
       </c>
       <c r="J229" s="4">
         <f t="shared" ca="1" si="68"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L229" s="4" t="str">
         <f t="shared" si="69"/>
@@ -12546,11 +12556,14 @@
         <v>200</v>
       </c>
       <c r="P229"/>
+      <c r="Q229" t="s">
+        <v>297</v>
+      </c>
       <c r="R229" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="230" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B230" t="s">
         <v>5</v>
       </c>
@@ -12569,7 +12582,7 @@
       </c>
       <c r="J230" s="4">
         <f t="shared" ca="1" si="68"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L230" s="4" t="str">
         <f t="shared" si="69"/>
@@ -12579,11 +12592,14 @@
         <v>200</v>
       </c>
       <c r="P230"/>
+      <c r="Q230" t="s">
+        <v>297</v>
+      </c>
       <c r="R230" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="231" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="231" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B231" t="s">
         <v>34</v>
       </c>
@@ -12608,7 +12624,7 @@
       </c>
       <c r="J231" s="4">
         <f t="shared" ca="1" si="68"/>
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K231" s="2">
         <v>45357</v>
@@ -12621,7 +12637,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="232" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="232" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B232" t="s">
         <v>34</v>
       </c>
@@ -12646,7 +12662,7 @@
       </c>
       <c r="J232" s="4">
         <f t="shared" ca="1" si="68"/>
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K232" s="2">
         <v>45357</v>
@@ -12659,7 +12675,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="233" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="233" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B233" t="s">
         <v>34</v>
       </c>
@@ -12684,7 +12700,7 @@
       </c>
       <c r="J233" s="4">
         <f t="shared" ca="1" si="68"/>
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K233" s="2">
         <v>45357</v>
@@ -12697,7 +12713,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="234" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="234" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B234" t="s">
         <v>34</v>
       </c>
@@ -12722,7 +12738,7 @@
       </c>
       <c r="J234" s="4">
         <f t="shared" ca="1" si="68"/>
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K234" s="2">
         <v>45357</v>
@@ -12735,7 +12751,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="235" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="235" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B235" t="s">
         <v>34</v>
       </c>
@@ -12760,7 +12776,7 @@
       </c>
       <c r="J235" s="4">
         <f t="shared" ca="1" si="68"/>
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K235" s="2">
         <v>45357</v>
@@ -12803,7 +12819,7 @@
       </c>
       <c r="P236"/>
     </row>
-    <row r="237" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="237" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B237" t="s">
         <v>34</v>
       </c>
@@ -12825,7 +12841,7 @@
       </c>
       <c r="J237" s="4">
         <f t="shared" ref="J237" ca="1" si="71">IF(_xlfn.DAYS(TODAY(),H237)&lt;10000, _xlfn.DAYS(TODAY(),H237), "-")</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L237" s="4" t="str">
         <f t="shared" ref="L237" si="72">IF(_xlfn.DAYS(K237,H237)&gt;0, _xlfn.DAYS(K237,H237), "-")</f>
@@ -12838,7 +12854,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="238" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="238" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B238" t="s">
         <v>34</v>
       </c>
@@ -12860,7 +12876,7 @@
       </c>
       <c r="J238" s="4">
         <f t="shared" ref="J238" ca="1" si="74">IF(_xlfn.DAYS(TODAY(),H238)&lt;10000, _xlfn.DAYS(TODAY(),H238), "-")</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L238" s="4" t="str">
         <f t="shared" ref="L238" si="75">IF(_xlfn.DAYS(K238,H238)&gt;0, _xlfn.DAYS(K238,H238), "-")</f>
@@ -12873,7 +12889,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="239" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="239" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B239" t="s">
         <v>34</v>
       </c>
@@ -12895,7 +12911,7 @@
       </c>
       <c r="J239" s="4">
         <f t="shared" ref="J239:J241" ca="1" si="77">IF(_xlfn.DAYS(TODAY(),H239)&lt;10000, _xlfn.DAYS(TODAY(),H239), "-")</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L239" s="4" t="str">
         <f t="shared" ref="L239:L255" si="78">IF(_xlfn.DAYS(K239,H239)&gt;0, _xlfn.DAYS(K239,H239), "-")</f>
@@ -12908,7 +12924,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="240" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="240" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B240" t="s">
         <v>34</v>
       </c>
@@ -12930,7 +12946,7 @@
       </c>
       <c r="J240" s="4">
         <f t="shared" ca="1" si="77"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L240" s="4" t="str">
         <f t="shared" si="78"/>
@@ -12965,7 +12981,7 @@
       </c>
       <c r="J241" s="4">
         <f t="shared" ca="1" si="77"/>
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K241" s="2">
         <v>45350</v>
@@ -13009,7 +13025,7 @@
       </c>
       <c r="J242" s="4">
         <f t="shared" ref="J242:J255" ca="1" si="80">IF(_xlfn.DAYS(TODAY(),H242)&lt;10000, _xlfn.DAYS(TODAY(),H242), "-")</f>
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K242" s="2">
         <v>45350</v>
@@ -13053,7 +13069,7 @@
       </c>
       <c r="J243" s="4">
         <f t="shared" ca="1" si="80"/>
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K243" s="2">
         <v>45350</v>
@@ -13097,7 +13113,7 @@
       </c>
       <c r="J244" s="4">
         <f t="shared" ca="1" si="80"/>
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K244" s="2">
         <v>45350</v>
@@ -13141,7 +13157,7 @@
       </c>
       <c r="J245" s="4">
         <f t="shared" ca="1" si="80"/>
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K245" s="2">
         <v>45350</v>
@@ -13185,7 +13201,7 @@
       </c>
       <c r="J246" s="4">
         <f t="shared" ca="1" si="80"/>
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K246" s="2">
         <v>45350</v>
@@ -13229,7 +13245,7 @@
       </c>
       <c r="J247" s="4">
         <f t="shared" ca="1" si="80"/>
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K247" s="2">
         <v>45350</v>
@@ -13273,7 +13289,7 @@
       </c>
       <c r="J248" s="4">
         <f t="shared" ca="1" si="80"/>
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K248" s="2">
         <v>45350</v>
@@ -13317,7 +13333,7 @@
       </c>
       <c r="J249" s="4">
         <f t="shared" ca="1" si="80"/>
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K249" s="2">
         <v>45350</v>
@@ -13361,7 +13377,7 @@
       </c>
       <c r="J250" s="4">
         <f t="shared" ca="1" si="80"/>
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K250" s="2">
         <v>45350</v>
@@ -13405,7 +13421,7 @@
       </c>
       <c r="J251" s="4">
         <f t="shared" ca="1" si="80"/>
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K251" s="2">
         <v>45350</v>
@@ -13449,7 +13465,7 @@
       </c>
       <c r="J252" s="4">
         <f t="shared" ca="1" si="80"/>
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K252" s="2">
         <v>45350</v>
@@ -13493,7 +13509,7 @@
       </c>
       <c r="J253" s="4">
         <f t="shared" ca="1" si="80"/>
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K253" s="2">
         <v>45350</v>
@@ -13537,7 +13553,7 @@
       </c>
       <c r="J254" s="4">
         <f t="shared" ca="1" si="80"/>
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K254" s="2">
         <v>45350</v>
@@ -13581,7 +13597,7 @@
       </c>
       <c r="J255" s="4">
         <f t="shared" ca="1" si="80"/>
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K255" s="2">
         <v>45350</v>
@@ -13603,7 +13619,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="256" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B256" t="s">
         <v>5</v>
       </c>
@@ -13622,7 +13638,7 @@
       </c>
       <c r="J256" s="4">
         <f t="shared" ref="J256" ca="1" si="82">IF(_xlfn.DAYS(TODAY(),H256)&lt;10000, _xlfn.DAYS(TODAY(),H256), "-")</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L256" s="4" t="str">
         <f t="shared" ref="L256" si="83">IF(_xlfn.DAYS(K256,H256)&gt;0, _xlfn.DAYS(K256,H256), "-")</f>
@@ -13632,11 +13648,14 @@
         <v>235</v>
       </c>
       <c r="P256"/>
+      <c r="Q256" t="s">
+        <v>297</v>
+      </c>
       <c r="R256" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="257" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B257" t="s">
         <v>5</v>
       </c>
@@ -13655,7 +13674,7 @@
       </c>
       <c r="J257" s="4">
         <f t="shared" ref="J257:J266" ca="1" si="85">IF(_xlfn.DAYS(TODAY(),H257)&lt;10000, _xlfn.DAYS(TODAY(),H257), "-")</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L257" s="4" t="str">
         <f t="shared" ref="L257:L266" si="86">IF(_xlfn.DAYS(K257,H257)&gt;0, _xlfn.DAYS(K257,H257), "-")</f>
@@ -13664,11 +13683,14 @@
       <c r="M257" t="s">
         <v>235</v>
       </c>
+      <c r="Q257" t="s">
+        <v>297</v>
+      </c>
       <c r="R257" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="258" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B258" t="s">
         <v>5</v>
       </c>
@@ -13687,7 +13709,7 @@
       </c>
       <c r="J258" s="4">
         <f t="shared" ca="1" si="85"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L258" s="4" t="str">
         <f t="shared" si="86"/>
@@ -13696,11 +13718,14 @@
       <c r="M258" t="s">
         <v>235</v>
       </c>
+      <c r="Q258" t="s">
+        <v>297</v>
+      </c>
       <c r="R258" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="259" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B259" t="s">
         <v>5</v>
       </c>
@@ -13719,7 +13744,7 @@
       </c>
       <c r="J259" s="4">
         <f t="shared" ca="1" si="85"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L259" s="4" t="str">
         <f t="shared" si="86"/>
@@ -13728,11 +13753,14 @@
       <c r="M259" t="s">
         <v>235</v>
       </c>
+      <c r="Q259" t="s">
+        <v>297</v>
+      </c>
       <c r="R259" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="260" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B260" t="s">
         <v>5</v>
       </c>
@@ -13751,7 +13779,7 @@
       </c>
       <c r="J260" s="4">
         <f t="shared" ca="1" si="85"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L260" s="4" t="str">
         <f t="shared" si="86"/>
@@ -13760,11 +13788,14 @@
       <c r="M260" t="s">
         <v>235</v>
       </c>
+      <c r="Q260" t="s">
+        <v>297</v>
+      </c>
       <c r="R260" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="261" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B261" t="s">
         <v>5</v>
       </c>
@@ -13783,7 +13814,7 @@
       </c>
       <c r="J261" s="4">
         <f t="shared" ca="1" si="85"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L261" s="4" t="str">
         <f t="shared" si="86"/>
@@ -13792,11 +13823,14 @@
       <c r="M261" t="s">
         <v>235</v>
       </c>
+      <c r="Q261" t="s">
+        <v>297</v>
+      </c>
       <c r="R261" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="262" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B262" t="s">
         <v>5</v>
       </c>
@@ -13815,7 +13849,7 @@
       </c>
       <c r="J262" s="4">
         <f t="shared" ca="1" si="85"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L262" s="4" t="str">
         <f t="shared" si="86"/>
@@ -13824,11 +13858,14 @@
       <c r="M262" t="s">
         <v>235</v>
       </c>
+      <c r="Q262" t="s">
+        <v>297</v>
+      </c>
       <c r="R262" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="263" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B263" t="s">
         <v>5</v>
       </c>
@@ -13847,7 +13884,7 @@
       </c>
       <c r="J263" s="4">
         <f t="shared" ca="1" si="85"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L263" s="4" t="str">
         <f t="shared" si="86"/>
@@ -13856,11 +13893,14 @@
       <c r="M263" t="s">
         <v>235</v>
       </c>
+      <c r="Q263" t="s">
+        <v>297</v>
+      </c>
       <c r="R263" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="264" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B264" t="s">
         <v>5</v>
       </c>
@@ -13879,7 +13919,7 @@
       </c>
       <c r="J264" s="4">
         <f t="shared" ca="1" si="85"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L264" s="4" t="str">
         <f t="shared" si="86"/>
@@ -13888,11 +13928,14 @@
       <c r="M264" t="s">
         <v>235</v>
       </c>
+      <c r="Q264" t="s">
+        <v>297</v>
+      </c>
       <c r="R264" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="265" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B265" t="s">
         <v>290</v>
       </c>
@@ -13907,11 +13950,11 @@
       </c>
       <c r="I265" s="4">
         <f t="shared" ca="1" si="84"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J265" s="4">
         <f t="shared" ca="1" si="85"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L265" s="4" t="str">
         <f t="shared" si="86"/>
@@ -13927,7 +13970,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="266" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="266" spans="2:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="B266" t="s">
         <v>34</v>
       </c>
@@ -13949,7 +13992,7 @@
       </c>
       <c r="J266" s="4">
         <f t="shared" ca="1" si="85"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L266" s="4" t="str">
         <f t="shared" si="86"/>
@@ -13968,15 +14011,10 @@
       <c r="L267" s="4"/>
     </row>
   </sheetData>
-  <autoFilter ref="B1:R265" xr:uid="{8D08DEC4-803F-4130-9E5E-30A83401A29D}">
+  <autoFilter ref="B1:R266" xr:uid="{8D08DEC4-803F-4130-9E5E-30A83401A29D}">
     <filterColumn colId="0">
       <filters>
-        <filter val="5F"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="1">
-      <filters>
-        <filter val="Tmem119-CreERT2; Tsg101-flox"/>
+        <filter val="SPF"/>
       </filters>
     </filterColumn>
     <filterColumn colId="13">
